--- a/docs/99-output/MyERP_Requirements.xlsx
+++ b/docs/99-output/MyERP_Requirements.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="1" r:id="Rd09f965c24d64d03"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Non-Functional" sheetId="2" r:id="R28130cf33b0441f5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Structure" sheetId="3" r:id="R9da22aab04474969"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interface" sheetId="4" r:id="Rd96187b01b2b4156"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traceability Matrix" sheetId="5" r:id="Raa216fbb0c0d4389"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BlueWhale Parity" sheetId="6" r:id="R27fe8f4fb1384399"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timeline" sheetId="7" r:id="R696fb43c99fc4f86"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Human Resources" sheetId="8" r:id="R50903c79698a49d5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="9" r:id="Rfeef86984d0240f9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="1" r:id="Rabe41bf7717f4e80"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Non-Functional" sheetId="2" r:id="Rda7c6f4a20184ffe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Structure" sheetId="3" r:id="Re16b5cd029b34b05"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interface" sheetId="4" r:id="R72c46644c32d4bbd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traceability Matrix" sheetId="5" r:id="R453413c11d6c490b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BlueWhale Parity" sheetId="6" r:id="R9282c6cf18324053"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timeline" sheetId="7" r:id="R077f9d7df3654734"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Human Resources" sheetId="8" r:id="R1941daa04f184713"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="9" r:id="R3156f4f4a97941f0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -63,12 +63,12 @@
   <x:cols>
     <x:col min="1" max="1" width="16" customWidth="1"/>
     <x:col min="2" max="2" width="10" customWidth="1"/>
-    <x:col min="3" max="3" width="14" customWidth="1"/>
+    <x:col min="3" max="3" width="23" customWidth="1"/>
     <x:col min="4" max="4" width="10" customWidth="1"/>
-    <x:col min="5" max="5" width="13" customWidth="1"/>
-    <x:col min="6" max="6" width="10" customWidth="1"/>
-    <x:col min="7" max="7" width="21" customWidth="1"/>
-    <x:col min="8" max="8" width="10" customWidth="1"/>
+    <x:col min="5" max="5" width="60" customWidth="1"/>
+    <x:col min="6" max="6" width="11" customWidth="1"/>
+    <x:col min="7" max="7" width="30" customWidth="1"/>
+    <x:col min="8" max="8" width="40" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -110,6 +110,426 @@
       <x:c r="H1" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Source</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.20.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B2" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C2" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Company Management</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D2" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E2" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow authorized users to view company details.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F2" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G2" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">僅有組織檢視權的用戶可見其獲授權公司；無權限回 403。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H2" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:13</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.20.2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B3" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C3" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Company Management</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D3" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E3" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow authorized users to create a company.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F3" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G3" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">代碼全系統唯一；代碼與名稱必填；重複代碼回 409。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H3" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:14</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.20.3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B4" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C4" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Company Management</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D4" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E4" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow authorized users to edit a company.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F4" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G4" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">版本不符回 409；審計欄位記錄修改者。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H4" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:15</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.20.4</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B5" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C5" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Company Management</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D5" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E5" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow authorized users to deactivate a company.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F5" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G5" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">停用後不能成為新操作的公司上下文；歷史資料保留。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H5" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:16</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.21.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B6" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C6" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Branch Management</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D6" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E6" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow authorized users to view branches in the selected company.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F6" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G6" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">公司 A 的查詢不返回公司 B 分店；未選公司結果為空。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H6" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:17</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.21.2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B7" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C7" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Branch Management</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D7" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E7" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow authorized users to create a branch.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F7" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G7" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">公司內代碼唯一；所屬公司必須為授權公司。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H7" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:18</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.21.3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B8" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C8" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Branch Management</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D8" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E8" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow authorized users to edit or deactivate a branch.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F8" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G8" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">版本不符回 409；被引用時只可停用，不得刪除。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H8" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:19</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.22.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B9" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C9" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Department Management</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D9" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E9" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow authorized users to view departments in the selected company.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F9" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G9" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">公司隔離、軟刪除篩選生效。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H9" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:20</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.22.2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B10" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C10" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Department Management</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D10" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E10" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow authorized users to create a department under a branch or parent department.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F10" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G10" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">分店與上級部門必須屬於同一公司；不得循環參照。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H10" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:21</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.22.3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B11" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C11" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Department Management</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D11" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E11" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow authorized users to edit or deactivate a department.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F11" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G11" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">版本不符回 409；被引用時只可停用。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H11" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:22</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -1054,10 +1474,10 @@
   <x:cols>
     <x:col min="1" max="1" width="16" customWidth="1"/>
     <x:col min="2" max="2" width="10" customWidth="1"/>
-    <x:col min="3" max="3" width="12" customWidth="1"/>
-    <x:col min="4" max="4" width="13" customWidth="1"/>
-    <x:col min="5" max="5" width="10" customWidth="1"/>
-    <x:col min="6" max="6" width="15" customWidth="1"/>
+    <x:col min="3" max="3" width="16" customWidth="1"/>
+    <x:col min="4" max="4" width="60" customWidth="1"/>
+    <x:col min="5" max="5" width="11" customWidth="1"/>
+    <x:col min="6" max="6" width="60" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -1089,6 +1509,102 @@
       <x:c r="F1" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Related REQ_F</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.20</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B2" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C2" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">sys_company</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D2" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Company isolation root; globally unique code, audit, version and soft deletion.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E2" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F2" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.20.1, REQ_F4118.20.2, REQ_F4118.20.3, REQ_F4118.20.4</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.22</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B3" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C3" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">sys_department</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D3" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Department master scoped to a company, optionally linked to a branch and parent department.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E3" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F3" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.22.1, REQ_F4118.22.2, REQ_F4118.22.3</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.89</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B4" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C4" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">sys_branch</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D4" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Branch master scoped to a company.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E4" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F4" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.21.1, REQ_F4118.21.2, REQ_F4118.21.3</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -1101,15 +1617,15 @@
   <x:cols>
     <x:col min="1" max="1" width="16" customWidth="1"/>
     <x:col min="2" max="2" width="15" customWidth="1"/>
-    <x:col min="3" max="3" width="11" customWidth="1"/>
-    <x:col min="4" max="4" width="10" customWidth="1"/>
+    <x:col min="3" max="3" width="27" customWidth="1"/>
+    <x:col min="4" max="4" width="30" customWidth="1"/>
     <x:col min="5" max="5" width="13" customWidth="1"/>
     <x:col min="6" max="6" width="10" customWidth="1"/>
-    <x:col min="7" max="7" width="10" customWidth="1"/>
+    <x:col min="7" max="7" width="15" customWidth="1"/>
     <x:col min="8" max="8" width="13" customWidth="1"/>
     <x:col min="9" max="9" width="13" customWidth="1"/>
     <x:col min="10" max="10" width="10" customWidth="1"/>
-    <x:col min="11" max="11" width="10" customWidth="1"/>
+    <x:col min="11" max="11" width="11" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -1166,6 +1682,291 @@
       <x:c r="K1" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Author</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.58.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B2" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.58</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C2" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Company View Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D2" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Company Code (Input)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E2" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">公司代碼</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F2" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">唯一識別公司</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G2" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">VARCHAR(30)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H2" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1–30 字元</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I2" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J2" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K2" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.58.2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B3" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.58</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C3" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Company View Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D3" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Company Name (Input)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E3" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">公司名稱</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F3" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">顯示公司</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G3" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">NVARCHAR(200)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H3" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1–200 字元</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I3" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J3" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K3" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.59.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B4" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.59</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C4" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Branch View Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D4" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Branch Code (Input)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E4" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">分店代碼</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F4" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">公司內唯一</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G4" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">VARCHAR(30)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H4" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1–30 字元</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I4" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J4" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K4" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.60.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B5" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.60</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C5" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Department View Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D5" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Department Code (Input)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E5" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">部門代碼</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F5" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">公司內唯一</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G5" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">VARCHAR(30)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H5" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1–30 字元</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I5" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J5" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K5" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.60.2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B6" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.60</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C6" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Department View Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D6" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Parent Department (Dropdown)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E6" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">上級部門</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F6" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">建立層級</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G6" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">bigint ID</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H6" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">同公司啟用部門</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I6" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J6" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K6" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -1176,12 +1977,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:cols>
-    <x:col min="1" max="1" width="10" customWidth="1"/>
-    <x:col min="2" max="2" width="13" customWidth="1"/>
-    <x:col min="3" max="3" width="10" customWidth="1"/>
+    <x:col min="1" max="1" width="16" customWidth="1"/>
+    <x:col min="2" max="2" width="60" customWidth="1"/>
+    <x:col min="3" max="3" width="13" customWidth="1"/>
     <x:col min="4" max="4" width="12" customWidth="1"/>
-    <x:col min="5" max="5" width="10" customWidth="1"/>
-    <x:col min="6" max="6" width="12" customWidth="1"/>
+    <x:col min="5" max="5" width="32" customWidth="1"/>
+    <x:col min="6" max="6" width="26" customWidth="1"/>
     <x:col min="7" max="7" width="10" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -1219,6 +2020,376 @@
       <x:c r="G1" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Coverage</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.20.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B2" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow authorized users to view company details.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C2" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.20</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D2" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.58</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E2" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F2" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-ORG-004</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G2" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Covered</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.20.2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B3" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow authorized users to create a company.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C3" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.20</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D3" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.58</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E3" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.58.1, REQ_IO_A8.58.2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F3" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-ORG-001</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G3" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Covered</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.20.3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B4" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow authorized users to edit a company.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C4" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.20</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D4" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.58</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E4" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F4" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-ORG-005</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G4" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Covered</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.20.4</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B5" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow authorized users to deactivate a company.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C5" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.20</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D5" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.58</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E5" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F5" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-ORG-006</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G5" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Covered</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.21.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B6" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow authorized users to view branches in the selected company.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C6" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.89</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D6" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.59</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E6" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F6" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-ORG-002, SYS-ORG-004</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G6" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Covered</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.21.2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B7" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow authorized users to create a branch.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C7" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.89</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D7" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.59</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E7" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.59.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F7" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-ORG-001</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G7" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Covered</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.21.3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B8" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow authorized users to edit or deactivate a branch.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C8" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.89</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D8" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.59</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E8" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F8" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-ORG-005</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G8" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Covered</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.22.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B9" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow authorized users to view departments in the selected company.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C9" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.22</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D9" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.60</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E9" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F9" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-ORG-002, SYS-ORG-004</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G9" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Covered</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.22.2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B10" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow authorized users to create a department under a branch or parent department.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C10" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.22</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D10" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.60</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E10" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.60.1, REQ_IO_A8.60.2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F10" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-ORG-001, SYS-ORG-003</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G10" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Covered</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.22.3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B11" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow authorized users to edit or deactivate a department.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C11" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.22</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D11" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.60</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E11" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F11" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-ORG-005</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G11" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -13809,7 +14980,7 @@
       </x:c>
       <x:c r="F393" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">未開始</x:t>
+          <x:t xml:space="preserve">進行中</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -13873,7 +15044,7 @@
       </x:c>
       <x:c r="F395" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">未開始</x:t>
+          <x:t xml:space="preserve">進行中</x:t>
         </x:is>
       </x:c>
     </x:row>

--- a/docs/99-output/MyERP_Requirements.xlsx
+++ b/docs/99-output/MyERP_Requirements.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="1" r:id="Rabe41bf7717f4e80"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Non-Functional" sheetId="2" r:id="Rda7c6f4a20184ffe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Structure" sheetId="3" r:id="Re16b5cd029b34b05"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interface" sheetId="4" r:id="R72c46644c32d4bbd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traceability Matrix" sheetId="5" r:id="R453413c11d6c490b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BlueWhale Parity" sheetId="6" r:id="R9282c6cf18324053"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timeline" sheetId="7" r:id="R077f9d7df3654734"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Human Resources" sheetId="8" r:id="R1941daa04f184713"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="9" r:id="R3156f4f4a97941f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="1" r:id="Rdd614df01d7d4a44"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Non-Functional" sheetId="2" r:id="Re9c235f08b0c4022"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Structure" sheetId="3" r:id="R6d55872db3594456"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interface" sheetId="4" r:id="Rf8e9e8ce6f984042"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traceability Matrix" sheetId="5" r:id="R6c9ba592a7fd4426"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BlueWhale Parity" sheetId="6" r:id="Rf75afa7538134e01"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timeline" sheetId="7" r:id="R751f0b4a99a24030"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Human Resources" sheetId="8" r:id="R4145721c8f8542ba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="9" r:id="Rbf5dd080ea04421f"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/docs/99-output/MyERP_Requirements.xlsx
+++ b/docs/99-output/MyERP_Requirements.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="1" r:id="Rdd614df01d7d4a44"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Non-Functional" sheetId="2" r:id="Re9c235f08b0c4022"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Structure" sheetId="3" r:id="R6d55872db3594456"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interface" sheetId="4" r:id="Rf8e9e8ce6f984042"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traceability Matrix" sheetId="5" r:id="R6c9ba592a7fd4426"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BlueWhale Parity" sheetId="6" r:id="Rf75afa7538134e01"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timeline" sheetId="7" r:id="R751f0b4a99a24030"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Human Resources" sheetId="8" r:id="R4145721c8f8542ba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="9" r:id="Rbf5dd080ea04421f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="1" r:id="Rad2996fbb9bd4b97"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Non-Functional" sheetId="2" r:id="R2ab50b8a7b04476e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Structure" sheetId="3" r:id="R4df1fc8b47744252"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interface" sheetId="4" r:id="R1e6cb695ed564486"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traceability Matrix" sheetId="5" r:id="Ra918025d32194f1a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BlueWhale Parity" sheetId="6" r:id="R4d38344d879b407f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timeline" sheetId="7" r:id="Rfebf2755ab0b44ad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Human Resources" sheetId="8" r:id="Rdb7cabb89e384a72"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="9" r:id="R319c32e0245a4886"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -67,7 +67,7 @@
     <x:col min="4" max="4" width="10" customWidth="1"/>
     <x:col min="5" max="5" width="60" customWidth="1"/>
     <x:col min="6" max="6" width="11" customWidth="1"/>
-    <x:col min="7" max="7" width="30" customWidth="1"/>
+    <x:col min="7" max="7" width="60" customWidth="1"/>
     <x:col min="8" max="8" width="40" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -173,7 +173,7 @@
       </x:c>
       <x:c r="D3" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1.0</x:t>
+          <x:t xml:space="preserve">1.1</x:t>
         </x:is>
       </x:c>
       <x:c r="E3" s="2" t="inlineStr">
@@ -188,7 +188,7 @@
       </x:c>
       <x:c r="G3" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">代碼全系統唯一；代碼與名稱必填；重複代碼回 409。</x:t>
+          <x:t xml:space="preserve">代碼全系統唯一；代碼與名稱必填；代碼限 1–30 字元的 ASCII 英文、數字、-、_，保存為大寫；重複代碼回 409。</x:t>
         </x:is>
       </x:c>
       <x:c r="H3" s="2" t="inlineStr">
@@ -1622,7 +1622,7 @@
     <x:col min="5" max="5" width="13" customWidth="1"/>
     <x:col min="6" max="6" width="10" customWidth="1"/>
     <x:col min="7" max="7" width="15" customWidth="1"/>
-    <x:col min="8" max="8" width="13" customWidth="1"/>
+    <x:col min="8" max="8" width="25" customWidth="1"/>
     <x:col min="9" max="9" width="13" customWidth="1"/>
     <x:col min="10" max="10" width="10" customWidth="1"/>
     <x:col min="11" max="11" width="11" customWidth="1"/>
@@ -1723,7 +1723,7 @@
       </x:c>
       <x:c r="H2" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1–30 字元</x:t>
+          <x:t xml:space="preserve">1–30 字元；ASCII 英文、數字、-、_</x:t>
         </x:is>
       </x:c>
       <x:c r="I2" s="2" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </x:c>
       <x:c r="H4" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1–30 字元</x:t>
+          <x:t xml:space="preserve">1–30 字元；ASCII 英文、數字、-、_</x:t>
         </x:is>
       </x:c>
       <x:c r="I4" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </x:c>
       <x:c r="H5" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1–30 字元</x:t>
+          <x:t xml:space="preserve">1–30 字元；ASCII 英文、數字、-、_</x:t>
         </x:is>
       </x:c>
       <x:c r="I5" s="2" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </x:c>
       <x:c r="F3" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-ORG-001</x:t>
+          <x:t xml:space="preserve">SYS-ORG-001, SYS-ORG-008</x:t>
         </x:is>
       </x:c>
       <x:c r="G3" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </x:c>
       <x:c r="F11" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-ORG-005</x:t>
+          <x:t xml:space="preserve">SYS-ORG-005, SYS-ORG-007</x:t>
         </x:is>
       </x:c>
       <x:c r="G11" s="2" t="inlineStr">

--- a/docs/99-output/MyERP_Requirements.xlsx
+++ b/docs/99-output/MyERP_Requirements.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="1" r:id="Rad2996fbb9bd4b97"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Non-Functional" sheetId="2" r:id="R2ab50b8a7b04476e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Structure" sheetId="3" r:id="R4df1fc8b47744252"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interface" sheetId="4" r:id="R1e6cb695ed564486"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traceability Matrix" sheetId="5" r:id="Ra918025d32194f1a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BlueWhale Parity" sheetId="6" r:id="R4d38344d879b407f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timeline" sheetId="7" r:id="Rfebf2755ab0b44ad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Human Resources" sheetId="8" r:id="Rdb7cabb89e384a72"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="9" r:id="R319c32e0245a4886"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="1" r:id="R4b87c127ccb54bf2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Non-Functional" sheetId="2" r:id="R98f00317b5264425"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Structure" sheetId="3" r:id="Rd991c3fa4a9546a0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interface" sheetId="4" r:id="Rac418e4833f54dea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traceability Matrix" sheetId="5" r:id="R1f0272cbc1b94f8a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BlueWhale Parity" sheetId="6" r:id="Rf1123e791a1f41c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timeline" sheetId="7" r:id="R50e16f7e0cee4e65"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Human Resources" sheetId="8" r:id="R1f4569a1d65b4ed0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="9" r:id="Rf35e4ffe47cb4d27"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1982,7 +1982,7 @@
     <x:col min="3" max="3" width="13" customWidth="1"/>
     <x:col min="4" max="4" width="12" customWidth="1"/>
     <x:col min="5" max="5" width="32" customWidth="1"/>
-    <x:col min="6" max="6" width="26" customWidth="1"/>
+    <x:col min="6" max="6" width="39" customWidth="1"/>
     <x:col min="7" max="7" width="10" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -2125,7 +2125,7 @@
       </x:c>
       <x:c r="F4" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-ORG-005</x:t>
+          <x:t xml:space="preserve">SYS-ORG-005, SYS-ORG-009</x:t>
         </x:is>
       </x:c>
       <x:c r="G4" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </x:c>
       <x:c r="F11" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-ORG-005, SYS-ORG-007</x:t>
+          <x:t xml:space="preserve">SYS-ORG-005, SYS-ORG-007, SYS-ORG-009</x:t>
         </x:is>
       </x:c>
       <x:c r="G11" s="2" t="inlineStr">

--- a/docs/99-output/MyERP_Requirements.xlsx
+++ b/docs/99-output/MyERP_Requirements.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="1" r:id="R4b87c127ccb54bf2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Non-Functional" sheetId="2" r:id="R98f00317b5264425"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Structure" sheetId="3" r:id="Rd991c3fa4a9546a0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interface" sheetId="4" r:id="Rac418e4833f54dea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traceability Matrix" sheetId="5" r:id="R1f0272cbc1b94f8a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BlueWhale Parity" sheetId="6" r:id="Rf1123e791a1f41c0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timeline" sheetId="7" r:id="R50e16f7e0cee4e65"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Human Resources" sheetId="8" r:id="R1f4569a1d65b4ed0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="9" r:id="Rf35e4ffe47cb4d27"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="1" r:id="R82bc1c13e09f4220"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Non-Functional" sheetId="2" r:id="R74bd908d2ee04eeb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Structure" sheetId="3" r:id="Rfdcc198f541a4440"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interface" sheetId="4" r:id="Ra7619d5ac1d545dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traceability Matrix" sheetId="5" r:id="Ra65783d7eaf64abf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BlueWhale Parity" sheetId="6" r:id="R19e42c6601e84ac3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timeline" sheetId="7" r:id="R5645b1bfd4364302"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Human Resources" sheetId="8" r:id="Rfc6a47f45613498c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="9" r:id="Rffb445f68d244ffc"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2199,7 +2199,7 @@
       </x:c>
       <x:c r="F6" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-ORG-002, SYS-ORG-004</x:t>
+          <x:t xml:space="preserve">SYS-ORG-002, SYS-ORG-004, SYS-ORG-010</x:t>
         </x:is>
       </x:c>
       <x:c r="G6" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </x:c>
       <x:c r="F9" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-ORG-002, SYS-ORG-004</x:t>
+          <x:t xml:space="preserve">SYS-ORG-002, SYS-ORG-004, SYS-ORG-010</x:t>
         </x:is>
       </x:c>
       <x:c r="G9" s="2" t="inlineStr">

--- a/docs/99-output/MyERP_Requirements.xlsx
+++ b/docs/99-output/MyERP_Requirements.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="1" r:id="R82bc1c13e09f4220"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Non-Functional" sheetId="2" r:id="R74bd908d2ee04eeb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Structure" sheetId="3" r:id="Rfdcc198f541a4440"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interface" sheetId="4" r:id="Ra7619d5ac1d545dc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traceability Matrix" sheetId="5" r:id="Ra65783d7eaf64abf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BlueWhale Parity" sheetId="6" r:id="R19e42c6601e84ac3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timeline" sheetId="7" r:id="R5645b1bfd4364302"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Human Resources" sheetId="8" r:id="Rfc6a47f45613498c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="9" r:id="Rffb445f68d244ffc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="1" r:id="Ra51adb1daf904a50"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Non-Functional" sheetId="2" r:id="R0cddb00515a44043"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Structure" sheetId="3" r:id="Rf2859e0b88d04c87"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interface" sheetId="4" r:id="Rf23a59a7ccb64ea2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traceability Matrix" sheetId="5" r:id="Rf3cfc594c28a456b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BlueWhale Parity" sheetId="6" r:id="Rb565557bcd424ac9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timeline" sheetId="7" r:id="R67e9d84ffbdd4858"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Human Resources" sheetId="8" r:id="Ra4fe6b12631647be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="9" r:id="Rcdd6c3b925ac4be5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -131,7 +131,7 @@
       </x:c>
       <x:c r="D2" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1.0</x:t>
+          <x:t xml:space="preserve">1.1</x:t>
         </x:is>
       </x:c>
       <x:c r="E2" s="2" t="inlineStr">
@@ -146,7 +146,7 @@
       </x:c>
       <x:c r="G2" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">僅有組織檢視權的用戶可見其獲授權公司；無權限回 403。</x:t>
+          <x:t xml:space="preserve">僅有組織檢視權的用戶可見其獲授權且啟用、未刪除的公司；列表支援分頁、關鍵字及代碼／名稱排序；無權限回 403。</x:t>
         </x:is>
       </x:c>
       <x:c r="H2" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </x:c>
       <x:c r="F2" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-ORG-004</x:t>
+          <x:t xml:space="preserve">SYS-ORG-004, SYS-ORG-011</x:t>
         </x:is>
       </x:c>
       <x:c r="G2" s="2" t="inlineStr">

--- a/docs/99-output/MyERP_Requirements.xlsx
+++ b/docs/99-output/MyERP_Requirements.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="1" r:id="Ra51adb1daf904a50"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Non-Functional" sheetId="2" r:id="R0cddb00515a44043"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Structure" sheetId="3" r:id="Rf2859e0b88d04c87"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interface" sheetId="4" r:id="Rf23a59a7ccb64ea2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traceability Matrix" sheetId="5" r:id="Rf3cfc594c28a456b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BlueWhale Parity" sheetId="6" r:id="Rb565557bcd424ac9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timeline" sheetId="7" r:id="R67e9d84ffbdd4858"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Human Resources" sheetId="8" r:id="Ra4fe6b12631647be"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="9" r:id="Rcdd6c3b925ac4be5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="1" r:id="R68f985d6ab084dc8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Non-Functional" sheetId="2" r:id="R9b21d50f44664792"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Structure" sheetId="3" r:id="R9bed53bdb2054ef4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interface" sheetId="4" r:id="Rf77c3ba0cad442f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traceability Matrix" sheetId="5" r:id="Rf3b9eca1f5ca490c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BlueWhale Parity" sheetId="6" r:id="Rdc29fceb741e4333"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timeline" sheetId="7" r:id="R27f3c71e4ba84941"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Human Resources" sheetId="8" r:id="Rdfb6975c28c64c16"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="9" r:id="R9f8187bea4f34786"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -63,7 +63,7 @@
   <x:cols>
     <x:col min="1" max="1" width="16" customWidth="1"/>
     <x:col min="2" max="2" width="10" customWidth="1"/>
-    <x:col min="3" max="3" width="23" customWidth="1"/>
+    <x:col min="3" max="3" width="37" customWidth="1"/>
     <x:col min="4" max="4" width="10" customWidth="1"/>
     <x:col min="5" max="5" width="60" customWidth="1"/>
     <x:col min="6" max="6" width="11" customWidth="1"/>
@@ -530,6 +530,678 @@
       <x:c r="H11" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:22</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.23.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B12" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C12" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">User Identity and Password Security</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D12" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E12" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow authorized users to create a unique user identity.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F12" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G12" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">帳號不分大小寫唯一，停用及軟刪除後仍不可重用；僅保存雜湊，不保存明文密碼。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H12" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:38</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.23.2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B13" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C13" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">User Identity and Password Security</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D13" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E13" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should enforce a configurable password policy.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F13" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G13" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">預設 12–128 字元且含大小寫、數字及符號；長度、複雜度與到期天數可由設定調整，不合法設定拒絕啟動。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H13" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:39</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.23.3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B14" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C14" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">User Identity and Password Security</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D14" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E14" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should lock an account after five consecutive failed password attempts.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F14" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G14" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">第 5 次連續失敗鎖定 15 分鐘；鎖定期間正確密碼亦不得通過；鎖定到期後開啟新失敗計數窗口，成功後清除計數。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H14" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:40</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.23.4</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B15" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C15" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">User Identity and Password Security</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D15" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E15" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should determine whether a user's password has expired.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F15" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G15" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">依設定天數及 password_changed_at 判斷；0 代表不設到期。登入簽發 Token 前必須檢查。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H15" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:41</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.24.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B16" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C16" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Login, Token and Captcha</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D16" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E16" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow a user to log in with username, password and a numeric captcha.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F16" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G16" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">帳號不分大小寫；Captcha 4–6 位數字，答案只存伺服器端，驗證一次即作廢（不論對錯）；帳密錯誤、帳號不存在、停用或鎖定一律回 401 SYS.AUTH.INVALID_CREDENTIALS；密碼到期回 403 SYS.AUTH.PASSWORD_EXPIRED 且不發 Token。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H16" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:53</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.24.2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B17" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C17" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Login, Token and Captcha</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D17" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E17" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should issue a 15-minute access token and a 7-day rotating refresh token.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F17" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G17" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Access Token 為 HS256 JWT，sub 為用戶 Id；Refresh Token 只以 SHA-256 雜湊存 Redis，使用一次即輪替，並發重放只有一個成功。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H17" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:54</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.24.3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B18" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C18" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Login, Token and Captcha</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D18" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E18" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow a logged-in user to log out and invalidate the refresh token.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F18" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G18" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">登出須帶有效 Access Token；只撤銷屬於本人的 Refresh Token，撤銷後刷新回 401。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H18" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:55</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.24.4</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B19" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C19" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Login, Token and Captcha</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D19" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E19" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should provide a development-only captcha master code with startup protection.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F19" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G19" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Captcha:MasterCode 只在 Development 生效且須為 4–6 位數字；其他環境有設定即寫 Error 並拒絕啟動；每次使用寫 Warning（帳號、IP），稽核日誌於 WU-SYS-007 補上。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H19" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:56</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.24.5</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B20" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C20" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Login, Token and Captcha</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D20" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E20" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should provide a trilingual login page that keeps the session and refreshes tokens automatically.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F20" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G20" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">未登入進入主框架導向 /login?returnUrl=…，登入後只回到站內路徑；Captcha 元件只收 4–6 位數字，失敗後換新圖並清空密碼；錯誤依 errorCode 三語顯示；API 請求帶 Bearer，401 時只刷新一次並重送，並發 401 共用同一 refresh；刷新失敗清除 Session 回登入頁；登出撤銷 Refresh Token，伺服器失敗也清除本機 Session。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H20" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:57</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.25.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B21" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C21" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Role, Permission and Data Scope</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D21" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E21" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow authorized users to view roles and the permission catalog.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F21" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G21" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">需 SYS.ROLE.VIEW；角色列表支援分頁、關鍵字（代碼／名稱）、code／name 排序；權限目錄列出各模組宣告的全部代碼；已軟刪除角色不顯示，查詢回 404。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H21" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:69</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.25.2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B22" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C22" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Role, Permission and Data Scope</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D22" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E22" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow authorized users to create a role with permissions and a data scope.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F22" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G22" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">需 SYS.ROLE.CREATE；代碼 1–50 字元 ASCII 英文、數字、-、_，保存為大寫，全系統唯一（含已刪除），重複回 409 SYS.ROLE.DUPLICATE_CODE；權限代碼不分大小寫輸入，必須在權限目錄內，否則 400；資料範圍為 Self／Department／Branch／Company。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H22" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:70</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.25.3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B23" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C23" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Role, Permission and Data Scope</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D23" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E23" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow authorized users to edit or deactivate a role.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F23" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G23" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">需 SYS.ROLE.EDIT；帶 version，不符回 409，且權限集合不變（同一交易）；停用角色立即不再授予權限。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H23" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:71</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.25.4</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B24" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C24" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Role, Permission and Data Scope</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D24" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E24" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow authorized users to delete an unused role.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F24" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G24" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">需 SYS.ROLE.DELETE；仍有用戶使用回 422 SYS.ROLE.IN_USE；軟刪除，代碼不可重用。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H24" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:72</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.25.5</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B25" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C25" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Role, Permission and Data Scope</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D25" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E25" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should enforce permission codes on every API with the backend as the authority.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F25" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G25" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">每個 API 動作標註 模組.資源.動作 權限（ArchitectureTests 檢查）；未登入 401；缺權限或沒有公司上下文 403 COMMON.PERMISSION.DENIED；已登入請求的 X-Company-Id 不可存取（未授權、用戶公司關聯停用、公司停用）一律 403 COMMON.COMPANY.ACCESS_DENIED。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H25" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:73</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.25.6</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B26" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C26" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Role, Permission and Data Scope</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D26" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E26" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow authorized users to grant a user access to a company with roles, organization and default company.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F26" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G26" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">需 SYS.USER.EDIT；公司必須啟用；分店／部門必須屬於該公司且啟用；角色必須存在且啟用；角色整組取代；每位用戶最多一間預設公司（設定新預設會取消舊預設）。用戶不存在回 404。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H26" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:74</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.25.7</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B27" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C27" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Role, Permission and Data Scope</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D27" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E27" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should resolve the user's effective permissions and data scope per company and hide unauthorized UI.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F27" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G27" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">同一權限取各啟用角色最寬的資料範圍；全權角色視為全部權限、全公司範圍；分店／部門範圍但用戶無對應歸屬時退回本人。GET /api/v1/sys/auth/authorization 回傳可存取公司（預設在前）與目前公司權限；前端 *erpHasPermission、permissionGuard 與選單依此隱藏，切換公司重新載入；本機記住的公司不可存取時改用預設公司。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H27" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:75</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -1474,7 +2146,7 @@
   <x:cols>
     <x:col min="1" max="1" width="16" customWidth="1"/>
     <x:col min="2" max="2" width="10" customWidth="1"/>
-    <x:col min="3" max="3" width="16" customWidth="1"/>
+    <x:col min="3" max="3" width="21" customWidth="1"/>
     <x:col min="4" max="4" width="60" customWidth="1"/>
     <x:col min="5" max="5" width="11" customWidth="1"/>
     <x:col min="6" max="6" width="60" customWidth="1"/>
@@ -1579,32 +2251,192 @@
     <x:row r="4">
       <x:c r="A4" s="2" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">REQ_DS43.82</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B4" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C4" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">sys_user</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D4" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Global login identities with password hash, failure count, lockout and audit fields.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E4" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F4" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.23.1, REQ_F4118.23.2, REQ_F4118.23.3, REQ_F4118.23.4</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="2" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">REQ_DS43.89</x:t>
         </x:is>
       </x:c>
-      <x:c r="B4" s="2" t="inlineStr">
+      <x:c r="B5" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="C4" s="2" t="inlineStr">
+      <x:c r="C5" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">sys_branch</x:t>
         </x:is>
       </x:c>
-      <x:c r="D4" s="2" t="inlineStr">
+      <x:c r="D5" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Branch master scoped to a company.</x:t>
         </x:is>
       </x:c>
-      <x:c r="E4" s="2" t="inlineStr">
+      <x:c r="E5" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Developer</x:t>
         </x:is>
       </x:c>
-      <x:c r="F4" s="2" t="inlineStr">
+      <x:c r="F5" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">REQ_F4118.21.1, REQ_F4118.21.2, REQ_F4118.21.3</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.90</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B6" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C6" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">sys_role</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D6" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System-wide role definitions with data scope, full-access flag, audit, version and soft deletion.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E6" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F6" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.25.1, REQ_F4118.25.2, REQ_F4118.25.3, REQ_F4118.25.4</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.91</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B7" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C7" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">sys_role_permission</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D7" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Permission codes granted by each role.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E7" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F7" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.25.2, REQ_F4118.25.3, REQ_F4118.25.7</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.92</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B8" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C8" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">sys_user_company</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D8" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Companies a user may access, with branch and department placement and the default company.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E8" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F8" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.25.5, REQ_F4118.25.6, REQ_F4118.25.7</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.93</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B9" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C9" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">sys_user_role</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D9" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Roles assigned to a user within a company.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E9" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F9" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.25.6, REQ_F4118.25.7</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -1617,13 +2449,13 @@
   <x:cols>
     <x:col min="1" max="1" width="16" customWidth="1"/>
     <x:col min="2" max="2" width="15" customWidth="1"/>
-    <x:col min="3" max="3" width="27" customWidth="1"/>
+    <x:col min="3" max="3" width="32" customWidth="1"/>
     <x:col min="4" max="4" width="30" customWidth="1"/>
     <x:col min="5" max="5" width="13" customWidth="1"/>
-    <x:col min="6" max="6" width="10" customWidth="1"/>
-    <x:col min="7" max="7" width="15" customWidth="1"/>
-    <x:col min="8" max="8" width="25" customWidth="1"/>
-    <x:col min="9" max="9" width="13" customWidth="1"/>
+    <x:col min="6" max="6" width="23" customWidth="1"/>
+    <x:col min="7" max="7" width="40" customWidth="1"/>
+    <x:col min="8" max="8" width="60" customWidth="1"/>
+    <x:col min="9" max="9" width="16" customWidth="1"/>
     <x:col min="10" max="10" width="10" customWidth="1"/>
     <x:col min="11" max="11" width="11" customWidth="1"/>
   </x:cols>
@@ -1965,6 +2797,462 @@
         </x:is>
       </x:c>
       <x:c r="K6" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.61.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B7" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.61</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C7" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">User Identity Create Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D7" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Username (Input)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E7" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">帳號</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F7" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">建立登入身分</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G7" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ASCII text</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H7" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">3–100 字元，字母／數字／點／底線／連字號</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I7" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J7" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K7" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.61.2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B8" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.61</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C8" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">User Identity Create Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D8" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Password (Input)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E8" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">初始密碼</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F8" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">依目前政策驗證，提交後清空</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G8" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Password text</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H8" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">預設 12–128 字元</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I8" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J8" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K8" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.62.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B9" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.62</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C9" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Login Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D9" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Username (Input)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E9" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">帳號</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F9" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">登入身分</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G9" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Text，autocomplete=username</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H9" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">必填、非空白，最多 100 字元；送出前去除前後空白</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I9" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J9" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K9" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.62.2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B10" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.62</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C10" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Login Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D10" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Password (Input)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E10" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">密碼</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F10" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">驗證身分</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G10" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Password，autocomplete=current-password</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H10" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">必填，最多 128 字元；失敗後清空</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I10" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J10" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K10" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.62.3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B11" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.62</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C11" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Login Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D11" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Captcha Code (Input)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E11" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">驗證碼</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F11" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">防自動化登入</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G11" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">數字，inputmode=numeric</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H11" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4–6 位數字（非數字自動移除）</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I11" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.62.4</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J11" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K11" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.62.4</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B12" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.62</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C12" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Login Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D12" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Captcha Image (Button)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E12" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">驗證碼圖片</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F12" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">顯示題目，點擊換圖</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G12" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SVG data URI</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H12" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">每次送出失敗後自動換新</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I12" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J12" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K12" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.62.5</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B13" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.62</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C13" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Login Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D13" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Sign In (Button)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E13" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">登入</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F13" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">送出</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G13" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Button</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H13" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">送出中顯示載入狀態，不可重複送出</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I13" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J13" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K13" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.62.6</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B14" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.62</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C14" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Login Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D14" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Error Message (Alert)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E14" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">錯誤訊息</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F14" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">顯示 errors.&lt;errorCode&gt;</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G14" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Text</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H14" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">INVALID_CREDENTIALS／CAPTCHA_INVALID／PASSWORD_EXPIRED／VALIDATION_FAILED／網路／未知</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I14" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J14" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K14" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Developer</x:t>
         </x:is>
@@ -1979,10 +3267,10 @@
   <x:cols>
     <x:col min="1" max="1" width="16" customWidth="1"/>
     <x:col min="2" max="2" width="60" customWidth="1"/>
-    <x:col min="3" max="3" width="13" customWidth="1"/>
+    <x:col min="3" max="3" width="39" customWidth="1"/>
     <x:col min="4" max="4" width="12" customWidth="1"/>
-    <x:col min="5" max="5" width="32" customWidth="1"/>
-    <x:col min="6" max="6" width="39" customWidth="1"/>
+    <x:col min="5" max="5" width="60" customWidth="1"/>
+    <x:col min="6" max="6" width="60" customWidth="1"/>
     <x:col min="7" max="7" width="10" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -2051,7 +3339,7 @@
       </x:c>
       <x:c r="F2" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-ORG-004, SYS-ORG-011</x:t>
+          <x:t xml:space="preserve">SYS-ORG-004, SYS-ORG-011, SYS-ORG-012</x:t>
         </x:is>
       </x:c>
       <x:c r="G2" s="2" t="inlineStr">
@@ -2088,7 +3376,7 @@
       </x:c>
       <x:c r="F3" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-ORG-001, SYS-ORG-008</x:t>
+          <x:t xml:space="preserve">SYS-ORG-001, SYS-ORG-008, SYS-ORG-013</x:t>
         </x:is>
       </x:c>
       <x:c r="G3" s="2" t="inlineStr">
@@ -2199,7 +3487,7 @@
       </x:c>
       <x:c r="F6" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-ORG-002, SYS-ORG-004, SYS-ORG-010</x:t>
+          <x:t xml:space="preserve">SYS-ORG-002, SYS-ORG-004, SYS-ORG-010, SYS-ORG-012</x:t>
         </x:is>
       </x:c>
       <x:c r="G6" s="2" t="inlineStr">
@@ -2236,7 +3524,7 @@
       </x:c>
       <x:c r="F7" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-ORG-001</x:t>
+          <x:t xml:space="preserve">SYS-ORG-001, SYS-ORG-013</x:t>
         </x:is>
       </x:c>
       <x:c r="G7" s="2" t="inlineStr">
@@ -2310,7 +3598,7 @@
       </x:c>
       <x:c r="F9" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-ORG-002, SYS-ORG-004, SYS-ORG-010</x:t>
+          <x:t xml:space="preserve">SYS-ORG-002, SYS-ORG-004, SYS-ORG-010, SYS-ORG-012</x:t>
         </x:is>
       </x:c>
       <x:c r="G9" s="2" t="inlineStr">
@@ -2347,7 +3635,7 @@
       </x:c>
       <x:c r="F10" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-ORG-001, SYS-ORG-003</x:t>
+          <x:t xml:space="preserve">SYS-ORG-001, SYS-ORG-003, SYS-ORG-013</x:t>
         </x:is>
       </x:c>
       <x:c r="G10" s="2" t="inlineStr">
@@ -2390,6 +3678,598 @@
       <x:c r="G11" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Covered</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.23.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B12" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow authorized users to create a unique user identity.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C12" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.82</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D12" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.61</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E12" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.61.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F12" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-USER-001, SYS-USER-004, SYS-USER-006</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G12" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Covered</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.23.2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B13" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should enforce a configurable password policy.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C13" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.82</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D13" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.61</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E13" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.61.2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F13" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-USER-001, SYS-USER-007, SYS-USER-006</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G13" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Covered</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.23.3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B14" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should lock an account after five consecutive failed password attempts.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C14" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.82</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D14" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="E14" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F14" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-USER-002, SYS-USER-003, SYS-USER-005, SYS-USER-006</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G14" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Partial</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.23.4</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B15" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should determine whether a user's password has expired.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C15" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.82</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D15" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="E15" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F15" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-USER-003, SYS-USER-006</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G15" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Partial</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.24.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B16" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow a user to log in with username, password and a numeric captcha.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C16" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="D16" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.62</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E16" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.62.1, REQ_IO_A8.62.2, REQ_IO_A8.62.3, REQ_IO_A8.62.4</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F16" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-AUTH-001, SYS-AUTH-002, SYS-AUTH-005, SYS-AUTH-006, SYS-AUTH-009, SYS-AUTH-014, SYS-AUTH-015, SYS-AUTH-016, SYS-AUTH-017</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G16" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Partial</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.24.2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B17" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should issue a 15-minute access token and a 7-day rotating refresh token.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C17" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="D17" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="E17" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F17" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-AUTH-001, SYS-AUTH-004, SYS-AUTH-007, SYS-AUTH-009, SYS-AUTH-010, SYS-AUTH-016, SYS-AUTH-017</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G17" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Partial</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.24.3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B18" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow a logged-in user to log out and invalidate the refresh token.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C18" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="D18" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="E18" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F18" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-AUTH-008, SYS-AUTH-016, SYS-AUTH-017</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G18" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Partial</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.24.4</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B19" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should provide a development-only captcha master code with startup protection.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C19" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="D19" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="E19" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F19" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-AUTH-003, SYS-AUTH-004, SYS-AUTH-016, SYS-AUTH-017</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G19" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Partial</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.24.5</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B20" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should provide a trilingual login page that keeps the session and refreshes tokens automatically.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C20" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="D20" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.62</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E20" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.62.5, REQ_IO_A8.62.6</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F20" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-AUTH-011, SYS-AUTH-012, SYS-AUTH-013, SYS-AUTH-015, SYS-AUTH-016, SYS-AUTH-017</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G20" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Partial</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.25.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B21" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow authorized users to view roles and the permission catalog.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C21" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.90</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D21" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="E21" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F21" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-PERM-004, SYS-PERM-011, SYS-PERM-024</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G21" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Partial</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.25.2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B22" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow authorized users to create a role with permissions and a data scope.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C22" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.90, REQ_DS43.91</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D22" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="E22" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F22" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-PERM-011, SYS-PERM-024</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G22" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Partial</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.25.3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B23" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow authorized users to edit or deactivate a role.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C23" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.90, REQ_DS43.91</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D23" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="E23" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F23" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-PERM-011, SYS-PERM-024</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G23" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Partial</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.25.4</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B24" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow authorized users to delete an unused role.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C24" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.90</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D24" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="E24" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F24" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-PERM-012, SYS-PERM-024</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G24" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Partial</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.25.5</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B25" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should enforce permission codes on every API with the backend as the authority.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C25" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.92</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D25" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="E25" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F25" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-PERM-001, SYS-PERM-005, SYS-PERM-006, SYS-PERM-010</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G25" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Partial</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.25.6</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B26" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow authorized users to grant a user access to a company with roles, organization and default company.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C26" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.92, REQ_DS43.93</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D26" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="E26" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F26" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-PERM-015, SYS-PERM-016, SYS-PERM-024</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G26" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Partial</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.25.7</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B27" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should resolve the user's effective permissions and data scope per company and hide unauthorized UI.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C27" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.91, REQ_DS43.92, REQ_DS43.93</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D27" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="E27" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F27" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-PERM-002, SYS-PERM-003, SYS-PERM-013, SYS-PERM-014, SYS-PERM-020, SYS-PERM-021, SYS-PERM-022, SYS-PERM-023</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G27" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Partial</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -16964,7 +18844,7 @@
       </x:c>
       <x:c r="F455" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">未開始</x:t>
+          <x:t xml:space="preserve">進行中</x:t>
         </x:is>
       </x:c>
     </x:row>

--- a/docs/99-output/MyERP_Requirements.xlsx
+++ b/docs/99-output/MyERP_Requirements.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="1" r:id="R68f985d6ab084dc8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Non-Functional" sheetId="2" r:id="R9b21d50f44664792"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Structure" sheetId="3" r:id="R9bed53bdb2054ef4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interface" sheetId="4" r:id="Rf77c3ba0cad442f2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traceability Matrix" sheetId="5" r:id="Rf3b9eca1f5ca490c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BlueWhale Parity" sheetId="6" r:id="Rdc29fceb741e4333"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timeline" sheetId="7" r:id="R27f3c71e4ba84941"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Human Resources" sheetId="8" r:id="Rdfb6975c28c64c16"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="9" r:id="R9f8187bea4f34786"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="1" r:id="R2563ce78a73b4d8c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Non-Functional" sheetId="2" r:id="Ra52784bd7a284867"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Structure" sheetId="3" r:id="R26d4540427c148b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interface" sheetId="4" r:id="R94a762b990774f90"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traceability Matrix" sheetId="5" r:id="Rbea054a32ced4542"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BlueWhale Parity" sheetId="6" r:id="R4a2eba0f67f94d2f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timeline" sheetId="7" r:id="R0653581235d14cea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Human Resources" sheetId="8" r:id="R3f2eab2c30a84330"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="9" r:id="R3940f2ef141e41bb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -131,7 +131,7 @@
       </x:c>
       <x:c r="D2" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1.1</x:t>
+          <x:t xml:space="preserve">1.2</x:t>
         </x:is>
       </x:c>
       <x:c r="E2" s="2" t="inlineStr">
@@ -146,7 +146,7 @@
       </x:c>
       <x:c r="G2" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">僅有組織檢視權的用戶可見其獲授權且啟用、未刪除的公司；列表支援分頁、關鍵字及代碼／名稱排序；無權限回 403。</x:t>
+          <x:t xml:space="preserve">僅有組織檢視權的用戶可見其獲授權且未刪除的公司；預設只列啟用公司，勾選「顯示已停用」時一併列出停用公司；列表支援分頁、關鍵字及代碼／名稱排序；無權限回 403。</x:t>
         </x:is>
       </x:c>
       <x:c r="H2" s="2" t="inlineStr">
@@ -173,7 +173,7 @@
       </x:c>
       <x:c r="D3" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1.1</x:t>
+          <x:t xml:space="preserve">1.2</x:t>
         </x:is>
       </x:c>
       <x:c r="E3" s="2" t="inlineStr">
@@ -188,7 +188,7 @@
       </x:c>
       <x:c r="G3" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">代碼全系統唯一；代碼與名稱必填；代碼限 1–30 字元的 ASCII 英文、數字、-、_，保存為大寫；重複代碼回 409。</x:t>
+          <x:t xml:space="preserve">代碼全系統唯一；代碼與名稱必填；代碼限 1–30 字元的 ASCII 英文、數字、-、_，保存為大寫；重複代碼回 409；建立者在同一交易內獲授權新公司，角色沿用其在目前公司的角色（ADR-015）。</x:t>
         </x:is>
       </x:c>
       <x:c r="H3" s="2" t="inlineStr">
@@ -215,7 +215,7 @@
       </x:c>
       <x:c r="D4" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1.0</x:t>
+          <x:t xml:space="preserve">1.1</x:t>
         </x:is>
       </x:c>
       <x:c r="E4" s="2" t="inlineStr">
@@ -230,7 +230,7 @@
       </x:c>
       <x:c r="G4" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">版本不符回 409；審計欄位記錄修改者。</x:t>
+          <x:t xml:space="preserve">版本不符回 409；審計欄位記錄修改者；目標公司不是用戶獲授權的公司時回 404。</x:t>
         </x:is>
       </x:c>
       <x:c r="H4" s="2" t="inlineStr">
@@ -571,7 +571,7 @@
       </x:c>
       <x:c r="H12" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:38</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:40</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -613,7 +613,7 @@
       </x:c>
       <x:c r="H13" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:39</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:41</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -655,7 +655,7 @@
       </x:c>
       <x:c r="H14" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:40</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:42</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -697,7 +697,7 @@
       </x:c>
       <x:c r="H15" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:41</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:43</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -739,7 +739,7 @@
       </x:c>
       <x:c r="H16" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:53</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:55</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -781,7 +781,7 @@
       </x:c>
       <x:c r="H17" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:54</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:56</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -823,7 +823,7 @@
       </x:c>
       <x:c r="H18" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:55</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:57</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -865,7 +865,7 @@
       </x:c>
       <x:c r="H19" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:56</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:58</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -907,7 +907,7 @@
       </x:c>
       <x:c r="H20" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:57</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:59</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -949,7 +949,7 @@
       </x:c>
       <x:c r="H21" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:69</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:71</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -991,7 +991,7 @@
       </x:c>
       <x:c r="H22" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:70</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:72</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -1033,7 +1033,7 @@
       </x:c>
       <x:c r="H23" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:71</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:73</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -1075,7 +1075,7 @@
       </x:c>
       <x:c r="H24" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:72</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:74</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -1117,7 +1117,7 @@
       </x:c>
       <x:c r="H25" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:73</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:75</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -1159,7 +1159,7 @@
       </x:c>
       <x:c r="H26" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:74</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:76</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -1201,7 +1201,7 @@
       </x:c>
       <x:c r="H27" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:75</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:77</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -3339,7 +3339,7 @@
       </x:c>
       <x:c r="F2" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-ORG-004, SYS-ORG-011, SYS-ORG-012</x:t>
+          <x:t xml:space="preserve">SYS-ORG-004, SYS-ORG-011, SYS-ORG-012, SYS-ORG-020, SYS-ORG-026</x:t>
         </x:is>
       </x:c>
       <x:c r="G2" s="2" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </x:c>
       <x:c r="F3" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-ORG-001, SYS-ORG-008, SYS-ORG-013</x:t>
+          <x:t xml:space="preserve">SYS-ORG-001, SYS-ORG-008, SYS-ORG-013, SYS-ORG-021</x:t>
         </x:is>
       </x:c>
       <x:c r="G3" s="2" t="inlineStr">
@@ -3413,7 +3413,7 @@
       </x:c>
       <x:c r="F4" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-ORG-005, SYS-ORG-009</x:t>
+          <x:t xml:space="preserve">SYS-ORG-005, SYS-ORG-009, SYS-ORG-013, SYS-ORG-021</x:t>
         </x:is>
       </x:c>
       <x:c r="G4" s="2" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </x:c>
       <x:c r="F5" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-ORG-006</x:t>
+          <x:t xml:space="preserve">SYS-ORG-006, SYS-ORG-021</x:t>
         </x:is>
       </x:c>
       <x:c r="G5" s="2" t="inlineStr">
@@ -3487,7 +3487,7 @@
       </x:c>
       <x:c r="F6" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-ORG-002, SYS-ORG-004, SYS-ORG-010, SYS-ORG-012</x:t>
+          <x:t xml:space="preserve">SYS-ORG-002, SYS-ORG-004, SYS-ORG-010, SYS-ORG-012, SYS-ORG-020, SYS-ORG-022, SYS-ORG-024, SYS-ORG-025</x:t>
         </x:is>
       </x:c>
       <x:c r="G6" s="2" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </x:c>
       <x:c r="F7" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-ORG-001, SYS-ORG-013</x:t>
+          <x:t xml:space="preserve">SYS-ORG-001, SYS-ORG-013, SYS-ORG-020, SYS-ORG-022, SYS-ORG-024</x:t>
         </x:is>
       </x:c>
       <x:c r="G7" s="2" t="inlineStr">
@@ -3561,7 +3561,7 @@
       </x:c>
       <x:c r="F8" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-ORG-005</x:t>
+          <x:t xml:space="preserve">SYS-ORG-005, SYS-ORG-022</x:t>
         </x:is>
       </x:c>
       <x:c r="G8" s="2" t="inlineStr">
@@ -3598,7 +3598,7 @@
       </x:c>
       <x:c r="F9" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-ORG-002, SYS-ORG-004, SYS-ORG-010, SYS-ORG-012</x:t>
+          <x:t xml:space="preserve">SYS-ORG-002, SYS-ORG-004, SYS-ORG-010, SYS-ORG-012, SYS-ORG-020, SYS-ORG-023, SYS-ORG-026</x:t>
         </x:is>
       </x:c>
       <x:c r="G9" s="2" t="inlineStr">
@@ -3635,7 +3635,7 @@
       </x:c>
       <x:c r="F10" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-ORG-001, SYS-ORG-003, SYS-ORG-013</x:t>
+          <x:t xml:space="preserve">SYS-ORG-001, SYS-ORG-003, SYS-ORG-013, SYS-ORG-023</x:t>
         </x:is>
       </x:c>
       <x:c r="G10" s="2" t="inlineStr">
@@ -3672,7 +3672,7 @@
       </x:c>
       <x:c r="F11" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-ORG-005, SYS-ORG-007, SYS-ORG-009</x:t>
+          <x:t xml:space="preserve">SYS-ORG-005, SYS-ORG-007, SYS-ORG-009, SYS-ORG-023, SYS-ORG-026</x:t>
         </x:is>
       </x:c>
       <x:c r="G11" s="2" t="inlineStr">

--- a/docs/99-output/MyERP_Requirements.xlsx
+++ b/docs/99-output/MyERP_Requirements.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="1" r:id="R2563ce78a73b4d8c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Non-Functional" sheetId="2" r:id="Ra52784bd7a284867"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Structure" sheetId="3" r:id="R26d4540427c148b6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interface" sheetId="4" r:id="R94a762b990774f90"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traceability Matrix" sheetId="5" r:id="Rbea054a32ced4542"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BlueWhale Parity" sheetId="6" r:id="R4a2eba0f67f94d2f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timeline" sheetId="7" r:id="R0653581235d14cea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Human Resources" sheetId="8" r:id="R3f2eab2c30a84330"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="9" r:id="R3940f2ef141e41bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="1" r:id="R23b7dea85ff1444a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Non-Functional" sheetId="2" r:id="R54dee6920b864470"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Structure" sheetId="3" r:id="R6389d2a2b1af49b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interface" sheetId="4" r:id="Ra10c7500e3ab4d9e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traceability Matrix" sheetId="5" r:id="R0d010cc04a25480c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BlueWhale Parity" sheetId="6" r:id="Reb09fd7f186f4200"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timeline" sheetId="7" r:id="R31275a1f3f7f48a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Human Resources" sheetId="8" r:id="R22dc2e391ce54910"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="9" r:id="Rdeff01a5e27d4fc9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -704,7 +704,7 @@
     <x:row r="16">
       <x:c r="A16" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.24.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.23.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B16" s="2" t="inlineStr">
@@ -714,7 +714,7 @@
       </x:c>
       <x:c r="C16" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Login, Token and Captcha</x:t>
+          <x:t xml:space="preserve">User Identity and Password Security</x:t>
         </x:is>
       </x:c>
       <x:c r="D16" s="2" t="inlineStr">
@@ -724,7 +724,7 @@
       </x:c>
       <x:c r="E16" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow a user to log in with username, password and a numeric captcha.</x:t>
+          <x:t xml:space="preserve">System should list the users of the current company with paging, keyword and sorting.</x:t>
         </x:is>
       </x:c>
       <x:c r="F16" s="2" t="inlineStr">
@@ -734,19 +734,19 @@
       </x:c>
       <x:c r="G16" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">帳號不分大小寫；Captcha 4–6 位數字，答案只存伺服器端，驗證一次即作廢（不論對錯）；帳密錯誤、帳號不存在、停用或鎖定一律回 401 SYS.AUTH.INVALID_CREDENTIALS；密碼到期回 403 SYS.AUTH.PASSWORD_EXPIRED 且不發 Token。</x:t>
+          <x:t xml:space="preserve">只列在目前公司有用戶公司關聯的用戶（含停用）；關鍵字不分大小寫比對帳號；排序 username／-username，其他欄位 400；回應不含雜湊、失敗次數及鎖定期限，只回 isLocked、isPasswordExpired（ADR-016）。</x:t>
         </x:is>
       </x:c>
       <x:c r="H16" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:55</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:44</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.24.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.23.6</x:t>
         </x:is>
       </x:c>
       <x:c r="B17" s="2" t="inlineStr">
@@ -756,7 +756,7 @@
       </x:c>
       <x:c r="C17" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Login, Token and Captcha</x:t>
+          <x:t xml:space="preserve">User Identity and Password Security</x:t>
         </x:is>
       </x:c>
       <x:c r="D17" s="2" t="inlineStr">
@@ -766,7 +766,7 @@
       </x:c>
       <x:c r="E17" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should issue a 15-minute access token and a 7-day rotating refresh token.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to create a user in the current company.</x:t>
         </x:is>
       </x:c>
       <x:c r="F17" s="2" t="inlineStr">
@@ -776,19 +776,19 @@
       </x:c>
       <x:c r="G17" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Access Token 為 HS256 JWT，sub 為用戶 Id；Refresh Token 只以 SHA-256 雜湊存 Redis，使用一次即輪替，並發重放只有一個成功。</x:t>
+          <x:t xml:space="preserve">需 SYS.USER.CREATE；同一交易建立身分及目前公司的預設關聯（無角色）；重複帳號（不分大小寫、含他公司）409 SYS.USER.DUPLICATE；弱密碼或帳號格式錯誤 400；建立後可登入。</x:t>
         </x:is>
       </x:c>
       <x:c r="H17" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:56</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:45</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.24.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.23.7</x:t>
         </x:is>
       </x:c>
       <x:c r="B18" s="2" t="inlineStr">
@@ -798,7 +798,7 @@
       </x:c>
       <x:c r="C18" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Login, Token and Captcha</x:t>
+          <x:t xml:space="preserve">User Identity and Password Security</x:t>
         </x:is>
       </x:c>
       <x:c r="D18" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </x:c>
       <x:c r="E18" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow a logged-in user to log out and invalidate the refresh token.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to activate or deactivate a user.</x:t>
         </x:is>
       </x:c>
       <x:c r="F18" s="2" t="inlineStr">
@@ -818,19 +818,19 @@
       </x:c>
       <x:c r="G18" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">登出須帶有效 Access Token；只撤銷屬於本人的 Refresh Token，撤銷後刷新回 401。</x:t>
+          <x:t xml:space="preserve">需 SYS.USER.EDIT 並帶 version（過期 409）；停用後不可登入與刷新，重新啟用後可登入；不可停用自己 422 SYS.USER.SELF_DEACTIVATION；他公司用戶 404。</x:t>
         </x:is>
       </x:c>
       <x:c r="H18" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:57</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:46</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.24.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.23.8</x:t>
         </x:is>
       </x:c>
       <x:c r="B19" s="2" t="inlineStr">
@@ -840,7 +840,7 @@
       </x:c>
       <x:c r="C19" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Login, Token and Captcha</x:t>
+          <x:t xml:space="preserve">User Identity and Password Security</x:t>
         </x:is>
       </x:c>
       <x:c r="D19" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </x:c>
       <x:c r="E19" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should provide a development-only captcha master code with startup protection.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to reset a password and unlock a locked user.</x:t>
         </x:is>
       </x:c>
       <x:c r="F19" s="2" t="inlineStr">
@@ -860,19 +860,19 @@
       </x:c>
       <x:c r="G19" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Captcha:MasterCode 只在 Development 生效且須為 4–6 位數字；其他環境有設定即寫 Error 並拒絕啟動；每次使用寫 Warning（帳號、IP），稽核日誌於 WU-SYS-007 補上。</x:t>
+          <x:t xml:space="preserve">重設密碼需 SYS.USER.RESET_PASSWORD，依密碼政策驗證，重新起算到期並清除鎖定，舊密碼即失效；解鎖需 SYS.USER.EDIT，清除失敗計數與鎖定，未鎖定時亦回 204；他公司用戶 404。</x:t>
         </x:is>
       </x:c>
       <x:c r="H19" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:58</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:47</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.24.5</x:t>
+          <x:t xml:space="preserve">REQ_F4118.24.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B20" s="2" t="inlineStr">
@@ -892,7 +892,7 @@
       </x:c>
       <x:c r="E20" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should provide a trilingual login page that keeps the session and refreshes tokens automatically.</x:t>
+          <x:t xml:space="preserve">System should allow a user to log in with username, password and a numeric captcha.</x:t>
         </x:is>
       </x:c>
       <x:c r="F20" s="2" t="inlineStr">
@@ -902,7 +902,7 @@
       </x:c>
       <x:c r="G20" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">未登入進入主框架導向 /login?returnUrl=…，登入後只回到站內路徑；Captcha 元件只收 4–6 位數字，失敗後換新圖並清空密碼；錯誤依 errorCode 三語顯示；API 請求帶 Bearer，401 時只刷新一次並重送，並發 401 共用同一 refresh；刷新失敗清除 Session 回登入頁；登出撤銷 Refresh Token，伺服器失敗也清除本機 Session。</x:t>
+          <x:t xml:space="preserve">帳號不分大小寫；Captcha 4–6 位數字，答案只存伺服器端，驗證一次即作廢（不論對錯）；帳密錯誤、帳號不存在、停用或鎖定一律回 401 SYS.AUTH.INVALID_CREDENTIALS；密碼到期回 403 SYS.AUTH.PASSWORD_EXPIRED 且不發 Token。</x:t>
         </x:is>
       </x:c>
       <x:c r="H20" s="2" t="inlineStr">
@@ -914,7 +914,7 @@
     <x:row r="21">
       <x:c r="A21" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.25.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.24.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B21" s="2" t="inlineStr">
@@ -924,7 +924,7 @@
       </x:c>
       <x:c r="C21" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Role, Permission and Data Scope</x:t>
+          <x:t xml:space="preserve">Login, Token and Captcha</x:t>
         </x:is>
       </x:c>
       <x:c r="D21" s="2" t="inlineStr">
@@ -934,7 +934,7 @@
       </x:c>
       <x:c r="E21" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to view roles and the permission catalog.</x:t>
+          <x:t xml:space="preserve">System should issue a 15-minute access token and a 7-day rotating refresh token.</x:t>
         </x:is>
       </x:c>
       <x:c r="F21" s="2" t="inlineStr">
@@ -944,19 +944,19 @@
       </x:c>
       <x:c r="G21" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">需 SYS.ROLE.VIEW；角色列表支援分頁、關鍵字（代碼／名稱）、code／name 排序；權限目錄列出各模組宣告的全部代碼；已軟刪除角色不顯示，查詢回 404。</x:t>
+          <x:t xml:space="preserve">Access Token 為 HS256 JWT，sub 為用戶 Id；Refresh Token 只以 SHA-256 雜湊存 Redis，使用一次即輪替，並發重放只有一個成功。</x:t>
         </x:is>
       </x:c>
       <x:c r="H21" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:71</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:60</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.25.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.24.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B22" s="2" t="inlineStr">
@@ -966,7 +966,7 @@
       </x:c>
       <x:c r="C22" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Role, Permission and Data Scope</x:t>
+          <x:t xml:space="preserve">Login, Token and Captcha</x:t>
         </x:is>
       </x:c>
       <x:c r="D22" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </x:c>
       <x:c r="E22" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to create a role with permissions and a data scope.</x:t>
+          <x:t xml:space="preserve">System should allow a logged-in user to log out and invalidate the refresh token.</x:t>
         </x:is>
       </x:c>
       <x:c r="F22" s="2" t="inlineStr">
@@ -986,19 +986,19 @@
       </x:c>
       <x:c r="G22" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">需 SYS.ROLE.CREATE；代碼 1–50 字元 ASCII 英文、數字、-、_，保存為大寫，全系統唯一（含已刪除），重複回 409 SYS.ROLE.DUPLICATE_CODE；權限代碼不分大小寫輸入，必須在權限目錄內，否則 400；資料範圍為 Self／Department／Branch／Company。</x:t>
+          <x:t xml:space="preserve">登出須帶有效 Access Token；只撤銷屬於本人的 Refresh Token，撤銷後刷新回 401。</x:t>
         </x:is>
       </x:c>
       <x:c r="H22" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:72</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:61</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.25.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.24.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B23" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </x:c>
       <x:c r="C23" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Role, Permission and Data Scope</x:t>
+          <x:t xml:space="preserve">Login, Token and Captcha</x:t>
         </x:is>
       </x:c>
       <x:c r="D23" s="2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </x:c>
       <x:c r="E23" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to edit or deactivate a role.</x:t>
+          <x:t xml:space="preserve">System should provide a development-only captcha master code with startup protection.</x:t>
         </x:is>
       </x:c>
       <x:c r="F23" s="2" t="inlineStr">
@@ -1028,19 +1028,19 @@
       </x:c>
       <x:c r="G23" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">需 SYS.ROLE.EDIT；帶 version，不符回 409，且權限集合不變（同一交易）；停用角色立即不再授予權限。</x:t>
+          <x:t xml:space="preserve">Captcha:MasterCode 只在 Development 生效且須為 4–6 位數字；其他環境有設定即寫 Error 並拒絕啟動；每次使用寫 Warning（帳號、IP），稽核日誌於 WU-SYS-007 補上。</x:t>
         </x:is>
       </x:c>
       <x:c r="H23" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:73</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:62</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.25.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.24.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B24" s="2" t="inlineStr">
@@ -1050,7 +1050,7 @@
       </x:c>
       <x:c r="C24" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Role, Permission and Data Scope</x:t>
+          <x:t xml:space="preserve">Login, Token and Captcha</x:t>
         </x:is>
       </x:c>
       <x:c r="D24" s="2" t="inlineStr">
@@ -1060,7 +1060,7 @@
       </x:c>
       <x:c r="E24" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to delete an unused role.</x:t>
+          <x:t xml:space="preserve">System should provide a trilingual login page that keeps the session and refreshes tokens automatically.</x:t>
         </x:is>
       </x:c>
       <x:c r="F24" s="2" t="inlineStr">
@@ -1070,19 +1070,19 @@
       </x:c>
       <x:c r="G24" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">需 SYS.ROLE.DELETE；仍有用戶使用回 422 SYS.ROLE.IN_USE；軟刪除，代碼不可重用。</x:t>
+          <x:t xml:space="preserve">未登入進入主框架導向 /login?returnUrl=…，登入後只回到站內路徑；Captcha 元件只收 4–6 位數字，失敗後換新圖並清空密碼；錯誤依 errorCode 三語顯示；API 請求帶 Bearer，401 時只刷新一次並重送，並發 401 共用同一 refresh；刷新失敗清除 Session 回登入頁；登出撤銷 Refresh Token，伺服器失敗也清除本機 Session。</x:t>
         </x:is>
       </x:c>
       <x:c r="H24" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:74</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:63</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.25.5</x:t>
+          <x:t xml:space="preserve">REQ_F4118.25.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B25" s="2" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </x:c>
       <x:c r="E25" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enforce permission codes on every API with the backend as the authority.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to view roles and the permission catalog.</x:t>
         </x:is>
       </x:c>
       <x:c r="F25" s="2" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </x:c>
       <x:c r="G25" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">每個 API 動作標註 模組.資源.動作 權限（ArchitectureTests 檢查）；未登入 401；缺權限或沒有公司上下文 403 COMMON.PERMISSION.DENIED；已登入請求的 X-Company-Id 不可存取（未授權、用戶公司關聯停用、公司停用）一律 403 COMMON.COMPANY.ACCESS_DENIED。</x:t>
+          <x:t xml:space="preserve">需 SYS.ROLE.VIEW；角色列表支援分頁、關鍵字（代碼／名稱）、code／name 排序；權限目錄列出各模組宣告的全部代碼；已軟刪除角色不顯示，查詢回 404。</x:t>
         </x:is>
       </x:c>
       <x:c r="H25" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
     <x:row r="26">
       <x:c r="A26" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.25.6</x:t>
+          <x:t xml:space="preserve">REQ_F4118.25.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B26" s="2" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </x:c>
       <x:c r="E26" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to grant a user access to a company with roles, organization and default company.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to create a role with permissions and a data scope.</x:t>
         </x:is>
       </x:c>
       <x:c r="F26" s="2" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </x:c>
       <x:c r="G26" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">需 SYS.USER.EDIT；公司必須啟用；分店／部門必須屬於該公司且啟用；角色必須存在且啟用；角色整組取代；每位用戶最多一間預設公司（設定新預設會取消舊預設）。用戶不存在回 404。</x:t>
+          <x:t xml:space="preserve">需 SYS.ROLE.CREATE；代碼 1–50 字元 ASCII 英文、數字、-、_，保存為大寫，全系統唯一（含已刪除），重複回 409 SYS.ROLE.DUPLICATE_CODE；權限代碼不分大小寫輸入，必須在權限目錄內，否則 400；資料範圍為 Self／Department／Branch／Company。</x:t>
         </x:is>
       </x:c>
       <x:c r="H26" s="2" t="inlineStr">
@@ -1166,42 +1166,210 @@
     <x:row r="27">
       <x:c r="A27" s="2" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">REQ_F4118.25.3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B27" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C27" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Role, Permission and Data Scope</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D27" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E27" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow authorized users to edit or deactivate a role.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F27" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G27" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">需 SYS.ROLE.EDIT；帶 version，不符回 409，且權限集合不變（同一交易）；停用角色立即不再授予權限。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H27" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:77</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.25.4</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B28" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C28" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Role, Permission and Data Scope</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D28" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E28" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow authorized users to delete an unused role.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F28" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G28" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">需 SYS.ROLE.DELETE；仍有用戶使用回 422 SYS.ROLE.IN_USE；軟刪除，代碼不可重用。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H28" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:78</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.25.5</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B29" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C29" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Role, Permission and Data Scope</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D29" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E29" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should enforce permission codes on every API with the backend as the authority.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F29" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G29" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">每個 API 動作標註 模組.資源.動作 權限（ArchitectureTests 檢查）；未登入 401；缺權限或沒有公司上下文 403 COMMON.PERMISSION.DENIED；已登入請求的 X-Company-Id 不可存取（未授權、用戶公司關聯停用、公司停用）一律 403 COMMON.COMPANY.ACCESS_DENIED。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H29" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:79</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.25.6</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B30" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C30" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Role, Permission and Data Scope</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D30" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E30" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow authorized users to grant a user access to a company with roles, organization and default company.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F30" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G30" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">需 SYS.USER.EDIT；公司必須啟用；分店／部門必須屬於該公司且啟用；角色必須存在且啟用；角色整組取代；每位用戶最多一間預設公司（設定新預設會取消舊預設）。用戶不存在回 404。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H30" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:80</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="2" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">REQ_F4118.25.7</x:t>
         </x:is>
       </x:c>
-      <x:c r="B27" s="2" t="inlineStr">
+      <x:c r="B31" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Settings</x:t>
         </x:is>
       </x:c>
-      <x:c r="C27" s="2" t="inlineStr">
+      <x:c r="C31" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Role, Permission and Data Scope</x:t>
         </x:is>
       </x:c>
-      <x:c r="D27" s="2" t="inlineStr">
+      <x:c r="D31" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="E27" s="2" t="inlineStr">
+      <x:c r="E31" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">System should resolve the user's effective permissions and data scope per company and hide unauthorized UI.</x:t>
         </x:is>
       </x:c>
-      <x:c r="F27" s="2" t="inlineStr">
+      <x:c r="F31" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Developer</x:t>
         </x:is>
       </x:c>
-      <x:c r="G27" s="2" t="inlineStr">
+      <x:c r="G31" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">同一權限取各啟用角色最寬的資料範圍；全權角色視為全部權限、全公司範圍；分店／部門範圍但用戶無對應歸屬時退回本人。GET /api/v1/sys/auth/authorization 回傳可存取公司（預設在前）與目前公司權限；前端 *erpHasPermission、permissionGuard 與選單依此隱藏，切換公司重新載入；本機記住的公司不可存取時改用預設公司。</x:t>
         </x:is>
       </x:c>
-      <x:c r="H27" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:77</x:t>
+      <x:c r="H31" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:81</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -2276,7 +2444,7 @@
       </x:c>
       <x:c r="F4" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.23.1, REQ_F4118.23.2, REQ_F4118.23.3, REQ_F4118.23.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.23.1, REQ_F4118.23.2, REQ_F4118.23.3, REQ_F4118.23.4, REQ_F4118.23.5, REQ_F4118.23.6, REQ_F4118.23.7, REQ_F4118.23.8</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -2404,7 +2572,7 @@
       </x:c>
       <x:c r="F8" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.25.5, REQ_F4118.25.6, REQ_F4118.25.7</x:t>
+          <x:t xml:space="preserve">REQ_F4118.23.5, REQ_F4118.23.6, REQ_F4118.25.5, REQ_F4118.25.6, REQ_F4118.25.7</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -2450,7 +2618,7 @@
     <x:col min="1" max="1" width="16" customWidth="1"/>
     <x:col min="2" max="2" width="15" customWidth="1"/>
     <x:col min="3" max="3" width="32" customWidth="1"/>
-    <x:col min="4" max="4" width="30" customWidth="1"/>
+    <x:col min="4" max="4" width="32" customWidth="1"/>
     <x:col min="5" max="5" width="13" customWidth="1"/>
     <x:col min="6" max="6" width="23" customWidth="1"/>
     <x:col min="7" max="7" width="40" customWidth="1"/>
@@ -2840,7 +3008,7 @@
       </x:c>
       <x:c r="H7" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">3–100 字元，字母／數字／點／底線／連字號</x:t>
+          <x:t xml:space="preserve">去除前後空白後 3–100 字元，字母／數字／點／底線／連字號；不分大小寫唯一</x:t>
         </x:is>
       </x:c>
       <x:c r="I7" s="2" t="inlineStr">
@@ -2892,17 +3060,17 @@
       </x:c>
       <x:c r="G8" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Password text</x:t>
+          <x:t xml:space="preserve">Password，autocomplete=new-password</x:t>
         </x:is>
       </x:c>
       <x:c r="H8" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">預設 12–128 字元</x:t>
+          <x:t xml:space="preserve">必填，最多 128 字元；其餘依政策（預設 12 字元以上，含大小寫、數字、符號），不符時顯示政策說明</x:t>
         </x:is>
       </x:c>
       <x:c r="I8" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">None</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.61.3</x:t>
         </x:is>
       </x:c>
       <x:c r="J8" s="2" t="inlineStr">
@@ -2919,47 +3087,47 @@
     <x:row r="9">
       <x:c r="A9" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.62.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.61.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B9" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.62</x:t>
+          <x:t xml:space="preserve">4.4.1.8.61</x:t>
         </x:is>
       </x:c>
       <x:c r="C9" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Login Interface</x:t>
+          <x:t xml:space="preserve">User Identity Create Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D9" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Username (Input)</x:t>
+          <x:t xml:space="preserve">Confirm Password (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E9" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">帳號</x:t>
+          <x:t xml:space="preserve">確認密碼</x:t>
         </x:is>
       </x:c>
       <x:c r="F9" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">登入身分</x:t>
+          <x:t xml:space="preserve">防止輸入錯誤</x:t>
         </x:is>
       </x:c>
       <x:c r="G9" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Text，autocomplete=username</x:t>
+          <x:t xml:space="preserve">Password</x:t>
         </x:is>
       </x:c>
       <x:c r="H9" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">必填、非空白，最多 100 字元；送出前去除前後空白</x:t>
+          <x:t xml:space="preserve">須與密碼相同</x:t>
         </x:is>
       </x:c>
       <x:c r="I9" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">None</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.61.2</x:t>
         </x:is>
       </x:c>
       <x:c r="J9" s="2" t="inlineStr">
@@ -2976,7 +3144,7 @@
     <x:row r="10">
       <x:c r="A10" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.62.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.62.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B10" s="2" t="inlineStr">
@@ -2991,27 +3159,27 @@
       </x:c>
       <x:c r="D10" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Password (Input)</x:t>
+          <x:t xml:space="preserve">Username (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E10" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">密碼</x:t>
+          <x:t xml:space="preserve">帳號</x:t>
         </x:is>
       </x:c>
       <x:c r="F10" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">驗證身分</x:t>
+          <x:t xml:space="preserve">登入身分</x:t>
         </x:is>
       </x:c>
       <x:c r="G10" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Password，autocomplete=current-password</x:t>
+          <x:t xml:space="preserve">Text，autocomplete=username</x:t>
         </x:is>
       </x:c>
       <x:c r="H10" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">必填，最多 128 字元；失敗後清空</x:t>
+          <x:t xml:space="preserve">必填、非空白，最多 100 字元；送出前去除前後空白</x:t>
         </x:is>
       </x:c>
       <x:c r="I10" s="2" t="inlineStr">
@@ -3033,7 +3201,7 @@
     <x:row r="11">
       <x:c r="A11" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.62.3</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.62.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B11" s="2" t="inlineStr">
@@ -3048,32 +3216,32 @@
       </x:c>
       <x:c r="D11" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Captcha Code (Input)</x:t>
+          <x:t xml:space="preserve">Password (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E11" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">驗證碼</x:t>
+          <x:t xml:space="preserve">密碼</x:t>
         </x:is>
       </x:c>
       <x:c r="F11" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">防自動化登入</x:t>
+          <x:t xml:space="preserve">驗證身分</x:t>
         </x:is>
       </x:c>
       <x:c r="G11" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">數字，inputmode=numeric</x:t>
+          <x:t xml:space="preserve">Password，autocomplete=current-password</x:t>
         </x:is>
       </x:c>
       <x:c r="H11" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4–6 位數字（非數字自動移除）</x:t>
+          <x:t xml:space="preserve">必填，最多 128 字元；失敗後清空</x:t>
         </x:is>
       </x:c>
       <x:c r="I11" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.62.4</x:t>
+          <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
       <x:c r="J11" s="2" t="inlineStr">
@@ -3090,47 +3258,47 @@
     <x:row r="12">
       <x:c r="A12" s="2" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.62.3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B12" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.62</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C12" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Login Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D12" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Captcha Code (Input)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E12" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">驗證碼</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F12" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">防自動化登入</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G12" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">數字，inputmode=numeric</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H12" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4–6 位數字（非數字自動移除）</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I12" s="2" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">REQ_IO_A8.62.4</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B12" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">4.4.1.8.62</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C12" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Login Interface</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D12" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Captcha Image (Button)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E12" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">驗證碼圖片</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F12" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">顯示題目，點擊換圖</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G12" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SVG data URI</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H12" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">每次送出失敗後自動換新</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I12" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
       <x:c r="J12" s="2" t="inlineStr">
@@ -3147,7 +3315,7 @@
     <x:row r="13">
       <x:c r="A13" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.62.5</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.62.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B13" s="2" t="inlineStr">
@@ -3162,27 +3330,27 @@
       </x:c>
       <x:c r="D13" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Sign In (Button)</x:t>
+          <x:t xml:space="preserve">Captcha Image (Button)</x:t>
         </x:is>
       </x:c>
       <x:c r="E13" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">登入</x:t>
+          <x:t xml:space="preserve">驗證碼圖片</x:t>
         </x:is>
       </x:c>
       <x:c r="F13" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">送出</x:t>
+          <x:t xml:space="preserve">顯示題目，點擊換圖</x:t>
         </x:is>
       </x:c>
       <x:c r="G13" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Button</x:t>
+          <x:t xml:space="preserve">SVG data URI</x:t>
         </x:is>
       </x:c>
       <x:c r="H13" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">送出中顯示載入狀態，不可重複送出</x:t>
+          <x:t xml:space="preserve">每次送出失敗後自動換新</x:t>
         </x:is>
       </x:c>
       <x:c r="I13" s="2" t="inlineStr">
@@ -3204,55 +3372,397 @@
     <x:row r="14">
       <x:c r="A14" s="2" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.62.5</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B14" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.62</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C14" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Login Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D14" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Sign In (Button)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E14" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">登入</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F14" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">送出</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G14" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Button</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H14" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">送出中顯示載入狀態，不可重複送出</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I14" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J14" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K14" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="2" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">REQ_IO_A8.62.6</x:t>
         </x:is>
       </x:c>
-      <x:c r="B14" s="2" t="inlineStr">
+      <x:c r="B15" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">4.4.1.8.62</x:t>
         </x:is>
       </x:c>
-      <x:c r="C14" s="2" t="inlineStr">
+      <x:c r="C15" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Login Interface</x:t>
         </x:is>
       </x:c>
-      <x:c r="D14" s="2" t="inlineStr">
+      <x:c r="D15" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Error Message (Alert)</x:t>
         </x:is>
       </x:c>
-      <x:c r="E14" s="2" t="inlineStr">
+      <x:c r="E15" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">錯誤訊息</x:t>
         </x:is>
       </x:c>
-      <x:c r="F14" s="2" t="inlineStr">
+      <x:c r="F15" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">顯示 errors.&lt;errorCode&gt;</x:t>
         </x:is>
       </x:c>
-      <x:c r="G14" s="2" t="inlineStr">
+      <x:c r="G15" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Text</x:t>
         </x:is>
       </x:c>
-      <x:c r="H14" s="2" t="inlineStr">
+      <x:c r="H15" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">INVALID_CREDENTIALS／CAPTCHA_INVALID／PASSWORD_EXPIRED／VALIDATION_FAILED／網路／未知</x:t>
         </x:is>
       </x:c>
-      <x:c r="I14" s="2" t="inlineStr">
+      <x:c r="I15" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
-      <x:c r="J14" s="2" t="inlineStr">
+      <x:c r="J15" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="K14" s="2" t="inlineStr">
+      <x:c r="K15" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.63.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B16" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.63</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C16" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">User Maintenance Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D16" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Keyword (Input)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E16" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">搜尋帳號</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F16" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">篩選列表</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G16" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Text</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H16" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">去除前後空白，不分大小寫</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I16" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J16" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K16" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.63.2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B17" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.63</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C17" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">User Maintenance Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D17" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Status (Tag)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E17" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">狀態</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F17" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">顯示啟用、鎖定、密碼過期</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G17" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Tag</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H17" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">啟用／停用；已鎖定；密碼已過期</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I17" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J17" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K17" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.63.3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B18" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.63</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C18" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">User Maintenance Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D18" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Activate / Deactivate (Button)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E18" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">啟用／停用</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F18" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">切換帳號狀態</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G18" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Button</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H18" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">帶讀取時的 version；不可停用自己</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I18" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J18" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K18" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.63.4</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B19" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.63</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C19" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">User Maintenance Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D19" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Unlock (Button)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E19" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">解鎖</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F19" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">清除鎖定</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G19" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Button</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H19" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">只在已鎖定時顯示</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I19" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J19" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K19" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.63.5</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B20" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.63</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C20" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">User Maintenance Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D20" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Reset Password (Button)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E20" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">重設密碼</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F20" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">開啟重設對話框</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G20" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Button</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H20" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">新密碼依政策驗證，成功後清除鎖定並重新起算到期</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I20" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.61.2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J20" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K20" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Developer</x:t>
         </x:is>
@@ -3709,7 +4219,7 @@
       </x:c>
       <x:c r="F12" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-USER-001, SYS-USER-004, SYS-USER-006</x:t>
+          <x:t xml:space="preserve">SYS-USER-001, SYS-USER-004, SYS-USER-012</x:t>
         </x:is>
       </x:c>
       <x:c r="G12" s="2" t="inlineStr">
@@ -3741,12 +4251,12 @@
       </x:c>
       <x:c r="E13" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.61.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.61.2, REQ_IO_A8.61.3</x:t>
         </x:is>
       </x:c>
       <x:c r="F13" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-USER-001, SYS-USER-007, SYS-USER-006</x:t>
+          <x:t xml:space="preserve">SYS-USER-001, SYS-USER-007, SYS-USER-012</x:t>
         </x:is>
       </x:c>
       <x:c r="G13" s="2" t="inlineStr">
@@ -3783,7 +4293,7 @@
       </x:c>
       <x:c r="F14" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-USER-002, SYS-USER-003, SYS-USER-005, SYS-USER-006</x:t>
+          <x:t xml:space="preserve">SYS-USER-002, SYS-USER-003, SYS-USER-005, SYS-USER-014</x:t>
         </x:is>
       </x:c>
       <x:c r="G14" s="2" t="inlineStr">
@@ -3820,7 +4330,7 @@
       </x:c>
       <x:c r="F15" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-USER-003, SYS-USER-006</x:t>
+          <x:t xml:space="preserve">SYS-USER-003</x:t>
         </x:is>
       </x:c>
       <x:c r="G15" s="2" t="inlineStr">
@@ -3832,160 +4342,160 @@
     <x:row r="16">
       <x:c r="A16" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.24.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.23.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B16" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow a user to log in with username, password and a numeric captcha.</x:t>
+          <x:t xml:space="preserve">System should list the users of the current company with paging, keyword and sorting.</x:t>
         </x:is>
       </x:c>
       <x:c r="C16" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_DS43.82, REQ_DS43.92</x:t>
         </x:is>
       </x:c>
       <x:c r="D16" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.62</x:t>
+          <x:t xml:space="preserve">4.4.1.8.63</x:t>
         </x:is>
       </x:c>
       <x:c r="E16" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.62.1, REQ_IO_A8.62.2, REQ_IO_A8.62.3, REQ_IO_A8.62.4</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.63.1, REQ_IO_A8.63.2</x:t>
         </x:is>
       </x:c>
       <x:c r="F16" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-AUTH-001, SYS-AUTH-002, SYS-AUTH-005, SYS-AUTH-006, SYS-AUTH-009, SYS-AUTH-014, SYS-AUTH-015, SYS-AUTH-016, SYS-AUTH-017</x:t>
+          <x:t xml:space="preserve">SYS-USER-006, SYS-USER-010, SYS-USER-011, SYS-USER-015</x:t>
         </x:is>
       </x:c>
       <x:c r="G16" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.24.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.23.6</x:t>
         </x:is>
       </x:c>
       <x:c r="B17" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should issue a 15-minute access token and a 7-day rotating refresh token.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to create a user in the current company.</x:t>
         </x:is>
       </x:c>
       <x:c r="C17" s="2" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">REQ_DS43.82, REQ_DS43.92</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D17" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.61</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E17" s="2" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
-      <x:c r="D17" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="E17" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
       <x:c r="F17" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-AUTH-001, SYS-AUTH-004, SYS-AUTH-007, SYS-AUTH-009, SYS-AUTH-010, SYS-AUTH-016, SYS-AUTH-017</x:t>
+          <x:t xml:space="preserve">SYS-USER-006, SYS-USER-010, SYS-USER-011, SYS-USER-012</x:t>
         </x:is>
       </x:c>
       <x:c r="G17" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.24.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.23.7</x:t>
         </x:is>
       </x:c>
       <x:c r="B18" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow a logged-in user to log out and invalidate the refresh token.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to activate or deactivate a user.</x:t>
         </x:is>
       </x:c>
       <x:c r="C18" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_DS43.82</x:t>
         </x:is>
       </x:c>
       <x:c r="D18" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">4.4.1.8.63</x:t>
         </x:is>
       </x:c>
       <x:c r="E18" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.63.3</x:t>
         </x:is>
       </x:c>
       <x:c r="F18" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-AUTH-008, SYS-AUTH-016, SYS-AUTH-017</x:t>
+          <x:t xml:space="preserve">SYS-USER-006, SYS-USER-010, SYS-USER-013, SYS-USER-015</x:t>
         </x:is>
       </x:c>
       <x:c r="G18" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.24.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.23.8</x:t>
         </x:is>
       </x:c>
       <x:c r="B19" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should provide a development-only captcha master code with startup protection.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to reset a password and unlock a locked user.</x:t>
         </x:is>
       </x:c>
       <x:c r="C19" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_DS43.82</x:t>
         </x:is>
       </x:c>
       <x:c r="D19" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">4.4.1.8.63</x:t>
         </x:is>
       </x:c>
       <x:c r="E19" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.63.4, REQ_IO_A8.63.5</x:t>
         </x:is>
       </x:c>
       <x:c r="F19" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-AUTH-003, SYS-AUTH-004, SYS-AUTH-016, SYS-AUTH-017</x:t>
+          <x:t xml:space="preserve">SYS-USER-006, SYS-USER-010, SYS-USER-014</x:t>
         </x:is>
       </x:c>
       <x:c r="G19" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.24.5</x:t>
+          <x:t xml:space="preserve">REQ_F4118.24.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B20" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should provide a trilingual login page that keeps the session and refreshes tokens automatically.</x:t>
+          <x:t xml:space="preserve">System should allow a user to log in with username, password and a numeric captcha.</x:t>
         </x:is>
       </x:c>
       <x:c r="C20" s="2" t="inlineStr">
@@ -4000,12 +4510,12 @@
       </x:c>
       <x:c r="E20" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.62.5, REQ_IO_A8.62.6</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.62.1, REQ_IO_A8.62.2, REQ_IO_A8.62.3, REQ_IO_A8.62.4</x:t>
         </x:is>
       </x:c>
       <x:c r="F20" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-AUTH-011, SYS-AUTH-012, SYS-AUTH-013, SYS-AUTH-015, SYS-AUTH-016, SYS-AUTH-017</x:t>
+          <x:t xml:space="preserve">SYS-AUTH-001, SYS-AUTH-002, SYS-AUTH-005, SYS-AUTH-006, SYS-AUTH-009, SYS-AUTH-014, SYS-AUTH-015, SYS-AUTH-016, SYS-AUTH-017</x:t>
         </x:is>
       </x:c>
       <x:c r="G20" s="2" t="inlineStr">
@@ -4017,17 +4527,17 @@
     <x:row r="21">
       <x:c r="A21" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.25.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.24.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B21" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to view roles and the permission catalog.</x:t>
+          <x:t xml:space="preserve">System should issue a 15-minute access token and a 7-day rotating refresh token.</x:t>
         </x:is>
       </x:c>
       <x:c r="C21" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.90</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="D21" s="2" t="inlineStr">
@@ -4042,7 +4552,7 @@
       </x:c>
       <x:c r="F21" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-PERM-004, SYS-PERM-011, SYS-PERM-024</x:t>
+          <x:t xml:space="preserve">SYS-AUTH-001, SYS-AUTH-004, SYS-AUTH-007, SYS-AUTH-009, SYS-AUTH-010, SYS-AUTH-016, SYS-AUTH-017</x:t>
         </x:is>
       </x:c>
       <x:c r="G21" s="2" t="inlineStr">
@@ -4054,17 +4564,17 @@
     <x:row r="22">
       <x:c r="A22" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.25.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.24.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B22" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to create a role with permissions and a data scope.</x:t>
+          <x:t xml:space="preserve">System should allow a logged-in user to log out and invalidate the refresh token.</x:t>
         </x:is>
       </x:c>
       <x:c r="C22" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.90, REQ_DS43.91</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="D22" s="2" t="inlineStr">
@@ -4079,7 +4589,7 @@
       </x:c>
       <x:c r="F22" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-PERM-011, SYS-PERM-024</x:t>
+          <x:t xml:space="preserve">SYS-AUTH-008, SYS-AUTH-016, SYS-AUTH-017</x:t>
         </x:is>
       </x:c>
       <x:c r="G22" s="2" t="inlineStr">
@@ -4091,17 +4601,17 @@
     <x:row r="23">
       <x:c r="A23" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.25.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.24.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B23" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to edit or deactivate a role.</x:t>
+          <x:t xml:space="preserve">System should provide a development-only captcha master code with startup protection.</x:t>
         </x:is>
       </x:c>
       <x:c r="C23" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.90, REQ_DS43.91</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="D23" s="2" t="inlineStr">
@@ -4116,7 +4626,7 @@
       </x:c>
       <x:c r="F23" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-PERM-011, SYS-PERM-024</x:t>
+          <x:t xml:space="preserve">SYS-AUTH-003, SYS-AUTH-004, SYS-AUTH-016, SYS-AUTH-017</x:t>
         </x:is>
       </x:c>
       <x:c r="G23" s="2" t="inlineStr">
@@ -4128,32 +4638,32 @@
     <x:row r="24">
       <x:c r="A24" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.25.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.24.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B24" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to delete an unused role.</x:t>
+          <x:t xml:space="preserve">System should provide a trilingual login page that keeps the session and refreshes tokens automatically.</x:t>
         </x:is>
       </x:c>
       <x:c r="C24" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.90</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="D24" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">4.4.1.8.62</x:t>
         </x:is>
       </x:c>
       <x:c r="E24" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.62.5, REQ_IO_A8.62.6</x:t>
         </x:is>
       </x:c>
       <x:c r="F24" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-PERM-012, SYS-PERM-024</x:t>
+          <x:t xml:space="preserve">SYS-AUTH-011, SYS-AUTH-012, SYS-AUTH-013, SYS-AUTH-015, SYS-AUTH-016, SYS-AUTH-017</x:t>
         </x:is>
       </x:c>
       <x:c r="G24" s="2" t="inlineStr">
@@ -4165,17 +4675,17 @@
     <x:row r="25">
       <x:c r="A25" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.25.5</x:t>
+          <x:t xml:space="preserve">REQ_F4118.25.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B25" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enforce permission codes on every API with the backend as the authority.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to view roles and the permission catalog.</x:t>
         </x:is>
       </x:c>
       <x:c r="C25" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.92</x:t>
+          <x:t xml:space="preserve">REQ_DS43.90</x:t>
         </x:is>
       </x:c>
       <x:c r="D25" s="2" t="inlineStr">
@@ -4190,7 +4700,7 @@
       </x:c>
       <x:c r="F25" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-PERM-001, SYS-PERM-005, SYS-PERM-006, SYS-PERM-010</x:t>
+          <x:t xml:space="preserve">SYS-PERM-004, SYS-PERM-011, SYS-PERM-024</x:t>
         </x:is>
       </x:c>
       <x:c r="G25" s="2" t="inlineStr">
@@ -4202,17 +4712,17 @@
     <x:row r="26">
       <x:c r="A26" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.25.6</x:t>
+          <x:t xml:space="preserve">REQ_F4118.25.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B26" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to grant a user access to a company with roles, organization and default company.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to create a role with permissions and a data scope.</x:t>
         </x:is>
       </x:c>
       <x:c r="C26" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.92, REQ_DS43.93</x:t>
+          <x:t xml:space="preserve">REQ_DS43.90, REQ_DS43.91</x:t>
         </x:is>
       </x:c>
       <x:c r="D26" s="2" t="inlineStr">
@@ -4227,7 +4737,7 @@
       </x:c>
       <x:c r="F26" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-PERM-015, SYS-PERM-016, SYS-PERM-024</x:t>
+          <x:t xml:space="preserve">SYS-PERM-011, SYS-PERM-024</x:t>
         </x:is>
       </x:c>
       <x:c r="G26" s="2" t="inlineStr">
@@ -4239,35 +4749,183 @@
     <x:row r="27">
       <x:c r="A27" s="2" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">REQ_F4118.25.3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B27" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow authorized users to edit or deactivate a role.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C27" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.90, REQ_DS43.91</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D27" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="E27" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F27" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-PERM-011, SYS-PERM-024</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G27" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Partial</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.25.4</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B28" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow authorized users to delete an unused role.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C28" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.90</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D28" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="E28" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F28" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-PERM-012, SYS-PERM-024</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G28" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Partial</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.25.5</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B29" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should enforce permission codes on every API with the backend as the authority.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C29" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.92</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D29" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="E29" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F29" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-PERM-001, SYS-PERM-005, SYS-PERM-006, SYS-PERM-010</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G29" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Partial</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.25.6</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B30" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow authorized users to grant a user access to a company with roles, organization and default company.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C30" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.92, REQ_DS43.93</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D30" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="E30" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F30" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-PERM-015, SYS-PERM-016, SYS-PERM-024</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G30" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Partial</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="2" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">REQ_F4118.25.7</x:t>
         </x:is>
       </x:c>
-      <x:c r="B27" s="2" t="inlineStr">
+      <x:c r="B31" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">System should resolve the user's effective permissions and data scope per company and hide unauthorized UI.</x:t>
         </x:is>
       </x:c>
-      <x:c r="C27" s="2" t="inlineStr">
+      <x:c r="C31" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">REQ_DS43.91, REQ_DS43.92, REQ_DS43.93</x:t>
         </x:is>
       </x:c>
-      <x:c r="D27" s="2" t="inlineStr">
+      <x:c r="D31" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
-      <x:c r="E27" s="2" t="inlineStr">
+      <x:c r="E31" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
-      <x:c r="F27" s="2" t="inlineStr">
+      <x:c r="F31" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">SYS-PERM-002, SYS-PERM-003, SYS-PERM-013, SYS-PERM-014, SYS-PERM-020, SYS-PERM-021, SYS-PERM-022, SYS-PERM-023</x:t>
         </x:is>
       </x:c>
-      <x:c r="G27" s="2" t="inlineStr">
+      <x:c r="G31" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Partial</x:t>
         </x:is>

--- a/docs/99-output/MyERP_Requirements.xlsx
+++ b/docs/99-output/MyERP_Requirements.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="1" r:id="R23b7dea85ff1444a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Non-Functional" sheetId="2" r:id="R54dee6920b864470"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Structure" sheetId="3" r:id="R6389d2a2b1af49b5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interface" sheetId="4" r:id="Ra10c7500e3ab4d9e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traceability Matrix" sheetId="5" r:id="R0d010cc04a25480c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BlueWhale Parity" sheetId="6" r:id="Reb09fd7f186f4200"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timeline" sheetId="7" r:id="R31275a1f3f7f48a7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Human Resources" sheetId="8" r:id="R22dc2e391ce54910"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="9" r:id="Rdeff01a5e27d4fc9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="1" r:id="R3d774857c42f45a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Non-Functional" sheetId="2" r:id="Rc7f5663132064e7a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Structure" sheetId="3" r:id="R309afbf6b838471e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interface" sheetId="4" r:id="R57122998222b4ce0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traceability Matrix" sheetId="5" r:id="R2e150bdb38594b7d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BlueWhale Parity" sheetId="6" r:id="R370a3df8acf24061"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timeline" sheetId="7" r:id="Ra29eb8a22c69427f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Human Resources" sheetId="8" r:id="Rcfe04b2e8a5f4caf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="9" r:id="Redfc728c80a040fa"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -68,7 +68,7 @@
     <x:col min="5" max="5" width="60" customWidth="1"/>
     <x:col min="6" max="6" width="11" customWidth="1"/>
     <x:col min="7" max="7" width="60" customWidth="1"/>
-    <x:col min="8" max="8" width="40" customWidth="1"/>
+    <x:col min="8" max="8" width="41" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -1322,7 +1322,7 @@
       </x:c>
       <x:c r="G30" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">需 SYS.USER.EDIT；公司必須啟用；分店／部門必須屬於該公司且啟用；角色必須存在且啟用；角色整組取代；每位用戶最多一間預設公司（設定新預設會取消舊預設）。用戶不存在回 404。</x:t>
+          <x:t xml:space="preserve">需 SYS.USER.EDIT；公司必須啟用；分店／部門必須屬於該公司且啟用；角色必須存在且啟用；角色整組取代；每位用戶最多一間預設公司（設定新預設會取消舊預設）。用戶不存在或不屬於目前公司回 404 SYS.USER.NOT_FOUND；目標公司不是操作者獲授權的公司回 404 SYS.COMPANY.NOT_FOUND；不可停用自己的公司授權（422 SYS.USER.SELF_DEACTIVATION）（ADR-017）。</x:t>
         </x:is>
       </x:c>
       <x:c r="H30" s="2" t="inlineStr">
@@ -1370,6 +1370,342 @@
       <x:c r="H31" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:81</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.25.8</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B32" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C32" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Role, Permission and Data Scope</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D32" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E32" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow authorized users to view a user's company access, organization and roles.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F32" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G32" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">需 SYS.USER.VIEW；用戶須屬於目前公司，否則 404；只列出操作者獲授權公司的指派（公司代碼／名稱、分店、部門、預設、啟用、角色 ID），依公司代碼排序（ADR-017）。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H32" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:82</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.26.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B33" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C33" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Web Security Middleware</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D33" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E33" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should enforce HTTPS with HSTS outside the development environment.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F33" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G33" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">非 Development：HTTP 請求 307 轉 HTTPS；HTTPS 回應帶 Strict-Transport-Security: max-age=31536000; includeSubDomains（天數可設定）。Development 不轉址、不送 HSTS。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H33" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:96</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.26.2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B34" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C34" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Web Security Middleware</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D34" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E34" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow cross-origin requests only from configured frontend origins.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F34" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G34" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">來源清單在 Security:Cors:AllowedOrigins，預設空（不允許跨來源）；只接受 scheme://host[:port]，萬用字元、含路徑或非 http(s) 拒絕啟動；不允許 Credentials；允許標頭 Authorization、Content-Type、Accept、Accept-Language、X-Company-Id；公開 Retry-After、Content-Disposition；未列明的來源預檢回應不含 Access-Control-Allow-Origin。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H34" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:97</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.26.3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B35" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C35" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Web Security Middleware</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D35" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E35" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should rate-limit login, token refresh and captcha requests per client IP.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F35" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G35" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">登入、Token 刷新每 IP 每端點每分鐘 5 次；Captcha 每 IP 每分鐘 10 次（ADR-018）；超過回 429 ProblemDetails，errorCode 為 COMMON.REQUEST.RATE_LIMITED，標題依 Accept-Language 三語，帶 Retry-After；寫 Warning 日誌（方法、路徑、IP）。CORS 預檢不計入。每個匿名端點必須套用按 IP 的限流政策（ArchitectureTests 檢查）。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H35" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:98</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.26.4</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B36" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C36" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Web Security Middleware</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D36" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E36" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should rate-limit authenticated API requests per user.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F36" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G36" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">已登入請求每用戶每分鐘 300 次（可設定），不同用戶分開計數；匯出報表政策每用戶每分鐘 10 次，供日後匯出端點套用。白名單內的 IP 仍受限流。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H36" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:99</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.26.5</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B37" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C37" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Web Security Middleware</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D37" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E37" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should add security headers to every API response.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F37" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G37" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">所有回應（含 404、429、500）帶 X-Content-Type-Options: nosniff、X-Frame-Options: DENY、Referrer-Policy: no-referrer、Content-Security-Policy: default-src 'none'; frame-ancestors 'none'; base-uri 'none'; form-action 'none'。前端站台的 CSP 見 architecture/security.md，E2E 在該 CSP 下執行。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H37" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:100</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.26.6</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B38" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C38" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Web Security Middleware</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D38" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E38" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should honour X-Forwarded-For only from configured proxies.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F38" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G38" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Security:ForwardedHeaders:KnownProxies（IP）與 KnownNetworks（CIDR）皆空時不處理 X-Forwarded-*；有設定時只信任列明來源，其他來源偽造的 X-Forwarded-For 被忽略，限流與日誌使用連線 IP；格式錯誤拒絕啟動。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H38" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:101</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.26.7</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B39" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C39" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Web Security Middleware</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D39" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E39" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should show a trilingual "too many requests" message when an API call is rate-limited.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F39" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G39" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">前端收到 429 一律顯示 errors.COMMON.REQUEST.RATE_LIMITED（三語），登入頁、組織、用戶、角色頁共用 apiErrorKey。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H39" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:102</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -1437,7 +1773,7 @@
       </x:c>
       <x:c r="E2" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/01-architecture/architecture.md:184</x:t>
+          <x:t xml:space="preserve">docs/01-architecture/architecture.md:186</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -1464,7 +1800,7 @@
       </x:c>
       <x:c r="E3" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/01-architecture/architecture.md:185</x:t>
+          <x:t xml:space="preserve">docs/01-architecture/architecture.md:187</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -1491,7 +1827,7 @@
       </x:c>
       <x:c r="E4" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/01-architecture/architecture.md:186</x:t>
+          <x:t xml:space="preserve">docs/01-architecture/architecture.md:188</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -1518,7 +1854,7 @@
       </x:c>
       <x:c r="E5" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/01-architecture/architecture.md:187</x:t>
+          <x:t xml:space="preserve">docs/01-architecture/architecture.md:189</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -1545,7 +1881,7 @@
       </x:c>
       <x:c r="E6" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/01-architecture/architecture.md:188</x:t>
+          <x:t xml:space="preserve">docs/01-architecture/architecture.md:190</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -1572,7 +1908,7 @@
       </x:c>
       <x:c r="E7" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/01-architecture/architecture.md:189</x:t>
+          <x:t xml:space="preserve">docs/01-architecture/architecture.md:191</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -1599,7 +1935,7 @@
       </x:c>
       <x:c r="E8" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/01-architecture/architecture.md:190</x:t>
+          <x:t xml:space="preserve">docs/01-architecture/architecture.md:192</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -1626,7 +1962,7 @@
       </x:c>
       <x:c r="E9" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/01-architecture/architecture.md:196</x:t>
+          <x:t xml:space="preserve">docs/01-architecture/architecture.md:198</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -1653,7 +1989,7 @@
       </x:c>
       <x:c r="E10" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/01-architecture/architecture.md:197</x:t>
+          <x:t xml:space="preserve">docs/01-architecture/architecture.md:199</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -1680,7 +2016,7 @@
       </x:c>
       <x:c r="E11" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/01-architecture/architecture.md:198</x:t>
+          <x:t xml:space="preserve">docs/01-architecture/architecture.md:200</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -1707,7 +2043,7 @@
       </x:c>
       <x:c r="E12" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/01-architecture/architecture.md:199</x:t>
+          <x:t xml:space="preserve">docs/01-architecture/architecture.md:201</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -1734,7 +2070,7 @@
       </x:c>
       <x:c r="E13" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/01-architecture/architecture.md:200</x:t>
+          <x:t xml:space="preserve">docs/01-architecture/architecture.md:202</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -1761,7 +2097,7 @@
       </x:c>
       <x:c r="E14" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/01-architecture/architecture.md:201</x:t>
+          <x:t xml:space="preserve">docs/01-architecture/architecture.md:203</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -1788,7 +2124,7 @@
       </x:c>
       <x:c r="E15" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/01-architecture/architecture.md:202</x:t>
+          <x:t xml:space="preserve">docs/01-architecture/architecture.md:204</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -1815,7 +2151,7 @@
       </x:c>
       <x:c r="E16" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/01-architecture/architecture.md:203</x:t>
+          <x:t xml:space="preserve">docs/01-architecture/architecture.md:205</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -1842,7 +2178,7 @@
       </x:c>
       <x:c r="E17" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/01-architecture/architecture.md:204</x:t>
+          <x:t xml:space="preserve">docs/01-architecture/architecture.md:206</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -1869,7 +2205,7 @@
       </x:c>
       <x:c r="E18" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/01-architecture/architecture.md:210</x:t>
+          <x:t xml:space="preserve">docs/01-architecture/architecture.md:212</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -1896,7 +2232,7 @@
       </x:c>
       <x:c r="E19" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/01-architecture/architecture.md:211</x:t>
+          <x:t xml:space="preserve">docs/01-architecture/architecture.md:213</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -1923,7 +2259,7 @@
       </x:c>
       <x:c r="E20" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/01-architecture/architecture.md:212</x:t>
+          <x:t xml:space="preserve">docs/01-architecture/architecture.md:214</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -1950,7 +2286,7 @@
       </x:c>
       <x:c r="E21" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/01-architecture/architecture.md:213</x:t>
+          <x:t xml:space="preserve">docs/01-architecture/architecture.md:215</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -1977,7 +2313,7 @@
       </x:c>
       <x:c r="E22" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/01-architecture/architecture.md:214</x:t>
+          <x:t xml:space="preserve">docs/01-architecture/architecture.md:216</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -2004,7 +2340,7 @@
       </x:c>
       <x:c r="E23" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/01-architecture/architecture.md:215</x:t>
+          <x:t xml:space="preserve">docs/01-architecture/architecture.md:217</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -2031,7 +2367,7 @@
       </x:c>
       <x:c r="E24" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/01-architecture/architecture.md:221</x:t>
+          <x:t xml:space="preserve">docs/01-architecture/architecture.md:223</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -2058,7 +2394,7 @@
       </x:c>
       <x:c r="E25" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/01-architecture/architecture.md:222</x:t>
+          <x:t xml:space="preserve">docs/01-architecture/architecture.md:224</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -2085,7 +2421,7 @@
       </x:c>
       <x:c r="E26" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/01-architecture/architecture.md:223</x:t>
+          <x:t xml:space="preserve">docs/01-architecture/architecture.md:225</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -2112,7 +2448,7 @@
       </x:c>
       <x:c r="E27" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/01-architecture/architecture.md:224</x:t>
+          <x:t xml:space="preserve">docs/01-architecture/architecture.md:226</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -2139,7 +2475,7 @@
       </x:c>
       <x:c r="E28" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/01-architecture/architecture.md:225</x:t>
+          <x:t xml:space="preserve">docs/01-architecture/architecture.md:227</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -2166,7 +2502,7 @@
       </x:c>
       <x:c r="E29" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/01-architecture/architecture.md:231</x:t>
+          <x:t xml:space="preserve">docs/01-architecture/architecture.md:233</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -2193,7 +2529,7 @@
       </x:c>
       <x:c r="E30" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/01-architecture/architecture.md:232</x:t>
+          <x:t xml:space="preserve">docs/01-architecture/architecture.md:234</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -2220,7 +2556,7 @@
       </x:c>
       <x:c r="E31" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/01-architecture/architecture.md:233</x:t>
+          <x:t xml:space="preserve">docs/01-architecture/architecture.md:235</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -2247,7 +2583,7 @@
       </x:c>
       <x:c r="E32" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/01-architecture/architecture.md:234</x:t>
+          <x:t xml:space="preserve">docs/01-architecture/architecture.md:236</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -2274,7 +2610,7 @@
       </x:c>
       <x:c r="E33" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/01-architecture/architecture.md:235</x:t>
+          <x:t xml:space="preserve">docs/01-architecture/architecture.md:237</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -2301,7 +2637,7 @@
       </x:c>
       <x:c r="E34" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/01-architecture/architecture.md:236</x:t>
+          <x:t xml:space="preserve">docs/01-architecture/architecture.md:238</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -2572,7 +2908,7 @@
       </x:c>
       <x:c r="F8" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.23.5, REQ_F4118.23.6, REQ_F4118.25.5, REQ_F4118.25.6, REQ_F4118.25.7</x:t>
+          <x:t xml:space="preserve">REQ_F4118.23.5, REQ_F4118.23.6, REQ_F4118.25.5, REQ_F4118.25.6, REQ_F4118.25.7, REQ_F4118.25.8</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -2604,7 +2940,7 @@
       </x:c>
       <x:c r="F9" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.25.6, REQ_F4118.25.7</x:t>
+          <x:t xml:space="preserve">REQ_F4118.25.6, REQ_F4118.25.7, REQ_F4118.25.8</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -2617,7 +2953,7 @@
   <x:cols>
     <x:col min="1" max="1" width="16" customWidth="1"/>
     <x:col min="2" max="2" width="15" customWidth="1"/>
-    <x:col min="3" max="3" width="32" customWidth="1"/>
+    <x:col min="3" max="3" width="54" customWidth="1"/>
     <x:col min="4" max="4" width="32" customWidth="1"/>
     <x:col min="5" max="5" width="13" customWidth="1"/>
     <x:col min="6" max="6" width="23" customWidth="1"/>
@@ -3763,6 +4099,633 @@
         </x:is>
       </x:c>
       <x:c r="K20" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.64.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B21" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.64</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C21" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Role Maintenance Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D21" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Role Code (Input)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E21" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">角色代碼</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F21" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">全系統唯一識別角色</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G21" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">VARCHAR(50)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H21" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1–50 字元；ASCII 英文、數字、-、_；保存為大寫；建立後不可修改</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I21" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J21" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K21" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.64.2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B22" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.64</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C22" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Role Maintenance Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D22" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Role Name (Input)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E22" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">角色名稱</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F22" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">顯示角色</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G22" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">NVARCHAR(200)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H22" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">去除空白後 1–200 字元</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I22" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J22" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K22" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.64.3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B23" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.64</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C23" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Role Maintenance Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D23" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Data Scope (Dropdown)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E23" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">資料範圍</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F23" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">決定可見單據範圍</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G23" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Self／Department／Branch／Company</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H23" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">必選，預設本人</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I23" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J23" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K23" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.64.4</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B24" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.64</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C24" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Role Maintenance Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D24" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Full Access (Checkbox)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E24" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">全權</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F24" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">擁有全部權限</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G24" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Boolean</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H24" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">勾選時權限清單停用</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I24" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.64.5</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J24" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K24" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.64.5</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B25" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.64</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C25" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Role Maintenance Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D25" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Permissions (Checkbox group)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E25" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">權限</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F25" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">依模組勾選權限代碼</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G25" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">模組.資源.動作</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H25" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">只可選權限目錄內的代碼；模組可全選</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I25" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.64.4</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J25" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K25" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.64.6</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B26" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.64</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C26" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Role Maintenance Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D26" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Delete (Button)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E26" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">刪除</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F26" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">軟刪除未使用的角色</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G26" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Button + popconfirm</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H26" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">帶 version；使用中回 SYS.ROLE.IN_USE</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I26" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J26" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K26" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.65.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B27" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.65</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C27" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">User Permission Edit Interface（BlueWhale 4.4.1.8.26）</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D27" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Company (Dropdown)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E27" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">公司</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F27" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">選擇要設定的公司</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G27" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">bigint ID</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H27" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">操作者可切換的公司</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I27" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.65.2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J27" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K27" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.65.2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B28" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.65</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C28" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">User Permission Edit Interface（BlueWhale 4.4.1.8.26）</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D28" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Branch / Department (Dropdown)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E28" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">分店／部門</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F28" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">組織歸屬（資料範圍用）</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G28" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">bigint ID，可清空</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H28" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">所選公司的啟用分店／部門</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I28" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.65.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J28" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K28" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.65.3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B29" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.65</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C29" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">User Permission Edit Interface（BlueWhale 4.4.1.8.26）</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D29" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Roles (Multi-select)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E29" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">角色</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F29" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">整組取代該公司的角色</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G29" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">bigint ID 陣列</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H29" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">啟用角色；可為空（無權限）</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I29" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J29" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K29" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.65.4</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B30" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.65</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C30" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">User Permission Edit Interface（BlueWhale 4.4.1.8.26）</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D30" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Default Company (Checkbox)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E30" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">預設公司</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F30" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">登入後預設的操作公司</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G30" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Boolean</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H30" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">設定後取消其他預設</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I30" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J30" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K30" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.65.5</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B31" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.65</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C31" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">User Permission Edit Interface（BlueWhale 4.4.1.8.26）</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D31" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Access Active (Checkbox)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E31" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">啟用存取</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F31" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">停用後該公司不授權</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G31" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Boolean</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H31" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">不可停用自己</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I31" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J31" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K31" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Developer</x:t>
         </x:is>
@@ -4690,22 +5653,22 @@
       </x:c>
       <x:c r="D25" s="2" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">4.4.1.8.64</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E25" s="2" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
-      <x:c r="E25" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
       <x:c r="F25" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-PERM-004, SYS-PERM-011, SYS-PERM-024</x:t>
+          <x:t xml:space="preserve">SYS-PERM-004, SYS-PERM-011, SYS-PERM-024, SYS-PERM-025</x:t>
         </x:is>
       </x:c>
       <x:c r="G25" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -4727,22 +5690,22 @@
       </x:c>
       <x:c r="D26" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">4.4.1.8.64</x:t>
         </x:is>
       </x:c>
       <x:c r="E26" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.64.1, REQ_IO_A8.64.2, REQ_IO_A8.64.3, REQ_IO_A8.64.4, REQ_IO_A8.64.5</x:t>
         </x:is>
       </x:c>
       <x:c r="F26" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-PERM-011, SYS-PERM-024</x:t>
+          <x:t xml:space="preserve">SYS-PERM-011, SYS-PERM-024, SYS-PERM-025</x:t>
         </x:is>
       </x:c>
       <x:c r="G26" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -4764,22 +5727,22 @@
       </x:c>
       <x:c r="D27" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">4.4.1.8.64</x:t>
         </x:is>
       </x:c>
       <x:c r="E27" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.64.2, REQ_IO_A8.64.5</x:t>
         </x:is>
       </x:c>
       <x:c r="F27" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-PERM-011, SYS-PERM-024</x:t>
+          <x:t xml:space="preserve">SYS-PERM-011, SYS-PERM-024, SYS-PERM-025</x:t>
         </x:is>
       </x:c>
       <x:c r="G27" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -4801,22 +5764,22 @@
       </x:c>
       <x:c r="D28" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">4.4.1.8.64</x:t>
         </x:is>
       </x:c>
       <x:c r="E28" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.64.6</x:t>
         </x:is>
       </x:c>
       <x:c r="F28" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-PERM-012, SYS-PERM-024</x:t>
+          <x:t xml:space="preserve">SYS-PERM-012, SYS-PERM-024, SYS-PERM-025</x:t>
         </x:is>
       </x:c>
       <x:c r="G28" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -4875,22 +5838,22 @@
       </x:c>
       <x:c r="D30" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">4.4.1.8.65</x:t>
         </x:is>
       </x:c>
       <x:c r="E30" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.65.1, REQ_IO_A8.65.2, REQ_IO_A8.65.3, REQ_IO_A8.65.4, REQ_IO_A8.65.5</x:t>
         </x:is>
       </x:c>
       <x:c r="F30" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-PERM-015, SYS-PERM-016, SYS-PERM-024</x:t>
+          <x:t xml:space="preserve">SYS-PERM-015, SYS-PERM-016, SYS-PERM-017, SYS-PERM-018, SYS-PERM-026, SYS-PERM-027</x:t>
         </x:is>
       </x:c>
       <x:c r="G30" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -4926,6 +5889,302 @@
         </x:is>
       </x:c>
       <x:c r="G31" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Partial</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.25.8</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B32" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow authorized users to view a user's company access, organization and roles.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C32" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.92, REQ_DS43.93</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D32" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.65</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E32" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.65.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F32" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-PERM-017, SYS-PERM-018, SYS-PERM-026, SYS-PERM-027</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G32" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Covered</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.26.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B33" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should enforce HTTPS with HSTS outside the development environment.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C33" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="D33" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="E33" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F33" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-SEC-004</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G33" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Partial</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.26.2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B34" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow cross-origin requests only from configured frontend origins.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C34" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="D34" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="E34" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F34" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-SEC-002, SYS-SEC-003, SYS-SEC-006</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G34" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Partial</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.26.3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B35" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should rate-limit login, token refresh and captcha requests per client IP.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C35" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="D35" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="E35" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F35" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-SEC-003, SYS-SEC-005, SYS-SEC-006, SYS-SEC-007, SYS-SEC-011, SYS-SEC-012</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G35" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Partial</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.26.4</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B36" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should rate-limit authenticated API requests per user.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C36" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="D36" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="E36" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F36" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-SEC-010</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G36" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Partial</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.26.5</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B37" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should add security headers to every API response.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C37" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="D37" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="E37" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F37" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-SEC-001, SYS-SEC-014</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G37" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Partial</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.26.6</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B38" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should honour X-Forwarded-For only from configured proxies.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C38" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="D38" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="E38" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F38" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-SEC-003, SYS-SEC-008, SYS-SEC-009</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G38" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Partial</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.26.7</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B39" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should show a trilingual "too many requests" message when an API call is rate-limited.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C39" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="D39" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="E39" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F39" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-SEC-013, SYS-SEC-014</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G39" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Partial</x:t>
         </x:is>

--- a/docs/99-output/MyERP_Requirements.xlsx
+++ b/docs/99-output/MyERP_Requirements.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="1" r:id="R3d774857c42f45a3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Non-Functional" sheetId="2" r:id="Rc7f5663132064e7a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Structure" sheetId="3" r:id="R309afbf6b838471e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interface" sheetId="4" r:id="R57122998222b4ce0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traceability Matrix" sheetId="5" r:id="R2e150bdb38594b7d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BlueWhale Parity" sheetId="6" r:id="R370a3df8acf24061"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timeline" sheetId="7" r:id="Ra29eb8a22c69427f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Human Resources" sheetId="8" r:id="Rcfe04b2e8a5f4caf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="9" r:id="Redfc728c80a040fa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="1" r:id="Rd2c593d0bbd14126"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Non-Functional" sheetId="2" r:id="R273907d1562f4530"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Structure" sheetId="3" r:id="Rac5af4f4a32446a6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interface" sheetId="4" r:id="Rc25761c568e64636"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traceability Matrix" sheetId="5" r:id="R608cfff5c9fa4300"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BlueWhale Parity" sheetId="6" r:id="Rd581ee1065db474d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timeline" sheetId="7" r:id="R90a4c51e3475470e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Human Resources" sheetId="8" r:id="R5fa75bb9ba4349e3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="9" r:id="R0d72eb9cabbb4a4b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1028,7 +1028,7 @@
       </x:c>
       <x:c r="G23" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Captcha:MasterCode 只在 Development 生效且須為 4–6 位數字；其他環境有設定即寫 Error 並拒絕啟動；每次使用寫 Warning（帳號、IP），稽核日誌於 WU-SYS-007 補上。</x:t>
+          <x:t xml:space="preserve">Captcha:MasterCode 只在 Development 生效且須為 4–6 位數字；其他環境有設定即寫 Error 並拒絕啟動；每次使用寫 Warning（帳號、IP），並寫 sys_audit_log 安全事件 MASTER_CODE_LOGIN（REQ_F4118.27.3）。</x:t>
         </x:is>
       </x:c>
       <x:c r="H23" s="2" t="inlineStr">
@@ -1706,6 +1706,258 @@
       <x:c r="H39" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:102</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.27.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B40" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C40" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Audit Log</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D40" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E40" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should record every data change in sys_audit_log within the same transaction.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F40" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G40" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">透過 EF 新增、修改、刪除（含軟刪除）都寫一筆記錄，內容包括公司、用戶（背景程序為系統用戶）、時間（IClock）、表名、記錄 Id、操作類型（CREATE／UPDATE／DELETE，可由 Application 指定 VOID／APPROVE／POST）、欄位差異 JSON（修改只列有變更的欄位）、來源 IP、TraceId。沒有欄位變更不寫記錄。交易回滾或 SaveChanges 失敗（含樂觀鎖衝突）不留記錄，重試時也不會重複（ADR-019）。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H40" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:114</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.27.2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B41" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C41" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Audit Log</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D41" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E41" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should protect audit records and sensitive values.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F41" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G41" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[SensitiveData] 欄位（例如 password_hash）的值以 * 遮蔽；主鍵、審計欄位、version、company_id 不記錄差異。sys_audit_log 只能新增，UPDATE 或 DELETE 由 trigger 拒絕（append-only）；changes 必須是 JSON。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H41" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:115</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.27.3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B42" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C42" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Audit Log</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D42" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E42" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should record login, failed login, logout and captcha master-code login as security events.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F42" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G42" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">安全事件記錄帳號、IP、時間與 TraceId。LOGIN_FAILED 的原因只寫 INVALID_CREDENTIALS 或 PASSWORD_EXPIRED，不寫密碼。萬用碼登入不論結果都寫 MASTER_CODE_LOGIN（REQ_F4118.24.4）。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H42" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:116</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.27.4</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B43" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C43" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Audit Log</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D43" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E43" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow authorized users to query audit logs of the current company.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F43" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G43" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GET /api/v1/sys/audit-logs 需 SYS.AUDIT.VIEW，支援分頁、日期範圍（含頭尾）、類別、操作類型、表名＋記錄 Id（單據修改歷史）、用戶篩選，以時間排序。只列出目前公司的記錄，以及屬於目前公司用戶、沒有公司的安全事件；其他公司的記錄看不到。資料變更記錄會補上帳號。to 早於 from、類別未知或長度超限時回 400。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H43" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:117</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.27.5</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B44" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C44" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Audit Log</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D44" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E44" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should record role permission and user company access changes as security events.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F44" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G44" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">修改角色的權限、資料範圍、全權或啟用狀態，以及指派用戶公司授權，都寫 PERMISSION_CHANGE，與變更同一交易。記錄內容包括操作者、公司、新增與移除的權限，或指派後的角色、組織、預設公司與啟用狀態。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H44" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:118</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.27.6</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B45" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C45" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Audit Log</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D45" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E45" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should provide a trilingual audit log page with per-record change history.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F45" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G45" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">待第二段：三語稽核查詢頁（介面 8.66），可用篩選條件查詢，可展開欄位差異，並支援從單據查看修改歷史。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H45" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:119</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -2941,6 +3193,38 @@
       <x:c r="F9" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">REQ_F4118.25.6, REQ_F4118.25.7, REQ_F4118.25.8</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.94</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B10" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C10" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">sys_audit_log</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D10" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Append-only audit trail of data changes (field old/new values) and security events, with company, user, IP and trace id.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E10" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F10" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.27.1, REQ_F4118.27.2, REQ_F4118.27.3, REQ_F4118.27.4, REQ_F4118.27.5</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -6190,6 +6474,228 @@
         </x:is>
       </x:c>
     </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.27.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B40" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should record every data change in sys_audit_log within the same transaction.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C40" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.94</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D40" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="E40" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F40" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-AUDIT-001, SYS-AUDIT-002, SYS-AUDIT-003, SYS-AUDIT-004, SYS-AUDIT-005, SYS-AUDIT-006, SYS-AUDIT-010</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G40" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Partial</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.27.2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B41" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should protect audit records and sensitive values.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C41" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.94</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D41" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="E41" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F41" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-AUDIT-003, SYS-AUDIT-008, SYS-AUDIT-011</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G41" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Partial</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.27.3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B42" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should record login, failed login, logout and captcha master-code login as security events.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C42" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.94</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D42" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="E42" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F42" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-AUDIT-007, SYS-AUDIT-012</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G42" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Partial</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.27.4</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B43" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow authorized users to query audit logs of the current company.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C43" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.94</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D43" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="E43" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F43" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-AUDIT-009, SYS-AUDIT-010</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G43" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Partial</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.27.5</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B44" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should record role permission and user company access changes as security events.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C44" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.94</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D44" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="E44" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F44" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-AUDIT-013</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G44" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Partial</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.27.6</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B45" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should provide a trilingual audit log page with per-record change history.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C45" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="D45" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="E45" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F45" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-AUDIT-014</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G45" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Partial</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
   </x:sheetData>
 </x:worksheet>
 </file>

--- a/docs/99-output/MyERP_Requirements.xlsx
+++ b/docs/99-output/MyERP_Requirements.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="1" r:id="Rd2c593d0bbd14126"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Non-Functional" sheetId="2" r:id="R273907d1562f4530"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Structure" sheetId="3" r:id="Rac5af4f4a32446a6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interface" sheetId="4" r:id="Rc25761c568e64636"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traceability Matrix" sheetId="5" r:id="R608cfff5c9fa4300"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BlueWhale Parity" sheetId="6" r:id="Rd581ee1065db474d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timeline" sheetId="7" r:id="R90a4c51e3475470e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Human Resources" sheetId="8" r:id="R5fa75bb9ba4349e3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="9" r:id="R0d72eb9cabbb4a4b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="1" r:id="R0160f9f877f748f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Non-Functional" sheetId="2" r:id="R79f644a96dcd46b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Structure" sheetId="3" r:id="Rb6b61804eb684750"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interface" sheetId="4" r:id="R3c5b21c9e5aa4814"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traceability Matrix" sheetId="5" r:id="R5d5be2b6fd91449d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BlueWhale Parity" sheetId="6" r:id="Rb8338e706f51440b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timeline" sheetId="7" r:id="R667e0de5a86a4bcc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Human Resources" sheetId="8" r:id="R0db5d66091f44454"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="9" r:id="R40c545e409324e32"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1952,7 +1952,7 @@
       </x:c>
       <x:c r="G45" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">待第二段：三語稽核查詢頁（介面 8.66），可用篩選條件查詢，可展開欄位差異，並支援從單據查看修改歷史。</x:t>
+          <x:t xml:space="preserve">三語稽核查詢頁 /sys/audit-logs（介面 8.66），需 SYS.AUDIT.VIEW，無權限時選單不顯示、直接進入顯示 403。可依日期範圍（含快選今天、近 7、30 天；結束日早於開始日時不送出）、類別、操作、資料表＋記錄 ID 篩選，伺服器端分頁並依時間排序。可展開欄位差異（修改前→修改後，* 照原樣顯示）或安全事件明細。?tableName=&amp;recordId= 開啟單筆記錄的修改歷史，供單據頁的稽核頁籤連結。操作與類別有三語標籤，未知操作顯示原代碼。切換公司後重新查詢。</x:t>
         </x:is>
       </x:c>
       <x:c r="H45" s="2" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </x:c>
       <x:c r="F10" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.27.1, REQ_F4118.27.2, REQ_F4118.27.3, REQ_F4118.27.4, REQ_F4118.27.5</x:t>
+          <x:t xml:space="preserve">REQ_F4118.27.1, REQ_F4118.27.2, REQ_F4118.27.3, REQ_F4118.27.4, REQ_F4118.27.5, REQ_F4118.27.6</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -3238,10 +3238,10 @@
     <x:col min="1" max="1" width="16" customWidth="1"/>
     <x:col min="2" max="2" width="15" customWidth="1"/>
     <x:col min="3" max="3" width="54" customWidth="1"/>
-    <x:col min="4" max="4" width="32" customWidth="1"/>
+    <x:col min="4" max="4" width="42" customWidth="1"/>
     <x:col min="5" max="5" width="13" customWidth="1"/>
     <x:col min="6" max="6" width="23" customWidth="1"/>
-    <x:col min="7" max="7" width="40" customWidth="1"/>
+    <x:col min="7" max="7" width="60" customWidth="1"/>
     <x:col min="8" max="8" width="60" customWidth="1"/>
     <x:col min="9" max="9" width="16" customWidth="1"/>
     <x:col min="10" max="10" width="10" customWidth="1"/>
@@ -5010,6 +5010,348 @@
         </x:is>
       </x:c>
       <x:c r="K31" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.66.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B32" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.66</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C32" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Audit Log Query Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D32" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Date Range (Date inputs + quick buttons)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E32" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">開始／結束日期</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F32" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">限制查詢期間</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G32" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">yyyy-MM-dd</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H32" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">含頭尾；結束日不可早於開始日；快選今天、近 7、30 天</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I32" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J32" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K32" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.66.2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B33" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.66</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C33" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Audit Log Query Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D33" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Category (Dropdown)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E33" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">類別</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F33" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">區分資料變更與安全事件</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G33" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">DATA／SECURITY</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H33" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">可清空</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I33" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J33" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K33" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.66.3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B34" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.66</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C34" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Audit Log Query Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D34" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Action (Dropdown)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E34" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">操作</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F34" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">依操作類型篩選</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G34" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">CREATE、UPDATE、DELETE、VOID、APPROVE、POST、LOGIN、LOGIN_FAILED、MASTER_CODE_LOGIN、LOGOUT、PERMISSION_CHANGE、EXPORT</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H34" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">可清空</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I34" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J34" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K34" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.66.4</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B35" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.66</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C35" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Audit Log Query Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D35" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Table / Record ID (Input)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E35" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">資料表、記錄 ID</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F35" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">查看單據修改歷史</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G35" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Text</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H35" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">資料表最多 128 字元、記錄 ID 最多 100 字元；去除前後空白</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I35" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.66.6</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J35" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K35" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.66.5</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B36" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.66</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C36" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Audit Log Query Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D36" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Changes (Expandable row)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E36" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">欄位差異</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F36" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">顯示修改前後的值</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G36" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">欄位／修改前／修改後</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H36" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">敏感欄位顯示 *；空值顯示「（空）」</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I36" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J36" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K36" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.66.6</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B37" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.66</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C37" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Audit Log Query Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D37" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Record History (Link / query string)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E37" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">修改歷史</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F37" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">由單據或列開啟單筆記錄歷史</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G37" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">?tableName=&amp;recordId=</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H37" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">安全事件沒有記錄 ID，不可開啟</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I37" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.66.4</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J37" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K37" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Developer</x:t>
         </x:is>
@@ -6534,7 +6876,7 @@
       </x:c>
       <x:c r="E41" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.66.5</x:t>
         </x:is>
       </x:c>
       <x:c r="F41" s="2" t="inlineStr">
@@ -6544,7 +6886,7 @@
       </x:c>
       <x:c r="G41" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -6603,12 +6945,12 @@
       </x:c>
       <x:c r="D43" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">4.4.1.8.66</x:t>
         </x:is>
       </x:c>
       <x:c r="E43" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.66.1</x:t>
         </x:is>
       </x:c>
       <x:c r="F43" s="2" t="inlineStr">
@@ -6618,7 +6960,7 @@
       </x:c>
       <x:c r="G43" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -6672,17 +7014,17 @@
       </x:c>
       <x:c r="C45" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_DS43.94</x:t>
         </x:is>
       </x:c>
       <x:c r="D45" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">4.4.1.8.66</x:t>
         </x:is>
       </x:c>
       <x:c r="E45" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.66.1, REQ_IO_A8.66.2, REQ_IO_A8.66.3, REQ_IO_A8.66.4, REQ_IO_A8.66.5, REQ_IO_A8.66.6</x:t>
         </x:is>
       </x:c>
       <x:c r="F45" s="2" t="inlineStr">
@@ -6692,7 +7034,7 @@
       </x:c>
       <x:c r="G45" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>

--- a/docs/99-output/MyERP_Requirements.xlsx
+++ b/docs/99-output/MyERP_Requirements.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="1" r:id="R0160f9f877f748f2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Non-Functional" sheetId="2" r:id="R79f644a96dcd46b6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Structure" sheetId="3" r:id="Rb6b61804eb684750"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interface" sheetId="4" r:id="R3c5b21c9e5aa4814"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traceability Matrix" sheetId="5" r:id="R5d5be2b6fd91449d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BlueWhale Parity" sheetId="6" r:id="Rb8338e706f51440b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timeline" sheetId="7" r:id="R667e0de5a86a4bcc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Human Resources" sheetId="8" r:id="R0db5d66091f44454"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="9" r:id="R40c545e409324e32"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="1" r:id="Rc570eda35bf6429e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Non-Functional" sheetId="2" r:id="R854030b7482948a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Structure" sheetId="3" r:id="Re6032a99bb98458f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interface" sheetId="4" r:id="R4ce832cd45d74977"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traceability Matrix" sheetId="5" r:id="R49b03cd0c4d148a5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BlueWhale Parity" sheetId="6" r:id="R01b9977fee3645ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timeline" sheetId="7" r:id="R48e32ff94c214d9a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Human Resources" sheetId="8" r:id="R2847e4b2f2754818"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="9" r:id="Rc12e25fcfb3546c5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1961,6 +1961,258 @@
         </x:is>
       </x:c>
     </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.28.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B46" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C46" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Document Number Rule</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D46" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E46" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow user to view document number rules of the current company.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F46" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G46" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="H46" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:132</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.28.2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B47" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C47" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Document Number Rule</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D47" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E47" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow user to create a document number rule with prefix, date format, sequence length and reset period.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F47" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G47" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="H47" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:133</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.28.3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B48" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C48" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Document Number Rule</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D48" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E48" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow user to edit or deactivate a document number rule without breaking issued numbers.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F48" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G48" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="H48" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:134</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.28.4</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B49" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C49" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Document Number Rule</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D49" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E49" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow user to preview the next document number for a business date.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F49" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G49" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="H49" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:135</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.28.5</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B50" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C50" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Document Number Rule</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D50" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E50" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should generate unique, gap-free document numbers for every module under concurrency.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F50" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G50" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="H50" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:136</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.28.6</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B51" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C51" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Document Number Rule</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D51" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E51" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should provide a trilingual number rule maintenance page.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F51" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G51" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="H51" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:137</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
   </x:sheetData>
 </x:worksheet>
 </file>
@@ -3225,6 +3477,70 @@
       <x:c r="F10" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">REQ_F4118.27.1, REQ_F4118.27.2, REQ_F4118.27.3, REQ_F4118.27.4, REQ_F4118.27.5, REQ_F4118.27.6</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.95</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B11" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C11" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">sys_number_rule</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D11" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Document number rule per company and document type: prefix, date format, sequence length, reset period and active flag.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E11" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F11" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.28.1, REQ_F4118.28.2, REQ_F4118.28.3, REQ_F4118.28.4, REQ_F4118.28.5</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.96</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B12" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C12" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">sys_number_sequence</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D12" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Running sequence counter per number rule and reset period, updated atomically when a number is issued.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E12" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F12" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.28.3, REQ_F4118.28.4, REQ_F4118.28.5</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -5370,7 +5686,7 @@
     <x:col min="4" max="4" width="12" customWidth="1"/>
     <x:col min="5" max="5" width="60" customWidth="1"/>
     <x:col min="6" max="6" width="60" customWidth="1"/>
-    <x:col min="7" max="7" width="10" customWidth="1"/>
+    <x:col min="7" max="7" width="13" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -7035,6 +7351,228 @@
       <x:c r="G45" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Covered</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.28.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B46" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow user to view document number rules of the current company.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C46" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.95</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D46" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="E46" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F46" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-NUM-006, SYS-NUM-008</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G46" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Partial</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.28.2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B47" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow user to create a document number rule with prefix, date format, sequence length and reset period.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C47" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.95</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D47" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="E47" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F47" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-NUM-006, SYS-NUM-007, SYS-NUM-008</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G47" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Partial</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.28.3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B48" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow user to edit or deactivate a document number rule without breaking issued numbers.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C48" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.95, REQ_DS43.96</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D48" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="E48" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F48" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-NUM-006, SYS-NUM-008, SYS-NUM-009</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G48" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Partial</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.28.4</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B49" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow user to preview the next document number for a business date.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C49" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.95, REQ_DS43.96</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D49" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="E49" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F49" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-NUM-006, SYS-NUM-008</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G49" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Partial</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.28.5</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B50" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should generate unique, gap-free document numbers for every module under concurrency.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C50" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.95, REQ_DS43.96</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D50" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="E50" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F50" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-NUM-001, SYS-NUM-002, SYS-NUM-003, SYS-NUM-004, SYS-NUM-005, SYS-NUM-009</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G50" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Partial</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.28.6</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B51" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should provide a trilingual number rule maintenance page.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C51" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="D51" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="E51" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F51" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="G51" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Not covered</x:t>
         </x:is>
       </x:c>
     </x:row>

--- a/docs/99-output/MyERP_Requirements.xlsx
+++ b/docs/99-output/MyERP_Requirements.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="1" r:id="Rc570eda35bf6429e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Non-Functional" sheetId="2" r:id="R854030b7482948a1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Structure" sheetId="3" r:id="Re6032a99bb98458f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interface" sheetId="4" r:id="R4ce832cd45d74977"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traceability Matrix" sheetId="5" r:id="R49b03cd0c4d148a5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BlueWhale Parity" sheetId="6" r:id="R01b9977fee3645ec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timeline" sheetId="7" r:id="R48e32ff94c214d9a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Human Resources" sheetId="8" r:id="R2847e4b2f2754818"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="9" r:id="Rc12e25fcfb3546c5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="1" r:id="R4484eb9e401d42dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Non-Functional" sheetId="2" r:id="Rda699110a72945d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Structure" sheetId="3" r:id="R33275d44c5a34e3d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interface" sheetId="4" r:id="R76b67ad55c5b4430"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traceability Matrix" sheetId="5" r:id="R668c5f6cf1d4465a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BlueWhale Parity" sheetId="6" r:id="R5b2e7626cc464fe1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timeline" sheetId="7" r:id="R122bcbbe87b4458c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Human Resources" sheetId="8" r:id="R201716bea0474bcf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="9" r:id="Reb0e219635e04bc7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3508,7 +3508,7 @@
       </x:c>
       <x:c r="F11" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.28.1, REQ_F4118.28.2, REQ_F4118.28.3, REQ_F4118.28.4, REQ_F4118.28.5</x:t>
+          <x:t xml:space="preserve">REQ_F4118.28.1, REQ_F4118.28.2, REQ_F4118.28.3, REQ_F4118.28.4, REQ_F4118.28.5, REQ_F4118.28.6</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -5673,6 +5673,519 @@
         </x:is>
       </x:c>
     </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.67.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B38" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.67</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C38" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Document Number Rule Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D38" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Document Type (Input)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E38" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">單據類型</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F38" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">識別規則所屬單據</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G38" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{PREFIX}.{DOCUMENT}，例如 SD.ORDER</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H38" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">英文字母、數字、底線，最多 50 字；保存為大寫；公司內唯一；建立後不可修改</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I38" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J38" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K38" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.67.2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B39" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.67</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C39" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Document Number Rule Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D39" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Name (Input)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E39" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">名稱</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F39" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">規則說明</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G39" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Text</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H39" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1–100 字元，去除前後空白</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I39" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J39" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K39" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.67.3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B40" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.67</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C40" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Document Number Rule Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D40" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Prefix (Input)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E40" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">前綴</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F40" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">單號開頭</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G40" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Text</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H40" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">0–10 個英數字、-、_；保存為大寫</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I40" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.67.7</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J40" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K40" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.67.4</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B41" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.67</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C41" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Document Number Rule Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D41" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Date Format (Dropdown)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E41" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">日期格式</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F41" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">單號的日期部分</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G41" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None／yyyy／yyyyMM／yyyyMMdd／yyMM／yyMMdd</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H41" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">已發號時不可修改</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I41" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.67.6</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J41" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K41" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.67.5</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B42" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.67</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C42" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Document Number Rule Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D42" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Sequence Length (Number)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E42" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">流水號長度</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F42" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">補零位數</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G42" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">整數</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H42" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">3–10；已發號時不可小於原長度</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I42" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.67.7</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J42" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K42" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.67.6</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B43" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.67</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C43" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Document Number Rule Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D43" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Reset Period (Dropdown)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E43" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">重設週期</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F43" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">流水號歸 1 的時機</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G43" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">不重設／每年／每月／每日</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H43" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">必須包含在日期格式內；已發號時不可修改</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I43" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.67.4</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J43" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K43" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.67.7</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B44" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.67</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C44" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Document Number Rule Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D44" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Sample (Text)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E44" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">樣式</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F44" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">即時顯示今天第 1 號</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G44" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">前綴＋日期＋補零流水號</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H44" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">唯讀</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I44" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.67.3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J44" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K44" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.67.8</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B45" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.67</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C45" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Document Number Rule Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D45" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Active (Checkbox)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E45" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">啟用</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F45" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">停用後各模組不可再取號</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G45" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Boolean</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H45" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">只在編輯時顯示</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I45" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J45" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K45" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.67.9</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B46" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.67</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C46" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Document Number Rule Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D46" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Preview Date (Date input)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E46" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">單據日期</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F46" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">預覽該日期的下一個單號</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G46" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">yyyy-MM-dd</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H46" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">預設今天；可清空（後端用今天）；不佔號</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I46" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J46" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K46" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
   </x:sheetData>
 </x:worksheet>
 </file>
@@ -5686,7 +6199,7 @@
     <x:col min="4" max="4" width="12" customWidth="1"/>
     <x:col min="5" max="5" width="60" customWidth="1"/>
     <x:col min="6" max="6" width="60" customWidth="1"/>
-    <x:col min="7" max="7" width="13" customWidth="1"/>
+    <x:col min="7" max="7" width="10" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -7372,22 +7885,22 @@
       </x:c>
       <x:c r="D46" s="2" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">4.4.1.8.67</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E46" s="2" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
-      <x:c r="E46" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
       <x:c r="F46" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-NUM-006, SYS-NUM-008</x:t>
+          <x:t xml:space="preserve">SYS-NUM-006, SYS-NUM-008, SYS-NUM-010</x:t>
         </x:is>
       </x:c>
       <x:c r="G46" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -7409,22 +7922,22 @@
       </x:c>
       <x:c r="D47" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">4.4.1.8.67</x:t>
         </x:is>
       </x:c>
       <x:c r="E47" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.67.1, REQ_IO_A8.67.2, REQ_IO_A8.67.3, REQ_IO_A8.67.4, REQ_IO_A8.67.5, REQ_IO_A8.67.6</x:t>
         </x:is>
       </x:c>
       <x:c r="F47" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-NUM-006, SYS-NUM-007, SYS-NUM-008</x:t>
+          <x:t xml:space="preserve">SYS-NUM-006, SYS-NUM-007, SYS-NUM-008, SYS-NUM-010, SYS-NUM-011</x:t>
         </x:is>
       </x:c>
       <x:c r="G47" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -7446,22 +7959,22 @@
       </x:c>
       <x:c r="D48" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">4.4.1.8.67</x:t>
         </x:is>
       </x:c>
       <x:c r="E48" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.67.2, REQ_IO_A8.67.3, REQ_IO_A8.67.4, REQ_IO_A8.67.5, REQ_IO_A8.67.6, REQ_IO_A8.67.8</x:t>
         </x:is>
       </x:c>
       <x:c r="F48" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-NUM-006, SYS-NUM-008, SYS-NUM-009</x:t>
+          <x:t xml:space="preserve">SYS-NUM-006, SYS-NUM-008, SYS-NUM-009, SYS-NUM-010, SYS-NUM-011</x:t>
         </x:is>
       </x:c>
       <x:c r="G48" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -7483,22 +7996,22 @@
       </x:c>
       <x:c r="D49" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">4.4.1.8.67</x:t>
         </x:is>
       </x:c>
       <x:c r="E49" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.67.9</x:t>
         </x:is>
       </x:c>
       <x:c r="F49" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-NUM-006, SYS-NUM-008</x:t>
+          <x:t xml:space="preserve">SYS-NUM-006, SYS-NUM-008, SYS-NUM-010, SYS-NUM-011</x:t>
         </x:is>
       </x:c>
       <x:c r="G49" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -7552,27 +8065,27 @@
       </x:c>
       <x:c r="C51" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_DS43.95</x:t>
         </x:is>
       </x:c>
       <x:c r="D51" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">4.4.1.8.67</x:t>
         </x:is>
       </x:c>
       <x:c r="E51" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.67.1, REQ_IO_A8.67.7</x:t>
         </x:is>
       </x:c>
       <x:c r="F51" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">SYS-NUM-010, SYS-NUM-011</x:t>
         </x:is>
       </x:c>
       <x:c r="G51" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Not covered</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>

--- a/docs/99-output/MyERP_Requirements.xlsx
+++ b/docs/99-output/MyERP_Requirements.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="1" r:id="R4484eb9e401d42dd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Non-Functional" sheetId="2" r:id="Rda699110a72945d7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Structure" sheetId="3" r:id="R33275d44c5a34e3d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interface" sheetId="4" r:id="R76b67ad55c5b4430"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traceability Matrix" sheetId="5" r:id="R668c5f6cf1d4465a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BlueWhale Parity" sheetId="6" r:id="R5b2e7626cc464fe1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timeline" sheetId="7" r:id="R122bcbbe87b4458c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Human Resources" sheetId="8" r:id="R201716bea0474bcf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="9" r:id="Reb0e219635e04bc7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="1" r:id="R8a9a72e8b02c4c69"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Non-Functional" sheetId="2" r:id="Rc6df7f0a79b84077"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Structure" sheetId="3" r:id="R10fb1a1c96c94949"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interface" sheetId="4" r:id="Rd3e86666e15f4683"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traceability Matrix" sheetId="5" r:id="R4d657a0aa340424e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BlueWhale Parity" sheetId="6" r:id="R34090fe3330d4462"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timeline" sheetId="7" r:id="R58ba9181f4334e76"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Human Resources" sheetId="8" r:id="Rdfa9fec9ace84aff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="9" r:id="R3e9de798a3a240e6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1999,7 +1999,7 @@
       </x:c>
       <x:c r="H46" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:132</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:153</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -2041,7 +2041,7 @@
       </x:c>
       <x:c r="H47" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:133</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:154</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -2083,7 +2083,7 @@
       </x:c>
       <x:c r="H48" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:134</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:155</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -2125,7 +2125,7 @@
       </x:c>
       <x:c r="H49" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:135</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:156</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -2167,7 +2167,7 @@
       </x:c>
       <x:c r="H50" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:136</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:157</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -2209,7 +2209,385 @@
       </x:c>
       <x:c r="H51" s="2" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:158</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.29.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B52" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C52" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Approval Workflow</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D52" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E52" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow user to view and create multi-level approval flows with amount thresholds.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F52" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G52" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="H52" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:132</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.29.2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B53" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C53" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Approval Workflow</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D53" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E53" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow user to edit or deactivate an approval flow without affecting pending approvals.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F53" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G53" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="H53" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:133</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.29.3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B54" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C54" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Approval Workflow</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D54" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E54" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow user to assign an approval delegate for a date range.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F54" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G54" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="H54" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:134</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.29.4</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B55" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C55" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Approval Workflow</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D55" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E55" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should enable every module to submit documents for approval through the shared workflow engine.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F55" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G55" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="H55" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:135</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.29.5</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B56" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C56" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Approval Workflow</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D56" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E56" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow approvers or their delegates to approve or reject the current approval step.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F56" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G56" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="H56" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:136</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.29.6</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B57" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C57" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Approval Workflow</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D57" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E57" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should list the pending approval tasks of the current user.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F57" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G57" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="H57" s="2" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:137</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.29.7</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B58" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C58" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Approval Workflow</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D58" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E58" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow user to view the approval history of a document.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F58" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G58" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="H58" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:138</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.29.8</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B59" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C59" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Approval Workflow</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D59" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E59" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should provide trilingual approval flow and delegation maintenance pages.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F59" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G59" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="H59" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:139</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.29.9</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B60" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C60" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Approval Workflow</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D60" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E60" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should provide a trilingual approval inbox with approval history.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F60" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G60" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="H60" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:140</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -3154,7 +3532,7 @@
   <x:cols>
     <x:col min="1" max="1" width="16" customWidth="1"/>
     <x:col min="2" max="2" width="10" customWidth="1"/>
-    <x:col min="3" max="3" width="21" customWidth="1"/>
+    <x:col min="3" max="3" width="28" customWidth="1"/>
     <x:col min="4" max="4" width="60" customWidth="1"/>
     <x:col min="5" max="5" width="11" customWidth="1"/>
     <x:col min="6" max="6" width="60" customWidth="1"/>
@@ -3541,6 +3919,166 @@
       <x:c r="F12" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">REQ_F4118.28.3, REQ_F4118.28.4, REQ_F4118.28.5</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.97</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B13" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C13" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">sys_approval_flow</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D13" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Approval flow per company and document type, with the self-approval setting and active flag.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E13" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F13" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.29.1, REQ_F4118.29.2, REQ_F4118.29.4, REQ_F4118.29.8</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.98</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B14" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C14" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">sys_approval_flow_step</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D14" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Ordered steps of an approval flow: approver role or user and the optional minimum amount that makes the step apply.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E14" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F14" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.29.1, REQ_F4118.29.2, REQ_F4118.29.4, REQ_F4118.29.8</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.99</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B15" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C15" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">sys_approval_delegation</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D15" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Approval delegation from one user to another within a date range.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E15" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F15" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.29.3, REQ_F4118.29.5, REQ_F4118.29.6, REQ_F4118.29.8</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.100</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B16" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C16" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">sys_approval_instance</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D16" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">One submission of a document for approval: document reference, amount, status, current step, submitter and completion time.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E16" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F16" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.29.4, REQ_F4118.29.5, REQ_F4118.29.6, REQ_F4118.29.7, REQ_F4118.29.9</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.101</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B17" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C17" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">sys_approval_instance_step</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D17" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Snapshot of the applicable flow steps of an approval instance with each step's decision, actor, delegator, time and comment.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E17" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F17" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.29.4, REQ_F4118.29.5, REQ_F4118.29.6, REQ_F4118.29.7, REQ_F4118.29.9</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -6186,6 +6724,804 @@
         </x:is>
       </x:c>
     </x:row>
+    <x:row r="47">
+      <x:c r="A47" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.68.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B47" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.68</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C47" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Approval Flow Maintenance Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D47" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Document Type (Input)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E47" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">單據類型</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F47" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">流程所屬單據</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G47" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{PREFIX}.{DOCUMENT}，例如 PUR.ORDER</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H47" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">英文字母、數字、底線，最多 50 字；保存為大寫；公司內唯一；建立後不可修改</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I47" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J47" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K47" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.68.2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B48" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.68</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C48" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Approval Flow Maintenance Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D48" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Flow Name (Input)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E48" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">流程名稱</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F48" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">流程說明</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G48" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Text</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H48" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1–100 字元，去除前後空白</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I48" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J48" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K48" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.68.3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B49" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.68</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C49" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Approval Flow Maintenance Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D49" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Allow Self-approval (Checkbox)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E49" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">允許自審</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F49" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">送審人可否審批自己的單據</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G49" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Boolean</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H49" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">預設否</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I49" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J49" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K49" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.68.4</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B50" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.68</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C50" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Approval Flow Maintenance Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D50" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Step Name (Input)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E50" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">步驟名稱</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F50" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">顯示於待辦與記錄</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G50" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Text</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H50" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1–100 字元</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I50" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J50" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K50" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.68.5</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B51" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.68</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C51" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Approval Flow Maintenance Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D51" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Approver Type (Dropdown)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E51" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">審批人類型</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F51" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">角色或指定用戶</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G51" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Role／User</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H51" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">必填</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I51" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.68.6</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J51" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K51" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.68.6</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B52" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.68</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C52" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Approval Flow Maintenance Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D52" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Approver (Dropdown)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E52" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">審批人</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F52" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">處理該步驟的角色或用戶</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G52" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">bigint ID</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H52" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">啟用角色或本公司啟用用戶</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I52" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.68.5</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J52" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K52" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.68.7</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B53" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.68</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C53" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Approval Flow Maintenance Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D53" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Minimum Amount (Input)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E53" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">最低金額</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F53" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">金額門檻（本位幣）</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G53" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">數字</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H53" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">選填；≥ 0，最多 11 位整數、4 位小數</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I53" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J53" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K53" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.68.8</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B54" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.68</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C54" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Approval Flow Maintenance Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D54" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Active (Checkbox)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E54" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">啟用</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F54" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">停用後送審自動核准</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G54" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Boolean</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H54" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">只在編輯時顯示</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I54" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J54" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K54" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.69.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B55" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.69</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C55" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Approval Delegation Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D55" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Delegator (Dropdown)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E55" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">被代理人</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F55" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">交出審批工作的用戶</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G55" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">bigint ID</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H55" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">本公司啟用用戶；建立後不可修改</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I55" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.69.2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J55" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K55" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.69.2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B56" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.69</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C56" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Approval Delegation Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D56" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Delegate (Dropdown)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E56" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">代理人</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F56" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">代為審批的用戶</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G56" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">bigint ID</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H56" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">本公司啟用用戶，不可與被代理人相同；建立後不可修改</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I56" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.69.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J56" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K56" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.69.3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B57" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.69</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C57" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Approval Delegation Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D57" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Start / End Date (Date input)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E57" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">開始／結束日期</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F57" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">代理期間（含頭尾）</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G57" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">yyyy-MM-dd</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H57" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">結束不早於開始；同一被代理人的啟用期間不可重疊</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I57" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J57" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K57" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.69.4</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B58" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.69</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C58" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Approval Delegation Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D58" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Remark (Textarea)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E58" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">備註</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F58" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">代理原因</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G58" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Text</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H58" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">0–200 字元</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I58" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J58" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K58" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.70.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B59" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.70</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C59" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Approval Inbox Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D59" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Comment (Textarea)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E59" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">意見</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F59" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">核准或駁回的說明</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G59" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Text</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H59" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">0–500 字元；駁回必填</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I59" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J59" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K59" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.70.2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B60" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.70</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C60" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Approval Inbox Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D60" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Status Filter (Dropdown)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E60" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">狀態</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F60" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">篩選審批歷史</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G60" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">審批中／已核准／已駁回／已撤回</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H60" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">可清除</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I60" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J60" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K60" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
   </x:sheetData>
 </x:worksheet>
 </file>
@@ -6195,8 +7531,8 @@
   <x:cols>
     <x:col min="1" max="1" width="16" customWidth="1"/>
     <x:col min="2" max="2" width="60" customWidth="1"/>
-    <x:col min="3" max="3" width="39" customWidth="1"/>
-    <x:col min="4" max="4" width="12" customWidth="1"/>
+    <x:col min="3" max="3" width="54" customWidth="1"/>
+    <x:col min="4" max="4" width="24" customWidth="1"/>
     <x:col min="5" max="5" width="60" customWidth="1"/>
     <x:col min="6" max="6" width="60" customWidth="1"/>
     <x:col min="7" max="7" width="10" customWidth="1"/>
@@ -8084,6 +9420,339 @@
         </x:is>
       </x:c>
       <x:c r="G51" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Covered</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.29.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B52" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow user to view and create multi-level approval flows with amount thresholds.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C52" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.97, REQ_DS43.98</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D52" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.68</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E52" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.68.1, REQ_IO_A8.68.2, REQ_IO_A8.68.3, REQ_IO_A8.68.4, REQ_IO_A8.68.5, REQ_IO_A8.68.6, REQ_IO_A8.68.7</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F52" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-APR-008, SYS-APR-010, SYS-APR-012, SYS-APR-013</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G52" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Covered</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.29.2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B53" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow user to edit or deactivate an approval flow without affecting pending approvals.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C53" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.97, REQ_DS43.98</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D53" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.68</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E53" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.68.2, REQ_IO_A8.68.3, REQ_IO_A8.68.8</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F53" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-APR-003, SYS-APR-008, SYS-APR-010, SYS-APR-012, SYS-APR-013</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G53" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Covered</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.29.3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B54" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow user to assign an approval delegate for a date range.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C54" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.99</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D54" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.69</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E54" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.69.1, REQ_IO_A8.69.2, REQ_IO_A8.69.3, REQ_IO_A8.69.4</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F54" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-APR-005, SYS-APR-010, SYS-APR-012, SYS-APR-013</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G54" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Covered</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.29.4</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B55" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should enable every module to submit documents for approval through the shared workflow engine.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C55" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.97, REQ_DS43.98, REQ_DS43.100, REQ_DS43.101</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D55" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="E55" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F55" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-APR-001, SYS-APR-002, SYS-APR-003, SYS-APR-007, SYS-APR-011</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G55" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Partial</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.29.5</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B56" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow approvers or their delegates to approve or reject the current approval step.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C56" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.99, REQ_DS43.100, REQ_DS43.101</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D56" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.70</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E56" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.70.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F56" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-APR-001, SYS-APR-002, SYS-APR-004, SYS-APR-005, SYS-APR-006, SYS-APR-007, SYS-APR-011, SYS-APR-012, SYS-APR-013</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G56" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Covered</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.29.6</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B57" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should list the pending approval tasks of the current user.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C57" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.99, REQ_DS43.100, REQ_DS43.101</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D57" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.70</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E57" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F57" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-APR-004, SYS-APR-005, SYS-APR-011, SYS-APR-012, SYS-APR-013</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G57" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Covered</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.29.7</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B58" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow user to view the approval history of a document.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C58" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.100, REQ_DS43.101</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D58" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.70</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E58" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.70.2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F58" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-APR-001, SYS-APR-002, SYS-APR-008, SYS-APR-011, SYS-APR-012, SYS-APR-013</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G58" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Covered</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.29.8</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B59" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should provide trilingual approval flow and delegation maintenance pages.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C59" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.97, REQ_DS43.98, REQ_DS43.99</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D59" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.68, 4.4.1.8.69</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E59" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.68.1, REQ_IO_A8.68.4, REQ_IO_A8.68.5, REQ_IO_A8.68.6, REQ_IO_A8.68.7</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F59" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-APR-012, SYS-APR-013</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G59" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Covered</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.29.9</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B60" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should provide a trilingual approval inbox with approval history.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C60" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.100, REQ_DS43.101</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D60" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.70</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E60" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.70.1, REQ_IO_A8.70.2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F60" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-APR-012, SYS-APR-013</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G60" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Covered</x:t>
         </x:is>

--- a/docs/99-output/MyERP_Requirements.xlsx
+++ b/docs/99-output/MyERP_Requirements.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="1" r:id="R8a9a72e8b02c4c69"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Non-Functional" sheetId="2" r:id="Rc6df7f0a79b84077"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Structure" sheetId="3" r:id="R10fb1a1c96c94949"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interface" sheetId="4" r:id="Rd3e86666e15f4683"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traceability Matrix" sheetId="5" r:id="R4d657a0aa340424e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BlueWhale Parity" sheetId="6" r:id="R34090fe3330d4462"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timeline" sheetId="7" r:id="R58ba9181f4334e76"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Human Resources" sheetId="8" r:id="Rdfa9fec9ace84aff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="9" r:id="R3e9de798a3a240e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="1" r:id="Re6ad69b918224735"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Non-Functional" sheetId="2" r:id="Ra7e0587e88734a7f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Structure" sheetId="3" r:id="R423e4857fb234118"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interface" sheetId="4" r:id="Rc6d76449e44e44f3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traceability Matrix" sheetId="5" r:id="R23ab5dcbf37a43de"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BlueWhale Parity" sheetId="6" r:id="R30c151c9f1d643f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timeline" sheetId="7" r:id="R99918af3ec494258"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Human Resources" sheetId="8" r:id="Rde99fb97f5d249a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="9" r:id="R06a8653ffa9849c8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2591,6 +2591,132 @@
         </x:is>
       </x:c>
     </x:row>
+    <x:row r="61">
+      <x:c r="A61" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.30.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B61" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C61" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Development Seed Data</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D61" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E61" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should load demo companies, branches, departments and roles for the Development environment.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F61" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G61" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="H61" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:172</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="62">
+      <x:c r="A62" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.30.2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B62" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C62" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Development Seed Data</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D62" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E62" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should create the test accounts of the SeedUsers setting with hashed passwords and company assignments.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F62" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G62" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="H62" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:173</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.30.3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B63" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C63" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Development Seed Data</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D63" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E63" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow the seed to run repeatedly without duplicating or overwriting data.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F63" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G63" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="H63" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:174</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
   </x:sheetData>
 </x:worksheet>
 </file>
@@ -3598,7 +3724,7 @@
       </x:c>
       <x:c r="F2" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.20.1, REQ_F4118.20.2, REQ_F4118.20.3, REQ_F4118.20.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.20.1, REQ_F4118.20.2, REQ_F4118.20.3, REQ_F4118.20.4, REQ_F4118.30.1, REQ_F4118.30.3</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -3630,7 +3756,7 @@
       </x:c>
       <x:c r="F3" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.22.1, REQ_F4118.22.2, REQ_F4118.22.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.22.1, REQ_F4118.22.2, REQ_F4118.22.3, REQ_F4118.30.1</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -3662,7 +3788,7 @@
       </x:c>
       <x:c r="F4" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.23.1, REQ_F4118.23.2, REQ_F4118.23.3, REQ_F4118.23.4, REQ_F4118.23.5, REQ_F4118.23.6, REQ_F4118.23.7, REQ_F4118.23.8</x:t>
+          <x:t xml:space="preserve">REQ_F4118.23.1, REQ_F4118.23.2, REQ_F4118.23.3, REQ_F4118.23.4, REQ_F4118.23.5, REQ_F4118.23.6, REQ_F4118.23.7, REQ_F4118.23.8, REQ_F4118.30.2, REQ_F4118.30.3</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -3694,7 +3820,7 @@
       </x:c>
       <x:c r="F5" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.21.1, REQ_F4118.21.2, REQ_F4118.21.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.21.1, REQ_F4118.21.2, REQ_F4118.21.3, REQ_F4118.30.1</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -3726,7 +3852,7 @@
       </x:c>
       <x:c r="F6" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.25.1, REQ_F4118.25.2, REQ_F4118.25.3, REQ_F4118.25.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.25.1, REQ_F4118.25.2, REQ_F4118.25.3, REQ_F4118.25.4, REQ_F4118.30.1</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -3758,7 +3884,7 @@
       </x:c>
       <x:c r="F7" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.25.2, REQ_F4118.25.3, REQ_F4118.25.7</x:t>
+          <x:t xml:space="preserve">REQ_F4118.25.2, REQ_F4118.25.3, REQ_F4118.25.7, REQ_F4118.30.1, REQ_F4118.30.3</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -3790,7 +3916,7 @@
       </x:c>
       <x:c r="F8" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.23.5, REQ_F4118.23.6, REQ_F4118.25.5, REQ_F4118.25.6, REQ_F4118.25.7, REQ_F4118.25.8</x:t>
+          <x:t xml:space="preserve">REQ_F4118.23.5, REQ_F4118.23.6, REQ_F4118.25.5, REQ_F4118.25.6, REQ_F4118.25.7, REQ_F4118.25.8, REQ_F4118.30.2</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -3822,7 +3948,7 @@
       </x:c>
       <x:c r="F9" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.25.6, REQ_F4118.25.7, REQ_F4118.25.8</x:t>
+          <x:t xml:space="preserve">REQ_F4118.25.6, REQ_F4118.25.7, REQ_F4118.25.8, REQ_F4118.30.2</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -7531,7 +7657,7 @@
   <x:cols>
     <x:col min="1" max="1" width="16" customWidth="1"/>
     <x:col min="2" max="2" width="60" customWidth="1"/>
-    <x:col min="3" max="3" width="54" customWidth="1"/>
+    <x:col min="3" max="3" width="60" customWidth="1"/>
     <x:col min="4" max="4" width="24" customWidth="1"/>
     <x:col min="5" max="5" width="60" customWidth="1"/>
     <x:col min="6" max="6" width="60" customWidth="1"/>
@@ -9755,6 +9881,117 @@
       <x:c r="G60" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Covered</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="61">
+      <x:c r="A61" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.30.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B61" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should load demo companies, branches, departments and roles for the Development environment.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C61" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.20, REQ_DS43.22, REQ_DS43.89, REQ_DS43.90, REQ_DS43.91</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D61" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="E61" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F61" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-SEED-001, SYS-SEED-002, SYS-SEED-003, SYS-SEED-006</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G61" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Partial</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="62">
+      <x:c r="A62" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.30.2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B62" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should create the test accounts of the SeedUsers setting with hashed passwords and company assignments.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C62" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.82, REQ_DS43.92, REQ_DS43.93</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D62" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="E62" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F62" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-SEED-001, SYS-SEED-005</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G62" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Partial</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.30.3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B63" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow the seed to run repeatedly without duplicating or overwriting data.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C63" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.20, REQ_DS43.82, REQ_DS43.91</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D63" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="E63" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F63" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-SEED-001, SYS-SEED-003, SYS-SEED-004</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G63" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Partial</x:t>
         </x:is>
       </x:c>
     </x:row>

--- a/docs/99-output/MyERP_Requirements.xlsx
+++ b/docs/99-output/MyERP_Requirements.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="1" r:id="Re6ad69b918224735"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Non-Functional" sheetId="2" r:id="Ra7e0587e88734a7f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Structure" sheetId="3" r:id="R423e4857fb234118"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interface" sheetId="4" r:id="Rc6d76449e44e44f3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traceability Matrix" sheetId="5" r:id="R23ab5dcbf37a43de"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BlueWhale Parity" sheetId="6" r:id="R30c151c9f1d643f8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timeline" sheetId="7" r:id="R99918af3ec494258"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Human Resources" sheetId="8" r:id="Rde99fb97f5d249a3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="9" r:id="R06a8653ffa9849c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="1" r:id="Rabb65e98e90d4fe9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Non-Functional" sheetId="2" r:id="Rc72b1a7703fc47e2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Structure" sheetId="3" r:id="R493857cb06894759"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interface" sheetId="4" r:id="R62568a8a0f2c4ab5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traceability Matrix" sheetId="5" r:id="Rda8e9146e6924d5c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BlueWhale Parity" sheetId="6" r:id="R79b7869c7ddd44b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timeline" sheetId="7" r:id="Rfd4740dbeb1046a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Human Resources" sheetId="8" r:id="Ra2b7c817e6dd4108"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="9" r:id="Rda868abf61bf4eb0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2717,6 +2717,258 @@
         </x:is>
       </x:c>
     </x:row>
+    <x:row r="64">
+      <x:c r="A64" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.31.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B64" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C64" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Shared Dialogs and Page Templates</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D64" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E64" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should ask for confirmation in a shared trilingual confirmation box before dangerous actions.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F64" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G64" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="H64" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:186</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="65">
+      <x:c r="A65" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.31.2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B65" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C65" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Shared Dialogs and Page Templates</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D65" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E65" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should show results that need the user's attention in a shared prompt box, and short success messages as toasts.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F65" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G65" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="H65" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:187</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="66">
+      <x:c r="A66" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.31.3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B66" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C66" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Shared Dialogs and Page Templates</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D66" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E66" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should provide a shared selection window for choosing master data with search and server-side paging.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F66" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G66" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="H66" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:188</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="67">
+      <x:c r="A67" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.31.4</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B67" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C67" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Shared Dialogs and Page Templates</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D67" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E67" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should provide a standard list page template reused by every module.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F67" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G67" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="H67" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:189</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="68">
+      <x:c r="A68" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.31.5</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B68" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C68" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Shared Dialogs and Page Templates</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D68" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E68" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should provide a standard document page template with status, previous / next navigation and unsaved-change protection.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F68" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G68" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="H68" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:190</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="69">
+      <x:c r="A69" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.31.6</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B69" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C69" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Shared Dialogs and Page Templates</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D69" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E69" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should provide a date range filter with quick ranges and a document status tag following the macaron status colours.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F69" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G69" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="H69" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:191</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
   </x:sheetData>
 </x:worksheet>
 </file>
@@ -4217,7 +4469,7 @@
   <x:cols>
     <x:col min="1" max="1" width="16" customWidth="1"/>
     <x:col min="2" max="2" width="15" customWidth="1"/>
-    <x:col min="3" max="3" width="54" customWidth="1"/>
+    <x:col min="3" max="3" width="60" customWidth="1"/>
     <x:col min="4" max="4" width="42" customWidth="1"/>
     <x:col min="5" max="5" width="13" customWidth="1"/>
     <x:col min="6" max="6" width="23" customWidth="1"/>
@@ -7643,6 +7895,348 @@
         </x:is>
       </x:c>
       <x:c r="K60" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="61">
+      <x:c r="A61" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.71.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B61" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.71</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C61" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Confirmation / Prompt Box Interface（BlueWhale 4.4.1.9）</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D61" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">OK / Cancel (Button)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E61" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">確定／取消</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F61" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">確認或放棄動作</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G61" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Button</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H61" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">確認框兩個按鈕，提示框只有確定；Esc 等同取消</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I61" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J61" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K61" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="62">
+      <x:c r="A62" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.72.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B62" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.72</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C62" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Select Dialog Interface（BlueWhale 4.4.1.9 Select Client / Supplier / Item）</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D62" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Keyword (Input)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E62" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">關鍵字</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F62" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">搜尋主檔</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G62" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Text</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H62" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">去除前後空白；查詢回到第 1 頁</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I62" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J62" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K62" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.72.2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B63" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.72</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C63" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Select Dialog Interface（BlueWhale 4.4.1.9 Select Client / Supplier / Item）</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D63" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Selection (Checkbox / Row)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E63" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">選取</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F63" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">選擇主檔資料</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G63" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Row key</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H63" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">單選 1 筆、多選跨頁累積；至少 1 筆才可確定</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I63" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.72.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J63" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K63" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="64">
+      <x:c r="A64" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.73.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B64" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.73</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C64" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Standard List Page Template</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D64" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Date Range (Date inputs + quick buttons)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E64" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">開始／結束日期</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F64" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">限制查詢期間</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G64" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">yyyy-MM-dd</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H64" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">含頭尾；快選今天、本週、本月、上月、本季、本年；開始晚於結束時提示</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I64" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J64" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K64" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="65">
+      <x:c r="A65" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.73.2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B65" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.73</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C65" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Standard List Page Template</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D65" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Page Size (Dropdown)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E65" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">每頁筆數</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F65" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">分頁</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G65" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">整數</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H65" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">10／20／50／100／200</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I65" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J65" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K65" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="66">
+      <x:c r="A66" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.74.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B66" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.74</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C66" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Standard Document Page Template</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D66" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Previous / Next (Button)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E66" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">上一筆／下一筆</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F66" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">依列表順序切換單據</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G66" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Button</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H66" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">第一筆停用上一筆、最後一筆停用下一筆</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I66" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J66" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K66" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Developer</x:t>
         </x:is>
@@ -9995,6 +10589,228 @@
         </x:is>
       </x:c>
     </x:row>
+    <x:row r="64">
+      <x:c r="A64" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.31.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B64" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should ask for confirmation in a shared trilingual confirmation box before dangerous actions.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C64" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="D64" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.71</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E64" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.71.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F64" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-UI-001, SYS-UI-002, SYS-UI-003</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G64" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Partial</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="65">
+      <x:c r="A65" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.31.2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B65" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should show results that need the user's attention in a shared prompt box, and short success messages as toasts.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C65" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="D65" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.71</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E65" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.71.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F65" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-UI-001</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G65" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Partial</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="66">
+      <x:c r="A66" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.31.3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B66" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should provide a shared selection window for choosing master data with search and server-side paging.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C66" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="D66" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.72</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E66" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.72.1, REQ_IO_A8.72.2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F66" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-UI-001</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G66" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Partial</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="67">
+      <x:c r="A67" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.31.4</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B67" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should provide a standard list page template reused by every module.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C67" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="D67" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.73</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E67" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.73.2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F67" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-UI-001, SYS-UI-002</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G67" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Partial</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="68">
+      <x:c r="A68" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.31.5</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B68" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should provide a standard document page template with status, previous / next navigation and unsaved-change protection.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C68" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="D68" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.74</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E68" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.74.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F68" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-UI-001</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G68" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Partial</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="69">
+      <x:c r="A69" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.31.6</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B69" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should provide a date range filter with quick ranges and a document status tag following the macaron status colours.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C69" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="D69" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.73, 4.4.1.8.74</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E69" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.73.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F69" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-UI-001</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G69" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Partial</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
   </x:sheetData>
 </x:worksheet>
 </file>

--- a/docs/99-output/MyERP_Requirements.xlsx
+++ b/docs/99-output/MyERP_Requirements.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="1" r:id="Rabb65e98e90d4fe9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Non-Functional" sheetId="2" r:id="Rc72b1a7703fc47e2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Structure" sheetId="3" r:id="R493857cb06894759"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interface" sheetId="4" r:id="R62568a8a0f2c4ab5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traceability Matrix" sheetId="5" r:id="Rda8e9146e6924d5c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BlueWhale Parity" sheetId="6" r:id="R79b7869c7ddd44b7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timeline" sheetId="7" r:id="Rfd4740dbeb1046a7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Human Resources" sheetId="8" r:id="Ra2b7c817e6dd4108"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="9" r:id="Rda868abf61bf4eb0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="1" r:id="R9e0a3cbb52f34d01"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Non-Functional" sheetId="2" r:id="R0f8903d72c5e4cda"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Structure" sheetId="3" r:id="R925b97ca4f234f51"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interface" sheetId="4" r:id="Rd70b9cec24c048b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traceability Matrix" sheetId="5" r:id="Rb937b9c7d9264b64"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BlueWhale Parity" sheetId="6" r:id="Rfc921749e0584fc1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timeline" sheetId="7" r:id="R2cf9e3ea83cd44f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Human Resources" sheetId="8" r:id="R4a004cc7daa44c89"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="9" r:id="R201018fe333f46dd"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2969,6 +2969,258 @@
         </x:is>
       </x:c>
     </x:row>
+    <x:row r="70">
+      <x:c r="A70" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.32.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B70" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C70" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">IP Whitelist</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D70" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E70" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow authorized users to view IP whitelist rules.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F70" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G70" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="H70" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:203</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="71">
+      <x:c r="A71" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.32.2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B71" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C71" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">IP Whitelist</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D71" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E71" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow authorized users to create and deactivate IP whitelist rules.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F71" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G71" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="H71" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:204</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="72">
+      <x:c r="A72" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.32.3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B72" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C72" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">IP Whitelist</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D72" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E72" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow single IPv4 or IPv6 addresses and CIDR networks in system, role or user scope.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F72" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G72" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="H72" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:205</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="73">
+      <x:c r="A73" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.32.4</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B73" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C73" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">IP Whitelist</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D73" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E73" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should reject disallowed requests and audit each rejection.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F73" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G73" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="H73" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:206</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="74">
+      <x:c r="A74" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.32.5</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B74" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C74" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">IP Whitelist</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D74" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E74" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow operators to disable IP filtering through server configuration.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F74" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G74" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="H74" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:207</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="75">
+      <x:c r="A75" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.32.6</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B75" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C75" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">IP Whitelist</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D75" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E75" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should provide a trilingual IP whitelist maintenance page.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F75" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G75" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="H75" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:208</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
   </x:sheetData>
 </x:worksheet>
 </file>
@@ -4457,6 +4709,38 @@
       <x:c r="F17" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">REQ_F4118.29.4, REQ_F4118.29.5, REQ_F4118.29.6, REQ_F4118.29.7, REQ_F4118.29.9</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.102</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B18" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C18" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">sys_ip_whitelist</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D18" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System-wide IP ranges scoped to the system, a role, or a user, with inclusive effective dates and audit/version fields.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E18" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F18" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.32.1, REQ_F4118.32.2, REQ_F4118.32.3, REQ_F4118.32.4</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -10811,6 +11095,228 @@
         </x:is>
       </x:c>
     </x:row>
+    <x:row r="70">
+      <x:c r="A70" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.32.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B70" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow authorized users to view IP whitelist rules.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C70" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.102</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D70" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="E70" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F70" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-IPW-004</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G70" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Partial</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="71">
+      <x:c r="A71" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.32.2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B71" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow authorized users to create and deactivate IP whitelist rules.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C71" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.102</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D71" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="E71" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F71" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-IPW-004, SYS-IPW-005</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G71" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Partial</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="72">
+      <x:c r="A72" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.32.3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B72" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow single IPv4 or IPv6 addresses and CIDR networks in system, role or user scope.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C72" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.102</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D72" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="E72" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F72" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-IPW-001, SYS-IPW-002, SYS-IPW-005</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G72" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Partial</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="73">
+      <x:c r="A73" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.32.4</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B73" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should reject disallowed requests and audit each rejection.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C73" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.102</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D73" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="E73" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F73" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-IPW-003, SYS-IPW-006</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G73" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Partial</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="74">
+      <x:c r="A74" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.32.5</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B74" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow operators to disable IP filtering through server configuration.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C74" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="D74" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="E74" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F74" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-IPW-006</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G74" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Partial</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="75">
+      <x:c r="A75" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.32.6</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B75" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should provide a trilingual IP whitelist maintenance page.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C75" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="D75" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="E75" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F75" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-IPW-007</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G75" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Partial</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
   </x:sheetData>
 </x:worksheet>
 </file>

--- a/docs/99-output/MyERP_Requirements.xlsx
+++ b/docs/99-output/MyERP_Requirements.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="1" r:id="R6882f1b0ae264c8e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Non-Functional" sheetId="2" r:id="R25557b6dbdec4d20"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Structure" sheetId="3" r:id="Ra60262dec98e4c15"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interface" sheetId="4" r:id="R2e9cf23ed85d4651"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traceability Matrix" sheetId="5" r:id="R7544f24ec07443a6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BlueWhale Parity" sheetId="6" r:id="R092b782c6af74c03"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timeline" sheetId="7" r:id="R8b268be8799e4b2f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Human Resources" sheetId="8" r:id="R32345f7fc087498f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="9" r:id="R788440bfd9874bae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="1" r:id="Ra8c920fbf8bc4a64"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Non-Functional" sheetId="2" r:id="R88b2b476cffe4ca1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Structure" sheetId="3" r:id="Rc9e22068e48d4d10"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interface" sheetId="4" r:id="Rd0a1695fef854f71"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traceability Matrix" sheetId="5" r:id="R967f051e10d14b02"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BlueWhale Parity" sheetId="6" r:id="Rac599ffce0274b1a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timeline" sheetId="7" r:id="Rc3f0375624ce4839"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Human Resources" sheetId="8" r:id="Rd51fd2db64414f55"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="9" r:id="R8c4e1e597e1843a3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3767,6 +3767,132 @@
         </x:is>
       </x:c>
     </x:row>
+    <x:row r="89">
+      <x:c r="A89" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.33.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B89" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C89" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">In-app Notification</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D89" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E89" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should enable modules to publish notifications to a user.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F89" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G89" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="H89" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:278</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="90">
+      <x:c r="A90" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.33.2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B90" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C90" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">In-app Notification</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D90" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E90" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should enable user to view notifications.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F90" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G90" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="H90" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:279</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="91">
+      <x:c r="A91" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.33.3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B91" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C91" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">In-app Notification</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D91" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E91" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should enable user to mark notifications as read.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F91" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G91" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="H91" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:280</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
   </x:sheetData>
 </x:worksheet>
 </file>
@@ -5351,6 +5477,38 @@
       <x:c r="F20" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">REQ_F4118.19.1, REQ_F4118.19.2, REQ_F4118.19.3</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.104</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B21" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C21" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">sys_notification</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D21" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">One recipient's company-scoped notification, source identity, read time and expiry.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E21" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F21" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.33.1, REQ_F4118.33.2, REQ_F4118.33.3</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -14631,6 +14789,117 @@
         </x:is>
       </x:c>
     </x:row>
+    <x:row r="89">
+      <x:c r="A89" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.33.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B89" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should enable modules to publish notifications to a user.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C89" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.104</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D89" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="E89" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F89" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-NOTIFY-001, SYS-NOTIFY-002, SYS-NOTIFY-003</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G89" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Partial</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="90">
+      <x:c r="A90" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.33.2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B90" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should enable user to view notifications.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C90" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.104</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D90" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="E90" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F90" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="G90" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Partial</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="91">
+      <x:c r="A91" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.33.3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B91" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should enable user to mark notifications as read.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C91" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.104</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D91" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="E91" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F91" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="G91" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Partial</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
   </x:sheetData>
 </x:worksheet>
 </file>

--- a/docs/99-output/MyERP_Requirements.xlsx
+++ b/docs/99-output/MyERP_Requirements.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="1" r:id="Ra8c920fbf8bc4a64"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Non-Functional" sheetId="2" r:id="R88b2b476cffe4ca1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Structure" sheetId="3" r:id="Rc9e22068e48d4d10"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interface" sheetId="4" r:id="Rd0a1695fef854f71"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traceability Matrix" sheetId="5" r:id="R967f051e10d14b02"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BlueWhale Parity" sheetId="6" r:id="Rac599ffce0274b1a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timeline" sheetId="7" r:id="Rc3f0375624ce4839"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Human Resources" sheetId="8" r:id="Rd51fd2db64414f55"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="9" r:id="R8c4e1e597e1843a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="1" r:id="R92a32419cf0544fb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Non-Functional" sheetId="2" r:id="R6ade4a7194f444bd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Structure" sheetId="3" r:id="R560d1c22942148d9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interface" sheetId="4" r:id="R82b6ca4308084c85"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traceability Matrix" sheetId="5" r:id="Red931584e52b44cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BlueWhale Parity" sheetId="6" r:id="R422d027e019a431f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timeline" sheetId="7" r:id="Rfbfa4b7545c740a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Human Resources" sheetId="8" r:id="R216092e974ac4c82"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="9" r:id="R39acce8a69084017"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3827,7 +3827,7 @@
       </x:c>
       <x:c r="D90" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1.0</x:t>
+          <x:t xml:space="preserve">1.1</x:t>
         </x:is>
       </x:c>
       <x:c r="E90" s="2" t="inlineStr">
@@ -3869,7 +3869,7 @@
       </x:c>
       <x:c r="D91" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1.0</x:t>
+          <x:t xml:space="preserve">1.1</x:t>
         </x:is>
       </x:c>
       <x:c r="E91" s="2" t="inlineStr">
@@ -5523,7 +5523,7 @@
     <x:col min="2" max="2" width="15" customWidth="1"/>
     <x:col min="3" max="3" width="60" customWidth="1"/>
     <x:col min="4" max="4" width="42" customWidth="1"/>
-    <x:col min="5" max="5" width="13" customWidth="1"/>
+    <x:col min="5" max="5" width="16" customWidth="1"/>
     <x:col min="6" max="6" width="23" customWidth="1"/>
     <x:col min="7" max="7" width="60" customWidth="1"/>
     <x:col min="8" max="8" width="60" customWidth="1"/>
@@ -11512,6 +11512,348 @@
         </x:is>
       </x:c>
       <x:c r="K105" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="106">
+      <x:c r="A106" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.76.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B106" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.76</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C106" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Notification View Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D106" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Unread Badge (Label)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E106" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">頂列未讀數</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F106" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">快速辨識新通知</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G106" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Integer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H106" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">0 隱藏；超過 99 顯示 99+</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I106" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">收件箱</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J106" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K106" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="107">
+      <x:c r="A107" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.76.2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B107" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.76</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C107" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Notification View Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D107" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Unread Only (Button)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E107" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">未讀篩選</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F107" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">切換全部／未讀</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G107" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Button</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H107" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">切換後回第 1 頁</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I107" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">通知列表</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J107" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K107" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="108">
+      <x:c r="A108" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.76.3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B108" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.76</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C108" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Notification View Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D108" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Notification List (Table)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E108" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">類別、標題、內文、時間、狀態</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F108" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">瀏覽本人通知</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G108" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Paged table</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H108" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">每頁 20，伺服器分頁</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I108" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">未讀篩選</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J108" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K108" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="109">
+      <x:c r="A109" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.76.4</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B109" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.76</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C109" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Notification View Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D109" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Mark Read (Button)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E109" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">單則已讀</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F109" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">清除該筆未讀狀態</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G109" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Button</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H109" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">只在未讀且有 READ 權限時顯示</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I109" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">通知列表</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J109" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K109" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="110">
+      <x:c r="A110" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.76.5</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B110" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.76</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C110" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Notification View Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D110" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Mark All Read (Button)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E110" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">全部已讀</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F110" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">清除目前公司本人未讀狀態</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G110" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Button</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H110" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">未讀數為 0 時停用</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I110" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">通知列表</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J110" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K110" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="111">
+      <x:c r="A111" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.76.6</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B111" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.76</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C111" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Notification View Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D111" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Open (Link)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E111" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">站內目標</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F111" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">跳至通知相關頁</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G111" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Internal route</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H111" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">無路徑則隱藏</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I111" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">通知列表</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J111" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K111" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Developer</x:t>
         </x:is>
@@ -14844,22 +15186,22 @@
       </x:c>
       <x:c r="D90" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">4.4.1.8.76</x:t>
         </x:is>
       </x:c>
       <x:c r="E90" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.76.1, REQ_IO_A8.76.2, REQ_IO_A8.76.3, REQ_IO_A8.76.6</x:t>
         </x:is>
       </x:c>
       <x:c r="F90" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">SYS-NOTIFY-004, SYS-NOTIFY-005, SYS-NOTIFY-006, SYS-NOTIFY-007</x:t>
         </x:is>
       </x:c>
       <x:c r="G90" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -14881,22 +15223,22 @@
       </x:c>
       <x:c r="D91" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">4.4.1.8.76</x:t>
         </x:is>
       </x:c>
       <x:c r="E91" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.76.4, REQ_IO_A8.76.5</x:t>
         </x:is>
       </x:c>
       <x:c r="F91" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">SYS-NOTIFY-004, SYS-NOTIFY-005, SYS-NOTIFY-006, SYS-NOTIFY-007</x:t>
         </x:is>
       </x:c>
       <x:c r="G91" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>

--- a/docs/99-output/MyERP_Requirements.xlsx
+++ b/docs/99-output/MyERP_Requirements.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="1" r:id="R92a32419cf0544fb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Non-Functional" sheetId="2" r:id="R6ade4a7194f444bd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Structure" sheetId="3" r:id="R560d1c22942148d9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interface" sheetId="4" r:id="R82b6ca4308084c85"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traceability Matrix" sheetId="5" r:id="Red931584e52b44cc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BlueWhale Parity" sheetId="6" r:id="R422d027e019a431f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timeline" sheetId="7" r:id="Rfbfa4b7545c740a1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Human Resources" sheetId="8" r:id="R216092e974ac4c82"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="9" r:id="R39acce8a69084017"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="1" r:id="R6c2d2eaa9fed4ac7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Non-Functional" sheetId="2" r:id="R40c85577b7784da3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Structure" sheetId="3" r:id="R258271d03688483f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interface" sheetId="4" r:id="Rc637c690780043b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traceability Matrix" sheetId="5" r:id="Rd46752d7adf64763"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BlueWhale Parity" sheetId="6" r:id="Rb3d18b34b69b480d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timeline" sheetId="7" r:id="R3c1c1f1926ad4edd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Human Resources" sheetId="8" r:id="R6fb13e6667884e21"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="9" r:id="Ra6d0736215244ec9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -131,7 +131,7 @@
       </x:c>
       <x:c r="D2" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1.1</x:t>
+          <x:t xml:space="preserve">1.2</x:t>
         </x:is>
       </x:c>
       <x:c r="E2" s="2" t="inlineStr">
@@ -146,7 +146,7 @@
       </x:c>
       <x:c r="G2" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">已登入用戶須提供目前密碼與符合政策、不同於舊密碼的新密碼；目前密碼錯誤計入五次鎖定。成功後重設到期日、寫不含密碼的安全稽核、撤銷先前簽發的全部 Refresh Token，回傳目前工作階段的新 Token，前端立即替換 Session。密碼到期不能登入時，登入頁提供入口，以帳號、舊密碼與一次性 Captcha 修改並登入；帳密錯誤維持相同 401。失敗後清空密碼並重新載入 Captcha。</x:t>
+          <x:t xml:space="preserve">已登入用戶須提供目前密碼與符合政策、不同於舊密碼的新密碼；目前密碼錯誤計入五次鎖定，並寫 LOGIN_FAILED 安全稽核（原因 CURRENT_PASSWORD_INVALID，不含密碼）。成功後重設到期日、寫不含密碼的安全稽核、撤銷先前簽發的全部 Refresh Token，回傳目前工作階段的新 Token，前端立即替換 Session。密碼到期不能登入時，登入頁提供入口，以帳號、舊密碼與一次性 Captcha 修改並登入；帳密錯誤維持相同 401。失敗後清空密碼並重新載入 Captcha。</x:t>
         </x:is>
       </x:c>
       <x:c r="H2" s="2" t="inlineStr">
@@ -761,7 +761,7 @@
       </x:c>
       <x:c r="D17" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1.1</x:t>
+          <x:t xml:space="preserve">1.2</x:t>
         </x:is>
       </x:c>
       <x:c r="E17" s="2" t="inlineStr">
@@ -776,7 +776,7 @@
       </x:c>
       <x:c r="G17" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">版本不符回 409；審計欄位記錄修改者；目標公司不是用戶獲授權的公司時回 404。</x:t>
+          <x:t xml:space="preserve">版本不符回 409；審計欄位記錄修改者；目標公司不是用戶獲授權的公司時回 404；操作者在被修改的公司（含已停用）亦須有 SYS.COMPANY.EDIT，否則 403（ADR-032）。</x:t>
         </x:is>
       </x:c>
       <x:c r="H17" s="2" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </x:c>
       <x:c r="D31" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1.0</x:t>
+          <x:t xml:space="preserve">1.1</x:t>
         </x:is>
       </x:c>
       <x:c r="E31" s="2" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </x:c>
       <x:c r="G31" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">需 SYS.USER.EDIT 並帶 version（過期 409）；停用後不可登入與刷新，重新啟用後可登入；不可停用自己 422 SYS.USER.SELF_DEACTIVATION；他公司用戶 404。</x:t>
+          <x:t xml:space="preserve">需 SYS.USER.EDIT 並帶 version（過期 409）；停用後不可登入與刷新，重新啟用後可登入；不可停用自己 422 SYS.USER.SELF_DEACTIVATION；他公司用戶 404；用戶亦屬於其他公司時，操作者在每間已啟用關聯的公司都要有 SYS.USER.EDIT（否則 403 COMMON.PERMISSION.DENIED），且用戶角色不超出操作者權限（否則 403 SYS.ROLE.BEYOND_AUTHORITY），ADR-032。</x:t>
         </x:is>
       </x:c>
       <x:c r="H31" s="2" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </x:c>
       <x:c r="D32" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1.0</x:t>
+          <x:t xml:space="preserve">1.1</x:t>
         </x:is>
       </x:c>
       <x:c r="E32" s="2" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </x:c>
       <x:c r="G32" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">重設密碼需 SYS.USER.RESET_PASSWORD，依密碼政策驗證，重新起算到期並清除鎖定，舊密碼即失效；解鎖需 SYS.USER.EDIT，清除失敗計數與鎖定，未鎖定時亦回 204；他公司用戶 404。</x:t>
+          <x:t xml:space="preserve">重設密碼需 SYS.USER.RESET_PASSWORD，依密碼政策驗證，重新起算到期並清除鎖定，舊密碼即失效；解鎖需 SYS.USER.EDIT，清除失敗計數與鎖定，未鎖定時亦回 204；他公司用戶 404；跨公司與角色上限檢查同 REQ_F4118.23.7（ADR-032）。</x:t>
         </x:is>
       </x:c>
       <x:c r="H32" s="2" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </x:c>
       <x:c r="G40" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">需 SYS.ROLE.EDIT；帶 version，不符回 409，且權限集合不變（同一交易）；停用角色立即不再授予權限。</x:t>
+          <x:t xml:space="preserve">需 SYS.ROLE.EDIT；帶 version，不符回 409，且權限集合不變（同一交易）；停用角色立即不再授予權限。角色是全系統定義：操作者在角色已指派的每間公司都必須全權，否則 403 SYS.AUTHORITY.FULL_ACCESS_REQUIRED（ADR-033）。</x:t>
         </x:is>
       </x:c>
       <x:c r="H40" s="2" t="inlineStr">
@@ -1853,7 +1853,7 @@
       </x:c>
       <x:c r="D43" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1.0</x:t>
+          <x:t xml:space="preserve">1.1</x:t>
         </x:is>
       </x:c>
       <x:c r="E43" s="2" t="inlineStr">
@@ -1868,7 +1868,7 @@
       </x:c>
       <x:c r="G43" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">需 SYS.USER.EDIT；公司必須啟用；分店／部門必須屬於該公司且啟用；角色必須存在且啟用；角色整組取代；每位用戶最多一間預設公司（設定新預設會取消舊預設）。用戶不存在或不屬於目前公司回 404 SYS.USER.NOT_FOUND；目標公司不是操作者獲授權的公司回 404 SYS.COMPANY.NOT_FOUND；不可停用自己的公司授權（422 SYS.USER.SELF_DEACTIVATION）（ADR-017）。</x:t>
+          <x:t xml:space="preserve">需 SYS.USER.EDIT；公司必須啟用；分店／部門必須屬於該公司且啟用；角色必須存在且啟用；角色整組取代；每位用戶最多一間預設公司（設定新預設會取消舊預設）。用戶不存在或不屬於目前公司回 404 SYS.USER.NOT_FOUND；目標公司不是操作者獲授權的公司回 404 SYS.COMPANY.NOT_FOUND；不可停用自己的公司授權（422 SYS.USER.SELF_DEACTIVATION）（ADR-017）。操作者在目標公司亦須有 SYS.USER.EDIT（否則 403 COMMON.PERMISSION.DENIED）；新增或移除的角色須在操作者權限之內（全權角色只限全權操作者；一般角色的每個權限操作者都有且範圍不窄於角色），否則 403 SYS.ROLE.BEYOND_AUTHORITY；不可變更自己的角色（422 SYS.USER.SELF_ROLE_CHANGE），角色不變時可改組織與預設公司（ADR-032）。</x:t>
         </x:is>
       </x:c>
       <x:c r="H43" s="2" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </x:c>
       <x:c r="D89" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1.0</x:t>
+          <x:t xml:space="preserve">1.1</x:t>
         </x:is>
       </x:c>
       <x:c r="E89" s="2" t="inlineStr">
@@ -12495,7 +12495,7 @@
       </x:c>
       <x:c r="F17" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-ORG-005, SYS-ORG-009, SYS-ORG-013, SYS-ORG-021</x:t>
+          <x:t xml:space="preserve">SYS-ORG-005, SYS-ORG-009, SYS-ORG-013, SYS-ORG-021, SYS-PERM-030</x:t>
         </x:is>
       </x:c>
       <x:c r="G17" s="2" t="inlineStr">
@@ -12569,7 +12569,7 @@
       </x:c>
       <x:c r="F19" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-ORG-002, SYS-ORG-004, SYS-ORG-010, SYS-ORG-012, SYS-ORG-020, SYS-ORG-022, SYS-ORG-024, SYS-ORG-025</x:t>
+          <x:t xml:space="preserve">SYS-ORG-002, SYS-ORG-004, SYS-ORG-010, SYS-ORG-012, SYS-ORG-020, SYS-ORG-022, SYS-ORG-024, SYS-ORG-025, SYS-ORG-027</x:t>
         </x:is>
       </x:c>
       <x:c r="G19" s="2" t="inlineStr">
@@ -12680,7 +12680,7 @@
       </x:c>
       <x:c r="F22" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-ORG-002, SYS-ORG-004, SYS-ORG-010, SYS-ORG-012, SYS-ORG-020, SYS-ORG-023, SYS-ORG-026</x:t>
+          <x:t xml:space="preserve">SYS-ORG-002, SYS-ORG-004, SYS-ORG-010, SYS-ORG-012, SYS-ORG-020, SYS-ORG-023, SYS-ORG-026, SYS-ORG-027</x:t>
         </x:is>
       </x:c>
       <x:c r="G22" s="2" t="inlineStr">
@@ -12791,7 +12791,7 @@
       </x:c>
       <x:c r="F25" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-USER-001, SYS-USER-004, SYS-USER-012</x:t>
+          <x:t xml:space="preserve">SYS-ORG-027, SYS-USER-001, SYS-USER-004, SYS-USER-012</x:t>
         </x:is>
       </x:c>
       <x:c r="G25" s="2" t="inlineStr">
@@ -13013,7 +13013,7 @@
       </x:c>
       <x:c r="F31" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-USER-006, SYS-USER-010, SYS-USER-013, SYS-USER-015</x:t>
+          <x:t xml:space="preserve">SYS-USER-006, SYS-USER-010, SYS-USER-013, SYS-USER-015, SYS-PERM-029</x:t>
         </x:is>
       </x:c>
       <x:c r="G31" s="2" t="inlineStr">
@@ -13050,7 +13050,7 @@
       </x:c>
       <x:c r="F32" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-USER-006, SYS-USER-010, SYS-USER-014</x:t>
+          <x:t xml:space="preserve">SYS-USER-006, SYS-USER-010, SYS-USER-014, SYS-PERM-029</x:t>
         </x:is>
       </x:c>
       <x:c r="G32" s="2" t="inlineStr">
@@ -13272,7 +13272,7 @@
       </x:c>
       <x:c r="F38" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-PERM-004, SYS-PERM-011, SYS-PERM-024, SYS-PERM-025</x:t>
+          <x:t xml:space="preserve">SYS-ORG-027, SYS-PERM-004, SYS-PERM-011, SYS-PERM-024, SYS-PERM-025</x:t>
         </x:is>
       </x:c>
       <x:c r="G38" s="2" t="inlineStr">
@@ -13346,7 +13346,7 @@
       </x:c>
       <x:c r="F40" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-PERM-011, SYS-PERM-024, SYS-PERM-025</x:t>
+          <x:t xml:space="preserve">SYS-PERM-011, SYS-PERM-024, SYS-PERM-025, SYS-PERM-031, SYS-PERM-032</x:t>
         </x:is>
       </x:c>
       <x:c r="G40" s="2" t="inlineStr">
@@ -13457,7 +13457,7 @@
       </x:c>
       <x:c r="F43" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-PERM-015, SYS-PERM-016, SYS-PERM-017, SYS-PERM-018, SYS-PERM-026, SYS-PERM-027</x:t>
+          <x:t xml:space="preserve">SYS-PERM-015, SYS-PERM-016, SYS-PERM-017, SYS-PERM-018, SYS-PERM-026, SYS-PERM-027, SYS-PERM-028</x:t>
         </x:is>
       </x:c>
       <x:c r="G43" s="2" t="inlineStr">
@@ -14937,7 +14937,7 @@
       </x:c>
       <x:c r="F83" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-IPW-004</x:t>
+          <x:t xml:space="preserve">SYS-IPW-004, SYS-IPW-009</x:t>
         </x:is>
       </x:c>
       <x:c r="G83" s="2" t="inlineStr">
@@ -14974,7 +14974,7 @@
       </x:c>
       <x:c r="F84" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-IPW-004, SYS-IPW-005</x:t>
+          <x:t xml:space="preserve">SYS-PERM-032, SYS-IPW-004, SYS-IPW-005, SYS-IPW-008, SYS-IPW-009</x:t>
         </x:is>
       </x:c>
       <x:c r="G84" s="2" t="inlineStr">
@@ -15312,12 +15312,12 @@
       </x:c>
       <x:c r="E2" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4111.1.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.24.1</x:t>
         </x:is>
       </x:c>
       <x:c r="F2" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">未開始</x:t>
+          <x:t xml:space="preserve">完成</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -15349,7 +15349,7 @@
       </x:c>
       <x:c r="F3" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">未開始</x:t>
+          <x:t xml:space="preserve">完成</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -15376,12 +15376,12 @@
       </x:c>
       <x:c r="E4" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4111.1.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.24.3</x:t>
         </x:is>
       </x:c>
       <x:c r="F4" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">未開始</x:t>
+          <x:t xml:space="preserve">完成</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -20880,12 +20880,12 @@
       </x:c>
       <x:c r="E176" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.6.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.23.5</x:t>
         </x:is>
       </x:c>
       <x:c r="F176" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">未開始</x:t>
+          <x:t xml:space="preserve">完成</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -20912,12 +20912,12 @@
       </x:c>
       <x:c r="E177" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.6.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.23.6</x:t>
         </x:is>
       </x:c>
       <x:c r="F177" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">未開始</x:t>
+          <x:t xml:space="preserve">完成</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -20944,12 +20944,12 @@
       </x:c>
       <x:c r="E178" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.6.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.25.6</x:t>
         </x:is>
       </x:c>
       <x:c r="F178" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">未開始</x:t>
+          <x:t xml:space="preserve">完成</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -20976,12 +20976,12 @@
       </x:c>
       <x:c r="E179" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.6.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.23.7</x:t>
         </x:is>
       </x:c>
       <x:c r="F179" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">未開始</x:t>
+          <x:t xml:space="preserve">完成</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -22160,12 +22160,12 @@
       </x:c>
       <x:c r="E216" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.16.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.27.6</x:t>
         </x:is>
       </x:c>
       <x:c r="F216" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">未開始</x:t>
+          <x:t xml:space="preserve">完成</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -22192,12 +22192,12 @@
       </x:c>
       <x:c r="E217" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.16.2</x:t>
+          <x:t xml:space="preserve">-</x:t>
         </x:is>
       </x:c>
       <x:c r="F217" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">未開始</x:t>
+          <x:t xml:space="preserve">WONT_DO</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -22416,12 +22416,12 @@
       </x:c>
       <x:c r="E224" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.1.1</x:t>
+          <x:t xml:space="preserve">4.4.1.8.62</x:t>
         </x:is>
       </x:c>
       <x:c r="F224" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">未開始</x:t>
+          <x:t xml:space="preserve">完成</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -22453,7 +22453,7 @@
       </x:c>
       <x:c r="F225" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">未開始</x:t>
+          <x:t xml:space="preserve">完成</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -22485,7 +22485,7 @@
       </x:c>
       <x:c r="F226" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">未開始</x:t>
+          <x:t xml:space="preserve">完成</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -26000,12 +26000,12 @@
       </x:c>
       <x:c r="E336" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.23</x:t>
+          <x:t xml:space="preserve">4.4.1.8.63</x:t>
         </x:is>
       </x:c>
       <x:c r="F336" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">未開始</x:t>
+          <x:t xml:space="preserve">完成</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -26032,12 +26032,12 @@
       </x:c>
       <x:c r="E337" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.24</x:t>
+          <x:t xml:space="preserve">4.4.1.8.61</x:t>
         </x:is>
       </x:c>
       <x:c r="F337" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">未開始</x:t>
+          <x:t xml:space="preserve">完成</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -26064,12 +26064,12 @@
       </x:c>
       <x:c r="E338" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.25</x:t>
+          <x:t xml:space="preserve">4.4.1.8.63</x:t>
         </x:is>
       </x:c>
       <x:c r="F338" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">未開始</x:t>
+          <x:t xml:space="preserve">完成</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -26096,12 +26096,12 @@
       </x:c>
       <x:c r="E339" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.26</x:t>
+          <x:t xml:space="preserve">4.4.1.8.65</x:t>
         </x:is>
       </x:c>
       <x:c r="F339" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">未開始</x:t>
+          <x:t xml:space="preserve">完成</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -26992,12 +26992,12 @@
       </x:c>
       <x:c r="E367" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.54</x:t>
+          <x:t xml:space="preserve">4.4.1.8.66</x:t>
         </x:is>
       </x:c>
       <x:c r="F367" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">未開始</x:t>
+          <x:t xml:space="preserve">完成</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -27829,7 +27829,7 @@
       </x:c>
       <x:c r="F393" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">進行中</x:t>
+          <x:t xml:space="preserve">完成</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -27893,7 +27893,7 @@
       </x:c>
       <x:c r="F395" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">進行中</x:t>
+          <x:t xml:space="preserve">完成</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -27920,12 +27920,12 @@
       </x:c>
       <x:c r="E396" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">sys_operation_log</x:t>
+          <x:t xml:space="preserve">sys_audit_log</x:t>
         </x:is>
       </x:c>
       <x:c r="F396" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">未開始</x:t>
+          <x:t xml:space="preserve">完成</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -28080,12 +28080,12 @@
       </x:c>
       <x:c r="E401" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">sys_announcement</x:t>
+          <x:t xml:space="preserve">—</x:t>
         </x:is>
       </x:c>
       <x:c r="F401" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">未開始</x:t>
+          <x:t xml:space="preserve">WONT_DO</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -28304,12 +28304,12 @@
       </x:c>
       <x:c r="E408" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">sys_announcement</x:t>
+          <x:t xml:space="preserve">sys_notification</x:t>
         </x:is>
       </x:c>
       <x:c r="F408" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">未開始</x:t>
+          <x:t xml:space="preserve">完成</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -28368,12 +28368,12 @@
       </x:c>
       <x:c r="E410" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">sys_menu</x:t>
+          <x:t xml:space="preserve">sys_role_permission</x:t>
         </x:is>
       </x:c>
       <x:c r="F410" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">未開始</x:t>
+          <x:t xml:space="preserve">完成</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -29296,12 +29296,12 @@
       </x:c>
       <x:c r="E439" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">sys_role_permission</x:t>
+          <x:t xml:space="preserve">sys_user_role</x:t>
         </x:is>
       </x:c>
       <x:c r="F439" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">未開始</x:t>
+          <x:t xml:space="preserve">完成</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -29461,7 +29461,7 @@
       </x:c>
       <x:c r="F444" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">未開始</x:t>
+          <x:t xml:space="preserve">完成</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -29557,7 +29557,7 @@
       </x:c>
       <x:c r="F447" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">未開始</x:t>
+          <x:t xml:space="preserve">完成</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -29776,12 +29776,12 @@
       </x:c>
       <x:c r="E454" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">sys_permission</x:t>
+          <x:t xml:space="preserve">sys_role_permission</x:t>
         </x:is>
       </x:c>
       <x:c r="F454" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">未開始</x:t>
+          <x:t xml:space="preserve">完成</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -29813,7 +29813,7 @@
       </x:c>
       <x:c r="F455" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">進行中</x:t>
+          <x:t xml:space="preserve">完成</x:t>
         </x:is>
       </x:c>
     </x:row>

--- a/docs/99-output/MyERP_Requirements.xlsx
+++ b/docs/99-output/MyERP_Requirements.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="1" r:id="Rc0da54706e924e91"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Non-Functional" sheetId="2" r:id="R02ff6b143efa477b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Structure" sheetId="3" r:id="Re68ee7b5cc654726"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interface" sheetId="4" r:id="Rbedc4a6c140140fe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traceability Matrix" sheetId="5" r:id="Rc2bdd853477d49df"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BlueWhale Parity" sheetId="6" r:id="R7724cbeaa76e4871"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timeline" sheetId="7" r:id="R6c3ed927a76b4e55"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Human Resources" sheetId="8" r:id="Rf50b488cc6e44767"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="9" r:id="Rea5a5e5f590f49fa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="1" r:id="Rb2b65739982c45a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Non-Functional" sheetId="2" r:id="Rdb394ae0acfc4077"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Structure" sheetId="3" r:id="R1e84137b65e94d87"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interface" sheetId="4" r:id="Refe5e5295e9a4d5e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traceability Matrix" sheetId="5" r:id="R6cc28b6ded364017"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BlueWhale Parity" sheetId="6" r:id="R07e1148bcf8841d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timeline" sheetId="7" r:id="R694e7a05ec494884"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Human Resources" sheetId="8" r:id="Rbef0760bd6b74b7c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="9" r:id="R91755afcdef04e9f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -830,7 +830,7 @@
     <x:row r="19">
       <x:c r="A19" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.13.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.10.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B19" s="2" t="inlineStr">
@@ -840,7 +840,7 @@
       </x:c>
       <x:c r="C19" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Unit of Measurement</x:t>
+          <x:t xml:space="preserve">Item Category</x:t>
         </x:is>
       </x:c>
       <x:c r="D19" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </x:c>
       <x:c r="E19" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to view unit of measurement.</x:t>
+          <x:t xml:space="preserve">System should enable user to view item category.</x:t>
         </x:is>
       </x:c>
       <x:c r="F19" s="2" t="inlineStr">
@@ -860,19 +860,19 @@
       </x:c>
       <x:c r="G19" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">具 MD.UOM.VIEW 可按目前公司以代碼或名稱搜尋、分頁及排序（代碼／名稱）單位，含停用單位；可查看全部換算及以換算試算數量（結果按目標單位小數位數四捨五入）。排除軟刪除及別公司資料；未選公司回 403。</x:t>
+          <x:t xml:space="preserve">具 MD.ITEM_CATEGORY.VIEW 可取得目前公司全部未刪除分類（含停用，按代碼排序），以 parentId 組成最多 5 層的樹；排除別公司資料；未選公司回 403。</x:t>
         </x:is>
       </x:c>
       <x:c r="H19" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:77</x:t>
+          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:93</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.13.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.10.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B20" s="2" t="inlineStr">
@@ -882,7 +882,7 @@
       </x:c>
       <x:c r="C20" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Unit of Measurement</x:t>
+          <x:t xml:space="preserve">Item Category</x:t>
         </x:is>
       </x:c>
       <x:c r="D20" s="2" t="inlineStr">
@@ -892,7 +892,7 @@
       </x:c>
       <x:c r="E20" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to create unit of measurement.</x:t>
+          <x:t xml:space="preserve">System should enable user to create item category.</x:t>
         </x:is>
       </x:c>
       <x:c r="F20" s="2" t="inlineStr">
@@ -902,19 +902,19 @@
       </x:c>
       <x:c r="G20" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">具 CREATE 權限可建立公司內唯一代碼（1–30 英數、-、_，轉大寫）、非空白名稱（最多 200 字）及小數位數（0–6）的單位；重複代碼回 409 MD.UOM.DUPLICATE_CODE。可新增換算（1 來源 = 係數 目標；係數 &gt; 0、最多 9 位整數及 6 位小數）：兩端須為本公司啟用單位且不同；兩單位已可直接、反向或經其他單位換算時回 409 MD.UOM_CONVERSION.PATH_EXISTS。</x:t>
+          <x:t xml:space="preserve">具 CREATE 權限可建立公司內唯一代碼（1–30 英數、-、_，轉大寫，軟刪除後仍保留）、非空白名稱（最多 200 字）的分類，可選上層；上層必須是本公司未刪除且啟用的分類（否則 422 MD.ITEM_CATEGORY.INVALID_PARENT），超過 5 層回 422 MD.ITEM_CATEGORY.TOO_DEEP；重複代碼 409 MD.ITEM_CATEGORY.DUPLICATE_CODE。</x:t>
         </x:is>
       </x:c>
       <x:c r="H20" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:78</x:t>
+          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:94</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.13.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.10.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B21" s="2" t="inlineStr">
@@ -924,7 +924,7 @@
       </x:c>
       <x:c r="C21" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Unit of Measurement</x:t>
+          <x:t xml:space="preserve">Item Category</x:t>
         </x:is>
       </x:c>
       <x:c r="D21" s="2" t="inlineStr">
@@ -934,7 +934,7 @@
       </x:c>
       <x:c r="E21" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to edit unit of measurement.</x:t>
+          <x:t xml:space="preserve">System should enable user to edit item category.</x:t>
         </x:is>
       </x:c>
       <x:c r="F21" s="2" t="inlineStr">
@@ -944,19 +944,19 @@
       </x:c>
       <x:c r="G21" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">具 EDIT 權限可帶版本修改單位名稱、小數位數及啟用狀態（代碼不可變），以及換算係數；版本衝突 409，別公司或不存在 404（MD.UOM.NOT_FOUND／MD.UOM_CONVERSION.NOT_FOUND）。</x:t>
+          <x:t xml:space="preserve">具 EDIT 權限可帶版本修改名稱、啟用狀態與上層（整棵子樹一起移動）；代碼不可變。不可掛到自己或子孫下（422 MD.ITEM_CATEGORY.CYCLE），移動後子樹不可超過 5 層；上層不變時即使已停用亦可保留。版本衝突 409，別公司或不存在 404 MD.ITEM_CATEGORY.NOT_FOUND。</x:t>
         </x:is>
       </x:c>
       <x:c r="H21" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:79</x:t>
+          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:95</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.13.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.10.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B22" s="2" t="inlineStr">
@@ -966,7 +966,7 @@
       </x:c>
       <x:c r="C22" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Unit of Measurement</x:t>
+          <x:t xml:space="preserve">Item Category</x:t>
         </x:is>
       </x:c>
       <x:c r="D22" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </x:c>
       <x:c r="E22" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to delete unit of measurement.</x:t>
+          <x:t xml:space="preserve">System should enable user to delete item category.</x:t>
         </x:is>
       </x:c>
       <x:c r="F22" s="2" t="inlineStr">
@@ -986,19 +986,19 @@
       </x:c>
       <x:c r="G22" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">具 DELETE 權限可帶版本軟刪除單位或換算；單位代碼刪除後仍保留；被換算引用的單位回 409 MD.UOM.IN_USE，只可停用。</x:t>
+          <x:t xml:space="preserve">具 DELETE 權限可帶版本軟刪除分類；有未刪除子分類時回 409 MD.ITEM_CATEGORY.HAS_CHILDREN。物料主檔（WU-MD-012）加入後，被物料引用的分類亦不可刪除。</x:t>
         </x:is>
       </x:c>
       <x:c r="H22" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:80</x:t>
+          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:96</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.17.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.11.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B23" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </x:c>
       <x:c r="C23" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Parameter Settings</x:t>
+          <x:t xml:space="preserve">Item Brand</x:t>
         </x:is>
       </x:c>
       <x:c r="D23" s="2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </x:c>
       <x:c r="E23" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to view parameter settings.</x:t>
+          <x:t xml:space="preserve">System should enable user to view item brand.</x:t>
         </x:is>
       </x:c>
       <x:c r="F23" s="2" t="inlineStr">
@@ -1028,19 +1028,19 @@
       </x:c>
       <x:c r="G23" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">具 MD.ITEM_BRAND.VIEW 可按目前公司以代碼或名稱搜尋、分頁及排序（代碼／名稱）品牌，含停用品牌；排除軟刪除及別公司資料；未選公司回 403。</x:t>
         </x:is>
       </x:c>
       <x:c r="H23" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:234</x:t>
+          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:97</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.17.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.11.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B24" s="2" t="inlineStr">
@@ -1050,7 +1050,7 @@
       </x:c>
       <x:c r="C24" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Parameter Settings</x:t>
+          <x:t xml:space="preserve">Item Brand</x:t>
         </x:is>
       </x:c>
       <x:c r="D24" s="2" t="inlineStr">
@@ -1060,7 +1060,7 @@
       </x:c>
       <x:c r="E24" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to edit parameter settings.</x:t>
+          <x:t xml:space="preserve">System should enable user to create item brand.</x:t>
         </x:is>
       </x:c>
       <x:c r="F24" s="2" t="inlineStr">
@@ -1070,19 +1070,19 @@
       </x:c>
       <x:c r="G24" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">具 CREATE 權限可建立公司內唯一代碼（規則同分類）、非空白名稱的品牌；重複代碼 409 MD.ITEM_BRAND.DUPLICATE_CODE。</x:t>
         </x:is>
       </x:c>
       <x:c r="H24" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:235</x:t>
+          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:98</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.17.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.11.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B25" s="2" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </x:c>
       <x:c r="C25" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Parameter Settings</x:t>
+          <x:t xml:space="preserve">Item Brand</x:t>
         </x:is>
       </x:c>
       <x:c r="D25" s="2" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </x:c>
       <x:c r="E25" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should let every module declare typed company parameters with defaults and read them in process.</x:t>
+          <x:t xml:space="preserve">System should enable user to edit item brand.</x:t>
         </x:is>
       </x:c>
       <x:c r="F25" s="2" t="inlineStr">
@@ -1112,19 +1112,19 @@
       </x:c>
       <x:c r="G25" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">具 EDIT 權限可帶版本修改名稱及啟用狀態（代碼不可變）；版本衝突 409，別公司或不存在 404 MD.ITEM_BRAND.NOT_FOUND。</x:t>
         </x:is>
       </x:c>
       <x:c r="H25" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:236</x:t>
+          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:99</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.17.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.11.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B26" s="2" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </x:c>
       <x:c r="C26" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Parameter Settings</x:t>
+          <x:t xml:space="preserve">Item Brand</x:t>
         </x:is>
       </x:c>
       <x:c r="D26" s="2" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </x:c>
       <x:c r="E26" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should provide a parameter edit interface grouped by module.</x:t>
+          <x:t xml:space="preserve">System should enable user to delete item brand.</x:t>
         </x:is>
       </x:c>
       <x:c r="F26" s="2" t="inlineStr">
@@ -1154,19 +1154,19 @@
       </x:c>
       <x:c r="G26" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">具 DELETE 權限可帶版本軟刪除品牌，代碼仍保留。物料主檔（WU-MD-012）加入後，被物料引用的品牌回 409 MD.ITEM_BRAND.IN_USE，只可停用。</x:t>
         </x:is>
       </x:c>
       <x:c r="H26" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:237</x:t>
+          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:100</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.18.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.13.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B27" s="2" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </x:c>
       <x:c r="C27" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Print Settings</x:t>
+          <x:t xml:space="preserve">Unit of Measurement</x:t>
         </x:is>
       </x:c>
       <x:c r="D27" s="2" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </x:c>
       <x:c r="E27" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to view print settings.</x:t>
+          <x:t xml:space="preserve">System should enable user to view unit of measurement.</x:t>
         </x:is>
       </x:c>
       <x:c r="F27" s="2" t="inlineStr">
@@ -1196,19 +1196,19 @@
       </x:c>
       <x:c r="G27" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">具 MD.UOM.VIEW 可按目前公司以代碼或名稱搜尋、分頁及排序（代碼／名稱）單位，含停用單位；可查看全部換算及以換算試算數量（結果按目標單位小數位數四捨五入）。排除軟刪除及別公司資料；未選公司回 403。</x:t>
         </x:is>
       </x:c>
       <x:c r="H27" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:250</x:t>
+          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:77</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.18.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.13.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B28" s="2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </x:c>
       <x:c r="C28" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Print Settings</x:t>
+          <x:t xml:space="preserve">Unit of Measurement</x:t>
         </x:is>
       </x:c>
       <x:c r="D28" s="2" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </x:c>
       <x:c r="E28" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to edit print settings.</x:t>
+          <x:t xml:space="preserve">System should enable user to create unit of measurement.</x:t>
         </x:is>
       </x:c>
       <x:c r="F28" s="2" t="inlineStr">
@@ -1238,19 +1238,19 @@
       </x:c>
       <x:c r="G28" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">具 CREATE 權限可建立公司內唯一代碼（1–30 英數、-、_，轉大寫）、非空白名稱（最多 200 字）及小數位數（0–6）的單位；重複代碼回 409 MD.UOM.DUPLICATE_CODE。可新增換算（1 來源 = 係數 目標；係數 &gt; 0、最多 9 位整數及 6 位小數）：兩端須為本公司啟用單位且不同；兩單位已可直接、反向或經其他單位換算時回 409 MD.UOM_CONVERSION.PATH_EXISTS。</x:t>
         </x:is>
       </x:c>
       <x:c r="H28" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:251</x:t>
+          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:78</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.18.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.13.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B29" s="2" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </x:c>
       <x:c r="C29" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Print Settings</x:t>
+          <x:t xml:space="preserve">Unit of Measurement</x:t>
         </x:is>
       </x:c>
       <x:c r="D29" s="2" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </x:c>
       <x:c r="E29" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should let printing modules read the company's print settings.</x:t>
+          <x:t xml:space="preserve">System should enable user to edit unit of measurement.</x:t>
         </x:is>
       </x:c>
       <x:c r="F29" s="2" t="inlineStr">
@@ -1280,19 +1280,19 @@
       </x:c>
       <x:c r="G29" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">具 EDIT 權限可帶版本修改單位名稱、小數位數及啟用狀態（代碼不可變），以及換算係數；版本衝突 409，別公司或不存在 404（MD.UOM.NOT_FOUND／MD.UOM_CONVERSION.NOT_FOUND）。</x:t>
         </x:is>
       </x:c>
       <x:c r="H29" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:252</x:t>
+          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:79</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.19.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.13.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B30" s="2" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </x:c>
       <x:c r="C30" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Logo &amp; Stamp</x:t>
+          <x:t xml:space="preserve">Unit of Measurement</x:t>
         </x:is>
       </x:c>
       <x:c r="D30" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </x:c>
       <x:c r="E30" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to view the logo and stamp.</x:t>
+          <x:t xml:space="preserve">System should enable user to delete unit of measurement.</x:t>
         </x:is>
       </x:c>
       <x:c r="F30" s="2" t="inlineStr">
@@ -1322,19 +1322,19 @@
       </x:c>
       <x:c r="G30" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">具 DELETE 權限可帶版本軟刪除單位或換算；單位代碼刪除後仍保留；被換算引用的單位回 409 MD.UOM.IN_USE，只可停用。</x:t>
         </x:is>
       </x:c>
       <x:c r="H30" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:264</x:t>
+          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:80</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.19.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.17.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B31" s="2" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </x:c>
       <x:c r="C31" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Logo &amp; Stamp</x:t>
+          <x:t xml:space="preserve">Parameter Settings</x:t>
         </x:is>
       </x:c>
       <x:c r="D31" s="2" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </x:c>
       <x:c r="E31" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to edit the logo and stamp.</x:t>
+          <x:t xml:space="preserve">System should enable user to view parameter settings.</x:t>
         </x:is>
       </x:c>
       <x:c r="F31" s="2" t="inlineStr">
@@ -1369,14 +1369,14 @@
       </x:c>
       <x:c r="H31" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:265</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:234</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.19.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.17.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B32" s="2" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </x:c>
       <x:c r="C32" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Logo &amp; Stamp</x:t>
+          <x:t xml:space="preserve">Parameter Settings</x:t>
         </x:is>
       </x:c>
       <x:c r="D32" s="2" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </x:c>
       <x:c r="E32" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should let printing modules read the company's logo and stamp.</x:t>
+          <x:t xml:space="preserve">System should enable user to edit parameter settings.</x:t>
         </x:is>
       </x:c>
       <x:c r="F32" s="2" t="inlineStr">
@@ -1411,14 +1411,14 @@
       </x:c>
       <x:c r="H32" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:266</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:235</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.20.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.17.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B33" s="2" t="inlineStr">
@@ -1428,17 +1428,17 @@
       </x:c>
       <x:c r="C33" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Company Management</x:t>
+          <x:t xml:space="preserve">Parameter Settings</x:t>
         </x:is>
       </x:c>
       <x:c r="D33" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1.2</x:t>
+          <x:t xml:space="preserve">1.0</x:t>
         </x:is>
       </x:c>
       <x:c r="E33" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to view company details.</x:t>
+          <x:t xml:space="preserve">System should let every module declare typed company parameters with defaults and read them in process.</x:t>
         </x:is>
       </x:c>
       <x:c r="F33" s="2" t="inlineStr">
@@ -1448,19 +1448,19 @@
       </x:c>
       <x:c r="G33" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">僅有組織檢視權的用戶可見其獲授權且未刪除的公司；預設只列啟用公司，勾選「顯示已停用」時一併列出停用公司；列表支援分頁、關鍵字及代碼／名稱排序；無權限回 403。</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="H33" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:13</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:236</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.20.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.17.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B34" s="2" t="inlineStr">
@@ -1470,17 +1470,17 @@
       </x:c>
       <x:c r="C34" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Company Management</x:t>
+          <x:t xml:space="preserve">Parameter Settings</x:t>
         </x:is>
       </x:c>
       <x:c r="D34" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1.2</x:t>
+          <x:t xml:space="preserve">1.0</x:t>
         </x:is>
       </x:c>
       <x:c r="E34" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to create a company.</x:t>
+          <x:t xml:space="preserve">System should provide a parameter edit interface grouped by module.</x:t>
         </x:is>
       </x:c>
       <x:c r="F34" s="2" t="inlineStr">
@@ -1490,19 +1490,19 @@
       </x:c>
       <x:c r="G34" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">代碼全系統唯一；代碼與名稱必填；代碼限 1–30 字元的 ASCII 英文、數字、-、_，保存為大寫；重複代碼回 409；建立者在同一交易內獲授權新公司，角色沿用其在目前公司的角色（ADR-015）。</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="H34" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:14</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:237</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.20.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.18.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B35" s="2" t="inlineStr">
@@ -1512,17 +1512,17 @@
       </x:c>
       <x:c r="C35" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Company Management</x:t>
+          <x:t xml:space="preserve">Print Settings</x:t>
         </x:is>
       </x:c>
       <x:c r="D35" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1.2</x:t>
+          <x:t xml:space="preserve">1.0</x:t>
         </x:is>
       </x:c>
       <x:c r="E35" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to edit a company.</x:t>
+          <x:t xml:space="preserve">System should enable user to view print settings.</x:t>
         </x:is>
       </x:c>
       <x:c r="F35" s="2" t="inlineStr">
@@ -1532,19 +1532,19 @@
       </x:c>
       <x:c r="G35" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">版本不符回 409；審計欄位記錄修改者；目標公司不是用戶獲授權的公司時回 404；操作者在被修改的公司（含已停用）亦須有 SYS.COMPANY.EDIT，否則 403（ADR-032）。</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="H35" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:15</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:250</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.20.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.18.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B36" s="2" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </x:c>
       <x:c r="C36" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Company Management</x:t>
+          <x:t xml:space="preserve">Print Settings</x:t>
         </x:is>
       </x:c>
       <x:c r="D36" s="2" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </x:c>
       <x:c r="E36" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to deactivate a company.</x:t>
+          <x:t xml:space="preserve">System should enable user to edit print settings.</x:t>
         </x:is>
       </x:c>
       <x:c r="F36" s="2" t="inlineStr">
@@ -1574,19 +1574,19 @@
       </x:c>
       <x:c r="G36" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">停用後不能成為新操作的公司上下文；歷史資料保留。</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="H36" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:16</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:251</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.21.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.18.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B37" s="2" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </x:c>
       <x:c r="C37" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Branch Management</x:t>
+          <x:t xml:space="preserve">Print Settings</x:t>
         </x:is>
       </x:c>
       <x:c r="D37" s="2" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </x:c>
       <x:c r="E37" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to view branches in the selected company.</x:t>
+          <x:t xml:space="preserve">System should let printing modules read the company's print settings.</x:t>
         </x:is>
       </x:c>
       <x:c r="F37" s="2" t="inlineStr">
@@ -1616,19 +1616,19 @@
       </x:c>
       <x:c r="G37" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">公司 A 的查詢不返回公司 B 分店；未選公司結果為空。</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="H37" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:17</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:252</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.21.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.19.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B38" s="2" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </x:c>
       <x:c r="C38" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Branch Management</x:t>
+          <x:t xml:space="preserve">Logo &amp; Stamp</x:t>
         </x:is>
       </x:c>
       <x:c r="D38" s="2" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </x:c>
       <x:c r="E38" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to create a branch.</x:t>
+          <x:t xml:space="preserve">System should enable user to view the logo and stamp.</x:t>
         </x:is>
       </x:c>
       <x:c r="F38" s="2" t="inlineStr">
@@ -1658,19 +1658,19 @@
       </x:c>
       <x:c r="G38" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">公司內代碼唯一；所屬公司必須為授權公司。</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="H38" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:18</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:264</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.21.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.19.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B39" s="2" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </x:c>
       <x:c r="C39" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Branch Management</x:t>
+          <x:t xml:space="preserve">Logo &amp; Stamp</x:t>
         </x:is>
       </x:c>
       <x:c r="D39" s="2" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </x:c>
       <x:c r="E39" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to edit or deactivate a branch.</x:t>
+          <x:t xml:space="preserve">System should enable user to edit the logo and stamp.</x:t>
         </x:is>
       </x:c>
       <x:c r="F39" s="2" t="inlineStr">
@@ -1700,19 +1700,19 @@
       </x:c>
       <x:c r="G39" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">版本不符回 409；被引用時只可停用，不得刪除。</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="H39" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:19</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:265</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.22.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.19.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B40" s="2" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </x:c>
       <x:c r="C40" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Department Management</x:t>
+          <x:t xml:space="preserve">Logo &amp; Stamp</x:t>
         </x:is>
       </x:c>
       <x:c r="D40" s="2" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </x:c>
       <x:c r="E40" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to view departments in the selected company.</x:t>
+          <x:t xml:space="preserve">System should let printing modules read the company's logo and stamp.</x:t>
         </x:is>
       </x:c>
       <x:c r="F40" s="2" t="inlineStr">
@@ -1742,19 +1742,19 @@
       </x:c>
       <x:c r="G40" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">公司隔離、軟刪除篩選生效。</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="H40" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:20</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:266</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.22.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.20.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B41" s="2" t="inlineStr">
@@ -1764,17 +1764,17 @@
       </x:c>
       <x:c r="C41" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Department Management</x:t>
+          <x:t xml:space="preserve">Company Management</x:t>
         </x:is>
       </x:c>
       <x:c r="D41" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1.0</x:t>
+          <x:t xml:space="preserve">1.2</x:t>
         </x:is>
       </x:c>
       <x:c r="E41" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to create a department under a branch or parent department.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to view company details.</x:t>
         </x:is>
       </x:c>
       <x:c r="F41" s="2" t="inlineStr">
@@ -1784,19 +1784,19 @@
       </x:c>
       <x:c r="G41" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">分店與上級部門必須屬於同一公司；不得循環參照。</x:t>
+          <x:t xml:space="preserve">僅有組織檢視權的用戶可見其獲授權且未刪除的公司；預設只列啟用公司，勾選「顯示已停用」時一併列出停用公司；列表支援分頁、關鍵字及代碼／名稱排序；無權限回 403。</x:t>
         </x:is>
       </x:c>
       <x:c r="H41" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:21</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:13</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.22.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.20.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B42" s="2" t="inlineStr">
@@ -1806,17 +1806,17 @@
       </x:c>
       <x:c r="C42" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Department Management</x:t>
+          <x:t xml:space="preserve">Company Management</x:t>
         </x:is>
       </x:c>
       <x:c r="D42" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1.0</x:t>
+          <x:t xml:space="preserve">1.2</x:t>
         </x:is>
       </x:c>
       <x:c r="E42" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to edit or deactivate a department.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to create a company.</x:t>
         </x:is>
       </x:c>
       <x:c r="F42" s="2" t="inlineStr">
@@ -1826,19 +1826,19 @@
       </x:c>
       <x:c r="G42" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">版本不符回 409；被引用時只可停用。</x:t>
+          <x:t xml:space="preserve">代碼全系統唯一；代碼與名稱必填；代碼限 1–30 字元的 ASCII 英文、數字、-、_，保存為大寫；重複代碼回 409；建立者在同一交易內獲授權新公司，角色沿用其在目前公司的角色（ADR-015）。</x:t>
         </x:is>
       </x:c>
       <x:c r="H42" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:22</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:14</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.23.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.20.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B43" s="2" t="inlineStr">
@@ -1848,17 +1848,17 @@
       </x:c>
       <x:c r="C43" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">User Identity and Password Security</x:t>
+          <x:t xml:space="preserve">Company Management</x:t>
         </x:is>
       </x:c>
       <x:c r="D43" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1.0</x:t>
+          <x:t xml:space="preserve">1.2</x:t>
         </x:is>
       </x:c>
       <x:c r="E43" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to create a unique user identity.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to edit a company.</x:t>
         </x:is>
       </x:c>
       <x:c r="F43" s="2" t="inlineStr">
@@ -1868,19 +1868,19 @@
       </x:c>
       <x:c r="G43" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">帳號不分大小寫唯一，停用及軟刪除後仍不可重用；僅保存雜湊，不保存明文密碼。</x:t>
+          <x:t xml:space="preserve">版本不符回 409；審計欄位記錄修改者；目標公司不是用戶獲授權的公司時回 404；操作者在被修改的公司（含已停用）亦須有 SYS.COMPANY.EDIT，否則 403（ADR-032）。</x:t>
         </x:is>
       </x:c>
       <x:c r="H43" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:54</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:15</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.23.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.20.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B44" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </x:c>
       <x:c r="C44" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">User Identity and Password Security</x:t>
+          <x:t xml:space="preserve">Company Management</x:t>
         </x:is>
       </x:c>
       <x:c r="D44" s="2" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </x:c>
       <x:c r="E44" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enforce a configurable password policy.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to deactivate a company.</x:t>
         </x:is>
       </x:c>
       <x:c r="F44" s="2" t="inlineStr">
@@ -1910,19 +1910,19 @@
       </x:c>
       <x:c r="G44" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">預設 12–128 字元且含大小寫、數字及符號；長度、複雜度與到期天數可由設定調整，不合法設定拒絕啟動。</x:t>
+          <x:t xml:space="preserve">停用後不能成為新操作的公司上下文；歷史資料保留。</x:t>
         </x:is>
       </x:c>
       <x:c r="H44" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:55</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:16</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.23.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.21.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B45" s="2" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </x:c>
       <x:c r="C45" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">User Identity and Password Security</x:t>
+          <x:t xml:space="preserve">Branch Management</x:t>
         </x:is>
       </x:c>
       <x:c r="D45" s="2" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </x:c>
       <x:c r="E45" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should lock an account after five consecutive failed password attempts.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to view branches in the selected company.</x:t>
         </x:is>
       </x:c>
       <x:c r="F45" s="2" t="inlineStr">
@@ -1952,19 +1952,19 @@
       </x:c>
       <x:c r="G45" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">第 5 次連續失敗鎖定 15 分鐘；鎖定期間正確密碼亦不得通過；鎖定到期後開啟新失敗計數窗口，成功後清除計數。</x:t>
+          <x:t xml:space="preserve">公司 A 的查詢不返回公司 B 分店；未選公司結果為空。</x:t>
         </x:is>
       </x:c>
       <x:c r="H45" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:56</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:17</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.23.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.21.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B46" s="2" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </x:c>
       <x:c r="C46" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">User Identity and Password Security</x:t>
+          <x:t xml:space="preserve">Branch Management</x:t>
         </x:is>
       </x:c>
       <x:c r="D46" s="2" t="inlineStr">
@@ -1984,7 +1984,7 @@
       </x:c>
       <x:c r="E46" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should determine whether a user's password has expired.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to create a branch.</x:t>
         </x:is>
       </x:c>
       <x:c r="F46" s="2" t="inlineStr">
@@ -1994,19 +1994,19 @@
       </x:c>
       <x:c r="G46" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">依設定天數及 password_changed_at 判斷；0 代表不設到期。登入簽發 Token 前必須檢查。</x:t>
+          <x:t xml:space="preserve">公司內代碼唯一；所屬公司必須為授權公司。</x:t>
         </x:is>
       </x:c>
       <x:c r="H46" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:57</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:18</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.23.5</x:t>
+          <x:t xml:space="preserve">REQ_F4118.21.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B47" s="2" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </x:c>
       <x:c r="C47" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">User Identity and Password Security</x:t>
+          <x:t xml:space="preserve">Branch Management</x:t>
         </x:is>
       </x:c>
       <x:c r="D47" s="2" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </x:c>
       <x:c r="E47" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should list the users of the current company with paging, keyword and sorting.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to edit or deactivate a branch.</x:t>
         </x:is>
       </x:c>
       <x:c r="F47" s="2" t="inlineStr">
@@ -2036,19 +2036,19 @@
       </x:c>
       <x:c r="G47" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">只列在目前公司有用戶公司關聯的用戶（含停用）；關鍵字不分大小寫比對帳號；排序 username／-username，其他欄位 400；回應不含雜湊、失敗次數及鎖定期限，只回 isLocked、isPasswordExpired（ADR-016）。</x:t>
+          <x:t xml:space="preserve">版本不符回 409；被引用時只可停用，不得刪除。</x:t>
         </x:is>
       </x:c>
       <x:c r="H47" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:58</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:19</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.23.6</x:t>
+          <x:t xml:space="preserve">REQ_F4118.22.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B48" s="2" t="inlineStr">
@@ -2058,7 +2058,7 @@
       </x:c>
       <x:c r="C48" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">User Identity and Password Security</x:t>
+          <x:t xml:space="preserve">Department Management</x:t>
         </x:is>
       </x:c>
       <x:c r="D48" s="2" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </x:c>
       <x:c r="E48" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to create a user in the current company.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to view departments in the selected company.</x:t>
         </x:is>
       </x:c>
       <x:c r="F48" s="2" t="inlineStr">
@@ -2078,19 +2078,19 @@
       </x:c>
       <x:c r="G48" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">需 SYS.USER.CREATE；同一交易建立身分及目前公司的預設關聯（無角色）；重複帳號（不分大小寫、含他公司）409 SYS.USER.DUPLICATE；弱密碼或帳號格式錯誤 400；建立後可登入。</x:t>
+          <x:t xml:space="preserve">公司隔離、軟刪除篩選生效。</x:t>
         </x:is>
       </x:c>
       <x:c r="H48" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:59</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:20</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.23.7</x:t>
+          <x:t xml:space="preserve">REQ_F4118.22.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B49" s="2" t="inlineStr">
@@ -2100,17 +2100,17 @@
       </x:c>
       <x:c r="C49" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">User Identity and Password Security</x:t>
+          <x:t xml:space="preserve">Department Management</x:t>
         </x:is>
       </x:c>
       <x:c r="D49" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1.1</x:t>
+          <x:t xml:space="preserve">1.0</x:t>
         </x:is>
       </x:c>
       <x:c r="E49" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to activate or deactivate a user.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to create a department under a branch or parent department.</x:t>
         </x:is>
       </x:c>
       <x:c r="F49" s="2" t="inlineStr">
@@ -2120,19 +2120,19 @@
       </x:c>
       <x:c r="G49" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">需 SYS.USER.EDIT 並帶 version（過期 409）；停用後不可登入與刷新，重新啟用後可登入；不可停用自己 422 SYS.USER.SELF_DEACTIVATION；他公司用戶 404；用戶亦屬於其他公司時，操作者在每間已啟用關聯的公司都要有 SYS.USER.EDIT（否則 403 COMMON.PERMISSION.DENIED），且用戶角色不超出操作者權限（否則 403 SYS.ROLE.BEYOND_AUTHORITY），ADR-032。</x:t>
+          <x:t xml:space="preserve">分店與上級部門必須屬於同一公司；不得循環參照。</x:t>
         </x:is>
       </x:c>
       <x:c r="H49" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:60</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:21</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.23.8</x:t>
+          <x:t xml:space="preserve">REQ_F4118.22.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B50" s="2" t="inlineStr">
@@ -2142,17 +2142,17 @@
       </x:c>
       <x:c r="C50" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">User Identity and Password Security</x:t>
+          <x:t xml:space="preserve">Department Management</x:t>
         </x:is>
       </x:c>
       <x:c r="D50" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1.1</x:t>
+          <x:t xml:space="preserve">1.0</x:t>
         </x:is>
       </x:c>
       <x:c r="E50" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to reset a password and unlock a locked user.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to edit or deactivate a department.</x:t>
         </x:is>
       </x:c>
       <x:c r="F50" s="2" t="inlineStr">
@@ -2162,19 +2162,19 @@
       </x:c>
       <x:c r="G50" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">重設密碼需 SYS.USER.RESET_PASSWORD，依密碼政策驗證，重新起算到期並清除鎖定，舊密碼即失效；解鎖需 SYS.USER.EDIT，清除失敗計數與鎖定，未鎖定時亦回 204；他公司用戶 404；跨公司與角色上限檢查同 REQ_F4118.23.7（ADR-032）。</x:t>
+          <x:t xml:space="preserve">版本不符回 409；被引用時只可停用。</x:t>
         </x:is>
       </x:c>
       <x:c r="H50" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:61</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:22</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.24.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.23.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B51" s="2" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </x:c>
       <x:c r="C51" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Login, Token and Captcha</x:t>
+          <x:t xml:space="preserve">User Identity and Password Security</x:t>
         </x:is>
       </x:c>
       <x:c r="D51" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </x:c>
       <x:c r="E51" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow a user to log in with username, password and a numeric captcha.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to create a unique user identity.</x:t>
         </x:is>
       </x:c>
       <x:c r="F51" s="2" t="inlineStr">
@@ -2204,19 +2204,19 @@
       </x:c>
       <x:c r="G51" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">帳號不分大小寫；Captcha 4–6 位數字，答案只存伺服器端，驗證一次即作廢（不論對錯）；帳密錯誤、帳號不存在、停用或鎖定一律回 401 SYS.AUTH.INVALID_CREDENTIALS；密碼到期回 403 SYS.AUTH.PASSWORD_EXPIRED 且不發 Token。</x:t>
+          <x:t xml:space="preserve">帳號不分大小寫唯一，停用及軟刪除後仍不可重用；僅保存雜湊，不保存明文密碼。</x:t>
         </x:is>
       </x:c>
       <x:c r="H51" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:73</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:54</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.24.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.23.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B52" s="2" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </x:c>
       <x:c r="C52" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Login, Token and Captcha</x:t>
+          <x:t xml:space="preserve">User Identity and Password Security</x:t>
         </x:is>
       </x:c>
       <x:c r="D52" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </x:c>
       <x:c r="E52" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should issue a 15-minute access token and a 7-day rotating refresh token.</x:t>
+          <x:t xml:space="preserve">System should enforce a configurable password policy.</x:t>
         </x:is>
       </x:c>
       <x:c r="F52" s="2" t="inlineStr">
@@ -2246,19 +2246,19 @@
       </x:c>
       <x:c r="G52" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Access Token 為 HS256 JWT，sub 為用戶 Id；Refresh Token 只以 SHA-256 雜湊存 Redis，使用一次即輪替，並發重放只有一個成功。</x:t>
+          <x:t xml:space="preserve">預設 12–128 字元且含大小寫、數字及符號；長度、複雜度與到期天數可由設定調整，不合法設定拒絕啟動。</x:t>
         </x:is>
       </x:c>
       <x:c r="H52" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:74</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:55</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.24.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.23.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B53" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </x:c>
       <x:c r="C53" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Login, Token and Captcha</x:t>
+          <x:t xml:space="preserve">User Identity and Password Security</x:t>
         </x:is>
       </x:c>
       <x:c r="D53" s="2" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </x:c>
       <x:c r="E53" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow a logged-in user to log out and invalidate the refresh token.</x:t>
+          <x:t xml:space="preserve">System should lock an account after five consecutive failed password attempts.</x:t>
         </x:is>
       </x:c>
       <x:c r="F53" s="2" t="inlineStr">
@@ -2288,19 +2288,19 @@
       </x:c>
       <x:c r="G53" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">登出須帶有效 Access Token；只撤銷屬於本人的 Refresh Token，撤銷後刷新回 401。</x:t>
+          <x:t xml:space="preserve">第 5 次連續失敗鎖定 15 分鐘；鎖定期間正確密碼亦不得通過；鎖定到期後開啟新失敗計數窗口，成功後清除計數。</x:t>
         </x:is>
       </x:c>
       <x:c r="H53" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:75</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:56</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.24.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.23.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B54" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </x:c>
       <x:c r="C54" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Login, Token and Captcha</x:t>
+          <x:t xml:space="preserve">User Identity and Password Security</x:t>
         </x:is>
       </x:c>
       <x:c r="D54" s="2" t="inlineStr">
@@ -2320,7 +2320,7 @@
       </x:c>
       <x:c r="E54" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should provide a development-only captcha master code with startup protection.</x:t>
+          <x:t xml:space="preserve">System should determine whether a user's password has expired.</x:t>
         </x:is>
       </x:c>
       <x:c r="F54" s="2" t="inlineStr">
@@ -2330,19 +2330,19 @@
       </x:c>
       <x:c r="G54" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Captcha:MasterCode 只在 Development 生效且須為 4–6 位數字；其他環境有設定即寫 Error 並拒絕啟動；每次使用寫 Warning（帳號、IP），並寫 sys_audit_log 安全事件 MASTER_CODE_LOGIN（REQ_F4118.27.3）。</x:t>
+          <x:t xml:space="preserve">依設定天數及 password_changed_at 判斷；0 代表不設到期。登入簽發 Token 前必須檢查。</x:t>
         </x:is>
       </x:c>
       <x:c r="H54" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:76</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:57</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="55">
       <x:c r="A55" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.24.5</x:t>
+          <x:t xml:space="preserve">REQ_F4118.23.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B55" s="2" t="inlineStr">
@@ -2352,7 +2352,7 @@
       </x:c>
       <x:c r="C55" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Login, Token and Captcha</x:t>
+          <x:t xml:space="preserve">User Identity and Password Security</x:t>
         </x:is>
       </x:c>
       <x:c r="D55" s="2" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </x:c>
       <x:c r="E55" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should provide a trilingual login page that keeps the session and refreshes tokens automatically.</x:t>
+          <x:t xml:space="preserve">System should list the users of the current company with paging, keyword and sorting.</x:t>
         </x:is>
       </x:c>
       <x:c r="F55" s="2" t="inlineStr">
@@ -2372,19 +2372,19 @@
       </x:c>
       <x:c r="G55" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">未登入進入主框架導向 /login?returnUrl=…，登入後只回到站內路徑；Captcha 元件只收 4–6 位數字，失敗後換新圖並清空密碼；錯誤依 errorCode 三語顯示；API 請求帶 Bearer，401 時只刷新一次並重送，並發 401 共用同一 refresh；刷新失敗清除 Session 回登入頁；登出撤銷 Refresh Token，伺服器失敗也清除本機 Session。</x:t>
+          <x:t xml:space="preserve">只列在目前公司有用戶公司關聯的用戶（含停用）；關鍵字不分大小寫比對帳號；排序 username／-username，其他欄位 400；回應不含雜湊、失敗次數及鎖定期限，只回 isLocked、isPasswordExpired（ADR-016）。</x:t>
         </x:is>
       </x:c>
       <x:c r="H55" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:77</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:58</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="56">
       <x:c r="A56" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.25.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.23.6</x:t>
         </x:is>
       </x:c>
       <x:c r="B56" s="2" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </x:c>
       <x:c r="C56" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Role, Permission and Data Scope</x:t>
+          <x:t xml:space="preserve">User Identity and Password Security</x:t>
         </x:is>
       </x:c>
       <x:c r="D56" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </x:c>
       <x:c r="E56" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to view roles and the permission catalog.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to create a user in the current company.</x:t>
         </x:is>
       </x:c>
       <x:c r="F56" s="2" t="inlineStr">
@@ -2414,19 +2414,19 @@
       </x:c>
       <x:c r="G56" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">需 SYS.ROLE.VIEW；角色列表支援分頁、關鍵字（代碼／名稱）、code／name 排序；權限目錄列出各模組宣告的全部代碼；已軟刪除角色不顯示，查詢回 404。</x:t>
+          <x:t xml:space="preserve">需 SYS.USER.CREATE；同一交易建立身分及目前公司的預設關聯（無角色）；重複帳號（不分大小寫、含他公司）409 SYS.USER.DUPLICATE；弱密碼或帳號格式錯誤 400；建立後可登入。</x:t>
         </x:is>
       </x:c>
       <x:c r="H56" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:89</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:59</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="57">
       <x:c r="A57" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.25.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.23.7</x:t>
         </x:is>
       </x:c>
       <x:c r="B57" s="2" t="inlineStr">
@@ -2436,17 +2436,17 @@
       </x:c>
       <x:c r="C57" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Role, Permission and Data Scope</x:t>
+          <x:t xml:space="preserve">User Identity and Password Security</x:t>
         </x:is>
       </x:c>
       <x:c r="D57" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1.0</x:t>
+          <x:t xml:space="preserve">1.1</x:t>
         </x:is>
       </x:c>
       <x:c r="E57" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to create a role with permissions and a data scope.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to activate or deactivate a user.</x:t>
         </x:is>
       </x:c>
       <x:c r="F57" s="2" t="inlineStr">
@@ -2456,19 +2456,19 @@
       </x:c>
       <x:c r="G57" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">需 SYS.ROLE.CREATE；代碼 1–50 字元 ASCII 英文、數字、-、_，保存為大寫，全系統唯一（含已刪除），重複回 409 SYS.ROLE.DUPLICATE_CODE；權限代碼不分大小寫輸入，必須在權限目錄內，否則 400；資料範圍為 Self／Department／Branch／Company。</x:t>
+          <x:t xml:space="preserve">需 SYS.USER.EDIT 並帶 version（過期 409）；停用後不可登入與刷新，重新啟用後可登入；不可停用自己 422 SYS.USER.SELF_DEACTIVATION；他公司用戶 404；用戶亦屬於其他公司時，操作者在每間已啟用關聯的公司都要有 SYS.USER.EDIT（否則 403 COMMON.PERMISSION.DENIED），且用戶角色不超出操作者權限（否則 403 SYS.ROLE.BEYOND_AUTHORITY），ADR-032。</x:t>
         </x:is>
       </x:c>
       <x:c r="H57" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:90</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:60</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="58">
       <x:c r="A58" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.25.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.23.8</x:t>
         </x:is>
       </x:c>
       <x:c r="B58" s="2" t="inlineStr">
@@ -2478,17 +2478,17 @@
       </x:c>
       <x:c r="C58" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Role, Permission and Data Scope</x:t>
+          <x:t xml:space="preserve">User Identity and Password Security</x:t>
         </x:is>
       </x:c>
       <x:c r="D58" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1.0</x:t>
+          <x:t xml:space="preserve">1.1</x:t>
         </x:is>
       </x:c>
       <x:c r="E58" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to edit or deactivate a role.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to reset a password and unlock a locked user.</x:t>
         </x:is>
       </x:c>
       <x:c r="F58" s="2" t="inlineStr">
@@ -2498,19 +2498,19 @@
       </x:c>
       <x:c r="G58" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">需 SYS.ROLE.EDIT；帶 version，不符回 409，且權限集合不變（同一交易）；停用角色立即不再授予權限。角色是全系統定義：操作者在角色已指派的每間公司都必須全權，否則 403 SYS.AUTHORITY.FULL_ACCESS_REQUIRED（ADR-033）。</x:t>
+          <x:t xml:space="preserve">重設密碼需 SYS.USER.RESET_PASSWORD，依密碼政策驗證，重新起算到期並清除鎖定，舊密碼即失效；解鎖需 SYS.USER.EDIT，清除失敗計數與鎖定，未鎖定時亦回 204；他公司用戶 404；跨公司與角色上限檢查同 REQ_F4118.23.7（ADR-032）。</x:t>
         </x:is>
       </x:c>
       <x:c r="H58" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:91</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:61</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="59">
       <x:c r="A59" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.25.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.24.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B59" s="2" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </x:c>
       <x:c r="C59" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Role, Permission and Data Scope</x:t>
+          <x:t xml:space="preserve">Login, Token and Captcha</x:t>
         </x:is>
       </x:c>
       <x:c r="D59" s="2" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </x:c>
       <x:c r="E59" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to delete an unused role.</x:t>
+          <x:t xml:space="preserve">System should allow a user to log in with username, password and a numeric captcha.</x:t>
         </x:is>
       </x:c>
       <x:c r="F59" s="2" t="inlineStr">
@@ -2540,19 +2540,19 @@
       </x:c>
       <x:c r="G59" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">需 SYS.ROLE.DELETE；仍有用戶使用回 422 SYS.ROLE.IN_USE；軟刪除，代碼不可重用。</x:t>
+          <x:t xml:space="preserve">帳號不分大小寫；Captcha 4–6 位數字，答案只存伺服器端，驗證一次即作廢（不論對錯）；帳密錯誤、帳號不存在、停用或鎖定一律回 401 SYS.AUTH.INVALID_CREDENTIALS；密碼到期回 403 SYS.AUTH.PASSWORD_EXPIRED 且不發 Token。</x:t>
         </x:is>
       </x:c>
       <x:c r="H59" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:92</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:73</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="60">
       <x:c r="A60" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.25.5</x:t>
+          <x:t xml:space="preserve">REQ_F4118.24.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B60" s="2" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </x:c>
       <x:c r="C60" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Role, Permission and Data Scope</x:t>
+          <x:t xml:space="preserve">Login, Token and Captcha</x:t>
         </x:is>
       </x:c>
       <x:c r="D60" s="2" t="inlineStr">
@@ -2572,7 +2572,7 @@
       </x:c>
       <x:c r="E60" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enforce permission codes on every API with the backend as the authority.</x:t>
+          <x:t xml:space="preserve">System should issue a 15-minute access token and a 7-day rotating refresh token.</x:t>
         </x:is>
       </x:c>
       <x:c r="F60" s="2" t="inlineStr">
@@ -2582,19 +2582,19 @@
       </x:c>
       <x:c r="G60" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">每個 API 動作標註 模組.資源.動作 權限（ArchitectureTests 檢查）；未登入 401；缺權限或沒有公司上下文 403 COMMON.PERMISSION.DENIED；已登入請求的 X-Company-Id 不可存取（未授權、用戶公司關聯停用、公司停用）一律 403 COMMON.COMPANY.ACCESS_DENIED。</x:t>
+          <x:t xml:space="preserve">Access Token 為 HS256 JWT，sub 為用戶 Id；Refresh Token 只以 SHA-256 雜湊存 Redis，使用一次即輪替，並發重放只有一個成功。</x:t>
         </x:is>
       </x:c>
       <x:c r="H60" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:93</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:74</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="61">
       <x:c r="A61" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.25.6</x:t>
+          <x:t xml:space="preserve">REQ_F4118.24.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B61" s="2" t="inlineStr">
@@ -2604,17 +2604,17 @@
       </x:c>
       <x:c r="C61" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Role, Permission and Data Scope</x:t>
+          <x:t xml:space="preserve">Login, Token and Captcha</x:t>
         </x:is>
       </x:c>
       <x:c r="D61" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1.1</x:t>
+          <x:t xml:space="preserve">1.0</x:t>
         </x:is>
       </x:c>
       <x:c r="E61" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to grant a user access to a company with roles, organization and default company.</x:t>
+          <x:t xml:space="preserve">System should allow a logged-in user to log out and invalidate the refresh token.</x:t>
         </x:is>
       </x:c>
       <x:c r="F61" s="2" t="inlineStr">
@@ -2624,19 +2624,19 @@
       </x:c>
       <x:c r="G61" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">需 SYS.USER.EDIT；公司必須啟用；分店／部門必須屬於該公司且啟用；角色必須存在且啟用；角色整組取代；每位用戶最多一間預設公司（設定新預設會取消舊預設）。用戶不存在或不屬於目前公司回 404 SYS.USER.NOT_FOUND；目標公司不是操作者獲授權的公司回 404 SYS.COMPANY.NOT_FOUND；不可停用自己的公司授權（422 SYS.USER.SELF_DEACTIVATION）（ADR-017）。操作者在目標公司亦須有 SYS.USER.EDIT（否則 403 COMMON.PERMISSION.DENIED）；新增或移除的角色須在操作者權限之內（全權角色只限全權操作者；一般角色的每個權限操作者都有且範圍不窄於角色），否則 403 SYS.ROLE.BEYOND_AUTHORITY；不可變更自己的角色（422 SYS.USER.SELF_ROLE_CHANGE），角色不變時可改組織與預設公司（ADR-032）。</x:t>
+          <x:t xml:space="preserve">登出須帶有效 Access Token；只撤銷屬於本人的 Refresh Token，撤銷後刷新回 401。</x:t>
         </x:is>
       </x:c>
       <x:c r="H61" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:94</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:75</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="62">
       <x:c r="A62" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.25.7</x:t>
+          <x:t xml:space="preserve">REQ_F4118.24.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B62" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </x:c>
       <x:c r="C62" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Role, Permission and Data Scope</x:t>
+          <x:t xml:space="preserve">Login, Token and Captcha</x:t>
         </x:is>
       </x:c>
       <x:c r="D62" s="2" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </x:c>
       <x:c r="E62" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should resolve the user's effective permissions and data scope per company and hide unauthorized UI.</x:t>
+          <x:t xml:space="preserve">System should provide a development-only captcha master code with startup protection.</x:t>
         </x:is>
       </x:c>
       <x:c r="F62" s="2" t="inlineStr">
@@ -2666,19 +2666,19 @@
       </x:c>
       <x:c r="G62" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">同一權限取各啟用角色最寬的資料範圍；全權角色視為全部權限、全公司範圍；分店／部門範圍但用戶無對應歸屬時退回本人。GET /api/v1/sys/auth/authorization 回傳可存取公司（預設在前）與目前公司權限；前端 *erpHasPermission、permissionGuard 與選單依此隱藏，切換公司重新載入；本機記住的公司不可存取時改用預設公司。</x:t>
+          <x:t xml:space="preserve">Captcha:MasterCode 只在 Development 生效且須為 4–6 位數字；其他環境有設定即寫 Error 並拒絕啟動；每次使用寫 Warning（帳號、IP），並寫 sys_audit_log 安全事件 MASTER_CODE_LOGIN（REQ_F4118.27.3）。</x:t>
         </x:is>
       </x:c>
       <x:c r="H62" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:95</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:76</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="63">
       <x:c r="A63" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.25.8</x:t>
+          <x:t xml:space="preserve">REQ_F4118.24.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B63" s="2" t="inlineStr">
@@ -2688,7 +2688,7 @@
       </x:c>
       <x:c r="C63" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Role, Permission and Data Scope</x:t>
+          <x:t xml:space="preserve">Login, Token and Captcha</x:t>
         </x:is>
       </x:c>
       <x:c r="D63" s="2" t="inlineStr">
@@ -2698,7 +2698,7 @@
       </x:c>
       <x:c r="E63" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to view a user's company access, organization and roles.</x:t>
+          <x:t xml:space="preserve">System should provide a trilingual login page that keeps the session and refreshes tokens automatically.</x:t>
         </x:is>
       </x:c>
       <x:c r="F63" s="2" t="inlineStr">
@@ -2708,19 +2708,19 @@
       </x:c>
       <x:c r="G63" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">需 SYS.USER.VIEW；用戶須屬於目前公司，否則 404；只列出操作者獲授權公司的指派（公司代碼／名稱、分店、部門、預設、啟用、角色 ID），依公司代碼排序（ADR-017）。</x:t>
+          <x:t xml:space="preserve">未登入進入主框架導向 /login?returnUrl=…，登入後只回到站內路徑；Captcha 元件只收 4–6 位數字，失敗後換新圖並清空密碼；錯誤依 errorCode 三語顯示；API 請求帶 Bearer，401 時只刷新一次並重送，並發 401 共用同一 refresh；刷新失敗清除 Session 回登入頁；登出撤銷 Refresh Token，伺服器失敗也清除本機 Session。</x:t>
         </x:is>
       </x:c>
       <x:c r="H63" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:96</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:77</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="64">
       <x:c r="A64" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.26.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.25.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B64" s="2" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </x:c>
       <x:c r="C64" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Web Security Middleware</x:t>
+          <x:t xml:space="preserve">Role, Permission and Data Scope</x:t>
         </x:is>
       </x:c>
       <x:c r="D64" s="2" t="inlineStr">
@@ -2740,7 +2740,7 @@
       </x:c>
       <x:c r="E64" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enforce HTTPS with HSTS outside the development environment.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to view roles and the permission catalog.</x:t>
         </x:is>
       </x:c>
       <x:c r="F64" s="2" t="inlineStr">
@@ -2750,19 +2750,19 @@
       </x:c>
       <x:c r="G64" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">非 Development：HTTP 請求 307 轉 HTTPS；HTTPS 回應帶 Strict-Transport-Security: max-age=31536000; includeSubDomains（天數可設定）。Development 不轉址、不送 HSTS。</x:t>
+          <x:t xml:space="preserve">需 SYS.ROLE.VIEW；角色列表支援分頁、關鍵字（代碼／名稱）、code／name 排序；權限目錄列出各模組宣告的全部代碼；已軟刪除角色不顯示，查詢回 404。</x:t>
         </x:is>
       </x:c>
       <x:c r="H64" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:110</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:89</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="65">
       <x:c r="A65" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.26.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.25.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B65" s="2" t="inlineStr">
@@ -2772,7 +2772,7 @@
       </x:c>
       <x:c r="C65" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Web Security Middleware</x:t>
+          <x:t xml:space="preserve">Role, Permission and Data Scope</x:t>
         </x:is>
       </x:c>
       <x:c r="D65" s="2" t="inlineStr">
@@ -2782,7 +2782,7 @@
       </x:c>
       <x:c r="E65" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow cross-origin requests only from configured frontend origins.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to create a role with permissions and a data scope.</x:t>
         </x:is>
       </x:c>
       <x:c r="F65" s="2" t="inlineStr">
@@ -2792,19 +2792,19 @@
       </x:c>
       <x:c r="G65" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">來源清單在 Security:Cors:AllowedOrigins，預設空（不允許跨來源）；只接受 scheme://host[:port]，萬用字元、含路徑或非 http(s) 拒絕啟動；不允許 Credentials；允許標頭 Authorization、Content-Type、Accept、Accept-Language、X-Company-Id；公開 Retry-After、Content-Disposition；未列明的來源預檢回應不含 Access-Control-Allow-Origin。</x:t>
+          <x:t xml:space="preserve">需 SYS.ROLE.CREATE；代碼 1–50 字元 ASCII 英文、數字、-、_，保存為大寫，全系統唯一（含已刪除），重複回 409 SYS.ROLE.DUPLICATE_CODE；權限代碼不分大小寫輸入，必須在權限目錄內，否則 400；資料範圍為 Self／Department／Branch／Company。</x:t>
         </x:is>
       </x:c>
       <x:c r="H65" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:111</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:90</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="66">
       <x:c r="A66" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.26.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.25.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B66" s="2" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </x:c>
       <x:c r="C66" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Web Security Middleware</x:t>
+          <x:t xml:space="preserve">Role, Permission and Data Scope</x:t>
         </x:is>
       </x:c>
       <x:c r="D66" s="2" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </x:c>
       <x:c r="E66" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should rate-limit login, token refresh and captcha requests per client IP.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to edit or deactivate a role.</x:t>
         </x:is>
       </x:c>
       <x:c r="F66" s="2" t="inlineStr">
@@ -2834,19 +2834,19 @@
       </x:c>
       <x:c r="G66" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">登入、Token 刷新每 IP 每端點每分鐘 5 次；Captcha 每 IP 每分鐘 10 次（ADR-018）；超過回 429 ProblemDetails，errorCode 為 COMMON.REQUEST.RATE_LIMITED，標題依 Accept-Language 三語，帶 Retry-After；寫 Warning 日誌（方法、路徑、IP）。CORS 預檢不計入。每個匿名端點必須套用按 IP 的限流政策（ArchitectureTests 檢查）。</x:t>
+          <x:t xml:space="preserve">需 SYS.ROLE.EDIT；帶 version，不符回 409，且權限集合不變（同一交易）；停用角色立即不再授予權限。角色是全系統定義：操作者在角色已指派的每間公司都必須全權，否則 403 SYS.AUTHORITY.FULL_ACCESS_REQUIRED（ADR-033）。</x:t>
         </x:is>
       </x:c>
       <x:c r="H66" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:112</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:91</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.26.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.25.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B67" s="2" t="inlineStr">
@@ -2856,7 +2856,7 @@
       </x:c>
       <x:c r="C67" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Web Security Middleware</x:t>
+          <x:t xml:space="preserve">Role, Permission and Data Scope</x:t>
         </x:is>
       </x:c>
       <x:c r="D67" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </x:c>
       <x:c r="E67" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should rate-limit authenticated API requests per user.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to delete an unused role.</x:t>
         </x:is>
       </x:c>
       <x:c r="F67" s="2" t="inlineStr">
@@ -2876,19 +2876,19 @@
       </x:c>
       <x:c r="G67" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">已登入請求每用戶每分鐘 300 次（可設定），不同用戶分開計數；匯出報表政策每用戶每分鐘 10 次，供日後匯出端點套用。白名單內的 IP 仍受限流。</x:t>
+          <x:t xml:space="preserve">需 SYS.ROLE.DELETE；仍有用戶使用回 422 SYS.ROLE.IN_USE；軟刪除，代碼不可重用。</x:t>
         </x:is>
       </x:c>
       <x:c r="H67" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:113</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:92</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.26.5</x:t>
+          <x:t xml:space="preserve">REQ_F4118.25.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B68" s="2" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </x:c>
       <x:c r="C68" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Web Security Middleware</x:t>
+          <x:t xml:space="preserve">Role, Permission and Data Scope</x:t>
         </x:is>
       </x:c>
       <x:c r="D68" s="2" t="inlineStr">
@@ -2908,7 +2908,7 @@
       </x:c>
       <x:c r="E68" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should add security headers to every API response.</x:t>
+          <x:t xml:space="preserve">System should enforce permission codes on every API with the backend as the authority.</x:t>
         </x:is>
       </x:c>
       <x:c r="F68" s="2" t="inlineStr">
@@ -2918,19 +2918,19 @@
       </x:c>
       <x:c r="G68" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">所有回應（含 404、429、500）帶 X-Content-Type-Options: nosniff、X-Frame-Options: DENY、Referrer-Policy: no-referrer、Content-Security-Policy: default-src 'none'; frame-ancestors 'none'; base-uri 'none'; form-action 'none'。前端站台的 CSP 見 architecture/security.md，E2E 在該 CSP 下執行。</x:t>
+          <x:t xml:space="preserve">每個 API 動作標註 模組.資源.動作 權限（ArchitectureTests 檢查）；未登入 401；缺權限或沒有公司上下文 403 COMMON.PERMISSION.DENIED；已登入請求的 X-Company-Id 不可存取（未授權、用戶公司關聯停用、公司停用）一律 403 COMMON.COMPANY.ACCESS_DENIED。</x:t>
         </x:is>
       </x:c>
       <x:c r="H68" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:114</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:93</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="69">
       <x:c r="A69" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.26.6</x:t>
+          <x:t xml:space="preserve">REQ_F4118.25.6</x:t>
         </x:is>
       </x:c>
       <x:c r="B69" s="2" t="inlineStr">
@@ -2940,17 +2940,17 @@
       </x:c>
       <x:c r="C69" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Web Security Middleware</x:t>
+          <x:t xml:space="preserve">Role, Permission and Data Scope</x:t>
         </x:is>
       </x:c>
       <x:c r="D69" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1.0</x:t>
+          <x:t xml:space="preserve">1.1</x:t>
         </x:is>
       </x:c>
       <x:c r="E69" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should honour X-Forwarded-For only from configured proxies.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to grant a user access to a company with roles, organization and default company.</x:t>
         </x:is>
       </x:c>
       <x:c r="F69" s="2" t="inlineStr">
@@ -2960,19 +2960,19 @@
       </x:c>
       <x:c r="G69" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Security:ForwardedHeaders:KnownProxies（IP）與 KnownNetworks（CIDR）皆空時不處理 X-Forwarded-*；有設定時只信任列明來源，其他來源偽造的 X-Forwarded-For 被忽略，限流與日誌使用連線 IP；格式錯誤拒絕啟動。</x:t>
+          <x:t xml:space="preserve">需 SYS.USER.EDIT；公司必須啟用；分店／部門必須屬於該公司且啟用；角色必須存在且啟用；角色整組取代；每位用戶最多一間預設公司（設定新預設會取消舊預設）。用戶不存在或不屬於目前公司回 404 SYS.USER.NOT_FOUND；目標公司不是操作者獲授權的公司回 404 SYS.COMPANY.NOT_FOUND；不可停用自己的公司授權（422 SYS.USER.SELF_DEACTIVATION）（ADR-017）。操作者在目標公司亦須有 SYS.USER.EDIT（否則 403 COMMON.PERMISSION.DENIED）；新增或移除的角色須在操作者權限之內（全權角色只限全權操作者；一般角色的每個權限操作者都有且範圍不窄於角色），否則 403 SYS.ROLE.BEYOND_AUTHORITY；不可變更自己的角色（422 SYS.USER.SELF_ROLE_CHANGE），角色不變時可改組織與預設公司（ADR-032）。</x:t>
         </x:is>
       </x:c>
       <x:c r="H69" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:115</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:94</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="70">
       <x:c r="A70" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.26.7</x:t>
+          <x:t xml:space="preserve">REQ_F4118.25.7</x:t>
         </x:is>
       </x:c>
       <x:c r="B70" s="2" t="inlineStr">
@@ -2982,7 +2982,7 @@
       </x:c>
       <x:c r="C70" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Web Security Middleware</x:t>
+          <x:t xml:space="preserve">Role, Permission and Data Scope</x:t>
         </x:is>
       </x:c>
       <x:c r="D70" s="2" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </x:c>
       <x:c r="E70" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should show a trilingual "too many requests" message when an API call is rate-limited.</x:t>
+          <x:t xml:space="preserve">System should resolve the user's effective permissions and data scope per company and hide unauthorized UI.</x:t>
         </x:is>
       </x:c>
       <x:c r="F70" s="2" t="inlineStr">
@@ -3002,19 +3002,19 @@
       </x:c>
       <x:c r="G70" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">前端收到 429 一律顯示 errors.COMMON.REQUEST.RATE_LIMITED（三語），登入頁、組織、用戶、角色頁共用 apiErrorKey。</x:t>
+          <x:t xml:space="preserve">同一權限取各啟用角色最寬的資料範圍；全權角色視為全部權限、全公司範圍；分店／部門範圍但用戶無對應歸屬時退回本人。GET /api/v1/sys/auth/authorization 回傳可存取公司（預設在前）與目前公司權限；前端 *erpHasPermission、permissionGuard 與選單依此隱藏，切換公司重新載入；本機記住的公司不可存取時改用預設公司。</x:t>
         </x:is>
       </x:c>
       <x:c r="H70" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:116</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:95</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="71">
       <x:c r="A71" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.27.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.25.8</x:t>
         </x:is>
       </x:c>
       <x:c r="B71" s="2" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </x:c>
       <x:c r="C71" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Audit Log</x:t>
+          <x:t xml:space="preserve">Role, Permission and Data Scope</x:t>
         </x:is>
       </x:c>
       <x:c r="D71" s="2" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </x:c>
       <x:c r="E71" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should record every data change in sys_audit_log within the same transaction.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to view a user's company access, organization and roles.</x:t>
         </x:is>
       </x:c>
       <x:c r="F71" s="2" t="inlineStr">
@@ -3044,19 +3044,19 @@
       </x:c>
       <x:c r="G71" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">透過 EF 新增、修改、刪除（含軟刪除）都寫一筆記錄，內容包括公司、用戶（背景程序為系統用戶）、時間（IClock）、表名、記錄 Id、操作類型（CREATE／UPDATE／DELETE，可由 Application 指定 VOID／APPROVE／POST）、欄位差異 JSON（修改只列有變更的欄位）、來源 IP、TraceId。沒有欄位變更不寫記錄。交易回滾或 SaveChanges 失敗（含樂觀鎖衝突）不留記錄，重試時也不會重複（ADR-019）。</x:t>
+          <x:t xml:space="preserve">需 SYS.USER.VIEW；用戶須屬於目前公司，否則 404；只列出操作者獲授權公司的指派（公司代碼／名稱、分店、部門、預設、啟用、角色 ID），依公司代碼排序（ADR-017）。</x:t>
         </x:is>
       </x:c>
       <x:c r="H71" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:128</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:96</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="72">
       <x:c r="A72" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.27.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.26.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B72" s="2" t="inlineStr">
@@ -3066,7 +3066,7 @@
       </x:c>
       <x:c r="C72" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Audit Log</x:t>
+          <x:t xml:space="preserve">Web Security Middleware</x:t>
         </x:is>
       </x:c>
       <x:c r="D72" s="2" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </x:c>
       <x:c r="E72" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should protect audit records and sensitive values.</x:t>
+          <x:t xml:space="preserve">System should enforce HTTPS with HSTS outside the development environment.</x:t>
         </x:is>
       </x:c>
       <x:c r="F72" s="2" t="inlineStr">
@@ -3086,19 +3086,19 @@
       </x:c>
       <x:c r="G72" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">[SensitiveData] 欄位（例如 password_hash）的值以 * 遮蔽；主鍵、審計欄位、version、company_id 不記錄差異。sys_audit_log 只能新增，UPDATE 或 DELETE 由 trigger 拒絕（append-only）；changes 必須是 JSON。</x:t>
+          <x:t xml:space="preserve">非 Development：HTTP 請求 307 轉 HTTPS；HTTPS 回應帶 Strict-Transport-Security: max-age=31536000; includeSubDomains（天數可設定）。Development 不轉址、不送 HSTS。</x:t>
         </x:is>
       </x:c>
       <x:c r="H72" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:129</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:110</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="73">
       <x:c r="A73" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.27.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.26.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B73" s="2" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </x:c>
       <x:c r="C73" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Audit Log</x:t>
+          <x:t xml:space="preserve">Web Security Middleware</x:t>
         </x:is>
       </x:c>
       <x:c r="D73" s="2" t="inlineStr">
@@ -3118,7 +3118,7 @@
       </x:c>
       <x:c r="E73" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should record login, failed login, logout and captcha master-code login as security events.</x:t>
+          <x:t xml:space="preserve">System should allow cross-origin requests only from configured frontend origins.</x:t>
         </x:is>
       </x:c>
       <x:c r="F73" s="2" t="inlineStr">
@@ -3128,19 +3128,19 @@
       </x:c>
       <x:c r="G73" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">安全事件記錄帳號、IP、時間與 TraceId。LOGIN_FAILED 的原因只寫 INVALID_CREDENTIALS 或 PASSWORD_EXPIRED，不寫密碼。萬用碼登入不論結果都寫 MASTER_CODE_LOGIN（REQ_F4118.24.4）。</x:t>
+          <x:t xml:space="preserve">來源清單在 Security:Cors:AllowedOrigins，預設空（不允許跨來源）；只接受 scheme://host[:port]，萬用字元、含路徑或非 http(s) 拒絕啟動；不允許 Credentials；允許標頭 Authorization、Content-Type、Accept、Accept-Language、X-Company-Id；公開 Retry-After、Content-Disposition；未列明的來源預檢回應不含 Access-Control-Allow-Origin。</x:t>
         </x:is>
       </x:c>
       <x:c r="H73" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:130</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:111</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="74">
       <x:c r="A74" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.27.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.26.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B74" s="2" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </x:c>
       <x:c r="C74" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Audit Log</x:t>
+          <x:t xml:space="preserve">Web Security Middleware</x:t>
         </x:is>
       </x:c>
       <x:c r="D74" s="2" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </x:c>
       <x:c r="E74" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to query audit logs of the current company.</x:t>
+          <x:t xml:space="preserve">System should rate-limit login, token refresh and captcha requests per client IP.</x:t>
         </x:is>
       </x:c>
       <x:c r="F74" s="2" t="inlineStr">
@@ -3170,19 +3170,19 @@
       </x:c>
       <x:c r="G74" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GET /api/v1/sys/audit-logs 需 SYS.AUDIT.VIEW，支援分頁、日期範圍（含頭尾）、類別、操作類型、表名＋記錄 Id（單據修改歷史）、用戶篩選，以時間排序。只列出目前公司的記錄，以及屬於目前公司用戶、沒有公司的安全事件；其他公司的記錄看不到。資料變更記錄會補上帳號。to 早於 from、類別未知或長度超限時回 400。</x:t>
+          <x:t xml:space="preserve">登入、Token 刷新每 IP 每端點每分鐘 5 次；Captcha 每 IP 每分鐘 10 次（ADR-018）；超過回 429 ProblemDetails，errorCode 為 COMMON.REQUEST.RATE_LIMITED，標題依 Accept-Language 三語，帶 Retry-After；寫 Warning 日誌（方法、路徑、IP）。CORS 預檢不計入。每個匿名端點必須套用按 IP 的限流政策（ArchitectureTests 檢查）。</x:t>
         </x:is>
       </x:c>
       <x:c r="H74" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:131</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:112</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="75">
       <x:c r="A75" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.27.5</x:t>
+          <x:t xml:space="preserve">REQ_F4118.26.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B75" s="2" t="inlineStr">
@@ -3192,7 +3192,7 @@
       </x:c>
       <x:c r="C75" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Audit Log</x:t>
+          <x:t xml:space="preserve">Web Security Middleware</x:t>
         </x:is>
       </x:c>
       <x:c r="D75" s="2" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </x:c>
       <x:c r="E75" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should record role permission and user company access changes as security events.</x:t>
+          <x:t xml:space="preserve">System should rate-limit authenticated API requests per user.</x:t>
         </x:is>
       </x:c>
       <x:c r="F75" s="2" t="inlineStr">
@@ -3212,19 +3212,19 @@
       </x:c>
       <x:c r="G75" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">修改角色的權限、資料範圍、全權或啟用狀態，以及指派用戶公司授權，都寫 PERMISSION_CHANGE，與變更同一交易。記錄內容包括操作者、公司、新增與移除的權限，或指派後的角色、組織、預設公司與啟用狀態。</x:t>
+          <x:t xml:space="preserve">已登入請求每用戶每分鐘 300 次（可設定），不同用戶分開計數；匯出報表政策每用戶每分鐘 10 次，供日後匯出端點套用。白名單內的 IP 仍受限流。</x:t>
         </x:is>
       </x:c>
       <x:c r="H75" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:132</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:113</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="76">
       <x:c r="A76" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.27.6</x:t>
+          <x:t xml:space="preserve">REQ_F4118.26.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B76" s="2" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </x:c>
       <x:c r="C76" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Audit Log</x:t>
+          <x:t xml:space="preserve">Web Security Middleware</x:t>
         </x:is>
       </x:c>
       <x:c r="D76" s="2" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </x:c>
       <x:c r="E76" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should provide a trilingual audit log page with per-record change history.</x:t>
+          <x:t xml:space="preserve">System should add security headers to every API response.</x:t>
         </x:is>
       </x:c>
       <x:c r="F76" s="2" t="inlineStr">
@@ -3254,19 +3254,19 @@
       </x:c>
       <x:c r="G76" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">三語稽核查詢頁 /sys/audit-logs（介面 8.66），需 SYS.AUDIT.VIEW，無權限時選單不顯示、直接進入顯示 403。可依日期範圍（含快選今天、近 7、30 天；結束日早於開始日時不送出）、類別、操作、資料表＋記錄 ID 篩選，伺服器端分頁並依時間排序。可展開欄位差異（修改前→修改後，* 照原樣顯示）或安全事件明細。?tableName=&amp;recordId= 開啟單筆記錄的修改歷史，供單據頁的稽核頁籤連結。操作與類別有三語標籤，未知操作顯示原代碼。切換公司後重新查詢。</x:t>
+          <x:t xml:space="preserve">所有回應（含 404、429、500）帶 X-Content-Type-Options: nosniff、X-Frame-Options: DENY、Referrer-Policy: no-referrer、Content-Security-Policy: default-src 'none'; frame-ancestors 'none'; base-uri 'none'; form-action 'none'。前端站台的 CSP 見 architecture/security.md，E2E 在該 CSP 下執行。</x:t>
         </x:is>
       </x:c>
       <x:c r="H76" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:133</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:114</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="77">
       <x:c r="A77" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.28.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.26.6</x:t>
         </x:is>
       </x:c>
       <x:c r="B77" s="2" t="inlineStr">
@@ -3276,7 +3276,7 @@
       </x:c>
       <x:c r="C77" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Document Number Rule</x:t>
+          <x:t xml:space="preserve">Web Security Middleware</x:t>
         </x:is>
       </x:c>
       <x:c r="D77" s="2" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </x:c>
       <x:c r="E77" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow user to view document number rules of the current company.</x:t>
+          <x:t xml:space="preserve">System should honour X-Forwarded-For only from configured proxies.</x:t>
         </x:is>
       </x:c>
       <x:c r="F77" s="2" t="inlineStr">
@@ -3296,19 +3296,19 @@
       </x:c>
       <x:c r="G77" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">Security:ForwardedHeaders:KnownProxies（IP）與 KnownNetworks（CIDR）皆空時不處理 X-Forwarded-*；有設定時只信任列明來源，其他來源偽造的 X-Forwarded-For 被忽略，限流與日誌使用連線 IP；格式錯誤拒絕啟動。</x:t>
         </x:is>
       </x:c>
       <x:c r="H77" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:167</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:115</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="78">
       <x:c r="A78" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.28.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.26.7</x:t>
         </x:is>
       </x:c>
       <x:c r="B78" s="2" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </x:c>
       <x:c r="C78" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Document Number Rule</x:t>
+          <x:t xml:space="preserve">Web Security Middleware</x:t>
         </x:is>
       </x:c>
       <x:c r="D78" s="2" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </x:c>
       <x:c r="E78" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow user to create a document number rule with prefix, date format, sequence length and reset period.</x:t>
+          <x:t xml:space="preserve">System should show a trilingual "too many requests" message when an API call is rate-limited.</x:t>
         </x:is>
       </x:c>
       <x:c r="F78" s="2" t="inlineStr">
@@ -3338,19 +3338,19 @@
       </x:c>
       <x:c r="G78" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">前端收到 429 一律顯示 errors.COMMON.REQUEST.RATE_LIMITED（三語），登入頁、組織、用戶、角色頁共用 apiErrorKey。</x:t>
         </x:is>
       </x:c>
       <x:c r="H78" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:168</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:116</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="79">
       <x:c r="A79" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.28.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.27.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B79" s="2" t="inlineStr">
@@ -3360,7 +3360,7 @@
       </x:c>
       <x:c r="C79" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Document Number Rule</x:t>
+          <x:t xml:space="preserve">Audit Log</x:t>
         </x:is>
       </x:c>
       <x:c r="D79" s="2" t="inlineStr">
@@ -3370,7 +3370,7 @@
       </x:c>
       <x:c r="E79" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow user to edit or deactivate a document number rule without breaking issued numbers.</x:t>
+          <x:t xml:space="preserve">System should record every data change in sys_audit_log within the same transaction.</x:t>
         </x:is>
       </x:c>
       <x:c r="F79" s="2" t="inlineStr">
@@ -3380,19 +3380,19 @@
       </x:c>
       <x:c r="G79" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">透過 EF 新增、修改、刪除（含軟刪除）都寫一筆記錄，內容包括公司、用戶（背景程序為系統用戶）、時間（IClock）、表名、記錄 Id、操作類型（CREATE／UPDATE／DELETE，可由 Application 指定 VOID／APPROVE／POST）、欄位差異 JSON（修改只列有變更的欄位）、來源 IP、TraceId。沒有欄位變更不寫記錄。交易回滾或 SaveChanges 失敗（含樂觀鎖衝突）不留記錄，重試時也不會重複（ADR-019）。</x:t>
         </x:is>
       </x:c>
       <x:c r="H79" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:169</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:128</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="80">
       <x:c r="A80" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.28.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.27.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B80" s="2" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </x:c>
       <x:c r="C80" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Document Number Rule</x:t>
+          <x:t xml:space="preserve">Audit Log</x:t>
         </x:is>
       </x:c>
       <x:c r="D80" s="2" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </x:c>
       <x:c r="E80" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow user to preview the next document number for a business date.</x:t>
+          <x:t xml:space="preserve">System should protect audit records and sensitive values.</x:t>
         </x:is>
       </x:c>
       <x:c r="F80" s="2" t="inlineStr">
@@ -3422,19 +3422,19 @@
       </x:c>
       <x:c r="G80" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">[SensitiveData] 欄位（例如 password_hash）的值以 * 遮蔽；主鍵、審計欄位、version、company_id 不記錄差異。sys_audit_log 只能新增，UPDATE 或 DELETE 由 trigger 拒絕（append-only）；changes 必須是 JSON。</x:t>
         </x:is>
       </x:c>
       <x:c r="H80" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:170</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:129</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="81">
       <x:c r="A81" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.28.5</x:t>
+          <x:t xml:space="preserve">REQ_F4118.27.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B81" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </x:c>
       <x:c r="C81" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Document Number Rule</x:t>
+          <x:t xml:space="preserve">Audit Log</x:t>
         </x:is>
       </x:c>
       <x:c r="D81" s="2" t="inlineStr">
@@ -3454,7 +3454,7 @@
       </x:c>
       <x:c r="E81" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should generate unique, gap-free document numbers for every module under concurrency.</x:t>
+          <x:t xml:space="preserve">System should record login, failed login, logout and captcha master-code login as security events.</x:t>
         </x:is>
       </x:c>
       <x:c r="F81" s="2" t="inlineStr">
@@ -3464,19 +3464,19 @@
       </x:c>
       <x:c r="G81" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">安全事件記錄帳號、IP、時間與 TraceId。LOGIN_FAILED 的原因只寫 INVALID_CREDENTIALS 或 PASSWORD_EXPIRED，不寫密碼。萬用碼登入不論結果都寫 MASTER_CODE_LOGIN（REQ_F4118.24.4）。</x:t>
         </x:is>
       </x:c>
       <x:c r="H81" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:171</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:130</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="82">
       <x:c r="A82" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.28.6</x:t>
+          <x:t xml:space="preserve">REQ_F4118.27.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B82" s="2" t="inlineStr">
@@ -3486,7 +3486,7 @@
       </x:c>
       <x:c r="C82" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Document Number Rule</x:t>
+          <x:t xml:space="preserve">Audit Log</x:t>
         </x:is>
       </x:c>
       <x:c r="D82" s="2" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </x:c>
       <x:c r="E82" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should provide a trilingual number rule maintenance page.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to query audit logs of the current company.</x:t>
         </x:is>
       </x:c>
       <x:c r="F82" s="2" t="inlineStr">
@@ -3506,19 +3506,19 @@
       </x:c>
       <x:c r="G82" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">GET /api/v1/sys/audit-logs 需 SYS.AUDIT.VIEW，支援分頁、日期範圍（含頭尾）、類別、操作類型、表名＋記錄 Id（單據修改歷史）、用戶篩選，以時間排序。只列出目前公司的記錄，以及屬於目前公司用戶、沒有公司的安全事件；其他公司的記錄看不到。資料變更記錄會補上帳號。to 早於 from、類別未知或長度超限時回 400。</x:t>
         </x:is>
       </x:c>
       <x:c r="H82" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:172</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:131</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="83">
       <x:c r="A83" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.29.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.27.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B83" s="2" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </x:c>
       <x:c r="C83" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Approval Workflow</x:t>
+          <x:t xml:space="preserve">Audit Log</x:t>
         </x:is>
       </x:c>
       <x:c r="D83" s="2" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </x:c>
       <x:c r="E83" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow user to view and create multi-level approval flows with amount thresholds.</x:t>
+          <x:t xml:space="preserve">System should record role permission and user company access changes as security events.</x:t>
         </x:is>
       </x:c>
       <x:c r="F83" s="2" t="inlineStr">
@@ -3548,19 +3548,19 @@
       </x:c>
       <x:c r="G83" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">修改角色的權限、資料範圍、全權或啟用狀態，以及指派用戶公司授權，都寫 PERMISSION_CHANGE，與變更同一交易。記錄內容包括操作者、公司、新增與移除的權限，或指派後的角色、組織、預設公司與啟用狀態。</x:t>
         </x:is>
       </x:c>
       <x:c r="H83" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:146</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:132</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="84">
       <x:c r="A84" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.29.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.27.6</x:t>
         </x:is>
       </x:c>
       <x:c r="B84" s="2" t="inlineStr">
@@ -3570,7 +3570,7 @@
       </x:c>
       <x:c r="C84" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Approval Workflow</x:t>
+          <x:t xml:space="preserve">Audit Log</x:t>
         </x:is>
       </x:c>
       <x:c r="D84" s="2" t="inlineStr">
@@ -3580,7 +3580,7 @@
       </x:c>
       <x:c r="E84" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow user to edit or deactivate an approval flow without affecting pending approvals.</x:t>
+          <x:t xml:space="preserve">System should provide a trilingual audit log page with per-record change history.</x:t>
         </x:is>
       </x:c>
       <x:c r="F84" s="2" t="inlineStr">
@@ -3590,19 +3590,19 @@
       </x:c>
       <x:c r="G84" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">三語稽核查詢頁 /sys/audit-logs（介面 8.66），需 SYS.AUDIT.VIEW，無權限時選單不顯示、直接進入顯示 403。可依日期範圍（含快選今天、近 7、30 天；結束日早於開始日時不送出）、類別、操作、資料表＋記錄 ID 篩選，伺服器端分頁並依時間排序。可展開欄位差異（修改前→修改後，* 照原樣顯示）或安全事件明細。?tableName=&amp;recordId= 開啟單筆記錄的修改歷史，供單據頁的稽核頁籤連結。操作與類別有三語標籤，未知操作顯示原代碼。切換公司後重新查詢。</x:t>
         </x:is>
       </x:c>
       <x:c r="H84" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:147</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:133</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="85">
       <x:c r="A85" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.29.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.28.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B85" s="2" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </x:c>
       <x:c r="C85" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Approval Workflow</x:t>
+          <x:t xml:space="preserve">Document Number Rule</x:t>
         </x:is>
       </x:c>
       <x:c r="D85" s="2" t="inlineStr">
@@ -3622,7 +3622,7 @@
       </x:c>
       <x:c r="E85" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow user to assign an approval delegate for a date range.</x:t>
+          <x:t xml:space="preserve">System should allow user to view document number rules of the current company.</x:t>
         </x:is>
       </x:c>
       <x:c r="F85" s="2" t="inlineStr">
@@ -3637,14 +3637,14 @@
       </x:c>
       <x:c r="H85" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:148</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:167</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="86">
       <x:c r="A86" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.29.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.28.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B86" s="2" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </x:c>
       <x:c r="C86" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Approval Workflow</x:t>
+          <x:t xml:space="preserve">Document Number Rule</x:t>
         </x:is>
       </x:c>
       <x:c r="D86" s="2" t="inlineStr">
@@ -3664,7 +3664,7 @@
       </x:c>
       <x:c r="E86" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable every module to submit documents for approval through the shared workflow engine.</x:t>
+          <x:t xml:space="preserve">System should allow user to create a document number rule with prefix, date format, sequence length and reset period.</x:t>
         </x:is>
       </x:c>
       <x:c r="F86" s="2" t="inlineStr">
@@ -3679,14 +3679,14 @@
       </x:c>
       <x:c r="H86" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:149</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:168</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="87">
       <x:c r="A87" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.29.5</x:t>
+          <x:t xml:space="preserve">REQ_F4118.28.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B87" s="2" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </x:c>
       <x:c r="C87" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Approval Workflow</x:t>
+          <x:t xml:space="preserve">Document Number Rule</x:t>
         </x:is>
       </x:c>
       <x:c r="D87" s="2" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </x:c>
       <x:c r="E87" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow approvers or their delegates to approve or reject the current approval step.</x:t>
+          <x:t xml:space="preserve">System should allow user to edit or deactivate a document number rule without breaking issued numbers.</x:t>
         </x:is>
       </x:c>
       <x:c r="F87" s="2" t="inlineStr">
@@ -3721,14 +3721,14 @@
       </x:c>
       <x:c r="H87" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:150</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:169</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="88">
       <x:c r="A88" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.29.6</x:t>
+          <x:t xml:space="preserve">REQ_F4118.28.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B88" s="2" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </x:c>
       <x:c r="C88" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Approval Workflow</x:t>
+          <x:t xml:space="preserve">Document Number Rule</x:t>
         </x:is>
       </x:c>
       <x:c r="D88" s="2" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </x:c>
       <x:c r="E88" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should list the pending approval tasks of the current user.</x:t>
+          <x:t xml:space="preserve">System should allow user to preview the next document number for a business date.</x:t>
         </x:is>
       </x:c>
       <x:c r="F88" s="2" t="inlineStr">
@@ -3763,14 +3763,14 @@
       </x:c>
       <x:c r="H88" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:151</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:170</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="89">
       <x:c r="A89" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.29.7</x:t>
+          <x:t xml:space="preserve">REQ_F4118.28.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B89" s="2" t="inlineStr">
@@ -3780,7 +3780,7 @@
       </x:c>
       <x:c r="C89" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Approval Workflow</x:t>
+          <x:t xml:space="preserve">Document Number Rule</x:t>
         </x:is>
       </x:c>
       <x:c r="D89" s="2" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </x:c>
       <x:c r="E89" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow user to view the approval history of a document.</x:t>
+          <x:t xml:space="preserve">System should generate unique, gap-free document numbers for every module under concurrency.</x:t>
         </x:is>
       </x:c>
       <x:c r="F89" s="2" t="inlineStr">
@@ -3805,14 +3805,14 @@
       </x:c>
       <x:c r="H89" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:152</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:171</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="90">
       <x:c r="A90" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.29.8</x:t>
+          <x:t xml:space="preserve">REQ_F4118.28.6</x:t>
         </x:is>
       </x:c>
       <x:c r="B90" s="2" t="inlineStr">
@@ -3822,7 +3822,7 @@
       </x:c>
       <x:c r="C90" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Approval Workflow</x:t>
+          <x:t xml:space="preserve">Document Number Rule</x:t>
         </x:is>
       </x:c>
       <x:c r="D90" s="2" t="inlineStr">
@@ -3832,7 +3832,7 @@
       </x:c>
       <x:c r="E90" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should provide trilingual approval flow and delegation maintenance pages.</x:t>
+          <x:t xml:space="preserve">System should provide a trilingual number rule maintenance page.</x:t>
         </x:is>
       </x:c>
       <x:c r="F90" s="2" t="inlineStr">
@@ -3847,14 +3847,14 @@
       </x:c>
       <x:c r="H90" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:153</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:172</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="91">
       <x:c r="A91" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.29.9</x:t>
+          <x:t xml:space="preserve">REQ_F4118.29.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B91" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </x:c>
       <x:c r="E91" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should provide a trilingual approval inbox with approval history.</x:t>
+          <x:t xml:space="preserve">System should allow user to view and create multi-level approval flows with amount thresholds.</x:t>
         </x:is>
       </x:c>
       <x:c r="F91" s="2" t="inlineStr">
@@ -3889,14 +3889,14 @@
       </x:c>
       <x:c r="H91" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:154</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:146</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="92">
       <x:c r="A92" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.30.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.29.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B92" s="2" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </x:c>
       <x:c r="C92" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Development Seed Data</x:t>
+          <x:t xml:space="preserve">Approval Workflow</x:t>
         </x:is>
       </x:c>
       <x:c r="D92" s="2" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </x:c>
       <x:c r="E92" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should load demo companies, branches, departments and roles for the Development environment.</x:t>
+          <x:t xml:space="preserve">System should allow user to edit or deactivate an approval flow without affecting pending approvals.</x:t>
         </x:is>
       </x:c>
       <x:c r="F92" s="2" t="inlineStr">
@@ -3931,14 +3931,14 @@
       </x:c>
       <x:c r="H92" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:186</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:147</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="93">
       <x:c r="A93" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.30.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.29.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B93" s="2" t="inlineStr">
@@ -3948,7 +3948,7 @@
       </x:c>
       <x:c r="C93" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Development Seed Data</x:t>
+          <x:t xml:space="preserve">Approval Workflow</x:t>
         </x:is>
       </x:c>
       <x:c r="D93" s="2" t="inlineStr">
@@ -3958,7 +3958,7 @@
       </x:c>
       <x:c r="E93" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should create the test accounts of the SeedUsers setting with hashed passwords and company assignments.</x:t>
+          <x:t xml:space="preserve">System should allow user to assign an approval delegate for a date range.</x:t>
         </x:is>
       </x:c>
       <x:c r="F93" s="2" t="inlineStr">
@@ -3973,14 +3973,14 @@
       </x:c>
       <x:c r="H93" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:187</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:148</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="94">
       <x:c r="A94" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.30.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.29.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B94" s="2" t="inlineStr">
@@ -3990,7 +3990,7 @@
       </x:c>
       <x:c r="C94" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Development Seed Data</x:t>
+          <x:t xml:space="preserve">Approval Workflow</x:t>
         </x:is>
       </x:c>
       <x:c r="D94" s="2" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </x:c>
       <x:c r="E94" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow the seed to run repeatedly without duplicating or overwriting data.</x:t>
+          <x:t xml:space="preserve">System should enable every module to submit documents for approval through the shared workflow engine.</x:t>
         </x:is>
       </x:c>
       <x:c r="F94" s="2" t="inlineStr">
@@ -4015,14 +4015,14 @@
       </x:c>
       <x:c r="H94" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:188</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:149</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="95">
       <x:c r="A95" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.31.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.29.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B95" s="2" t="inlineStr">
@@ -4032,7 +4032,7 @@
       </x:c>
       <x:c r="C95" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Shared Dialogs and Page Templates</x:t>
+          <x:t xml:space="preserve">Approval Workflow</x:t>
         </x:is>
       </x:c>
       <x:c r="D95" s="2" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </x:c>
       <x:c r="E95" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should ask for confirmation in a shared trilingual confirmation box before dangerous actions.</x:t>
+          <x:t xml:space="preserve">System should allow approvers or their delegates to approve or reject the current approval step.</x:t>
         </x:is>
       </x:c>
       <x:c r="F95" s="2" t="inlineStr">
@@ -4057,14 +4057,14 @@
       </x:c>
       <x:c r="H95" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:200</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:150</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="96">
       <x:c r="A96" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.31.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.29.6</x:t>
         </x:is>
       </x:c>
       <x:c r="B96" s="2" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </x:c>
       <x:c r="C96" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Shared Dialogs and Page Templates</x:t>
+          <x:t xml:space="preserve">Approval Workflow</x:t>
         </x:is>
       </x:c>
       <x:c r="D96" s="2" t="inlineStr">
@@ -4084,7 +4084,7 @@
       </x:c>
       <x:c r="E96" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should show results that need the user's attention in a shared prompt box, and short success messages as toasts.</x:t>
+          <x:t xml:space="preserve">System should list the pending approval tasks of the current user.</x:t>
         </x:is>
       </x:c>
       <x:c r="F96" s="2" t="inlineStr">
@@ -4099,14 +4099,14 @@
       </x:c>
       <x:c r="H96" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:201</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:151</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="97">
       <x:c r="A97" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.31.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.29.7</x:t>
         </x:is>
       </x:c>
       <x:c r="B97" s="2" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </x:c>
       <x:c r="C97" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Shared Dialogs and Page Templates</x:t>
+          <x:t xml:space="preserve">Approval Workflow</x:t>
         </x:is>
       </x:c>
       <x:c r="D97" s="2" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </x:c>
       <x:c r="E97" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should provide a shared selection window for choosing master data with search and server-side paging.</x:t>
+          <x:t xml:space="preserve">System should allow user to view the approval history of a document.</x:t>
         </x:is>
       </x:c>
       <x:c r="F97" s="2" t="inlineStr">
@@ -4141,14 +4141,14 @@
       </x:c>
       <x:c r="H97" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:202</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:152</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="98">
       <x:c r="A98" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.31.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.29.8</x:t>
         </x:is>
       </x:c>
       <x:c r="B98" s="2" t="inlineStr">
@@ -4158,7 +4158,7 @@
       </x:c>
       <x:c r="C98" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Shared Dialogs and Page Templates</x:t>
+          <x:t xml:space="preserve">Approval Workflow</x:t>
         </x:is>
       </x:c>
       <x:c r="D98" s="2" t="inlineStr">
@@ -4168,7 +4168,7 @@
       </x:c>
       <x:c r="E98" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should provide a standard list page template reused by every module.</x:t>
+          <x:t xml:space="preserve">System should provide trilingual approval flow and delegation maintenance pages.</x:t>
         </x:is>
       </x:c>
       <x:c r="F98" s="2" t="inlineStr">
@@ -4183,14 +4183,14 @@
       </x:c>
       <x:c r="H98" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:203</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:153</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="99">
       <x:c r="A99" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.31.5</x:t>
+          <x:t xml:space="preserve">REQ_F4118.29.9</x:t>
         </x:is>
       </x:c>
       <x:c r="B99" s="2" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </x:c>
       <x:c r="C99" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Shared Dialogs and Page Templates</x:t>
+          <x:t xml:space="preserve">Approval Workflow</x:t>
         </x:is>
       </x:c>
       <x:c r="D99" s="2" t="inlineStr">
@@ -4210,7 +4210,7 @@
       </x:c>
       <x:c r="E99" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should provide a standard document page template with status, previous / next navigation and unsaved-change protection.</x:t>
+          <x:t xml:space="preserve">System should provide a trilingual approval inbox with approval history.</x:t>
         </x:is>
       </x:c>
       <x:c r="F99" s="2" t="inlineStr">
@@ -4225,14 +4225,14 @@
       </x:c>
       <x:c r="H99" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:204</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:154</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="100">
       <x:c r="A100" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.31.6</x:t>
+          <x:t xml:space="preserve">REQ_F4118.30.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B100" s="2" t="inlineStr">
@@ -4242,7 +4242,7 @@
       </x:c>
       <x:c r="C100" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Shared Dialogs and Page Templates</x:t>
+          <x:t xml:space="preserve">Development Seed Data</x:t>
         </x:is>
       </x:c>
       <x:c r="D100" s="2" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </x:c>
       <x:c r="E100" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should provide a date range filter with quick ranges and a document status tag following the macaron status colours.</x:t>
+          <x:t xml:space="preserve">System should load demo companies, branches, departments and roles for the Development environment.</x:t>
         </x:is>
       </x:c>
       <x:c r="F100" s="2" t="inlineStr">
@@ -4267,14 +4267,14 @@
       </x:c>
       <x:c r="H100" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:205</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:186</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="101">
       <x:c r="A101" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.32.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.30.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B101" s="2" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </x:c>
       <x:c r="C101" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">IP Whitelist</x:t>
+          <x:t xml:space="preserve">Development Seed Data</x:t>
         </x:is>
       </x:c>
       <x:c r="D101" s="2" t="inlineStr">
@@ -4294,7 +4294,7 @@
       </x:c>
       <x:c r="E101" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to view IP whitelist rules.</x:t>
+          <x:t xml:space="preserve">System should create the test accounts of the SeedUsers setting with hashed passwords and company assignments.</x:t>
         </x:is>
       </x:c>
       <x:c r="F101" s="2" t="inlineStr">
@@ -4309,14 +4309,14 @@
       </x:c>
       <x:c r="H101" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:217</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:187</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="102">
       <x:c r="A102" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.32.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.30.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B102" s="2" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </x:c>
       <x:c r="C102" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">IP Whitelist</x:t>
+          <x:t xml:space="preserve">Development Seed Data</x:t>
         </x:is>
       </x:c>
       <x:c r="D102" s="2" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </x:c>
       <x:c r="E102" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to create and deactivate IP whitelist rules.</x:t>
+          <x:t xml:space="preserve">System should allow the seed to run repeatedly without duplicating or overwriting data.</x:t>
         </x:is>
       </x:c>
       <x:c r="F102" s="2" t="inlineStr">
@@ -4351,14 +4351,14 @@
       </x:c>
       <x:c r="H102" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:218</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:188</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="103">
       <x:c r="A103" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.32.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.31.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B103" s="2" t="inlineStr">
@@ -4368,7 +4368,7 @@
       </x:c>
       <x:c r="C103" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">IP Whitelist</x:t>
+          <x:t xml:space="preserve">Shared Dialogs and Page Templates</x:t>
         </x:is>
       </x:c>
       <x:c r="D103" s="2" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </x:c>
       <x:c r="E103" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow single IPv4 or IPv6 addresses and CIDR networks in system, role or user scope.</x:t>
+          <x:t xml:space="preserve">System should ask for confirmation in a shared trilingual confirmation box before dangerous actions.</x:t>
         </x:is>
       </x:c>
       <x:c r="F103" s="2" t="inlineStr">
@@ -4393,14 +4393,14 @@
       </x:c>
       <x:c r="H103" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:219</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:200</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="104">
       <x:c r="A104" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.32.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.31.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B104" s="2" t="inlineStr">
@@ -4410,7 +4410,7 @@
       </x:c>
       <x:c r="C104" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">IP Whitelist</x:t>
+          <x:t xml:space="preserve">Shared Dialogs and Page Templates</x:t>
         </x:is>
       </x:c>
       <x:c r="D104" s="2" t="inlineStr">
@@ -4420,7 +4420,7 @@
       </x:c>
       <x:c r="E104" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should reject disallowed requests and audit each rejection.</x:t>
+          <x:t xml:space="preserve">System should show results that need the user's attention in a shared prompt box, and short success messages as toasts.</x:t>
         </x:is>
       </x:c>
       <x:c r="F104" s="2" t="inlineStr">
@@ -4435,14 +4435,14 @@
       </x:c>
       <x:c r="H104" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:220</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:201</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="105">
       <x:c r="A105" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.32.5</x:t>
+          <x:t xml:space="preserve">REQ_F4118.31.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B105" s="2" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </x:c>
       <x:c r="C105" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">IP Whitelist</x:t>
+          <x:t xml:space="preserve">Shared Dialogs and Page Templates</x:t>
         </x:is>
       </x:c>
       <x:c r="D105" s="2" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </x:c>
       <x:c r="E105" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow operators to disable IP filtering through server configuration.</x:t>
+          <x:t xml:space="preserve">System should provide a shared selection window for choosing master data with search and server-side paging.</x:t>
         </x:is>
       </x:c>
       <x:c r="F105" s="2" t="inlineStr">
@@ -4477,14 +4477,14 @@
       </x:c>
       <x:c r="H105" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:221</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:202</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="106">
       <x:c r="A106" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.32.6</x:t>
+          <x:t xml:space="preserve">REQ_F4118.31.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B106" s="2" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </x:c>
       <x:c r="C106" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">IP Whitelist</x:t>
+          <x:t xml:space="preserve">Shared Dialogs and Page Templates</x:t>
         </x:is>
       </x:c>
       <x:c r="D106" s="2" t="inlineStr">
@@ -4504,7 +4504,7 @@
       </x:c>
       <x:c r="E106" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should provide a trilingual IP whitelist maintenance page.</x:t>
+          <x:t xml:space="preserve">System should provide a standard list page template reused by every module.</x:t>
         </x:is>
       </x:c>
       <x:c r="F106" s="2" t="inlineStr">
@@ -4519,14 +4519,14 @@
       </x:c>
       <x:c r="H106" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:222</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:203</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="107">
       <x:c r="A107" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.33.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.31.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B107" s="2" t="inlineStr">
@@ -4536,17 +4536,17 @@
       </x:c>
       <x:c r="C107" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">In-app Notification</x:t>
+          <x:t xml:space="preserve">Shared Dialogs and Page Templates</x:t>
         </x:is>
       </x:c>
       <x:c r="D107" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1.1</x:t>
+          <x:t xml:space="preserve">1.0</x:t>
         </x:is>
       </x:c>
       <x:c r="E107" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable modules to publish notifications to a user.</x:t>
+          <x:t xml:space="preserve">System should provide a standard document page template with status, previous / next navigation and unsaved-change protection.</x:t>
         </x:is>
       </x:c>
       <x:c r="F107" s="2" t="inlineStr">
@@ -4561,14 +4561,14 @@
       </x:c>
       <x:c r="H107" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:278</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:204</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="108">
       <x:c r="A108" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.33.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.31.6</x:t>
         </x:is>
       </x:c>
       <x:c r="B108" s="2" t="inlineStr">
@@ -4578,17 +4578,17 @@
       </x:c>
       <x:c r="C108" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">In-app Notification</x:t>
+          <x:t xml:space="preserve">Shared Dialogs and Page Templates</x:t>
         </x:is>
       </x:c>
       <x:c r="D108" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1.1</x:t>
+          <x:t xml:space="preserve">1.0</x:t>
         </x:is>
       </x:c>
       <x:c r="E108" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to view notifications.</x:t>
+          <x:t xml:space="preserve">System should provide a date range filter with quick ranges and a document status tag following the macaron status colours.</x:t>
         </x:is>
       </x:c>
       <x:c r="F108" s="2" t="inlineStr">
@@ -4603,14 +4603,14 @@
       </x:c>
       <x:c r="H108" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:279</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:205</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="109">
       <x:c r="A109" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.33.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.32.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B109" s="2" t="inlineStr">
@@ -4620,17 +4620,17 @@
       </x:c>
       <x:c r="C109" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">In-app Notification</x:t>
+          <x:t xml:space="preserve">IP Whitelist</x:t>
         </x:is>
       </x:c>
       <x:c r="D109" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1.1</x:t>
+          <x:t xml:space="preserve">1.0</x:t>
         </x:is>
       </x:c>
       <x:c r="E109" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to mark notifications as read.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to view IP whitelist rules.</x:t>
         </x:is>
       </x:c>
       <x:c r="F109" s="2" t="inlineStr">
@@ -4645,47 +4645,383 @@
       </x:c>
       <x:c r="H109" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:280</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:217</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="110">
       <x:c r="A110" s="2" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">REQ_F4118.32.2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B110" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C110" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">IP Whitelist</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D110" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E110" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow authorized users to create and deactivate IP whitelist rules.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F110" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G110" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="H110" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:218</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="111">
+      <x:c r="A111" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.32.3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B111" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C111" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">IP Whitelist</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D111" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E111" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow single IPv4 or IPv6 addresses and CIDR networks in system, role or user scope.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F111" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G111" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="H111" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:219</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="112">
+      <x:c r="A112" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.32.4</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B112" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C112" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">IP Whitelist</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D112" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E112" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should reject disallowed requests and audit each rejection.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F112" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G112" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="H112" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:220</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="113">
+      <x:c r="A113" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.32.5</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B113" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C113" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">IP Whitelist</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D113" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E113" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow operators to disable IP filtering through server configuration.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F113" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G113" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="H113" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:221</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="114">
+      <x:c r="A114" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.32.6</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B114" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C114" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">IP Whitelist</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D114" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E114" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should provide a trilingual IP whitelist maintenance page.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F114" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G114" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="H114" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:222</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="115">
+      <x:c r="A115" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.33.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B115" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C115" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">In-app Notification</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D115" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E115" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should enable modules to publish notifications to a user.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F115" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G115" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="H115" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:278</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="116">
+      <x:c r="A116" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.33.2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B116" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C116" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">In-app Notification</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D116" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E116" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should enable user to view notifications.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F116" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G116" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="H116" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:279</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="117">
+      <x:c r="A117" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.33.3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B117" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C117" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">In-app Notification</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D117" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E117" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should enable user to mark notifications as read.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F117" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G117" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="H117" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:280</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="118">
+      <x:c r="A118" s="2" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">REQ_F4118.34.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="B110" s="2" t="inlineStr">
+      <x:c r="B118" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Settings</x:t>
         </x:is>
       </x:c>
-      <x:c r="C110" s="2" t="inlineStr">
+      <x:c r="C118" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Master Data Portal</x:t>
         </x:is>
       </x:c>
-      <x:c r="D110" s="2" t="inlineStr">
+      <x:c r="D118" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="E110" s="2" t="inlineStr">
+      <x:c r="E118" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">System should allow authorized users to view the master data portal.</x:t>
         </x:is>
       </x:c>
-      <x:c r="F110" s="2" t="inlineStr">
+      <x:c r="F118" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Developer</x:t>
         </x:is>
       </x:c>
-      <x:c r="G110" s="2" t="inlineStr">
+      <x:c r="G118" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">/md 僅向已登入且在目前公司有 MD.MASTER.VIEW 的用戶開放；無權限導向 403；三語標題與說明一致。</x:t>
         </x:is>
       </x:c>
-      <x:c r="H110" s="2" t="inlineStr">
+      <x:c r="H118" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:11</x:t>
         </x:is>
@@ -6499,6 +6835,70 @@
       <x:c r="F27" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">REQ_F4118.13.1, REQ_F4118.13.2, REQ_F4118.13.3, REQ_F4118.13.4</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.111</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B28" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C28" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">md_item_brand</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D28" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">This table stores item brands within a company.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E28" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F28" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.11.1, REQ_F4118.11.2, REQ_F4118.11.3, REQ_F4118.11.4</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.112</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B29" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C29" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">md_item_category</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D29" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">This table stores the item category tree within a company.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E29" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F29" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.10.1, REQ_F4118.10.2, REQ_F4118.10.3, REQ_F4118.10.4</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -16099,170 +16499,170 @@
     <x:row r="19">
       <x:c r="A19" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.13.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.10.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B19" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to view unit of measurement.</x:t>
+          <x:t xml:space="preserve">System should enable user to view item category.</x:t>
         </x:is>
       </x:c>
       <x:c r="C19" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.109, REQ_DS43.110</x:t>
+          <x:t xml:space="preserve">REQ_DS43.112</x:t>
         </x:is>
       </x:c>
       <x:c r="D19" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.45</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="E19" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.45.1, REQ_IO_A8.45.2, REQ_IO_A8.45.3, REQ_IO_A8.45.4</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="F19" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MD-UOM-001, MD-UOM-002, MD-UOM-003, MD-UOM-004, MD-UOM-005</x:t>
+          <x:t xml:space="preserve">MD-ICAT-001</x:t>
         </x:is>
       </x:c>
       <x:c r="G19" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Covered</x:t>
+          <x:t xml:space="preserve">Partial</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.13.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.10.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B20" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to create unit of measurement.</x:t>
+          <x:t xml:space="preserve">System should enable user to create item category.</x:t>
         </x:is>
       </x:c>
       <x:c r="C20" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.109, REQ_DS43.110</x:t>
+          <x:t xml:space="preserve">REQ_DS43.112</x:t>
         </x:is>
       </x:c>
       <x:c r="D20" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.46</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="E20" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.46.1, REQ_IO_A8.46.2, REQ_IO_A8.46.3, REQ_IO_A8.46.4, REQ_IO_A8.46.5</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="F20" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MD-UOM-001, MD-UOM-002, MD-UOM-003, MD-UOM-004, MD-UOM-005</x:t>
+          <x:t xml:space="preserve">MD-ICAT-001, MD-ICAT-002</x:t>
         </x:is>
       </x:c>
       <x:c r="G20" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Covered</x:t>
+          <x:t xml:space="preserve">Partial</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.13.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.10.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B21" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to edit unit of measurement.</x:t>
+          <x:t xml:space="preserve">System should enable user to edit item category.</x:t>
         </x:is>
       </x:c>
       <x:c r="C21" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.109, REQ_DS43.110</x:t>
+          <x:t xml:space="preserve">REQ_DS43.112</x:t>
         </x:is>
       </x:c>
       <x:c r="D21" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.47</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="E21" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.47.1, REQ_IO_A8.47.2, REQ_IO_A8.47.3</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="F21" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MD-UOM-001, MD-UOM-003, MD-UOM-004, MD-UOM-005</x:t>
+          <x:t xml:space="preserve">MD-ICAT-001, MD-ICAT-002</x:t>
         </x:is>
       </x:c>
       <x:c r="G21" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Covered</x:t>
+          <x:t xml:space="preserve">Partial</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.13.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.10.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B22" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to delete unit of measurement.</x:t>
+          <x:t xml:space="preserve">System should enable user to delete item category.</x:t>
         </x:is>
       </x:c>
       <x:c r="C22" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.109, REQ_DS43.110</x:t>
+          <x:t xml:space="preserve">REQ_DS43.112</x:t>
         </x:is>
       </x:c>
       <x:c r="D22" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.47</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="E22" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.47.4</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="F22" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MD-UOM-001, MD-UOM-003, MD-UOM-004, MD-UOM-005</x:t>
+          <x:t xml:space="preserve">MD-ICAT-003</x:t>
         </x:is>
       </x:c>
       <x:c r="G22" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Covered</x:t>
+          <x:t xml:space="preserve">Partial</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.17.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.11.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B23" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to view parameter settings.</x:t>
+          <x:t xml:space="preserve">System should enable user to view item brand.</x:t>
         </x:is>
       </x:c>
       <x:c r="C23" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.73</x:t>
+          <x:t xml:space="preserve">REQ_DS43.111</x:t>
         </x:is>
       </x:c>
       <x:c r="D23" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.55</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="E23" s="2" t="inlineStr">
@@ -16272,66 +16672,66 @@
       </x:c>
       <x:c r="F23" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-PARAM-002</x:t>
+          <x:t xml:space="preserve">MD-BRD-001</x:t>
         </x:is>
       </x:c>
       <x:c r="G23" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Covered</x:t>
+          <x:t xml:space="preserve">Partial</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.17.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.11.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B24" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to edit parameter settings.</x:t>
+          <x:t xml:space="preserve">System should enable user to create item brand.</x:t>
         </x:is>
       </x:c>
       <x:c r="C24" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.73</x:t>
+          <x:t xml:space="preserve">REQ_DS43.111</x:t>
         </x:is>
       </x:c>
       <x:c r="D24" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.55</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="E24" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.55.1, REQ_IO_A8.55.2, REQ_IO_A8.55.3, REQ_IO_A8.55.4, REQ_IO_A8.55.5, REQ_IO_A8.55.7</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="F24" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-PARAM-002, SYS-PARAM-003</x:t>
+          <x:t xml:space="preserve">MD-BRD-001</x:t>
         </x:is>
       </x:c>
       <x:c r="G24" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Covered</x:t>
+          <x:t xml:space="preserve">Partial</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.17.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.11.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B25" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should let every module declare typed company parameters with defaults and read them in process.</x:t>
+          <x:t xml:space="preserve">System should enable user to edit item brand.</x:t>
         </x:is>
       </x:c>
       <x:c r="C25" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.73</x:t>
+          <x:t xml:space="preserve">REQ_DS43.111</x:t>
         </x:is>
       </x:c>
       <x:c r="D25" s="2" t="inlineStr">
@@ -16346,7 +16746,7 @@
       </x:c>
       <x:c r="F25" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-PARAM-001, SYS-PARAM-004</x:t>
+          <x:t xml:space="preserve">MD-BRD-001</x:t>
         </x:is>
       </x:c>
       <x:c r="G25" s="2" t="inlineStr">
@@ -16358,69 +16758,69 @@
     <x:row r="26">
       <x:c r="A26" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.17.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.11.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B26" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should provide a parameter edit interface grouped by module.</x:t>
+          <x:t xml:space="preserve">System should enable user to delete item brand.</x:t>
         </x:is>
       </x:c>
       <x:c r="C26" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.73</x:t>
+          <x:t xml:space="preserve">REQ_DS43.111</x:t>
         </x:is>
       </x:c>
       <x:c r="D26" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.55</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="E26" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.55.1, REQ_IO_A8.55.2, REQ_IO_A8.55.3, REQ_IO_A8.55.4, REQ_IO_A8.55.5, REQ_IO_A8.55.6, REQ_IO_A8.55.7</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="F26" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-PARAM-005, SYS-PARAM-006, SYS-PARAM-007</x:t>
+          <x:t xml:space="preserve">MD-BRD-001</x:t>
         </x:is>
       </x:c>
       <x:c r="G26" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Covered</x:t>
+          <x:t xml:space="preserve">Partial</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.18.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.13.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B27" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to view print settings.</x:t>
+          <x:t xml:space="preserve">System should enable user to view unit of measurement.</x:t>
         </x:is>
       </x:c>
       <x:c r="C27" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.73</x:t>
+          <x:t xml:space="preserve">REQ_DS43.109, REQ_DS43.110</x:t>
         </x:is>
       </x:c>
       <x:c r="D27" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.56</x:t>
+          <x:t xml:space="preserve">4.4.1.8.45</x:t>
         </x:is>
       </x:c>
       <x:c r="E27" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.56.1, REQ_IO_A8.56.2, REQ_IO_A8.56.3, REQ_IO_A8.56.4, REQ_IO_A8.56.5, REQ_IO_A8.56.6, REQ_IO_A8.56.7, REQ_IO_A8.56.8, REQ_IO_A8.56.9, REQ_IO_A8.56.10</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.45.1, REQ_IO_A8.45.2, REQ_IO_A8.45.3, REQ_IO_A8.45.4</x:t>
         </x:is>
       </x:c>
       <x:c r="F27" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-PRINT-004, SYS-PRINT-005</x:t>
+          <x:t xml:space="preserve">MD-UOM-001, MD-UOM-002, MD-UOM-003, MD-UOM-004, MD-UOM-005</x:t>
         </x:is>
       </x:c>
       <x:c r="G27" s="2" t="inlineStr">
@@ -16432,32 +16832,32 @@
     <x:row r="28">
       <x:c r="A28" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.18.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.13.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B28" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to edit print settings.</x:t>
+          <x:t xml:space="preserve">System should enable user to create unit of measurement.</x:t>
         </x:is>
       </x:c>
       <x:c r="C28" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.73</x:t>
+          <x:t xml:space="preserve">REQ_DS43.109, REQ_DS43.110</x:t>
         </x:is>
       </x:c>
       <x:c r="D28" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.56</x:t>
+          <x:t xml:space="preserve">4.4.1.8.46</x:t>
         </x:is>
       </x:c>
       <x:c r="E28" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.56.1, REQ_IO_A8.56.2, REQ_IO_A8.56.3, REQ_IO_A8.56.4, REQ_IO_A8.56.5, REQ_IO_A8.56.6, REQ_IO_A8.56.7, REQ_IO_A8.56.8, REQ_IO_A8.56.9, REQ_IO_A8.56.11</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.46.1, REQ_IO_A8.46.2, REQ_IO_A8.46.3, REQ_IO_A8.46.4, REQ_IO_A8.46.5</x:t>
         </x:is>
       </x:c>
       <x:c r="F28" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-PRINT-001, SYS-PRINT-002, SYS-PRINT-004, SYS-PRINT-005</x:t>
+          <x:t xml:space="preserve">MD-UOM-001, MD-UOM-002, MD-UOM-003, MD-UOM-004, MD-UOM-005</x:t>
         </x:is>
       </x:c>
       <x:c r="G28" s="2" t="inlineStr">
@@ -16469,69 +16869,69 @@
     <x:row r="29">
       <x:c r="A29" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.18.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.13.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B29" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should let printing modules read the company's print settings.</x:t>
+          <x:t xml:space="preserve">System should enable user to edit unit of measurement.</x:t>
         </x:is>
       </x:c>
       <x:c r="C29" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.73</x:t>
+          <x:t xml:space="preserve">REQ_DS43.109, REQ_DS43.110</x:t>
         </x:is>
       </x:c>
       <x:c r="D29" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">4.4.1.8.47</x:t>
         </x:is>
       </x:c>
       <x:c r="E29" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.47.1, REQ_IO_A8.47.2, REQ_IO_A8.47.3</x:t>
         </x:is>
       </x:c>
       <x:c r="F29" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-PRINT-003</x:t>
+          <x:t xml:space="preserve">MD-UOM-001, MD-UOM-003, MD-UOM-004, MD-UOM-005</x:t>
         </x:is>
       </x:c>
       <x:c r="G29" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.19.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.13.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B30" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to view the logo and stamp.</x:t>
+          <x:t xml:space="preserve">System should enable user to delete unit of measurement.</x:t>
         </x:is>
       </x:c>
       <x:c r="C30" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.103</x:t>
+          <x:t xml:space="preserve">REQ_DS43.109, REQ_DS43.110</x:t>
         </x:is>
       </x:c>
       <x:c r="D30" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.57</x:t>
+          <x:t xml:space="preserve">4.4.1.8.47</x:t>
         </x:is>
       </x:c>
       <x:c r="E30" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.57.1, REQ_IO_A8.57.2, REQ_IO_A8.57.3</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.47.4</x:t>
         </x:is>
       </x:c>
       <x:c r="F30" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-IMG-003, SYS-IMG-005, SYS-IMG-007, SYS-IMG-008</x:t>
+          <x:t xml:space="preserve">MD-UOM-001, MD-UOM-003, MD-UOM-004, MD-UOM-005</x:t>
         </x:is>
       </x:c>
       <x:c r="G30" s="2" t="inlineStr">
@@ -16543,32 +16943,32 @@
     <x:row r="31">
       <x:c r="A31" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.19.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.17.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B31" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to edit the logo and stamp.</x:t>
+          <x:t xml:space="preserve">System should enable user to view parameter settings.</x:t>
         </x:is>
       </x:c>
       <x:c r="C31" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.103</x:t>
+          <x:t xml:space="preserve">REQ_DS43.73</x:t>
         </x:is>
       </x:c>
       <x:c r="D31" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.57</x:t>
+          <x:t xml:space="preserve">4.4.1.8.55</x:t>
         </x:is>
       </x:c>
       <x:c r="E31" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.57.4, REQ_IO_A8.57.5</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="F31" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-IMG-001, SYS-IMG-002, SYS-IMG-003, SYS-IMG-004, SYS-IMG-005, SYS-IMG-007, SYS-IMG-008</x:t>
+          <x:t xml:space="preserve">SYS-PARAM-002</x:t>
         </x:is>
       </x:c>
       <x:c r="G31" s="2" t="inlineStr">
@@ -16580,59 +16980,59 @@
     <x:row r="32">
       <x:c r="A32" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.19.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.17.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B32" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should let printing modules read the company's logo and stamp.</x:t>
+          <x:t xml:space="preserve">System should enable user to edit parameter settings.</x:t>
         </x:is>
       </x:c>
       <x:c r="C32" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.103</x:t>
+          <x:t xml:space="preserve">REQ_DS43.73</x:t>
         </x:is>
       </x:c>
       <x:c r="D32" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">4.4.1.8.55</x:t>
         </x:is>
       </x:c>
       <x:c r="E32" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.55.1, REQ_IO_A8.55.2, REQ_IO_A8.55.3, REQ_IO_A8.55.4, REQ_IO_A8.55.5, REQ_IO_A8.55.7</x:t>
         </x:is>
       </x:c>
       <x:c r="F32" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-IMG-006</x:t>
+          <x:t xml:space="preserve">SYS-PARAM-002, SYS-PARAM-003</x:t>
         </x:is>
       </x:c>
       <x:c r="G32" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.20.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.17.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B33" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to view company details.</x:t>
+          <x:t xml:space="preserve">System should let every module declare typed company parameters with defaults and read them in process.</x:t>
         </x:is>
       </x:c>
       <x:c r="C33" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.20</x:t>
+          <x:t xml:space="preserve">REQ_DS43.73</x:t>
         </x:is>
       </x:c>
       <x:c r="D33" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.58</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="E33" s="2" t="inlineStr">
@@ -16642,44 +17042,44 @@
       </x:c>
       <x:c r="F33" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-ORG-004, SYS-ORG-011, SYS-ORG-012, SYS-ORG-020, SYS-ORG-026</x:t>
+          <x:t xml:space="preserve">SYS-PARAM-001, SYS-PARAM-004</x:t>
         </x:is>
       </x:c>
       <x:c r="G33" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Covered</x:t>
+          <x:t xml:space="preserve">Partial</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.20.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.17.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B34" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to create a company.</x:t>
+          <x:t xml:space="preserve">System should provide a parameter edit interface grouped by module.</x:t>
         </x:is>
       </x:c>
       <x:c r="C34" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.20</x:t>
+          <x:t xml:space="preserve">REQ_DS43.73</x:t>
         </x:is>
       </x:c>
       <x:c r="D34" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.58</x:t>
+          <x:t xml:space="preserve">4.4.1.8.55</x:t>
         </x:is>
       </x:c>
       <x:c r="E34" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.58.1, REQ_IO_A8.58.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.55.1, REQ_IO_A8.55.2, REQ_IO_A8.55.3, REQ_IO_A8.55.4, REQ_IO_A8.55.5, REQ_IO_A8.55.6, REQ_IO_A8.55.7</x:t>
         </x:is>
       </x:c>
       <x:c r="F34" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-ORG-001, SYS-ORG-008, SYS-ORG-013, SYS-ORG-021</x:t>
+          <x:t xml:space="preserve">SYS-PARAM-005, SYS-PARAM-006, SYS-PARAM-007</x:t>
         </x:is>
       </x:c>
       <x:c r="G34" s="2" t="inlineStr">
@@ -16691,32 +17091,32 @@
     <x:row r="35">
       <x:c r="A35" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.20.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.18.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B35" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to edit a company.</x:t>
+          <x:t xml:space="preserve">System should enable user to view print settings.</x:t>
         </x:is>
       </x:c>
       <x:c r="C35" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.20</x:t>
+          <x:t xml:space="preserve">REQ_DS43.73</x:t>
         </x:is>
       </x:c>
       <x:c r="D35" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.58</x:t>
+          <x:t xml:space="preserve">4.4.1.8.56</x:t>
         </x:is>
       </x:c>
       <x:c r="E35" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.56.1, REQ_IO_A8.56.2, REQ_IO_A8.56.3, REQ_IO_A8.56.4, REQ_IO_A8.56.5, REQ_IO_A8.56.6, REQ_IO_A8.56.7, REQ_IO_A8.56.8, REQ_IO_A8.56.9, REQ_IO_A8.56.10</x:t>
         </x:is>
       </x:c>
       <x:c r="F35" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-ORG-005, SYS-ORG-009, SYS-ORG-013, SYS-ORG-021, SYS-PERM-030</x:t>
+          <x:t xml:space="preserve">SYS-PRINT-004, SYS-PRINT-005</x:t>
         </x:is>
       </x:c>
       <x:c r="G35" s="2" t="inlineStr">
@@ -16728,32 +17128,32 @@
     <x:row r="36">
       <x:c r="A36" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.20.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.18.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B36" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to deactivate a company.</x:t>
+          <x:t xml:space="preserve">System should enable user to edit print settings.</x:t>
         </x:is>
       </x:c>
       <x:c r="C36" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.20</x:t>
+          <x:t xml:space="preserve">REQ_DS43.73</x:t>
         </x:is>
       </x:c>
       <x:c r="D36" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.58</x:t>
+          <x:t xml:space="preserve">4.4.1.8.56</x:t>
         </x:is>
       </x:c>
       <x:c r="E36" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.56.1, REQ_IO_A8.56.2, REQ_IO_A8.56.3, REQ_IO_A8.56.4, REQ_IO_A8.56.5, REQ_IO_A8.56.6, REQ_IO_A8.56.7, REQ_IO_A8.56.8, REQ_IO_A8.56.9, REQ_IO_A8.56.11</x:t>
         </x:is>
       </x:c>
       <x:c r="F36" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-ORG-006, SYS-ORG-021</x:t>
+          <x:t xml:space="preserve">SYS-PRINT-001, SYS-PRINT-002, SYS-PRINT-004, SYS-PRINT-005</x:t>
         </x:is>
       </x:c>
       <x:c r="G36" s="2" t="inlineStr">
@@ -16765,22 +17165,22 @@
     <x:row r="37">
       <x:c r="A37" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.21.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.18.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B37" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to view branches in the selected company.</x:t>
+          <x:t xml:space="preserve">System should let printing modules read the company's print settings.</x:t>
         </x:is>
       </x:c>
       <x:c r="C37" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.89</x:t>
+          <x:t xml:space="preserve">REQ_DS43.73</x:t>
         </x:is>
       </x:c>
       <x:c r="D37" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.59</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="E37" s="2" t="inlineStr">
@@ -16790,44 +17190,44 @@
       </x:c>
       <x:c r="F37" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-ORG-002, SYS-ORG-004, SYS-ORG-010, SYS-ORG-012, SYS-ORG-020, SYS-ORG-022, SYS-ORG-024, SYS-ORG-025, SYS-ORG-027</x:t>
+          <x:t xml:space="preserve">SYS-PRINT-003</x:t>
         </x:is>
       </x:c>
       <x:c r="G37" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Covered</x:t>
+          <x:t xml:space="preserve">Partial</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.21.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.19.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B38" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to create a branch.</x:t>
+          <x:t xml:space="preserve">System should enable user to view the logo and stamp.</x:t>
         </x:is>
       </x:c>
       <x:c r="C38" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.89</x:t>
+          <x:t xml:space="preserve">REQ_DS43.103</x:t>
         </x:is>
       </x:c>
       <x:c r="D38" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.59</x:t>
+          <x:t xml:space="preserve">4.4.1.8.57</x:t>
         </x:is>
       </x:c>
       <x:c r="E38" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.59.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.57.1, REQ_IO_A8.57.2, REQ_IO_A8.57.3</x:t>
         </x:is>
       </x:c>
       <x:c r="F38" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-ORG-001, SYS-ORG-013, SYS-ORG-020, SYS-ORG-022, SYS-ORG-024</x:t>
+          <x:t xml:space="preserve">SYS-IMG-003, SYS-IMG-005, SYS-IMG-007, SYS-IMG-008</x:t>
         </x:is>
       </x:c>
       <x:c r="G38" s="2" t="inlineStr">
@@ -16839,32 +17239,32 @@
     <x:row r="39">
       <x:c r="A39" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.21.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.19.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B39" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to edit or deactivate a branch.</x:t>
+          <x:t xml:space="preserve">System should enable user to edit the logo and stamp.</x:t>
         </x:is>
       </x:c>
       <x:c r="C39" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.89</x:t>
+          <x:t xml:space="preserve">REQ_DS43.103</x:t>
         </x:is>
       </x:c>
       <x:c r="D39" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.59</x:t>
+          <x:t xml:space="preserve">4.4.1.8.57</x:t>
         </x:is>
       </x:c>
       <x:c r="E39" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.57.4, REQ_IO_A8.57.5</x:t>
         </x:is>
       </x:c>
       <x:c r="F39" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-ORG-005, SYS-ORG-022</x:t>
+          <x:t xml:space="preserve">SYS-IMG-001, SYS-IMG-002, SYS-IMG-003, SYS-IMG-004, SYS-IMG-005, SYS-IMG-007, SYS-IMG-008</x:t>
         </x:is>
       </x:c>
       <x:c r="G39" s="2" t="inlineStr">
@@ -16876,22 +17276,22 @@
     <x:row r="40">
       <x:c r="A40" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.22.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.19.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B40" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to view departments in the selected company.</x:t>
+          <x:t xml:space="preserve">System should let printing modules read the company's logo and stamp.</x:t>
         </x:is>
       </x:c>
       <x:c r="C40" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.22</x:t>
+          <x:t xml:space="preserve">REQ_DS43.103</x:t>
         </x:is>
       </x:c>
       <x:c r="D40" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.60</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="E40" s="2" t="inlineStr">
@@ -16901,44 +17301,44 @@
       </x:c>
       <x:c r="F40" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-ORG-002, SYS-ORG-004, SYS-ORG-010, SYS-ORG-012, SYS-ORG-020, SYS-ORG-023, SYS-ORG-026, SYS-ORG-027</x:t>
+          <x:t xml:space="preserve">SYS-IMG-006</x:t>
         </x:is>
       </x:c>
       <x:c r="G40" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Covered</x:t>
+          <x:t xml:space="preserve">Partial</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.22.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.20.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B41" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to create a department under a branch or parent department.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to view company details.</x:t>
         </x:is>
       </x:c>
       <x:c r="C41" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.22</x:t>
+          <x:t xml:space="preserve">REQ_DS43.20</x:t>
         </x:is>
       </x:c>
       <x:c r="D41" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.60</x:t>
+          <x:t xml:space="preserve">4.4.1.8.58</x:t>
         </x:is>
       </x:c>
       <x:c r="E41" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.60.1, REQ_IO_A8.60.2</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="F41" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-ORG-001, SYS-ORG-003, SYS-ORG-013, SYS-ORG-023</x:t>
+          <x:t xml:space="preserve">SYS-ORG-004, SYS-ORG-011, SYS-ORG-012, SYS-ORG-020, SYS-ORG-026</x:t>
         </x:is>
       </x:c>
       <x:c r="G41" s="2" t="inlineStr">
@@ -16950,32 +17350,32 @@
     <x:row r="42">
       <x:c r="A42" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.22.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.20.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B42" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to edit or deactivate a department.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to create a company.</x:t>
         </x:is>
       </x:c>
       <x:c r="C42" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.22</x:t>
+          <x:t xml:space="preserve">REQ_DS43.20</x:t>
         </x:is>
       </x:c>
       <x:c r="D42" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.60</x:t>
+          <x:t xml:space="preserve">4.4.1.8.58</x:t>
         </x:is>
       </x:c>
       <x:c r="E42" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.58.1, REQ_IO_A8.58.2</x:t>
         </x:is>
       </x:c>
       <x:c r="F42" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-ORG-005, SYS-ORG-007, SYS-ORG-009, SYS-ORG-023, SYS-ORG-026</x:t>
+          <x:t xml:space="preserve">SYS-ORG-001, SYS-ORG-008, SYS-ORG-013, SYS-ORG-021</x:t>
         </x:is>
       </x:c>
       <x:c r="G42" s="2" t="inlineStr">
@@ -16987,32 +17387,32 @@
     <x:row r="43">
       <x:c r="A43" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.23.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.20.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B43" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to create a unique user identity.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to edit a company.</x:t>
         </x:is>
       </x:c>
       <x:c r="C43" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.82</x:t>
+          <x:t xml:space="preserve">REQ_DS43.20</x:t>
         </x:is>
       </x:c>
       <x:c r="D43" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.61</x:t>
+          <x:t xml:space="preserve">4.4.1.8.58</x:t>
         </x:is>
       </x:c>
       <x:c r="E43" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.61.1</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="F43" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-ORG-027, SYS-USER-001, SYS-USER-004, SYS-USER-012</x:t>
+          <x:t xml:space="preserve">SYS-ORG-005, SYS-ORG-009, SYS-ORG-013, SYS-ORG-021, SYS-PERM-030</x:t>
         </x:is>
       </x:c>
       <x:c r="G43" s="2" t="inlineStr">
@@ -17024,32 +17424,32 @@
     <x:row r="44">
       <x:c r="A44" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.23.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.20.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B44" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enforce a configurable password policy.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to deactivate a company.</x:t>
         </x:is>
       </x:c>
       <x:c r="C44" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.82</x:t>
+          <x:t xml:space="preserve">REQ_DS43.20</x:t>
         </x:is>
       </x:c>
       <x:c r="D44" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.61</x:t>
+          <x:t xml:space="preserve">4.4.1.8.58</x:t>
         </x:is>
       </x:c>
       <x:c r="E44" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.61.2, REQ_IO_A8.61.3</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="F44" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-USER-001, SYS-USER-007, SYS-USER-012</x:t>
+          <x:t xml:space="preserve">SYS-ORG-006, SYS-ORG-021</x:t>
         </x:is>
       </x:c>
       <x:c r="G44" s="2" t="inlineStr">
@@ -17061,106 +17461,106 @@
     <x:row r="45">
       <x:c r="A45" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.23.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.21.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B45" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should lock an account after five consecutive failed password attempts.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to view branches in the selected company.</x:t>
         </x:is>
       </x:c>
       <x:c r="C45" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.82</x:t>
+          <x:t xml:space="preserve">REQ_DS43.89</x:t>
         </x:is>
       </x:c>
       <x:c r="D45" s="2" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">4.4.1.8.59</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E45" s="2" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
-      <x:c r="E45" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
       <x:c r="F45" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-USER-002, SYS-USER-003, SYS-USER-005, SYS-USER-014</x:t>
+          <x:t xml:space="preserve">SYS-ORG-002, SYS-ORG-004, SYS-ORG-010, SYS-ORG-012, SYS-ORG-020, SYS-ORG-022, SYS-ORG-024, SYS-ORG-025, SYS-ORG-027</x:t>
         </x:is>
       </x:c>
       <x:c r="G45" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.23.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.21.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B46" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should determine whether a user's password has expired.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to create a branch.</x:t>
         </x:is>
       </x:c>
       <x:c r="C46" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.82</x:t>
+          <x:t xml:space="preserve">REQ_DS43.89</x:t>
         </x:is>
       </x:c>
       <x:c r="D46" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">4.4.1.8.59</x:t>
         </x:is>
       </x:c>
       <x:c r="E46" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.59.1</x:t>
         </x:is>
       </x:c>
       <x:c r="F46" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-USER-003</x:t>
+          <x:t xml:space="preserve">SYS-ORG-001, SYS-ORG-013, SYS-ORG-020, SYS-ORG-022, SYS-ORG-024</x:t>
         </x:is>
       </x:c>
       <x:c r="G46" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.23.5</x:t>
+          <x:t xml:space="preserve">REQ_F4118.21.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B47" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should list the users of the current company with paging, keyword and sorting.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to edit or deactivate a branch.</x:t>
         </x:is>
       </x:c>
       <x:c r="C47" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.82, REQ_DS43.92</x:t>
+          <x:t xml:space="preserve">REQ_DS43.89</x:t>
         </x:is>
       </x:c>
       <x:c r="D47" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.63</x:t>
+          <x:t xml:space="preserve">4.4.1.8.59</x:t>
         </x:is>
       </x:c>
       <x:c r="E47" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.63.1, REQ_IO_A8.63.2</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="F47" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-USER-006, SYS-USER-010, SYS-USER-011, SYS-USER-015</x:t>
+          <x:t xml:space="preserve">SYS-ORG-005, SYS-ORG-022</x:t>
         </x:is>
       </x:c>
       <x:c r="G47" s="2" t="inlineStr">
@@ -17172,22 +17572,22 @@
     <x:row r="48">
       <x:c r="A48" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.23.6</x:t>
+          <x:t xml:space="preserve">REQ_F4118.22.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B48" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to create a user in the current company.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to view departments in the selected company.</x:t>
         </x:is>
       </x:c>
       <x:c r="C48" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.82, REQ_DS43.92</x:t>
+          <x:t xml:space="preserve">REQ_DS43.22</x:t>
         </x:is>
       </x:c>
       <x:c r="D48" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.61</x:t>
+          <x:t xml:space="preserve">4.4.1.8.60</x:t>
         </x:is>
       </x:c>
       <x:c r="E48" s="2" t="inlineStr">
@@ -17197,7 +17597,7 @@
       </x:c>
       <x:c r="F48" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-USER-006, SYS-USER-010, SYS-USER-011, SYS-USER-012</x:t>
+          <x:t xml:space="preserve">SYS-ORG-002, SYS-ORG-004, SYS-ORG-010, SYS-ORG-012, SYS-ORG-020, SYS-ORG-023, SYS-ORG-026, SYS-ORG-027</x:t>
         </x:is>
       </x:c>
       <x:c r="G48" s="2" t="inlineStr">
@@ -17209,32 +17609,32 @@
     <x:row r="49">
       <x:c r="A49" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.23.7</x:t>
+          <x:t xml:space="preserve">REQ_F4118.22.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B49" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to activate or deactivate a user.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to create a department under a branch or parent department.</x:t>
         </x:is>
       </x:c>
       <x:c r="C49" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.82</x:t>
+          <x:t xml:space="preserve">REQ_DS43.22</x:t>
         </x:is>
       </x:c>
       <x:c r="D49" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.63</x:t>
+          <x:t xml:space="preserve">4.4.1.8.60</x:t>
         </x:is>
       </x:c>
       <x:c r="E49" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.63.3</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.60.1, REQ_IO_A8.60.2</x:t>
         </x:is>
       </x:c>
       <x:c r="F49" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-USER-006, SYS-USER-010, SYS-USER-013, SYS-USER-015, SYS-PERM-029</x:t>
+          <x:t xml:space="preserve">SYS-ORG-001, SYS-ORG-003, SYS-ORG-013, SYS-ORG-023</x:t>
         </x:is>
       </x:c>
       <x:c r="G49" s="2" t="inlineStr">
@@ -17246,32 +17646,32 @@
     <x:row r="50">
       <x:c r="A50" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.23.8</x:t>
+          <x:t xml:space="preserve">REQ_F4118.22.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B50" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to reset a password and unlock a locked user.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to edit or deactivate a department.</x:t>
         </x:is>
       </x:c>
       <x:c r="C50" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.82</x:t>
+          <x:t xml:space="preserve">REQ_DS43.22</x:t>
         </x:is>
       </x:c>
       <x:c r="D50" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.63</x:t>
+          <x:t xml:space="preserve">4.4.1.8.60</x:t>
         </x:is>
       </x:c>
       <x:c r="E50" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.63.4, REQ_IO_A8.63.5</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="F50" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-USER-006, SYS-USER-010, SYS-USER-014, SYS-PERM-029</x:t>
+          <x:t xml:space="preserve">SYS-ORG-005, SYS-ORG-007, SYS-ORG-009, SYS-ORG-023, SYS-ORG-026</x:t>
         </x:is>
       </x:c>
       <x:c r="G50" s="2" t="inlineStr">
@@ -17283,106 +17683,106 @@
     <x:row r="51">
       <x:c r="A51" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.24.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.23.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B51" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow a user to log in with username, password and a numeric captcha.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to create a unique user identity.</x:t>
         </x:is>
       </x:c>
       <x:c r="C51" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_DS43.82</x:t>
         </x:is>
       </x:c>
       <x:c r="D51" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.62</x:t>
+          <x:t xml:space="preserve">4.4.1.8.61</x:t>
         </x:is>
       </x:c>
       <x:c r="E51" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.62.1, REQ_IO_A8.62.2, REQ_IO_A8.62.3, REQ_IO_A8.62.4</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.61.1</x:t>
         </x:is>
       </x:c>
       <x:c r="F51" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-AUTH-001, SYS-AUTH-002, SYS-AUTH-005, SYS-AUTH-006, SYS-AUTH-009, SYS-AUTH-014, SYS-AUTH-015, SYS-AUTH-016, SYS-AUTH-017</x:t>
+          <x:t xml:space="preserve">SYS-ORG-027, SYS-USER-001, SYS-USER-004, SYS-USER-012</x:t>
         </x:is>
       </x:c>
       <x:c r="G51" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.24.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.23.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B52" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should issue a 15-minute access token and a 7-day rotating refresh token.</x:t>
+          <x:t xml:space="preserve">System should enforce a configurable password policy.</x:t>
         </x:is>
       </x:c>
       <x:c r="C52" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_DS43.82</x:t>
         </x:is>
       </x:c>
       <x:c r="D52" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">4.4.1.8.61</x:t>
         </x:is>
       </x:c>
       <x:c r="E52" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.61.2, REQ_IO_A8.61.3</x:t>
         </x:is>
       </x:c>
       <x:c r="F52" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-AUTH-001, SYS-AUTH-004, SYS-AUTH-007, SYS-AUTH-009, SYS-AUTH-010, SYS-AUTH-016, SYS-AUTH-017</x:t>
+          <x:t xml:space="preserve">SYS-USER-001, SYS-USER-007, SYS-USER-012</x:t>
         </x:is>
       </x:c>
       <x:c r="G52" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.24.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.23.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B53" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow a logged-in user to log out and invalidate the refresh token.</x:t>
+          <x:t xml:space="preserve">System should lock an account after five consecutive failed password attempts.</x:t>
         </x:is>
       </x:c>
       <x:c r="C53" s="2" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">REQ_DS43.82</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D53" s="2" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
-      <x:c r="D53" s="2" t="inlineStr">
+      <x:c r="E53" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
-      <x:c r="E53" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
       <x:c r="F53" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-AUTH-008, SYS-AUTH-016, SYS-AUTH-017</x:t>
+          <x:t xml:space="preserve">SYS-USER-002, SYS-USER-003, SYS-USER-005, SYS-USER-014</x:t>
         </x:is>
       </x:c>
       <x:c r="G53" s="2" t="inlineStr">
@@ -17394,32 +17794,32 @@
     <x:row r="54">
       <x:c r="A54" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.24.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.23.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B54" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should provide a development-only captcha master code with startup protection.</x:t>
+          <x:t xml:space="preserve">System should determine whether a user's password has expired.</x:t>
         </x:is>
       </x:c>
       <x:c r="C54" s="2" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">REQ_DS43.82</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D54" s="2" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
-      <x:c r="D54" s="2" t="inlineStr">
+      <x:c r="E54" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
-      <x:c r="E54" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
       <x:c r="F54" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-AUTH-003, SYS-AUTH-004, SYS-AUTH-016, SYS-AUTH-017</x:t>
+          <x:t xml:space="preserve">SYS-USER-003</x:t>
         </x:is>
       </x:c>
       <x:c r="G54" s="2" t="inlineStr">
@@ -17431,59 +17831,59 @@
     <x:row r="55">
       <x:c r="A55" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.24.5</x:t>
+          <x:t xml:space="preserve">REQ_F4118.23.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B55" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should provide a trilingual login page that keeps the session and refreshes tokens automatically.</x:t>
+          <x:t xml:space="preserve">System should list the users of the current company with paging, keyword and sorting.</x:t>
         </x:is>
       </x:c>
       <x:c r="C55" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_DS43.82, REQ_DS43.92</x:t>
         </x:is>
       </x:c>
       <x:c r="D55" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.62</x:t>
+          <x:t xml:space="preserve">4.4.1.8.63</x:t>
         </x:is>
       </x:c>
       <x:c r="E55" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.62.5, REQ_IO_A8.62.6</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.63.1, REQ_IO_A8.63.2</x:t>
         </x:is>
       </x:c>
       <x:c r="F55" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-AUTH-011, SYS-AUTH-012, SYS-AUTH-013, SYS-AUTH-015, SYS-AUTH-016, SYS-AUTH-017</x:t>
+          <x:t xml:space="preserve">SYS-USER-006, SYS-USER-010, SYS-USER-011, SYS-USER-015</x:t>
         </x:is>
       </x:c>
       <x:c r="G55" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="56">
       <x:c r="A56" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.25.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.23.6</x:t>
         </x:is>
       </x:c>
       <x:c r="B56" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to view roles and the permission catalog.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to create a user in the current company.</x:t>
         </x:is>
       </x:c>
       <x:c r="C56" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.90</x:t>
+          <x:t xml:space="preserve">REQ_DS43.82, REQ_DS43.92</x:t>
         </x:is>
       </x:c>
       <x:c r="D56" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.64</x:t>
+          <x:t xml:space="preserve">4.4.1.8.61</x:t>
         </x:is>
       </x:c>
       <x:c r="E56" s="2" t="inlineStr">
@@ -17493,7 +17893,7 @@
       </x:c>
       <x:c r="F56" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-ORG-027, SYS-PERM-004, SYS-PERM-011, SYS-PERM-024, SYS-PERM-025</x:t>
+          <x:t xml:space="preserve">SYS-USER-006, SYS-USER-010, SYS-USER-011, SYS-USER-012</x:t>
         </x:is>
       </x:c>
       <x:c r="G56" s="2" t="inlineStr">
@@ -17505,32 +17905,32 @@
     <x:row r="57">
       <x:c r="A57" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.25.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.23.7</x:t>
         </x:is>
       </x:c>
       <x:c r="B57" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to create a role with permissions and a data scope.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to activate or deactivate a user.</x:t>
         </x:is>
       </x:c>
       <x:c r="C57" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.90, REQ_DS43.91</x:t>
+          <x:t xml:space="preserve">REQ_DS43.82</x:t>
         </x:is>
       </x:c>
       <x:c r="D57" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.64</x:t>
+          <x:t xml:space="preserve">4.4.1.8.63</x:t>
         </x:is>
       </x:c>
       <x:c r="E57" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.64.1, REQ_IO_A8.64.2, REQ_IO_A8.64.3, REQ_IO_A8.64.4, REQ_IO_A8.64.5</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.63.3</x:t>
         </x:is>
       </x:c>
       <x:c r="F57" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-PERM-011, SYS-PERM-024, SYS-PERM-025</x:t>
+          <x:t xml:space="preserve">SYS-USER-006, SYS-USER-010, SYS-USER-013, SYS-USER-015, SYS-PERM-029</x:t>
         </x:is>
       </x:c>
       <x:c r="G57" s="2" t="inlineStr">
@@ -17542,32 +17942,32 @@
     <x:row r="58">
       <x:c r="A58" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.25.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.23.8</x:t>
         </x:is>
       </x:c>
       <x:c r="B58" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to edit or deactivate a role.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to reset a password and unlock a locked user.</x:t>
         </x:is>
       </x:c>
       <x:c r="C58" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.90, REQ_DS43.91</x:t>
+          <x:t xml:space="preserve">REQ_DS43.82</x:t>
         </x:is>
       </x:c>
       <x:c r="D58" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.64</x:t>
+          <x:t xml:space="preserve">4.4.1.8.63</x:t>
         </x:is>
       </x:c>
       <x:c r="E58" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.64.2, REQ_IO_A8.64.5</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.63.4, REQ_IO_A8.63.5</x:t>
         </x:is>
       </x:c>
       <x:c r="F58" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-PERM-011, SYS-PERM-024, SYS-PERM-025, SYS-PERM-031, SYS-PERM-032</x:t>
+          <x:t xml:space="preserve">SYS-USER-006, SYS-USER-010, SYS-USER-014, SYS-PERM-029</x:t>
         </x:is>
       </x:c>
       <x:c r="G58" s="2" t="inlineStr">
@@ -17579,54 +17979,54 @@
     <x:row r="59">
       <x:c r="A59" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.25.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.24.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B59" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to delete an unused role.</x:t>
+          <x:t xml:space="preserve">System should allow a user to log in with username, password and a numeric captcha.</x:t>
         </x:is>
       </x:c>
       <x:c r="C59" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.90</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="D59" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.64</x:t>
+          <x:t xml:space="preserve">4.4.1.8.62</x:t>
         </x:is>
       </x:c>
       <x:c r="E59" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.64.6</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.62.1, REQ_IO_A8.62.2, REQ_IO_A8.62.3, REQ_IO_A8.62.4</x:t>
         </x:is>
       </x:c>
       <x:c r="F59" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-PERM-012, SYS-PERM-024, SYS-PERM-025</x:t>
+          <x:t xml:space="preserve">SYS-AUTH-001, SYS-AUTH-002, SYS-AUTH-005, SYS-AUTH-006, SYS-AUTH-009, SYS-AUTH-014, SYS-AUTH-015, SYS-AUTH-016, SYS-AUTH-017</x:t>
         </x:is>
       </x:c>
       <x:c r="G59" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Covered</x:t>
+          <x:t xml:space="preserve">Partial</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="60">
       <x:c r="A60" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.25.5</x:t>
+          <x:t xml:space="preserve">REQ_F4118.24.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B60" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enforce permission codes on every API with the backend as the authority.</x:t>
+          <x:t xml:space="preserve">System should issue a 15-minute access token and a 7-day rotating refresh token.</x:t>
         </x:is>
       </x:c>
       <x:c r="C60" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.92</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="D60" s="2" t="inlineStr">
@@ -17641,7 +18041,7 @@
       </x:c>
       <x:c r="F60" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-PERM-001, SYS-PERM-005, SYS-PERM-006, SYS-PERM-010</x:t>
+          <x:t xml:space="preserve">SYS-AUTH-001, SYS-AUTH-004, SYS-AUTH-007, SYS-AUTH-009, SYS-AUTH-010, SYS-AUTH-016, SYS-AUTH-017</x:t>
         </x:is>
       </x:c>
       <x:c r="G60" s="2" t="inlineStr">
@@ -17653,54 +18053,54 @@
     <x:row r="61">
       <x:c r="A61" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.25.6</x:t>
+          <x:t xml:space="preserve">REQ_F4118.24.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B61" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to grant a user access to a company with roles, organization and default company.</x:t>
+          <x:t xml:space="preserve">System should allow a logged-in user to log out and invalidate the refresh token.</x:t>
         </x:is>
       </x:c>
       <x:c r="C61" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.92, REQ_DS43.93</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="D61" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.65</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="E61" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.65.1, REQ_IO_A8.65.2, REQ_IO_A8.65.3, REQ_IO_A8.65.4, REQ_IO_A8.65.5</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="F61" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-PERM-015, SYS-PERM-016, SYS-PERM-017, SYS-PERM-018, SYS-PERM-026, SYS-PERM-027, SYS-PERM-028</x:t>
+          <x:t xml:space="preserve">SYS-AUTH-008, SYS-AUTH-016, SYS-AUTH-017</x:t>
         </x:is>
       </x:c>
       <x:c r="G61" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Covered</x:t>
+          <x:t xml:space="preserve">Partial</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="62">
       <x:c r="A62" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.25.7</x:t>
+          <x:t xml:space="preserve">REQ_F4118.24.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B62" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should resolve the user's effective permissions and data scope per company and hide unauthorized UI.</x:t>
+          <x:t xml:space="preserve">System should provide a development-only captcha master code with startup protection.</x:t>
         </x:is>
       </x:c>
       <x:c r="C62" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.91, REQ_DS43.92, REQ_DS43.93</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="D62" s="2" t="inlineStr">
@@ -17715,7 +18115,7 @@
       </x:c>
       <x:c r="F62" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-PERM-002, SYS-PERM-003, SYS-PERM-013, SYS-PERM-014, SYS-PERM-020, SYS-PERM-021, SYS-PERM-022, SYS-PERM-023</x:t>
+          <x:t xml:space="preserve">SYS-AUTH-003, SYS-AUTH-004, SYS-AUTH-016, SYS-AUTH-017</x:t>
         </x:is>
       </x:c>
       <x:c r="G62" s="2" t="inlineStr">
@@ -17727,217 +18127,217 @@
     <x:row r="63">
       <x:c r="A63" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.25.8</x:t>
+          <x:t xml:space="preserve">REQ_F4118.24.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B63" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to view a user's company access, organization and roles.</x:t>
+          <x:t xml:space="preserve">System should provide a trilingual login page that keeps the session and refreshes tokens automatically.</x:t>
         </x:is>
       </x:c>
       <x:c r="C63" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.92, REQ_DS43.93</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="D63" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.65</x:t>
+          <x:t xml:space="preserve">4.4.1.8.62</x:t>
         </x:is>
       </x:c>
       <x:c r="E63" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.65.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.62.5, REQ_IO_A8.62.6</x:t>
         </x:is>
       </x:c>
       <x:c r="F63" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-PERM-017, SYS-PERM-018, SYS-PERM-026, SYS-PERM-027</x:t>
+          <x:t xml:space="preserve">SYS-AUTH-011, SYS-AUTH-012, SYS-AUTH-013, SYS-AUTH-015, SYS-AUTH-016, SYS-AUTH-017</x:t>
         </x:is>
       </x:c>
       <x:c r="G63" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Covered</x:t>
+          <x:t xml:space="preserve">Partial</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="64">
       <x:c r="A64" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.26.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.25.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B64" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enforce HTTPS with HSTS outside the development environment.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to view roles and the permission catalog.</x:t>
         </x:is>
       </x:c>
       <x:c r="C64" s="2" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">REQ_DS43.90</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D64" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.64</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E64" s="2" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
-      <x:c r="D64" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="E64" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
       <x:c r="F64" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-SEC-004</x:t>
+          <x:t xml:space="preserve">SYS-ORG-027, SYS-PERM-004, SYS-PERM-011, SYS-PERM-024, SYS-PERM-025</x:t>
         </x:is>
       </x:c>
       <x:c r="G64" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="65">
       <x:c r="A65" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.26.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.25.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B65" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow cross-origin requests only from configured frontend origins.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to create a role with permissions and a data scope.</x:t>
         </x:is>
       </x:c>
       <x:c r="C65" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_DS43.90, REQ_DS43.91</x:t>
         </x:is>
       </x:c>
       <x:c r="D65" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">4.4.1.8.64</x:t>
         </x:is>
       </x:c>
       <x:c r="E65" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.64.1, REQ_IO_A8.64.2, REQ_IO_A8.64.3, REQ_IO_A8.64.4, REQ_IO_A8.64.5</x:t>
         </x:is>
       </x:c>
       <x:c r="F65" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-SEC-002, SYS-SEC-003, SYS-SEC-006</x:t>
+          <x:t xml:space="preserve">SYS-PERM-011, SYS-PERM-024, SYS-PERM-025</x:t>
         </x:is>
       </x:c>
       <x:c r="G65" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="66">
       <x:c r="A66" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.26.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.25.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B66" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should rate-limit login, token refresh and captcha requests per client IP.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to edit or deactivate a role.</x:t>
         </x:is>
       </x:c>
       <x:c r="C66" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_DS43.90, REQ_DS43.91</x:t>
         </x:is>
       </x:c>
       <x:c r="D66" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">4.4.1.8.64</x:t>
         </x:is>
       </x:c>
       <x:c r="E66" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.64.2, REQ_IO_A8.64.5</x:t>
         </x:is>
       </x:c>
       <x:c r="F66" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-SEC-003, SYS-SEC-005, SYS-SEC-006, SYS-SEC-007, SYS-SEC-011, SYS-SEC-012</x:t>
+          <x:t xml:space="preserve">SYS-PERM-011, SYS-PERM-024, SYS-PERM-025, SYS-PERM-031, SYS-PERM-032</x:t>
         </x:is>
       </x:c>
       <x:c r="G66" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.26.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.25.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B67" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should rate-limit authenticated API requests per user.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to delete an unused role.</x:t>
         </x:is>
       </x:c>
       <x:c r="C67" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_DS43.90</x:t>
         </x:is>
       </x:c>
       <x:c r="D67" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">4.4.1.8.64</x:t>
         </x:is>
       </x:c>
       <x:c r="E67" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.64.6</x:t>
         </x:is>
       </x:c>
       <x:c r="F67" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-SEC-010</x:t>
+          <x:t xml:space="preserve">SYS-PERM-012, SYS-PERM-024, SYS-PERM-025</x:t>
         </x:is>
       </x:c>
       <x:c r="G67" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.26.5</x:t>
+          <x:t xml:space="preserve">REQ_F4118.25.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B68" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should add security headers to every API response.</x:t>
+          <x:t xml:space="preserve">System should enforce permission codes on every API with the backend as the authority.</x:t>
         </x:is>
       </x:c>
       <x:c r="C68" s="2" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">REQ_DS43.92</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D68" s="2" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
-      <x:c r="D68" s="2" t="inlineStr">
+      <x:c r="E68" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
-      <x:c r="E68" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
       <x:c r="F68" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-SEC-001, SYS-SEC-014</x:t>
+          <x:t xml:space="preserve">SYS-PERM-001, SYS-PERM-005, SYS-PERM-006, SYS-PERM-010</x:t>
         </x:is>
       </x:c>
       <x:c r="G68" s="2" t="inlineStr">
@@ -17949,69 +18349,69 @@
     <x:row r="69">
       <x:c r="A69" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.26.6</x:t>
+          <x:t xml:space="preserve">REQ_F4118.25.6</x:t>
         </x:is>
       </x:c>
       <x:c r="B69" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should honour X-Forwarded-For only from configured proxies.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to grant a user access to a company with roles, organization and default company.</x:t>
         </x:is>
       </x:c>
       <x:c r="C69" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_DS43.92, REQ_DS43.93</x:t>
         </x:is>
       </x:c>
       <x:c r="D69" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">4.4.1.8.65</x:t>
         </x:is>
       </x:c>
       <x:c r="E69" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.65.1, REQ_IO_A8.65.2, REQ_IO_A8.65.3, REQ_IO_A8.65.4, REQ_IO_A8.65.5</x:t>
         </x:is>
       </x:c>
       <x:c r="F69" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-SEC-003, SYS-SEC-008, SYS-SEC-009</x:t>
+          <x:t xml:space="preserve">SYS-PERM-015, SYS-PERM-016, SYS-PERM-017, SYS-PERM-018, SYS-PERM-026, SYS-PERM-027, SYS-PERM-028</x:t>
         </x:is>
       </x:c>
       <x:c r="G69" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="70">
       <x:c r="A70" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.26.7</x:t>
+          <x:t xml:space="preserve">REQ_F4118.25.7</x:t>
         </x:is>
       </x:c>
       <x:c r="B70" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should show a trilingual "too many requests" message when an API call is rate-limited.</x:t>
+          <x:t xml:space="preserve">System should resolve the user's effective permissions and data scope per company and hide unauthorized UI.</x:t>
         </x:is>
       </x:c>
       <x:c r="C70" s="2" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">REQ_DS43.91, REQ_DS43.92, REQ_DS43.93</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D70" s="2" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
-      <x:c r="D70" s="2" t="inlineStr">
+      <x:c r="E70" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
-      <x:c r="E70" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
       <x:c r="F70" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-SEC-013, SYS-SEC-014</x:t>
+          <x:t xml:space="preserve">SYS-PERM-002, SYS-PERM-003, SYS-PERM-013, SYS-PERM-014, SYS-PERM-020, SYS-PERM-021, SYS-PERM-022, SYS-PERM-023</x:t>
         </x:is>
       </x:c>
       <x:c r="G70" s="2" t="inlineStr">
@@ -18023,54 +18423,54 @@
     <x:row r="71">
       <x:c r="A71" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.27.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.25.8</x:t>
         </x:is>
       </x:c>
       <x:c r="B71" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should record every data change in sys_audit_log within the same transaction.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to view a user's company access, organization and roles.</x:t>
         </x:is>
       </x:c>
       <x:c r="C71" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.94</x:t>
+          <x:t xml:space="preserve">REQ_DS43.92, REQ_DS43.93</x:t>
         </x:is>
       </x:c>
       <x:c r="D71" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">4.4.1.8.65</x:t>
         </x:is>
       </x:c>
       <x:c r="E71" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.65.1</x:t>
         </x:is>
       </x:c>
       <x:c r="F71" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-AUDIT-001, SYS-AUDIT-002, SYS-AUDIT-003, SYS-AUDIT-004, SYS-AUDIT-005, SYS-AUDIT-006, SYS-AUDIT-010</x:t>
+          <x:t xml:space="preserve">SYS-PERM-017, SYS-PERM-018, SYS-PERM-026, SYS-PERM-027</x:t>
         </x:is>
       </x:c>
       <x:c r="G71" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="72">
       <x:c r="A72" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.27.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.26.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B72" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should protect audit records and sensitive values.</x:t>
+          <x:t xml:space="preserve">System should enforce HTTPS with HSTS outside the development environment.</x:t>
         </x:is>
       </x:c>
       <x:c r="C72" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.94</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="D72" s="2" t="inlineStr">
@@ -18080,34 +18480,34 @@
       </x:c>
       <x:c r="E72" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.66.5</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="F72" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-AUDIT-003, SYS-AUDIT-008, SYS-AUDIT-011</x:t>
+          <x:t xml:space="preserve">SYS-SEC-004</x:t>
         </x:is>
       </x:c>
       <x:c r="G72" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Covered</x:t>
+          <x:t xml:space="preserve">Partial</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="73">
       <x:c r="A73" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.27.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.26.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B73" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should record login, failed login, logout and captcha master-code login as security events.</x:t>
+          <x:t xml:space="preserve">System should allow cross-origin requests only from configured frontend origins.</x:t>
         </x:is>
       </x:c>
       <x:c r="C73" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.94</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="D73" s="2" t="inlineStr">
@@ -18122,7 +18522,7 @@
       </x:c>
       <x:c r="F73" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-AUDIT-007, SYS-AUDIT-012</x:t>
+          <x:t xml:space="preserve">SYS-SEC-002, SYS-SEC-003, SYS-SEC-006</x:t>
         </x:is>
       </x:c>
       <x:c r="G73" s="2" t="inlineStr">
@@ -18134,54 +18534,54 @@
     <x:row r="74">
       <x:c r="A74" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.27.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.26.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B74" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to query audit logs of the current company.</x:t>
+          <x:t xml:space="preserve">System should rate-limit login, token refresh and captcha requests per client IP.</x:t>
         </x:is>
       </x:c>
       <x:c r="C74" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.94</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="D74" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.66</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="E74" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.66.1</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="F74" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-AUDIT-009, SYS-AUDIT-010</x:t>
+          <x:t xml:space="preserve">SYS-SEC-003, SYS-SEC-005, SYS-SEC-006, SYS-SEC-007, SYS-SEC-011, SYS-SEC-012</x:t>
         </x:is>
       </x:c>
       <x:c r="G74" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Covered</x:t>
+          <x:t xml:space="preserve">Partial</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="75">
       <x:c r="A75" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.27.5</x:t>
+          <x:t xml:space="preserve">REQ_F4118.26.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B75" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should record role permission and user company access changes as security events.</x:t>
+          <x:t xml:space="preserve">System should rate-limit authenticated API requests per user.</x:t>
         </x:is>
       </x:c>
       <x:c r="C75" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.94</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="D75" s="2" t="inlineStr">
@@ -18196,7 +18596,7 @@
       </x:c>
       <x:c r="F75" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-AUDIT-013</x:t>
+          <x:t xml:space="preserve">SYS-SEC-010</x:t>
         </x:is>
       </x:c>
       <x:c r="G75" s="2" t="inlineStr">
@@ -18208,59 +18608,59 @@
     <x:row r="76">
       <x:c r="A76" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.27.6</x:t>
+          <x:t xml:space="preserve">REQ_F4118.26.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B76" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should provide a trilingual audit log page with per-record change history.</x:t>
+          <x:t xml:space="preserve">System should add security headers to every API response.</x:t>
         </x:is>
       </x:c>
       <x:c r="C76" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.94</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="D76" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.66</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="E76" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.66.1, REQ_IO_A8.66.2, REQ_IO_A8.66.3, REQ_IO_A8.66.4, REQ_IO_A8.66.5, REQ_IO_A8.66.6</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="F76" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-AUDIT-014</x:t>
+          <x:t xml:space="preserve">SYS-SEC-001, SYS-SEC-014</x:t>
         </x:is>
       </x:c>
       <x:c r="G76" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Covered</x:t>
+          <x:t xml:space="preserve">Partial</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="77">
       <x:c r="A77" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.28.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.26.6</x:t>
         </x:is>
       </x:c>
       <x:c r="B77" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow user to view document number rules of the current company.</x:t>
+          <x:t xml:space="preserve">System should honour X-Forwarded-For only from configured proxies.</x:t>
         </x:is>
       </x:c>
       <x:c r="C77" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.95</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="D77" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.67</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="E77" s="2" t="inlineStr">
@@ -18270,118 +18670,118 @@
       </x:c>
       <x:c r="F77" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-NUM-006, SYS-NUM-008, SYS-NUM-010</x:t>
+          <x:t xml:space="preserve">SYS-SEC-003, SYS-SEC-008, SYS-SEC-009</x:t>
         </x:is>
       </x:c>
       <x:c r="G77" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Covered</x:t>
+          <x:t xml:space="preserve">Partial</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="78">
       <x:c r="A78" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.28.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.26.7</x:t>
         </x:is>
       </x:c>
       <x:c r="B78" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow user to create a document number rule with prefix, date format, sequence length and reset period.</x:t>
+          <x:t xml:space="preserve">System should show a trilingual "too many requests" message when an API call is rate-limited.</x:t>
         </x:is>
       </x:c>
       <x:c r="C78" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.95</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="D78" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.67</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="E78" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.67.1, REQ_IO_A8.67.2, REQ_IO_A8.67.3, REQ_IO_A8.67.4, REQ_IO_A8.67.5, REQ_IO_A8.67.6</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="F78" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-NUM-006, SYS-NUM-007, SYS-NUM-008, SYS-NUM-010, SYS-NUM-011</x:t>
+          <x:t xml:space="preserve">SYS-SEC-013, SYS-SEC-014</x:t>
         </x:is>
       </x:c>
       <x:c r="G78" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Covered</x:t>
+          <x:t xml:space="preserve">Partial</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="79">
       <x:c r="A79" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.28.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.27.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B79" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow user to edit or deactivate a document number rule without breaking issued numbers.</x:t>
+          <x:t xml:space="preserve">System should record every data change in sys_audit_log within the same transaction.</x:t>
         </x:is>
       </x:c>
       <x:c r="C79" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.95, REQ_DS43.96</x:t>
+          <x:t xml:space="preserve">REQ_DS43.94</x:t>
         </x:is>
       </x:c>
       <x:c r="D79" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.67</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="E79" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.67.2, REQ_IO_A8.67.3, REQ_IO_A8.67.4, REQ_IO_A8.67.5, REQ_IO_A8.67.6, REQ_IO_A8.67.8</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="F79" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-NUM-006, SYS-NUM-008, SYS-NUM-009, SYS-NUM-010, SYS-NUM-011</x:t>
+          <x:t xml:space="preserve">SYS-AUDIT-001, SYS-AUDIT-002, SYS-AUDIT-003, SYS-AUDIT-004, SYS-AUDIT-005, SYS-AUDIT-006, SYS-AUDIT-010</x:t>
         </x:is>
       </x:c>
       <x:c r="G79" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Covered</x:t>
+          <x:t xml:space="preserve">Partial</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="80">
       <x:c r="A80" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.28.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.27.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B80" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow user to preview the next document number for a business date.</x:t>
+          <x:t xml:space="preserve">System should protect audit records and sensitive values.</x:t>
         </x:is>
       </x:c>
       <x:c r="C80" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.95, REQ_DS43.96</x:t>
+          <x:t xml:space="preserve">REQ_DS43.94</x:t>
         </x:is>
       </x:c>
       <x:c r="D80" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.67</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="E80" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.67.9</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.66.5</x:t>
         </x:is>
       </x:c>
       <x:c r="F80" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-NUM-006, SYS-NUM-008, SYS-NUM-010, SYS-NUM-011</x:t>
+          <x:t xml:space="preserve">SYS-AUDIT-003, SYS-AUDIT-008, SYS-AUDIT-011</x:t>
         </x:is>
       </x:c>
       <x:c r="G80" s="2" t="inlineStr">
@@ -18393,17 +18793,17 @@
     <x:row r="81">
       <x:c r="A81" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.28.5</x:t>
+          <x:t xml:space="preserve">REQ_F4118.27.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B81" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should generate unique, gap-free document numbers for every module under concurrency.</x:t>
+          <x:t xml:space="preserve">System should record login, failed login, logout and captcha master-code login as security events.</x:t>
         </x:is>
       </x:c>
       <x:c r="C81" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.95, REQ_DS43.96</x:t>
+          <x:t xml:space="preserve">REQ_DS43.94</x:t>
         </x:is>
       </x:c>
       <x:c r="D81" s="2" t="inlineStr">
@@ -18418,7 +18818,7 @@
       </x:c>
       <x:c r="F81" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-NUM-001, SYS-NUM-002, SYS-NUM-003, SYS-NUM-004, SYS-NUM-005, SYS-NUM-009</x:t>
+          <x:t xml:space="preserve">SYS-AUDIT-007, SYS-AUDIT-012</x:t>
         </x:is>
       </x:c>
       <x:c r="G81" s="2" t="inlineStr">
@@ -18430,32 +18830,32 @@
     <x:row r="82">
       <x:c r="A82" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.28.6</x:t>
+          <x:t xml:space="preserve">REQ_F4118.27.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B82" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should provide a trilingual number rule maintenance page.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to query audit logs of the current company.</x:t>
         </x:is>
       </x:c>
       <x:c r="C82" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.95</x:t>
+          <x:t xml:space="preserve">REQ_DS43.94</x:t>
         </x:is>
       </x:c>
       <x:c r="D82" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.67</x:t>
+          <x:t xml:space="preserve">4.4.1.8.66</x:t>
         </x:is>
       </x:c>
       <x:c r="E82" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.67.1, REQ_IO_A8.67.7</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.66.1</x:t>
         </x:is>
       </x:c>
       <x:c r="F82" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-NUM-010, SYS-NUM-011</x:t>
+          <x:t xml:space="preserve">SYS-AUDIT-009, SYS-AUDIT-010</x:t>
         </x:is>
       </x:c>
       <x:c r="G82" s="2" t="inlineStr">
@@ -18467,69 +18867,69 @@
     <x:row r="83">
       <x:c r="A83" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.29.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.27.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B83" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow user to view and create multi-level approval flows with amount thresholds.</x:t>
+          <x:t xml:space="preserve">System should record role permission and user company access changes as security events.</x:t>
         </x:is>
       </x:c>
       <x:c r="C83" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.97, REQ_DS43.98</x:t>
+          <x:t xml:space="preserve">REQ_DS43.94</x:t>
         </x:is>
       </x:c>
       <x:c r="D83" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.68</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="E83" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.68.1, REQ_IO_A8.68.2, REQ_IO_A8.68.3, REQ_IO_A8.68.4, REQ_IO_A8.68.5, REQ_IO_A8.68.6, REQ_IO_A8.68.7</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="F83" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-APR-008, SYS-APR-010, SYS-APR-012, SYS-APR-013</x:t>
+          <x:t xml:space="preserve">SYS-AUDIT-013</x:t>
         </x:is>
       </x:c>
       <x:c r="G83" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Covered</x:t>
+          <x:t xml:space="preserve">Partial</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="84">
       <x:c r="A84" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.29.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.27.6</x:t>
         </x:is>
       </x:c>
       <x:c r="B84" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow user to edit or deactivate an approval flow without affecting pending approvals.</x:t>
+          <x:t xml:space="preserve">System should provide a trilingual audit log page with per-record change history.</x:t>
         </x:is>
       </x:c>
       <x:c r="C84" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.97, REQ_DS43.98</x:t>
+          <x:t xml:space="preserve">REQ_DS43.94</x:t>
         </x:is>
       </x:c>
       <x:c r="D84" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.68</x:t>
+          <x:t xml:space="preserve">4.4.1.8.66</x:t>
         </x:is>
       </x:c>
       <x:c r="E84" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.68.2, REQ_IO_A8.68.3, REQ_IO_A8.68.8</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.66.1, REQ_IO_A8.66.2, REQ_IO_A8.66.3, REQ_IO_A8.66.4, REQ_IO_A8.66.5, REQ_IO_A8.66.6</x:t>
         </x:is>
       </x:c>
       <x:c r="F84" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-APR-003, SYS-APR-008, SYS-APR-010, SYS-APR-012, SYS-APR-013</x:t>
+          <x:t xml:space="preserve">SYS-AUDIT-014</x:t>
         </x:is>
       </x:c>
       <x:c r="G84" s="2" t="inlineStr">
@@ -18541,32 +18941,32 @@
     <x:row r="85">
       <x:c r="A85" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.29.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.28.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B85" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow user to assign an approval delegate for a date range.</x:t>
+          <x:t xml:space="preserve">System should allow user to view document number rules of the current company.</x:t>
         </x:is>
       </x:c>
       <x:c r="C85" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.99</x:t>
+          <x:t xml:space="preserve">REQ_DS43.95</x:t>
         </x:is>
       </x:c>
       <x:c r="D85" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.69</x:t>
+          <x:t xml:space="preserve">4.4.1.8.67</x:t>
         </x:is>
       </x:c>
       <x:c r="E85" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.69.1, REQ_IO_A8.69.2, REQ_IO_A8.69.3, REQ_IO_A8.69.4</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="F85" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-APR-005, SYS-APR-010, SYS-APR-012, SYS-APR-013</x:t>
+          <x:t xml:space="preserve">SYS-NUM-006, SYS-NUM-008, SYS-NUM-010</x:t>
         </x:is>
       </x:c>
       <x:c r="G85" s="2" t="inlineStr">
@@ -18578,69 +18978,69 @@
     <x:row r="86">
       <x:c r="A86" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.29.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.28.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B86" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable every module to submit documents for approval through the shared workflow engine.</x:t>
+          <x:t xml:space="preserve">System should allow user to create a document number rule with prefix, date format, sequence length and reset period.</x:t>
         </x:is>
       </x:c>
       <x:c r="C86" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.97, REQ_DS43.98, REQ_DS43.100, REQ_DS43.101</x:t>
+          <x:t xml:space="preserve">REQ_DS43.95</x:t>
         </x:is>
       </x:c>
       <x:c r="D86" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">4.4.1.8.67</x:t>
         </x:is>
       </x:c>
       <x:c r="E86" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.67.1, REQ_IO_A8.67.2, REQ_IO_A8.67.3, REQ_IO_A8.67.4, REQ_IO_A8.67.5, REQ_IO_A8.67.6</x:t>
         </x:is>
       </x:c>
       <x:c r="F86" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-APR-001, SYS-APR-002, SYS-APR-003, SYS-APR-007, SYS-APR-011</x:t>
+          <x:t xml:space="preserve">SYS-NUM-006, SYS-NUM-007, SYS-NUM-008, SYS-NUM-010, SYS-NUM-011</x:t>
         </x:is>
       </x:c>
       <x:c r="G86" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="87">
       <x:c r="A87" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.29.5</x:t>
+          <x:t xml:space="preserve">REQ_F4118.28.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B87" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow approvers or their delegates to approve or reject the current approval step.</x:t>
+          <x:t xml:space="preserve">System should allow user to edit or deactivate a document number rule without breaking issued numbers.</x:t>
         </x:is>
       </x:c>
       <x:c r="C87" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.99, REQ_DS43.100, REQ_DS43.101</x:t>
+          <x:t xml:space="preserve">REQ_DS43.95, REQ_DS43.96</x:t>
         </x:is>
       </x:c>
       <x:c r="D87" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.70</x:t>
+          <x:t xml:space="preserve">4.4.1.8.67</x:t>
         </x:is>
       </x:c>
       <x:c r="E87" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.70.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.67.2, REQ_IO_A8.67.3, REQ_IO_A8.67.4, REQ_IO_A8.67.5, REQ_IO_A8.67.6, REQ_IO_A8.67.8</x:t>
         </x:is>
       </x:c>
       <x:c r="F87" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-APR-001, SYS-APR-002, SYS-APR-004, SYS-APR-005, SYS-APR-006, SYS-APR-007, SYS-APR-011, SYS-APR-012, SYS-APR-013</x:t>
+          <x:t xml:space="preserve">SYS-NUM-006, SYS-NUM-008, SYS-NUM-009, SYS-NUM-010, SYS-NUM-011</x:t>
         </x:is>
       </x:c>
       <x:c r="G87" s="2" t="inlineStr">
@@ -18652,32 +19052,32 @@
     <x:row r="88">
       <x:c r="A88" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.29.6</x:t>
+          <x:t xml:space="preserve">REQ_F4118.28.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B88" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should list the pending approval tasks of the current user.</x:t>
+          <x:t xml:space="preserve">System should allow user to preview the next document number for a business date.</x:t>
         </x:is>
       </x:c>
       <x:c r="C88" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.99, REQ_DS43.100, REQ_DS43.101</x:t>
+          <x:t xml:space="preserve">REQ_DS43.95, REQ_DS43.96</x:t>
         </x:is>
       </x:c>
       <x:c r="D88" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.70</x:t>
+          <x:t xml:space="preserve">4.4.1.8.67</x:t>
         </x:is>
       </x:c>
       <x:c r="E88" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.67.9</x:t>
         </x:is>
       </x:c>
       <x:c r="F88" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-APR-004, SYS-APR-005, SYS-APR-011, SYS-APR-012, SYS-APR-013</x:t>
+          <x:t xml:space="preserve">SYS-NUM-006, SYS-NUM-008, SYS-NUM-010, SYS-NUM-011</x:t>
         </x:is>
       </x:c>
       <x:c r="G88" s="2" t="inlineStr">
@@ -18689,69 +19089,69 @@
     <x:row r="89">
       <x:c r="A89" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.29.7</x:t>
+          <x:t xml:space="preserve">REQ_F4118.28.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B89" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow user to view the approval history of a document.</x:t>
+          <x:t xml:space="preserve">System should generate unique, gap-free document numbers for every module under concurrency.</x:t>
         </x:is>
       </x:c>
       <x:c r="C89" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.100, REQ_DS43.101</x:t>
+          <x:t xml:space="preserve">REQ_DS43.95, REQ_DS43.96</x:t>
         </x:is>
       </x:c>
       <x:c r="D89" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.70</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="E89" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.70.2</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="F89" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-APR-001, SYS-APR-002, SYS-APR-008, SYS-APR-011, SYS-APR-012, SYS-APR-013</x:t>
+          <x:t xml:space="preserve">SYS-NUM-001, SYS-NUM-002, SYS-NUM-003, SYS-NUM-004, SYS-NUM-005, SYS-NUM-009</x:t>
         </x:is>
       </x:c>
       <x:c r="G89" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Covered</x:t>
+          <x:t xml:space="preserve">Partial</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="90">
       <x:c r="A90" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.29.8</x:t>
+          <x:t xml:space="preserve">REQ_F4118.28.6</x:t>
         </x:is>
       </x:c>
       <x:c r="B90" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should provide trilingual approval flow and delegation maintenance pages.</x:t>
+          <x:t xml:space="preserve">System should provide a trilingual number rule maintenance page.</x:t>
         </x:is>
       </x:c>
       <x:c r="C90" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.97, REQ_DS43.98, REQ_DS43.99</x:t>
+          <x:t xml:space="preserve">REQ_DS43.95</x:t>
         </x:is>
       </x:c>
       <x:c r="D90" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.68, 4.4.1.8.69</x:t>
+          <x:t xml:space="preserve">4.4.1.8.67</x:t>
         </x:is>
       </x:c>
       <x:c r="E90" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.68.1, REQ_IO_A8.68.4, REQ_IO_A8.68.5, REQ_IO_A8.68.6, REQ_IO_A8.68.7</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.67.1, REQ_IO_A8.67.7</x:t>
         </x:is>
       </x:c>
       <x:c r="F90" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-APR-012, SYS-APR-013</x:t>
+          <x:t xml:space="preserve">SYS-NUM-010, SYS-NUM-011</x:t>
         </x:is>
       </x:c>
       <x:c r="G90" s="2" t="inlineStr">
@@ -18763,32 +19163,32 @@
     <x:row r="91">
       <x:c r="A91" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.29.9</x:t>
+          <x:t xml:space="preserve">REQ_F4118.29.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B91" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should provide a trilingual approval inbox with approval history.</x:t>
+          <x:t xml:space="preserve">System should allow user to view and create multi-level approval flows with amount thresholds.</x:t>
         </x:is>
       </x:c>
       <x:c r="C91" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.100, REQ_DS43.101</x:t>
+          <x:t xml:space="preserve">REQ_DS43.97, REQ_DS43.98</x:t>
         </x:is>
       </x:c>
       <x:c r="D91" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.70</x:t>
+          <x:t xml:space="preserve">4.4.1.8.68</x:t>
         </x:is>
       </x:c>
       <x:c r="E91" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.70.1, REQ_IO_A8.70.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.68.1, REQ_IO_A8.68.2, REQ_IO_A8.68.3, REQ_IO_A8.68.4, REQ_IO_A8.68.5, REQ_IO_A8.68.6, REQ_IO_A8.68.7</x:t>
         </x:is>
       </x:c>
       <x:c r="F91" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-APR-012, SYS-APR-013</x:t>
+          <x:t xml:space="preserve">SYS-APR-008, SYS-APR-010, SYS-APR-012, SYS-APR-013</x:t>
         </x:is>
       </x:c>
       <x:c r="G91" s="2" t="inlineStr">
@@ -18800,91 +19200,91 @@
     <x:row r="92">
       <x:c r="A92" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.30.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.29.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B92" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should load demo companies, branches, departments and roles for the Development environment.</x:t>
+          <x:t xml:space="preserve">System should allow user to edit or deactivate an approval flow without affecting pending approvals.</x:t>
         </x:is>
       </x:c>
       <x:c r="C92" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.20, REQ_DS43.22, REQ_DS43.89, REQ_DS43.90, REQ_DS43.91</x:t>
+          <x:t xml:space="preserve">REQ_DS43.97, REQ_DS43.98</x:t>
         </x:is>
       </x:c>
       <x:c r="D92" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">4.4.1.8.68</x:t>
         </x:is>
       </x:c>
       <x:c r="E92" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.68.2, REQ_IO_A8.68.3, REQ_IO_A8.68.8</x:t>
         </x:is>
       </x:c>
       <x:c r="F92" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-SEED-001, SYS-SEED-002, SYS-SEED-003, SYS-SEED-006</x:t>
+          <x:t xml:space="preserve">SYS-APR-003, SYS-APR-008, SYS-APR-010, SYS-APR-012, SYS-APR-013</x:t>
         </x:is>
       </x:c>
       <x:c r="G92" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="93">
       <x:c r="A93" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.30.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.29.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B93" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should create the test accounts of the SeedUsers setting with hashed passwords and company assignments.</x:t>
+          <x:t xml:space="preserve">System should allow user to assign an approval delegate for a date range.</x:t>
         </x:is>
       </x:c>
       <x:c r="C93" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.82, REQ_DS43.92, REQ_DS43.93</x:t>
+          <x:t xml:space="preserve">REQ_DS43.99</x:t>
         </x:is>
       </x:c>
       <x:c r="D93" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">4.4.1.8.69</x:t>
         </x:is>
       </x:c>
       <x:c r="E93" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.69.1, REQ_IO_A8.69.2, REQ_IO_A8.69.3, REQ_IO_A8.69.4</x:t>
         </x:is>
       </x:c>
       <x:c r="F93" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-SEED-001, SYS-SEED-005</x:t>
+          <x:t xml:space="preserve">SYS-APR-005, SYS-APR-010, SYS-APR-012, SYS-APR-013</x:t>
         </x:is>
       </x:c>
       <x:c r="G93" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="94">
       <x:c r="A94" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.30.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.29.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B94" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow the seed to run repeatedly without duplicating or overwriting data.</x:t>
+          <x:t xml:space="preserve">System should enable every module to submit documents for approval through the shared workflow engine.</x:t>
         </x:is>
       </x:c>
       <x:c r="C94" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.20, REQ_DS43.82, REQ_DS43.91</x:t>
+          <x:t xml:space="preserve">REQ_DS43.97, REQ_DS43.98, REQ_DS43.100, REQ_DS43.101</x:t>
         </x:is>
       </x:c>
       <x:c r="D94" s="2" t="inlineStr">
@@ -18899,7 +19299,7 @@
       </x:c>
       <x:c r="F94" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-SEED-001, SYS-SEED-003, SYS-SEED-004</x:t>
+          <x:t xml:space="preserve">SYS-APR-001, SYS-APR-002, SYS-APR-003, SYS-APR-007, SYS-APR-011</x:t>
         </x:is>
       </x:c>
       <x:c r="G94" s="2" t="inlineStr">
@@ -18911,217 +19311,217 @@
     <x:row r="95">
       <x:c r="A95" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.31.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.29.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B95" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should ask for confirmation in a shared trilingual confirmation box before dangerous actions.</x:t>
+          <x:t xml:space="preserve">System should allow approvers or their delegates to approve or reject the current approval step.</x:t>
         </x:is>
       </x:c>
       <x:c r="C95" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_DS43.99, REQ_DS43.100, REQ_DS43.101</x:t>
         </x:is>
       </x:c>
       <x:c r="D95" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.71</x:t>
+          <x:t xml:space="preserve">4.4.1.8.70</x:t>
         </x:is>
       </x:c>
       <x:c r="E95" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.71.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.70.1</x:t>
         </x:is>
       </x:c>
       <x:c r="F95" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-UI-001, SYS-UI-002, SYS-UI-003</x:t>
+          <x:t xml:space="preserve">SYS-APR-001, SYS-APR-002, SYS-APR-004, SYS-APR-005, SYS-APR-006, SYS-APR-007, SYS-APR-011, SYS-APR-012, SYS-APR-013</x:t>
         </x:is>
       </x:c>
       <x:c r="G95" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="96">
       <x:c r="A96" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.31.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.29.6</x:t>
         </x:is>
       </x:c>
       <x:c r="B96" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should show results that need the user's attention in a shared prompt box, and short success messages as toasts.</x:t>
+          <x:t xml:space="preserve">System should list the pending approval tasks of the current user.</x:t>
         </x:is>
       </x:c>
       <x:c r="C96" s="2" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">REQ_DS43.99, REQ_DS43.100, REQ_DS43.101</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D96" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.70</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E96" s="2" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
-      <x:c r="D96" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">4.4.1.8.71</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E96" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.71.1</x:t>
-        </x:is>
-      </x:c>
       <x:c r="F96" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-UI-001</x:t>
+          <x:t xml:space="preserve">SYS-APR-004, SYS-APR-005, SYS-APR-011, SYS-APR-012, SYS-APR-013</x:t>
         </x:is>
       </x:c>
       <x:c r="G96" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="97">
       <x:c r="A97" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.31.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.29.7</x:t>
         </x:is>
       </x:c>
       <x:c r="B97" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should provide a shared selection window for choosing master data with search and server-side paging.</x:t>
+          <x:t xml:space="preserve">System should allow user to view the approval history of a document.</x:t>
         </x:is>
       </x:c>
       <x:c r="C97" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_DS43.100, REQ_DS43.101</x:t>
         </x:is>
       </x:c>
       <x:c r="D97" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.72</x:t>
+          <x:t xml:space="preserve">4.4.1.8.70</x:t>
         </x:is>
       </x:c>
       <x:c r="E97" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.72.1, REQ_IO_A8.72.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.70.2</x:t>
         </x:is>
       </x:c>
       <x:c r="F97" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-UI-001</x:t>
+          <x:t xml:space="preserve">SYS-APR-001, SYS-APR-002, SYS-APR-008, SYS-APR-011, SYS-APR-012, SYS-APR-013</x:t>
         </x:is>
       </x:c>
       <x:c r="G97" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="98">
       <x:c r="A98" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.31.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.29.8</x:t>
         </x:is>
       </x:c>
       <x:c r="B98" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should provide a standard list page template reused by every module.</x:t>
+          <x:t xml:space="preserve">System should provide trilingual approval flow and delegation maintenance pages.</x:t>
         </x:is>
       </x:c>
       <x:c r="C98" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_DS43.97, REQ_DS43.98, REQ_DS43.99</x:t>
         </x:is>
       </x:c>
       <x:c r="D98" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.73</x:t>
+          <x:t xml:space="preserve">4.4.1.8.68, 4.4.1.8.69</x:t>
         </x:is>
       </x:c>
       <x:c r="E98" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.73.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.68.1, REQ_IO_A8.68.4, REQ_IO_A8.68.5, REQ_IO_A8.68.6, REQ_IO_A8.68.7</x:t>
         </x:is>
       </x:c>
       <x:c r="F98" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-UI-001, SYS-UI-002</x:t>
+          <x:t xml:space="preserve">SYS-APR-012, SYS-APR-013</x:t>
         </x:is>
       </x:c>
       <x:c r="G98" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="99">
       <x:c r="A99" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.31.5</x:t>
+          <x:t xml:space="preserve">REQ_F4118.29.9</x:t>
         </x:is>
       </x:c>
       <x:c r="B99" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should provide a standard document page template with status, previous / next navigation and unsaved-change protection.</x:t>
+          <x:t xml:space="preserve">System should provide a trilingual approval inbox with approval history.</x:t>
         </x:is>
       </x:c>
       <x:c r="C99" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_DS43.100, REQ_DS43.101</x:t>
         </x:is>
       </x:c>
       <x:c r="D99" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.74</x:t>
+          <x:t xml:space="preserve">4.4.1.8.70</x:t>
         </x:is>
       </x:c>
       <x:c r="E99" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.74.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.70.1, REQ_IO_A8.70.2</x:t>
         </x:is>
       </x:c>
       <x:c r="F99" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-UI-001</x:t>
+          <x:t xml:space="preserve">SYS-APR-012, SYS-APR-013</x:t>
         </x:is>
       </x:c>
       <x:c r="G99" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="100">
       <x:c r="A100" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.31.6</x:t>
+          <x:t xml:space="preserve">REQ_F4118.30.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B100" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should provide a date range filter with quick ranges and a document status tag following the macaron status colours.</x:t>
+          <x:t xml:space="preserve">System should load demo companies, branches, departments and roles for the Development environment.</x:t>
         </x:is>
       </x:c>
       <x:c r="C100" s="2" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">REQ_DS43.20, REQ_DS43.22, REQ_DS43.89, REQ_DS43.90, REQ_DS43.91</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D100" s="2" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
-      <x:c r="D100" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">4.4.1.8.73, 4.4.1.8.74</x:t>
-        </x:is>
-      </x:c>
       <x:c r="E100" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.73.1</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="F100" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-UI-001</x:t>
+          <x:t xml:space="preserve">SYS-SEED-001, SYS-SEED-002, SYS-SEED-003, SYS-SEED-006</x:t>
         </x:is>
       </x:c>
       <x:c r="G100" s="2" t="inlineStr">
@@ -19133,143 +19533,143 @@
     <x:row r="101">
       <x:c r="A101" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.32.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.30.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B101" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to view IP whitelist rules.</x:t>
+          <x:t xml:space="preserve">System should create the test accounts of the SeedUsers setting with hashed passwords and company assignments.</x:t>
         </x:is>
       </x:c>
       <x:c r="C101" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.102</x:t>
+          <x:t xml:space="preserve">REQ_DS43.82, REQ_DS43.92, REQ_DS43.93</x:t>
         </x:is>
       </x:c>
       <x:c r="D101" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.75</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="E101" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.75.1</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="F101" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-IPW-004, SYS-IPW-009</x:t>
+          <x:t xml:space="preserve">SYS-SEED-001, SYS-SEED-005</x:t>
         </x:is>
       </x:c>
       <x:c r="G101" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Covered</x:t>
+          <x:t xml:space="preserve">Partial</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="102">
       <x:c r="A102" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.32.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.30.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B102" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to create and deactivate IP whitelist rules.</x:t>
+          <x:t xml:space="preserve">System should allow the seed to run repeatedly without duplicating or overwriting data.</x:t>
         </x:is>
       </x:c>
       <x:c r="C102" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.102</x:t>
+          <x:t xml:space="preserve">REQ_DS43.20, REQ_DS43.82, REQ_DS43.91</x:t>
         </x:is>
       </x:c>
       <x:c r="D102" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.75</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="E102" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.75.2, REQ_IO_A8.75.3, REQ_IO_A8.75.5, REQ_IO_A8.75.6, REQ_IO_A8.75.7</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="F102" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-PERM-032, SYS-IPW-004, SYS-IPW-005, SYS-IPW-008, SYS-IPW-009</x:t>
+          <x:t xml:space="preserve">SYS-SEED-001, SYS-SEED-003, SYS-SEED-004</x:t>
         </x:is>
       </x:c>
       <x:c r="G102" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Covered</x:t>
+          <x:t xml:space="preserve">Partial</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="103">
       <x:c r="A103" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.32.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.31.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B103" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow single IPv4 or IPv6 addresses and CIDR networks in system, role or user scope.</x:t>
+          <x:t xml:space="preserve">System should ask for confirmation in a shared trilingual confirmation box before dangerous actions.</x:t>
         </x:is>
       </x:c>
       <x:c r="C103" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.102</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="D103" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.75</x:t>
+          <x:t xml:space="preserve">4.4.1.8.71</x:t>
         </x:is>
       </x:c>
       <x:c r="E103" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.75.4</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.71.1</x:t>
         </x:is>
       </x:c>
       <x:c r="F103" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-IPW-001, SYS-IPW-002, SYS-IPW-005, SYS-IPW-006</x:t>
+          <x:t xml:space="preserve">SYS-UI-001, SYS-UI-002, SYS-UI-003</x:t>
         </x:is>
       </x:c>
       <x:c r="G103" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Covered</x:t>
+          <x:t xml:space="preserve">Partial</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="104">
       <x:c r="A104" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.32.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.31.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B104" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should reject disallowed requests and audit each rejection.</x:t>
+          <x:t xml:space="preserve">System should show results that need the user's attention in a shared prompt box, and short success messages as toasts.</x:t>
         </x:is>
       </x:c>
       <x:c r="C104" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.102</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="D104" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">4.4.1.8.71</x:t>
         </x:is>
       </x:c>
       <x:c r="E104" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.71.1</x:t>
         </x:is>
       </x:c>
       <x:c r="F104" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-IPW-003, SYS-IPW-006</x:t>
+          <x:t xml:space="preserve">SYS-UI-001</x:t>
         </x:is>
       </x:c>
       <x:c r="G104" s="2" t="inlineStr">
@@ -19281,12 +19681,12 @@
     <x:row r="105">
       <x:c r="A105" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.32.5</x:t>
+          <x:t xml:space="preserve">REQ_F4118.31.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B105" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow operators to disable IP filtering through server configuration.</x:t>
+          <x:t xml:space="preserve">System should provide a shared selection window for choosing master data with search and server-side paging.</x:t>
         </x:is>
       </x:c>
       <x:c r="C105" s="2" t="inlineStr">
@@ -19296,17 +19696,17 @@
       </x:c>
       <x:c r="D105" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">4.4.1.8.72</x:t>
         </x:is>
       </x:c>
       <x:c r="E105" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.72.1, REQ_IO_A8.72.2</x:t>
         </x:is>
       </x:c>
       <x:c r="F105" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-IPW-006</x:t>
+          <x:t xml:space="preserve">SYS-UI-001</x:t>
         </x:is>
       </x:c>
       <x:c r="G105" s="2" t="inlineStr">
@@ -19318,12 +19718,12 @@
     <x:row r="106">
       <x:c r="A106" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.32.6</x:t>
+          <x:t xml:space="preserve">REQ_F4118.31.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B106" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should provide a trilingual IP whitelist maintenance page.</x:t>
+          <x:t xml:space="preserve">System should provide a standard list page template reused by every module.</x:t>
         </x:is>
       </x:c>
       <x:c r="C106" s="2" t="inlineStr">
@@ -19333,17 +19733,17 @@
       </x:c>
       <x:c r="D106" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.75</x:t>
+          <x:t xml:space="preserve">4.4.1.8.73</x:t>
         </x:is>
       </x:c>
       <x:c r="E106" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.75.1, REQ_IO_A8.75.2, REQ_IO_A8.75.3, REQ_IO_A8.75.4, REQ_IO_A8.75.5, REQ_IO_A8.75.6, REQ_IO_A8.75.7</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.73.2</x:t>
         </x:is>
       </x:c>
       <x:c r="F106" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-IPW-007</x:t>
+          <x:t xml:space="preserve">SYS-UI-001, SYS-UI-002</x:t>
         </x:is>
       </x:c>
       <x:c r="G106" s="2" t="inlineStr">
@@ -19355,32 +19755,32 @@
     <x:row r="107">
       <x:c r="A107" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.33.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.31.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B107" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable modules to publish notifications to a user.</x:t>
+          <x:t xml:space="preserve">System should provide a standard document page template with status, previous / next navigation and unsaved-change protection.</x:t>
         </x:is>
       </x:c>
       <x:c r="C107" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.104</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="D107" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">4.4.1.8.74</x:t>
         </x:is>
       </x:c>
       <x:c r="E107" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.74.1</x:t>
         </x:is>
       </x:c>
       <x:c r="F107" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-NOTIFY-001, SYS-NOTIFY-002, SYS-NOTIFY-003</x:t>
+          <x:t xml:space="preserve">SYS-UI-001</x:t>
         </x:is>
       </x:c>
       <x:c r="G107" s="2" t="inlineStr">
@@ -19392,69 +19792,69 @@
     <x:row r="108">
       <x:c r="A108" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.33.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.31.6</x:t>
         </x:is>
       </x:c>
       <x:c r="B108" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to view notifications.</x:t>
+          <x:t xml:space="preserve">System should provide a date range filter with quick ranges and a document status tag following the macaron status colours.</x:t>
         </x:is>
       </x:c>
       <x:c r="C108" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.104</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="D108" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.76</x:t>
+          <x:t xml:space="preserve">4.4.1.8.73, 4.4.1.8.74</x:t>
         </x:is>
       </x:c>
       <x:c r="E108" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.76.1, REQ_IO_A8.76.2, REQ_IO_A8.76.3, REQ_IO_A8.76.6</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.73.1</x:t>
         </x:is>
       </x:c>
       <x:c r="F108" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-NOTIFY-004, SYS-NOTIFY-005, SYS-NOTIFY-006, SYS-NOTIFY-007</x:t>
+          <x:t xml:space="preserve">SYS-UI-001</x:t>
         </x:is>
       </x:c>
       <x:c r="G108" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Covered</x:t>
+          <x:t xml:space="preserve">Partial</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="109">
       <x:c r="A109" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.33.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.32.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B109" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to mark notifications as read.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to view IP whitelist rules.</x:t>
         </x:is>
       </x:c>
       <x:c r="C109" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.104</x:t>
+          <x:t xml:space="preserve">REQ_DS43.102</x:t>
         </x:is>
       </x:c>
       <x:c r="D109" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.76</x:t>
+          <x:t xml:space="preserve">4.4.1.8.75</x:t>
         </x:is>
       </x:c>
       <x:c r="E109" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.76.4, REQ_IO_A8.76.5</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.75.1</x:t>
         </x:is>
       </x:c>
       <x:c r="F109" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-NOTIFY-004, SYS-NOTIFY-005, SYS-NOTIFY-006, SYS-NOTIFY-007</x:t>
+          <x:t xml:space="preserve">SYS-IPW-004, SYS-IPW-009</x:t>
         </x:is>
       </x:c>
       <x:c r="G109" s="2" t="inlineStr">
@@ -19466,35 +19866,331 @@
     <x:row r="110">
       <x:c r="A110" s="2" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">REQ_F4118.32.2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B110" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow authorized users to create and deactivate IP whitelist rules.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C110" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.102</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D110" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.75</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E110" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.75.2, REQ_IO_A8.75.3, REQ_IO_A8.75.5, REQ_IO_A8.75.6, REQ_IO_A8.75.7</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F110" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-PERM-032, SYS-IPW-004, SYS-IPW-005, SYS-IPW-008, SYS-IPW-009</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G110" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Covered</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="111">
+      <x:c r="A111" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.32.3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B111" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow single IPv4 or IPv6 addresses and CIDR networks in system, role or user scope.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C111" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.102</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D111" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.75</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E111" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.75.4</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F111" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-IPW-001, SYS-IPW-002, SYS-IPW-005, SYS-IPW-006</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G111" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Covered</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="112">
+      <x:c r="A112" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.32.4</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B112" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should reject disallowed requests and audit each rejection.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C112" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.102</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D112" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="E112" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F112" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-IPW-003, SYS-IPW-006</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G112" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Partial</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="113">
+      <x:c r="A113" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.32.5</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B113" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should allow operators to disable IP filtering through server configuration.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C113" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="D113" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="E113" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F113" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-IPW-006</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G113" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Partial</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="114">
+      <x:c r="A114" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.32.6</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B114" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should provide a trilingual IP whitelist maintenance page.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C114" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="D114" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.75</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E114" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.75.1, REQ_IO_A8.75.2, REQ_IO_A8.75.3, REQ_IO_A8.75.4, REQ_IO_A8.75.5, REQ_IO_A8.75.6, REQ_IO_A8.75.7</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F114" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-IPW-007</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G114" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Partial</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="115">
+      <x:c r="A115" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.33.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B115" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should enable modules to publish notifications to a user.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C115" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.104</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D115" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="E115" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F115" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-NOTIFY-001, SYS-NOTIFY-002, SYS-NOTIFY-003</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G115" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Partial</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="116">
+      <x:c r="A116" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.33.2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B116" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should enable user to view notifications.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C116" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.104</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D116" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.76</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E116" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.76.1, REQ_IO_A8.76.2, REQ_IO_A8.76.3, REQ_IO_A8.76.6</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F116" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-NOTIFY-004, SYS-NOTIFY-005, SYS-NOTIFY-006, SYS-NOTIFY-007</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G116" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Covered</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="117">
+      <x:c r="A117" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.33.3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B117" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should enable user to mark notifications as read.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C117" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.104</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D117" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.76</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E117" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.76.4, REQ_IO_A8.76.5</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F117" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-NOTIFY-004, SYS-NOTIFY-005, SYS-NOTIFY-006, SYS-NOTIFY-007</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G117" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Covered</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="118">
+      <x:c r="A118" s="2" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">REQ_F4118.34.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="B110" s="2" t="inlineStr">
+      <x:c r="B118" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">System should allow authorized users to view the master data portal.</x:t>
         </x:is>
       </x:c>
-      <x:c r="C110" s="2" t="inlineStr">
+      <x:c r="C118" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
-      <x:c r="D110" s="2" t="inlineStr">
+      <x:c r="D118" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
-      <x:c r="E110" s="2" t="inlineStr">
+      <x:c r="E118" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
-      <x:c r="F110" s="2" t="inlineStr">
+      <x:c r="F118" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
-      <x:c r="G110" s="2" t="inlineStr">
+      <x:c r="G118" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Not covered</x:t>
         </x:is>
@@ -25655,7 +26351,7 @@
       </x:c>
       <x:c r="F192" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">未開始</x:t>
+          <x:t xml:space="preserve">進行中</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -25687,7 +26383,7 @@
       </x:c>
       <x:c r="F193" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">未開始</x:t>
+          <x:t xml:space="preserve">進行中</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -25719,7 +26415,7 @@
       </x:c>
       <x:c r="F194" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">未開始</x:t>
+          <x:t xml:space="preserve">進行中</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -25751,7 +26447,7 @@
       </x:c>
       <x:c r="F195" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">未開始</x:t>
+          <x:t xml:space="preserve">進行中</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -25783,7 +26479,7 @@
       </x:c>
       <x:c r="F196" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">未開始</x:t>
+          <x:t xml:space="preserve">進行中</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -25815,7 +26511,7 @@
       </x:c>
       <x:c r="F197" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">未開始</x:t>
+          <x:t xml:space="preserve">進行中</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -25847,7 +26543,7 @@
       </x:c>
       <x:c r="F198" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">未開始</x:t>
+          <x:t xml:space="preserve">進行中</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -25879,7 +26575,7 @@
       </x:c>
       <x:c r="F199" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">未開始</x:t>
+          <x:t xml:space="preserve">進行中</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -31543,7 +32239,7 @@
       </x:c>
       <x:c r="F376" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">未開始</x:t>
+          <x:t xml:space="preserve">進行中</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -32855,7 +33551,7 @@
       </x:c>
       <x:c r="F417" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">未開始</x:t>
+          <x:t xml:space="preserve">進行中</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -33111,7 +33807,7 @@
       </x:c>
       <x:c r="F425" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">未開始</x:t>
+          <x:t xml:space="preserve">進行中</x:t>
         </x:is>
       </x:c>
     </x:row>

--- a/docs/99-output/MyERP_Requirements.xlsx
+++ b/docs/99-output/MyERP_Requirements.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="1" r:id="Rb2b65739982c45a7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Non-Functional" sheetId="2" r:id="Rdb394ae0acfc4077"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Structure" sheetId="3" r:id="R1e84137b65e94d87"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interface" sheetId="4" r:id="Refe5e5295e9a4d5e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traceability Matrix" sheetId="5" r:id="R6cc28b6ded364017"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BlueWhale Parity" sheetId="6" r:id="R07e1148bcf8841d7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timeline" sheetId="7" r:id="R694e7a05ec494884"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Human Resources" sheetId="8" r:id="Rbef0760bd6b74b7c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="9" r:id="R91755afcdef04e9f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="1" r:id="R6acb67cfdf9841cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Non-Functional" sheetId="2" r:id="R5ee178f522c348e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Structure" sheetId="3" r:id="Ra46848f0742c4e7e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interface" sheetId="4" r:id="R40cb58c45a254efb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traceability Matrix" sheetId="5" r:id="R1e7cba6250544ebb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BlueWhale Parity" sheetId="6" r:id="R1644876a9dbe457b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timeline" sheetId="7" r:id="Rd983a65e2d2041d3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Human Resources" sheetId="8" r:id="R9d51d44899e34677"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="9" r:id="R05dbace492b446ba"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -9319,17 +9319,17 @@
     <x:row r="43">
       <x:c r="A43" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.45.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.36.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B43" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.45</x:t>
+          <x:t xml:space="preserve">4.4.1.8.36</x:t>
         </x:is>
       </x:c>
       <x:c r="C43" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Unit of Measurement View Interface</x:t>
+          <x:t xml:space="preserve">Item Category View Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D43" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </x:c>
       <x:c r="E43" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">代碼或名稱關鍵字。</x:t>
+          <x:t xml:space="preserve">依代碼或名稱過濾分類樹，保留命中節點的上層。</x:t>
         </x:is>
       </x:c>
       <x:c r="F43" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">縮小目前公司單位列表。</x:t>
+          <x:t xml:space="preserve">找到分類。</x:t>
         </x:is>
       </x:c>
       <x:c r="G43" s="2" t="inlineStr">
@@ -9359,7 +9359,7 @@
       </x:c>
       <x:c r="I43" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.45.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.36.2</x:t>
         </x:is>
       </x:c>
       <x:c r="J43" s="2" t="inlineStr">
@@ -9376,32 +9376,32 @@
     <x:row r="44">
       <x:c r="A44" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.45.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.36.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B44" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.45</x:t>
+          <x:t xml:space="preserve">4.4.1.8.36</x:t>
         </x:is>
       </x:c>
       <x:c r="C44" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Unit of Measurement View Interface</x:t>
+          <x:t xml:space="preserve">Item Category View Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D44" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Unit List (Table)</x:t>
+          <x:t xml:space="preserve">Category Tree (Table)</x:t>
         </x:is>
       </x:c>
       <x:c r="E44" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">代碼、名稱、小數位數、狀態及編輯／刪除操作；代碼與名稱可排序，伺服器分頁。</x:t>
+          <x:t xml:space="preserve">代碼（按層級縮排）、名稱、狀態及新增子分類／編輯／刪除操作。</x:t>
         </x:is>
       </x:c>
       <x:c r="F44" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">查看單位。</x:t>
+          <x:t xml:space="preserve">檢視分類階層。</x:t>
         </x:is>
       </x:c>
       <x:c r="G44" s="2" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </x:c>
       <x:c r="H44" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">每頁 10／20／50／100／200</x:t>
+          <x:t xml:space="preserve">全部未刪除分類，最多 5 層</x:t>
         </x:is>
       </x:c>
       <x:c r="I44" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.46.1, REQ_IO_A8.47.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.37.1, REQ_IO_A8.38.1</x:t>
         </x:is>
       </x:c>
       <x:c r="J44" s="2" t="inlineStr">
@@ -9433,47 +9433,47 @@
     <x:row r="45">
       <x:c r="A45" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.45.3</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.36.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B45" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.45</x:t>
+          <x:t xml:space="preserve">4.4.1.8.36</x:t>
         </x:is>
       </x:c>
       <x:c r="C45" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Unit of Measurement View Interface</x:t>
+          <x:t xml:space="preserve">Item Category View Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D45" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Conversion List (Table)</x:t>
+          <x:t xml:space="preserve">Delete (Button)</x:t>
         </x:is>
       </x:c>
       <x:c r="E45" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">來源、目標、換算規則及編輯／刪除操作。</x:t>
+          <x:t xml:space="preserve">二次確認後按版本軟刪除；有子分類時顯示錯誤。</x:t>
         </x:is>
       </x:c>
       <x:c r="F45" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">查看換算。</x:t>
+          <x:t xml:space="preserve">移除未使用的分類。</x:t>
         </x:is>
       </x:c>
       <x:c r="G45" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Table</x:t>
+          <x:t xml:space="preserve">Button</x:t>
         </x:is>
       </x:c>
       <x:c r="H45" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">全部換算</x:t>
+          <x:t xml:space="preserve">DELETE 權限</x:t>
         </x:is>
       </x:c>
       <x:c r="I45" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.46.4</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.36.2</x:t>
         </x:is>
       </x:c>
       <x:c r="J45" s="2" t="inlineStr">
@@ -9490,47 +9490,47 @@
     <x:row r="46">
       <x:c r="A46" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.45.4</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.37.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B46" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.45</x:t>
+          <x:t xml:space="preserve">4.4.1.8.37</x:t>
         </x:is>
       </x:c>
       <x:c r="C46" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Unit of Measurement View Interface</x:t>
+          <x:t xml:space="preserve">Item Category Create Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D46" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Calculator (Form)</x:t>
+          <x:t xml:space="preserve">Code (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E46" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">數量、來源單位、目標單位、換算按鈕與結果。</x:t>
+          <x:t xml:space="preserve">建立時填寫並轉大寫。</x:t>
         </x:is>
       </x:c>
       <x:c r="F46" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">試算換算結果。</x:t>
+          <x:t xml:space="preserve">公司內唯一識別。</x:t>
         </x:is>
       </x:c>
       <x:c r="G46" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Decimal</x:t>
+          <x:t xml:space="preserve">Text</x:t>
         </x:is>
       </x:c>
       <x:c r="H46" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">數量最多 12 位整數及 6 位小數</x:t>
+          <x:t xml:space="preserve">1–30 位英數、-、_</x:t>
         </x:is>
       </x:c>
       <x:c r="I46" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.45.3</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.36.2</x:t>
         </x:is>
       </x:c>
       <x:c r="J46" s="2" t="inlineStr">
@@ -9547,32 +9547,32 @@
     <x:row r="47">
       <x:c r="A47" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.46.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.37.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B47" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.46</x:t>
+          <x:t xml:space="preserve">4.4.1.8.37</x:t>
         </x:is>
       </x:c>
       <x:c r="C47" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Unit of Measurement Create Interface</x:t>
+          <x:t xml:space="preserve">Item Category Create Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D47" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Code (Input)</x:t>
+          <x:t xml:space="preserve">Name (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E47" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">建立時輸入並轉大寫。</x:t>
+          <x:t xml:space="preserve">分類名稱。</x:t>
         </x:is>
       </x:c>
       <x:c r="F47" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">公司內唯一識別。</x:t>
+          <x:t xml:space="preserve">向用戶顯示。</x:t>
         </x:is>
       </x:c>
       <x:c r="G47" s="2" t="inlineStr">
@@ -9582,12 +9582,12 @@
       </x:c>
       <x:c r="H47" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1–30 位英數、-、_</x:t>
+          <x:t xml:space="preserve">非空白，最多 200 字</x:t>
         </x:is>
       </x:c>
       <x:c r="I47" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.45.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.36.2</x:t>
         </x:is>
       </x:c>
       <x:c r="J47" s="2" t="inlineStr">
@@ -9604,47 +9604,47 @@
     <x:row r="48">
       <x:c r="A48" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.46.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.37.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B48" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.46</x:t>
+          <x:t xml:space="preserve">4.4.1.8.37</x:t>
         </x:is>
       </x:c>
       <x:c r="C48" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Unit of Measurement Create Interface</x:t>
+          <x:t xml:space="preserve">Item Category Create Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D48" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Name (Input)</x:t>
+          <x:t xml:space="preserve">Parent (Dropdown)</x:t>
         </x:is>
       </x:c>
       <x:c r="E48" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">單位名稱。</x:t>
+          <x:t xml:space="preserve">上層分類，可不選（最上層）；選項按層級縮排。</x:t>
         </x:is>
       </x:c>
       <x:c r="F48" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">顯示單位。</x:t>
+          <x:t xml:space="preserve">決定分類位置。</x:t>
         </x:is>
       </x:c>
       <x:c r="G48" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Text</x:t>
+          <x:t xml:space="preserve">Category ID</x:t>
         </x:is>
       </x:c>
       <x:c r="H48" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">非空白、最多 200 字</x:t>
+          <x:t xml:space="preserve">本公司啟用分類，新節點不超過第 5 層</x:t>
         </x:is>
       </x:c>
       <x:c r="I48" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.45.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.36.2</x:t>
         </x:is>
       </x:c>
       <x:c r="J48" s="2" t="inlineStr">
@@ -9661,47 +9661,47 @@
     <x:row r="49">
       <x:c r="A49" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.46.3</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.38.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B49" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.46</x:t>
+          <x:t xml:space="preserve">4.4.1.8.38</x:t>
         </x:is>
       </x:c>
       <x:c r="C49" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Unit of Measurement Create Interface</x:t>
+          <x:t xml:space="preserve">Item Category Edit Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D49" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Decimal Places (Dropdown)</x:t>
+          <x:t xml:space="preserve">Code (Label)</x:t>
         </x:is>
       </x:c>
       <x:c r="E49" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">數量小數位數。</x:t>
+          <x:t xml:space="preserve">編輯時只讀。</x:t>
         </x:is>
       </x:c>
       <x:c r="F49" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">換算結果捨入。</x:t>
+          <x:t xml:space="preserve">防止歷史引用變更識別。</x:t>
         </x:is>
       </x:c>
       <x:c r="G49" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Integer</x:t>
+          <x:t xml:space="preserve">Text</x:t>
         </x:is>
       </x:c>
       <x:c r="H49" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">0–6</x:t>
+          <x:t xml:space="preserve">最多 30 字</x:t>
         </x:is>
       </x:c>
       <x:c r="I49" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.45.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.36.2</x:t>
         </x:is>
       </x:c>
       <x:c r="J49" s="2" t="inlineStr">
@@ -9718,47 +9718,47 @@
     <x:row r="50">
       <x:c r="A50" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.46.4</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.38.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B50" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.46</x:t>
+          <x:t xml:space="preserve">4.4.1.8.38</x:t>
         </x:is>
       </x:c>
       <x:c r="C50" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Unit of Measurement Create Interface</x:t>
+          <x:t xml:space="preserve">Item Category Edit Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D50" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">From / To Unit (Dropdown)</x:t>
+          <x:t xml:space="preserve">Name / Active</x:t>
         </x:is>
       </x:c>
       <x:c r="E50" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">換算兩端單位；停用單位不可選，兩端不可相同。</x:t>
+          <x:t xml:space="preserve">修改名稱與啟用狀態。</x:t>
         </x:is>
       </x:c>
       <x:c r="F50" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">定義換算。</x:t>
+          <x:t xml:space="preserve">維護分類。</x:t>
         </x:is>
       </x:c>
       <x:c r="G50" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Unit ID</x:t>
+          <x:t xml:space="preserve">Text／Boolean</x:t>
         </x:is>
       </x:c>
       <x:c r="H50" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">本公司啟用單位</x:t>
+          <x:t xml:space="preserve">同建立</x:t>
         </x:is>
       </x:c>
       <x:c r="I50" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.45.3</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.36.2</x:t>
         </x:is>
       </x:c>
       <x:c r="J50" s="2" t="inlineStr">
@@ -9775,47 +9775,47 @@
     <x:row r="51">
       <x:c r="A51" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.46.5</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.38.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B51" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.46</x:t>
+          <x:t xml:space="preserve">4.4.1.8.38</x:t>
         </x:is>
       </x:c>
       <x:c r="C51" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Unit of Measurement Create Interface</x:t>
+          <x:t xml:space="preserve">Item Category Edit Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D51" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Factor (Input)</x:t>
+          <x:t xml:space="preserve">Parent (Dropdown)</x:t>
         </x:is>
       </x:c>
       <x:c r="E51" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1 來源 = 係數 目標。</x:t>
+          <x:t xml:space="preserve">搬移整棵子樹；排除自己與子孫。</x:t>
         </x:is>
       </x:c>
       <x:c r="F51" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">換算係數。</x:t>
+          <x:t xml:space="preserve">調整階層。</x:t>
         </x:is>
       </x:c>
       <x:c r="G51" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Decimal</x:t>
+          <x:t xml:space="preserve">Category ID</x:t>
         </x:is>
       </x:c>
       <x:c r="H51" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">大於 0，最多 9 位整數及 6 位小數</x:t>
+          <x:t xml:space="preserve">啟用分類或目前上層，搬移後不超過 5 層</x:t>
         </x:is>
       </x:c>
       <x:c r="I51" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.45.3</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.36.2</x:t>
         </x:is>
       </x:c>
       <x:c r="J51" s="2" t="inlineStr">
@@ -9832,32 +9832,32 @@
     <x:row r="52">
       <x:c r="A52" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.47.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.39.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B52" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.47</x:t>
+          <x:t xml:space="preserve">4.4.1.8.39</x:t>
         </x:is>
       </x:c>
       <x:c r="C52" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Unit of Measurement Edit Interface</x:t>
+          <x:t xml:space="preserve">Item Brand View Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D52" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Code (Label)</x:t>
+          <x:t xml:space="preserve">Search (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E52" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">編輯時唯讀。</x:t>
+          <x:t xml:space="preserve">依代碼或名稱搜尋目前公司品牌。</x:t>
         </x:is>
       </x:c>
       <x:c r="F52" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">保持歷史識別。</x:t>
+          <x:t xml:space="preserve">縮小列表。</x:t>
         </x:is>
       </x:c>
       <x:c r="G52" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </x:c>
       <x:c r="H52" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">最多 30 字</x:t>
+          <x:t xml:space="preserve">任意文字</x:t>
         </x:is>
       </x:c>
       <x:c r="I52" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.45.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.39.2</x:t>
         </x:is>
       </x:c>
       <x:c r="J52" s="2" t="inlineStr">
@@ -9889,47 +9889,47 @@
     <x:row r="53">
       <x:c r="A53" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.47.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.39.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B53" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.47</x:t>
+          <x:t xml:space="preserve">4.4.1.8.39</x:t>
         </x:is>
       </x:c>
       <x:c r="C53" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Unit of Measurement Edit Interface</x:t>
+          <x:t xml:space="preserve">Item Brand View Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D53" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Name / Decimal Places / Active</x:t>
+          <x:t xml:space="preserve">Brand List (Table)</x:t>
         </x:is>
       </x:c>
       <x:c r="E53" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">修改名稱、小數位數、啟用狀態。</x:t>
+          <x:t xml:space="preserve">代碼、名稱、啟用狀態，代碼及名稱可排序，伺服器分頁。</x:t>
         </x:is>
       </x:c>
       <x:c r="F53" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">維護單位。</x:t>
+          <x:t xml:space="preserve">檢視品牌。</x:t>
         </x:is>
       </x:c>
       <x:c r="G53" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Text／Integer／Boolean</x:t>
+          <x:t xml:space="preserve">Table</x:t>
         </x:is>
       </x:c>
       <x:c r="H53" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">同建立</x:t>
+          <x:t xml:space="preserve">每頁 10／20／50／100／200</x:t>
         </x:is>
       </x:c>
       <x:c r="I53" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.45.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.40.1, REQ_IO_A8.41.1</x:t>
         </x:is>
       </x:c>
       <x:c r="J53" s="2" t="inlineStr">
@@ -9946,47 +9946,47 @@
     <x:row r="54">
       <x:c r="A54" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.47.3</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.39.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B54" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.47</x:t>
+          <x:t xml:space="preserve">4.4.1.8.39</x:t>
         </x:is>
       </x:c>
       <x:c r="C54" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Unit of Measurement Edit Interface</x:t>
+          <x:t xml:space="preserve">Item Brand View Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D54" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Factor (Input)</x:t>
+          <x:t xml:space="preserve">Delete (Button)</x:t>
         </x:is>
       </x:c>
       <x:c r="E54" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">編輯換算時只可改係數。</x:t>
+          <x:t xml:space="preserve">二次確認後按版本軟刪除。</x:t>
         </x:is>
       </x:c>
       <x:c r="F54" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">修正換算。</x:t>
+          <x:t xml:space="preserve">移除未使用的品牌。</x:t>
         </x:is>
       </x:c>
       <x:c r="G54" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Decimal</x:t>
+          <x:t xml:space="preserve">Button</x:t>
         </x:is>
       </x:c>
       <x:c r="H54" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">同建立</x:t>
+          <x:t xml:space="preserve">DELETE 權限</x:t>
         </x:is>
       </x:c>
       <x:c r="I54" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.45.3</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.39.2</x:t>
         </x:is>
       </x:c>
       <x:c r="J54" s="2" t="inlineStr">
@@ -10003,47 +10003,47 @@
     <x:row r="55">
       <x:c r="A55" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.47.4</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.40.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B55" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.47</x:t>
+          <x:t xml:space="preserve">4.4.1.8.40</x:t>
         </x:is>
       </x:c>
       <x:c r="C55" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Unit of Measurement Edit Interface</x:t>
+          <x:t xml:space="preserve">Item Brand Create Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D55" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Delete (Button)</x:t>
+          <x:t xml:space="preserve">Code (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E55" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">確認後帶版本刪除單位或換算；被引用單位顯示 IN_USE。</x:t>
+          <x:t xml:space="preserve">建立時填寫並轉大寫。</x:t>
         </x:is>
       </x:c>
       <x:c r="F55" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">移除錯誤資料。</x:t>
+          <x:t xml:space="preserve">公司內唯一識別。</x:t>
         </x:is>
       </x:c>
       <x:c r="G55" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Action</x:t>
+          <x:t xml:space="preserve">Text</x:t>
         </x:is>
       </x:c>
       <x:c r="H55" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">-</x:t>
+          <x:t xml:space="preserve">1–30 位英數、-、_</x:t>
         </x:is>
       </x:c>
       <x:c r="I55" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.45.2, REQ_IO_A8.45.3</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.39.2</x:t>
         </x:is>
       </x:c>
       <x:c r="J55" s="2" t="inlineStr">
@@ -10060,47 +10060,47 @@
     <x:row r="56">
       <x:c r="A56" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.55.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.40.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B56" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.55</x:t>
+          <x:t xml:space="preserve">4.4.1.8.40</x:t>
         </x:is>
       </x:c>
       <x:c r="C56" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Parameter Edit Interface</x:t>
+          <x:t xml:space="preserve">Item Brand Create Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D56" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Boolean Parameter (Switch)</x:t>
+          <x:t xml:space="preserve">Name (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E56" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">開關型參數</x:t>
+          <x:t xml:space="preserve">品牌名稱。</x:t>
         </x:is>
       </x:c>
       <x:c r="F56" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">啟用／停用功能</x:t>
+          <x:t xml:space="preserve">向用戶顯示。</x:t>
         </x:is>
       </x:c>
       <x:c r="G56" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">true／false</x:t>
+          <x:t xml:space="preserve">Text</x:t>
         </x:is>
       </x:c>
       <x:c r="H56" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">—</x:t>
+          <x:t xml:space="preserve">非空白，最多 200 字</x:t>
         </x:is>
       </x:c>
       <x:c r="I56" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">None</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.39.2</x:t>
         </x:is>
       </x:c>
       <x:c r="J56" s="2" t="inlineStr">
@@ -10117,47 +10117,47 @@
     <x:row r="57">
       <x:c r="A57" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.55.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.41.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B57" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.55</x:t>
+          <x:t xml:space="preserve">4.4.1.8.41</x:t>
         </x:is>
       </x:c>
       <x:c r="C57" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Parameter Edit Interface</x:t>
+          <x:t xml:space="preserve">Item Brand Edit Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D57" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Whole Number Parameter (Input)</x:t>
+          <x:t xml:space="preserve">Code (Label)</x:t>
         </x:is>
       </x:c>
       <x:c r="E57" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">整數參數</x:t>
+          <x:t xml:space="preserve">編輯時只讀。</x:t>
         </x:is>
       </x:c>
       <x:c r="F57" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">例如小數位數</x:t>
+          <x:t xml:space="preserve">防止歷史引用變更識別。</x:t>
         </x:is>
       </x:c>
       <x:c r="G57" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">整數字串</x:t>
+          <x:t xml:space="preserve">Text</x:t>
         </x:is>
       </x:c>
       <x:c r="H57" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">宣告的最小值至最大值</x:t>
+          <x:t xml:space="preserve">最多 30 字</x:t>
         </x:is>
       </x:c>
       <x:c r="I57" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">None</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.39.2</x:t>
         </x:is>
       </x:c>
       <x:c r="J57" s="2" t="inlineStr">
@@ -10174,47 +10174,47 @@
     <x:row r="58">
       <x:c r="A58" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.55.3</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.41.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B58" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.55</x:t>
+          <x:t xml:space="preserve">4.4.1.8.41</x:t>
         </x:is>
       </x:c>
       <x:c r="C58" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Parameter Edit Interface</x:t>
+          <x:t xml:space="preserve">Item Brand Edit Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D58" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Number Parameter (Input)</x:t>
+          <x:t xml:space="preserve">Name / Active</x:t>
         </x:is>
       </x:c>
       <x:c r="E58" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">十進位參數</x:t>
+          <x:t xml:space="preserve">修改名稱與啟用狀態。</x:t>
         </x:is>
       </x:c>
       <x:c r="F58" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">數值設定</x:t>
+          <x:t xml:space="preserve">維護品牌。</x:t>
         </x:is>
       </x:c>
       <x:c r="G58" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">十進位字串（不使用指數）</x:t>
+          <x:t xml:space="preserve">Text／Boolean</x:t>
         </x:is>
       </x:c>
       <x:c r="H58" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">宣告的範圍；精度由伺服器判斷</x:t>
+          <x:t xml:space="preserve">同建立</x:t>
         </x:is>
       </x:c>
       <x:c r="I58" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">None</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.39.2</x:t>
         </x:is>
       </x:c>
       <x:c r="J58" s="2" t="inlineStr">
@@ -10231,32 +10231,32 @@
     <x:row r="59">
       <x:c r="A59" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.55.4</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.45.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B59" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.55</x:t>
+          <x:t xml:space="preserve">4.4.1.8.45</x:t>
         </x:is>
       </x:c>
       <x:c r="C59" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Parameter Edit Interface</x:t>
+          <x:t xml:space="preserve">Unit of Measurement View Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D59" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Text Parameter (Input)</x:t>
+          <x:t xml:space="preserve">Search (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E59" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">文字參數</x:t>
+          <x:t xml:space="preserve">代碼或名稱關鍵字。</x:t>
         </x:is>
       </x:c>
       <x:c r="F59" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">名稱、備註等</x:t>
+          <x:t xml:space="preserve">縮小目前公司單位列表。</x:t>
         </x:is>
       </x:c>
       <x:c r="G59" s="2" t="inlineStr">
@@ -10266,12 +10266,12 @@
       </x:c>
       <x:c r="H59" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">宣告的長度上限</x:t>
+          <x:t xml:space="preserve">任意文字</x:t>
         </x:is>
       </x:c>
       <x:c r="I59" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">None</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.45.2</x:t>
         </x:is>
       </x:c>
       <x:c r="J59" s="2" t="inlineStr">
@@ -10288,47 +10288,47 @@
     <x:row r="60">
       <x:c r="A60" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.55.5</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.45.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B60" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.55</x:t>
+          <x:t xml:space="preserve">4.4.1.8.45</x:t>
         </x:is>
       </x:c>
       <x:c r="C60" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Parameter Edit Interface</x:t>
+          <x:t xml:space="preserve">Unit of Measurement View Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D60" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Option Parameter (Dropdown)</x:t>
+          <x:t xml:space="preserve">Unit List (Table)</x:t>
         </x:is>
       </x:c>
       <x:c r="E60" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">選項參數</x:t>
+          <x:t xml:space="preserve">代碼、名稱、小數位數、狀態及編輯／刪除操作；代碼與名稱可排序，伺服器分頁。</x:t>
         </x:is>
       </x:c>
       <x:c r="F60" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">從固定選項選擇</x:t>
+          <x:t xml:space="preserve">查看單位。</x:t>
         </x:is>
       </x:c>
       <x:c r="G60" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Enum</x:t>
+          <x:t xml:space="preserve">Table</x:t>
         </x:is>
       </x:c>
       <x:c r="H60" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">宣告的選項</x:t>
+          <x:t xml:space="preserve">每頁 10／20／50／100／200</x:t>
         </x:is>
       </x:c>
       <x:c r="I60" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">None</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.46.1, REQ_IO_A8.47.1</x:t>
         </x:is>
       </x:c>
       <x:c r="J60" s="2" t="inlineStr">
@@ -10345,47 +10345,47 @@
     <x:row r="61">
       <x:c r="A61" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.55.6</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.45.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B61" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.55</x:t>
+          <x:t xml:space="preserve">4.4.1.8.45</x:t>
         </x:is>
       </x:c>
       <x:c r="C61" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Parameter Edit Interface</x:t>
+          <x:t xml:space="preserve">Unit of Measurement View Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D61" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Restore Default (Button)</x:t>
+          <x:t xml:space="preserve">Conversion List (Table)</x:t>
         </x:is>
       </x:c>
       <x:c r="E61" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">恢復預設</x:t>
+          <x:t xml:space="preserve">來源、目標、換算規則及編輯／刪除操作。</x:t>
         </x:is>
       </x:c>
       <x:c r="F61" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">把欄位設回預設值</x:t>
+          <x:t xml:space="preserve">查看換算。</x:t>
         </x:is>
       </x:c>
       <x:c r="G61" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Button</x:t>
+          <x:t xml:space="preserve">Table</x:t>
         </x:is>
       </x:c>
       <x:c r="H61" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">需 EDIT；保存後才生效</x:t>
+          <x:t xml:space="preserve">全部換算</x:t>
         </x:is>
       </x:c>
       <x:c r="I61" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.55.1, REQ_IO_A8.55.2, REQ_IO_A8.55.3, REQ_IO_A8.55.4, REQ_IO_A8.55.5</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.46.4</x:t>
         </x:is>
       </x:c>
       <x:c r="J61" s="2" t="inlineStr">
@@ -10402,47 +10402,47 @@
     <x:row r="62">
       <x:c r="A62" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.55.7</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.45.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B62" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.55</x:t>
+          <x:t xml:space="preserve">4.4.1.8.45</x:t>
         </x:is>
       </x:c>
       <x:c r="C62" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Parameter Edit Interface</x:t>
+          <x:t xml:space="preserve">Unit of Measurement View Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D62" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Save (Button)</x:t>
+          <x:t xml:space="preserve">Calculator (Form)</x:t>
         </x:is>
       </x:c>
       <x:c r="E62" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">保存</x:t>
+          <x:t xml:space="preserve">數量、來源單位、目標單位、換算按鈕與結果。</x:t>
         </x:is>
       </x:c>
       <x:c r="F62" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">批次保存有修改的參數</x:t>
+          <x:t xml:space="preserve">試算換算結果。</x:t>
         </x:is>
       </x:c>
       <x:c r="G62" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Button</x:t>
+          <x:t xml:space="preserve">Decimal</x:t>
         </x:is>
       </x:c>
       <x:c r="H62" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">需 EDIT；只送有修改的項目並帶 version</x:t>
+          <x:t xml:space="preserve">數量最多 12 位整數及 6 位小數</x:t>
         </x:is>
       </x:c>
       <x:c r="I62" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.55.1, REQ_IO_A8.55.2, REQ_IO_A8.55.3, REQ_IO_A8.55.4, REQ_IO_A8.55.5</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.45.3</x:t>
         </x:is>
       </x:c>
       <x:c r="J62" s="2" t="inlineStr">
@@ -10459,32 +10459,32 @@
     <x:row r="63">
       <x:c r="A63" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.56.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.46.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B63" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.56</x:t>
+          <x:t xml:space="preserve">4.4.1.8.46</x:t>
         </x:is>
       </x:c>
       <x:c r="C63" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Print Settings Edit Interface</x:t>
+          <x:t xml:space="preserve">Unit of Measurement Create Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D63" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Company Name (Input)</x:t>
+          <x:t xml:space="preserve">Code (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E63" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">列印公司名稱</x:t>
+          <x:t xml:space="preserve">建立時輸入並轉大寫。</x:t>
         </x:is>
       </x:c>
       <x:c r="F63" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">單據抬頭</x:t>
+          <x:t xml:space="preserve">公司內唯一識別。</x:t>
         </x:is>
       </x:c>
       <x:c r="G63" s="2" t="inlineStr">
@@ -10494,12 +10494,12 @@
       </x:c>
       <x:c r="H63" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">最多 100 字；空白時用公司主檔名稱</x:t>
+          <x:t xml:space="preserve">1–30 位英數、-、_</x:t>
         </x:is>
       </x:c>
       <x:c r="I63" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">None</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.45.2</x:t>
         </x:is>
       </x:c>
       <x:c r="J63" s="2" t="inlineStr">
@@ -10516,32 +10516,32 @@
     <x:row r="64">
       <x:c r="A64" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.56.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.46.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B64" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.56</x:t>
+          <x:t xml:space="preserve">4.4.1.8.46</x:t>
         </x:is>
       </x:c>
       <x:c r="C64" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Print Settings Edit Interface</x:t>
+          <x:t xml:space="preserve">Unit of Measurement Create Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D64" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Address (Input)</x:t>
+          <x:t xml:space="preserve">Name (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E64" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">地址</x:t>
+          <x:t xml:space="preserve">單位名稱。</x:t>
         </x:is>
       </x:c>
       <x:c r="F64" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">單據抬頭</x:t>
+          <x:t xml:space="preserve">顯示單位。</x:t>
         </x:is>
       </x:c>
       <x:c r="G64" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </x:c>
       <x:c r="H64" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">最多 200 字</x:t>
+          <x:t xml:space="preserve">非空白、最多 200 字</x:t>
         </x:is>
       </x:c>
       <x:c r="I64" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">None</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.45.2</x:t>
         </x:is>
       </x:c>
       <x:c r="J64" s="2" t="inlineStr">
@@ -10573,47 +10573,47 @@
     <x:row r="65">
       <x:c r="A65" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.56.3</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.46.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B65" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.56</x:t>
+          <x:t xml:space="preserve">4.4.1.8.46</x:t>
         </x:is>
       </x:c>
       <x:c r="C65" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Print Settings Edit Interface</x:t>
+          <x:t xml:space="preserve">Unit of Measurement Create Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D65" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Postal Code (Input)</x:t>
+          <x:t xml:space="preserve">Decimal Places (Dropdown)</x:t>
         </x:is>
       </x:c>
       <x:c r="E65" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">郵遞區號</x:t>
+          <x:t xml:space="preserve">數量小數位數。</x:t>
         </x:is>
       </x:c>
       <x:c r="F65" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">單據抬頭</x:t>
+          <x:t xml:space="preserve">換算結果捨入。</x:t>
         </x:is>
       </x:c>
       <x:c r="G65" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Text</x:t>
+          <x:t xml:space="preserve">Integer</x:t>
         </x:is>
       </x:c>
       <x:c r="H65" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">最多 10 字</x:t>
+          <x:t xml:space="preserve">0–6</x:t>
         </x:is>
       </x:c>
       <x:c r="I65" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">None</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.45.2</x:t>
         </x:is>
       </x:c>
       <x:c r="J65" s="2" t="inlineStr">
@@ -10630,47 +10630,47 @@
     <x:row r="66">
       <x:c r="A66" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.56.4</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.46.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B66" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.56</x:t>
+          <x:t xml:space="preserve">4.4.1.8.46</x:t>
         </x:is>
       </x:c>
       <x:c r="C66" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Print Settings Edit Interface</x:t>
+          <x:t xml:space="preserve">Unit of Measurement Create Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D66" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Phone (Input)</x:t>
+          <x:t xml:space="preserve">From / To Unit (Dropdown)</x:t>
         </x:is>
       </x:c>
       <x:c r="E66" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">電話</x:t>
+          <x:t xml:space="preserve">換算兩端單位；停用單位不可選，兩端不可相同。</x:t>
         </x:is>
       </x:c>
       <x:c r="F66" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">單據抬頭</x:t>
+          <x:t xml:space="preserve">定義換算。</x:t>
         </x:is>
       </x:c>
       <x:c r="G66" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Text</x:t>
+          <x:t xml:space="preserve">Unit ID</x:t>
         </x:is>
       </x:c>
       <x:c r="H66" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">最多 30 字</x:t>
+          <x:t xml:space="preserve">本公司啟用單位</x:t>
         </x:is>
       </x:c>
       <x:c r="I66" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">None</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.45.3</x:t>
         </x:is>
       </x:c>
       <x:c r="J66" s="2" t="inlineStr">
@@ -10687,47 +10687,47 @@
     <x:row r="67">
       <x:c r="A67" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.56.5</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.46.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B67" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.56</x:t>
+          <x:t xml:space="preserve">4.4.1.8.46</x:t>
         </x:is>
       </x:c>
       <x:c r="C67" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Print Settings Edit Interface</x:t>
+          <x:t xml:space="preserve">Unit of Measurement Create Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D67" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Fax (Input)</x:t>
+          <x:t xml:space="preserve">Factor (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E67" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">傳真</x:t>
+          <x:t xml:space="preserve">1 來源 = 係數 目標。</x:t>
         </x:is>
       </x:c>
       <x:c r="F67" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">單據抬頭</x:t>
+          <x:t xml:space="preserve">換算係數。</x:t>
         </x:is>
       </x:c>
       <x:c r="G67" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Text</x:t>
+          <x:t xml:space="preserve">Decimal</x:t>
         </x:is>
       </x:c>
       <x:c r="H67" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">最多 30 字</x:t>
+          <x:t xml:space="preserve">大於 0，最多 9 位整數及 6 位小數</x:t>
         </x:is>
       </x:c>
       <x:c r="I67" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">None</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.45.3</x:t>
         </x:is>
       </x:c>
       <x:c r="J67" s="2" t="inlineStr">
@@ -10744,47 +10744,47 @@
     <x:row r="68">
       <x:c r="A68" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.56.6</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.47.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B68" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.56</x:t>
+          <x:t xml:space="preserve">4.4.1.8.47</x:t>
         </x:is>
       </x:c>
       <x:c r="C68" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Print Settings Edit Interface</x:t>
+          <x:t xml:space="preserve">Unit of Measurement Edit Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D68" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Purchase Order Footer (Textarea)</x:t>
+          <x:t xml:space="preserve">Code (Label)</x:t>
         </x:is>
       </x:c>
       <x:c r="E68" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">採購單頁尾備註</x:t>
+          <x:t xml:space="preserve">編輯時唯讀。</x:t>
         </x:is>
       </x:c>
       <x:c r="F68" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">列印在採購單底部</x:t>
+          <x:t xml:space="preserve">保持歷史識別。</x:t>
         </x:is>
       </x:c>
       <x:c r="G68" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Text（可多行）</x:t>
+          <x:t xml:space="preserve">Text</x:t>
         </x:is>
       </x:c>
       <x:c r="H68" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">最多 500 字</x:t>
+          <x:t xml:space="preserve">最多 30 字</x:t>
         </x:is>
       </x:c>
       <x:c r="I68" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">None</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.45.2</x:t>
         </x:is>
       </x:c>
       <x:c r="J68" s="2" t="inlineStr">
@@ -10801,47 +10801,47 @@
     <x:row r="69">
       <x:c r="A69" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.56.7</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.47.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B69" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.56</x:t>
+          <x:t xml:space="preserve">4.4.1.8.47</x:t>
         </x:is>
       </x:c>
       <x:c r="C69" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Print Settings Edit Interface</x:t>
+          <x:t xml:space="preserve">Unit of Measurement Edit Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D69" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Sales Delivery Footer (Textarea)</x:t>
+          <x:t xml:space="preserve">Name / Decimal Places / Active</x:t>
         </x:is>
       </x:c>
       <x:c r="E69" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">銷售出貨單頁尾備註</x:t>
+          <x:t xml:space="preserve">修改名稱、小數位數、啟用狀態。</x:t>
         </x:is>
       </x:c>
       <x:c r="F69" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">列印在出貨單底部</x:t>
+          <x:t xml:space="preserve">維護單位。</x:t>
         </x:is>
       </x:c>
       <x:c r="G69" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Text（可多行）</x:t>
+          <x:t xml:space="preserve">Text／Integer／Boolean</x:t>
         </x:is>
       </x:c>
       <x:c r="H69" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">最多 500 字</x:t>
+          <x:t xml:space="preserve">同建立</x:t>
         </x:is>
       </x:c>
       <x:c r="I69" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">None</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.45.2</x:t>
         </x:is>
       </x:c>
       <x:c r="J69" s="2" t="inlineStr">
@@ -10858,47 +10858,47 @@
     <x:row r="70">
       <x:c r="A70" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.56.8</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.47.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B70" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.56</x:t>
+          <x:t xml:space="preserve">4.4.1.8.47</x:t>
         </x:is>
       </x:c>
       <x:c r="C70" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Print Settings Edit Interface</x:t>
+          <x:t xml:space="preserve">Unit of Measurement Edit Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D70" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Print Logo (Switch)</x:t>
+          <x:t xml:space="preserve">Factor (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E70" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">是否列印 Logo</x:t>
+          <x:t xml:space="preserve">編輯換算時只可改係數。</x:t>
         </x:is>
       </x:c>
       <x:c r="F70" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">控制單據顯示 Logo</x:t>
+          <x:t xml:space="preserve">修正換算。</x:t>
         </x:is>
       </x:c>
       <x:c r="G70" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">true／false</x:t>
+          <x:t xml:space="preserve">Decimal</x:t>
         </x:is>
       </x:c>
       <x:c r="H70" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">預設否</x:t>
+          <x:t xml:space="preserve">同建立</x:t>
         </x:is>
       </x:c>
       <x:c r="I70" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">None</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.45.3</x:t>
         </x:is>
       </x:c>
       <x:c r="J70" s="2" t="inlineStr">
@@ -10915,47 +10915,47 @@
     <x:row r="71">
       <x:c r="A71" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.56.9</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.47.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B71" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.56</x:t>
+          <x:t xml:space="preserve">4.4.1.8.47</x:t>
         </x:is>
       </x:c>
       <x:c r="C71" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Print Settings Edit Interface</x:t>
+          <x:t xml:space="preserve">Unit of Measurement Edit Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D71" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Print Stamp (Switch)</x:t>
+          <x:t xml:space="preserve">Delete (Button)</x:t>
         </x:is>
       </x:c>
       <x:c r="E71" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">是否列印印章</x:t>
+          <x:t xml:space="preserve">確認後帶版本刪除單位或換算；被引用單位顯示 IN_USE。</x:t>
         </x:is>
       </x:c>
       <x:c r="F71" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">控制單據顯示公司印章</x:t>
+          <x:t xml:space="preserve">移除錯誤資料。</x:t>
         </x:is>
       </x:c>
       <x:c r="G71" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">true／false</x:t>
+          <x:t xml:space="preserve">Action</x:t>
         </x:is>
       </x:c>
       <x:c r="H71" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">預設否</x:t>
+          <x:t xml:space="preserve">-</x:t>
         </x:is>
       </x:c>
       <x:c r="I71" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">None</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.45.2, REQ_IO_A8.45.3</x:t>
         </x:is>
       </x:c>
       <x:c r="J71" s="2" t="inlineStr">
@@ -10972,47 +10972,47 @@
     <x:row r="72">
       <x:c r="A72" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.56.10</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.55.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B72" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.56</x:t>
+          <x:t xml:space="preserve">4.4.1.8.55</x:t>
         </x:is>
       </x:c>
       <x:c r="C72" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Print Settings Edit Interface</x:t>
+          <x:t xml:space="preserve">Parameter Edit Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D72" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Header Preview (Panel)</x:t>
+          <x:t xml:space="preserve">Boolean Parameter (Switch)</x:t>
         </x:is>
       </x:c>
       <x:c r="E72" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">抬頭預覽</x:t>
+          <x:t xml:space="preserve">開關型參數</x:t>
         </x:is>
       </x:c>
       <x:c r="F72" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">保存前確認版面</x:t>
+          <x:t xml:space="preserve">啟用／停用功能</x:t>
         </x:is>
       </x:c>
       <x:c r="G72" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">唯讀</x:t>
+          <x:t xml:space="preserve">true／false</x:t>
         </x:is>
       </x:c>
       <x:c r="H72" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">依草稿即時更新</x:t>
+          <x:t xml:space="preserve">—</x:t>
         </x:is>
       </x:c>
       <x:c r="I72" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.56.1, REQ_IO_A8.56.2, REQ_IO_A8.56.3, REQ_IO_A8.56.4, REQ_IO_A8.56.5, REQ_IO_A8.56.8, REQ_IO_A8.56.9</x:t>
+          <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
       <x:c r="J72" s="2" t="inlineStr">
@@ -11029,47 +11029,47 @@
     <x:row r="73">
       <x:c r="A73" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.56.11</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.55.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B73" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.56</x:t>
+          <x:t xml:space="preserve">4.4.1.8.55</x:t>
         </x:is>
       </x:c>
       <x:c r="C73" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Print Settings Edit Interface</x:t>
+          <x:t xml:space="preserve">Parameter Edit Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D73" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Save (Button)</x:t>
+          <x:t xml:space="preserve">Whole Number Parameter (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E73" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">保存</x:t>
+          <x:t xml:space="preserve">整數參數</x:t>
         </x:is>
       </x:c>
       <x:c r="F73" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">批次保存有修改的列印設定</x:t>
+          <x:t xml:space="preserve">例如小數位數</x:t>
         </x:is>
       </x:c>
       <x:c r="G73" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Button</x:t>
+          <x:t xml:space="preserve">整數字串</x:t>
         </x:is>
       </x:c>
       <x:c r="H73" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">需 EDIT；只送有修改的項目並帶 version</x:t>
+          <x:t xml:space="preserve">宣告的最小值至最大值</x:t>
         </x:is>
       </x:c>
       <x:c r="I73" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.56.1, REQ_IO_A8.56.2, REQ_IO_A8.56.3, REQ_IO_A8.56.4, REQ_IO_A8.56.5, REQ_IO_A8.56.6, REQ_IO_A8.56.7, REQ_IO_A8.56.8, REQ_IO_A8.56.9</x:t>
+          <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
       <x:c r="J73" s="2" t="inlineStr">
@@ -11086,42 +11086,42 @@
     <x:row r="74">
       <x:c r="A74" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.57.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.55.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B74" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.57</x:t>
+          <x:t xml:space="preserve">4.4.1.8.55</x:t>
         </x:is>
       </x:c>
       <x:c r="C74" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Logo &amp; Stamp Edit Interface</x:t>
+          <x:t xml:space="preserve">Parameter Edit Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D74" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Logo Preview (Image)</x:t>
+          <x:t xml:space="preserve">Number Parameter (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E74" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Logo 預覽</x:t>
+          <x:t xml:space="preserve">十進位參數</x:t>
         </x:is>
       </x:c>
       <x:c r="F74" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">確認目前的 Logo</x:t>
+          <x:t xml:space="preserve">數值設定</x:t>
         </x:is>
       </x:c>
       <x:c r="G74" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">唯讀圖片</x:t>
+          <x:t xml:space="preserve">十進位字串（不使用指數）</x:t>
         </x:is>
       </x:c>
       <x:c r="H74" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">PNG／JPEG</x:t>
+          <x:t xml:space="preserve">宣告的範圍；精度由伺服器判斷</x:t>
         </x:is>
       </x:c>
       <x:c r="I74" s="2" t="inlineStr">
@@ -11143,42 +11143,42 @@
     <x:row r="75">
       <x:c r="A75" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.57.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.55.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B75" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.57</x:t>
+          <x:t xml:space="preserve">4.4.1.8.55</x:t>
         </x:is>
       </x:c>
       <x:c r="C75" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Logo &amp; Stamp Edit Interface</x:t>
+          <x:t xml:space="preserve">Parameter Edit Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D75" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Stamp Preview (Image)</x:t>
+          <x:t xml:space="preserve">Text Parameter (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E75" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">印章預覽</x:t>
+          <x:t xml:space="preserve">文字參數</x:t>
         </x:is>
       </x:c>
       <x:c r="F75" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">確認目前的印章</x:t>
+          <x:t xml:space="preserve">名稱、備註等</x:t>
         </x:is>
       </x:c>
       <x:c r="G75" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">唯讀圖片</x:t>
+          <x:t xml:space="preserve">Text</x:t>
         </x:is>
       </x:c>
       <x:c r="H75" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">PNG／JPEG</x:t>
+          <x:t xml:space="preserve">宣告的長度上限</x:t>
         </x:is>
       </x:c>
       <x:c r="I75" s="2" t="inlineStr">
@@ -11200,47 +11200,47 @@
     <x:row r="76">
       <x:c r="A76" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.57.3</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.55.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B76" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.57</x:t>
+          <x:t xml:space="preserve">4.4.1.8.55</x:t>
         </x:is>
       </x:c>
       <x:c r="C76" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Logo &amp; Stamp Edit Interface</x:t>
+          <x:t xml:space="preserve">Parameter Edit Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D76" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Image Details (Text)</x:t>
+          <x:t xml:space="preserve">Option Parameter (Dropdown)</x:t>
         </x:is>
       </x:c>
       <x:c r="E76" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">檔案資料</x:t>
+          <x:t xml:space="preserve">選項參數</x:t>
         </x:is>
       </x:c>
       <x:c r="F76" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">顯示檔名、大小、寬高、上傳時間</x:t>
+          <x:t xml:space="preserve">從固定選項選擇</x:t>
         </x:is>
       </x:c>
       <x:c r="G76" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">唯讀</x:t>
+          <x:t xml:space="preserve">Enum</x:t>
         </x:is>
       </x:c>
       <x:c r="H76" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">-</x:t>
+          <x:t xml:space="preserve">宣告的選項</x:t>
         </x:is>
       </x:c>
       <x:c r="I76" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.57.1, REQ_IO_A8.57.2</x:t>
+          <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
       <x:c r="J76" s="2" t="inlineStr">
@@ -11257,47 +11257,47 @@
     <x:row r="77">
       <x:c r="A77" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.57.4</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.55.6</x:t>
         </x:is>
       </x:c>
       <x:c r="B77" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.57</x:t>
+          <x:t xml:space="preserve">4.4.1.8.55</x:t>
         </x:is>
       </x:c>
       <x:c r="C77" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Logo &amp; Stamp Edit Interface</x:t>
+          <x:t xml:space="preserve">Parameter Edit Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D77" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Upload / Replace (Button)</x:t>
+          <x:t xml:space="preserve">Restore Default (Button)</x:t>
         </x:is>
       </x:c>
       <x:c r="E77" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">上傳／替換</x:t>
+          <x:t xml:space="preserve">恢復預設</x:t>
         </x:is>
       </x:c>
       <x:c r="F77" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">選擇圖片檔並上傳</x:t>
+          <x:t xml:space="preserve">把欄位設回預設值</x:t>
         </x:is>
       </x:c>
       <x:c r="G77" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">File（accept="image/png,image/jpeg"）</x:t>
+          <x:t xml:space="preserve">Button</x:t>
         </x:is>
       </x:c>
       <x:c r="H77" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">需 EDIT；PNG／JPEG、1 MB、寬高 16–2048 像素</x:t>
+          <x:t xml:space="preserve">需 EDIT；保存後才生效</x:t>
         </x:is>
       </x:c>
       <x:c r="I77" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.57.1, REQ_IO_A8.57.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.55.1, REQ_IO_A8.55.2, REQ_IO_A8.55.3, REQ_IO_A8.55.4, REQ_IO_A8.55.5</x:t>
         </x:is>
       </x:c>
       <x:c r="J77" s="2" t="inlineStr">
@@ -11314,32 +11314,32 @@
     <x:row r="78">
       <x:c r="A78" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.57.5</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.55.7</x:t>
         </x:is>
       </x:c>
       <x:c r="B78" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.57</x:t>
+          <x:t xml:space="preserve">4.4.1.8.55</x:t>
         </x:is>
       </x:c>
       <x:c r="C78" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Logo &amp; Stamp Edit Interface</x:t>
+          <x:t xml:space="preserve">Parameter Edit Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D78" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Delete (Button)</x:t>
+          <x:t xml:space="preserve">Save (Button)</x:t>
         </x:is>
       </x:c>
       <x:c r="E78" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">刪除</x:t>
+          <x:t xml:space="preserve">保存</x:t>
         </x:is>
       </x:c>
       <x:c r="F78" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">刪除圖片</x:t>
+          <x:t xml:space="preserve">批次保存有修改的參數</x:t>
         </x:is>
       </x:c>
       <x:c r="G78" s="2" t="inlineStr">
@@ -11349,12 +11349,12 @@
       </x:c>
       <x:c r="H78" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">需 EDIT；確認後帶 version 刪除</x:t>
+          <x:t xml:space="preserve">需 EDIT；只送有修改的項目並帶 version</x:t>
         </x:is>
       </x:c>
       <x:c r="I78" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.57.1, REQ_IO_A8.57.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.55.1, REQ_IO_A8.55.2, REQ_IO_A8.55.3, REQ_IO_A8.55.4, REQ_IO_A8.55.5</x:t>
         </x:is>
       </x:c>
       <x:c r="J78" s="2" t="inlineStr">
@@ -11371,42 +11371,42 @@
     <x:row r="79">
       <x:c r="A79" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.58.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.56.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B79" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.58</x:t>
+          <x:t xml:space="preserve">4.4.1.8.56</x:t>
         </x:is>
       </x:c>
       <x:c r="C79" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Company View Interface</x:t>
+          <x:t xml:space="preserve">Print Settings Edit Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D79" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Company Code (Input)</x:t>
+          <x:t xml:space="preserve">Company Name (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E79" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">公司代碼</x:t>
+          <x:t xml:space="preserve">列印公司名稱</x:t>
         </x:is>
       </x:c>
       <x:c r="F79" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">唯一識別公司</x:t>
+          <x:t xml:space="preserve">單據抬頭</x:t>
         </x:is>
       </x:c>
       <x:c r="G79" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">VARCHAR(30)</x:t>
+          <x:t xml:space="preserve">Text</x:t>
         </x:is>
       </x:c>
       <x:c r="H79" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1–30 字元；ASCII 英文、數字、-、_</x:t>
+          <x:t xml:space="preserve">最多 100 字；空白時用公司主檔名稱</x:t>
         </x:is>
       </x:c>
       <x:c r="I79" s="2" t="inlineStr">
@@ -11428,42 +11428,42 @@
     <x:row r="80">
       <x:c r="A80" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.58.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.56.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B80" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.58</x:t>
+          <x:t xml:space="preserve">4.4.1.8.56</x:t>
         </x:is>
       </x:c>
       <x:c r="C80" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Company View Interface</x:t>
+          <x:t xml:space="preserve">Print Settings Edit Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D80" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Company Name (Input)</x:t>
+          <x:t xml:space="preserve">Address (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E80" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">公司名稱</x:t>
+          <x:t xml:space="preserve">地址</x:t>
         </x:is>
       </x:c>
       <x:c r="F80" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">顯示公司</x:t>
+          <x:t xml:space="preserve">單據抬頭</x:t>
         </x:is>
       </x:c>
       <x:c r="G80" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">NVARCHAR(200)</x:t>
+          <x:t xml:space="preserve">Text</x:t>
         </x:is>
       </x:c>
       <x:c r="H80" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1–200 字元</x:t>
+          <x:t xml:space="preserve">最多 200 字</x:t>
         </x:is>
       </x:c>
       <x:c r="I80" s="2" t="inlineStr">
@@ -11485,42 +11485,42 @@
     <x:row r="81">
       <x:c r="A81" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.59.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.56.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B81" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.59</x:t>
+          <x:t xml:space="preserve">4.4.1.8.56</x:t>
         </x:is>
       </x:c>
       <x:c r="C81" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Branch View Interface</x:t>
+          <x:t xml:space="preserve">Print Settings Edit Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D81" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Branch Code (Input)</x:t>
+          <x:t xml:space="preserve">Postal Code (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E81" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">分店代碼</x:t>
+          <x:t xml:space="preserve">郵遞區號</x:t>
         </x:is>
       </x:c>
       <x:c r="F81" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">公司內唯一</x:t>
+          <x:t xml:space="preserve">單據抬頭</x:t>
         </x:is>
       </x:c>
       <x:c r="G81" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">VARCHAR(30)</x:t>
+          <x:t xml:space="preserve">Text</x:t>
         </x:is>
       </x:c>
       <x:c r="H81" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1–30 字元；ASCII 英文、數字、-、_</x:t>
+          <x:t xml:space="preserve">最多 10 字</x:t>
         </x:is>
       </x:c>
       <x:c r="I81" s="2" t="inlineStr">
@@ -11542,42 +11542,42 @@
     <x:row r="82">
       <x:c r="A82" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.60.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.56.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B82" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.60</x:t>
+          <x:t xml:space="preserve">4.4.1.8.56</x:t>
         </x:is>
       </x:c>
       <x:c r="C82" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Department View Interface</x:t>
+          <x:t xml:space="preserve">Print Settings Edit Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D82" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Department Code (Input)</x:t>
+          <x:t xml:space="preserve">Phone (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E82" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">部門代碼</x:t>
+          <x:t xml:space="preserve">電話</x:t>
         </x:is>
       </x:c>
       <x:c r="F82" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">公司內唯一</x:t>
+          <x:t xml:space="preserve">單據抬頭</x:t>
         </x:is>
       </x:c>
       <x:c r="G82" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">VARCHAR(30)</x:t>
+          <x:t xml:space="preserve">Text</x:t>
         </x:is>
       </x:c>
       <x:c r="H82" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1–30 字元；ASCII 英文、數字、-、_</x:t>
+          <x:t xml:space="preserve">最多 30 字</x:t>
         </x:is>
       </x:c>
       <x:c r="I82" s="2" t="inlineStr">
@@ -11599,42 +11599,42 @@
     <x:row r="83">
       <x:c r="A83" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.60.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.56.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B83" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.60</x:t>
+          <x:t xml:space="preserve">4.4.1.8.56</x:t>
         </x:is>
       </x:c>
       <x:c r="C83" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Department View Interface</x:t>
+          <x:t xml:space="preserve">Print Settings Edit Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D83" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Parent Department (Dropdown)</x:t>
+          <x:t xml:space="preserve">Fax (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E83" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">上級部門</x:t>
+          <x:t xml:space="preserve">傳真</x:t>
         </x:is>
       </x:c>
       <x:c r="F83" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">建立層級</x:t>
+          <x:t xml:space="preserve">單據抬頭</x:t>
         </x:is>
       </x:c>
       <x:c r="G83" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">bigint ID</x:t>
+          <x:t xml:space="preserve">Text</x:t>
         </x:is>
       </x:c>
       <x:c r="H83" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">同公司啟用部門</x:t>
+          <x:t xml:space="preserve">最多 30 字</x:t>
         </x:is>
       </x:c>
       <x:c r="I83" s="2" t="inlineStr">
@@ -11656,42 +11656,42 @@
     <x:row r="84">
       <x:c r="A84" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.61.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.56.6</x:t>
         </x:is>
       </x:c>
       <x:c r="B84" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.61</x:t>
+          <x:t xml:space="preserve">4.4.1.8.56</x:t>
         </x:is>
       </x:c>
       <x:c r="C84" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">User Identity Create Interface</x:t>
+          <x:t xml:space="preserve">Print Settings Edit Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D84" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Username (Input)</x:t>
+          <x:t xml:space="preserve">Purchase Order Footer (Textarea)</x:t>
         </x:is>
       </x:c>
       <x:c r="E84" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">帳號</x:t>
+          <x:t xml:space="preserve">採購單頁尾備註</x:t>
         </x:is>
       </x:c>
       <x:c r="F84" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">建立登入身分</x:t>
+          <x:t xml:space="preserve">列印在採購單底部</x:t>
         </x:is>
       </x:c>
       <x:c r="G84" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ASCII text</x:t>
+          <x:t xml:space="preserve">Text（可多行）</x:t>
         </x:is>
       </x:c>
       <x:c r="H84" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">去除前後空白後 3–100 字元，字母／數字／點／底線／連字號；不分大小寫唯一</x:t>
+          <x:t xml:space="preserve">最多 500 字</x:t>
         </x:is>
       </x:c>
       <x:c r="I84" s="2" t="inlineStr">
@@ -11713,47 +11713,47 @@
     <x:row r="85">
       <x:c r="A85" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.61.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.56.7</x:t>
         </x:is>
       </x:c>
       <x:c r="B85" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.61</x:t>
+          <x:t xml:space="preserve">4.4.1.8.56</x:t>
         </x:is>
       </x:c>
       <x:c r="C85" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">User Identity Create Interface</x:t>
+          <x:t xml:space="preserve">Print Settings Edit Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D85" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Password (Input)</x:t>
+          <x:t xml:space="preserve">Sales Delivery Footer (Textarea)</x:t>
         </x:is>
       </x:c>
       <x:c r="E85" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">初始密碼</x:t>
+          <x:t xml:space="preserve">銷售出貨單頁尾備註</x:t>
         </x:is>
       </x:c>
       <x:c r="F85" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">依目前政策驗證，提交後清空</x:t>
+          <x:t xml:space="preserve">列印在出貨單底部</x:t>
         </x:is>
       </x:c>
       <x:c r="G85" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Password，autocomplete=new-password</x:t>
+          <x:t xml:space="preserve">Text（可多行）</x:t>
         </x:is>
       </x:c>
       <x:c r="H85" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">必填，最多 128 字元；其餘依政策（預設 12 字元以上，含大小寫、數字、符號），不符時顯示政策說明</x:t>
+          <x:t xml:space="preserve">最多 500 字</x:t>
         </x:is>
       </x:c>
       <x:c r="I85" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.61.3</x:t>
+          <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
       <x:c r="J85" s="2" t="inlineStr">
@@ -11770,47 +11770,47 @@
     <x:row r="86">
       <x:c r="A86" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.61.3</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.56.8</x:t>
         </x:is>
       </x:c>
       <x:c r="B86" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.61</x:t>
+          <x:t xml:space="preserve">4.4.1.8.56</x:t>
         </x:is>
       </x:c>
       <x:c r="C86" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">User Identity Create Interface</x:t>
+          <x:t xml:space="preserve">Print Settings Edit Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D86" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Confirm Password (Input)</x:t>
+          <x:t xml:space="preserve">Print Logo (Switch)</x:t>
         </x:is>
       </x:c>
       <x:c r="E86" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">確認密碼</x:t>
+          <x:t xml:space="preserve">是否列印 Logo</x:t>
         </x:is>
       </x:c>
       <x:c r="F86" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">防止輸入錯誤</x:t>
+          <x:t xml:space="preserve">控制單據顯示 Logo</x:t>
         </x:is>
       </x:c>
       <x:c r="G86" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Password</x:t>
+          <x:t xml:space="preserve">true／false</x:t>
         </x:is>
       </x:c>
       <x:c r="H86" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">須與密碼相同</x:t>
+          <x:t xml:space="preserve">預設否</x:t>
         </x:is>
       </x:c>
       <x:c r="I86" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.61.2</x:t>
+          <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
       <x:c r="J86" s="2" t="inlineStr">
@@ -11827,42 +11827,42 @@
     <x:row r="87">
       <x:c r="A87" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.62.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.56.9</x:t>
         </x:is>
       </x:c>
       <x:c r="B87" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.62</x:t>
+          <x:t xml:space="preserve">4.4.1.8.56</x:t>
         </x:is>
       </x:c>
       <x:c r="C87" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Login Interface</x:t>
+          <x:t xml:space="preserve">Print Settings Edit Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D87" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Username (Input)</x:t>
+          <x:t xml:space="preserve">Print Stamp (Switch)</x:t>
         </x:is>
       </x:c>
       <x:c r="E87" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">帳號</x:t>
+          <x:t xml:space="preserve">是否列印印章</x:t>
         </x:is>
       </x:c>
       <x:c r="F87" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">登入身分</x:t>
+          <x:t xml:space="preserve">控制單據顯示公司印章</x:t>
         </x:is>
       </x:c>
       <x:c r="G87" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Text，autocomplete=username</x:t>
+          <x:t xml:space="preserve">true／false</x:t>
         </x:is>
       </x:c>
       <x:c r="H87" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">必填、非空白，最多 100 字元；送出前去除前後空白</x:t>
+          <x:t xml:space="preserve">預設否</x:t>
         </x:is>
       </x:c>
       <x:c r="I87" s="2" t="inlineStr">
@@ -11884,47 +11884,47 @@
     <x:row r="88">
       <x:c r="A88" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.62.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.56.10</x:t>
         </x:is>
       </x:c>
       <x:c r="B88" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.62</x:t>
+          <x:t xml:space="preserve">4.4.1.8.56</x:t>
         </x:is>
       </x:c>
       <x:c r="C88" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Login Interface</x:t>
+          <x:t xml:space="preserve">Print Settings Edit Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D88" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Password (Input)</x:t>
+          <x:t xml:space="preserve">Header Preview (Panel)</x:t>
         </x:is>
       </x:c>
       <x:c r="E88" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">密碼</x:t>
+          <x:t xml:space="preserve">抬頭預覽</x:t>
         </x:is>
       </x:c>
       <x:c r="F88" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">驗證身分</x:t>
+          <x:t xml:space="preserve">保存前確認版面</x:t>
         </x:is>
       </x:c>
       <x:c r="G88" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Password，autocomplete=current-password</x:t>
+          <x:t xml:space="preserve">唯讀</x:t>
         </x:is>
       </x:c>
       <x:c r="H88" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">必填，最多 128 字元；失敗後清空</x:t>
+          <x:t xml:space="preserve">依草稿即時更新</x:t>
         </x:is>
       </x:c>
       <x:c r="I88" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">None</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.56.1, REQ_IO_A8.56.2, REQ_IO_A8.56.3, REQ_IO_A8.56.4, REQ_IO_A8.56.5, REQ_IO_A8.56.8, REQ_IO_A8.56.9</x:t>
         </x:is>
       </x:c>
       <x:c r="J88" s="2" t="inlineStr">
@@ -11941,47 +11941,47 @@
     <x:row r="89">
       <x:c r="A89" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.62.3</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.56.11</x:t>
         </x:is>
       </x:c>
       <x:c r="B89" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.62</x:t>
+          <x:t xml:space="preserve">4.4.1.8.56</x:t>
         </x:is>
       </x:c>
       <x:c r="C89" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Login Interface</x:t>
+          <x:t xml:space="preserve">Print Settings Edit Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D89" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Captcha Code (Input)</x:t>
+          <x:t xml:space="preserve">Save (Button)</x:t>
         </x:is>
       </x:c>
       <x:c r="E89" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">驗證碼</x:t>
+          <x:t xml:space="preserve">保存</x:t>
         </x:is>
       </x:c>
       <x:c r="F89" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">防自動化登入</x:t>
+          <x:t xml:space="preserve">批次保存有修改的列印設定</x:t>
         </x:is>
       </x:c>
       <x:c r="G89" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">數字，inputmode=numeric</x:t>
+          <x:t xml:space="preserve">Button</x:t>
         </x:is>
       </x:c>
       <x:c r="H89" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4–6 位數字（非數字自動移除）</x:t>
+          <x:t xml:space="preserve">需 EDIT；只送有修改的項目並帶 version</x:t>
         </x:is>
       </x:c>
       <x:c r="I89" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.62.4</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.56.1, REQ_IO_A8.56.2, REQ_IO_A8.56.3, REQ_IO_A8.56.4, REQ_IO_A8.56.5, REQ_IO_A8.56.6, REQ_IO_A8.56.7, REQ_IO_A8.56.8, REQ_IO_A8.56.9</x:t>
         </x:is>
       </x:c>
       <x:c r="J89" s="2" t="inlineStr">
@@ -11998,42 +11998,42 @@
     <x:row r="90">
       <x:c r="A90" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.62.4</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.57.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B90" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.62</x:t>
+          <x:t xml:space="preserve">4.4.1.8.57</x:t>
         </x:is>
       </x:c>
       <x:c r="C90" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Login Interface</x:t>
+          <x:t xml:space="preserve">Logo &amp; Stamp Edit Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D90" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Captcha Image (Button)</x:t>
+          <x:t xml:space="preserve">Logo Preview (Image)</x:t>
         </x:is>
       </x:c>
       <x:c r="E90" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">驗證碼圖片</x:t>
+          <x:t xml:space="preserve">Logo 預覽</x:t>
         </x:is>
       </x:c>
       <x:c r="F90" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">顯示題目，點擊換圖</x:t>
+          <x:t xml:space="preserve">確認目前的 Logo</x:t>
         </x:is>
       </x:c>
       <x:c r="G90" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SVG data URI</x:t>
+          <x:t xml:space="preserve">唯讀圖片</x:t>
         </x:is>
       </x:c>
       <x:c r="H90" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">每次送出失敗後自動換新</x:t>
+          <x:t xml:space="preserve">PNG／JPEG</x:t>
         </x:is>
       </x:c>
       <x:c r="I90" s="2" t="inlineStr">
@@ -12055,42 +12055,42 @@
     <x:row r="91">
       <x:c r="A91" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.62.5</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.57.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B91" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.62</x:t>
+          <x:t xml:space="preserve">4.4.1.8.57</x:t>
         </x:is>
       </x:c>
       <x:c r="C91" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Login Interface</x:t>
+          <x:t xml:space="preserve">Logo &amp; Stamp Edit Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D91" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Sign In (Button)</x:t>
+          <x:t xml:space="preserve">Stamp Preview (Image)</x:t>
         </x:is>
       </x:c>
       <x:c r="E91" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">登入</x:t>
+          <x:t xml:space="preserve">印章預覽</x:t>
         </x:is>
       </x:c>
       <x:c r="F91" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">送出</x:t>
+          <x:t xml:space="preserve">確認目前的印章</x:t>
         </x:is>
       </x:c>
       <x:c r="G91" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Button</x:t>
+          <x:t xml:space="preserve">唯讀圖片</x:t>
         </x:is>
       </x:c>
       <x:c r="H91" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">送出中顯示載入狀態，不可重複送出</x:t>
+          <x:t xml:space="preserve">PNG／JPEG</x:t>
         </x:is>
       </x:c>
       <x:c r="I91" s="2" t="inlineStr">
@@ -12112,47 +12112,47 @@
     <x:row r="92">
       <x:c r="A92" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.62.6</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.57.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B92" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.62</x:t>
+          <x:t xml:space="preserve">4.4.1.8.57</x:t>
         </x:is>
       </x:c>
       <x:c r="C92" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Login Interface</x:t>
+          <x:t xml:space="preserve">Logo &amp; Stamp Edit Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D92" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Error Message (Alert)</x:t>
+          <x:t xml:space="preserve">Image Details (Text)</x:t>
         </x:is>
       </x:c>
       <x:c r="E92" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">錯誤訊息</x:t>
+          <x:t xml:space="preserve">檔案資料</x:t>
         </x:is>
       </x:c>
       <x:c r="F92" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">顯示 errors.&lt;errorCode&gt;</x:t>
+          <x:t xml:space="preserve">顯示檔名、大小、寬高、上傳時間</x:t>
         </x:is>
       </x:c>
       <x:c r="G92" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Text</x:t>
+          <x:t xml:space="preserve">唯讀</x:t>
         </x:is>
       </x:c>
       <x:c r="H92" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">INVALID_CREDENTIALS／CAPTCHA_INVALID／PASSWORD_EXPIRED／VALIDATION_FAILED／網路／未知</x:t>
+          <x:t xml:space="preserve">-</x:t>
         </x:is>
       </x:c>
       <x:c r="I92" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">None</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.57.1, REQ_IO_A8.57.2</x:t>
         </x:is>
       </x:c>
       <x:c r="J92" s="2" t="inlineStr">
@@ -12169,47 +12169,47 @@
     <x:row r="93">
       <x:c r="A93" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.63.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.57.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B93" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.63</x:t>
+          <x:t xml:space="preserve">4.4.1.8.57</x:t>
         </x:is>
       </x:c>
       <x:c r="C93" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">User Maintenance Interface</x:t>
+          <x:t xml:space="preserve">Logo &amp; Stamp Edit Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D93" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Keyword (Input)</x:t>
+          <x:t xml:space="preserve">Upload / Replace (Button)</x:t>
         </x:is>
       </x:c>
       <x:c r="E93" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">搜尋帳號</x:t>
+          <x:t xml:space="preserve">上傳／替換</x:t>
         </x:is>
       </x:c>
       <x:c r="F93" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">篩選列表</x:t>
+          <x:t xml:space="preserve">選擇圖片檔並上傳</x:t>
         </x:is>
       </x:c>
       <x:c r="G93" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Text</x:t>
+          <x:t xml:space="preserve">File（accept="image/png,image/jpeg"）</x:t>
         </x:is>
       </x:c>
       <x:c r="H93" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">去除前後空白，不分大小寫</x:t>
+          <x:t xml:space="preserve">需 EDIT；PNG／JPEG、1 MB、寬高 16–2048 像素</x:t>
         </x:is>
       </x:c>
       <x:c r="I93" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">None</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.57.1, REQ_IO_A8.57.2</x:t>
         </x:is>
       </x:c>
       <x:c r="J93" s="2" t="inlineStr">
@@ -12226,47 +12226,47 @@
     <x:row r="94">
       <x:c r="A94" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.63.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.57.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B94" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.63</x:t>
+          <x:t xml:space="preserve">4.4.1.8.57</x:t>
         </x:is>
       </x:c>
       <x:c r="C94" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">User Maintenance Interface</x:t>
+          <x:t xml:space="preserve">Logo &amp; Stamp Edit Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D94" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Status (Tag)</x:t>
+          <x:t xml:space="preserve">Delete (Button)</x:t>
         </x:is>
       </x:c>
       <x:c r="E94" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">狀態</x:t>
+          <x:t xml:space="preserve">刪除</x:t>
         </x:is>
       </x:c>
       <x:c r="F94" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">顯示啟用、鎖定、密碼過期</x:t>
+          <x:t xml:space="preserve">刪除圖片</x:t>
         </x:is>
       </x:c>
       <x:c r="G94" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Tag</x:t>
+          <x:t xml:space="preserve">Button</x:t>
         </x:is>
       </x:c>
       <x:c r="H94" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">啟用／停用；已鎖定；密碼已過期</x:t>
+          <x:t xml:space="preserve">需 EDIT；確認後帶 version 刪除</x:t>
         </x:is>
       </x:c>
       <x:c r="I94" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">None</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.57.1, REQ_IO_A8.57.2</x:t>
         </x:is>
       </x:c>
       <x:c r="J94" s="2" t="inlineStr">
@@ -12283,42 +12283,42 @@
     <x:row r="95">
       <x:c r="A95" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.63.3</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.58.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B95" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.63</x:t>
+          <x:t xml:space="preserve">4.4.1.8.58</x:t>
         </x:is>
       </x:c>
       <x:c r="C95" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">User Maintenance Interface</x:t>
+          <x:t xml:space="preserve">Company View Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D95" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Activate / Deactivate (Button)</x:t>
+          <x:t xml:space="preserve">Company Code (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E95" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">啟用／停用</x:t>
+          <x:t xml:space="preserve">公司代碼</x:t>
         </x:is>
       </x:c>
       <x:c r="F95" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">切換帳號狀態</x:t>
+          <x:t xml:space="preserve">唯一識別公司</x:t>
         </x:is>
       </x:c>
       <x:c r="G95" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Button</x:t>
+          <x:t xml:space="preserve">VARCHAR(30)</x:t>
         </x:is>
       </x:c>
       <x:c r="H95" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">帶讀取時的 version；不可停用自己</x:t>
+          <x:t xml:space="preserve">1–30 字元；ASCII 英文、數字、-、_</x:t>
         </x:is>
       </x:c>
       <x:c r="I95" s="2" t="inlineStr">
@@ -12340,42 +12340,42 @@
     <x:row r="96">
       <x:c r="A96" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.63.4</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.58.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B96" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.63</x:t>
+          <x:t xml:space="preserve">4.4.1.8.58</x:t>
         </x:is>
       </x:c>
       <x:c r="C96" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">User Maintenance Interface</x:t>
+          <x:t xml:space="preserve">Company View Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D96" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Unlock (Button)</x:t>
+          <x:t xml:space="preserve">Company Name (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E96" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">解鎖</x:t>
+          <x:t xml:space="preserve">公司名稱</x:t>
         </x:is>
       </x:c>
       <x:c r="F96" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">清除鎖定</x:t>
+          <x:t xml:space="preserve">顯示公司</x:t>
         </x:is>
       </x:c>
       <x:c r="G96" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Button</x:t>
+          <x:t xml:space="preserve">NVARCHAR(200)</x:t>
         </x:is>
       </x:c>
       <x:c r="H96" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">只在已鎖定時顯示</x:t>
+          <x:t xml:space="preserve">1–200 字元</x:t>
         </x:is>
       </x:c>
       <x:c r="I96" s="2" t="inlineStr">
@@ -12397,47 +12397,47 @@
     <x:row r="97">
       <x:c r="A97" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.63.5</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.59.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B97" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.63</x:t>
+          <x:t xml:space="preserve">4.4.1.8.59</x:t>
         </x:is>
       </x:c>
       <x:c r="C97" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">User Maintenance Interface</x:t>
+          <x:t xml:space="preserve">Branch View Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D97" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Reset Password (Button)</x:t>
+          <x:t xml:space="preserve">Branch Code (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E97" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">重設密碼</x:t>
+          <x:t xml:space="preserve">分店代碼</x:t>
         </x:is>
       </x:c>
       <x:c r="F97" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">開啟重設對話框</x:t>
+          <x:t xml:space="preserve">公司內唯一</x:t>
         </x:is>
       </x:c>
       <x:c r="G97" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Button</x:t>
+          <x:t xml:space="preserve">VARCHAR(30)</x:t>
         </x:is>
       </x:c>
       <x:c r="H97" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">新密碼依政策驗證，成功後清除鎖定並重新起算到期</x:t>
+          <x:t xml:space="preserve">1–30 字元；ASCII 英文、數字、-、_</x:t>
         </x:is>
       </x:c>
       <x:c r="I97" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.61.2</x:t>
+          <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
       <x:c r="J97" s="2" t="inlineStr">
@@ -12454,42 +12454,42 @@
     <x:row r="98">
       <x:c r="A98" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.64.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.60.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B98" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.64</x:t>
+          <x:t xml:space="preserve">4.4.1.8.60</x:t>
         </x:is>
       </x:c>
       <x:c r="C98" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Role Maintenance Interface</x:t>
+          <x:t xml:space="preserve">Department View Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D98" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Role Code (Input)</x:t>
+          <x:t xml:space="preserve">Department Code (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E98" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">角色代碼</x:t>
+          <x:t xml:space="preserve">部門代碼</x:t>
         </x:is>
       </x:c>
       <x:c r="F98" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">全系統唯一識別角色</x:t>
+          <x:t xml:space="preserve">公司內唯一</x:t>
         </x:is>
       </x:c>
       <x:c r="G98" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">VARCHAR(50)</x:t>
+          <x:t xml:space="preserve">VARCHAR(30)</x:t>
         </x:is>
       </x:c>
       <x:c r="H98" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1–50 字元；ASCII 英文、數字、-、_；保存為大寫；建立後不可修改</x:t>
+          <x:t xml:space="preserve">1–30 字元；ASCII 英文、數字、-、_</x:t>
         </x:is>
       </x:c>
       <x:c r="I98" s="2" t="inlineStr">
@@ -12511,42 +12511,42 @@
     <x:row r="99">
       <x:c r="A99" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.64.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.60.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B99" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.64</x:t>
+          <x:t xml:space="preserve">4.4.1.8.60</x:t>
         </x:is>
       </x:c>
       <x:c r="C99" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Role Maintenance Interface</x:t>
+          <x:t xml:space="preserve">Department View Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D99" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Role Name (Input)</x:t>
+          <x:t xml:space="preserve">Parent Department (Dropdown)</x:t>
         </x:is>
       </x:c>
       <x:c r="E99" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">角色名稱</x:t>
+          <x:t xml:space="preserve">上級部門</x:t>
         </x:is>
       </x:c>
       <x:c r="F99" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">顯示角色</x:t>
+          <x:t xml:space="preserve">建立層級</x:t>
         </x:is>
       </x:c>
       <x:c r="G99" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">NVARCHAR(200)</x:t>
+          <x:t xml:space="preserve">bigint ID</x:t>
         </x:is>
       </x:c>
       <x:c r="H99" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">去除空白後 1–200 字元</x:t>
+          <x:t xml:space="preserve">同公司啟用部門</x:t>
         </x:is>
       </x:c>
       <x:c r="I99" s="2" t="inlineStr">
@@ -12568,42 +12568,42 @@
     <x:row r="100">
       <x:c r="A100" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.64.3</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.61.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B100" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.64</x:t>
+          <x:t xml:space="preserve">4.4.1.8.61</x:t>
         </x:is>
       </x:c>
       <x:c r="C100" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Role Maintenance Interface</x:t>
+          <x:t xml:space="preserve">User Identity Create Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D100" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Data Scope (Dropdown)</x:t>
+          <x:t xml:space="preserve">Username (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E100" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">資料範圍</x:t>
+          <x:t xml:space="preserve">帳號</x:t>
         </x:is>
       </x:c>
       <x:c r="F100" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">決定可見單據範圍</x:t>
+          <x:t xml:space="preserve">建立登入身分</x:t>
         </x:is>
       </x:c>
       <x:c r="G100" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Self／Department／Branch／Company</x:t>
+          <x:t xml:space="preserve">ASCII text</x:t>
         </x:is>
       </x:c>
       <x:c r="H100" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">必選，預設本人</x:t>
+          <x:t xml:space="preserve">去除前後空白後 3–100 字元，字母／數字／點／底線／連字號；不分大小寫唯一</x:t>
         </x:is>
       </x:c>
       <x:c r="I100" s="2" t="inlineStr">
@@ -12625,47 +12625,47 @@
     <x:row r="101">
       <x:c r="A101" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.64.4</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.61.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B101" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.64</x:t>
+          <x:t xml:space="preserve">4.4.1.8.61</x:t>
         </x:is>
       </x:c>
       <x:c r="C101" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Role Maintenance Interface</x:t>
+          <x:t xml:space="preserve">User Identity Create Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D101" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Full Access (Checkbox)</x:t>
+          <x:t xml:space="preserve">Password (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E101" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">全權</x:t>
+          <x:t xml:space="preserve">初始密碼</x:t>
         </x:is>
       </x:c>
       <x:c r="F101" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">擁有全部權限</x:t>
+          <x:t xml:space="preserve">依目前政策驗證，提交後清空</x:t>
         </x:is>
       </x:c>
       <x:c r="G101" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Boolean</x:t>
+          <x:t xml:space="preserve">Password，autocomplete=new-password</x:t>
         </x:is>
       </x:c>
       <x:c r="H101" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">勾選時權限清單停用</x:t>
+          <x:t xml:space="preserve">必填，最多 128 字元；其餘依政策（預設 12 字元以上，含大小寫、數字、符號），不符時顯示政策說明</x:t>
         </x:is>
       </x:c>
       <x:c r="I101" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.64.5</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.61.3</x:t>
         </x:is>
       </x:c>
       <x:c r="J101" s="2" t="inlineStr">
@@ -12682,47 +12682,47 @@
     <x:row r="102">
       <x:c r="A102" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.64.5</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.61.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B102" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.64</x:t>
+          <x:t xml:space="preserve">4.4.1.8.61</x:t>
         </x:is>
       </x:c>
       <x:c r="C102" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Role Maintenance Interface</x:t>
+          <x:t xml:space="preserve">User Identity Create Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D102" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Permissions (Checkbox group)</x:t>
+          <x:t xml:space="preserve">Confirm Password (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E102" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">權限</x:t>
+          <x:t xml:space="preserve">確認密碼</x:t>
         </x:is>
       </x:c>
       <x:c r="F102" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">依模組勾選權限代碼</x:t>
+          <x:t xml:space="preserve">防止輸入錯誤</x:t>
         </x:is>
       </x:c>
       <x:c r="G102" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">模組.資源.動作</x:t>
+          <x:t xml:space="preserve">Password</x:t>
         </x:is>
       </x:c>
       <x:c r="H102" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">只可選權限目錄內的代碼；模組可全選</x:t>
+          <x:t xml:space="preserve">須與密碼相同</x:t>
         </x:is>
       </x:c>
       <x:c r="I102" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.64.4</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.61.2</x:t>
         </x:is>
       </x:c>
       <x:c r="J102" s="2" t="inlineStr">
@@ -12739,42 +12739,42 @@
     <x:row r="103">
       <x:c r="A103" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.64.6</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.62.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B103" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.64</x:t>
+          <x:t xml:space="preserve">4.4.1.8.62</x:t>
         </x:is>
       </x:c>
       <x:c r="C103" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Role Maintenance Interface</x:t>
+          <x:t xml:space="preserve">Login Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D103" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Delete (Button)</x:t>
+          <x:t xml:space="preserve">Username (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E103" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">刪除</x:t>
+          <x:t xml:space="preserve">帳號</x:t>
         </x:is>
       </x:c>
       <x:c r="F103" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">軟刪除未使用的角色</x:t>
+          <x:t xml:space="preserve">登入身分</x:t>
         </x:is>
       </x:c>
       <x:c r="G103" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Button + popconfirm</x:t>
+          <x:t xml:space="preserve">Text，autocomplete=username</x:t>
         </x:is>
       </x:c>
       <x:c r="H103" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">帶 version；使用中回 SYS.ROLE.IN_USE</x:t>
+          <x:t xml:space="preserve">必填、非空白，最多 100 字元；送出前去除前後空白</x:t>
         </x:is>
       </x:c>
       <x:c r="I103" s="2" t="inlineStr">
@@ -12796,47 +12796,47 @@
     <x:row r="104">
       <x:c r="A104" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.65.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.62.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B104" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.65</x:t>
+          <x:t xml:space="preserve">4.4.1.8.62</x:t>
         </x:is>
       </x:c>
       <x:c r="C104" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">User Permission Edit Interface（BlueWhale 4.4.1.8.26）</x:t>
+          <x:t xml:space="preserve">Login Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D104" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Company (Dropdown)</x:t>
+          <x:t xml:space="preserve">Password (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E104" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">公司</x:t>
+          <x:t xml:space="preserve">密碼</x:t>
         </x:is>
       </x:c>
       <x:c r="F104" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">選擇要設定的公司</x:t>
+          <x:t xml:space="preserve">驗證身分</x:t>
         </x:is>
       </x:c>
       <x:c r="G104" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">bigint ID</x:t>
+          <x:t xml:space="preserve">Password，autocomplete=current-password</x:t>
         </x:is>
       </x:c>
       <x:c r="H104" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">操作者可切換的公司</x:t>
+          <x:t xml:space="preserve">必填，最多 128 字元；失敗後清空</x:t>
         </x:is>
       </x:c>
       <x:c r="I104" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.65.2</x:t>
+          <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
       <x:c r="J104" s="2" t="inlineStr">
@@ -12853,47 +12853,47 @@
     <x:row r="105">
       <x:c r="A105" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.65.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.62.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B105" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.65</x:t>
+          <x:t xml:space="preserve">4.4.1.8.62</x:t>
         </x:is>
       </x:c>
       <x:c r="C105" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">User Permission Edit Interface（BlueWhale 4.4.1.8.26）</x:t>
+          <x:t xml:space="preserve">Login Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D105" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Branch / Department (Dropdown)</x:t>
+          <x:t xml:space="preserve">Captcha Code (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E105" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">分店／部門</x:t>
+          <x:t xml:space="preserve">驗證碼</x:t>
         </x:is>
       </x:c>
       <x:c r="F105" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">組織歸屬（資料範圍用）</x:t>
+          <x:t xml:space="preserve">防自動化登入</x:t>
         </x:is>
       </x:c>
       <x:c r="G105" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">bigint ID，可清空</x:t>
+          <x:t xml:space="preserve">數字，inputmode=numeric</x:t>
         </x:is>
       </x:c>
       <x:c r="H105" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">所選公司的啟用分店／部門</x:t>
+          <x:t xml:space="preserve">4–6 位數字（非數字自動移除）</x:t>
         </x:is>
       </x:c>
       <x:c r="I105" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.65.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.62.4</x:t>
         </x:is>
       </x:c>
       <x:c r="J105" s="2" t="inlineStr">
@@ -12910,42 +12910,42 @@
     <x:row r="106">
       <x:c r="A106" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.65.3</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.62.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B106" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.65</x:t>
+          <x:t xml:space="preserve">4.4.1.8.62</x:t>
         </x:is>
       </x:c>
       <x:c r="C106" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">User Permission Edit Interface（BlueWhale 4.4.1.8.26）</x:t>
+          <x:t xml:space="preserve">Login Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D106" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Roles (Multi-select)</x:t>
+          <x:t xml:space="preserve">Captcha Image (Button)</x:t>
         </x:is>
       </x:c>
       <x:c r="E106" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">角色</x:t>
+          <x:t xml:space="preserve">驗證碼圖片</x:t>
         </x:is>
       </x:c>
       <x:c r="F106" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">整組取代該公司的角色</x:t>
+          <x:t xml:space="preserve">顯示題目，點擊換圖</x:t>
         </x:is>
       </x:c>
       <x:c r="G106" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">bigint ID 陣列</x:t>
+          <x:t xml:space="preserve">SVG data URI</x:t>
         </x:is>
       </x:c>
       <x:c r="H106" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">啟用角色；可為空（無權限）</x:t>
+          <x:t xml:space="preserve">每次送出失敗後自動換新</x:t>
         </x:is>
       </x:c>
       <x:c r="I106" s="2" t="inlineStr">
@@ -12967,42 +12967,42 @@
     <x:row r="107">
       <x:c r="A107" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.65.4</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.62.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B107" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.65</x:t>
+          <x:t xml:space="preserve">4.4.1.8.62</x:t>
         </x:is>
       </x:c>
       <x:c r="C107" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">User Permission Edit Interface（BlueWhale 4.4.1.8.26）</x:t>
+          <x:t xml:space="preserve">Login Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D107" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Default Company (Checkbox)</x:t>
+          <x:t xml:space="preserve">Sign In (Button)</x:t>
         </x:is>
       </x:c>
       <x:c r="E107" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">預設公司</x:t>
+          <x:t xml:space="preserve">登入</x:t>
         </x:is>
       </x:c>
       <x:c r="F107" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">登入後預設的操作公司</x:t>
+          <x:t xml:space="preserve">送出</x:t>
         </x:is>
       </x:c>
       <x:c r="G107" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Boolean</x:t>
+          <x:t xml:space="preserve">Button</x:t>
         </x:is>
       </x:c>
       <x:c r="H107" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">設定後取消其他預設</x:t>
+          <x:t xml:space="preserve">送出中顯示載入狀態，不可重複送出</x:t>
         </x:is>
       </x:c>
       <x:c r="I107" s="2" t="inlineStr">
@@ -13024,42 +13024,42 @@
     <x:row r="108">
       <x:c r="A108" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.65.5</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.62.6</x:t>
         </x:is>
       </x:c>
       <x:c r="B108" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.65</x:t>
+          <x:t xml:space="preserve">4.4.1.8.62</x:t>
         </x:is>
       </x:c>
       <x:c r="C108" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">User Permission Edit Interface（BlueWhale 4.4.1.8.26）</x:t>
+          <x:t xml:space="preserve">Login Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D108" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Access Active (Checkbox)</x:t>
+          <x:t xml:space="preserve">Error Message (Alert)</x:t>
         </x:is>
       </x:c>
       <x:c r="E108" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">啟用存取</x:t>
+          <x:t xml:space="preserve">錯誤訊息</x:t>
         </x:is>
       </x:c>
       <x:c r="F108" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">停用後該公司不授權</x:t>
+          <x:t xml:space="preserve">顯示 errors.&lt;errorCode&gt;</x:t>
         </x:is>
       </x:c>
       <x:c r="G108" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Boolean</x:t>
+          <x:t xml:space="preserve">Text</x:t>
         </x:is>
       </x:c>
       <x:c r="H108" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">不可停用自己</x:t>
+          <x:t xml:space="preserve">INVALID_CREDENTIALS／CAPTCHA_INVALID／PASSWORD_EXPIRED／VALIDATION_FAILED／網路／未知</x:t>
         </x:is>
       </x:c>
       <x:c r="I108" s="2" t="inlineStr">
@@ -13081,42 +13081,42 @@
     <x:row r="109">
       <x:c r="A109" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.66.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.63.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B109" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.66</x:t>
+          <x:t xml:space="preserve">4.4.1.8.63</x:t>
         </x:is>
       </x:c>
       <x:c r="C109" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Audit Log Query Interface</x:t>
+          <x:t xml:space="preserve">User Maintenance Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D109" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Date Range (Date inputs + quick buttons)</x:t>
+          <x:t xml:space="preserve">Keyword (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E109" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">開始／結束日期</x:t>
+          <x:t xml:space="preserve">搜尋帳號</x:t>
         </x:is>
       </x:c>
       <x:c r="F109" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">限制查詢期間</x:t>
+          <x:t xml:space="preserve">篩選列表</x:t>
         </x:is>
       </x:c>
       <x:c r="G109" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">yyyy-MM-dd</x:t>
+          <x:t xml:space="preserve">Text</x:t>
         </x:is>
       </x:c>
       <x:c r="H109" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">含頭尾；結束日不可早於開始日；快選今天、近 7、30 天</x:t>
+          <x:t xml:space="preserve">去除前後空白，不分大小寫</x:t>
         </x:is>
       </x:c>
       <x:c r="I109" s="2" t="inlineStr">
@@ -13138,42 +13138,42 @@
     <x:row r="110">
       <x:c r="A110" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.66.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.63.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B110" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.66</x:t>
+          <x:t xml:space="preserve">4.4.1.8.63</x:t>
         </x:is>
       </x:c>
       <x:c r="C110" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Audit Log Query Interface</x:t>
+          <x:t xml:space="preserve">User Maintenance Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D110" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Category (Dropdown)</x:t>
+          <x:t xml:space="preserve">Status (Tag)</x:t>
         </x:is>
       </x:c>
       <x:c r="E110" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">類別</x:t>
+          <x:t xml:space="preserve">狀態</x:t>
         </x:is>
       </x:c>
       <x:c r="F110" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">區分資料變更與安全事件</x:t>
+          <x:t xml:space="preserve">顯示啟用、鎖定、密碼過期</x:t>
         </x:is>
       </x:c>
       <x:c r="G110" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">DATA／SECURITY</x:t>
+          <x:t xml:space="preserve">Tag</x:t>
         </x:is>
       </x:c>
       <x:c r="H110" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">可清空</x:t>
+          <x:t xml:space="preserve">啟用／停用；已鎖定；密碼已過期</x:t>
         </x:is>
       </x:c>
       <x:c r="I110" s="2" t="inlineStr">
@@ -13195,42 +13195,42 @@
     <x:row r="111">
       <x:c r="A111" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.66.3</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.63.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B111" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.66</x:t>
+          <x:t xml:space="preserve">4.4.1.8.63</x:t>
         </x:is>
       </x:c>
       <x:c r="C111" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Audit Log Query Interface</x:t>
+          <x:t xml:space="preserve">User Maintenance Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D111" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Action (Dropdown)</x:t>
+          <x:t xml:space="preserve">Activate / Deactivate (Button)</x:t>
         </x:is>
       </x:c>
       <x:c r="E111" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">操作</x:t>
+          <x:t xml:space="preserve">啟用／停用</x:t>
         </x:is>
       </x:c>
       <x:c r="F111" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">依操作類型篩選</x:t>
+          <x:t xml:space="preserve">切換帳號狀態</x:t>
         </x:is>
       </x:c>
       <x:c r="G111" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">CREATE、UPDATE、DELETE、VOID、APPROVE、POST、LOGIN、LOGIN_FAILED、MASTER_CODE_LOGIN、LOGOUT、PERMISSION_CHANGE、EXPORT</x:t>
+          <x:t xml:space="preserve">Button</x:t>
         </x:is>
       </x:c>
       <x:c r="H111" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">可清空</x:t>
+          <x:t xml:space="preserve">帶讀取時的 version；不可停用自己</x:t>
         </x:is>
       </x:c>
       <x:c r="I111" s="2" t="inlineStr">
@@ -13252,47 +13252,47 @@
     <x:row r="112">
       <x:c r="A112" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.66.4</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.63.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B112" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.66</x:t>
+          <x:t xml:space="preserve">4.4.1.8.63</x:t>
         </x:is>
       </x:c>
       <x:c r="C112" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Audit Log Query Interface</x:t>
+          <x:t xml:space="preserve">User Maintenance Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D112" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Table / Record ID (Input)</x:t>
+          <x:t xml:space="preserve">Unlock (Button)</x:t>
         </x:is>
       </x:c>
       <x:c r="E112" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">資料表、記錄 ID</x:t>
+          <x:t xml:space="preserve">解鎖</x:t>
         </x:is>
       </x:c>
       <x:c r="F112" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">查看單據修改歷史</x:t>
+          <x:t xml:space="preserve">清除鎖定</x:t>
         </x:is>
       </x:c>
       <x:c r="G112" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Text</x:t>
+          <x:t xml:space="preserve">Button</x:t>
         </x:is>
       </x:c>
       <x:c r="H112" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">資料表最多 128 字元、記錄 ID 最多 100 字元；去除前後空白</x:t>
+          <x:t xml:space="preserve">只在已鎖定時顯示</x:t>
         </x:is>
       </x:c>
       <x:c r="I112" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.66.6</x:t>
+          <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
       <x:c r="J112" s="2" t="inlineStr">
@@ -13309,47 +13309,47 @@
     <x:row r="113">
       <x:c r="A113" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.66.5</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.63.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B113" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.66</x:t>
+          <x:t xml:space="preserve">4.4.1.8.63</x:t>
         </x:is>
       </x:c>
       <x:c r="C113" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Audit Log Query Interface</x:t>
+          <x:t xml:space="preserve">User Maintenance Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D113" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Changes (Expandable row)</x:t>
+          <x:t xml:space="preserve">Reset Password (Button)</x:t>
         </x:is>
       </x:c>
       <x:c r="E113" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">欄位差異</x:t>
+          <x:t xml:space="preserve">重設密碼</x:t>
         </x:is>
       </x:c>
       <x:c r="F113" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">顯示修改前後的值</x:t>
+          <x:t xml:space="preserve">開啟重設對話框</x:t>
         </x:is>
       </x:c>
       <x:c r="G113" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">欄位／修改前／修改後</x:t>
+          <x:t xml:space="preserve">Button</x:t>
         </x:is>
       </x:c>
       <x:c r="H113" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">敏感欄位顯示 *；空值顯示「（空）」</x:t>
+          <x:t xml:space="preserve">新密碼依政策驗證，成功後清除鎖定並重新起算到期</x:t>
         </x:is>
       </x:c>
       <x:c r="I113" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">None</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.61.2</x:t>
         </x:is>
       </x:c>
       <x:c r="J113" s="2" t="inlineStr">
@@ -13366,47 +13366,47 @@
     <x:row r="114">
       <x:c r="A114" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.66.6</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.64.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B114" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.66</x:t>
+          <x:t xml:space="preserve">4.4.1.8.64</x:t>
         </x:is>
       </x:c>
       <x:c r="C114" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Audit Log Query Interface</x:t>
+          <x:t xml:space="preserve">Role Maintenance Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D114" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Record History (Link / query string)</x:t>
+          <x:t xml:space="preserve">Role Code (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E114" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">修改歷史</x:t>
+          <x:t xml:space="preserve">角色代碼</x:t>
         </x:is>
       </x:c>
       <x:c r="F114" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">由單據或列開啟單筆記錄歷史</x:t>
+          <x:t xml:space="preserve">全系統唯一識別角色</x:t>
         </x:is>
       </x:c>
       <x:c r="G114" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">?tableName=&amp;recordId=</x:t>
+          <x:t xml:space="preserve">VARCHAR(50)</x:t>
         </x:is>
       </x:c>
       <x:c r="H114" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">安全事件沒有記錄 ID，不可開啟</x:t>
+          <x:t xml:space="preserve">1–50 字元；ASCII 英文、數字、-、_；保存為大寫；建立後不可修改</x:t>
         </x:is>
       </x:c>
       <x:c r="I114" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.66.4</x:t>
+          <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
       <x:c r="J114" s="2" t="inlineStr">
@@ -13423,42 +13423,42 @@
     <x:row r="115">
       <x:c r="A115" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.67.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.64.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B115" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.67</x:t>
+          <x:t xml:space="preserve">4.4.1.8.64</x:t>
         </x:is>
       </x:c>
       <x:c r="C115" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Document Number Rule Interface</x:t>
+          <x:t xml:space="preserve">Role Maintenance Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D115" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Document Type (Input)</x:t>
+          <x:t xml:space="preserve">Role Name (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E115" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">單據類型</x:t>
+          <x:t xml:space="preserve">角色名稱</x:t>
         </x:is>
       </x:c>
       <x:c r="F115" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">識別規則所屬單據</x:t>
+          <x:t xml:space="preserve">顯示角色</x:t>
         </x:is>
       </x:c>
       <x:c r="G115" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">{PREFIX}.{DOCUMENT}，例如 SD.ORDER</x:t>
+          <x:t xml:space="preserve">NVARCHAR(200)</x:t>
         </x:is>
       </x:c>
       <x:c r="H115" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">英文字母、數字、底線，最多 50 字；保存為大寫；公司內唯一；建立後不可修改</x:t>
+          <x:t xml:space="preserve">去除空白後 1–200 字元</x:t>
         </x:is>
       </x:c>
       <x:c r="I115" s="2" t="inlineStr">
@@ -13480,42 +13480,42 @@
     <x:row r="116">
       <x:c r="A116" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.67.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.64.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B116" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.67</x:t>
+          <x:t xml:space="preserve">4.4.1.8.64</x:t>
         </x:is>
       </x:c>
       <x:c r="C116" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Document Number Rule Interface</x:t>
+          <x:t xml:space="preserve">Role Maintenance Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D116" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Name (Input)</x:t>
+          <x:t xml:space="preserve">Data Scope (Dropdown)</x:t>
         </x:is>
       </x:c>
       <x:c r="E116" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">名稱</x:t>
+          <x:t xml:space="preserve">資料範圍</x:t>
         </x:is>
       </x:c>
       <x:c r="F116" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">規則說明</x:t>
+          <x:t xml:space="preserve">決定可見單據範圍</x:t>
         </x:is>
       </x:c>
       <x:c r="G116" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Text</x:t>
+          <x:t xml:space="preserve">Self／Department／Branch／Company</x:t>
         </x:is>
       </x:c>
       <x:c r="H116" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1–100 字元，去除前後空白</x:t>
+          <x:t xml:space="preserve">必選，預設本人</x:t>
         </x:is>
       </x:c>
       <x:c r="I116" s="2" t="inlineStr">
@@ -13537,47 +13537,47 @@
     <x:row r="117">
       <x:c r="A117" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.67.3</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.64.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B117" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.67</x:t>
+          <x:t xml:space="preserve">4.4.1.8.64</x:t>
         </x:is>
       </x:c>
       <x:c r="C117" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Document Number Rule Interface</x:t>
+          <x:t xml:space="preserve">Role Maintenance Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D117" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Prefix (Input)</x:t>
+          <x:t xml:space="preserve">Full Access (Checkbox)</x:t>
         </x:is>
       </x:c>
       <x:c r="E117" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">前綴</x:t>
+          <x:t xml:space="preserve">全權</x:t>
         </x:is>
       </x:c>
       <x:c r="F117" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">單號開頭</x:t>
+          <x:t xml:space="preserve">擁有全部權限</x:t>
         </x:is>
       </x:c>
       <x:c r="G117" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Text</x:t>
+          <x:t xml:space="preserve">Boolean</x:t>
         </x:is>
       </x:c>
       <x:c r="H117" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">0–10 個英數字、-、_；保存為大寫</x:t>
+          <x:t xml:space="preserve">勾選時權限清單停用</x:t>
         </x:is>
       </x:c>
       <x:c r="I117" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.67.7</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.64.5</x:t>
         </x:is>
       </x:c>
       <x:c r="J117" s="2" t="inlineStr">
@@ -13594,47 +13594,47 @@
     <x:row r="118">
       <x:c r="A118" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.67.4</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.64.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B118" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.67</x:t>
+          <x:t xml:space="preserve">4.4.1.8.64</x:t>
         </x:is>
       </x:c>
       <x:c r="C118" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Document Number Rule Interface</x:t>
+          <x:t xml:space="preserve">Role Maintenance Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D118" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Date Format (Dropdown)</x:t>
+          <x:t xml:space="preserve">Permissions (Checkbox group)</x:t>
         </x:is>
       </x:c>
       <x:c r="E118" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">日期格式</x:t>
+          <x:t xml:space="preserve">權限</x:t>
         </x:is>
       </x:c>
       <x:c r="F118" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">單號的日期部分</x:t>
+          <x:t xml:space="preserve">依模組勾選權限代碼</x:t>
         </x:is>
       </x:c>
       <x:c r="G118" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">None／yyyy／yyyyMM／yyyyMMdd／yyMM／yyMMdd</x:t>
+          <x:t xml:space="preserve">模組.資源.動作</x:t>
         </x:is>
       </x:c>
       <x:c r="H118" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">已發號時不可修改</x:t>
+          <x:t xml:space="preserve">只可選權限目錄內的代碼；模組可全選</x:t>
         </x:is>
       </x:c>
       <x:c r="I118" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.67.6</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.64.4</x:t>
         </x:is>
       </x:c>
       <x:c r="J118" s="2" t="inlineStr">
@@ -13651,47 +13651,47 @@
     <x:row r="119">
       <x:c r="A119" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.67.5</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.64.6</x:t>
         </x:is>
       </x:c>
       <x:c r="B119" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.67</x:t>
+          <x:t xml:space="preserve">4.4.1.8.64</x:t>
         </x:is>
       </x:c>
       <x:c r="C119" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Document Number Rule Interface</x:t>
+          <x:t xml:space="preserve">Role Maintenance Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D119" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Sequence Length (Number)</x:t>
+          <x:t xml:space="preserve">Delete (Button)</x:t>
         </x:is>
       </x:c>
       <x:c r="E119" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">流水號長度</x:t>
+          <x:t xml:space="preserve">刪除</x:t>
         </x:is>
       </x:c>
       <x:c r="F119" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">補零位數</x:t>
+          <x:t xml:space="preserve">軟刪除未使用的角色</x:t>
         </x:is>
       </x:c>
       <x:c r="G119" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">整數</x:t>
+          <x:t xml:space="preserve">Button + popconfirm</x:t>
         </x:is>
       </x:c>
       <x:c r="H119" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">3–10；已發號時不可小於原長度</x:t>
+          <x:t xml:space="preserve">帶 version；使用中回 SYS.ROLE.IN_USE</x:t>
         </x:is>
       </x:c>
       <x:c r="I119" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.67.7</x:t>
+          <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
       <x:c r="J119" s="2" t="inlineStr">
@@ -13708,47 +13708,47 @@
     <x:row r="120">
       <x:c r="A120" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.67.6</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.65.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B120" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.67</x:t>
+          <x:t xml:space="preserve">4.4.1.8.65</x:t>
         </x:is>
       </x:c>
       <x:c r="C120" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Document Number Rule Interface</x:t>
+          <x:t xml:space="preserve">User Permission Edit Interface（BlueWhale 4.4.1.8.26）</x:t>
         </x:is>
       </x:c>
       <x:c r="D120" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Reset Period (Dropdown)</x:t>
+          <x:t xml:space="preserve">Company (Dropdown)</x:t>
         </x:is>
       </x:c>
       <x:c r="E120" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">重設週期</x:t>
+          <x:t xml:space="preserve">公司</x:t>
         </x:is>
       </x:c>
       <x:c r="F120" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">流水號歸 1 的時機</x:t>
+          <x:t xml:space="preserve">選擇要設定的公司</x:t>
         </x:is>
       </x:c>
       <x:c r="G120" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">不重設／每年／每月／每日</x:t>
+          <x:t xml:space="preserve">bigint ID</x:t>
         </x:is>
       </x:c>
       <x:c r="H120" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">必須包含在日期格式內；已發號時不可修改</x:t>
+          <x:t xml:space="preserve">操作者可切換的公司</x:t>
         </x:is>
       </x:c>
       <x:c r="I120" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.67.4</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.65.2</x:t>
         </x:is>
       </x:c>
       <x:c r="J120" s="2" t="inlineStr">
@@ -13765,47 +13765,47 @@
     <x:row r="121">
       <x:c r="A121" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.67.7</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.65.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B121" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.67</x:t>
+          <x:t xml:space="preserve">4.4.1.8.65</x:t>
         </x:is>
       </x:c>
       <x:c r="C121" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Document Number Rule Interface</x:t>
+          <x:t xml:space="preserve">User Permission Edit Interface（BlueWhale 4.4.1.8.26）</x:t>
         </x:is>
       </x:c>
       <x:c r="D121" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Sample (Text)</x:t>
+          <x:t xml:space="preserve">Branch / Department (Dropdown)</x:t>
         </x:is>
       </x:c>
       <x:c r="E121" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">樣式</x:t>
+          <x:t xml:space="preserve">分店／部門</x:t>
         </x:is>
       </x:c>
       <x:c r="F121" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">即時顯示今天第 1 號</x:t>
+          <x:t xml:space="preserve">組織歸屬（資料範圍用）</x:t>
         </x:is>
       </x:c>
       <x:c r="G121" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">前綴＋日期＋補零流水號</x:t>
+          <x:t xml:space="preserve">bigint ID，可清空</x:t>
         </x:is>
       </x:c>
       <x:c r="H121" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">唯讀</x:t>
+          <x:t xml:space="preserve">所選公司的啟用分店／部門</x:t>
         </x:is>
       </x:c>
       <x:c r="I121" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.67.3</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.65.1</x:t>
         </x:is>
       </x:c>
       <x:c r="J121" s="2" t="inlineStr">
@@ -13822,42 +13822,42 @@
     <x:row r="122">
       <x:c r="A122" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.67.8</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.65.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B122" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.67</x:t>
+          <x:t xml:space="preserve">4.4.1.8.65</x:t>
         </x:is>
       </x:c>
       <x:c r="C122" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Document Number Rule Interface</x:t>
+          <x:t xml:space="preserve">User Permission Edit Interface（BlueWhale 4.4.1.8.26）</x:t>
         </x:is>
       </x:c>
       <x:c r="D122" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Active (Checkbox)</x:t>
+          <x:t xml:space="preserve">Roles (Multi-select)</x:t>
         </x:is>
       </x:c>
       <x:c r="E122" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">啟用</x:t>
+          <x:t xml:space="preserve">角色</x:t>
         </x:is>
       </x:c>
       <x:c r="F122" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">停用後各模組不可再取號</x:t>
+          <x:t xml:space="preserve">整組取代該公司的角色</x:t>
         </x:is>
       </x:c>
       <x:c r="G122" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Boolean</x:t>
+          <x:t xml:space="preserve">bigint ID 陣列</x:t>
         </x:is>
       </x:c>
       <x:c r="H122" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">只在編輯時顯示</x:t>
+          <x:t xml:space="preserve">啟用角色；可為空（無權限）</x:t>
         </x:is>
       </x:c>
       <x:c r="I122" s="2" t="inlineStr">
@@ -13879,42 +13879,42 @@
     <x:row r="123">
       <x:c r="A123" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.67.9</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.65.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B123" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.67</x:t>
+          <x:t xml:space="preserve">4.4.1.8.65</x:t>
         </x:is>
       </x:c>
       <x:c r="C123" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Document Number Rule Interface</x:t>
+          <x:t xml:space="preserve">User Permission Edit Interface（BlueWhale 4.4.1.8.26）</x:t>
         </x:is>
       </x:c>
       <x:c r="D123" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Preview Date (Date input)</x:t>
+          <x:t xml:space="preserve">Default Company (Checkbox)</x:t>
         </x:is>
       </x:c>
       <x:c r="E123" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">單據日期</x:t>
+          <x:t xml:space="preserve">預設公司</x:t>
         </x:is>
       </x:c>
       <x:c r="F123" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">預覽該日期的下一個單號</x:t>
+          <x:t xml:space="preserve">登入後預設的操作公司</x:t>
         </x:is>
       </x:c>
       <x:c r="G123" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">yyyy-MM-dd</x:t>
+          <x:t xml:space="preserve">Boolean</x:t>
         </x:is>
       </x:c>
       <x:c r="H123" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">預設今天；可清空（後端用今天）；不佔號</x:t>
+          <x:t xml:space="preserve">設定後取消其他預設</x:t>
         </x:is>
       </x:c>
       <x:c r="I123" s="2" t="inlineStr">
@@ -13936,42 +13936,42 @@
     <x:row r="124">
       <x:c r="A124" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.68.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.65.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B124" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.68</x:t>
+          <x:t xml:space="preserve">4.4.1.8.65</x:t>
         </x:is>
       </x:c>
       <x:c r="C124" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Approval Flow Maintenance Interface</x:t>
+          <x:t xml:space="preserve">User Permission Edit Interface（BlueWhale 4.4.1.8.26）</x:t>
         </x:is>
       </x:c>
       <x:c r="D124" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Document Type (Input)</x:t>
+          <x:t xml:space="preserve">Access Active (Checkbox)</x:t>
         </x:is>
       </x:c>
       <x:c r="E124" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">單據類型</x:t>
+          <x:t xml:space="preserve">啟用存取</x:t>
         </x:is>
       </x:c>
       <x:c r="F124" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">流程所屬單據</x:t>
+          <x:t xml:space="preserve">停用後該公司不授權</x:t>
         </x:is>
       </x:c>
       <x:c r="G124" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">{PREFIX}.{DOCUMENT}，例如 PUR.ORDER</x:t>
+          <x:t xml:space="preserve">Boolean</x:t>
         </x:is>
       </x:c>
       <x:c r="H124" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">英文字母、數字、底線，最多 50 字；保存為大寫；公司內唯一；建立後不可修改</x:t>
+          <x:t xml:space="preserve">不可停用自己</x:t>
         </x:is>
       </x:c>
       <x:c r="I124" s="2" t="inlineStr">
@@ -13993,42 +13993,42 @@
     <x:row r="125">
       <x:c r="A125" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.68.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.66.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B125" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.68</x:t>
+          <x:t xml:space="preserve">4.4.1.8.66</x:t>
         </x:is>
       </x:c>
       <x:c r="C125" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Approval Flow Maintenance Interface</x:t>
+          <x:t xml:space="preserve">Audit Log Query Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D125" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Flow Name (Input)</x:t>
+          <x:t xml:space="preserve">Date Range (Date inputs + quick buttons)</x:t>
         </x:is>
       </x:c>
       <x:c r="E125" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">流程名稱</x:t>
+          <x:t xml:space="preserve">開始／結束日期</x:t>
         </x:is>
       </x:c>
       <x:c r="F125" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">流程說明</x:t>
+          <x:t xml:space="preserve">限制查詢期間</x:t>
         </x:is>
       </x:c>
       <x:c r="G125" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Text</x:t>
+          <x:t xml:space="preserve">yyyy-MM-dd</x:t>
         </x:is>
       </x:c>
       <x:c r="H125" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1–100 字元，去除前後空白</x:t>
+          <x:t xml:space="preserve">含頭尾；結束日不可早於開始日；快選今天、近 7、30 天</x:t>
         </x:is>
       </x:c>
       <x:c r="I125" s="2" t="inlineStr">
@@ -14050,42 +14050,42 @@
     <x:row r="126">
       <x:c r="A126" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.68.3</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.66.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B126" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.68</x:t>
+          <x:t xml:space="preserve">4.4.1.8.66</x:t>
         </x:is>
       </x:c>
       <x:c r="C126" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Approval Flow Maintenance Interface</x:t>
+          <x:t xml:space="preserve">Audit Log Query Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D126" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Allow Self-approval (Checkbox)</x:t>
+          <x:t xml:space="preserve">Category (Dropdown)</x:t>
         </x:is>
       </x:c>
       <x:c r="E126" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">允許自審</x:t>
+          <x:t xml:space="preserve">類別</x:t>
         </x:is>
       </x:c>
       <x:c r="F126" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">送審人可否審批自己的單據</x:t>
+          <x:t xml:space="preserve">區分資料變更與安全事件</x:t>
         </x:is>
       </x:c>
       <x:c r="G126" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Boolean</x:t>
+          <x:t xml:space="preserve">DATA／SECURITY</x:t>
         </x:is>
       </x:c>
       <x:c r="H126" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">預設否</x:t>
+          <x:t xml:space="preserve">可清空</x:t>
         </x:is>
       </x:c>
       <x:c r="I126" s="2" t="inlineStr">
@@ -14107,42 +14107,42 @@
     <x:row r="127">
       <x:c r="A127" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.68.4</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.66.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B127" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.68</x:t>
+          <x:t xml:space="preserve">4.4.1.8.66</x:t>
         </x:is>
       </x:c>
       <x:c r="C127" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Approval Flow Maintenance Interface</x:t>
+          <x:t xml:space="preserve">Audit Log Query Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D127" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Step Name (Input)</x:t>
+          <x:t xml:space="preserve">Action (Dropdown)</x:t>
         </x:is>
       </x:c>
       <x:c r="E127" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">步驟名稱</x:t>
+          <x:t xml:space="preserve">操作</x:t>
         </x:is>
       </x:c>
       <x:c r="F127" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">顯示於待辦與記錄</x:t>
+          <x:t xml:space="preserve">依操作類型篩選</x:t>
         </x:is>
       </x:c>
       <x:c r="G127" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Text</x:t>
+          <x:t xml:space="preserve">CREATE、UPDATE、DELETE、VOID、APPROVE、POST、LOGIN、LOGIN_FAILED、MASTER_CODE_LOGIN、LOGOUT、PERMISSION_CHANGE、EXPORT</x:t>
         </x:is>
       </x:c>
       <x:c r="H127" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1–100 字元</x:t>
+          <x:t xml:space="preserve">可清空</x:t>
         </x:is>
       </x:c>
       <x:c r="I127" s="2" t="inlineStr">
@@ -14164,47 +14164,47 @@
     <x:row r="128">
       <x:c r="A128" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.68.5</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.66.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B128" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.68</x:t>
+          <x:t xml:space="preserve">4.4.1.8.66</x:t>
         </x:is>
       </x:c>
       <x:c r="C128" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Approval Flow Maintenance Interface</x:t>
+          <x:t xml:space="preserve">Audit Log Query Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D128" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Approver Type (Dropdown)</x:t>
+          <x:t xml:space="preserve">Table / Record ID (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E128" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">審批人類型</x:t>
+          <x:t xml:space="preserve">資料表、記錄 ID</x:t>
         </x:is>
       </x:c>
       <x:c r="F128" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">角色或指定用戶</x:t>
+          <x:t xml:space="preserve">查看單據修改歷史</x:t>
         </x:is>
       </x:c>
       <x:c r="G128" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Role／User</x:t>
+          <x:t xml:space="preserve">Text</x:t>
         </x:is>
       </x:c>
       <x:c r="H128" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">必填</x:t>
+          <x:t xml:space="preserve">資料表最多 128 字元、記錄 ID 最多 100 字元；去除前後空白</x:t>
         </x:is>
       </x:c>
       <x:c r="I128" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.68.6</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.66.6</x:t>
         </x:is>
       </x:c>
       <x:c r="J128" s="2" t="inlineStr">
@@ -14221,47 +14221,47 @@
     <x:row r="129">
       <x:c r="A129" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.68.6</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.66.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B129" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.68</x:t>
+          <x:t xml:space="preserve">4.4.1.8.66</x:t>
         </x:is>
       </x:c>
       <x:c r="C129" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Approval Flow Maintenance Interface</x:t>
+          <x:t xml:space="preserve">Audit Log Query Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D129" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Approver (Dropdown)</x:t>
+          <x:t xml:space="preserve">Changes (Expandable row)</x:t>
         </x:is>
       </x:c>
       <x:c r="E129" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">審批人</x:t>
+          <x:t xml:space="preserve">欄位差異</x:t>
         </x:is>
       </x:c>
       <x:c r="F129" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">處理該步驟的角色或用戶</x:t>
+          <x:t xml:space="preserve">顯示修改前後的值</x:t>
         </x:is>
       </x:c>
       <x:c r="G129" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">bigint ID</x:t>
+          <x:t xml:space="preserve">欄位／修改前／修改後</x:t>
         </x:is>
       </x:c>
       <x:c r="H129" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">啟用角色或本公司啟用用戶</x:t>
+          <x:t xml:space="preserve">敏感欄位顯示 *；空值顯示「（空）」</x:t>
         </x:is>
       </x:c>
       <x:c r="I129" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.68.5</x:t>
+          <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
       <x:c r="J129" s="2" t="inlineStr">
@@ -14278,47 +14278,47 @@
     <x:row r="130">
       <x:c r="A130" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.68.7</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.66.6</x:t>
         </x:is>
       </x:c>
       <x:c r="B130" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.68</x:t>
+          <x:t xml:space="preserve">4.4.1.8.66</x:t>
         </x:is>
       </x:c>
       <x:c r="C130" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Approval Flow Maintenance Interface</x:t>
+          <x:t xml:space="preserve">Audit Log Query Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D130" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Minimum Amount (Input)</x:t>
+          <x:t xml:space="preserve">Record History (Link / query string)</x:t>
         </x:is>
       </x:c>
       <x:c r="E130" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">最低金額</x:t>
+          <x:t xml:space="preserve">修改歷史</x:t>
         </x:is>
       </x:c>
       <x:c r="F130" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">金額門檻（本位幣）</x:t>
+          <x:t xml:space="preserve">由單據或列開啟單筆記錄歷史</x:t>
         </x:is>
       </x:c>
       <x:c r="G130" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">數字</x:t>
+          <x:t xml:space="preserve">?tableName=&amp;recordId=</x:t>
         </x:is>
       </x:c>
       <x:c r="H130" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">選填；≥ 0，最多 11 位整數、4 位小數</x:t>
+          <x:t xml:space="preserve">安全事件沒有記錄 ID，不可開啟</x:t>
         </x:is>
       </x:c>
       <x:c r="I130" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">None</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.66.4</x:t>
         </x:is>
       </x:c>
       <x:c r="J130" s="2" t="inlineStr">
@@ -14335,42 +14335,42 @@
     <x:row r="131">
       <x:c r="A131" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.68.8</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.67.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B131" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.68</x:t>
+          <x:t xml:space="preserve">4.4.1.8.67</x:t>
         </x:is>
       </x:c>
       <x:c r="C131" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Approval Flow Maintenance Interface</x:t>
+          <x:t xml:space="preserve">Document Number Rule Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D131" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Active (Checkbox)</x:t>
+          <x:t xml:space="preserve">Document Type (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E131" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">啟用</x:t>
+          <x:t xml:space="preserve">單據類型</x:t>
         </x:is>
       </x:c>
       <x:c r="F131" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">停用後送審自動核准</x:t>
+          <x:t xml:space="preserve">識別規則所屬單據</x:t>
         </x:is>
       </x:c>
       <x:c r="G131" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Boolean</x:t>
+          <x:t xml:space="preserve">{PREFIX}.{DOCUMENT}，例如 SD.ORDER</x:t>
         </x:is>
       </x:c>
       <x:c r="H131" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">只在編輯時顯示</x:t>
+          <x:t xml:space="preserve">英文字母、數字、底線，最多 50 字；保存為大寫；公司內唯一；建立後不可修改</x:t>
         </x:is>
       </x:c>
       <x:c r="I131" s="2" t="inlineStr">
@@ -14392,47 +14392,47 @@
     <x:row r="132">
       <x:c r="A132" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.69.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.67.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B132" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.69</x:t>
+          <x:t xml:space="preserve">4.4.1.8.67</x:t>
         </x:is>
       </x:c>
       <x:c r="C132" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Approval Delegation Interface</x:t>
+          <x:t xml:space="preserve">Document Number Rule Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D132" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Delegator (Dropdown)</x:t>
+          <x:t xml:space="preserve">Name (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E132" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">被代理人</x:t>
+          <x:t xml:space="preserve">名稱</x:t>
         </x:is>
       </x:c>
       <x:c r="F132" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">交出審批工作的用戶</x:t>
+          <x:t xml:space="preserve">規則說明</x:t>
         </x:is>
       </x:c>
       <x:c r="G132" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">bigint ID</x:t>
+          <x:t xml:space="preserve">Text</x:t>
         </x:is>
       </x:c>
       <x:c r="H132" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">本公司啟用用戶；建立後不可修改</x:t>
+          <x:t xml:space="preserve">1–100 字元，去除前後空白</x:t>
         </x:is>
       </x:c>
       <x:c r="I132" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.69.2</x:t>
+          <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
       <x:c r="J132" s="2" t="inlineStr">
@@ -14449,47 +14449,47 @@
     <x:row r="133">
       <x:c r="A133" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.69.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.67.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B133" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.69</x:t>
+          <x:t xml:space="preserve">4.4.1.8.67</x:t>
         </x:is>
       </x:c>
       <x:c r="C133" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Approval Delegation Interface</x:t>
+          <x:t xml:space="preserve">Document Number Rule Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D133" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Delegate (Dropdown)</x:t>
+          <x:t xml:space="preserve">Prefix (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E133" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">代理人</x:t>
+          <x:t xml:space="preserve">前綴</x:t>
         </x:is>
       </x:c>
       <x:c r="F133" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">代為審批的用戶</x:t>
+          <x:t xml:space="preserve">單號開頭</x:t>
         </x:is>
       </x:c>
       <x:c r="G133" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">bigint ID</x:t>
+          <x:t xml:space="preserve">Text</x:t>
         </x:is>
       </x:c>
       <x:c r="H133" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">本公司啟用用戶，不可與被代理人相同；建立後不可修改</x:t>
+          <x:t xml:space="preserve">0–10 個英數字、-、_；保存為大寫</x:t>
         </x:is>
       </x:c>
       <x:c r="I133" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.69.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.67.7</x:t>
         </x:is>
       </x:c>
       <x:c r="J133" s="2" t="inlineStr">
@@ -14506,47 +14506,47 @@
     <x:row r="134">
       <x:c r="A134" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.69.3</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.67.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B134" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.69</x:t>
+          <x:t xml:space="preserve">4.4.1.8.67</x:t>
         </x:is>
       </x:c>
       <x:c r="C134" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Approval Delegation Interface</x:t>
+          <x:t xml:space="preserve">Document Number Rule Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D134" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Start / End Date (Date input)</x:t>
+          <x:t xml:space="preserve">Date Format (Dropdown)</x:t>
         </x:is>
       </x:c>
       <x:c r="E134" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">開始／結束日期</x:t>
+          <x:t xml:space="preserve">日期格式</x:t>
         </x:is>
       </x:c>
       <x:c r="F134" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">代理期間（含頭尾）</x:t>
+          <x:t xml:space="preserve">單號的日期部分</x:t>
         </x:is>
       </x:c>
       <x:c r="G134" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">yyyy-MM-dd</x:t>
+          <x:t xml:space="preserve">None／yyyy／yyyyMM／yyyyMMdd／yyMM／yyMMdd</x:t>
         </x:is>
       </x:c>
       <x:c r="H134" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">結束不早於開始；同一被代理人的啟用期間不可重疊</x:t>
+          <x:t xml:space="preserve">已發號時不可修改</x:t>
         </x:is>
       </x:c>
       <x:c r="I134" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">None</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.67.6</x:t>
         </x:is>
       </x:c>
       <x:c r="J134" s="2" t="inlineStr">
@@ -14563,47 +14563,47 @@
     <x:row r="135">
       <x:c r="A135" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.69.4</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.67.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B135" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.69</x:t>
+          <x:t xml:space="preserve">4.4.1.8.67</x:t>
         </x:is>
       </x:c>
       <x:c r="C135" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Approval Delegation Interface</x:t>
+          <x:t xml:space="preserve">Document Number Rule Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D135" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Remark (Textarea)</x:t>
+          <x:t xml:space="preserve">Sequence Length (Number)</x:t>
         </x:is>
       </x:c>
       <x:c r="E135" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">備註</x:t>
+          <x:t xml:space="preserve">流水號長度</x:t>
         </x:is>
       </x:c>
       <x:c r="F135" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">代理原因</x:t>
+          <x:t xml:space="preserve">補零位數</x:t>
         </x:is>
       </x:c>
       <x:c r="G135" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Text</x:t>
+          <x:t xml:space="preserve">整數</x:t>
         </x:is>
       </x:c>
       <x:c r="H135" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">0–200 字元</x:t>
+          <x:t xml:space="preserve">3–10；已發號時不可小於原長度</x:t>
         </x:is>
       </x:c>
       <x:c r="I135" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">None</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.67.7</x:t>
         </x:is>
       </x:c>
       <x:c r="J135" s="2" t="inlineStr">
@@ -14620,47 +14620,47 @@
     <x:row r="136">
       <x:c r="A136" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.70.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.67.6</x:t>
         </x:is>
       </x:c>
       <x:c r="B136" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.70</x:t>
+          <x:t xml:space="preserve">4.4.1.8.67</x:t>
         </x:is>
       </x:c>
       <x:c r="C136" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Approval Inbox Interface</x:t>
+          <x:t xml:space="preserve">Document Number Rule Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D136" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Comment (Textarea)</x:t>
+          <x:t xml:space="preserve">Reset Period (Dropdown)</x:t>
         </x:is>
       </x:c>
       <x:c r="E136" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">意見</x:t>
+          <x:t xml:space="preserve">重設週期</x:t>
         </x:is>
       </x:c>
       <x:c r="F136" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">核准或駁回的說明</x:t>
+          <x:t xml:space="preserve">流水號歸 1 的時機</x:t>
         </x:is>
       </x:c>
       <x:c r="G136" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Text</x:t>
+          <x:t xml:space="preserve">不重設／每年／每月／每日</x:t>
         </x:is>
       </x:c>
       <x:c r="H136" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">0–500 字元；駁回必填</x:t>
+          <x:t xml:space="preserve">必須包含在日期格式內；已發號時不可修改</x:t>
         </x:is>
       </x:c>
       <x:c r="I136" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">None</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.67.4</x:t>
         </x:is>
       </x:c>
       <x:c r="J136" s="2" t="inlineStr">
@@ -14677,47 +14677,47 @@
     <x:row r="137">
       <x:c r="A137" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.70.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.67.7</x:t>
         </x:is>
       </x:c>
       <x:c r="B137" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.70</x:t>
+          <x:t xml:space="preserve">4.4.1.8.67</x:t>
         </x:is>
       </x:c>
       <x:c r="C137" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Approval Inbox Interface</x:t>
+          <x:t xml:space="preserve">Document Number Rule Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D137" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Status Filter (Dropdown)</x:t>
+          <x:t xml:space="preserve">Sample (Text)</x:t>
         </x:is>
       </x:c>
       <x:c r="E137" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">狀態</x:t>
+          <x:t xml:space="preserve">樣式</x:t>
         </x:is>
       </x:c>
       <x:c r="F137" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">篩選審批歷史</x:t>
+          <x:t xml:space="preserve">即時顯示今天第 1 號</x:t>
         </x:is>
       </x:c>
       <x:c r="G137" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">審批中／已核准／已駁回／已撤回</x:t>
+          <x:t xml:space="preserve">前綴＋日期＋補零流水號</x:t>
         </x:is>
       </x:c>
       <x:c r="H137" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">可清除</x:t>
+          <x:t xml:space="preserve">唯讀</x:t>
         </x:is>
       </x:c>
       <x:c r="I137" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">None</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.67.3</x:t>
         </x:is>
       </x:c>
       <x:c r="J137" s="2" t="inlineStr">
@@ -14734,42 +14734,42 @@
     <x:row r="138">
       <x:c r="A138" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.71.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.67.8</x:t>
         </x:is>
       </x:c>
       <x:c r="B138" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.71</x:t>
+          <x:t xml:space="preserve">4.4.1.8.67</x:t>
         </x:is>
       </x:c>
       <x:c r="C138" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Confirmation / Prompt Box Interface（BlueWhale 4.4.1.9）</x:t>
+          <x:t xml:space="preserve">Document Number Rule Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D138" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">OK / Cancel (Button)</x:t>
+          <x:t xml:space="preserve">Active (Checkbox)</x:t>
         </x:is>
       </x:c>
       <x:c r="E138" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">確定／取消</x:t>
+          <x:t xml:space="preserve">啟用</x:t>
         </x:is>
       </x:c>
       <x:c r="F138" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">確認或放棄動作</x:t>
+          <x:t xml:space="preserve">停用後各模組不可再取號</x:t>
         </x:is>
       </x:c>
       <x:c r="G138" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Button</x:t>
+          <x:t xml:space="preserve">Boolean</x:t>
         </x:is>
       </x:c>
       <x:c r="H138" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">確認框兩個按鈕，提示框只有確定；Esc 等同取消</x:t>
+          <x:t xml:space="preserve">只在編輯時顯示</x:t>
         </x:is>
       </x:c>
       <x:c r="I138" s="2" t="inlineStr">
@@ -14791,42 +14791,42 @@
     <x:row r="139">
       <x:c r="A139" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.72.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.67.9</x:t>
         </x:is>
       </x:c>
       <x:c r="B139" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.72</x:t>
+          <x:t xml:space="preserve">4.4.1.8.67</x:t>
         </x:is>
       </x:c>
       <x:c r="C139" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Select Dialog Interface（BlueWhale 4.4.1.9 Select Client / Supplier / Item）</x:t>
+          <x:t xml:space="preserve">Document Number Rule Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D139" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Keyword (Input)</x:t>
+          <x:t xml:space="preserve">Preview Date (Date input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E139" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">關鍵字</x:t>
+          <x:t xml:space="preserve">單據日期</x:t>
         </x:is>
       </x:c>
       <x:c r="F139" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">搜尋主檔</x:t>
+          <x:t xml:space="preserve">預覽該日期的下一個單號</x:t>
         </x:is>
       </x:c>
       <x:c r="G139" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Text</x:t>
+          <x:t xml:space="preserve">yyyy-MM-dd</x:t>
         </x:is>
       </x:c>
       <x:c r="H139" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">去除前後空白；查詢回到第 1 頁</x:t>
+          <x:t xml:space="preserve">預設今天；可清空（後端用今天）；不佔號</x:t>
         </x:is>
       </x:c>
       <x:c r="I139" s="2" t="inlineStr">
@@ -14848,47 +14848,47 @@
     <x:row r="140">
       <x:c r="A140" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.72.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.68.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B140" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.72</x:t>
+          <x:t xml:space="preserve">4.4.1.8.68</x:t>
         </x:is>
       </x:c>
       <x:c r="C140" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Select Dialog Interface（BlueWhale 4.4.1.9 Select Client / Supplier / Item）</x:t>
+          <x:t xml:space="preserve">Approval Flow Maintenance Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D140" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Selection (Checkbox / Row)</x:t>
+          <x:t xml:space="preserve">Document Type (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E140" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">選取</x:t>
+          <x:t xml:space="preserve">單據類型</x:t>
         </x:is>
       </x:c>
       <x:c r="F140" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">選擇主檔資料</x:t>
+          <x:t xml:space="preserve">流程所屬單據</x:t>
         </x:is>
       </x:c>
       <x:c r="G140" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Row key</x:t>
+          <x:t xml:space="preserve">{PREFIX}.{DOCUMENT}，例如 PUR.ORDER</x:t>
         </x:is>
       </x:c>
       <x:c r="H140" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">單選 1 筆、多選跨頁累積；至少 1 筆才可確定</x:t>
+          <x:t xml:space="preserve">英文字母、數字、底線，最多 50 字；保存為大寫；公司內唯一；建立後不可修改</x:t>
         </x:is>
       </x:c>
       <x:c r="I140" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.72.1</x:t>
+          <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
       <x:c r="J140" s="2" t="inlineStr">
@@ -14905,42 +14905,42 @@
     <x:row r="141">
       <x:c r="A141" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.73.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.68.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B141" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.73</x:t>
+          <x:t xml:space="preserve">4.4.1.8.68</x:t>
         </x:is>
       </x:c>
       <x:c r="C141" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Standard List Page Template</x:t>
+          <x:t xml:space="preserve">Approval Flow Maintenance Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D141" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Date Range (Date inputs + quick buttons)</x:t>
+          <x:t xml:space="preserve">Flow Name (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E141" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">開始／結束日期</x:t>
+          <x:t xml:space="preserve">流程名稱</x:t>
         </x:is>
       </x:c>
       <x:c r="F141" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">限制查詢期間</x:t>
+          <x:t xml:space="preserve">流程說明</x:t>
         </x:is>
       </x:c>
       <x:c r="G141" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">yyyy-MM-dd</x:t>
+          <x:t xml:space="preserve">Text</x:t>
         </x:is>
       </x:c>
       <x:c r="H141" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">含頭尾；快選今天、本週、本月、上月、本季、本年；開始晚於結束時提示</x:t>
+          <x:t xml:space="preserve">1–100 字元，去除前後空白</x:t>
         </x:is>
       </x:c>
       <x:c r="I141" s="2" t="inlineStr">
@@ -14962,42 +14962,42 @@
     <x:row r="142">
       <x:c r="A142" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.73.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.68.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B142" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.73</x:t>
+          <x:t xml:space="preserve">4.4.1.8.68</x:t>
         </x:is>
       </x:c>
       <x:c r="C142" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Standard List Page Template</x:t>
+          <x:t xml:space="preserve">Approval Flow Maintenance Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D142" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Page Size (Dropdown)</x:t>
+          <x:t xml:space="preserve">Allow Self-approval (Checkbox)</x:t>
         </x:is>
       </x:c>
       <x:c r="E142" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">每頁筆數</x:t>
+          <x:t xml:space="preserve">允許自審</x:t>
         </x:is>
       </x:c>
       <x:c r="F142" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">分頁</x:t>
+          <x:t xml:space="preserve">送審人可否審批自己的單據</x:t>
         </x:is>
       </x:c>
       <x:c r="G142" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">整數</x:t>
+          <x:t xml:space="preserve">Boolean</x:t>
         </x:is>
       </x:c>
       <x:c r="H142" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">10／20／50／100／200</x:t>
+          <x:t xml:space="preserve">預設否</x:t>
         </x:is>
       </x:c>
       <x:c r="I142" s="2" t="inlineStr">
@@ -15019,42 +15019,42 @@
     <x:row r="143">
       <x:c r="A143" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.74.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.68.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B143" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.74</x:t>
+          <x:t xml:space="preserve">4.4.1.8.68</x:t>
         </x:is>
       </x:c>
       <x:c r="C143" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Standard Document Page Template</x:t>
+          <x:t xml:space="preserve">Approval Flow Maintenance Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D143" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Previous / Next (Button)</x:t>
+          <x:t xml:space="preserve">Step Name (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E143" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">上一筆／下一筆</x:t>
+          <x:t xml:space="preserve">步驟名稱</x:t>
         </x:is>
       </x:c>
       <x:c r="F143" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">依列表順序切換單據</x:t>
+          <x:t xml:space="preserve">顯示於待辦與記錄</x:t>
         </x:is>
       </x:c>
       <x:c r="G143" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Button</x:t>
+          <x:t xml:space="preserve">Text</x:t>
         </x:is>
       </x:c>
       <x:c r="H143" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">第一筆停用上一筆、最後一筆停用下一筆</x:t>
+          <x:t xml:space="preserve">1–100 字元</x:t>
         </x:is>
       </x:c>
       <x:c r="I143" s="2" t="inlineStr">
@@ -15076,47 +15076,47 @@
     <x:row r="144">
       <x:c r="A144" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.75.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.68.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B144" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.75</x:t>
+          <x:t xml:space="preserve">4.4.1.8.68</x:t>
         </x:is>
       </x:c>
       <x:c r="C144" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">IP Whitelist Interface</x:t>
+          <x:t xml:space="preserve">Approval Flow Maintenance Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D144" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Keyword (Input)</x:t>
+          <x:t xml:space="preserve">Approver Type (Dropdown)</x:t>
         </x:is>
       </x:c>
       <x:c r="E144" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">網段或備註關鍵字</x:t>
+          <x:t xml:space="preserve">審批人類型</x:t>
         </x:is>
       </x:c>
       <x:c r="F144" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">篩選列表</x:t>
+          <x:t xml:space="preserve">角色或指定用戶</x:t>
         </x:is>
       </x:c>
       <x:c r="G144" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Text</x:t>
+          <x:t xml:space="preserve">Role／User</x:t>
         </x:is>
       </x:c>
       <x:c r="H144" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">去除前後空白，查詢回第 1 頁</x:t>
+          <x:t xml:space="preserve">必填</x:t>
         </x:is>
       </x:c>
       <x:c r="I144" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">None</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.68.6</x:t>
         </x:is>
       </x:c>
       <x:c r="J144" s="2" t="inlineStr">
@@ -15133,47 +15133,47 @@
     <x:row r="145">
       <x:c r="A145" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.75.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.68.6</x:t>
         </x:is>
       </x:c>
       <x:c r="B145" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.75</x:t>
+          <x:t xml:space="preserve">4.4.1.8.68</x:t>
         </x:is>
       </x:c>
       <x:c r="C145" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">IP Whitelist Interface</x:t>
+          <x:t xml:space="preserve">Approval Flow Maintenance Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D145" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Scope (Dropdown)</x:t>
+          <x:t xml:space="preserve">Approver (Dropdown)</x:t>
         </x:is>
       </x:c>
       <x:c r="E145" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">全系統／角色／用戶</x:t>
+          <x:t xml:space="preserve">審批人</x:t>
         </x:is>
       </x:c>
       <x:c r="F145" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">設定比對層級</x:t>
+          <x:t xml:space="preserve">處理該步驟的角色或用戶</x:t>
         </x:is>
       </x:c>
       <x:c r="G145" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Enum</x:t>
+          <x:t xml:space="preserve">bigint ID</x:t>
         </x:is>
       </x:c>
       <x:c r="H145" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">建立時可選；編輯唯讀</x:t>
+          <x:t xml:space="preserve">啟用角色或本公司啟用用戶</x:t>
         </x:is>
       </x:c>
       <x:c r="I145" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.75.3</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.68.5</x:t>
         </x:is>
       </x:c>
       <x:c r="J145" s="2" t="inlineStr">
@@ -15190,47 +15190,47 @@
     <x:row r="146">
       <x:c r="A146" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.75.3</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.68.7</x:t>
         </x:is>
       </x:c>
       <x:c r="B146" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.75</x:t>
+          <x:t xml:space="preserve">4.4.1.8.68</x:t>
         </x:is>
       </x:c>
       <x:c r="C146" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">IP Whitelist Interface</x:t>
+          <x:t xml:space="preserve">Approval Flow Maintenance Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D146" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Target ID (Input)</x:t>
+          <x:t xml:space="preserve">Minimum Amount (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E146" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">角色或用戶 ID</x:t>
+          <x:t xml:space="preserve">最低金額</x:t>
         </x:is>
       </x:c>
       <x:c r="F146" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">指定對象</x:t>
+          <x:t xml:space="preserve">金額門檻（本位幣）</x:t>
         </x:is>
       </x:c>
       <x:c r="G146" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Positive integer</x:t>
+          <x:t xml:space="preserve">數字</x:t>
         </x:is>
       </x:c>
       <x:c r="H146" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">全系統留空；角色／用戶必填</x:t>
+          <x:t xml:space="preserve">選填；≥ 0，最多 11 位整數、4 位小數</x:t>
         </x:is>
       </x:c>
       <x:c r="I146" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.75.2</x:t>
+          <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
       <x:c r="J146" s="2" t="inlineStr">
@@ -15247,42 +15247,42 @@
     <x:row r="147">
       <x:c r="A147" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.75.4</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.68.8</x:t>
         </x:is>
       </x:c>
       <x:c r="B147" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.75</x:t>
+          <x:t xml:space="preserve">4.4.1.8.68</x:t>
         </x:is>
       </x:c>
       <x:c r="C147" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">IP Whitelist Interface</x:t>
+          <x:t xml:space="preserve">Approval Flow Maintenance Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D147" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">IP Address / Range (Input)</x:t>
+          <x:t xml:space="preserve">Active (Checkbox)</x:t>
         </x:is>
       </x:c>
       <x:c r="E147" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">IP 或 CIDR</x:t>
+          <x:t xml:space="preserve">啟用</x:t>
         </x:is>
       </x:c>
       <x:c r="F147" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">設定允許來源</x:t>
+          <x:t xml:space="preserve">停用後送審自動核准</x:t>
         </x:is>
       </x:c>
       <x:c r="G147" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">IPv4 / IPv6 / CIDR</x:t>
+          <x:t xml:space="preserve">Boolean</x:t>
         </x:is>
       </x:c>
       <x:c r="H147" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">完整位址；CIDR 網段從網路位址開始；伺服器作最終驗證</x:t>
+          <x:t xml:space="preserve">只在編輯時顯示</x:t>
         </x:is>
       </x:c>
       <x:c r="I147" s="2" t="inlineStr">
@@ -15304,47 +15304,47 @@
     <x:row r="148">
       <x:c r="A148" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.75.5</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.69.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B148" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.75</x:t>
+          <x:t xml:space="preserve">4.4.1.8.69</x:t>
         </x:is>
       </x:c>
       <x:c r="C148" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">IP Whitelist Interface</x:t>
+          <x:t xml:space="preserve">Approval Delegation Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D148" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Valid From / To (Date Picker)</x:t>
+          <x:t xml:space="preserve">Delegator (Dropdown)</x:t>
         </x:is>
       </x:c>
       <x:c r="E148" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">有效期間</x:t>
+          <x:t xml:space="preserve">被代理人</x:t>
         </x:is>
       </x:c>
       <x:c r="F148" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">控制規則生效日期</x:t>
+          <x:t xml:space="preserve">交出審批工作的用戶</x:t>
         </x:is>
       </x:c>
       <x:c r="G148" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">yyyy-MM-dd</x:t>
+          <x:t xml:space="preserve">bigint ID</x:t>
         </x:is>
       </x:c>
       <x:c r="H148" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">可留空；結束不得早於開始</x:t>
+          <x:t xml:space="preserve">本公司啟用用戶；建立後不可修改</x:t>
         </x:is>
       </x:c>
       <x:c r="I148" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">None</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.69.2</x:t>
         </x:is>
       </x:c>
       <x:c r="J148" s="2" t="inlineStr">
@@ -15361,47 +15361,47 @@
     <x:row r="149">
       <x:c r="A149" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.75.6</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.69.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B149" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.75</x:t>
+          <x:t xml:space="preserve">4.4.1.8.69</x:t>
         </x:is>
       </x:c>
       <x:c r="C149" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">IP Whitelist Interface</x:t>
+          <x:t xml:space="preserve">Approval Delegation Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D149" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Description (Input)</x:t>
+          <x:t xml:space="preserve">Delegate (Dropdown)</x:t>
         </x:is>
       </x:c>
       <x:c r="E149" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">備註</x:t>
+          <x:t xml:space="preserve">代理人</x:t>
         </x:is>
       </x:c>
       <x:c r="F149" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">辨識規則用途</x:t>
+          <x:t xml:space="preserve">代為審批的用戶</x:t>
         </x:is>
       </x:c>
       <x:c r="G149" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Text</x:t>
+          <x:t xml:space="preserve">bigint ID</x:t>
         </x:is>
       </x:c>
       <x:c r="H149" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">最長 200 字元</x:t>
+          <x:t xml:space="preserve">本公司啟用用戶，不可與被代理人相同；建立後不可修改</x:t>
         </x:is>
       </x:c>
       <x:c r="I149" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">None</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.69.1</x:t>
         </x:is>
       </x:c>
       <x:c r="J149" s="2" t="inlineStr">
@@ -15418,47 +15418,47 @@
     <x:row r="150">
       <x:c r="A150" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.75.7</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.69.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B150" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.75</x:t>
+          <x:t xml:space="preserve">4.4.1.8.69</x:t>
         </x:is>
       </x:c>
       <x:c r="C150" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">IP Whitelist Interface</x:t>
+          <x:t xml:space="preserve">Approval Delegation Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D150" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Disable (Button)</x:t>
+          <x:t xml:space="preserve">Start / End Date (Date input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E150" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">停用規則</x:t>
+          <x:t xml:space="preserve">開始／結束日期</x:t>
         </x:is>
       </x:c>
       <x:c r="F150" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">保留稽核歷史</x:t>
+          <x:t xml:space="preserve">代理期間（含頭尾）</x:t>
         </x:is>
       </x:c>
       <x:c r="G150" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Button</x:t>
+          <x:t xml:space="preserve">yyyy-MM-dd</x:t>
         </x:is>
       </x:c>
       <x:c r="H150" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">需 EDIT 權限；確認後帶版本送出</x:t>
+          <x:t xml:space="preserve">結束不早於開始；同一被代理人的啟用期間不可重疊</x:t>
         </x:is>
       </x:c>
       <x:c r="I150" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.75.4</x:t>
+          <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
       <x:c r="J150" s="2" t="inlineStr">
@@ -15475,47 +15475,47 @@
     <x:row r="151">
       <x:c r="A151" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.76.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.69.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B151" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.76</x:t>
+          <x:t xml:space="preserve">4.4.1.8.69</x:t>
         </x:is>
       </x:c>
       <x:c r="C151" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Notification View Interface</x:t>
+          <x:t xml:space="preserve">Approval Delegation Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D151" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Unread Badge (Label)</x:t>
+          <x:t xml:space="preserve">Remark (Textarea)</x:t>
         </x:is>
       </x:c>
       <x:c r="E151" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">頂列未讀數</x:t>
+          <x:t xml:space="preserve">備註</x:t>
         </x:is>
       </x:c>
       <x:c r="F151" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">快速辨識新通知</x:t>
+          <x:t xml:space="preserve">代理原因</x:t>
         </x:is>
       </x:c>
       <x:c r="G151" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Integer</x:t>
+          <x:t xml:space="preserve">Text</x:t>
         </x:is>
       </x:c>
       <x:c r="H151" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">0 隱藏；超過 99 顯示 99+</x:t>
+          <x:t xml:space="preserve">0–200 字元</x:t>
         </x:is>
       </x:c>
       <x:c r="I151" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">收件箱</x:t>
+          <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
       <x:c r="J151" s="2" t="inlineStr">
@@ -15532,47 +15532,47 @@
     <x:row r="152">
       <x:c r="A152" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.76.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.70.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B152" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.76</x:t>
+          <x:t xml:space="preserve">4.4.1.8.70</x:t>
         </x:is>
       </x:c>
       <x:c r="C152" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Notification View Interface</x:t>
+          <x:t xml:space="preserve">Approval Inbox Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D152" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Unread Only (Button)</x:t>
+          <x:t xml:space="preserve">Comment (Textarea)</x:t>
         </x:is>
       </x:c>
       <x:c r="E152" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">未讀篩選</x:t>
+          <x:t xml:space="preserve">意見</x:t>
         </x:is>
       </x:c>
       <x:c r="F152" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">切換全部／未讀</x:t>
+          <x:t xml:space="preserve">核准或駁回的說明</x:t>
         </x:is>
       </x:c>
       <x:c r="G152" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Button</x:t>
+          <x:t xml:space="preserve">Text</x:t>
         </x:is>
       </x:c>
       <x:c r="H152" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">切換後回第 1 頁</x:t>
+          <x:t xml:space="preserve">0–500 字元；駁回必填</x:t>
         </x:is>
       </x:c>
       <x:c r="I152" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">通知列表</x:t>
+          <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
       <x:c r="J152" s="2" t="inlineStr">
@@ -15589,47 +15589,47 @@
     <x:row r="153">
       <x:c r="A153" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.76.3</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.70.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B153" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.76</x:t>
+          <x:t xml:space="preserve">4.4.1.8.70</x:t>
         </x:is>
       </x:c>
       <x:c r="C153" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Notification View Interface</x:t>
+          <x:t xml:space="preserve">Approval Inbox Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D153" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Notification List (Table)</x:t>
+          <x:t xml:space="preserve">Status Filter (Dropdown)</x:t>
         </x:is>
       </x:c>
       <x:c r="E153" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">類別、標題、內文、時間、狀態</x:t>
+          <x:t xml:space="preserve">狀態</x:t>
         </x:is>
       </x:c>
       <x:c r="F153" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">瀏覽本人通知</x:t>
+          <x:t xml:space="preserve">篩選審批歷史</x:t>
         </x:is>
       </x:c>
       <x:c r="G153" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Paged table</x:t>
+          <x:t xml:space="preserve">審批中／已核准／已駁回／已撤回</x:t>
         </x:is>
       </x:c>
       <x:c r="H153" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">每頁 20，伺服器分頁</x:t>
+          <x:t xml:space="preserve">可清除</x:t>
         </x:is>
       </x:c>
       <x:c r="I153" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">未讀篩選</x:t>
+          <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
       <x:c r="J153" s="2" t="inlineStr">
@@ -15646,32 +15646,32 @@
     <x:row r="154">
       <x:c r="A154" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.76.4</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.71.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B154" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.76</x:t>
+          <x:t xml:space="preserve">4.4.1.8.71</x:t>
         </x:is>
       </x:c>
       <x:c r="C154" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Notification View Interface</x:t>
+          <x:t xml:space="preserve">Confirmation / Prompt Box Interface（BlueWhale 4.4.1.9）</x:t>
         </x:is>
       </x:c>
       <x:c r="D154" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Mark Read (Button)</x:t>
+          <x:t xml:space="preserve">OK / Cancel (Button)</x:t>
         </x:is>
       </x:c>
       <x:c r="E154" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">單則已讀</x:t>
+          <x:t xml:space="preserve">確定／取消</x:t>
         </x:is>
       </x:c>
       <x:c r="F154" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">清除該筆未讀狀態</x:t>
+          <x:t xml:space="preserve">確認或放棄動作</x:t>
         </x:is>
       </x:c>
       <x:c r="G154" s="2" t="inlineStr">
@@ -15681,12 +15681,12 @@
       </x:c>
       <x:c r="H154" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">只在未讀且有 READ 權限時顯示</x:t>
+          <x:t xml:space="preserve">確認框兩個按鈕，提示框只有確定；Esc 等同取消</x:t>
         </x:is>
       </x:c>
       <x:c r="I154" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">通知列表</x:t>
+          <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
       <x:c r="J154" s="2" t="inlineStr">
@@ -15703,47 +15703,47 @@
     <x:row r="155">
       <x:c r="A155" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.76.5</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.72.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B155" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.76</x:t>
+          <x:t xml:space="preserve">4.4.1.8.72</x:t>
         </x:is>
       </x:c>
       <x:c r="C155" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Notification View Interface</x:t>
+          <x:t xml:space="preserve">Select Dialog Interface（BlueWhale 4.4.1.9 Select Client / Supplier / Item）</x:t>
         </x:is>
       </x:c>
       <x:c r="D155" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Mark All Read (Button)</x:t>
+          <x:t xml:space="preserve">Keyword (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E155" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">全部已讀</x:t>
+          <x:t xml:space="preserve">關鍵字</x:t>
         </x:is>
       </x:c>
       <x:c r="F155" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">清除目前公司本人未讀狀態</x:t>
+          <x:t xml:space="preserve">搜尋主檔</x:t>
         </x:is>
       </x:c>
       <x:c r="G155" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Button</x:t>
+          <x:t xml:space="preserve">Text</x:t>
         </x:is>
       </x:c>
       <x:c r="H155" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">未讀數為 0 時停用</x:t>
+          <x:t xml:space="preserve">去除前後空白；查詢回到第 1 頁</x:t>
         </x:is>
       </x:c>
       <x:c r="I155" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">通知列表</x:t>
+          <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
       <x:c r="J155" s="2" t="inlineStr">
@@ -15760,55 +15760,967 @@
     <x:row r="156">
       <x:c r="A156" s="2" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.72.2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B156" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.72</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C156" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Select Dialog Interface（BlueWhale 4.4.1.9 Select Client / Supplier / Item）</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D156" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Selection (Checkbox / Row)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E156" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">選取</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F156" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">選擇主檔資料</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G156" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Row key</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H156" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">單選 1 筆、多選跨頁累積；至少 1 筆才可確定</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I156" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.72.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J156" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K156" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="157">
+      <x:c r="A157" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.73.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B157" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.73</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C157" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Standard List Page Template</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D157" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Date Range (Date inputs + quick buttons)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E157" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">開始／結束日期</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F157" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">限制查詢期間</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G157" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">yyyy-MM-dd</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H157" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">含頭尾；快選今天、本週、本月、上月、本季、本年；開始晚於結束時提示</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I157" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J157" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K157" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="158">
+      <x:c r="A158" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.73.2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B158" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.73</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C158" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Standard List Page Template</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D158" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Page Size (Dropdown)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E158" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">每頁筆數</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F158" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">分頁</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G158" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">整數</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H158" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">10／20／50／100／200</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I158" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J158" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K158" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="159">
+      <x:c r="A159" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.74.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B159" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.74</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C159" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Standard Document Page Template</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D159" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Previous / Next (Button)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E159" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">上一筆／下一筆</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F159" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">依列表順序切換單據</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G159" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Button</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H159" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">第一筆停用上一筆、最後一筆停用下一筆</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I159" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J159" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K159" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="160">
+      <x:c r="A160" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.75.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B160" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.75</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C160" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">IP Whitelist Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D160" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Keyword (Input)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E160" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">網段或備註關鍵字</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F160" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">篩選列表</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G160" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Text</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H160" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">去除前後空白，查詢回第 1 頁</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I160" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J160" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K160" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="161">
+      <x:c r="A161" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.75.2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B161" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.75</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C161" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">IP Whitelist Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D161" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Scope (Dropdown)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E161" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">全系統／角色／用戶</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F161" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">設定比對層級</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G161" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Enum</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H161" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">建立時可選；編輯唯讀</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I161" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.75.3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J161" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K161" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="162">
+      <x:c r="A162" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.75.3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B162" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.75</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C162" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">IP Whitelist Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D162" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Target ID (Input)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E162" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">角色或用戶 ID</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F162" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">指定對象</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G162" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Positive integer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H162" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">全系統留空；角色／用戶必填</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I162" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.75.2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J162" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K162" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="163">
+      <x:c r="A163" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.75.4</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B163" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.75</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C163" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">IP Whitelist Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D163" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">IP Address / Range (Input)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E163" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">IP 或 CIDR</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F163" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">設定允許來源</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G163" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">IPv4 / IPv6 / CIDR</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H163" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">完整位址；CIDR 網段從網路位址開始；伺服器作最終驗證</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I163" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J163" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K163" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="164">
+      <x:c r="A164" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.75.5</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B164" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.75</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C164" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">IP Whitelist Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D164" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Valid From / To (Date Picker)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E164" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">有效期間</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F164" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">控制規則生效日期</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G164" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">yyyy-MM-dd</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H164" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">可留空；結束不得早於開始</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I164" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J164" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K164" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="165">
+      <x:c r="A165" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.75.6</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B165" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.75</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C165" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">IP Whitelist Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D165" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Description (Input)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E165" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">備註</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F165" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">辨識規則用途</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G165" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Text</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H165" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">最長 200 字元</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I165" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J165" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K165" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="166">
+      <x:c r="A166" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.75.7</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B166" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.75</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C166" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">IP Whitelist Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D166" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Disable (Button)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E166" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">停用規則</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F166" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">保留稽核歷史</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G166" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Button</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H166" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">需 EDIT 權限；確認後帶版本送出</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I166" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.75.4</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J166" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K166" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="167">
+      <x:c r="A167" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.76.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B167" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.76</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C167" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Notification View Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D167" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Unread Badge (Label)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E167" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">頂列未讀數</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F167" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">快速辨識新通知</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G167" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Integer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H167" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">0 隱藏；超過 99 顯示 99+</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I167" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">收件箱</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J167" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K167" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="168">
+      <x:c r="A168" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.76.2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B168" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.76</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C168" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Notification View Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D168" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Unread Only (Button)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E168" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">未讀篩選</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F168" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">切換全部／未讀</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G168" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Button</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H168" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">切換後回第 1 頁</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I168" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">通知列表</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J168" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K168" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="169">
+      <x:c r="A169" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.76.3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B169" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.76</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C169" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Notification View Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D169" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Notification List (Table)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E169" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">類別、標題、內文、時間、狀態</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F169" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">瀏覽本人通知</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G169" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Paged table</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H169" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">每頁 20，伺服器分頁</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I169" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">未讀篩選</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J169" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K169" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="170">
+      <x:c r="A170" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.76.4</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B170" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.76</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C170" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Notification View Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D170" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Mark Read (Button)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E170" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">單則已讀</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F170" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">清除該筆未讀狀態</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G170" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Button</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H170" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">只在未讀且有 READ 權限時顯示</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I170" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">通知列表</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J170" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K170" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="171">
+      <x:c r="A171" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.76.5</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B171" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.76</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C171" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Notification View Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D171" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Mark All Read (Button)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E171" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">全部已讀</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F171" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">清除目前公司本人未讀狀態</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G171" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Button</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H171" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">未讀數為 0 時停用</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I171" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">通知列表</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J171" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K171" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="172">
+      <x:c r="A172" s="2" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">REQ_IO_A8.76.6</x:t>
         </x:is>
       </x:c>
-      <x:c r="B156" s="2" t="inlineStr">
+      <x:c r="B172" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">4.4.1.8.76</x:t>
         </x:is>
       </x:c>
-      <x:c r="C156" s="2" t="inlineStr">
+      <x:c r="C172" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Notification View Interface</x:t>
         </x:is>
       </x:c>
-      <x:c r="D156" s="2" t="inlineStr">
+      <x:c r="D172" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Open (Link)</x:t>
         </x:is>
       </x:c>
-      <x:c r="E156" s="2" t="inlineStr">
+      <x:c r="E172" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">站內目標</x:t>
         </x:is>
       </x:c>
-      <x:c r="F156" s="2" t="inlineStr">
+      <x:c r="F172" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">跳至通知相關頁</x:t>
         </x:is>
       </x:c>
-      <x:c r="G156" s="2" t="inlineStr">
+      <x:c r="G172" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Internal route</x:t>
         </x:is>
       </x:c>
-      <x:c r="H156" s="2" t="inlineStr">
+      <x:c r="H172" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">無路徑則隱藏</x:t>
         </x:is>
       </x:c>
-      <x:c r="I156" s="2" t="inlineStr">
+      <x:c r="I172" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">通知列表</x:t>
         </x:is>
       </x:c>
-      <x:c r="J156" s="2" t="inlineStr">
+      <x:c r="J172" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="K156" s="2" t="inlineStr">
+      <x:c r="K172" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Developer</x:t>
         </x:is>
@@ -16514,22 +17426,22 @@
       </x:c>
       <x:c r="D19" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">4.4.1.8.36</x:t>
         </x:is>
       </x:c>
       <x:c r="E19" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.36.1, REQ_IO_A8.36.2</x:t>
         </x:is>
       </x:c>
       <x:c r="F19" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MD-ICAT-001</x:t>
+          <x:t xml:space="preserve">MD-ICAT-001, MD-ICAT-004, MD-ICAT-005, MD-ICAT-006</x:t>
         </x:is>
       </x:c>
       <x:c r="G19" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -16551,22 +17463,22 @@
       </x:c>
       <x:c r="D20" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">4.4.1.8.37</x:t>
         </x:is>
       </x:c>
       <x:c r="E20" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.37.1, REQ_IO_A8.37.2, REQ_IO_A8.37.3</x:t>
         </x:is>
       </x:c>
       <x:c r="F20" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MD-ICAT-001, MD-ICAT-002</x:t>
+          <x:t xml:space="preserve">MD-ICAT-001, MD-ICAT-002, MD-ICAT-004, MD-ICAT-005, MD-ICAT-006</x:t>
         </x:is>
       </x:c>
       <x:c r="G20" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -16588,22 +17500,22 @@
       </x:c>
       <x:c r="D21" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">4.4.1.8.38</x:t>
         </x:is>
       </x:c>
       <x:c r="E21" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.38.1, REQ_IO_A8.38.2, REQ_IO_A8.38.3</x:t>
         </x:is>
       </x:c>
       <x:c r="F21" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MD-ICAT-001, MD-ICAT-002</x:t>
+          <x:t xml:space="preserve">MD-ICAT-001, MD-ICAT-002, MD-ICAT-004, MD-ICAT-005, MD-ICAT-006</x:t>
         </x:is>
       </x:c>
       <x:c r="G21" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -16625,22 +17537,22 @@
       </x:c>
       <x:c r="D22" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">4.4.1.8.36</x:t>
         </x:is>
       </x:c>
       <x:c r="E22" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.36.3</x:t>
         </x:is>
       </x:c>
       <x:c r="F22" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MD-ICAT-003</x:t>
+          <x:t xml:space="preserve">MD-ICAT-003, MD-ICAT-004, MD-ICAT-005, MD-ICAT-006</x:t>
         </x:is>
       </x:c>
       <x:c r="G22" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -16662,22 +17574,22 @@
       </x:c>
       <x:c r="D23" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">4.4.1.8.39</x:t>
         </x:is>
       </x:c>
       <x:c r="E23" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.39.1, REQ_IO_A8.39.2</x:t>
         </x:is>
       </x:c>
       <x:c r="F23" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MD-BRD-001</x:t>
+          <x:t xml:space="preserve">MD-BRD-001, MD-BRD-002, MD-BRD-003</x:t>
         </x:is>
       </x:c>
       <x:c r="G23" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -16699,22 +17611,22 @@
       </x:c>
       <x:c r="D24" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">4.4.1.8.40</x:t>
         </x:is>
       </x:c>
       <x:c r="E24" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.40.1, REQ_IO_A8.40.2</x:t>
         </x:is>
       </x:c>
       <x:c r="F24" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MD-BRD-001</x:t>
+          <x:t xml:space="preserve">MD-BRD-001, MD-BRD-002, MD-BRD-003</x:t>
         </x:is>
       </x:c>
       <x:c r="G24" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -16736,22 +17648,22 @@
       </x:c>
       <x:c r="D25" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">4.4.1.8.41</x:t>
         </x:is>
       </x:c>
       <x:c r="E25" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.41.1, REQ_IO_A8.41.2</x:t>
         </x:is>
       </x:c>
       <x:c r="F25" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MD-BRD-001</x:t>
+          <x:t xml:space="preserve">MD-BRD-001, MD-BRD-002, MD-BRD-003</x:t>
         </x:is>
       </x:c>
       <x:c r="G25" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -16773,22 +17685,22 @@
       </x:c>
       <x:c r="D26" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">4.4.1.8.39</x:t>
         </x:is>
       </x:c>
       <x:c r="E26" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.39.3</x:t>
         </x:is>
       </x:c>
       <x:c r="F26" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MD-BRD-001</x:t>
+          <x:t xml:space="preserve">MD-BRD-001, MD-BRD-002, MD-BRD-003</x:t>
         </x:is>
       </x:c>
       <x:c r="G26" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -26351,7 +27263,7 @@
       </x:c>
       <x:c r="F192" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">進行中</x:t>
+          <x:t xml:space="preserve">完成</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -26383,7 +27295,7 @@
       </x:c>
       <x:c r="F193" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">進行中</x:t>
+          <x:t xml:space="preserve">完成</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -26415,7 +27327,7 @@
       </x:c>
       <x:c r="F194" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">進行中</x:t>
+          <x:t xml:space="preserve">完成</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -26447,7 +27359,7 @@
       </x:c>
       <x:c r="F195" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">進行中</x:t>
+          <x:t xml:space="preserve">完成</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -26479,7 +27391,7 @@
       </x:c>
       <x:c r="F196" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">進行中</x:t>
+          <x:t xml:space="preserve">完成</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -26511,7 +27423,7 @@
       </x:c>
       <x:c r="F197" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">進行中</x:t>
+          <x:t xml:space="preserve">完成</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -26543,7 +27455,7 @@
       </x:c>
       <x:c r="F198" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">進行中</x:t>
+          <x:t xml:space="preserve">完成</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -26575,7 +27487,7 @@
       </x:c>
       <x:c r="F199" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">進行中</x:t>
+          <x:t xml:space="preserve">完成</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -31375,7 +32287,7 @@
       </x:c>
       <x:c r="F349" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">未開始</x:t>
+          <x:t xml:space="preserve">完成</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -31407,7 +32319,7 @@
       </x:c>
       <x:c r="F350" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">未開始</x:t>
+          <x:t xml:space="preserve">完成</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -31439,7 +32351,7 @@
       </x:c>
       <x:c r="F351" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">未開始</x:t>
+          <x:t xml:space="preserve">完成</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -31471,7 +32383,7 @@
       </x:c>
       <x:c r="F352" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">未開始</x:t>
+          <x:t xml:space="preserve">完成</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -31503,7 +32415,7 @@
       </x:c>
       <x:c r="F353" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">未開始</x:t>
+          <x:t xml:space="preserve">完成</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -31535,7 +32447,7 @@
       </x:c>
       <x:c r="F354" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">未開始</x:t>
+          <x:t xml:space="preserve">完成</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -32239,7 +33151,7 @@
       </x:c>
       <x:c r="F376" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">進行中</x:t>
+          <x:t xml:space="preserve">完成</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -33551,7 +34463,7 @@
       </x:c>
       <x:c r="F417" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">進行中</x:t>
+          <x:t xml:space="preserve">完成</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -33807,7 +34719,7 @@
       </x:c>
       <x:c r="F425" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">進行中</x:t>
+          <x:t xml:space="preserve">完成</x:t>
         </x:is>
       </x:c>
     </x:row>

--- a/docs/99-output/MyERP_Requirements.xlsx
+++ b/docs/99-output/MyERP_Requirements.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="1" r:id="R6acb67cfdf9841cb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Non-Functional" sheetId="2" r:id="R5ee178f522c348e6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Structure" sheetId="3" r:id="Ra46848f0742c4e7e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interface" sheetId="4" r:id="R40cb58c45a254efb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traceability Matrix" sheetId="5" r:id="R1e7cba6250544ebb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BlueWhale Parity" sheetId="6" r:id="R1644876a9dbe457b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timeline" sheetId="7" r:id="Rd983a65e2d2041d3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Human Resources" sheetId="8" r:id="R9d51d44899e34677"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="9" r:id="R05dbace492b446ba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="1" r:id="R1bbaf91e656b4e8d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Non-Functional" sheetId="2" r:id="R4f3e80f853834aed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Structure" sheetId="3" r:id="R417d27cee9814548"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interface" sheetId="4" r:id="R85de35af473f4270"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traceability Matrix" sheetId="5" r:id="Rdda1e9e4901a44a9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BlueWhale Parity" sheetId="6" r:id="Re323366eb6414bab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timeline" sheetId="7" r:id="R484c0405b65e4860"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Human Resources" sheetId="8" r:id="Rf78e353cb89c4068"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="9" r:id="R69dc4208c2c948de"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1166,7 +1166,7 @@
     <x:row r="27">
       <x:c r="A27" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.13.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.12.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B27" s="2" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </x:c>
       <x:c r="C27" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Unit of Measurement</x:t>
+          <x:t xml:space="preserve">Item Master</x:t>
         </x:is>
       </x:c>
       <x:c r="D27" s="2" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </x:c>
       <x:c r="E27" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to view unit of measurement.</x:t>
+          <x:t xml:space="preserve">System should enable user to view items.</x:t>
         </x:is>
       </x:c>
       <x:c r="F27" s="2" t="inlineStr">
@@ -1196,19 +1196,19 @@
       </x:c>
       <x:c r="G27" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">具 MD.UOM.VIEW 可按目前公司以代碼或名稱搜尋、分頁及排序（代碼／名稱）單位，含停用單位；可查看全部換算及以換算試算數量（結果按目標單位小數位數四捨五入）。排除軟刪除及別公司資料；未選公司回 403。</x:t>
+          <x:t xml:space="preserve">MD.ITEM.VIEW 可在目前公司按代碼、名稱或規格搜尋，按代碼／名稱排序及分頁；含停用物料，不含其他公司。未選公司回 403。</x:t>
         </x:is>
       </x:c>
       <x:c r="H27" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:77</x:t>
+          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:110</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.13.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.12.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B28" s="2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </x:c>
       <x:c r="C28" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Unit of Measurement</x:t>
+          <x:t xml:space="preserve">Item Master</x:t>
         </x:is>
       </x:c>
       <x:c r="D28" s="2" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </x:c>
       <x:c r="E28" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to create unit of measurement.</x:t>
+          <x:t xml:space="preserve">System should enable user to create items.</x:t>
         </x:is>
       </x:c>
       <x:c r="F28" s="2" t="inlineStr">
@@ -1238,19 +1238,19 @@
       </x:c>
       <x:c r="G28" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">具 CREATE 權限可建立公司內唯一代碼（1–30 英數、-、_，轉大寫）、非空白名稱（最多 200 字）及小數位數（0–6）的單位；重複代碼回 409 MD.UOM.DUPLICATE_CODE。可新增換算（1 來源 = 係數 目標；係數 &gt; 0、最多 9 位整數及 6 位小數）：兩端須為本公司啟用單位且不同；兩單位已可直接、反向或經其他單位換算時回 409 MD.UOM_CONVERSION.PATH_EXISTS。</x:t>
+          <x:t xml:space="preserve">MD.ITEM.CREATE 可建立公司內永久唯一、轉大寫的 1–30 位代碼、非空白名稱（最多 200 字）、可空規格（最多 500 字）、本公司啟用的基本單位、可空的啟用品牌與分類。重複代碼 409，別公司／停用參照 400。</x:t>
         </x:is>
       </x:c>
       <x:c r="H28" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:78</x:t>
+          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:111</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.13.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.12.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B29" s="2" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </x:c>
       <x:c r="C29" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Unit of Measurement</x:t>
+          <x:t xml:space="preserve">Item Master</x:t>
         </x:is>
       </x:c>
       <x:c r="D29" s="2" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </x:c>
       <x:c r="E29" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to edit unit of measurement.</x:t>
+          <x:t xml:space="preserve">System should enable user to edit items.</x:t>
         </x:is>
       </x:c>
       <x:c r="F29" s="2" t="inlineStr">
@@ -1280,19 +1280,19 @@
       </x:c>
       <x:c r="G29" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">具 EDIT 權限可帶版本修改單位名稱、小數位數及啟用狀態（代碼不可變），以及換算係數；版本衝突 409，別公司或不存在 404（MD.UOM.NOT_FOUND／MD.UOM_CONVERSION.NOT_FOUND）。</x:t>
+          <x:t xml:space="preserve">MD.ITEM.EDIT 可帶版本修改名稱、規格、基本單位、品牌、分類、啟用狀態，代碼不可改；原參照停用後可保留，重新選擇須啟用。舊版本 409、別公司物料 404。已被物料引用的單位、品牌、分類不可刪除，只可停用。</x:t>
         </x:is>
       </x:c>
       <x:c r="H29" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:79</x:t>
+          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:112</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.13.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.13.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B30" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </x:c>
       <x:c r="E30" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to delete unit of measurement.</x:t>
+          <x:t xml:space="preserve">System should enable user to view unit of measurement.</x:t>
         </x:is>
       </x:c>
       <x:c r="F30" s="2" t="inlineStr">
@@ -1322,19 +1322,19 @@
       </x:c>
       <x:c r="G30" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">具 DELETE 權限可帶版本軟刪除單位或換算；單位代碼刪除後仍保留；被換算引用的單位回 409 MD.UOM.IN_USE，只可停用。</x:t>
+          <x:t xml:space="preserve">具 MD.UOM.VIEW 可按目前公司以代碼或名稱搜尋、分頁及排序（代碼／名稱）單位，含停用單位；可查看全部換算及以換算試算數量（結果按目標單位小數位數四捨五入）。排除軟刪除及別公司資料；未選公司回 403。</x:t>
         </x:is>
       </x:c>
       <x:c r="H30" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:80</x:t>
+          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:77</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.17.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.13.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B31" s="2" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </x:c>
       <x:c r="C31" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Parameter Settings</x:t>
+          <x:t xml:space="preserve">Unit of Measurement</x:t>
         </x:is>
       </x:c>
       <x:c r="D31" s="2" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </x:c>
       <x:c r="E31" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to view parameter settings.</x:t>
+          <x:t xml:space="preserve">System should enable user to create unit of measurement.</x:t>
         </x:is>
       </x:c>
       <x:c r="F31" s="2" t="inlineStr">
@@ -1364,19 +1364,19 @@
       </x:c>
       <x:c r="G31" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">具 CREATE 權限可建立公司內唯一代碼（1–30 英數、-、_，轉大寫）、非空白名稱（最多 200 字）及小數位數（0–6）的單位；重複代碼回 409 MD.UOM.DUPLICATE_CODE。可新增換算（1 來源 = 係數 目標；係數 &gt; 0、最多 9 位整數及 6 位小數）：兩端須為本公司啟用單位且不同；兩單位已可直接、反向或經其他單位換算時回 409 MD.UOM_CONVERSION.PATH_EXISTS。</x:t>
         </x:is>
       </x:c>
       <x:c r="H31" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:234</x:t>
+          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:78</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.17.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.13.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B32" s="2" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </x:c>
       <x:c r="C32" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Parameter Settings</x:t>
+          <x:t xml:space="preserve">Unit of Measurement</x:t>
         </x:is>
       </x:c>
       <x:c r="D32" s="2" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </x:c>
       <x:c r="E32" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to edit parameter settings.</x:t>
+          <x:t xml:space="preserve">System should enable user to edit unit of measurement.</x:t>
         </x:is>
       </x:c>
       <x:c r="F32" s="2" t="inlineStr">
@@ -1406,19 +1406,19 @@
       </x:c>
       <x:c r="G32" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">具 EDIT 權限可帶版本修改單位名稱、小數位數及啟用狀態（代碼不可變），以及換算係數；版本衝突 409，別公司或不存在 404（MD.UOM.NOT_FOUND／MD.UOM_CONVERSION.NOT_FOUND）。</x:t>
         </x:is>
       </x:c>
       <x:c r="H32" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:235</x:t>
+          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:79</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.17.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.13.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B33" s="2" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </x:c>
       <x:c r="C33" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Parameter Settings</x:t>
+          <x:t xml:space="preserve">Unit of Measurement</x:t>
         </x:is>
       </x:c>
       <x:c r="D33" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </x:c>
       <x:c r="E33" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should let every module declare typed company parameters with defaults and read them in process.</x:t>
+          <x:t xml:space="preserve">System should enable user to delete unit of measurement.</x:t>
         </x:is>
       </x:c>
       <x:c r="F33" s="2" t="inlineStr">
@@ -1448,19 +1448,19 @@
       </x:c>
       <x:c r="G33" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">具 DELETE 權限可帶版本軟刪除單位或換算；單位代碼刪除後仍保留；被換算引用的單位回 409 MD.UOM.IN_USE，只可停用。</x:t>
         </x:is>
       </x:c>
       <x:c r="H33" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:236</x:t>
+          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:80</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.17.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.17.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B34" s="2" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </x:c>
       <x:c r="E34" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should provide a parameter edit interface grouped by module.</x:t>
+          <x:t xml:space="preserve">System should enable user to view parameter settings.</x:t>
         </x:is>
       </x:c>
       <x:c r="F34" s="2" t="inlineStr">
@@ -1495,14 +1495,14 @@
       </x:c>
       <x:c r="H34" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:237</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:234</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.18.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.17.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B35" s="2" t="inlineStr">
@@ -1512,7 +1512,7 @@
       </x:c>
       <x:c r="C35" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Print Settings</x:t>
+          <x:t xml:space="preserve">Parameter Settings</x:t>
         </x:is>
       </x:c>
       <x:c r="D35" s="2" t="inlineStr">
@@ -1522,7 +1522,7 @@
       </x:c>
       <x:c r="E35" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to view print settings.</x:t>
+          <x:t xml:space="preserve">System should enable user to edit parameter settings.</x:t>
         </x:is>
       </x:c>
       <x:c r="F35" s="2" t="inlineStr">
@@ -1537,14 +1537,14 @@
       </x:c>
       <x:c r="H35" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:250</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:235</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.18.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.17.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B36" s="2" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </x:c>
       <x:c r="C36" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Print Settings</x:t>
+          <x:t xml:space="preserve">Parameter Settings</x:t>
         </x:is>
       </x:c>
       <x:c r="D36" s="2" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </x:c>
       <x:c r="E36" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to edit print settings.</x:t>
+          <x:t xml:space="preserve">System should let every module declare typed company parameters with defaults and read them in process.</x:t>
         </x:is>
       </x:c>
       <x:c r="F36" s="2" t="inlineStr">
@@ -1579,14 +1579,14 @@
       </x:c>
       <x:c r="H36" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:251</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:236</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.18.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.17.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B37" s="2" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </x:c>
       <x:c r="C37" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Print Settings</x:t>
+          <x:t xml:space="preserve">Parameter Settings</x:t>
         </x:is>
       </x:c>
       <x:c r="D37" s="2" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </x:c>
       <x:c r="E37" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should let printing modules read the company's print settings.</x:t>
+          <x:t xml:space="preserve">System should provide a parameter edit interface grouped by module.</x:t>
         </x:is>
       </x:c>
       <x:c r="F37" s="2" t="inlineStr">
@@ -1621,14 +1621,14 @@
       </x:c>
       <x:c r="H37" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:252</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:237</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.19.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.18.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B38" s="2" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </x:c>
       <x:c r="C38" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Logo &amp; Stamp</x:t>
+          <x:t xml:space="preserve">Print Settings</x:t>
         </x:is>
       </x:c>
       <x:c r="D38" s="2" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </x:c>
       <x:c r="E38" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to view the logo and stamp.</x:t>
+          <x:t xml:space="preserve">System should enable user to view print settings.</x:t>
         </x:is>
       </x:c>
       <x:c r="F38" s="2" t="inlineStr">
@@ -1663,14 +1663,14 @@
       </x:c>
       <x:c r="H38" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:264</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:250</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.19.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.18.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B39" s="2" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </x:c>
       <x:c r="C39" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Logo &amp; Stamp</x:t>
+          <x:t xml:space="preserve">Print Settings</x:t>
         </x:is>
       </x:c>
       <x:c r="D39" s="2" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </x:c>
       <x:c r="E39" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to edit the logo and stamp.</x:t>
+          <x:t xml:space="preserve">System should enable user to edit print settings.</x:t>
         </x:is>
       </x:c>
       <x:c r="F39" s="2" t="inlineStr">
@@ -1705,14 +1705,14 @@
       </x:c>
       <x:c r="H39" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:265</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:251</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.19.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.18.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B40" s="2" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </x:c>
       <x:c r="C40" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Logo &amp; Stamp</x:t>
+          <x:t xml:space="preserve">Print Settings</x:t>
         </x:is>
       </x:c>
       <x:c r="D40" s="2" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </x:c>
       <x:c r="E40" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should let printing modules read the company's logo and stamp.</x:t>
+          <x:t xml:space="preserve">System should let printing modules read the company's print settings.</x:t>
         </x:is>
       </x:c>
       <x:c r="F40" s="2" t="inlineStr">
@@ -1747,14 +1747,14 @@
       </x:c>
       <x:c r="H40" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:266</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:252</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.20.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.19.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B41" s="2" t="inlineStr">
@@ -1764,17 +1764,17 @@
       </x:c>
       <x:c r="C41" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Company Management</x:t>
+          <x:t xml:space="preserve">Logo &amp; Stamp</x:t>
         </x:is>
       </x:c>
       <x:c r="D41" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1.2</x:t>
+          <x:t xml:space="preserve">1.0</x:t>
         </x:is>
       </x:c>
       <x:c r="E41" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to view company details.</x:t>
+          <x:t xml:space="preserve">System should enable user to view the logo and stamp.</x:t>
         </x:is>
       </x:c>
       <x:c r="F41" s="2" t="inlineStr">
@@ -1784,19 +1784,19 @@
       </x:c>
       <x:c r="G41" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">僅有組織檢視權的用戶可見其獲授權且未刪除的公司；預設只列啟用公司，勾選「顯示已停用」時一併列出停用公司；列表支援分頁、關鍵字及代碼／名稱排序；無權限回 403。</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="H41" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:13</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:264</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.20.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.19.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B42" s="2" t="inlineStr">
@@ -1806,17 +1806,17 @@
       </x:c>
       <x:c r="C42" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Company Management</x:t>
+          <x:t xml:space="preserve">Logo &amp; Stamp</x:t>
         </x:is>
       </x:c>
       <x:c r="D42" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1.2</x:t>
+          <x:t xml:space="preserve">1.0</x:t>
         </x:is>
       </x:c>
       <x:c r="E42" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to create a company.</x:t>
+          <x:t xml:space="preserve">System should enable user to edit the logo and stamp.</x:t>
         </x:is>
       </x:c>
       <x:c r="F42" s="2" t="inlineStr">
@@ -1826,19 +1826,19 @@
       </x:c>
       <x:c r="G42" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">代碼全系統唯一；代碼與名稱必填；代碼限 1–30 字元的 ASCII 英文、數字、-、_，保存為大寫；重複代碼回 409；建立者在同一交易內獲授權新公司，角色沿用其在目前公司的角色（ADR-015）。</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="H42" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:14</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:265</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.20.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.19.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B43" s="2" t="inlineStr">
@@ -1848,17 +1848,17 @@
       </x:c>
       <x:c r="C43" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Company Management</x:t>
+          <x:t xml:space="preserve">Logo &amp; Stamp</x:t>
         </x:is>
       </x:c>
       <x:c r="D43" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1.2</x:t>
+          <x:t xml:space="preserve">1.0</x:t>
         </x:is>
       </x:c>
       <x:c r="E43" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to edit a company.</x:t>
+          <x:t xml:space="preserve">System should let printing modules read the company's logo and stamp.</x:t>
         </x:is>
       </x:c>
       <x:c r="F43" s="2" t="inlineStr">
@@ -1868,19 +1868,19 @@
       </x:c>
       <x:c r="G43" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">版本不符回 409；審計欄位記錄修改者；目標公司不是用戶獲授權的公司時回 404；操作者在被修改的公司（含已停用）亦須有 SYS.COMPANY.EDIT，否則 403（ADR-032）。</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="H43" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:15</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:266</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.20.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.20.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B44" s="2" t="inlineStr">
@@ -1895,12 +1895,12 @@
       </x:c>
       <x:c r="D44" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1.0</x:t>
+          <x:t xml:space="preserve">1.2</x:t>
         </x:is>
       </x:c>
       <x:c r="E44" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to deactivate a company.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to view company details.</x:t>
         </x:is>
       </x:c>
       <x:c r="F44" s="2" t="inlineStr">
@@ -1910,19 +1910,19 @@
       </x:c>
       <x:c r="G44" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">停用後不能成為新操作的公司上下文；歷史資料保留。</x:t>
+          <x:t xml:space="preserve">僅有組織檢視權的用戶可見其獲授權且未刪除的公司；預設只列啟用公司，勾選「顯示已停用」時一併列出停用公司；列表支援分頁、關鍵字及代碼／名稱排序；無權限回 403。</x:t>
         </x:is>
       </x:c>
       <x:c r="H44" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:16</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:13</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.21.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.20.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B45" s="2" t="inlineStr">
@@ -1932,17 +1932,17 @@
       </x:c>
       <x:c r="C45" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Branch Management</x:t>
+          <x:t xml:space="preserve">Company Management</x:t>
         </x:is>
       </x:c>
       <x:c r="D45" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1.0</x:t>
+          <x:t xml:space="preserve">1.2</x:t>
         </x:is>
       </x:c>
       <x:c r="E45" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to view branches in the selected company.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to create a company.</x:t>
         </x:is>
       </x:c>
       <x:c r="F45" s="2" t="inlineStr">
@@ -1952,19 +1952,19 @@
       </x:c>
       <x:c r="G45" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">公司 A 的查詢不返回公司 B 分店；未選公司結果為空。</x:t>
+          <x:t xml:space="preserve">代碼全系統唯一；代碼與名稱必填；代碼限 1–30 字元的 ASCII 英文、數字、-、_，保存為大寫；重複代碼回 409；建立者在同一交易內獲授權新公司，角色沿用其在目前公司的角色（ADR-015）。</x:t>
         </x:is>
       </x:c>
       <x:c r="H45" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:17</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:14</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.21.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.20.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B46" s="2" t="inlineStr">
@@ -1974,17 +1974,17 @@
       </x:c>
       <x:c r="C46" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Branch Management</x:t>
+          <x:t xml:space="preserve">Company Management</x:t>
         </x:is>
       </x:c>
       <x:c r="D46" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1.0</x:t>
+          <x:t xml:space="preserve">1.2</x:t>
         </x:is>
       </x:c>
       <x:c r="E46" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to create a branch.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to edit a company.</x:t>
         </x:is>
       </x:c>
       <x:c r="F46" s="2" t="inlineStr">
@@ -1994,19 +1994,19 @@
       </x:c>
       <x:c r="G46" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">公司內代碼唯一；所屬公司必須為授權公司。</x:t>
+          <x:t xml:space="preserve">版本不符回 409；審計欄位記錄修改者；目標公司不是用戶獲授權的公司時回 404；操作者在被修改的公司（含已停用）亦須有 SYS.COMPANY.EDIT，否則 403（ADR-032）。</x:t>
         </x:is>
       </x:c>
       <x:c r="H46" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:18</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:15</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.21.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.20.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B47" s="2" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </x:c>
       <x:c r="C47" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Branch Management</x:t>
+          <x:t xml:space="preserve">Company Management</x:t>
         </x:is>
       </x:c>
       <x:c r="D47" s="2" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </x:c>
       <x:c r="E47" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to edit or deactivate a branch.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to deactivate a company.</x:t>
         </x:is>
       </x:c>
       <x:c r="F47" s="2" t="inlineStr">
@@ -2036,19 +2036,19 @@
       </x:c>
       <x:c r="G47" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">版本不符回 409；被引用時只可停用，不得刪除。</x:t>
+          <x:t xml:space="preserve">停用後不能成為新操作的公司上下文；歷史資料保留。</x:t>
         </x:is>
       </x:c>
       <x:c r="H47" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:19</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:16</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.22.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.21.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B48" s="2" t="inlineStr">
@@ -2058,7 +2058,7 @@
       </x:c>
       <x:c r="C48" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Department Management</x:t>
+          <x:t xml:space="preserve">Branch Management</x:t>
         </x:is>
       </x:c>
       <x:c r="D48" s="2" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </x:c>
       <x:c r="E48" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to view departments in the selected company.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to view branches in the selected company.</x:t>
         </x:is>
       </x:c>
       <x:c r="F48" s="2" t="inlineStr">
@@ -2078,19 +2078,19 @@
       </x:c>
       <x:c r="G48" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">公司隔離、軟刪除篩選生效。</x:t>
+          <x:t xml:space="preserve">公司 A 的查詢不返回公司 B 分店；未選公司結果為空。</x:t>
         </x:is>
       </x:c>
       <x:c r="H48" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:20</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:17</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.22.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.21.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B49" s="2" t="inlineStr">
@@ -2100,7 +2100,7 @@
       </x:c>
       <x:c r="C49" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Department Management</x:t>
+          <x:t xml:space="preserve">Branch Management</x:t>
         </x:is>
       </x:c>
       <x:c r="D49" s="2" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </x:c>
       <x:c r="E49" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to create a department under a branch or parent department.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to create a branch.</x:t>
         </x:is>
       </x:c>
       <x:c r="F49" s="2" t="inlineStr">
@@ -2120,19 +2120,19 @@
       </x:c>
       <x:c r="G49" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">分店與上級部門必須屬於同一公司；不得循環參照。</x:t>
+          <x:t xml:space="preserve">公司內代碼唯一；所屬公司必須為授權公司。</x:t>
         </x:is>
       </x:c>
       <x:c r="H49" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:21</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:18</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.22.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.21.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B50" s="2" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </x:c>
       <x:c r="C50" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Department Management</x:t>
+          <x:t xml:space="preserve">Branch Management</x:t>
         </x:is>
       </x:c>
       <x:c r="D50" s="2" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </x:c>
       <x:c r="E50" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to edit or deactivate a department.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to edit or deactivate a branch.</x:t>
         </x:is>
       </x:c>
       <x:c r="F50" s="2" t="inlineStr">
@@ -2162,19 +2162,19 @@
       </x:c>
       <x:c r="G50" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">版本不符回 409；被引用時只可停用。</x:t>
+          <x:t xml:space="preserve">版本不符回 409；被引用時只可停用，不得刪除。</x:t>
         </x:is>
       </x:c>
       <x:c r="H50" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:22</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:19</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.23.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.22.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B51" s="2" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </x:c>
       <x:c r="C51" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">User Identity and Password Security</x:t>
+          <x:t xml:space="preserve">Department Management</x:t>
         </x:is>
       </x:c>
       <x:c r="D51" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </x:c>
       <x:c r="E51" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to create a unique user identity.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to view departments in the selected company.</x:t>
         </x:is>
       </x:c>
       <x:c r="F51" s="2" t="inlineStr">
@@ -2204,19 +2204,19 @@
       </x:c>
       <x:c r="G51" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">帳號不分大小寫唯一，停用及軟刪除後仍不可重用；僅保存雜湊，不保存明文密碼。</x:t>
+          <x:t xml:space="preserve">公司隔離、軟刪除篩選生效。</x:t>
         </x:is>
       </x:c>
       <x:c r="H51" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:54</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:20</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.23.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.22.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B52" s="2" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </x:c>
       <x:c r="C52" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">User Identity and Password Security</x:t>
+          <x:t xml:space="preserve">Department Management</x:t>
         </x:is>
       </x:c>
       <x:c r="D52" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </x:c>
       <x:c r="E52" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enforce a configurable password policy.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to create a department under a branch or parent department.</x:t>
         </x:is>
       </x:c>
       <x:c r="F52" s="2" t="inlineStr">
@@ -2246,19 +2246,19 @@
       </x:c>
       <x:c r="G52" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">預設 12–128 字元且含大小寫、數字及符號；長度、複雜度與到期天數可由設定調整，不合法設定拒絕啟動。</x:t>
+          <x:t xml:space="preserve">分店與上級部門必須屬於同一公司；不得循環參照。</x:t>
         </x:is>
       </x:c>
       <x:c r="H52" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:55</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:21</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.23.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.22.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B53" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </x:c>
       <x:c r="C53" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">User Identity and Password Security</x:t>
+          <x:t xml:space="preserve">Department Management</x:t>
         </x:is>
       </x:c>
       <x:c r="D53" s="2" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </x:c>
       <x:c r="E53" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should lock an account after five consecutive failed password attempts.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to edit or deactivate a department.</x:t>
         </x:is>
       </x:c>
       <x:c r="F53" s="2" t="inlineStr">
@@ -2288,19 +2288,19 @@
       </x:c>
       <x:c r="G53" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">第 5 次連續失敗鎖定 15 分鐘；鎖定期間正確密碼亦不得通過；鎖定到期後開啟新失敗計數窗口，成功後清除計數。</x:t>
+          <x:t xml:space="preserve">版本不符回 409；被引用時只可停用。</x:t>
         </x:is>
       </x:c>
       <x:c r="H53" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:56</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:22</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.23.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.23.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B54" s="2" t="inlineStr">
@@ -2320,7 +2320,7 @@
       </x:c>
       <x:c r="E54" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should determine whether a user's password has expired.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to create a unique user identity.</x:t>
         </x:is>
       </x:c>
       <x:c r="F54" s="2" t="inlineStr">
@@ -2330,19 +2330,19 @@
       </x:c>
       <x:c r="G54" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">依設定天數及 password_changed_at 判斷；0 代表不設到期。登入簽發 Token 前必須檢查。</x:t>
+          <x:t xml:space="preserve">帳號不分大小寫唯一，停用及軟刪除後仍不可重用；僅保存雜湊，不保存明文密碼。</x:t>
         </x:is>
       </x:c>
       <x:c r="H54" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:57</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:54</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="55">
       <x:c r="A55" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.23.5</x:t>
+          <x:t xml:space="preserve">REQ_F4118.23.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B55" s="2" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </x:c>
       <x:c r="E55" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should list the users of the current company with paging, keyword and sorting.</x:t>
+          <x:t xml:space="preserve">System should enforce a configurable password policy.</x:t>
         </x:is>
       </x:c>
       <x:c r="F55" s="2" t="inlineStr">
@@ -2372,19 +2372,19 @@
       </x:c>
       <x:c r="G55" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">只列在目前公司有用戶公司關聯的用戶（含停用）；關鍵字不分大小寫比對帳號；排序 username／-username，其他欄位 400；回應不含雜湊、失敗次數及鎖定期限，只回 isLocked、isPasswordExpired（ADR-016）。</x:t>
+          <x:t xml:space="preserve">預設 12–128 字元且含大小寫、數字及符號；長度、複雜度與到期天數可由設定調整，不合法設定拒絕啟動。</x:t>
         </x:is>
       </x:c>
       <x:c r="H55" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:58</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:55</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="56">
       <x:c r="A56" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.23.6</x:t>
+          <x:t xml:space="preserve">REQ_F4118.23.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B56" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </x:c>
       <x:c r="E56" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to create a user in the current company.</x:t>
+          <x:t xml:space="preserve">System should lock an account after five consecutive failed password attempts.</x:t>
         </x:is>
       </x:c>
       <x:c r="F56" s="2" t="inlineStr">
@@ -2414,19 +2414,19 @@
       </x:c>
       <x:c r="G56" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">需 SYS.USER.CREATE；同一交易建立身分及目前公司的預設關聯（無角色）；重複帳號（不分大小寫、含他公司）409 SYS.USER.DUPLICATE；弱密碼或帳號格式錯誤 400；建立後可登入。</x:t>
+          <x:t xml:space="preserve">第 5 次連續失敗鎖定 15 分鐘；鎖定期間正確密碼亦不得通過；鎖定到期後開啟新失敗計數窗口，成功後清除計數。</x:t>
         </x:is>
       </x:c>
       <x:c r="H56" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:59</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:56</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="57">
       <x:c r="A57" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.23.7</x:t>
+          <x:t xml:space="preserve">REQ_F4118.23.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B57" s="2" t="inlineStr">
@@ -2441,12 +2441,12 @@
       </x:c>
       <x:c r="D57" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1.1</x:t>
+          <x:t xml:space="preserve">1.0</x:t>
         </x:is>
       </x:c>
       <x:c r="E57" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to activate or deactivate a user.</x:t>
+          <x:t xml:space="preserve">System should determine whether a user's password has expired.</x:t>
         </x:is>
       </x:c>
       <x:c r="F57" s="2" t="inlineStr">
@@ -2456,19 +2456,19 @@
       </x:c>
       <x:c r="G57" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">需 SYS.USER.EDIT 並帶 version（過期 409）；停用後不可登入與刷新，重新啟用後可登入；不可停用自己 422 SYS.USER.SELF_DEACTIVATION；他公司用戶 404；用戶亦屬於其他公司時，操作者在每間已啟用關聯的公司都要有 SYS.USER.EDIT（否則 403 COMMON.PERMISSION.DENIED），且用戶角色不超出操作者權限（否則 403 SYS.ROLE.BEYOND_AUTHORITY），ADR-032。</x:t>
+          <x:t xml:space="preserve">依設定天數及 password_changed_at 判斷；0 代表不設到期。登入簽發 Token 前必須檢查。</x:t>
         </x:is>
       </x:c>
       <x:c r="H57" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:60</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:57</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="58">
       <x:c r="A58" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.23.8</x:t>
+          <x:t xml:space="preserve">REQ_F4118.23.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B58" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </x:c>
       <x:c r="D58" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1.1</x:t>
+          <x:t xml:space="preserve">1.0</x:t>
         </x:is>
       </x:c>
       <x:c r="E58" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to reset a password and unlock a locked user.</x:t>
+          <x:t xml:space="preserve">System should list the users of the current company with paging, keyword and sorting.</x:t>
         </x:is>
       </x:c>
       <x:c r="F58" s="2" t="inlineStr">
@@ -2498,19 +2498,19 @@
       </x:c>
       <x:c r="G58" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">重設密碼需 SYS.USER.RESET_PASSWORD，依密碼政策驗證，重新起算到期並清除鎖定，舊密碼即失效；解鎖需 SYS.USER.EDIT，清除失敗計數與鎖定，未鎖定時亦回 204；他公司用戶 404；跨公司與角色上限檢查同 REQ_F4118.23.7（ADR-032）。</x:t>
+          <x:t xml:space="preserve">只列在目前公司有用戶公司關聯的用戶（含停用）；關鍵字不分大小寫比對帳號；排序 username／-username，其他欄位 400；回應不含雜湊、失敗次數及鎖定期限，只回 isLocked、isPasswordExpired（ADR-016）。</x:t>
         </x:is>
       </x:c>
       <x:c r="H58" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:61</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:58</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="59">
       <x:c r="A59" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.24.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.23.6</x:t>
         </x:is>
       </x:c>
       <x:c r="B59" s="2" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </x:c>
       <x:c r="C59" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Login, Token and Captcha</x:t>
+          <x:t xml:space="preserve">User Identity and Password Security</x:t>
         </x:is>
       </x:c>
       <x:c r="D59" s="2" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </x:c>
       <x:c r="E59" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow a user to log in with username, password and a numeric captcha.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to create a user in the current company.</x:t>
         </x:is>
       </x:c>
       <x:c r="F59" s="2" t="inlineStr">
@@ -2540,19 +2540,19 @@
       </x:c>
       <x:c r="G59" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">帳號不分大小寫；Captcha 4–6 位數字，答案只存伺服器端，驗證一次即作廢（不論對錯）；帳密錯誤、帳號不存在、停用或鎖定一律回 401 SYS.AUTH.INVALID_CREDENTIALS；密碼到期回 403 SYS.AUTH.PASSWORD_EXPIRED 且不發 Token。</x:t>
+          <x:t xml:space="preserve">需 SYS.USER.CREATE；同一交易建立身分及目前公司的預設關聯（無角色）；重複帳號（不分大小寫、含他公司）409 SYS.USER.DUPLICATE；弱密碼或帳號格式錯誤 400；建立後可登入。</x:t>
         </x:is>
       </x:c>
       <x:c r="H59" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:73</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:59</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="60">
       <x:c r="A60" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.24.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.23.7</x:t>
         </x:is>
       </x:c>
       <x:c r="B60" s="2" t="inlineStr">
@@ -2562,17 +2562,17 @@
       </x:c>
       <x:c r="C60" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Login, Token and Captcha</x:t>
+          <x:t xml:space="preserve">User Identity and Password Security</x:t>
         </x:is>
       </x:c>
       <x:c r="D60" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1.0</x:t>
+          <x:t xml:space="preserve">1.1</x:t>
         </x:is>
       </x:c>
       <x:c r="E60" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should issue a 15-minute access token and a 7-day rotating refresh token.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to activate or deactivate a user.</x:t>
         </x:is>
       </x:c>
       <x:c r="F60" s="2" t="inlineStr">
@@ -2582,19 +2582,19 @@
       </x:c>
       <x:c r="G60" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Access Token 為 HS256 JWT，sub 為用戶 Id；Refresh Token 只以 SHA-256 雜湊存 Redis，使用一次即輪替，並發重放只有一個成功。</x:t>
+          <x:t xml:space="preserve">需 SYS.USER.EDIT 並帶 version（過期 409）；停用後不可登入與刷新，重新啟用後可登入；不可停用自己 422 SYS.USER.SELF_DEACTIVATION；他公司用戶 404；用戶亦屬於其他公司時，操作者在每間已啟用關聯的公司都要有 SYS.USER.EDIT（否則 403 COMMON.PERMISSION.DENIED），且用戶角色不超出操作者權限（否則 403 SYS.ROLE.BEYOND_AUTHORITY），ADR-032。</x:t>
         </x:is>
       </x:c>
       <x:c r="H60" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:74</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:60</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="61">
       <x:c r="A61" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.24.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.23.8</x:t>
         </x:is>
       </x:c>
       <x:c r="B61" s="2" t="inlineStr">
@@ -2604,17 +2604,17 @@
       </x:c>
       <x:c r="C61" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Login, Token and Captcha</x:t>
+          <x:t xml:space="preserve">User Identity and Password Security</x:t>
         </x:is>
       </x:c>
       <x:c r="D61" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1.0</x:t>
+          <x:t xml:space="preserve">1.1</x:t>
         </x:is>
       </x:c>
       <x:c r="E61" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow a logged-in user to log out and invalidate the refresh token.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to reset a password and unlock a locked user.</x:t>
         </x:is>
       </x:c>
       <x:c r="F61" s="2" t="inlineStr">
@@ -2624,19 +2624,19 @@
       </x:c>
       <x:c r="G61" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">登出須帶有效 Access Token；只撤銷屬於本人的 Refresh Token，撤銷後刷新回 401。</x:t>
+          <x:t xml:space="preserve">重設密碼需 SYS.USER.RESET_PASSWORD，依密碼政策驗證，重新起算到期並清除鎖定，舊密碼即失效；解鎖需 SYS.USER.EDIT，清除失敗計數與鎖定，未鎖定時亦回 204；他公司用戶 404；跨公司與角色上限檢查同 REQ_F4118.23.7（ADR-032）。</x:t>
         </x:is>
       </x:c>
       <x:c r="H61" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:75</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:61</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="62">
       <x:c r="A62" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.24.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.24.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B62" s="2" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </x:c>
       <x:c r="E62" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should provide a development-only captcha master code with startup protection.</x:t>
+          <x:t xml:space="preserve">System should allow a user to log in with username, password and a numeric captcha.</x:t>
         </x:is>
       </x:c>
       <x:c r="F62" s="2" t="inlineStr">
@@ -2666,19 +2666,19 @@
       </x:c>
       <x:c r="G62" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Captcha:MasterCode 只在 Development 生效且須為 4–6 位數字；其他環境有設定即寫 Error 並拒絕啟動；每次使用寫 Warning（帳號、IP），並寫 sys_audit_log 安全事件 MASTER_CODE_LOGIN（REQ_F4118.27.3）。</x:t>
+          <x:t xml:space="preserve">帳號不分大小寫；Captcha 4–6 位數字，答案只存伺服器端，驗證一次即作廢（不論對錯）；帳密錯誤、帳號不存在、停用或鎖定一律回 401 SYS.AUTH.INVALID_CREDENTIALS；密碼到期回 403 SYS.AUTH.PASSWORD_EXPIRED 且不發 Token。</x:t>
         </x:is>
       </x:c>
       <x:c r="H62" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:76</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:73</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="63">
       <x:c r="A63" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.24.5</x:t>
+          <x:t xml:space="preserve">REQ_F4118.24.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B63" s="2" t="inlineStr">
@@ -2698,7 +2698,7 @@
       </x:c>
       <x:c r="E63" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should provide a trilingual login page that keeps the session and refreshes tokens automatically.</x:t>
+          <x:t xml:space="preserve">System should issue a 15-minute access token and a 7-day rotating refresh token.</x:t>
         </x:is>
       </x:c>
       <x:c r="F63" s="2" t="inlineStr">
@@ -2708,19 +2708,19 @@
       </x:c>
       <x:c r="G63" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">未登入進入主框架導向 /login?returnUrl=…，登入後只回到站內路徑；Captcha 元件只收 4–6 位數字，失敗後換新圖並清空密碼；錯誤依 errorCode 三語顯示；API 請求帶 Bearer，401 時只刷新一次並重送，並發 401 共用同一 refresh；刷新失敗清除 Session 回登入頁；登出撤銷 Refresh Token，伺服器失敗也清除本機 Session。</x:t>
+          <x:t xml:space="preserve">Access Token 為 HS256 JWT，sub 為用戶 Id；Refresh Token 只以 SHA-256 雜湊存 Redis，使用一次即輪替，並發重放只有一個成功。</x:t>
         </x:is>
       </x:c>
       <x:c r="H63" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:77</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:74</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="64">
       <x:c r="A64" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.25.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.24.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B64" s="2" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </x:c>
       <x:c r="C64" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Role, Permission and Data Scope</x:t>
+          <x:t xml:space="preserve">Login, Token and Captcha</x:t>
         </x:is>
       </x:c>
       <x:c r="D64" s="2" t="inlineStr">
@@ -2740,7 +2740,7 @@
       </x:c>
       <x:c r="E64" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to view roles and the permission catalog.</x:t>
+          <x:t xml:space="preserve">System should allow a logged-in user to log out and invalidate the refresh token.</x:t>
         </x:is>
       </x:c>
       <x:c r="F64" s="2" t="inlineStr">
@@ -2750,19 +2750,19 @@
       </x:c>
       <x:c r="G64" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">需 SYS.ROLE.VIEW；角色列表支援分頁、關鍵字（代碼／名稱）、code／name 排序；權限目錄列出各模組宣告的全部代碼；已軟刪除角色不顯示，查詢回 404。</x:t>
+          <x:t xml:space="preserve">登出須帶有效 Access Token；只撤銷屬於本人的 Refresh Token，撤銷後刷新回 401。</x:t>
         </x:is>
       </x:c>
       <x:c r="H64" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:89</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:75</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="65">
       <x:c r="A65" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.25.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.24.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B65" s="2" t="inlineStr">
@@ -2772,7 +2772,7 @@
       </x:c>
       <x:c r="C65" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Role, Permission and Data Scope</x:t>
+          <x:t xml:space="preserve">Login, Token and Captcha</x:t>
         </x:is>
       </x:c>
       <x:c r="D65" s="2" t="inlineStr">
@@ -2782,7 +2782,7 @@
       </x:c>
       <x:c r="E65" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to create a role with permissions and a data scope.</x:t>
+          <x:t xml:space="preserve">System should provide a development-only captcha master code with startup protection.</x:t>
         </x:is>
       </x:c>
       <x:c r="F65" s="2" t="inlineStr">
@@ -2792,19 +2792,19 @@
       </x:c>
       <x:c r="G65" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">需 SYS.ROLE.CREATE；代碼 1–50 字元 ASCII 英文、數字、-、_，保存為大寫，全系統唯一（含已刪除），重複回 409 SYS.ROLE.DUPLICATE_CODE；權限代碼不分大小寫輸入，必須在權限目錄內，否則 400；資料範圍為 Self／Department／Branch／Company。</x:t>
+          <x:t xml:space="preserve">Captcha:MasterCode 只在 Development 生效且須為 4–6 位數字；其他環境有設定即寫 Error 並拒絕啟動；每次使用寫 Warning（帳號、IP），並寫 sys_audit_log 安全事件 MASTER_CODE_LOGIN（REQ_F4118.27.3）。</x:t>
         </x:is>
       </x:c>
       <x:c r="H65" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:90</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:76</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="66">
       <x:c r="A66" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.25.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.24.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B66" s="2" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </x:c>
       <x:c r="C66" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Role, Permission and Data Scope</x:t>
+          <x:t xml:space="preserve">Login, Token and Captcha</x:t>
         </x:is>
       </x:c>
       <x:c r="D66" s="2" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </x:c>
       <x:c r="E66" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to edit or deactivate a role.</x:t>
+          <x:t xml:space="preserve">System should provide a trilingual login page that keeps the session and refreshes tokens automatically.</x:t>
         </x:is>
       </x:c>
       <x:c r="F66" s="2" t="inlineStr">
@@ -2834,19 +2834,19 @@
       </x:c>
       <x:c r="G66" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">需 SYS.ROLE.EDIT；帶 version，不符回 409，且權限集合不變（同一交易）；停用角色立即不再授予權限。角色是全系統定義：操作者在角色已指派的每間公司都必須全權，否則 403 SYS.AUTHORITY.FULL_ACCESS_REQUIRED（ADR-033）。</x:t>
+          <x:t xml:space="preserve">未登入進入主框架導向 /login?returnUrl=…，登入後只回到站內路徑；Captcha 元件只收 4–6 位數字，失敗後換新圖並清空密碼；錯誤依 errorCode 三語顯示；API 請求帶 Bearer，401 時只刷新一次並重送，並發 401 共用同一 refresh；刷新失敗清除 Session 回登入頁；登出撤銷 Refresh Token，伺服器失敗也清除本機 Session。</x:t>
         </x:is>
       </x:c>
       <x:c r="H66" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:91</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:77</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.25.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.25.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B67" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </x:c>
       <x:c r="E67" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to delete an unused role.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to view roles and the permission catalog.</x:t>
         </x:is>
       </x:c>
       <x:c r="F67" s="2" t="inlineStr">
@@ -2876,19 +2876,19 @@
       </x:c>
       <x:c r="G67" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">需 SYS.ROLE.DELETE；仍有用戶使用回 422 SYS.ROLE.IN_USE；軟刪除，代碼不可重用。</x:t>
+          <x:t xml:space="preserve">需 SYS.ROLE.VIEW；角色列表支援分頁、關鍵字（代碼／名稱）、code／name 排序；權限目錄列出各模組宣告的全部代碼；已軟刪除角色不顯示，查詢回 404。</x:t>
         </x:is>
       </x:c>
       <x:c r="H67" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:92</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:89</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.25.5</x:t>
+          <x:t xml:space="preserve">REQ_F4118.25.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B68" s="2" t="inlineStr">
@@ -2908,7 +2908,7 @@
       </x:c>
       <x:c r="E68" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enforce permission codes on every API with the backend as the authority.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to create a role with permissions and a data scope.</x:t>
         </x:is>
       </x:c>
       <x:c r="F68" s="2" t="inlineStr">
@@ -2918,19 +2918,19 @@
       </x:c>
       <x:c r="G68" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">每個 API 動作標註 模組.資源.動作 權限（ArchitectureTests 檢查）；未登入 401；缺權限或沒有公司上下文 403 COMMON.PERMISSION.DENIED；已登入請求的 X-Company-Id 不可存取（未授權、用戶公司關聯停用、公司停用）一律 403 COMMON.COMPANY.ACCESS_DENIED。</x:t>
+          <x:t xml:space="preserve">需 SYS.ROLE.CREATE；代碼 1–50 字元 ASCII 英文、數字、-、_，保存為大寫，全系統唯一（含已刪除），重複回 409 SYS.ROLE.DUPLICATE_CODE；權限代碼不分大小寫輸入，必須在權限目錄內，否則 400；資料範圍為 Self／Department／Branch／Company。</x:t>
         </x:is>
       </x:c>
       <x:c r="H68" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:93</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:90</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="69">
       <x:c r="A69" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.25.6</x:t>
+          <x:t xml:space="preserve">REQ_F4118.25.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B69" s="2" t="inlineStr">
@@ -2945,12 +2945,12 @@
       </x:c>
       <x:c r="D69" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1.1</x:t>
+          <x:t xml:space="preserve">1.0</x:t>
         </x:is>
       </x:c>
       <x:c r="E69" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to grant a user access to a company with roles, organization and default company.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to edit or deactivate a role.</x:t>
         </x:is>
       </x:c>
       <x:c r="F69" s="2" t="inlineStr">
@@ -2960,19 +2960,19 @@
       </x:c>
       <x:c r="G69" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">需 SYS.USER.EDIT；公司必須啟用；分店／部門必須屬於該公司且啟用；角色必須存在且啟用；角色整組取代；每位用戶最多一間預設公司（設定新預設會取消舊預設）。用戶不存在或不屬於目前公司回 404 SYS.USER.NOT_FOUND；目標公司不是操作者獲授權的公司回 404 SYS.COMPANY.NOT_FOUND；不可停用自己的公司授權（422 SYS.USER.SELF_DEACTIVATION）（ADR-017）。操作者在目標公司亦須有 SYS.USER.EDIT（否則 403 COMMON.PERMISSION.DENIED）；新增或移除的角色須在操作者權限之內（全權角色只限全權操作者；一般角色的每個權限操作者都有且範圍不窄於角色），否則 403 SYS.ROLE.BEYOND_AUTHORITY；不可變更自己的角色（422 SYS.USER.SELF_ROLE_CHANGE），角色不變時可改組織與預設公司（ADR-032）。</x:t>
+          <x:t xml:space="preserve">需 SYS.ROLE.EDIT；帶 version，不符回 409，且權限集合不變（同一交易）；停用角色立即不再授予權限。角色是全系統定義：操作者在角色已指派的每間公司都必須全權，否則 403 SYS.AUTHORITY.FULL_ACCESS_REQUIRED（ADR-033）。</x:t>
         </x:is>
       </x:c>
       <x:c r="H69" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:94</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:91</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="70">
       <x:c r="A70" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.25.7</x:t>
+          <x:t xml:space="preserve">REQ_F4118.25.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B70" s="2" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </x:c>
       <x:c r="E70" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should resolve the user's effective permissions and data scope per company and hide unauthorized UI.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to delete an unused role.</x:t>
         </x:is>
       </x:c>
       <x:c r="F70" s="2" t="inlineStr">
@@ -3002,19 +3002,19 @@
       </x:c>
       <x:c r="G70" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">同一權限取各啟用角色最寬的資料範圍；全權角色視為全部權限、全公司範圍；分店／部門範圍但用戶無對應歸屬時退回本人。GET /api/v1/sys/auth/authorization 回傳可存取公司（預設在前）與目前公司權限；前端 *erpHasPermission、permissionGuard 與選單依此隱藏，切換公司重新載入；本機記住的公司不可存取時改用預設公司。</x:t>
+          <x:t xml:space="preserve">需 SYS.ROLE.DELETE；仍有用戶使用回 422 SYS.ROLE.IN_USE；軟刪除，代碼不可重用。</x:t>
         </x:is>
       </x:c>
       <x:c r="H70" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:95</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:92</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="71">
       <x:c r="A71" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.25.8</x:t>
+          <x:t xml:space="preserve">REQ_F4118.25.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B71" s="2" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </x:c>
       <x:c r="E71" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to view a user's company access, organization and roles.</x:t>
+          <x:t xml:space="preserve">System should enforce permission codes on every API with the backend as the authority.</x:t>
         </x:is>
       </x:c>
       <x:c r="F71" s="2" t="inlineStr">
@@ -3044,19 +3044,19 @@
       </x:c>
       <x:c r="G71" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">需 SYS.USER.VIEW；用戶須屬於目前公司，否則 404；只列出操作者獲授權公司的指派（公司代碼／名稱、分店、部門、預設、啟用、角色 ID），依公司代碼排序（ADR-017）。</x:t>
+          <x:t xml:space="preserve">每個 API 動作標註 模組.資源.動作 權限（ArchitectureTests 檢查）；未登入 401；缺權限或沒有公司上下文 403 COMMON.PERMISSION.DENIED；已登入請求的 X-Company-Id 不可存取（未授權、用戶公司關聯停用、公司停用）一律 403 COMMON.COMPANY.ACCESS_DENIED。</x:t>
         </x:is>
       </x:c>
       <x:c r="H71" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:96</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:93</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="72">
       <x:c r="A72" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.26.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.25.6</x:t>
         </x:is>
       </x:c>
       <x:c r="B72" s="2" t="inlineStr">
@@ -3066,17 +3066,17 @@
       </x:c>
       <x:c r="C72" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Web Security Middleware</x:t>
+          <x:t xml:space="preserve">Role, Permission and Data Scope</x:t>
         </x:is>
       </x:c>
       <x:c r="D72" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1.0</x:t>
+          <x:t xml:space="preserve">1.1</x:t>
         </x:is>
       </x:c>
       <x:c r="E72" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enforce HTTPS with HSTS outside the development environment.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to grant a user access to a company with roles, organization and default company.</x:t>
         </x:is>
       </x:c>
       <x:c r="F72" s="2" t="inlineStr">
@@ -3086,19 +3086,19 @@
       </x:c>
       <x:c r="G72" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">非 Development：HTTP 請求 307 轉 HTTPS；HTTPS 回應帶 Strict-Transport-Security: max-age=31536000; includeSubDomains（天數可設定）。Development 不轉址、不送 HSTS。</x:t>
+          <x:t xml:space="preserve">需 SYS.USER.EDIT；公司必須啟用；分店／部門必須屬於該公司且啟用；角色必須存在且啟用；角色整組取代；每位用戶最多一間預設公司（設定新預設會取消舊預設）。用戶不存在或不屬於目前公司回 404 SYS.USER.NOT_FOUND；目標公司不是操作者獲授權的公司回 404 SYS.COMPANY.NOT_FOUND；不可停用自己的公司授權（422 SYS.USER.SELF_DEACTIVATION）（ADR-017）。操作者在目標公司亦須有 SYS.USER.EDIT（否則 403 COMMON.PERMISSION.DENIED）；新增或移除的角色須在操作者權限之內（全權角色只限全權操作者；一般角色的每個權限操作者都有且範圍不窄於角色），否則 403 SYS.ROLE.BEYOND_AUTHORITY；不可變更自己的角色（422 SYS.USER.SELF_ROLE_CHANGE），角色不變時可改組織與預設公司（ADR-032）。</x:t>
         </x:is>
       </x:c>
       <x:c r="H72" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:110</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:94</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="73">
       <x:c r="A73" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.26.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.25.7</x:t>
         </x:is>
       </x:c>
       <x:c r="B73" s="2" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </x:c>
       <x:c r="C73" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Web Security Middleware</x:t>
+          <x:t xml:space="preserve">Role, Permission and Data Scope</x:t>
         </x:is>
       </x:c>
       <x:c r="D73" s="2" t="inlineStr">
@@ -3118,7 +3118,7 @@
       </x:c>
       <x:c r="E73" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow cross-origin requests only from configured frontend origins.</x:t>
+          <x:t xml:space="preserve">System should resolve the user's effective permissions and data scope per company and hide unauthorized UI.</x:t>
         </x:is>
       </x:c>
       <x:c r="F73" s="2" t="inlineStr">
@@ -3128,19 +3128,19 @@
       </x:c>
       <x:c r="G73" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">來源清單在 Security:Cors:AllowedOrigins，預設空（不允許跨來源）；只接受 scheme://host[:port]，萬用字元、含路徑或非 http(s) 拒絕啟動；不允許 Credentials；允許標頭 Authorization、Content-Type、Accept、Accept-Language、X-Company-Id；公開 Retry-After、Content-Disposition；未列明的來源預檢回應不含 Access-Control-Allow-Origin。</x:t>
+          <x:t xml:space="preserve">同一權限取各啟用角色最寬的資料範圍；全權角色視為全部權限、全公司範圍；分店／部門範圍但用戶無對應歸屬時退回本人。GET /api/v1/sys/auth/authorization 回傳可存取公司（預設在前）與目前公司權限；前端 *erpHasPermission、permissionGuard 與選單依此隱藏，切換公司重新載入；本機記住的公司不可存取時改用預設公司。</x:t>
         </x:is>
       </x:c>
       <x:c r="H73" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:111</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:95</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="74">
       <x:c r="A74" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.26.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.25.8</x:t>
         </x:is>
       </x:c>
       <x:c r="B74" s="2" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </x:c>
       <x:c r="C74" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Web Security Middleware</x:t>
+          <x:t xml:space="preserve">Role, Permission and Data Scope</x:t>
         </x:is>
       </x:c>
       <x:c r="D74" s="2" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </x:c>
       <x:c r="E74" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should rate-limit login, token refresh and captcha requests per client IP.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to view a user's company access, organization and roles.</x:t>
         </x:is>
       </x:c>
       <x:c r="F74" s="2" t="inlineStr">
@@ -3170,19 +3170,19 @@
       </x:c>
       <x:c r="G74" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">登入、Token 刷新每 IP 每端點每分鐘 5 次；Captcha 每 IP 每分鐘 10 次（ADR-018）；超過回 429 ProblemDetails，errorCode 為 COMMON.REQUEST.RATE_LIMITED，標題依 Accept-Language 三語，帶 Retry-After；寫 Warning 日誌（方法、路徑、IP）。CORS 預檢不計入。每個匿名端點必須套用按 IP 的限流政策（ArchitectureTests 檢查）。</x:t>
+          <x:t xml:space="preserve">需 SYS.USER.VIEW；用戶須屬於目前公司，否則 404；只列出操作者獲授權公司的指派（公司代碼／名稱、分店、部門、預設、啟用、角色 ID），依公司代碼排序（ADR-017）。</x:t>
         </x:is>
       </x:c>
       <x:c r="H74" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:112</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:96</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="75">
       <x:c r="A75" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.26.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.26.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B75" s="2" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </x:c>
       <x:c r="E75" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should rate-limit authenticated API requests per user.</x:t>
+          <x:t xml:space="preserve">System should enforce HTTPS with HSTS outside the development environment.</x:t>
         </x:is>
       </x:c>
       <x:c r="F75" s="2" t="inlineStr">
@@ -3212,19 +3212,19 @@
       </x:c>
       <x:c r="G75" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">已登入請求每用戶每分鐘 300 次（可設定），不同用戶分開計數；匯出報表政策每用戶每分鐘 10 次，供日後匯出端點套用。白名單內的 IP 仍受限流。</x:t>
+          <x:t xml:space="preserve">非 Development：HTTP 請求 307 轉 HTTPS；HTTPS 回應帶 Strict-Transport-Security: max-age=31536000; includeSubDomains（天數可設定）。Development 不轉址、不送 HSTS。</x:t>
         </x:is>
       </x:c>
       <x:c r="H75" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:113</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:110</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="76">
       <x:c r="A76" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.26.5</x:t>
+          <x:t xml:space="preserve">REQ_F4118.26.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B76" s="2" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </x:c>
       <x:c r="E76" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should add security headers to every API response.</x:t>
+          <x:t xml:space="preserve">System should allow cross-origin requests only from configured frontend origins.</x:t>
         </x:is>
       </x:c>
       <x:c r="F76" s="2" t="inlineStr">
@@ -3254,19 +3254,19 @@
       </x:c>
       <x:c r="G76" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">所有回應（含 404、429、500）帶 X-Content-Type-Options: nosniff、X-Frame-Options: DENY、Referrer-Policy: no-referrer、Content-Security-Policy: default-src 'none'; frame-ancestors 'none'; base-uri 'none'; form-action 'none'。前端站台的 CSP 見 architecture/security.md，E2E 在該 CSP 下執行。</x:t>
+          <x:t xml:space="preserve">來源清單在 Security:Cors:AllowedOrigins，預設空（不允許跨來源）；只接受 scheme://host[:port]，萬用字元、含路徑或非 http(s) 拒絕啟動；不允許 Credentials；允許標頭 Authorization、Content-Type、Accept、Accept-Language、X-Company-Id；公開 Retry-After、Content-Disposition；未列明的來源預檢回應不含 Access-Control-Allow-Origin。</x:t>
         </x:is>
       </x:c>
       <x:c r="H76" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:114</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:111</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="77">
       <x:c r="A77" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.26.6</x:t>
+          <x:t xml:space="preserve">REQ_F4118.26.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B77" s="2" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </x:c>
       <x:c r="E77" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should honour X-Forwarded-For only from configured proxies.</x:t>
+          <x:t xml:space="preserve">System should rate-limit login, token refresh and captcha requests per client IP.</x:t>
         </x:is>
       </x:c>
       <x:c r="F77" s="2" t="inlineStr">
@@ -3296,19 +3296,19 @@
       </x:c>
       <x:c r="G77" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Security:ForwardedHeaders:KnownProxies（IP）與 KnownNetworks（CIDR）皆空時不處理 X-Forwarded-*；有設定時只信任列明來源，其他來源偽造的 X-Forwarded-For 被忽略，限流與日誌使用連線 IP；格式錯誤拒絕啟動。</x:t>
+          <x:t xml:space="preserve">登入、Token 刷新每 IP 每端點每分鐘 5 次；Captcha 每 IP 每分鐘 10 次（ADR-018）；超過回 429 ProblemDetails，errorCode 為 COMMON.REQUEST.RATE_LIMITED，標題依 Accept-Language 三語，帶 Retry-After；寫 Warning 日誌（方法、路徑、IP）。CORS 預檢不計入。每個匿名端點必須套用按 IP 的限流政策（ArchitectureTests 檢查）。</x:t>
         </x:is>
       </x:c>
       <x:c r="H77" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:115</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:112</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="78">
       <x:c r="A78" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.26.7</x:t>
+          <x:t xml:space="preserve">REQ_F4118.26.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B78" s="2" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </x:c>
       <x:c r="E78" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should show a trilingual "too many requests" message when an API call is rate-limited.</x:t>
+          <x:t xml:space="preserve">System should rate-limit authenticated API requests per user.</x:t>
         </x:is>
       </x:c>
       <x:c r="F78" s="2" t="inlineStr">
@@ -3338,19 +3338,19 @@
       </x:c>
       <x:c r="G78" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">前端收到 429 一律顯示 errors.COMMON.REQUEST.RATE_LIMITED（三語），登入頁、組織、用戶、角色頁共用 apiErrorKey。</x:t>
+          <x:t xml:space="preserve">已登入請求每用戶每分鐘 300 次（可設定），不同用戶分開計數；匯出報表政策每用戶每分鐘 10 次，供日後匯出端點套用。白名單內的 IP 仍受限流。</x:t>
         </x:is>
       </x:c>
       <x:c r="H78" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:116</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:113</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="79">
       <x:c r="A79" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.27.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.26.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B79" s="2" t="inlineStr">
@@ -3360,7 +3360,7 @@
       </x:c>
       <x:c r="C79" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Audit Log</x:t>
+          <x:t xml:space="preserve">Web Security Middleware</x:t>
         </x:is>
       </x:c>
       <x:c r="D79" s="2" t="inlineStr">
@@ -3370,7 +3370,7 @@
       </x:c>
       <x:c r="E79" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should record every data change in sys_audit_log within the same transaction.</x:t>
+          <x:t xml:space="preserve">System should add security headers to every API response.</x:t>
         </x:is>
       </x:c>
       <x:c r="F79" s="2" t="inlineStr">
@@ -3380,19 +3380,19 @@
       </x:c>
       <x:c r="G79" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">透過 EF 新增、修改、刪除（含軟刪除）都寫一筆記錄，內容包括公司、用戶（背景程序為系統用戶）、時間（IClock）、表名、記錄 Id、操作類型（CREATE／UPDATE／DELETE，可由 Application 指定 VOID／APPROVE／POST）、欄位差異 JSON（修改只列有變更的欄位）、來源 IP、TraceId。沒有欄位變更不寫記錄。交易回滾或 SaveChanges 失敗（含樂觀鎖衝突）不留記錄，重試時也不會重複（ADR-019）。</x:t>
+          <x:t xml:space="preserve">所有回應（含 404、429、500）帶 X-Content-Type-Options: nosniff、X-Frame-Options: DENY、Referrer-Policy: no-referrer、Content-Security-Policy: default-src 'none'; frame-ancestors 'none'; base-uri 'none'; form-action 'none'。前端站台的 CSP 見 architecture/security.md，E2E 在該 CSP 下執行。</x:t>
         </x:is>
       </x:c>
       <x:c r="H79" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:128</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:114</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="80">
       <x:c r="A80" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.27.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.26.6</x:t>
         </x:is>
       </x:c>
       <x:c r="B80" s="2" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </x:c>
       <x:c r="C80" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Audit Log</x:t>
+          <x:t xml:space="preserve">Web Security Middleware</x:t>
         </x:is>
       </x:c>
       <x:c r="D80" s="2" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </x:c>
       <x:c r="E80" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should protect audit records and sensitive values.</x:t>
+          <x:t xml:space="preserve">System should honour X-Forwarded-For only from configured proxies.</x:t>
         </x:is>
       </x:c>
       <x:c r="F80" s="2" t="inlineStr">
@@ -3422,19 +3422,19 @@
       </x:c>
       <x:c r="G80" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">[SensitiveData] 欄位（例如 password_hash）的值以 * 遮蔽；主鍵、審計欄位、version、company_id 不記錄差異。sys_audit_log 只能新增，UPDATE 或 DELETE 由 trigger 拒絕（append-only）；changes 必須是 JSON。</x:t>
+          <x:t xml:space="preserve">Security:ForwardedHeaders:KnownProxies（IP）與 KnownNetworks（CIDR）皆空時不處理 X-Forwarded-*；有設定時只信任列明來源，其他來源偽造的 X-Forwarded-For 被忽略，限流與日誌使用連線 IP；格式錯誤拒絕啟動。</x:t>
         </x:is>
       </x:c>
       <x:c r="H80" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:129</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:115</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="81">
       <x:c r="A81" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.27.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.26.7</x:t>
         </x:is>
       </x:c>
       <x:c r="B81" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </x:c>
       <x:c r="C81" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Audit Log</x:t>
+          <x:t xml:space="preserve">Web Security Middleware</x:t>
         </x:is>
       </x:c>
       <x:c r="D81" s="2" t="inlineStr">
@@ -3454,7 +3454,7 @@
       </x:c>
       <x:c r="E81" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should record login, failed login, logout and captcha master-code login as security events.</x:t>
+          <x:t xml:space="preserve">System should show a trilingual "too many requests" message when an API call is rate-limited.</x:t>
         </x:is>
       </x:c>
       <x:c r="F81" s="2" t="inlineStr">
@@ -3464,19 +3464,19 @@
       </x:c>
       <x:c r="G81" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">安全事件記錄帳號、IP、時間與 TraceId。LOGIN_FAILED 的原因只寫 INVALID_CREDENTIALS 或 PASSWORD_EXPIRED，不寫密碼。萬用碼登入不論結果都寫 MASTER_CODE_LOGIN（REQ_F4118.24.4）。</x:t>
+          <x:t xml:space="preserve">前端收到 429 一律顯示 errors.COMMON.REQUEST.RATE_LIMITED（三語），登入頁、組織、用戶、角色頁共用 apiErrorKey。</x:t>
         </x:is>
       </x:c>
       <x:c r="H81" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:130</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:116</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="82">
       <x:c r="A82" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.27.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.27.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B82" s="2" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </x:c>
       <x:c r="E82" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to query audit logs of the current company.</x:t>
+          <x:t xml:space="preserve">System should record every data change in sys_audit_log within the same transaction.</x:t>
         </x:is>
       </x:c>
       <x:c r="F82" s="2" t="inlineStr">
@@ -3506,19 +3506,19 @@
       </x:c>
       <x:c r="G82" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GET /api/v1/sys/audit-logs 需 SYS.AUDIT.VIEW，支援分頁、日期範圍（含頭尾）、類別、操作類型、表名＋記錄 Id（單據修改歷史）、用戶篩選，以時間排序。只列出目前公司的記錄，以及屬於目前公司用戶、沒有公司的安全事件；其他公司的記錄看不到。資料變更記錄會補上帳號。to 早於 from、類別未知或長度超限時回 400。</x:t>
+          <x:t xml:space="preserve">透過 EF 新增、修改、刪除（含軟刪除）都寫一筆記錄，內容包括公司、用戶（背景程序為系統用戶）、時間（IClock）、表名、記錄 Id、操作類型（CREATE／UPDATE／DELETE，可由 Application 指定 VOID／APPROVE／POST）、欄位差異 JSON（修改只列有變更的欄位）、來源 IP、TraceId。沒有欄位變更不寫記錄。交易回滾或 SaveChanges 失敗（含樂觀鎖衝突）不留記錄，重試時也不會重複（ADR-019）。</x:t>
         </x:is>
       </x:c>
       <x:c r="H82" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:131</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:128</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="83">
       <x:c r="A83" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.27.5</x:t>
+          <x:t xml:space="preserve">REQ_F4118.27.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B83" s="2" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </x:c>
       <x:c r="E83" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should record role permission and user company access changes as security events.</x:t>
+          <x:t xml:space="preserve">System should protect audit records and sensitive values.</x:t>
         </x:is>
       </x:c>
       <x:c r="F83" s="2" t="inlineStr">
@@ -3548,19 +3548,19 @@
       </x:c>
       <x:c r="G83" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">修改角色的權限、資料範圍、全權或啟用狀態，以及指派用戶公司授權，都寫 PERMISSION_CHANGE，與變更同一交易。記錄內容包括操作者、公司、新增與移除的權限，或指派後的角色、組織、預設公司與啟用狀態。</x:t>
+          <x:t xml:space="preserve">[SensitiveData] 欄位（例如 password_hash）的值以 * 遮蔽；主鍵、審計欄位、version、company_id 不記錄差異。sys_audit_log 只能新增，UPDATE 或 DELETE 由 trigger 拒絕（append-only）；changes 必須是 JSON。</x:t>
         </x:is>
       </x:c>
       <x:c r="H83" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:132</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:129</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="84">
       <x:c r="A84" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.27.6</x:t>
+          <x:t xml:space="preserve">REQ_F4118.27.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B84" s="2" t="inlineStr">
@@ -3580,7 +3580,7 @@
       </x:c>
       <x:c r="E84" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should provide a trilingual audit log page with per-record change history.</x:t>
+          <x:t xml:space="preserve">System should record login, failed login, logout and captcha master-code login as security events.</x:t>
         </x:is>
       </x:c>
       <x:c r="F84" s="2" t="inlineStr">
@@ -3590,19 +3590,19 @@
       </x:c>
       <x:c r="G84" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">三語稽核查詢頁 /sys/audit-logs（介面 8.66），需 SYS.AUDIT.VIEW，無權限時選單不顯示、直接進入顯示 403。可依日期範圍（含快選今天、近 7、30 天；結束日早於開始日時不送出）、類別、操作、資料表＋記錄 ID 篩選，伺服器端分頁並依時間排序。可展開欄位差異（修改前→修改後，* 照原樣顯示）或安全事件明細。?tableName=&amp;recordId= 開啟單筆記錄的修改歷史，供單據頁的稽核頁籤連結。操作與類別有三語標籤，未知操作顯示原代碼。切換公司後重新查詢。</x:t>
+          <x:t xml:space="preserve">安全事件記錄帳號、IP、時間與 TraceId。LOGIN_FAILED 的原因只寫 INVALID_CREDENTIALS 或 PASSWORD_EXPIRED，不寫密碼。萬用碼登入不論結果都寫 MASTER_CODE_LOGIN（REQ_F4118.24.4）。</x:t>
         </x:is>
       </x:c>
       <x:c r="H84" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:133</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:130</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="85">
       <x:c r="A85" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.28.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.27.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B85" s="2" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </x:c>
       <x:c r="C85" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Document Number Rule</x:t>
+          <x:t xml:space="preserve">Audit Log</x:t>
         </x:is>
       </x:c>
       <x:c r="D85" s="2" t="inlineStr">
@@ -3622,7 +3622,7 @@
       </x:c>
       <x:c r="E85" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow user to view document number rules of the current company.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to query audit logs of the current company.</x:t>
         </x:is>
       </x:c>
       <x:c r="F85" s="2" t="inlineStr">
@@ -3632,19 +3632,19 @@
       </x:c>
       <x:c r="G85" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">GET /api/v1/sys/audit-logs 需 SYS.AUDIT.VIEW，支援分頁、日期範圍（含頭尾）、類別、操作類型、表名＋記錄 Id（單據修改歷史）、用戶篩選，以時間排序。只列出目前公司的記錄，以及屬於目前公司用戶、沒有公司的安全事件；其他公司的記錄看不到。資料變更記錄會補上帳號。to 早於 from、類別未知或長度超限時回 400。</x:t>
         </x:is>
       </x:c>
       <x:c r="H85" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:167</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:131</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="86">
       <x:c r="A86" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.28.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.27.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B86" s="2" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </x:c>
       <x:c r="C86" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Document Number Rule</x:t>
+          <x:t xml:space="preserve">Audit Log</x:t>
         </x:is>
       </x:c>
       <x:c r="D86" s="2" t="inlineStr">
@@ -3664,7 +3664,7 @@
       </x:c>
       <x:c r="E86" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow user to create a document number rule with prefix, date format, sequence length and reset period.</x:t>
+          <x:t xml:space="preserve">System should record role permission and user company access changes as security events.</x:t>
         </x:is>
       </x:c>
       <x:c r="F86" s="2" t="inlineStr">
@@ -3674,19 +3674,19 @@
       </x:c>
       <x:c r="G86" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">修改角色的權限、資料範圍、全權或啟用狀態，以及指派用戶公司授權，都寫 PERMISSION_CHANGE，與變更同一交易。記錄內容包括操作者、公司、新增與移除的權限，或指派後的角色、組織、預設公司與啟用狀態。</x:t>
         </x:is>
       </x:c>
       <x:c r="H86" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:168</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:132</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="87">
       <x:c r="A87" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.28.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.27.6</x:t>
         </x:is>
       </x:c>
       <x:c r="B87" s="2" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </x:c>
       <x:c r="C87" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Document Number Rule</x:t>
+          <x:t xml:space="preserve">Audit Log</x:t>
         </x:is>
       </x:c>
       <x:c r="D87" s="2" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </x:c>
       <x:c r="E87" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow user to edit or deactivate a document number rule without breaking issued numbers.</x:t>
+          <x:t xml:space="preserve">System should provide a trilingual audit log page with per-record change history.</x:t>
         </x:is>
       </x:c>
       <x:c r="F87" s="2" t="inlineStr">
@@ -3716,19 +3716,19 @@
       </x:c>
       <x:c r="G87" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">三語稽核查詢頁 /sys/audit-logs（介面 8.66），需 SYS.AUDIT.VIEW，無權限時選單不顯示、直接進入顯示 403。可依日期範圍（含快選今天、近 7、30 天；結束日早於開始日時不送出）、類別、操作、資料表＋記錄 ID 篩選，伺服器端分頁並依時間排序。可展開欄位差異（修改前→修改後，* 照原樣顯示）或安全事件明細。?tableName=&amp;recordId= 開啟單筆記錄的修改歷史，供單據頁的稽核頁籤連結。操作與類別有三語標籤，未知操作顯示原代碼。切換公司後重新查詢。</x:t>
         </x:is>
       </x:c>
       <x:c r="H87" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:169</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:133</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="88">
       <x:c r="A88" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.28.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.28.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B88" s="2" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </x:c>
       <x:c r="E88" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow user to preview the next document number for a business date.</x:t>
+          <x:t xml:space="preserve">System should allow user to view document number rules of the current company.</x:t>
         </x:is>
       </x:c>
       <x:c r="F88" s="2" t="inlineStr">
@@ -3763,14 +3763,14 @@
       </x:c>
       <x:c r="H88" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:170</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:167</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="89">
       <x:c r="A89" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.28.5</x:t>
+          <x:t xml:space="preserve">REQ_F4118.28.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B89" s="2" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </x:c>
       <x:c r="E89" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should generate unique, gap-free document numbers for every module under concurrency.</x:t>
+          <x:t xml:space="preserve">System should allow user to create a document number rule with prefix, date format, sequence length and reset period.</x:t>
         </x:is>
       </x:c>
       <x:c r="F89" s="2" t="inlineStr">
@@ -3805,14 +3805,14 @@
       </x:c>
       <x:c r="H89" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:171</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:168</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="90">
       <x:c r="A90" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.28.6</x:t>
+          <x:t xml:space="preserve">REQ_F4118.28.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B90" s="2" t="inlineStr">
@@ -3832,7 +3832,7 @@
       </x:c>
       <x:c r="E90" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should provide a trilingual number rule maintenance page.</x:t>
+          <x:t xml:space="preserve">System should allow user to edit or deactivate a document number rule without breaking issued numbers.</x:t>
         </x:is>
       </x:c>
       <x:c r="F90" s="2" t="inlineStr">
@@ -3847,14 +3847,14 @@
       </x:c>
       <x:c r="H90" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:172</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:169</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="91">
       <x:c r="A91" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.29.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.28.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B91" s="2" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </x:c>
       <x:c r="C91" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Approval Workflow</x:t>
+          <x:t xml:space="preserve">Document Number Rule</x:t>
         </x:is>
       </x:c>
       <x:c r="D91" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </x:c>
       <x:c r="E91" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow user to view and create multi-level approval flows with amount thresholds.</x:t>
+          <x:t xml:space="preserve">System should allow user to preview the next document number for a business date.</x:t>
         </x:is>
       </x:c>
       <x:c r="F91" s="2" t="inlineStr">
@@ -3889,14 +3889,14 @@
       </x:c>
       <x:c r="H91" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:146</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:170</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="92">
       <x:c r="A92" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.29.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.28.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B92" s="2" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </x:c>
       <x:c r="C92" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Approval Workflow</x:t>
+          <x:t xml:space="preserve">Document Number Rule</x:t>
         </x:is>
       </x:c>
       <x:c r="D92" s="2" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </x:c>
       <x:c r="E92" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow user to edit or deactivate an approval flow without affecting pending approvals.</x:t>
+          <x:t xml:space="preserve">System should generate unique, gap-free document numbers for every module under concurrency.</x:t>
         </x:is>
       </x:c>
       <x:c r="F92" s="2" t="inlineStr">
@@ -3931,14 +3931,14 @@
       </x:c>
       <x:c r="H92" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:147</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:171</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="93">
       <x:c r="A93" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.29.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.28.6</x:t>
         </x:is>
       </x:c>
       <x:c r="B93" s="2" t="inlineStr">
@@ -3948,7 +3948,7 @@
       </x:c>
       <x:c r="C93" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Approval Workflow</x:t>
+          <x:t xml:space="preserve">Document Number Rule</x:t>
         </x:is>
       </x:c>
       <x:c r="D93" s="2" t="inlineStr">
@@ -3958,7 +3958,7 @@
       </x:c>
       <x:c r="E93" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow user to assign an approval delegate for a date range.</x:t>
+          <x:t xml:space="preserve">System should provide a trilingual number rule maintenance page.</x:t>
         </x:is>
       </x:c>
       <x:c r="F93" s="2" t="inlineStr">
@@ -3973,14 +3973,14 @@
       </x:c>
       <x:c r="H93" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:148</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:172</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="94">
       <x:c r="A94" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.29.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.29.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B94" s="2" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </x:c>
       <x:c r="E94" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable every module to submit documents for approval through the shared workflow engine.</x:t>
+          <x:t xml:space="preserve">System should allow user to view and create multi-level approval flows with amount thresholds.</x:t>
         </x:is>
       </x:c>
       <x:c r="F94" s="2" t="inlineStr">
@@ -4015,14 +4015,14 @@
       </x:c>
       <x:c r="H94" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:149</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:146</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="95">
       <x:c r="A95" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.29.5</x:t>
+          <x:t xml:space="preserve">REQ_F4118.29.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B95" s="2" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </x:c>
       <x:c r="E95" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow approvers or their delegates to approve or reject the current approval step.</x:t>
+          <x:t xml:space="preserve">System should allow user to edit or deactivate an approval flow without affecting pending approvals.</x:t>
         </x:is>
       </x:c>
       <x:c r="F95" s="2" t="inlineStr">
@@ -4057,14 +4057,14 @@
       </x:c>
       <x:c r="H95" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:150</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:147</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="96">
       <x:c r="A96" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.29.6</x:t>
+          <x:t xml:space="preserve">REQ_F4118.29.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B96" s="2" t="inlineStr">
@@ -4084,7 +4084,7 @@
       </x:c>
       <x:c r="E96" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should list the pending approval tasks of the current user.</x:t>
+          <x:t xml:space="preserve">System should allow user to assign an approval delegate for a date range.</x:t>
         </x:is>
       </x:c>
       <x:c r="F96" s="2" t="inlineStr">
@@ -4099,14 +4099,14 @@
       </x:c>
       <x:c r="H96" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:151</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:148</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="97">
       <x:c r="A97" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.29.7</x:t>
+          <x:t xml:space="preserve">REQ_F4118.29.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B97" s="2" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </x:c>
       <x:c r="E97" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow user to view the approval history of a document.</x:t>
+          <x:t xml:space="preserve">System should enable every module to submit documents for approval through the shared workflow engine.</x:t>
         </x:is>
       </x:c>
       <x:c r="F97" s="2" t="inlineStr">
@@ -4141,14 +4141,14 @@
       </x:c>
       <x:c r="H97" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:152</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:149</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="98">
       <x:c r="A98" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.29.8</x:t>
+          <x:t xml:space="preserve">REQ_F4118.29.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B98" s="2" t="inlineStr">
@@ -4168,7 +4168,7 @@
       </x:c>
       <x:c r="E98" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should provide trilingual approval flow and delegation maintenance pages.</x:t>
+          <x:t xml:space="preserve">System should allow approvers or their delegates to approve or reject the current approval step.</x:t>
         </x:is>
       </x:c>
       <x:c r="F98" s="2" t="inlineStr">
@@ -4183,14 +4183,14 @@
       </x:c>
       <x:c r="H98" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:153</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:150</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="99">
       <x:c r="A99" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.29.9</x:t>
+          <x:t xml:space="preserve">REQ_F4118.29.6</x:t>
         </x:is>
       </x:c>
       <x:c r="B99" s="2" t="inlineStr">
@@ -4210,7 +4210,7 @@
       </x:c>
       <x:c r="E99" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should provide a trilingual approval inbox with approval history.</x:t>
+          <x:t xml:space="preserve">System should list the pending approval tasks of the current user.</x:t>
         </x:is>
       </x:c>
       <x:c r="F99" s="2" t="inlineStr">
@@ -4225,14 +4225,14 @@
       </x:c>
       <x:c r="H99" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:154</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:151</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="100">
       <x:c r="A100" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.30.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.29.7</x:t>
         </x:is>
       </x:c>
       <x:c r="B100" s="2" t="inlineStr">
@@ -4242,7 +4242,7 @@
       </x:c>
       <x:c r="C100" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Development Seed Data</x:t>
+          <x:t xml:space="preserve">Approval Workflow</x:t>
         </x:is>
       </x:c>
       <x:c r="D100" s="2" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </x:c>
       <x:c r="E100" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should load demo companies, branches, departments and roles for the Development environment.</x:t>
+          <x:t xml:space="preserve">System should allow user to view the approval history of a document.</x:t>
         </x:is>
       </x:c>
       <x:c r="F100" s="2" t="inlineStr">
@@ -4267,14 +4267,14 @@
       </x:c>
       <x:c r="H100" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:186</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:152</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="101">
       <x:c r="A101" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.30.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.29.8</x:t>
         </x:is>
       </x:c>
       <x:c r="B101" s="2" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </x:c>
       <x:c r="C101" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Development Seed Data</x:t>
+          <x:t xml:space="preserve">Approval Workflow</x:t>
         </x:is>
       </x:c>
       <x:c r="D101" s="2" t="inlineStr">
@@ -4294,7 +4294,7 @@
       </x:c>
       <x:c r="E101" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should create the test accounts of the SeedUsers setting with hashed passwords and company assignments.</x:t>
+          <x:t xml:space="preserve">System should provide trilingual approval flow and delegation maintenance pages.</x:t>
         </x:is>
       </x:c>
       <x:c r="F101" s="2" t="inlineStr">
@@ -4309,14 +4309,14 @@
       </x:c>
       <x:c r="H101" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:187</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:153</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="102">
       <x:c r="A102" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.30.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.29.9</x:t>
         </x:is>
       </x:c>
       <x:c r="B102" s="2" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </x:c>
       <x:c r="C102" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Development Seed Data</x:t>
+          <x:t xml:space="preserve">Approval Workflow</x:t>
         </x:is>
       </x:c>
       <x:c r="D102" s="2" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </x:c>
       <x:c r="E102" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow the seed to run repeatedly without duplicating or overwriting data.</x:t>
+          <x:t xml:space="preserve">System should provide a trilingual approval inbox with approval history.</x:t>
         </x:is>
       </x:c>
       <x:c r="F102" s="2" t="inlineStr">
@@ -4351,14 +4351,14 @@
       </x:c>
       <x:c r="H102" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:188</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:154</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="103">
       <x:c r="A103" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.31.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.30.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B103" s="2" t="inlineStr">
@@ -4368,7 +4368,7 @@
       </x:c>
       <x:c r="C103" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Shared Dialogs and Page Templates</x:t>
+          <x:t xml:space="preserve">Development Seed Data</x:t>
         </x:is>
       </x:c>
       <x:c r="D103" s="2" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </x:c>
       <x:c r="E103" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should ask for confirmation in a shared trilingual confirmation box before dangerous actions.</x:t>
+          <x:t xml:space="preserve">System should load demo companies, branches, departments and roles for the Development environment.</x:t>
         </x:is>
       </x:c>
       <x:c r="F103" s="2" t="inlineStr">
@@ -4393,14 +4393,14 @@
       </x:c>
       <x:c r="H103" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:200</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:186</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="104">
       <x:c r="A104" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.31.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.30.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B104" s="2" t="inlineStr">
@@ -4410,7 +4410,7 @@
       </x:c>
       <x:c r="C104" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Shared Dialogs and Page Templates</x:t>
+          <x:t xml:space="preserve">Development Seed Data</x:t>
         </x:is>
       </x:c>
       <x:c r="D104" s="2" t="inlineStr">
@@ -4420,7 +4420,7 @@
       </x:c>
       <x:c r="E104" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should show results that need the user's attention in a shared prompt box, and short success messages as toasts.</x:t>
+          <x:t xml:space="preserve">System should create the test accounts of the SeedUsers setting with hashed passwords and company assignments.</x:t>
         </x:is>
       </x:c>
       <x:c r="F104" s="2" t="inlineStr">
@@ -4435,14 +4435,14 @@
       </x:c>
       <x:c r="H104" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:201</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:187</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="105">
       <x:c r="A105" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.31.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.30.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B105" s="2" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </x:c>
       <x:c r="C105" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Shared Dialogs and Page Templates</x:t>
+          <x:t xml:space="preserve">Development Seed Data</x:t>
         </x:is>
       </x:c>
       <x:c r="D105" s="2" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </x:c>
       <x:c r="E105" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should provide a shared selection window for choosing master data with search and server-side paging.</x:t>
+          <x:t xml:space="preserve">System should allow the seed to run repeatedly without duplicating or overwriting data.</x:t>
         </x:is>
       </x:c>
       <x:c r="F105" s="2" t="inlineStr">
@@ -4477,14 +4477,14 @@
       </x:c>
       <x:c r="H105" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:202</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:188</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="106">
       <x:c r="A106" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.31.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.31.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B106" s="2" t="inlineStr">
@@ -4504,7 +4504,7 @@
       </x:c>
       <x:c r="E106" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should provide a standard list page template reused by every module.</x:t>
+          <x:t xml:space="preserve">System should ask for confirmation in a shared trilingual confirmation box before dangerous actions.</x:t>
         </x:is>
       </x:c>
       <x:c r="F106" s="2" t="inlineStr">
@@ -4519,14 +4519,14 @@
       </x:c>
       <x:c r="H106" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:203</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:200</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="107">
       <x:c r="A107" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.31.5</x:t>
+          <x:t xml:space="preserve">REQ_F4118.31.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B107" s="2" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </x:c>
       <x:c r="E107" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should provide a standard document page template with status, previous / next navigation and unsaved-change protection.</x:t>
+          <x:t xml:space="preserve">System should show results that need the user's attention in a shared prompt box, and short success messages as toasts.</x:t>
         </x:is>
       </x:c>
       <x:c r="F107" s="2" t="inlineStr">
@@ -4561,14 +4561,14 @@
       </x:c>
       <x:c r="H107" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:204</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:201</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="108">
       <x:c r="A108" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.31.6</x:t>
+          <x:t xml:space="preserve">REQ_F4118.31.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B108" s="2" t="inlineStr">
@@ -4588,7 +4588,7 @@
       </x:c>
       <x:c r="E108" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should provide a date range filter with quick ranges and a document status tag following the macaron status colours.</x:t>
+          <x:t xml:space="preserve">System should provide a shared selection window for choosing master data with search and server-side paging.</x:t>
         </x:is>
       </x:c>
       <x:c r="F108" s="2" t="inlineStr">
@@ -4603,14 +4603,14 @@
       </x:c>
       <x:c r="H108" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:205</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:202</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="109">
       <x:c r="A109" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.32.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.31.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B109" s="2" t="inlineStr">
@@ -4620,7 +4620,7 @@
       </x:c>
       <x:c r="C109" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">IP Whitelist</x:t>
+          <x:t xml:space="preserve">Shared Dialogs and Page Templates</x:t>
         </x:is>
       </x:c>
       <x:c r="D109" s="2" t="inlineStr">
@@ -4630,7 +4630,7 @@
       </x:c>
       <x:c r="E109" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to view IP whitelist rules.</x:t>
+          <x:t xml:space="preserve">System should provide a standard list page template reused by every module.</x:t>
         </x:is>
       </x:c>
       <x:c r="F109" s="2" t="inlineStr">
@@ -4645,14 +4645,14 @@
       </x:c>
       <x:c r="H109" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:217</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:203</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="110">
       <x:c r="A110" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.32.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.31.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B110" s="2" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </x:c>
       <x:c r="C110" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">IP Whitelist</x:t>
+          <x:t xml:space="preserve">Shared Dialogs and Page Templates</x:t>
         </x:is>
       </x:c>
       <x:c r="D110" s="2" t="inlineStr">
@@ -4672,7 +4672,7 @@
       </x:c>
       <x:c r="E110" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to create and deactivate IP whitelist rules.</x:t>
+          <x:t xml:space="preserve">System should provide a standard document page template with status, previous / next navigation and unsaved-change protection.</x:t>
         </x:is>
       </x:c>
       <x:c r="F110" s="2" t="inlineStr">
@@ -4687,14 +4687,14 @@
       </x:c>
       <x:c r="H110" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:218</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:204</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="111">
       <x:c r="A111" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.32.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.31.6</x:t>
         </x:is>
       </x:c>
       <x:c r="B111" s="2" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </x:c>
       <x:c r="C111" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">IP Whitelist</x:t>
+          <x:t xml:space="preserve">Shared Dialogs and Page Templates</x:t>
         </x:is>
       </x:c>
       <x:c r="D111" s="2" t="inlineStr">
@@ -4714,7 +4714,7 @@
       </x:c>
       <x:c r="E111" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow single IPv4 or IPv6 addresses and CIDR networks in system, role or user scope.</x:t>
+          <x:t xml:space="preserve">System should provide a date range filter with quick ranges and a document status tag following the macaron status colours.</x:t>
         </x:is>
       </x:c>
       <x:c r="F111" s="2" t="inlineStr">
@@ -4729,14 +4729,14 @@
       </x:c>
       <x:c r="H111" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:219</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:205</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="112">
       <x:c r="A112" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.32.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.32.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B112" s="2" t="inlineStr">
@@ -4756,7 +4756,7 @@
       </x:c>
       <x:c r="E112" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should reject disallowed requests and audit each rejection.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to view IP whitelist rules.</x:t>
         </x:is>
       </x:c>
       <x:c r="F112" s="2" t="inlineStr">
@@ -4771,14 +4771,14 @@
       </x:c>
       <x:c r="H112" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:220</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:217</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="113">
       <x:c r="A113" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.32.5</x:t>
+          <x:t xml:space="preserve">REQ_F4118.32.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B113" s="2" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </x:c>
       <x:c r="E113" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow operators to disable IP filtering through server configuration.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to create and deactivate IP whitelist rules.</x:t>
         </x:is>
       </x:c>
       <x:c r="F113" s="2" t="inlineStr">
@@ -4813,14 +4813,14 @@
       </x:c>
       <x:c r="H113" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:221</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:218</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="114">
       <x:c r="A114" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.32.6</x:t>
+          <x:t xml:space="preserve">REQ_F4118.32.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B114" s="2" t="inlineStr">
@@ -4840,7 +4840,7 @@
       </x:c>
       <x:c r="E114" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should provide a trilingual IP whitelist maintenance page.</x:t>
+          <x:t xml:space="preserve">System should allow single IPv4 or IPv6 addresses and CIDR networks in system, role or user scope.</x:t>
         </x:is>
       </x:c>
       <x:c r="F114" s="2" t="inlineStr">
@@ -4855,14 +4855,14 @@
       </x:c>
       <x:c r="H114" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:222</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:219</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="115">
       <x:c r="A115" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.33.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.32.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B115" s="2" t="inlineStr">
@@ -4872,17 +4872,17 @@
       </x:c>
       <x:c r="C115" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">In-app Notification</x:t>
+          <x:t xml:space="preserve">IP Whitelist</x:t>
         </x:is>
       </x:c>
       <x:c r="D115" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1.1</x:t>
+          <x:t xml:space="preserve">1.0</x:t>
         </x:is>
       </x:c>
       <x:c r="E115" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable modules to publish notifications to a user.</x:t>
+          <x:t xml:space="preserve">System should reject disallowed requests and audit each rejection.</x:t>
         </x:is>
       </x:c>
       <x:c r="F115" s="2" t="inlineStr">
@@ -4897,14 +4897,14 @@
       </x:c>
       <x:c r="H115" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:278</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:220</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="116">
       <x:c r="A116" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.33.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.32.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B116" s="2" t="inlineStr">
@@ -4914,17 +4914,17 @@
       </x:c>
       <x:c r="C116" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">In-app Notification</x:t>
+          <x:t xml:space="preserve">IP Whitelist</x:t>
         </x:is>
       </x:c>
       <x:c r="D116" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1.1</x:t>
+          <x:t xml:space="preserve">1.0</x:t>
         </x:is>
       </x:c>
       <x:c r="E116" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to view notifications.</x:t>
+          <x:t xml:space="preserve">System should allow operators to disable IP filtering through server configuration.</x:t>
         </x:is>
       </x:c>
       <x:c r="F116" s="2" t="inlineStr">
@@ -4939,14 +4939,14 @@
       </x:c>
       <x:c r="H116" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:279</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:221</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="117">
       <x:c r="A117" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.33.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.32.6</x:t>
         </x:is>
       </x:c>
       <x:c r="B117" s="2" t="inlineStr">
@@ -4956,17 +4956,17 @@
       </x:c>
       <x:c r="C117" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">In-app Notification</x:t>
+          <x:t xml:space="preserve">IP Whitelist</x:t>
         </x:is>
       </x:c>
       <x:c r="D117" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1.1</x:t>
+          <x:t xml:space="preserve">1.0</x:t>
         </x:is>
       </x:c>
       <x:c r="E117" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to mark notifications as read.</x:t>
+          <x:t xml:space="preserve">System should provide a trilingual IP whitelist maintenance page.</x:t>
         </x:is>
       </x:c>
       <x:c r="F117" s="2" t="inlineStr">
@@ -4981,47 +4981,173 @@
       </x:c>
       <x:c r="H117" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:280</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:222</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="118">
       <x:c r="A118" s="2" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">REQ_F4118.33.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B118" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C118" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">In-app Notification</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D118" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E118" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should enable modules to publish notifications to a user.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F118" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G118" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="H118" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:278</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="119">
+      <x:c r="A119" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.33.2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B119" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C119" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">In-app Notification</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D119" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E119" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should enable user to view notifications.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F119" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G119" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="H119" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:279</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="120">
+      <x:c r="A120" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.33.3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B120" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C120" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">In-app Notification</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D120" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E120" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should enable user to mark notifications as read.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F120" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G120" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="H120" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:280</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="121">
+      <x:c r="A121" s="2" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">REQ_F4118.34.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="B118" s="2" t="inlineStr">
+      <x:c r="B121" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Settings</x:t>
         </x:is>
       </x:c>
-      <x:c r="C118" s="2" t="inlineStr">
+      <x:c r="C121" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Master Data Portal</x:t>
         </x:is>
       </x:c>
-      <x:c r="D118" s="2" t="inlineStr">
+      <x:c r="D121" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="E118" s="2" t="inlineStr">
+      <x:c r="E121" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">System should allow authorized users to view the master data portal.</x:t>
         </x:is>
       </x:c>
-      <x:c r="F118" s="2" t="inlineStr">
+      <x:c r="F121" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Developer</x:t>
         </x:is>
       </x:c>
-      <x:c r="G118" s="2" t="inlineStr">
+      <x:c r="G121" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">/md 僅向已登入且在目前公司有 MD.MASTER.VIEW 的用戶開放；無權限導向 403；三語標題與說明一致。</x:t>
         </x:is>
       </x:c>
-      <x:c r="H118" s="2" t="inlineStr">
+      <x:c r="H121" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:11</x:t>
         </x:is>
@@ -6899,6 +7025,38 @@
       <x:c r="F29" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">REQ_F4118.10.1, REQ_F4118.10.2, REQ_F4118.10.3, REQ_F4118.10.4</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.113</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B30" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C30" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">md_item</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D30" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">This table stores company item masters without inventory balances.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E30" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F30" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.12.1, REQ_F4118.12.2, REQ_F4118.12.3</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -17707,123 +17865,123 @@
     <x:row r="27">
       <x:c r="A27" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.13.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.12.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B27" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to view unit of measurement.</x:t>
+          <x:t xml:space="preserve">System should enable user to view items.</x:t>
         </x:is>
       </x:c>
       <x:c r="C27" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.109, REQ_DS43.110</x:t>
+          <x:t xml:space="preserve">REQ_DS43.113</x:t>
         </x:is>
       </x:c>
       <x:c r="D27" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.45</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="E27" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.45.1, REQ_IO_A8.45.2, REQ_IO_A8.45.3, REQ_IO_A8.45.4</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="F27" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MD-UOM-001, MD-UOM-002, MD-UOM-003, MD-UOM-004, MD-UOM-005</x:t>
+          <x:t xml:space="preserve">MD-ITEM-001</x:t>
         </x:is>
       </x:c>
       <x:c r="G27" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Covered</x:t>
+          <x:t xml:space="preserve">Partial</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.13.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.12.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B28" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to create unit of measurement.</x:t>
+          <x:t xml:space="preserve">System should enable user to create items.</x:t>
         </x:is>
       </x:c>
       <x:c r="C28" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.109, REQ_DS43.110</x:t>
+          <x:t xml:space="preserve">REQ_DS43.113</x:t>
         </x:is>
       </x:c>
       <x:c r="D28" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.46</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="E28" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.46.1, REQ_IO_A8.46.2, REQ_IO_A8.46.3, REQ_IO_A8.46.4, REQ_IO_A8.46.5</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="F28" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MD-UOM-001, MD-UOM-002, MD-UOM-003, MD-UOM-004, MD-UOM-005</x:t>
+          <x:t xml:space="preserve">MD-ITEM-001, MD-ITEM-002</x:t>
         </x:is>
       </x:c>
       <x:c r="G28" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Covered</x:t>
+          <x:t xml:space="preserve">Partial</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.13.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.12.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B29" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to edit unit of measurement.</x:t>
+          <x:t xml:space="preserve">System should enable user to edit items.</x:t>
         </x:is>
       </x:c>
       <x:c r="C29" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.109, REQ_DS43.110</x:t>
+          <x:t xml:space="preserve">REQ_DS43.113</x:t>
         </x:is>
       </x:c>
       <x:c r="D29" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.47</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="E29" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.47.1, REQ_IO_A8.47.2, REQ_IO_A8.47.3</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="F29" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MD-UOM-001, MD-UOM-003, MD-UOM-004, MD-UOM-005</x:t>
+          <x:t xml:space="preserve">MD-ITEM-001, MD-ITEM-002</x:t>
         </x:is>
       </x:c>
       <x:c r="G29" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Covered</x:t>
+          <x:t xml:space="preserve">Partial</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.13.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.13.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B30" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to delete unit of measurement.</x:t>
+          <x:t xml:space="preserve">System should enable user to view unit of measurement.</x:t>
         </x:is>
       </x:c>
       <x:c r="C30" s="2" t="inlineStr">
@@ -17833,17 +17991,17 @@
       </x:c>
       <x:c r="D30" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.47</x:t>
+          <x:t xml:space="preserve">4.4.1.8.45</x:t>
         </x:is>
       </x:c>
       <x:c r="E30" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.47.4</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.45.1, REQ_IO_A8.45.2, REQ_IO_A8.45.3, REQ_IO_A8.45.4</x:t>
         </x:is>
       </x:c>
       <x:c r="F30" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MD-UOM-001, MD-UOM-003, MD-UOM-004, MD-UOM-005</x:t>
+          <x:t xml:space="preserve">MD-UOM-001, MD-UOM-002, MD-UOM-003, MD-UOM-004, MD-UOM-005</x:t>
         </x:is>
       </x:c>
       <x:c r="G30" s="2" t="inlineStr">
@@ -17855,32 +18013,32 @@
     <x:row r="31">
       <x:c r="A31" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.17.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.13.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B31" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to view parameter settings.</x:t>
+          <x:t xml:space="preserve">System should enable user to create unit of measurement.</x:t>
         </x:is>
       </x:c>
       <x:c r="C31" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.73</x:t>
+          <x:t xml:space="preserve">REQ_DS43.109, REQ_DS43.110</x:t>
         </x:is>
       </x:c>
       <x:c r="D31" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.55</x:t>
+          <x:t xml:space="preserve">4.4.1.8.46</x:t>
         </x:is>
       </x:c>
       <x:c r="E31" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.46.1, REQ_IO_A8.46.2, REQ_IO_A8.46.3, REQ_IO_A8.46.4, REQ_IO_A8.46.5</x:t>
         </x:is>
       </x:c>
       <x:c r="F31" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-PARAM-002</x:t>
+          <x:t xml:space="preserve">MD-UOM-001, MD-UOM-002, MD-UOM-003, MD-UOM-004, MD-UOM-005</x:t>
         </x:is>
       </x:c>
       <x:c r="G31" s="2" t="inlineStr">
@@ -17892,32 +18050,32 @@
     <x:row r="32">
       <x:c r="A32" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.17.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.13.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B32" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to edit parameter settings.</x:t>
+          <x:t xml:space="preserve">System should enable user to edit unit of measurement.</x:t>
         </x:is>
       </x:c>
       <x:c r="C32" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.73</x:t>
+          <x:t xml:space="preserve">REQ_DS43.109, REQ_DS43.110</x:t>
         </x:is>
       </x:c>
       <x:c r="D32" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.55</x:t>
+          <x:t xml:space="preserve">4.4.1.8.47</x:t>
         </x:is>
       </x:c>
       <x:c r="E32" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.55.1, REQ_IO_A8.55.2, REQ_IO_A8.55.3, REQ_IO_A8.55.4, REQ_IO_A8.55.5, REQ_IO_A8.55.7</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.47.1, REQ_IO_A8.47.2, REQ_IO_A8.47.3</x:t>
         </x:is>
       </x:c>
       <x:c r="F32" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-PARAM-002, SYS-PARAM-003</x:t>
+          <x:t xml:space="preserve">MD-UOM-001, MD-UOM-003, MD-UOM-004, MD-UOM-005</x:t>
         </x:is>
       </x:c>
       <x:c r="G32" s="2" t="inlineStr">
@@ -17929,49 +18087,49 @@
     <x:row r="33">
       <x:c r="A33" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.17.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.13.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B33" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should let every module declare typed company parameters with defaults and read them in process.</x:t>
+          <x:t xml:space="preserve">System should enable user to delete unit of measurement.</x:t>
         </x:is>
       </x:c>
       <x:c r="C33" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.73</x:t>
+          <x:t xml:space="preserve">REQ_DS43.109, REQ_DS43.110</x:t>
         </x:is>
       </x:c>
       <x:c r="D33" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">4.4.1.8.47</x:t>
         </x:is>
       </x:c>
       <x:c r="E33" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.47.4</x:t>
         </x:is>
       </x:c>
       <x:c r="F33" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-PARAM-001, SYS-PARAM-004</x:t>
+          <x:t xml:space="preserve">MD-UOM-001, MD-UOM-003, MD-UOM-004, MD-UOM-005</x:t>
         </x:is>
       </x:c>
       <x:c r="G33" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.17.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.17.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B34" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should provide a parameter edit interface grouped by module.</x:t>
+          <x:t xml:space="preserve">System should enable user to view parameter settings.</x:t>
         </x:is>
       </x:c>
       <x:c r="C34" s="2" t="inlineStr">
@@ -17986,12 +18144,12 @@
       </x:c>
       <x:c r="E34" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.55.1, REQ_IO_A8.55.2, REQ_IO_A8.55.3, REQ_IO_A8.55.4, REQ_IO_A8.55.5, REQ_IO_A8.55.6, REQ_IO_A8.55.7</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="F34" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-PARAM-005, SYS-PARAM-006, SYS-PARAM-007</x:t>
+          <x:t xml:space="preserve">SYS-PARAM-002</x:t>
         </x:is>
       </x:c>
       <x:c r="G34" s="2" t="inlineStr">
@@ -18003,12 +18161,12 @@
     <x:row r="35">
       <x:c r="A35" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.18.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.17.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B35" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to view print settings.</x:t>
+          <x:t xml:space="preserve">System should enable user to edit parameter settings.</x:t>
         </x:is>
       </x:c>
       <x:c r="C35" s="2" t="inlineStr">
@@ -18018,17 +18176,17 @@
       </x:c>
       <x:c r="D35" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.56</x:t>
+          <x:t xml:space="preserve">4.4.1.8.55</x:t>
         </x:is>
       </x:c>
       <x:c r="E35" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.56.1, REQ_IO_A8.56.2, REQ_IO_A8.56.3, REQ_IO_A8.56.4, REQ_IO_A8.56.5, REQ_IO_A8.56.6, REQ_IO_A8.56.7, REQ_IO_A8.56.8, REQ_IO_A8.56.9, REQ_IO_A8.56.10</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.55.1, REQ_IO_A8.55.2, REQ_IO_A8.55.3, REQ_IO_A8.55.4, REQ_IO_A8.55.5, REQ_IO_A8.55.7</x:t>
         </x:is>
       </x:c>
       <x:c r="F35" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-PRINT-004, SYS-PRINT-005</x:t>
+          <x:t xml:space="preserve">SYS-PARAM-002, SYS-PARAM-003</x:t>
         </x:is>
       </x:c>
       <x:c r="G35" s="2" t="inlineStr">
@@ -18040,12 +18198,12 @@
     <x:row r="36">
       <x:c r="A36" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.18.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.17.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B36" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to edit print settings.</x:t>
+          <x:t xml:space="preserve">System should let every module declare typed company parameters with defaults and read them in process.</x:t>
         </x:is>
       </x:c>
       <x:c r="C36" s="2" t="inlineStr">
@@ -18055,34 +18213,34 @@
       </x:c>
       <x:c r="D36" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.56</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="E36" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.56.1, REQ_IO_A8.56.2, REQ_IO_A8.56.3, REQ_IO_A8.56.4, REQ_IO_A8.56.5, REQ_IO_A8.56.6, REQ_IO_A8.56.7, REQ_IO_A8.56.8, REQ_IO_A8.56.9, REQ_IO_A8.56.11</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="F36" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-PRINT-001, SYS-PRINT-002, SYS-PRINT-004, SYS-PRINT-005</x:t>
+          <x:t xml:space="preserve">SYS-PARAM-001, SYS-PARAM-004</x:t>
         </x:is>
       </x:c>
       <x:c r="G36" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Covered</x:t>
+          <x:t xml:space="preserve">Partial</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.18.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.17.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B37" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should let printing modules read the company's print settings.</x:t>
+          <x:t xml:space="preserve">System should provide a parameter edit interface grouped by module.</x:t>
         </x:is>
       </x:c>
       <x:c r="C37" s="2" t="inlineStr">
@@ -18092,54 +18250,54 @@
       </x:c>
       <x:c r="D37" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">4.4.1.8.55</x:t>
         </x:is>
       </x:c>
       <x:c r="E37" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.55.1, REQ_IO_A8.55.2, REQ_IO_A8.55.3, REQ_IO_A8.55.4, REQ_IO_A8.55.5, REQ_IO_A8.55.6, REQ_IO_A8.55.7</x:t>
         </x:is>
       </x:c>
       <x:c r="F37" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-PRINT-003</x:t>
+          <x:t xml:space="preserve">SYS-PARAM-005, SYS-PARAM-006, SYS-PARAM-007</x:t>
         </x:is>
       </x:c>
       <x:c r="G37" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.19.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.18.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B38" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to view the logo and stamp.</x:t>
+          <x:t xml:space="preserve">System should enable user to view print settings.</x:t>
         </x:is>
       </x:c>
       <x:c r="C38" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.103</x:t>
+          <x:t xml:space="preserve">REQ_DS43.73</x:t>
         </x:is>
       </x:c>
       <x:c r="D38" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.57</x:t>
+          <x:t xml:space="preserve">4.4.1.8.56</x:t>
         </x:is>
       </x:c>
       <x:c r="E38" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.57.1, REQ_IO_A8.57.2, REQ_IO_A8.57.3</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.56.1, REQ_IO_A8.56.2, REQ_IO_A8.56.3, REQ_IO_A8.56.4, REQ_IO_A8.56.5, REQ_IO_A8.56.6, REQ_IO_A8.56.7, REQ_IO_A8.56.8, REQ_IO_A8.56.9, REQ_IO_A8.56.10</x:t>
         </x:is>
       </x:c>
       <x:c r="F38" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-IMG-003, SYS-IMG-005, SYS-IMG-007, SYS-IMG-008</x:t>
+          <x:t xml:space="preserve">SYS-PRINT-004, SYS-PRINT-005</x:t>
         </x:is>
       </x:c>
       <x:c r="G38" s="2" t="inlineStr">
@@ -18151,32 +18309,32 @@
     <x:row r="39">
       <x:c r="A39" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.19.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.18.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B39" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to edit the logo and stamp.</x:t>
+          <x:t xml:space="preserve">System should enable user to edit print settings.</x:t>
         </x:is>
       </x:c>
       <x:c r="C39" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.103</x:t>
+          <x:t xml:space="preserve">REQ_DS43.73</x:t>
         </x:is>
       </x:c>
       <x:c r="D39" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.57</x:t>
+          <x:t xml:space="preserve">4.4.1.8.56</x:t>
         </x:is>
       </x:c>
       <x:c r="E39" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.57.4, REQ_IO_A8.57.5</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.56.1, REQ_IO_A8.56.2, REQ_IO_A8.56.3, REQ_IO_A8.56.4, REQ_IO_A8.56.5, REQ_IO_A8.56.6, REQ_IO_A8.56.7, REQ_IO_A8.56.8, REQ_IO_A8.56.9, REQ_IO_A8.56.11</x:t>
         </x:is>
       </x:c>
       <x:c r="F39" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-IMG-001, SYS-IMG-002, SYS-IMG-003, SYS-IMG-004, SYS-IMG-005, SYS-IMG-007, SYS-IMG-008</x:t>
+          <x:t xml:space="preserve">SYS-PRINT-001, SYS-PRINT-002, SYS-PRINT-004, SYS-PRINT-005</x:t>
         </x:is>
       </x:c>
       <x:c r="G39" s="2" t="inlineStr">
@@ -18188,17 +18346,17 @@
     <x:row r="40">
       <x:c r="A40" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.19.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.18.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B40" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should let printing modules read the company's logo and stamp.</x:t>
+          <x:t xml:space="preserve">System should let printing modules read the company's print settings.</x:t>
         </x:is>
       </x:c>
       <x:c r="C40" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.103</x:t>
+          <x:t xml:space="preserve">REQ_DS43.73</x:t>
         </x:is>
       </x:c>
       <x:c r="D40" s="2" t="inlineStr">
@@ -18213,7 +18371,7 @@
       </x:c>
       <x:c r="F40" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-IMG-006</x:t>
+          <x:t xml:space="preserve">SYS-PRINT-003</x:t>
         </x:is>
       </x:c>
       <x:c r="G40" s="2" t="inlineStr">
@@ -18225,32 +18383,32 @@
     <x:row r="41">
       <x:c r="A41" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.20.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.19.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B41" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to view company details.</x:t>
+          <x:t xml:space="preserve">System should enable user to view the logo and stamp.</x:t>
         </x:is>
       </x:c>
       <x:c r="C41" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.20</x:t>
+          <x:t xml:space="preserve">REQ_DS43.103</x:t>
         </x:is>
       </x:c>
       <x:c r="D41" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.58</x:t>
+          <x:t xml:space="preserve">4.4.1.8.57</x:t>
         </x:is>
       </x:c>
       <x:c r="E41" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.57.1, REQ_IO_A8.57.2, REQ_IO_A8.57.3</x:t>
         </x:is>
       </x:c>
       <x:c r="F41" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-ORG-004, SYS-ORG-011, SYS-ORG-012, SYS-ORG-020, SYS-ORG-026</x:t>
+          <x:t xml:space="preserve">SYS-IMG-003, SYS-IMG-005, SYS-IMG-007, SYS-IMG-008</x:t>
         </x:is>
       </x:c>
       <x:c r="G41" s="2" t="inlineStr">
@@ -18262,32 +18420,32 @@
     <x:row r="42">
       <x:c r="A42" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.20.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.19.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B42" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to create a company.</x:t>
+          <x:t xml:space="preserve">System should enable user to edit the logo and stamp.</x:t>
         </x:is>
       </x:c>
       <x:c r="C42" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.20</x:t>
+          <x:t xml:space="preserve">REQ_DS43.103</x:t>
         </x:is>
       </x:c>
       <x:c r="D42" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.58</x:t>
+          <x:t xml:space="preserve">4.4.1.8.57</x:t>
         </x:is>
       </x:c>
       <x:c r="E42" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.58.1, REQ_IO_A8.58.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.57.4, REQ_IO_A8.57.5</x:t>
         </x:is>
       </x:c>
       <x:c r="F42" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-ORG-001, SYS-ORG-008, SYS-ORG-013, SYS-ORG-021</x:t>
+          <x:t xml:space="preserve">SYS-IMG-001, SYS-IMG-002, SYS-IMG-003, SYS-IMG-004, SYS-IMG-005, SYS-IMG-007, SYS-IMG-008</x:t>
         </x:is>
       </x:c>
       <x:c r="G42" s="2" t="inlineStr">
@@ -18299,22 +18457,22 @@
     <x:row r="43">
       <x:c r="A43" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.20.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.19.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B43" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to edit a company.</x:t>
+          <x:t xml:space="preserve">System should let printing modules read the company's logo and stamp.</x:t>
         </x:is>
       </x:c>
       <x:c r="C43" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.20</x:t>
+          <x:t xml:space="preserve">REQ_DS43.103</x:t>
         </x:is>
       </x:c>
       <x:c r="D43" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.58</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="E43" s="2" t="inlineStr">
@@ -18324,24 +18482,24 @@
       </x:c>
       <x:c r="F43" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-ORG-005, SYS-ORG-009, SYS-ORG-013, SYS-ORG-021, SYS-PERM-030</x:t>
+          <x:t xml:space="preserve">SYS-IMG-006</x:t>
         </x:is>
       </x:c>
       <x:c r="G43" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Covered</x:t>
+          <x:t xml:space="preserve">Partial</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.20.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.20.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B44" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to deactivate a company.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to view company details.</x:t>
         </x:is>
       </x:c>
       <x:c r="C44" s="2" t="inlineStr">
@@ -18361,7 +18519,7 @@
       </x:c>
       <x:c r="F44" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-ORG-006, SYS-ORG-021</x:t>
+          <x:t xml:space="preserve">SYS-ORG-004, SYS-ORG-011, SYS-ORG-012, SYS-ORG-020, SYS-ORG-026</x:t>
         </x:is>
       </x:c>
       <x:c r="G44" s="2" t="inlineStr">
@@ -18373,32 +18531,32 @@
     <x:row r="45">
       <x:c r="A45" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.21.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.20.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B45" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to view branches in the selected company.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to create a company.</x:t>
         </x:is>
       </x:c>
       <x:c r="C45" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.89</x:t>
+          <x:t xml:space="preserve">REQ_DS43.20</x:t>
         </x:is>
       </x:c>
       <x:c r="D45" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.59</x:t>
+          <x:t xml:space="preserve">4.4.1.8.58</x:t>
         </x:is>
       </x:c>
       <x:c r="E45" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.58.1, REQ_IO_A8.58.2</x:t>
         </x:is>
       </x:c>
       <x:c r="F45" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-ORG-002, SYS-ORG-004, SYS-ORG-010, SYS-ORG-012, SYS-ORG-020, SYS-ORG-022, SYS-ORG-024, SYS-ORG-025, SYS-ORG-027</x:t>
+          <x:t xml:space="preserve">SYS-ORG-001, SYS-ORG-008, SYS-ORG-013, SYS-ORG-021</x:t>
         </x:is>
       </x:c>
       <x:c r="G45" s="2" t="inlineStr">
@@ -18410,32 +18568,32 @@
     <x:row r="46">
       <x:c r="A46" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.21.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.20.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B46" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to create a branch.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to edit a company.</x:t>
         </x:is>
       </x:c>
       <x:c r="C46" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.89</x:t>
+          <x:t xml:space="preserve">REQ_DS43.20</x:t>
         </x:is>
       </x:c>
       <x:c r="D46" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.59</x:t>
+          <x:t xml:space="preserve">4.4.1.8.58</x:t>
         </x:is>
       </x:c>
       <x:c r="E46" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.59.1</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="F46" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-ORG-001, SYS-ORG-013, SYS-ORG-020, SYS-ORG-022, SYS-ORG-024</x:t>
+          <x:t xml:space="preserve">SYS-ORG-005, SYS-ORG-009, SYS-ORG-013, SYS-ORG-021, SYS-PERM-030</x:t>
         </x:is>
       </x:c>
       <x:c r="G46" s="2" t="inlineStr">
@@ -18447,22 +18605,22 @@
     <x:row r="47">
       <x:c r="A47" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.21.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.20.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B47" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to edit or deactivate a branch.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to deactivate a company.</x:t>
         </x:is>
       </x:c>
       <x:c r="C47" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.89</x:t>
+          <x:t xml:space="preserve">REQ_DS43.20</x:t>
         </x:is>
       </x:c>
       <x:c r="D47" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.59</x:t>
+          <x:t xml:space="preserve">4.4.1.8.58</x:t>
         </x:is>
       </x:c>
       <x:c r="E47" s="2" t="inlineStr">
@@ -18472,7 +18630,7 @@
       </x:c>
       <x:c r="F47" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-ORG-005, SYS-ORG-022</x:t>
+          <x:t xml:space="preserve">SYS-ORG-006, SYS-ORG-021</x:t>
         </x:is>
       </x:c>
       <x:c r="G47" s="2" t="inlineStr">
@@ -18484,22 +18642,22 @@
     <x:row r="48">
       <x:c r="A48" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.22.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.21.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B48" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to view departments in the selected company.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to view branches in the selected company.</x:t>
         </x:is>
       </x:c>
       <x:c r="C48" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.22</x:t>
+          <x:t xml:space="preserve">REQ_DS43.89</x:t>
         </x:is>
       </x:c>
       <x:c r="D48" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.60</x:t>
+          <x:t xml:space="preserve">4.4.1.8.59</x:t>
         </x:is>
       </x:c>
       <x:c r="E48" s="2" t="inlineStr">
@@ -18509,7 +18667,7 @@
       </x:c>
       <x:c r="F48" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-ORG-002, SYS-ORG-004, SYS-ORG-010, SYS-ORG-012, SYS-ORG-020, SYS-ORG-023, SYS-ORG-026, SYS-ORG-027</x:t>
+          <x:t xml:space="preserve">SYS-ORG-002, SYS-ORG-004, SYS-ORG-010, SYS-ORG-012, SYS-ORG-020, SYS-ORG-022, SYS-ORG-024, SYS-ORG-025, SYS-ORG-027</x:t>
         </x:is>
       </x:c>
       <x:c r="G48" s="2" t="inlineStr">
@@ -18521,32 +18679,32 @@
     <x:row r="49">
       <x:c r="A49" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.22.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.21.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B49" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to create a department under a branch or parent department.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to create a branch.</x:t>
         </x:is>
       </x:c>
       <x:c r="C49" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.22</x:t>
+          <x:t xml:space="preserve">REQ_DS43.89</x:t>
         </x:is>
       </x:c>
       <x:c r="D49" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.60</x:t>
+          <x:t xml:space="preserve">4.4.1.8.59</x:t>
         </x:is>
       </x:c>
       <x:c r="E49" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.60.1, REQ_IO_A8.60.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.59.1</x:t>
         </x:is>
       </x:c>
       <x:c r="F49" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-ORG-001, SYS-ORG-003, SYS-ORG-013, SYS-ORG-023</x:t>
+          <x:t xml:space="preserve">SYS-ORG-001, SYS-ORG-013, SYS-ORG-020, SYS-ORG-022, SYS-ORG-024</x:t>
         </x:is>
       </x:c>
       <x:c r="G49" s="2" t="inlineStr">
@@ -18558,22 +18716,22 @@
     <x:row r="50">
       <x:c r="A50" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.22.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.21.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B50" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to edit or deactivate a department.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to edit or deactivate a branch.</x:t>
         </x:is>
       </x:c>
       <x:c r="C50" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.22</x:t>
+          <x:t xml:space="preserve">REQ_DS43.89</x:t>
         </x:is>
       </x:c>
       <x:c r="D50" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.60</x:t>
+          <x:t xml:space="preserve">4.4.1.8.59</x:t>
         </x:is>
       </x:c>
       <x:c r="E50" s="2" t="inlineStr">
@@ -18583,7 +18741,7 @@
       </x:c>
       <x:c r="F50" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-ORG-005, SYS-ORG-007, SYS-ORG-009, SYS-ORG-023, SYS-ORG-026</x:t>
+          <x:t xml:space="preserve">SYS-ORG-005, SYS-ORG-022</x:t>
         </x:is>
       </x:c>
       <x:c r="G50" s="2" t="inlineStr">
@@ -18595,32 +18753,32 @@
     <x:row r="51">
       <x:c r="A51" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.23.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.22.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B51" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to create a unique user identity.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to view departments in the selected company.</x:t>
         </x:is>
       </x:c>
       <x:c r="C51" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.82</x:t>
+          <x:t xml:space="preserve">REQ_DS43.22</x:t>
         </x:is>
       </x:c>
       <x:c r="D51" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.61</x:t>
+          <x:t xml:space="preserve">4.4.1.8.60</x:t>
         </x:is>
       </x:c>
       <x:c r="E51" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.61.1</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="F51" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-ORG-027, SYS-USER-001, SYS-USER-004, SYS-USER-012</x:t>
+          <x:t xml:space="preserve">SYS-ORG-002, SYS-ORG-004, SYS-ORG-010, SYS-ORG-012, SYS-ORG-020, SYS-ORG-023, SYS-ORG-026, SYS-ORG-027</x:t>
         </x:is>
       </x:c>
       <x:c r="G51" s="2" t="inlineStr">
@@ -18632,32 +18790,32 @@
     <x:row r="52">
       <x:c r="A52" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.23.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.22.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B52" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enforce a configurable password policy.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to create a department under a branch or parent department.</x:t>
         </x:is>
       </x:c>
       <x:c r="C52" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.82</x:t>
+          <x:t xml:space="preserve">REQ_DS43.22</x:t>
         </x:is>
       </x:c>
       <x:c r="D52" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.61</x:t>
+          <x:t xml:space="preserve">4.4.1.8.60</x:t>
         </x:is>
       </x:c>
       <x:c r="E52" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.61.2, REQ_IO_A8.61.3</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.60.1, REQ_IO_A8.60.2</x:t>
         </x:is>
       </x:c>
       <x:c r="F52" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-USER-001, SYS-USER-007, SYS-USER-012</x:t>
+          <x:t xml:space="preserve">SYS-ORG-001, SYS-ORG-003, SYS-ORG-013, SYS-ORG-023</x:t>
         </x:is>
       </x:c>
       <x:c r="G52" s="2" t="inlineStr">
@@ -18669,49 +18827,49 @@
     <x:row r="53">
       <x:c r="A53" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.23.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.22.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B53" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should lock an account after five consecutive failed password attempts.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to edit or deactivate a department.</x:t>
         </x:is>
       </x:c>
       <x:c r="C53" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.82</x:t>
+          <x:t xml:space="preserve">REQ_DS43.22</x:t>
         </x:is>
       </x:c>
       <x:c r="D53" s="2" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">4.4.1.8.60</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E53" s="2" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
-      <x:c r="E53" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
       <x:c r="F53" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-USER-002, SYS-USER-003, SYS-USER-005, SYS-USER-014</x:t>
+          <x:t xml:space="preserve">SYS-ORG-005, SYS-ORG-007, SYS-ORG-009, SYS-ORG-023, SYS-ORG-026</x:t>
         </x:is>
       </x:c>
       <x:c r="G53" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.23.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.23.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B54" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should determine whether a user's password has expired.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to create a unique user identity.</x:t>
         </x:is>
       </x:c>
       <x:c r="C54" s="2" t="inlineStr">
@@ -18721,54 +18879,54 @@
       </x:c>
       <x:c r="D54" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">4.4.1.8.61</x:t>
         </x:is>
       </x:c>
       <x:c r="E54" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.61.1</x:t>
         </x:is>
       </x:c>
       <x:c r="F54" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-USER-003</x:t>
+          <x:t xml:space="preserve">SYS-ORG-027, SYS-USER-001, SYS-USER-004, SYS-USER-012</x:t>
         </x:is>
       </x:c>
       <x:c r="G54" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="55">
       <x:c r="A55" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.23.5</x:t>
+          <x:t xml:space="preserve">REQ_F4118.23.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B55" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should list the users of the current company with paging, keyword and sorting.</x:t>
+          <x:t xml:space="preserve">System should enforce a configurable password policy.</x:t>
         </x:is>
       </x:c>
       <x:c r="C55" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.82, REQ_DS43.92</x:t>
+          <x:t xml:space="preserve">REQ_DS43.82</x:t>
         </x:is>
       </x:c>
       <x:c r="D55" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.63</x:t>
+          <x:t xml:space="preserve">4.4.1.8.61</x:t>
         </x:is>
       </x:c>
       <x:c r="E55" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.63.1, REQ_IO_A8.63.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.61.2, REQ_IO_A8.61.3</x:t>
         </x:is>
       </x:c>
       <x:c r="F55" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-USER-006, SYS-USER-010, SYS-USER-011, SYS-USER-015</x:t>
+          <x:t xml:space="preserve">SYS-USER-001, SYS-USER-007, SYS-USER-012</x:t>
         </x:is>
       </x:c>
       <x:c r="G55" s="2" t="inlineStr">
@@ -18780,22 +18938,22 @@
     <x:row r="56">
       <x:c r="A56" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.23.6</x:t>
+          <x:t xml:space="preserve">REQ_F4118.23.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B56" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to create a user in the current company.</x:t>
+          <x:t xml:space="preserve">System should lock an account after five consecutive failed password attempts.</x:t>
         </x:is>
       </x:c>
       <x:c r="C56" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.82, REQ_DS43.92</x:t>
+          <x:t xml:space="preserve">REQ_DS43.82</x:t>
         </x:is>
       </x:c>
       <x:c r="D56" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.61</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="E56" s="2" t="inlineStr">
@@ -18805,24 +18963,24 @@
       </x:c>
       <x:c r="F56" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-USER-006, SYS-USER-010, SYS-USER-011, SYS-USER-012</x:t>
+          <x:t xml:space="preserve">SYS-USER-002, SYS-USER-003, SYS-USER-005, SYS-USER-014</x:t>
         </x:is>
       </x:c>
       <x:c r="G56" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Covered</x:t>
+          <x:t xml:space="preserve">Partial</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="57">
       <x:c r="A57" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.23.7</x:t>
+          <x:t xml:space="preserve">REQ_F4118.23.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B57" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to activate or deactivate a user.</x:t>
+          <x:t xml:space="preserve">System should determine whether a user's password has expired.</x:t>
         </x:is>
       </x:c>
       <x:c r="C57" s="2" t="inlineStr">
@@ -18832,39 +18990,39 @@
       </x:c>
       <x:c r="D57" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.63</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="E57" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.63.3</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="F57" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-USER-006, SYS-USER-010, SYS-USER-013, SYS-USER-015, SYS-PERM-029</x:t>
+          <x:t xml:space="preserve">SYS-USER-003</x:t>
         </x:is>
       </x:c>
       <x:c r="G57" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Covered</x:t>
+          <x:t xml:space="preserve">Partial</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="58">
       <x:c r="A58" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.23.8</x:t>
+          <x:t xml:space="preserve">REQ_F4118.23.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B58" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to reset a password and unlock a locked user.</x:t>
+          <x:t xml:space="preserve">System should list the users of the current company with paging, keyword and sorting.</x:t>
         </x:is>
       </x:c>
       <x:c r="C58" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.82</x:t>
+          <x:t xml:space="preserve">REQ_DS43.82, REQ_DS43.92</x:t>
         </x:is>
       </x:c>
       <x:c r="D58" s="2" t="inlineStr">
@@ -18874,12 +19032,12 @@
       </x:c>
       <x:c r="E58" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.63.4, REQ_IO_A8.63.5</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.63.1, REQ_IO_A8.63.2</x:t>
         </x:is>
       </x:c>
       <x:c r="F58" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-USER-006, SYS-USER-010, SYS-USER-014, SYS-PERM-029</x:t>
+          <x:t xml:space="preserve">SYS-USER-006, SYS-USER-010, SYS-USER-011, SYS-USER-015</x:t>
         </x:is>
       </x:c>
       <x:c r="G58" s="2" t="inlineStr">
@@ -18891,123 +19049,123 @@
     <x:row r="59">
       <x:c r="A59" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.24.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.23.6</x:t>
         </x:is>
       </x:c>
       <x:c r="B59" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow a user to log in with username, password and a numeric captcha.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to create a user in the current company.</x:t>
         </x:is>
       </x:c>
       <x:c r="C59" s="2" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">REQ_DS43.82, REQ_DS43.92</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D59" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.61</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E59" s="2" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
-      <x:c r="D59" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">4.4.1.8.62</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E59" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.62.1, REQ_IO_A8.62.2, REQ_IO_A8.62.3, REQ_IO_A8.62.4</x:t>
-        </x:is>
-      </x:c>
       <x:c r="F59" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-AUTH-001, SYS-AUTH-002, SYS-AUTH-005, SYS-AUTH-006, SYS-AUTH-009, SYS-AUTH-014, SYS-AUTH-015, SYS-AUTH-016, SYS-AUTH-017</x:t>
+          <x:t xml:space="preserve">SYS-USER-006, SYS-USER-010, SYS-USER-011, SYS-USER-012</x:t>
         </x:is>
       </x:c>
       <x:c r="G59" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="60">
       <x:c r="A60" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.24.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.23.7</x:t>
         </x:is>
       </x:c>
       <x:c r="B60" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should issue a 15-minute access token and a 7-day rotating refresh token.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to activate or deactivate a user.</x:t>
         </x:is>
       </x:c>
       <x:c r="C60" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_DS43.82</x:t>
         </x:is>
       </x:c>
       <x:c r="D60" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">4.4.1.8.63</x:t>
         </x:is>
       </x:c>
       <x:c r="E60" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.63.3</x:t>
         </x:is>
       </x:c>
       <x:c r="F60" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-AUTH-001, SYS-AUTH-004, SYS-AUTH-007, SYS-AUTH-009, SYS-AUTH-010, SYS-AUTH-016, SYS-AUTH-017</x:t>
+          <x:t xml:space="preserve">SYS-USER-006, SYS-USER-010, SYS-USER-013, SYS-USER-015, SYS-PERM-029</x:t>
         </x:is>
       </x:c>
       <x:c r="G60" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="61">
       <x:c r="A61" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.24.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.23.8</x:t>
         </x:is>
       </x:c>
       <x:c r="B61" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow a logged-in user to log out and invalidate the refresh token.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to reset a password and unlock a locked user.</x:t>
         </x:is>
       </x:c>
       <x:c r="C61" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_DS43.82</x:t>
         </x:is>
       </x:c>
       <x:c r="D61" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">4.4.1.8.63</x:t>
         </x:is>
       </x:c>
       <x:c r="E61" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.63.4, REQ_IO_A8.63.5</x:t>
         </x:is>
       </x:c>
       <x:c r="F61" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-AUTH-008, SYS-AUTH-016, SYS-AUTH-017</x:t>
+          <x:t xml:space="preserve">SYS-USER-006, SYS-USER-010, SYS-USER-014, SYS-PERM-029</x:t>
         </x:is>
       </x:c>
       <x:c r="G61" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="62">
       <x:c r="A62" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.24.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.24.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B62" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should provide a development-only captcha master code with startup protection.</x:t>
+          <x:t xml:space="preserve">System should allow a user to log in with username, password and a numeric captcha.</x:t>
         </x:is>
       </x:c>
       <x:c r="C62" s="2" t="inlineStr">
@@ -19017,17 +19175,17 @@
       </x:c>
       <x:c r="D62" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">4.4.1.8.62</x:t>
         </x:is>
       </x:c>
       <x:c r="E62" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.62.1, REQ_IO_A8.62.2, REQ_IO_A8.62.3, REQ_IO_A8.62.4</x:t>
         </x:is>
       </x:c>
       <x:c r="F62" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-AUTH-003, SYS-AUTH-004, SYS-AUTH-016, SYS-AUTH-017</x:t>
+          <x:t xml:space="preserve">SYS-AUTH-001, SYS-AUTH-002, SYS-AUTH-005, SYS-AUTH-006, SYS-AUTH-009, SYS-AUTH-014, SYS-AUTH-015, SYS-AUTH-016, SYS-AUTH-017</x:t>
         </x:is>
       </x:c>
       <x:c r="G62" s="2" t="inlineStr">
@@ -19039,12 +19197,12 @@
     <x:row r="63">
       <x:c r="A63" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.24.5</x:t>
+          <x:t xml:space="preserve">REQ_F4118.24.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B63" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should provide a trilingual login page that keeps the session and refreshes tokens automatically.</x:t>
+          <x:t xml:space="preserve">System should issue a 15-minute access token and a 7-day rotating refresh token.</x:t>
         </x:is>
       </x:c>
       <x:c r="C63" s="2" t="inlineStr">
@@ -19054,17 +19212,17 @@
       </x:c>
       <x:c r="D63" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.62</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="E63" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.62.5, REQ_IO_A8.62.6</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="F63" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-AUTH-011, SYS-AUTH-012, SYS-AUTH-013, SYS-AUTH-015, SYS-AUTH-016, SYS-AUTH-017</x:t>
+          <x:t xml:space="preserve">SYS-AUTH-001, SYS-AUTH-004, SYS-AUTH-007, SYS-AUTH-009, SYS-AUTH-010, SYS-AUTH-016, SYS-AUTH-017</x:t>
         </x:is>
       </x:c>
       <x:c r="G63" s="2" t="inlineStr">
@@ -19076,22 +19234,22 @@
     <x:row r="64">
       <x:c r="A64" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.25.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.24.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B64" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to view roles and the permission catalog.</x:t>
+          <x:t xml:space="preserve">System should allow a logged-in user to log out and invalidate the refresh token.</x:t>
         </x:is>
       </x:c>
       <x:c r="C64" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.90</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="D64" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.64</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="E64" s="2" t="inlineStr">
@@ -19101,98 +19259,98 @@
       </x:c>
       <x:c r="F64" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-ORG-027, SYS-PERM-004, SYS-PERM-011, SYS-PERM-024, SYS-PERM-025</x:t>
+          <x:t xml:space="preserve">SYS-AUTH-008, SYS-AUTH-016, SYS-AUTH-017</x:t>
         </x:is>
       </x:c>
       <x:c r="G64" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Covered</x:t>
+          <x:t xml:space="preserve">Partial</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="65">
       <x:c r="A65" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.25.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.24.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B65" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to create a role with permissions and a data scope.</x:t>
+          <x:t xml:space="preserve">System should provide a development-only captcha master code with startup protection.</x:t>
         </x:is>
       </x:c>
       <x:c r="C65" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.90, REQ_DS43.91</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="D65" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.64</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="E65" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.64.1, REQ_IO_A8.64.2, REQ_IO_A8.64.3, REQ_IO_A8.64.4, REQ_IO_A8.64.5</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="F65" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-PERM-011, SYS-PERM-024, SYS-PERM-025</x:t>
+          <x:t xml:space="preserve">SYS-AUTH-003, SYS-AUTH-004, SYS-AUTH-016, SYS-AUTH-017</x:t>
         </x:is>
       </x:c>
       <x:c r="G65" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Covered</x:t>
+          <x:t xml:space="preserve">Partial</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="66">
       <x:c r="A66" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.25.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.24.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B66" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to edit or deactivate a role.</x:t>
+          <x:t xml:space="preserve">System should provide a trilingual login page that keeps the session and refreshes tokens automatically.</x:t>
         </x:is>
       </x:c>
       <x:c r="C66" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.90, REQ_DS43.91</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="D66" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.64</x:t>
+          <x:t xml:space="preserve">4.4.1.8.62</x:t>
         </x:is>
       </x:c>
       <x:c r="E66" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.64.2, REQ_IO_A8.64.5</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.62.5, REQ_IO_A8.62.6</x:t>
         </x:is>
       </x:c>
       <x:c r="F66" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-PERM-011, SYS-PERM-024, SYS-PERM-025, SYS-PERM-031, SYS-PERM-032</x:t>
+          <x:t xml:space="preserve">SYS-AUTH-011, SYS-AUTH-012, SYS-AUTH-013, SYS-AUTH-015, SYS-AUTH-016, SYS-AUTH-017</x:t>
         </x:is>
       </x:c>
       <x:c r="G66" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Covered</x:t>
+          <x:t xml:space="preserve">Partial</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.25.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.25.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B67" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to delete an unused role.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to view roles and the permission catalog.</x:t>
         </x:is>
       </x:c>
       <x:c r="C67" s="2" t="inlineStr">
@@ -19207,12 +19365,12 @@
       </x:c>
       <x:c r="E67" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.64.6</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="F67" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-PERM-012, SYS-PERM-024, SYS-PERM-025</x:t>
+          <x:t xml:space="preserve">SYS-ORG-027, SYS-PERM-004, SYS-PERM-011, SYS-PERM-024, SYS-PERM-025</x:t>
         </x:is>
       </x:c>
       <x:c r="G67" s="2" t="inlineStr">
@@ -19224,69 +19382,69 @@
     <x:row r="68">
       <x:c r="A68" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.25.5</x:t>
+          <x:t xml:space="preserve">REQ_F4118.25.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B68" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enforce permission codes on every API with the backend as the authority.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to create a role with permissions and a data scope.</x:t>
         </x:is>
       </x:c>
       <x:c r="C68" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.92</x:t>
+          <x:t xml:space="preserve">REQ_DS43.90, REQ_DS43.91</x:t>
         </x:is>
       </x:c>
       <x:c r="D68" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">4.4.1.8.64</x:t>
         </x:is>
       </x:c>
       <x:c r="E68" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.64.1, REQ_IO_A8.64.2, REQ_IO_A8.64.3, REQ_IO_A8.64.4, REQ_IO_A8.64.5</x:t>
         </x:is>
       </x:c>
       <x:c r="F68" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-PERM-001, SYS-PERM-005, SYS-PERM-006, SYS-PERM-010</x:t>
+          <x:t xml:space="preserve">SYS-PERM-011, SYS-PERM-024, SYS-PERM-025</x:t>
         </x:is>
       </x:c>
       <x:c r="G68" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="69">
       <x:c r="A69" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.25.6</x:t>
+          <x:t xml:space="preserve">REQ_F4118.25.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B69" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to grant a user access to a company with roles, organization and default company.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to edit or deactivate a role.</x:t>
         </x:is>
       </x:c>
       <x:c r="C69" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.92, REQ_DS43.93</x:t>
+          <x:t xml:space="preserve">REQ_DS43.90, REQ_DS43.91</x:t>
         </x:is>
       </x:c>
       <x:c r="D69" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.65</x:t>
+          <x:t xml:space="preserve">4.4.1.8.64</x:t>
         </x:is>
       </x:c>
       <x:c r="E69" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.65.1, REQ_IO_A8.65.2, REQ_IO_A8.65.3, REQ_IO_A8.65.4, REQ_IO_A8.65.5</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.64.2, REQ_IO_A8.64.5</x:t>
         </x:is>
       </x:c>
       <x:c r="F69" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-PERM-015, SYS-PERM-016, SYS-PERM-017, SYS-PERM-018, SYS-PERM-026, SYS-PERM-027, SYS-PERM-028</x:t>
+          <x:t xml:space="preserve">SYS-PERM-011, SYS-PERM-024, SYS-PERM-025, SYS-PERM-031, SYS-PERM-032</x:t>
         </x:is>
       </x:c>
       <x:c r="G69" s="2" t="inlineStr">
@@ -19298,143 +19456,143 @@
     <x:row r="70">
       <x:c r="A70" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.25.7</x:t>
+          <x:t xml:space="preserve">REQ_F4118.25.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B70" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should resolve the user's effective permissions and data scope per company and hide unauthorized UI.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to delete an unused role.</x:t>
         </x:is>
       </x:c>
       <x:c r="C70" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.91, REQ_DS43.92, REQ_DS43.93</x:t>
+          <x:t xml:space="preserve">REQ_DS43.90</x:t>
         </x:is>
       </x:c>
       <x:c r="D70" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">4.4.1.8.64</x:t>
         </x:is>
       </x:c>
       <x:c r="E70" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.64.6</x:t>
         </x:is>
       </x:c>
       <x:c r="F70" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-PERM-002, SYS-PERM-003, SYS-PERM-013, SYS-PERM-014, SYS-PERM-020, SYS-PERM-021, SYS-PERM-022, SYS-PERM-023</x:t>
+          <x:t xml:space="preserve">SYS-PERM-012, SYS-PERM-024, SYS-PERM-025</x:t>
         </x:is>
       </x:c>
       <x:c r="G70" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="71">
       <x:c r="A71" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.25.8</x:t>
+          <x:t xml:space="preserve">REQ_F4118.25.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B71" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to view a user's company access, organization and roles.</x:t>
+          <x:t xml:space="preserve">System should enforce permission codes on every API with the backend as the authority.</x:t>
         </x:is>
       </x:c>
       <x:c r="C71" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.92, REQ_DS43.93</x:t>
+          <x:t xml:space="preserve">REQ_DS43.92</x:t>
         </x:is>
       </x:c>
       <x:c r="D71" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.65</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="E71" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.65.1</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="F71" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-PERM-017, SYS-PERM-018, SYS-PERM-026, SYS-PERM-027</x:t>
+          <x:t xml:space="preserve">SYS-PERM-001, SYS-PERM-005, SYS-PERM-006, SYS-PERM-010</x:t>
         </x:is>
       </x:c>
       <x:c r="G71" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Covered</x:t>
+          <x:t xml:space="preserve">Partial</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="72">
       <x:c r="A72" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.26.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.25.6</x:t>
         </x:is>
       </x:c>
       <x:c r="B72" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enforce HTTPS with HSTS outside the development environment.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to grant a user access to a company with roles, organization and default company.</x:t>
         </x:is>
       </x:c>
       <x:c r="C72" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_DS43.92, REQ_DS43.93</x:t>
         </x:is>
       </x:c>
       <x:c r="D72" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">4.4.1.8.65</x:t>
         </x:is>
       </x:c>
       <x:c r="E72" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.65.1, REQ_IO_A8.65.2, REQ_IO_A8.65.3, REQ_IO_A8.65.4, REQ_IO_A8.65.5</x:t>
         </x:is>
       </x:c>
       <x:c r="F72" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-SEC-004</x:t>
+          <x:t xml:space="preserve">SYS-PERM-015, SYS-PERM-016, SYS-PERM-017, SYS-PERM-018, SYS-PERM-026, SYS-PERM-027, SYS-PERM-028</x:t>
         </x:is>
       </x:c>
       <x:c r="G72" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="73">
       <x:c r="A73" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.26.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.25.7</x:t>
         </x:is>
       </x:c>
       <x:c r="B73" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow cross-origin requests only from configured frontend origins.</x:t>
+          <x:t xml:space="preserve">System should resolve the user's effective permissions and data scope per company and hide unauthorized UI.</x:t>
         </x:is>
       </x:c>
       <x:c r="C73" s="2" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">REQ_DS43.91, REQ_DS43.92, REQ_DS43.93</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D73" s="2" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
-      <x:c r="D73" s="2" t="inlineStr">
+      <x:c r="E73" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
-      <x:c r="E73" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
       <x:c r="F73" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-SEC-002, SYS-SEC-003, SYS-SEC-006</x:t>
+          <x:t xml:space="preserve">SYS-PERM-002, SYS-PERM-003, SYS-PERM-013, SYS-PERM-014, SYS-PERM-020, SYS-PERM-021, SYS-PERM-022, SYS-PERM-023</x:t>
         </x:is>
       </x:c>
       <x:c r="G73" s="2" t="inlineStr">
@@ -19446,49 +19604,49 @@
     <x:row r="74">
       <x:c r="A74" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.26.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.25.8</x:t>
         </x:is>
       </x:c>
       <x:c r="B74" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should rate-limit login, token refresh and captcha requests per client IP.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to view a user's company access, organization and roles.</x:t>
         </x:is>
       </x:c>
       <x:c r="C74" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_DS43.92, REQ_DS43.93</x:t>
         </x:is>
       </x:c>
       <x:c r="D74" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">4.4.1.8.65</x:t>
         </x:is>
       </x:c>
       <x:c r="E74" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.65.1</x:t>
         </x:is>
       </x:c>
       <x:c r="F74" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-SEC-003, SYS-SEC-005, SYS-SEC-006, SYS-SEC-007, SYS-SEC-011, SYS-SEC-012</x:t>
+          <x:t xml:space="preserve">SYS-PERM-017, SYS-PERM-018, SYS-PERM-026, SYS-PERM-027</x:t>
         </x:is>
       </x:c>
       <x:c r="G74" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="75">
       <x:c r="A75" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.26.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.26.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B75" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should rate-limit authenticated API requests per user.</x:t>
+          <x:t xml:space="preserve">System should enforce HTTPS with HSTS outside the development environment.</x:t>
         </x:is>
       </x:c>
       <x:c r="C75" s="2" t="inlineStr">
@@ -19508,7 +19666,7 @@
       </x:c>
       <x:c r="F75" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-SEC-010</x:t>
+          <x:t xml:space="preserve">SYS-SEC-004</x:t>
         </x:is>
       </x:c>
       <x:c r="G75" s="2" t="inlineStr">
@@ -19520,12 +19678,12 @@
     <x:row r="76">
       <x:c r="A76" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.26.5</x:t>
+          <x:t xml:space="preserve">REQ_F4118.26.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B76" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should add security headers to every API response.</x:t>
+          <x:t xml:space="preserve">System should allow cross-origin requests only from configured frontend origins.</x:t>
         </x:is>
       </x:c>
       <x:c r="C76" s="2" t="inlineStr">
@@ -19545,7 +19703,7 @@
       </x:c>
       <x:c r="F76" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-SEC-001, SYS-SEC-014</x:t>
+          <x:t xml:space="preserve">SYS-SEC-002, SYS-SEC-003, SYS-SEC-006</x:t>
         </x:is>
       </x:c>
       <x:c r="G76" s="2" t="inlineStr">
@@ -19557,12 +19715,12 @@
     <x:row r="77">
       <x:c r="A77" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.26.6</x:t>
+          <x:t xml:space="preserve">REQ_F4118.26.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B77" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should honour X-Forwarded-For only from configured proxies.</x:t>
+          <x:t xml:space="preserve">System should rate-limit login, token refresh and captcha requests per client IP.</x:t>
         </x:is>
       </x:c>
       <x:c r="C77" s="2" t="inlineStr">
@@ -19582,7 +19740,7 @@
       </x:c>
       <x:c r="F77" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-SEC-003, SYS-SEC-008, SYS-SEC-009</x:t>
+          <x:t xml:space="preserve">SYS-SEC-003, SYS-SEC-005, SYS-SEC-006, SYS-SEC-007, SYS-SEC-011, SYS-SEC-012</x:t>
         </x:is>
       </x:c>
       <x:c r="G77" s="2" t="inlineStr">
@@ -19594,12 +19752,12 @@
     <x:row r="78">
       <x:c r="A78" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.26.7</x:t>
+          <x:t xml:space="preserve">REQ_F4118.26.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B78" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should show a trilingual "too many requests" message when an API call is rate-limited.</x:t>
+          <x:t xml:space="preserve">System should rate-limit authenticated API requests per user.</x:t>
         </x:is>
       </x:c>
       <x:c r="C78" s="2" t="inlineStr">
@@ -19619,7 +19777,7 @@
       </x:c>
       <x:c r="F78" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-SEC-013, SYS-SEC-014</x:t>
+          <x:t xml:space="preserve">SYS-SEC-010</x:t>
         </x:is>
       </x:c>
       <x:c r="G78" s="2" t="inlineStr">
@@ -19631,17 +19789,17 @@
     <x:row r="79">
       <x:c r="A79" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.27.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.26.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B79" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should record every data change in sys_audit_log within the same transaction.</x:t>
+          <x:t xml:space="preserve">System should add security headers to every API response.</x:t>
         </x:is>
       </x:c>
       <x:c r="C79" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.94</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="D79" s="2" t="inlineStr">
@@ -19656,7 +19814,7 @@
       </x:c>
       <x:c r="F79" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-AUDIT-001, SYS-AUDIT-002, SYS-AUDIT-003, SYS-AUDIT-004, SYS-AUDIT-005, SYS-AUDIT-006, SYS-AUDIT-010</x:t>
+          <x:t xml:space="preserve">SYS-SEC-001, SYS-SEC-014</x:t>
         </x:is>
       </x:c>
       <x:c r="G79" s="2" t="inlineStr">
@@ -19668,17 +19826,17 @@
     <x:row r="80">
       <x:c r="A80" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.27.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.26.6</x:t>
         </x:is>
       </x:c>
       <x:c r="B80" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should protect audit records and sensitive values.</x:t>
+          <x:t xml:space="preserve">System should honour X-Forwarded-For only from configured proxies.</x:t>
         </x:is>
       </x:c>
       <x:c r="C80" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.94</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="D80" s="2" t="inlineStr">
@@ -19688,34 +19846,34 @@
       </x:c>
       <x:c r="E80" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.66.5</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="F80" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-AUDIT-003, SYS-AUDIT-008, SYS-AUDIT-011</x:t>
+          <x:t xml:space="preserve">SYS-SEC-003, SYS-SEC-008, SYS-SEC-009</x:t>
         </x:is>
       </x:c>
       <x:c r="G80" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Covered</x:t>
+          <x:t xml:space="preserve">Partial</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="81">
       <x:c r="A81" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.27.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.26.7</x:t>
         </x:is>
       </x:c>
       <x:c r="B81" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should record login, failed login, logout and captcha master-code login as security events.</x:t>
+          <x:t xml:space="preserve">System should show a trilingual "too many requests" message when an API call is rate-limited.</x:t>
         </x:is>
       </x:c>
       <x:c r="C81" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.94</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="D81" s="2" t="inlineStr">
@@ -19730,7 +19888,7 @@
       </x:c>
       <x:c r="F81" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-AUDIT-007, SYS-AUDIT-012</x:t>
+          <x:t xml:space="preserve">SYS-SEC-013, SYS-SEC-014</x:t>
         </x:is>
       </x:c>
       <x:c r="G81" s="2" t="inlineStr">
@@ -19742,12 +19900,12 @@
     <x:row r="82">
       <x:c r="A82" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.27.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.27.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B82" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to query audit logs of the current company.</x:t>
+          <x:t xml:space="preserve">System should record every data change in sys_audit_log within the same transaction.</x:t>
         </x:is>
       </x:c>
       <x:c r="C82" s="2" t="inlineStr">
@@ -19757,34 +19915,34 @@
       </x:c>
       <x:c r="D82" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.66</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="E82" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.66.1</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="F82" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-AUDIT-009, SYS-AUDIT-010</x:t>
+          <x:t xml:space="preserve">SYS-AUDIT-001, SYS-AUDIT-002, SYS-AUDIT-003, SYS-AUDIT-004, SYS-AUDIT-005, SYS-AUDIT-006, SYS-AUDIT-010</x:t>
         </x:is>
       </x:c>
       <x:c r="G82" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Covered</x:t>
+          <x:t xml:space="preserve">Partial</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="83">
       <x:c r="A83" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.27.5</x:t>
+          <x:t xml:space="preserve">REQ_F4118.27.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B83" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should record role permission and user company access changes as security events.</x:t>
+          <x:t xml:space="preserve">System should protect audit records and sensitive values.</x:t>
         </x:is>
       </x:c>
       <x:c r="C83" s="2" t="inlineStr">
@@ -19799,29 +19957,29 @@
       </x:c>
       <x:c r="E83" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.66.5</x:t>
         </x:is>
       </x:c>
       <x:c r="F83" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-AUDIT-013</x:t>
+          <x:t xml:space="preserve">SYS-AUDIT-003, SYS-AUDIT-008, SYS-AUDIT-011</x:t>
         </x:is>
       </x:c>
       <x:c r="G83" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="84">
       <x:c r="A84" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.27.6</x:t>
+          <x:t xml:space="preserve">REQ_F4118.27.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B84" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should provide a trilingual audit log page with per-record change history.</x:t>
+          <x:t xml:space="preserve">System should record login, failed login, logout and captcha master-code login as security events.</x:t>
         </x:is>
       </x:c>
       <x:c r="C84" s="2" t="inlineStr">
@@ -19831,54 +19989,54 @@
       </x:c>
       <x:c r="D84" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.66</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="E84" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.66.1, REQ_IO_A8.66.2, REQ_IO_A8.66.3, REQ_IO_A8.66.4, REQ_IO_A8.66.5, REQ_IO_A8.66.6</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="F84" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-AUDIT-014</x:t>
+          <x:t xml:space="preserve">SYS-AUDIT-007, SYS-AUDIT-012</x:t>
         </x:is>
       </x:c>
       <x:c r="G84" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Covered</x:t>
+          <x:t xml:space="preserve">Partial</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="85">
       <x:c r="A85" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.28.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.27.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B85" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow user to view document number rules of the current company.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to query audit logs of the current company.</x:t>
         </x:is>
       </x:c>
       <x:c r="C85" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.95</x:t>
+          <x:t xml:space="preserve">REQ_DS43.94</x:t>
         </x:is>
       </x:c>
       <x:c r="D85" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.67</x:t>
+          <x:t xml:space="preserve">4.4.1.8.66</x:t>
         </x:is>
       </x:c>
       <x:c r="E85" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.66.1</x:t>
         </x:is>
       </x:c>
       <x:c r="F85" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-NUM-006, SYS-NUM-008, SYS-NUM-010</x:t>
+          <x:t xml:space="preserve">SYS-AUDIT-009, SYS-AUDIT-010</x:t>
         </x:is>
       </x:c>
       <x:c r="G85" s="2" t="inlineStr">
@@ -19890,69 +20048,69 @@
     <x:row r="86">
       <x:c r="A86" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.28.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.27.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B86" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow user to create a document number rule with prefix, date format, sequence length and reset period.</x:t>
+          <x:t xml:space="preserve">System should record role permission and user company access changes as security events.</x:t>
         </x:is>
       </x:c>
       <x:c r="C86" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.95</x:t>
+          <x:t xml:space="preserve">REQ_DS43.94</x:t>
         </x:is>
       </x:c>
       <x:c r="D86" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.67</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="E86" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.67.1, REQ_IO_A8.67.2, REQ_IO_A8.67.3, REQ_IO_A8.67.4, REQ_IO_A8.67.5, REQ_IO_A8.67.6</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="F86" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-NUM-006, SYS-NUM-007, SYS-NUM-008, SYS-NUM-010, SYS-NUM-011</x:t>
+          <x:t xml:space="preserve">SYS-AUDIT-013</x:t>
         </x:is>
       </x:c>
       <x:c r="G86" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Covered</x:t>
+          <x:t xml:space="preserve">Partial</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="87">
       <x:c r="A87" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.28.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.27.6</x:t>
         </x:is>
       </x:c>
       <x:c r="B87" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow user to edit or deactivate a document number rule without breaking issued numbers.</x:t>
+          <x:t xml:space="preserve">System should provide a trilingual audit log page with per-record change history.</x:t>
         </x:is>
       </x:c>
       <x:c r="C87" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.95, REQ_DS43.96</x:t>
+          <x:t xml:space="preserve">REQ_DS43.94</x:t>
         </x:is>
       </x:c>
       <x:c r="D87" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.67</x:t>
+          <x:t xml:space="preserve">4.4.1.8.66</x:t>
         </x:is>
       </x:c>
       <x:c r="E87" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.67.2, REQ_IO_A8.67.3, REQ_IO_A8.67.4, REQ_IO_A8.67.5, REQ_IO_A8.67.6, REQ_IO_A8.67.8</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.66.1, REQ_IO_A8.66.2, REQ_IO_A8.66.3, REQ_IO_A8.66.4, REQ_IO_A8.66.5, REQ_IO_A8.66.6</x:t>
         </x:is>
       </x:c>
       <x:c r="F87" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-NUM-006, SYS-NUM-008, SYS-NUM-009, SYS-NUM-010, SYS-NUM-011</x:t>
+          <x:t xml:space="preserve">SYS-AUDIT-014</x:t>
         </x:is>
       </x:c>
       <x:c r="G87" s="2" t="inlineStr">
@@ -19964,17 +20122,17 @@
     <x:row r="88">
       <x:c r="A88" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.28.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.28.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B88" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow user to preview the next document number for a business date.</x:t>
+          <x:t xml:space="preserve">System should allow user to view document number rules of the current company.</x:t>
         </x:is>
       </x:c>
       <x:c r="C88" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.95, REQ_DS43.96</x:t>
+          <x:t xml:space="preserve">REQ_DS43.95</x:t>
         </x:is>
       </x:c>
       <x:c r="D88" s="2" t="inlineStr">
@@ -19984,12 +20142,12 @@
       </x:c>
       <x:c r="E88" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.67.9</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="F88" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-NUM-006, SYS-NUM-008, SYS-NUM-010, SYS-NUM-011</x:t>
+          <x:t xml:space="preserve">SYS-NUM-006, SYS-NUM-008, SYS-NUM-010</x:t>
         </x:is>
       </x:c>
       <x:c r="G88" s="2" t="inlineStr">
@@ -20001,54 +20159,54 @@
     <x:row r="89">
       <x:c r="A89" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.28.5</x:t>
+          <x:t xml:space="preserve">REQ_F4118.28.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B89" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should generate unique, gap-free document numbers for every module under concurrency.</x:t>
+          <x:t xml:space="preserve">System should allow user to create a document number rule with prefix, date format, sequence length and reset period.</x:t>
         </x:is>
       </x:c>
       <x:c r="C89" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.95, REQ_DS43.96</x:t>
+          <x:t xml:space="preserve">REQ_DS43.95</x:t>
         </x:is>
       </x:c>
       <x:c r="D89" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">4.4.1.8.67</x:t>
         </x:is>
       </x:c>
       <x:c r="E89" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.67.1, REQ_IO_A8.67.2, REQ_IO_A8.67.3, REQ_IO_A8.67.4, REQ_IO_A8.67.5, REQ_IO_A8.67.6</x:t>
         </x:is>
       </x:c>
       <x:c r="F89" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-NUM-001, SYS-NUM-002, SYS-NUM-003, SYS-NUM-004, SYS-NUM-005, SYS-NUM-009</x:t>
+          <x:t xml:space="preserve">SYS-NUM-006, SYS-NUM-007, SYS-NUM-008, SYS-NUM-010, SYS-NUM-011</x:t>
         </x:is>
       </x:c>
       <x:c r="G89" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="90">
       <x:c r="A90" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.28.6</x:t>
+          <x:t xml:space="preserve">REQ_F4118.28.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B90" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should provide a trilingual number rule maintenance page.</x:t>
+          <x:t xml:space="preserve">System should allow user to edit or deactivate a document number rule without breaking issued numbers.</x:t>
         </x:is>
       </x:c>
       <x:c r="C90" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.95</x:t>
+          <x:t xml:space="preserve">REQ_DS43.95, REQ_DS43.96</x:t>
         </x:is>
       </x:c>
       <x:c r="D90" s="2" t="inlineStr">
@@ -20058,12 +20216,12 @@
       </x:c>
       <x:c r="E90" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.67.1, REQ_IO_A8.67.7</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.67.2, REQ_IO_A8.67.3, REQ_IO_A8.67.4, REQ_IO_A8.67.5, REQ_IO_A8.67.6, REQ_IO_A8.67.8</x:t>
         </x:is>
       </x:c>
       <x:c r="F90" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-NUM-010, SYS-NUM-011</x:t>
+          <x:t xml:space="preserve">SYS-NUM-006, SYS-NUM-008, SYS-NUM-009, SYS-NUM-010, SYS-NUM-011</x:t>
         </x:is>
       </x:c>
       <x:c r="G90" s="2" t="inlineStr">
@@ -20075,32 +20233,32 @@
     <x:row r="91">
       <x:c r="A91" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.29.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.28.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B91" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow user to view and create multi-level approval flows with amount thresholds.</x:t>
+          <x:t xml:space="preserve">System should allow user to preview the next document number for a business date.</x:t>
         </x:is>
       </x:c>
       <x:c r="C91" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.97, REQ_DS43.98</x:t>
+          <x:t xml:space="preserve">REQ_DS43.95, REQ_DS43.96</x:t>
         </x:is>
       </x:c>
       <x:c r="D91" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.68</x:t>
+          <x:t xml:space="preserve">4.4.1.8.67</x:t>
         </x:is>
       </x:c>
       <x:c r="E91" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.68.1, REQ_IO_A8.68.2, REQ_IO_A8.68.3, REQ_IO_A8.68.4, REQ_IO_A8.68.5, REQ_IO_A8.68.6, REQ_IO_A8.68.7</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.67.9</x:t>
         </x:is>
       </x:c>
       <x:c r="F91" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-APR-008, SYS-APR-010, SYS-APR-012, SYS-APR-013</x:t>
+          <x:t xml:space="preserve">SYS-NUM-006, SYS-NUM-008, SYS-NUM-010, SYS-NUM-011</x:t>
         </x:is>
       </x:c>
       <x:c r="G91" s="2" t="inlineStr">
@@ -20112,69 +20270,69 @@
     <x:row r="92">
       <x:c r="A92" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.29.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.28.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B92" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow user to edit or deactivate an approval flow without affecting pending approvals.</x:t>
+          <x:t xml:space="preserve">System should generate unique, gap-free document numbers for every module under concurrency.</x:t>
         </x:is>
       </x:c>
       <x:c r="C92" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.97, REQ_DS43.98</x:t>
+          <x:t xml:space="preserve">REQ_DS43.95, REQ_DS43.96</x:t>
         </x:is>
       </x:c>
       <x:c r="D92" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.68</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="E92" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.68.2, REQ_IO_A8.68.3, REQ_IO_A8.68.8</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="F92" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-APR-003, SYS-APR-008, SYS-APR-010, SYS-APR-012, SYS-APR-013</x:t>
+          <x:t xml:space="preserve">SYS-NUM-001, SYS-NUM-002, SYS-NUM-003, SYS-NUM-004, SYS-NUM-005, SYS-NUM-009</x:t>
         </x:is>
       </x:c>
       <x:c r="G92" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Covered</x:t>
+          <x:t xml:space="preserve">Partial</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="93">
       <x:c r="A93" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.29.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.28.6</x:t>
         </x:is>
       </x:c>
       <x:c r="B93" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow user to assign an approval delegate for a date range.</x:t>
+          <x:t xml:space="preserve">System should provide a trilingual number rule maintenance page.</x:t>
         </x:is>
       </x:c>
       <x:c r="C93" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.99</x:t>
+          <x:t xml:space="preserve">REQ_DS43.95</x:t>
         </x:is>
       </x:c>
       <x:c r="D93" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.69</x:t>
+          <x:t xml:space="preserve">4.4.1.8.67</x:t>
         </x:is>
       </x:c>
       <x:c r="E93" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.69.1, REQ_IO_A8.69.2, REQ_IO_A8.69.3, REQ_IO_A8.69.4</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.67.1, REQ_IO_A8.67.7</x:t>
         </x:is>
       </x:c>
       <x:c r="F93" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-APR-005, SYS-APR-010, SYS-APR-012, SYS-APR-013</x:t>
+          <x:t xml:space="preserve">SYS-NUM-010, SYS-NUM-011</x:t>
         </x:is>
       </x:c>
       <x:c r="G93" s="2" t="inlineStr">
@@ -20186,69 +20344,69 @@
     <x:row r="94">
       <x:c r="A94" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.29.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.29.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B94" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable every module to submit documents for approval through the shared workflow engine.</x:t>
+          <x:t xml:space="preserve">System should allow user to view and create multi-level approval flows with amount thresholds.</x:t>
         </x:is>
       </x:c>
       <x:c r="C94" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.97, REQ_DS43.98, REQ_DS43.100, REQ_DS43.101</x:t>
+          <x:t xml:space="preserve">REQ_DS43.97, REQ_DS43.98</x:t>
         </x:is>
       </x:c>
       <x:c r="D94" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">4.4.1.8.68</x:t>
         </x:is>
       </x:c>
       <x:c r="E94" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.68.1, REQ_IO_A8.68.2, REQ_IO_A8.68.3, REQ_IO_A8.68.4, REQ_IO_A8.68.5, REQ_IO_A8.68.6, REQ_IO_A8.68.7</x:t>
         </x:is>
       </x:c>
       <x:c r="F94" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-APR-001, SYS-APR-002, SYS-APR-003, SYS-APR-007, SYS-APR-011</x:t>
+          <x:t xml:space="preserve">SYS-APR-008, SYS-APR-010, SYS-APR-012, SYS-APR-013</x:t>
         </x:is>
       </x:c>
       <x:c r="G94" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="95">
       <x:c r="A95" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.29.5</x:t>
+          <x:t xml:space="preserve">REQ_F4118.29.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B95" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow approvers or their delegates to approve or reject the current approval step.</x:t>
+          <x:t xml:space="preserve">System should allow user to edit or deactivate an approval flow without affecting pending approvals.</x:t>
         </x:is>
       </x:c>
       <x:c r="C95" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.99, REQ_DS43.100, REQ_DS43.101</x:t>
+          <x:t xml:space="preserve">REQ_DS43.97, REQ_DS43.98</x:t>
         </x:is>
       </x:c>
       <x:c r="D95" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.70</x:t>
+          <x:t xml:space="preserve">4.4.1.8.68</x:t>
         </x:is>
       </x:c>
       <x:c r="E95" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.70.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.68.2, REQ_IO_A8.68.3, REQ_IO_A8.68.8</x:t>
         </x:is>
       </x:c>
       <x:c r="F95" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-APR-001, SYS-APR-002, SYS-APR-004, SYS-APR-005, SYS-APR-006, SYS-APR-007, SYS-APR-011, SYS-APR-012, SYS-APR-013</x:t>
+          <x:t xml:space="preserve">SYS-APR-003, SYS-APR-008, SYS-APR-010, SYS-APR-012, SYS-APR-013</x:t>
         </x:is>
       </x:c>
       <x:c r="G95" s="2" t="inlineStr">
@@ -20260,32 +20418,32 @@
     <x:row r="96">
       <x:c r="A96" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.29.6</x:t>
+          <x:t xml:space="preserve">REQ_F4118.29.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B96" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should list the pending approval tasks of the current user.</x:t>
+          <x:t xml:space="preserve">System should allow user to assign an approval delegate for a date range.</x:t>
         </x:is>
       </x:c>
       <x:c r="C96" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.99, REQ_DS43.100, REQ_DS43.101</x:t>
+          <x:t xml:space="preserve">REQ_DS43.99</x:t>
         </x:is>
       </x:c>
       <x:c r="D96" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.70</x:t>
+          <x:t xml:space="preserve">4.4.1.8.69</x:t>
         </x:is>
       </x:c>
       <x:c r="E96" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.69.1, REQ_IO_A8.69.2, REQ_IO_A8.69.3, REQ_IO_A8.69.4</x:t>
         </x:is>
       </x:c>
       <x:c r="F96" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-APR-004, SYS-APR-005, SYS-APR-011, SYS-APR-012, SYS-APR-013</x:t>
+          <x:t xml:space="preserve">SYS-APR-005, SYS-APR-010, SYS-APR-012, SYS-APR-013</x:t>
         </x:is>
       </x:c>
       <x:c r="G96" s="2" t="inlineStr">
@@ -20297,69 +20455,69 @@
     <x:row r="97">
       <x:c r="A97" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.29.7</x:t>
+          <x:t xml:space="preserve">REQ_F4118.29.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B97" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow user to view the approval history of a document.</x:t>
+          <x:t xml:space="preserve">System should enable every module to submit documents for approval through the shared workflow engine.</x:t>
         </x:is>
       </x:c>
       <x:c r="C97" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.100, REQ_DS43.101</x:t>
+          <x:t xml:space="preserve">REQ_DS43.97, REQ_DS43.98, REQ_DS43.100, REQ_DS43.101</x:t>
         </x:is>
       </x:c>
       <x:c r="D97" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.70</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="E97" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.70.2</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="F97" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-APR-001, SYS-APR-002, SYS-APR-008, SYS-APR-011, SYS-APR-012, SYS-APR-013</x:t>
+          <x:t xml:space="preserve">SYS-APR-001, SYS-APR-002, SYS-APR-003, SYS-APR-007, SYS-APR-011</x:t>
         </x:is>
       </x:c>
       <x:c r="G97" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Covered</x:t>
+          <x:t xml:space="preserve">Partial</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="98">
       <x:c r="A98" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.29.8</x:t>
+          <x:t xml:space="preserve">REQ_F4118.29.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B98" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should provide trilingual approval flow and delegation maintenance pages.</x:t>
+          <x:t xml:space="preserve">System should allow approvers or their delegates to approve or reject the current approval step.</x:t>
         </x:is>
       </x:c>
       <x:c r="C98" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.97, REQ_DS43.98, REQ_DS43.99</x:t>
+          <x:t xml:space="preserve">REQ_DS43.99, REQ_DS43.100, REQ_DS43.101</x:t>
         </x:is>
       </x:c>
       <x:c r="D98" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.68, 4.4.1.8.69</x:t>
+          <x:t xml:space="preserve">4.4.1.8.70</x:t>
         </x:is>
       </x:c>
       <x:c r="E98" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.68.1, REQ_IO_A8.68.4, REQ_IO_A8.68.5, REQ_IO_A8.68.6, REQ_IO_A8.68.7</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.70.1</x:t>
         </x:is>
       </x:c>
       <x:c r="F98" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-APR-012, SYS-APR-013</x:t>
+          <x:t xml:space="preserve">SYS-APR-001, SYS-APR-002, SYS-APR-004, SYS-APR-005, SYS-APR-006, SYS-APR-007, SYS-APR-011, SYS-APR-012, SYS-APR-013</x:t>
         </x:is>
       </x:c>
       <x:c r="G98" s="2" t="inlineStr">
@@ -20371,17 +20529,17 @@
     <x:row r="99">
       <x:c r="A99" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.29.9</x:t>
+          <x:t xml:space="preserve">REQ_F4118.29.6</x:t>
         </x:is>
       </x:c>
       <x:c r="B99" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should provide a trilingual approval inbox with approval history.</x:t>
+          <x:t xml:space="preserve">System should list the pending approval tasks of the current user.</x:t>
         </x:is>
       </x:c>
       <x:c r="C99" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.100, REQ_DS43.101</x:t>
+          <x:t xml:space="preserve">REQ_DS43.99, REQ_DS43.100, REQ_DS43.101</x:t>
         </x:is>
       </x:c>
       <x:c r="D99" s="2" t="inlineStr">
@@ -20391,12 +20549,12 @@
       </x:c>
       <x:c r="E99" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.70.1, REQ_IO_A8.70.2</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="F99" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-APR-012, SYS-APR-013</x:t>
+          <x:t xml:space="preserve">SYS-APR-004, SYS-APR-005, SYS-APR-011, SYS-APR-012, SYS-APR-013</x:t>
         </x:is>
       </x:c>
       <x:c r="G99" s="2" t="inlineStr">
@@ -20408,143 +20566,143 @@
     <x:row r="100">
       <x:c r="A100" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.30.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.29.7</x:t>
         </x:is>
       </x:c>
       <x:c r="B100" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should load demo companies, branches, departments and roles for the Development environment.</x:t>
+          <x:t xml:space="preserve">System should allow user to view the approval history of a document.</x:t>
         </x:is>
       </x:c>
       <x:c r="C100" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.20, REQ_DS43.22, REQ_DS43.89, REQ_DS43.90, REQ_DS43.91</x:t>
+          <x:t xml:space="preserve">REQ_DS43.100, REQ_DS43.101</x:t>
         </x:is>
       </x:c>
       <x:c r="D100" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">4.4.1.8.70</x:t>
         </x:is>
       </x:c>
       <x:c r="E100" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.70.2</x:t>
         </x:is>
       </x:c>
       <x:c r="F100" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-SEED-001, SYS-SEED-002, SYS-SEED-003, SYS-SEED-006</x:t>
+          <x:t xml:space="preserve">SYS-APR-001, SYS-APR-002, SYS-APR-008, SYS-APR-011, SYS-APR-012, SYS-APR-013</x:t>
         </x:is>
       </x:c>
       <x:c r="G100" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="101">
       <x:c r="A101" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.30.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.29.8</x:t>
         </x:is>
       </x:c>
       <x:c r="B101" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should create the test accounts of the SeedUsers setting with hashed passwords and company assignments.</x:t>
+          <x:t xml:space="preserve">System should provide trilingual approval flow and delegation maintenance pages.</x:t>
         </x:is>
       </x:c>
       <x:c r="C101" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.82, REQ_DS43.92, REQ_DS43.93</x:t>
+          <x:t xml:space="preserve">REQ_DS43.97, REQ_DS43.98, REQ_DS43.99</x:t>
         </x:is>
       </x:c>
       <x:c r="D101" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">4.4.1.8.68, 4.4.1.8.69</x:t>
         </x:is>
       </x:c>
       <x:c r="E101" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.68.1, REQ_IO_A8.68.4, REQ_IO_A8.68.5, REQ_IO_A8.68.6, REQ_IO_A8.68.7</x:t>
         </x:is>
       </x:c>
       <x:c r="F101" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-SEED-001, SYS-SEED-005</x:t>
+          <x:t xml:space="preserve">SYS-APR-012, SYS-APR-013</x:t>
         </x:is>
       </x:c>
       <x:c r="G101" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="102">
       <x:c r="A102" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.30.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.29.9</x:t>
         </x:is>
       </x:c>
       <x:c r="B102" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow the seed to run repeatedly without duplicating or overwriting data.</x:t>
+          <x:t xml:space="preserve">System should provide a trilingual approval inbox with approval history.</x:t>
         </x:is>
       </x:c>
       <x:c r="C102" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.20, REQ_DS43.82, REQ_DS43.91</x:t>
+          <x:t xml:space="preserve">REQ_DS43.100, REQ_DS43.101</x:t>
         </x:is>
       </x:c>
       <x:c r="D102" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">4.4.1.8.70</x:t>
         </x:is>
       </x:c>
       <x:c r="E102" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.70.1, REQ_IO_A8.70.2</x:t>
         </x:is>
       </x:c>
       <x:c r="F102" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-SEED-001, SYS-SEED-003, SYS-SEED-004</x:t>
+          <x:t xml:space="preserve">SYS-APR-012, SYS-APR-013</x:t>
         </x:is>
       </x:c>
       <x:c r="G102" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="103">
       <x:c r="A103" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.31.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.30.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B103" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should ask for confirmation in a shared trilingual confirmation box before dangerous actions.</x:t>
+          <x:t xml:space="preserve">System should load demo companies, branches, departments and roles for the Development environment.</x:t>
         </x:is>
       </x:c>
       <x:c r="C103" s="2" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">REQ_DS43.20, REQ_DS43.22, REQ_DS43.89, REQ_DS43.90, REQ_DS43.91</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D103" s="2" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
-      <x:c r="D103" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">4.4.1.8.71</x:t>
-        </x:is>
-      </x:c>
       <x:c r="E103" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.71.1</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="F103" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-UI-001, SYS-UI-002, SYS-UI-003</x:t>
+          <x:t xml:space="preserve">SYS-SEED-001, SYS-SEED-002, SYS-SEED-003, SYS-SEED-006</x:t>
         </x:is>
       </x:c>
       <x:c r="G103" s="2" t="inlineStr">
@@ -20556,32 +20714,32 @@
     <x:row r="104">
       <x:c r="A104" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.31.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.30.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B104" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should show results that need the user's attention in a shared prompt box, and short success messages as toasts.</x:t>
+          <x:t xml:space="preserve">System should create the test accounts of the SeedUsers setting with hashed passwords and company assignments.</x:t>
         </x:is>
       </x:c>
       <x:c r="C104" s="2" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">REQ_DS43.82, REQ_DS43.92, REQ_DS43.93</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D104" s="2" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
-      <x:c r="D104" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">4.4.1.8.71</x:t>
-        </x:is>
-      </x:c>
       <x:c r="E104" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.71.1</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="F104" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-UI-001</x:t>
+          <x:t xml:space="preserve">SYS-SEED-001, SYS-SEED-005</x:t>
         </x:is>
       </x:c>
       <x:c r="G104" s="2" t="inlineStr">
@@ -20593,32 +20751,32 @@
     <x:row r="105">
       <x:c r="A105" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.31.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.30.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B105" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should provide a shared selection window for choosing master data with search and server-side paging.</x:t>
+          <x:t xml:space="preserve">System should allow the seed to run repeatedly without duplicating or overwriting data.</x:t>
         </x:is>
       </x:c>
       <x:c r="C105" s="2" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">REQ_DS43.20, REQ_DS43.82, REQ_DS43.91</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D105" s="2" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
-      <x:c r="D105" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">4.4.1.8.72</x:t>
-        </x:is>
-      </x:c>
       <x:c r="E105" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.72.1, REQ_IO_A8.72.2</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="F105" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-UI-001</x:t>
+          <x:t xml:space="preserve">SYS-SEED-001, SYS-SEED-003, SYS-SEED-004</x:t>
         </x:is>
       </x:c>
       <x:c r="G105" s="2" t="inlineStr">
@@ -20630,12 +20788,12 @@
     <x:row r="106">
       <x:c r="A106" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.31.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.31.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B106" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should provide a standard list page template reused by every module.</x:t>
+          <x:t xml:space="preserve">System should ask for confirmation in a shared trilingual confirmation box before dangerous actions.</x:t>
         </x:is>
       </x:c>
       <x:c r="C106" s="2" t="inlineStr">
@@ -20645,17 +20803,17 @@
       </x:c>
       <x:c r="D106" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.73</x:t>
+          <x:t xml:space="preserve">4.4.1.8.71</x:t>
         </x:is>
       </x:c>
       <x:c r="E106" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.73.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.71.1</x:t>
         </x:is>
       </x:c>
       <x:c r="F106" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-UI-001, SYS-UI-002</x:t>
+          <x:t xml:space="preserve">SYS-UI-001, SYS-UI-002, SYS-UI-003</x:t>
         </x:is>
       </x:c>
       <x:c r="G106" s="2" t="inlineStr">
@@ -20667,12 +20825,12 @@
     <x:row r="107">
       <x:c r="A107" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.31.5</x:t>
+          <x:t xml:space="preserve">REQ_F4118.31.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B107" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should provide a standard document page template with status, previous / next navigation and unsaved-change protection.</x:t>
+          <x:t xml:space="preserve">System should show results that need the user's attention in a shared prompt box, and short success messages as toasts.</x:t>
         </x:is>
       </x:c>
       <x:c r="C107" s="2" t="inlineStr">
@@ -20682,12 +20840,12 @@
       </x:c>
       <x:c r="D107" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.74</x:t>
+          <x:t xml:space="preserve">4.4.1.8.71</x:t>
         </x:is>
       </x:c>
       <x:c r="E107" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.74.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.71.1</x:t>
         </x:is>
       </x:c>
       <x:c r="F107" s="2" t="inlineStr">
@@ -20704,12 +20862,12 @@
     <x:row r="108">
       <x:c r="A108" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.31.6</x:t>
+          <x:t xml:space="preserve">REQ_F4118.31.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B108" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should provide a date range filter with quick ranges and a document status tag following the macaron status colours.</x:t>
+          <x:t xml:space="preserve">System should provide a shared selection window for choosing master data with search and server-side paging.</x:t>
         </x:is>
       </x:c>
       <x:c r="C108" s="2" t="inlineStr">
@@ -20719,12 +20877,12 @@
       </x:c>
       <x:c r="D108" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.73, 4.4.1.8.74</x:t>
+          <x:t xml:space="preserve">4.4.1.8.72</x:t>
         </x:is>
       </x:c>
       <x:c r="E108" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.73.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.72.1, REQ_IO_A8.72.2</x:t>
         </x:is>
       </x:c>
       <x:c r="F108" s="2" t="inlineStr">
@@ -20741,123 +20899,123 @@
     <x:row r="109">
       <x:c r="A109" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.32.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.31.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B109" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to view IP whitelist rules.</x:t>
+          <x:t xml:space="preserve">System should provide a standard list page template reused by every module.</x:t>
         </x:is>
       </x:c>
       <x:c r="C109" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.102</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="D109" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.75</x:t>
+          <x:t xml:space="preserve">4.4.1.8.73</x:t>
         </x:is>
       </x:c>
       <x:c r="E109" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.75.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.73.2</x:t>
         </x:is>
       </x:c>
       <x:c r="F109" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-IPW-004, SYS-IPW-009</x:t>
+          <x:t xml:space="preserve">SYS-UI-001, SYS-UI-002</x:t>
         </x:is>
       </x:c>
       <x:c r="G109" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Covered</x:t>
+          <x:t xml:space="preserve">Partial</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="110">
       <x:c r="A110" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.32.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.31.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B110" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to create and deactivate IP whitelist rules.</x:t>
+          <x:t xml:space="preserve">System should provide a standard document page template with status, previous / next navigation and unsaved-change protection.</x:t>
         </x:is>
       </x:c>
       <x:c r="C110" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.102</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="D110" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.75</x:t>
+          <x:t xml:space="preserve">4.4.1.8.74</x:t>
         </x:is>
       </x:c>
       <x:c r="E110" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.75.2, REQ_IO_A8.75.3, REQ_IO_A8.75.5, REQ_IO_A8.75.6, REQ_IO_A8.75.7</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.74.1</x:t>
         </x:is>
       </x:c>
       <x:c r="F110" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-PERM-032, SYS-IPW-004, SYS-IPW-005, SYS-IPW-008, SYS-IPW-009</x:t>
+          <x:t xml:space="preserve">SYS-UI-001</x:t>
         </x:is>
       </x:c>
       <x:c r="G110" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Covered</x:t>
+          <x:t xml:space="preserve">Partial</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="111">
       <x:c r="A111" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.32.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.31.6</x:t>
         </x:is>
       </x:c>
       <x:c r="B111" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow single IPv4 or IPv6 addresses and CIDR networks in system, role or user scope.</x:t>
+          <x:t xml:space="preserve">System should provide a date range filter with quick ranges and a document status tag following the macaron status colours.</x:t>
         </x:is>
       </x:c>
       <x:c r="C111" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.102</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="D111" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.75</x:t>
+          <x:t xml:space="preserve">4.4.1.8.73, 4.4.1.8.74</x:t>
         </x:is>
       </x:c>
       <x:c r="E111" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.75.4</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.73.1</x:t>
         </x:is>
       </x:c>
       <x:c r="F111" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-IPW-001, SYS-IPW-002, SYS-IPW-005, SYS-IPW-006</x:t>
+          <x:t xml:space="preserve">SYS-UI-001</x:t>
         </x:is>
       </x:c>
       <x:c r="G111" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Covered</x:t>
+          <x:t xml:space="preserve">Partial</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="112">
       <x:c r="A112" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.32.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.32.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B112" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should reject disallowed requests and audit each rejection.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to view IP whitelist rules.</x:t>
         </x:is>
       </x:c>
       <x:c r="C112" s="2" t="inlineStr">
@@ -20867,76 +21025,76 @@
       </x:c>
       <x:c r="D112" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">4.4.1.8.75</x:t>
         </x:is>
       </x:c>
       <x:c r="E112" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.75.1</x:t>
         </x:is>
       </x:c>
       <x:c r="F112" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-IPW-003, SYS-IPW-006</x:t>
+          <x:t xml:space="preserve">SYS-IPW-004, SYS-IPW-009</x:t>
         </x:is>
       </x:c>
       <x:c r="G112" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="113">
       <x:c r="A113" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.32.5</x:t>
+          <x:t xml:space="preserve">REQ_F4118.32.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B113" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow operators to disable IP filtering through server configuration.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to create and deactivate IP whitelist rules.</x:t>
         </x:is>
       </x:c>
       <x:c r="C113" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_DS43.102</x:t>
         </x:is>
       </x:c>
       <x:c r="D113" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">4.4.1.8.75</x:t>
         </x:is>
       </x:c>
       <x:c r="E113" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.75.2, REQ_IO_A8.75.3, REQ_IO_A8.75.5, REQ_IO_A8.75.6, REQ_IO_A8.75.7</x:t>
         </x:is>
       </x:c>
       <x:c r="F113" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-IPW-006</x:t>
+          <x:t xml:space="preserve">SYS-PERM-032, SYS-IPW-004, SYS-IPW-005, SYS-IPW-008, SYS-IPW-009</x:t>
         </x:is>
       </x:c>
       <x:c r="G113" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="114">
       <x:c r="A114" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.32.6</x:t>
+          <x:t xml:space="preserve">REQ_F4118.32.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B114" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should provide a trilingual IP whitelist maintenance page.</x:t>
+          <x:t xml:space="preserve">System should allow single IPv4 or IPv6 addresses and CIDR networks in system, role or user scope.</x:t>
         </x:is>
       </x:c>
       <x:c r="C114" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_DS43.102</x:t>
         </x:is>
       </x:c>
       <x:c r="D114" s="2" t="inlineStr">
@@ -20946,34 +21104,34 @@
       </x:c>
       <x:c r="E114" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.75.1, REQ_IO_A8.75.2, REQ_IO_A8.75.3, REQ_IO_A8.75.4, REQ_IO_A8.75.5, REQ_IO_A8.75.6, REQ_IO_A8.75.7</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.75.4</x:t>
         </x:is>
       </x:c>
       <x:c r="F114" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-IPW-007</x:t>
+          <x:t xml:space="preserve">SYS-IPW-001, SYS-IPW-002, SYS-IPW-005, SYS-IPW-006</x:t>
         </x:is>
       </x:c>
       <x:c r="G114" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="115">
       <x:c r="A115" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.33.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.32.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B115" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable modules to publish notifications to a user.</x:t>
+          <x:t xml:space="preserve">System should reject disallowed requests and audit each rejection.</x:t>
         </x:is>
       </x:c>
       <x:c r="C115" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.104</x:t>
+          <x:t xml:space="preserve">REQ_DS43.102</x:t>
         </x:is>
       </x:c>
       <x:c r="D115" s="2" t="inlineStr">
@@ -20988,7 +21146,7 @@
       </x:c>
       <x:c r="F115" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-NOTIFY-001, SYS-NOTIFY-002, SYS-NOTIFY-003</x:t>
+          <x:t xml:space="preserve">SYS-IPW-003, SYS-IPW-006</x:t>
         </x:is>
       </x:c>
       <x:c r="G115" s="2" t="inlineStr">
@@ -21000,109 +21158,220 @@
     <x:row r="116">
       <x:c r="A116" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.33.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.32.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B116" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to view notifications.</x:t>
+          <x:t xml:space="preserve">System should allow operators to disable IP filtering through server configuration.</x:t>
         </x:is>
       </x:c>
       <x:c r="C116" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.104</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="D116" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.76</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="E116" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.76.1, REQ_IO_A8.76.2, REQ_IO_A8.76.3, REQ_IO_A8.76.6</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="F116" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-NOTIFY-004, SYS-NOTIFY-005, SYS-NOTIFY-006, SYS-NOTIFY-007</x:t>
+          <x:t xml:space="preserve">SYS-IPW-006</x:t>
         </x:is>
       </x:c>
       <x:c r="G116" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Covered</x:t>
+          <x:t xml:space="preserve">Partial</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="117">
       <x:c r="A117" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.33.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.32.6</x:t>
         </x:is>
       </x:c>
       <x:c r="B117" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to mark notifications as read.</x:t>
+          <x:t xml:space="preserve">System should provide a trilingual IP whitelist maintenance page.</x:t>
         </x:is>
       </x:c>
       <x:c r="C117" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.104</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="D117" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.76</x:t>
+          <x:t xml:space="preserve">4.4.1.8.75</x:t>
         </x:is>
       </x:c>
       <x:c r="E117" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.76.4, REQ_IO_A8.76.5</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.75.1, REQ_IO_A8.75.2, REQ_IO_A8.75.3, REQ_IO_A8.75.4, REQ_IO_A8.75.5, REQ_IO_A8.75.6, REQ_IO_A8.75.7</x:t>
         </x:is>
       </x:c>
       <x:c r="F117" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-NOTIFY-004, SYS-NOTIFY-005, SYS-NOTIFY-006, SYS-NOTIFY-007</x:t>
+          <x:t xml:space="preserve">SYS-IPW-007</x:t>
         </x:is>
       </x:c>
       <x:c r="G117" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Covered</x:t>
+          <x:t xml:space="preserve">Partial</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="118">
       <x:c r="A118" s="2" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">REQ_F4118.33.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B118" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should enable modules to publish notifications to a user.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C118" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.104</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D118" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="E118" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="F118" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-NOTIFY-001, SYS-NOTIFY-002, SYS-NOTIFY-003</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G118" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Partial</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="119">
+      <x:c r="A119" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.33.2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B119" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should enable user to view notifications.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C119" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.104</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D119" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.76</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E119" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.76.1, REQ_IO_A8.76.2, REQ_IO_A8.76.3, REQ_IO_A8.76.6</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F119" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-NOTIFY-004, SYS-NOTIFY-005, SYS-NOTIFY-006, SYS-NOTIFY-007</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G119" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Covered</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="120">
+      <x:c r="A120" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.33.3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B120" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should enable user to mark notifications as read.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C120" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.104</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D120" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.76</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E120" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.76.4, REQ_IO_A8.76.5</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F120" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-NOTIFY-004, SYS-NOTIFY-005, SYS-NOTIFY-006, SYS-NOTIFY-007</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G120" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Covered</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="121">
+      <x:c r="A121" s="2" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">REQ_F4118.34.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="B118" s="2" t="inlineStr">
+      <x:c r="B121" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">System should allow authorized users to view the master data portal.</x:t>
         </x:is>
       </x:c>
-      <x:c r="C118" s="2" t="inlineStr">
+      <x:c r="C121" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
-      <x:c r="D118" s="2" t="inlineStr">
+      <x:c r="D121" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
-      <x:c r="E118" s="2" t="inlineStr">
+      <x:c r="E121" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
-      <x:c r="F118" s="2" t="inlineStr">
+      <x:c r="F121" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
-      <x:c r="G118" s="2" t="inlineStr">
+      <x:c r="G121" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Not covered</x:t>
         </x:is>

--- a/docs/99-output/MyERP_Requirements.xlsx
+++ b/docs/99-output/MyERP_Requirements.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="1" r:id="R1bbaf91e656b4e8d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Non-Functional" sheetId="2" r:id="R4f3e80f853834aed"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Structure" sheetId="3" r:id="R417d27cee9814548"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interface" sheetId="4" r:id="R85de35af473f4270"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traceability Matrix" sheetId="5" r:id="Rdda1e9e4901a44a9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BlueWhale Parity" sheetId="6" r:id="Re323366eb6414bab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timeline" sheetId="7" r:id="R484c0405b65e4860"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Human Resources" sheetId="8" r:id="Rf78e353cb89c4068"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="9" r:id="R69dc4208c2c948de"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="1" r:id="R603da4a0fae5476d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Non-Functional" sheetId="2" r:id="Rdf2b37433cf04c47"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Structure" sheetId="3" r:id="R2dfe845f850c46b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interface" sheetId="4" r:id="R36b00d86e5a541d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traceability Matrix" sheetId="5" r:id="R01138b28362d45e5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BlueWhale Parity" sheetId="6" r:id="R45c45d59174d453b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timeline" sheetId="7" r:id="R5e59aba686a849d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Human Resources" sheetId="8" r:id="R5fa68518848e4db5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="9" r:id="R175b889a503c47c0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -8565,17 +8565,17 @@
     <x:row r="27">
       <x:c r="A27" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.30.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.11.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B27" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.30</x:t>
+          <x:t xml:space="preserve">4.4.1.8.11</x:t>
         </x:is>
       </x:c>
       <x:c r="C27" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Client Category View Interface</x:t>
+          <x:t xml:space="preserve">Item View Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D27" s="2" t="inlineStr">
@@ -8585,12 +8585,12 @@
       </x:c>
       <x:c r="E27" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">依代碼或名稱搜尋目前公司分類。</x:t>
+          <x:t xml:space="preserve">搜尋代碼、名稱或規格。</x:t>
         </x:is>
       </x:c>
       <x:c r="F27" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">縮小列表。</x:t>
+          <x:t xml:space="preserve">找到目前公司物料。</x:t>
         </x:is>
       </x:c>
       <x:c r="G27" s="2" t="inlineStr">
@@ -8605,7 +8605,7 @@
       </x:c>
       <x:c r="I27" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.30.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.11.2</x:t>
         </x:is>
       </x:c>
       <x:c r="J27" s="2" t="inlineStr">
@@ -8622,32 +8622,32 @@
     <x:row r="28">
       <x:c r="A28" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.30.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.11.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B28" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.30</x:t>
+          <x:t xml:space="preserve">4.4.1.8.11</x:t>
         </x:is>
       </x:c>
       <x:c r="C28" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Client Category View Interface</x:t>
+          <x:t xml:space="preserve">Item View Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D28" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Category List (Table)</x:t>
+          <x:t xml:space="preserve">Item List (Table)</x:t>
         </x:is>
       </x:c>
       <x:c r="E28" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">代碼、名稱、啟用狀態，代碼及名稱可排序，伺服器分頁。</x:t>
+          <x:t xml:space="preserve">代碼、名稱、規格、單位、品牌、分類、狀態；代碼與名稱可排序，伺服器分頁。</x:t>
         </x:is>
       </x:c>
       <x:c r="F28" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">檢視分類。</x:t>
+          <x:t xml:space="preserve">查看物料。</x:t>
         </x:is>
       </x:c>
       <x:c r="G28" s="2" t="inlineStr">
@@ -8662,7 +8662,7 @@
       </x:c>
       <x:c r="I28" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.31.1, REQ_IO_A8.32.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.12.1, REQ_IO_A8.13.1</x:t>
         </x:is>
       </x:c>
       <x:c r="J28" s="2" t="inlineStr">
@@ -8679,47 +8679,47 @@
     <x:row r="29">
       <x:c r="A29" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.30.3</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.12.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B29" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.30</x:t>
+          <x:t xml:space="preserve">4.4.1.8.12</x:t>
         </x:is>
       </x:c>
       <x:c r="C29" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Client Category View Interface</x:t>
+          <x:t xml:space="preserve">Item Create Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D29" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Delete (Button)</x:t>
+          <x:t xml:space="preserve">Code (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E29" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">二次確認後按版本軟刪除。</x:t>
+          <x:t xml:space="preserve">建立時轉大寫，公司內永久唯一。</x:t>
         </x:is>
       </x:c>
       <x:c r="F29" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">移除未使用的分類。</x:t>
+          <x:t xml:space="preserve">識別物料。</x:t>
         </x:is>
       </x:c>
       <x:c r="G29" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Button</x:t>
+          <x:t xml:space="preserve">Text</x:t>
         </x:is>
       </x:c>
       <x:c r="H29" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">DELETE 權限</x:t>
+          <x:t xml:space="preserve">1–30 位英數、-、_</x:t>
         </x:is>
       </x:c>
       <x:c r="I29" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.30.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.11.2</x:t>
         </x:is>
       </x:c>
       <x:c r="J29" s="2" t="inlineStr">
@@ -8736,32 +8736,32 @@
     <x:row r="30">
       <x:c r="A30" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.31.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.12.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B30" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.31</x:t>
+          <x:t xml:space="preserve">4.4.1.8.12</x:t>
         </x:is>
       </x:c>
       <x:c r="C30" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Client Category Create Interface</x:t>
+          <x:t xml:space="preserve">Item Create Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D30" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Code (Input)</x:t>
+          <x:t xml:space="preserve">Name (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E30" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">建立時填寫並轉大寫。</x:t>
+          <x:t xml:space="preserve">物料名稱。</x:t>
         </x:is>
       </x:c>
       <x:c r="F30" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">公司內唯一識別。</x:t>
+          <x:t xml:space="preserve">顯示物料。</x:t>
         </x:is>
       </x:c>
       <x:c r="G30" s="2" t="inlineStr">
@@ -8771,12 +8771,12 @@
       </x:c>
       <x:c r="H30" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1–30 位英數、-、_</x:t>
+          <x:t xml:space="preserve">非空白，最多 200 字</x:t>
         </x:is>
       </x:c>
       <x:c r="I30" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.30.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.11.2</x:t>
         </x:is>
       </x:c>
       <x:c r="J30" s="2" t="inlineStr">
@@ -8793,32 +8793,32 @@
     <x:row r="31">
       <x:c r="A31" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.31.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.12.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B31" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.31</x:t>
+          <x:t xml:space="preserve">4.4.1.8.12</x:t>
         </x:is>
       </x:c>
       <x:c r="C31" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Client Category Create Interface</x:t>
+          <x:t xml:space="preserve">Item Create Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D31" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Name (Input)</x:t>
+          <x:t xml:space="preserve">Specification (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E31" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">分類名稱。</x:t>
+          <x:t xml:space="preserve">可空規格，去除前後空白。</x:t>
         </x:is>
       </x:c>
       <x:c r="F31" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">向用戶顯示。</x:t>
+          <x:t xml:space="preserve">區分型號。</x:t>
         </x:is>
       </x:c>
       <x:c r="G31" s="2" t="inlineStr">
@@ -8828,12 +8828,12 @@
       </x:c>
       <x:c r="H31" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">非空白，最多 200 字</x:t>
+          <x:t xml:space="preserve">最多 500 字</x:t>
         </x:is>
       </x:c>
       <x:c r="I31" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.30.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.11.2</x:t>
         </x:is>
       </x:c>
       <x:c r="J31" s="2" t="inlineStr">
@@ -8850,47 +8850,47 @@
     <x:row r="32">
       <x:c r="A32" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.32.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.12.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B32" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.32</x:t>
+          <x:t xml:space="preserve">4.4.1.8.12</x:t>
         </x:is>
       </x:c>
       <x:c r="C32" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Client Category Edit Interface</x:t>
+          <x:t xml:space="preserve">Item Create Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D32" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Code (Label)</x:t>
+          <x:t xml:space="preserve">Base Unit (Dropdown)</x:t>
         </x:is>
       </x:c>
       <x:c r="E32" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">編輯時只讀。</x:t>
+          <x:t xml:space="preserve">必選本公司啟用單位。</x:t>
         </x:is>
       </x:c>
       <x:c r="F32" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">防止歷史引用變更識別。</x:t>
+          <x:t xml:space="preserve">設定基本計量單位。</x:t>
         </x:is>
       </x:c>
       <x:c r="G32" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Text</x:t>
+          <x:t xml:space="preserve">Unit ID</x:t>
         </x:is>
       </x:c>
       <x:c r="H32" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">最多 30 字</x:t>
+          <x:t xml:space="preserve">MD.UOM.VIEW 可見的啟用單位</x:t>
         </x:is>
       </x:c>
       <x:c r="I32" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.30.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.11.2</x:t>
         </x:is>
       </x:c>
       <x:c r="J32" s="2" t="inlineStr">
@@ -8907,47 +8907,47 @@
     <x:row r="33">
       <x:c r="A33" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.32.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.12.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B33" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.32</x:t>
+          <x:t xml:space="preserve">4.4.1.8.12</x:t>
         </x:is>
       </x:c>
       <x:c r="C33" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Client Category Edit Interface</x:t>
+          <x:t xml:space="preserve">Item Create Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D33" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Name (Input)</x:t>
+          <x:t xml:space="preserve">Brand (Dropdown)</x:t>
         </x:is>
       </x:c>
       <x:c r="E33" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">編輯分類名稱。</x:t>
+          <x:t xml:space="preserve">可空品牌。</x:t>
         </x:is>
       </x:c>
       <x:c r="F33" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">更新顯示名稱。</x:t>
+          <x:t xml:space="preserve">分類品牌。</x:t>
         </x:is>
       </x:c>
       <x:c r="G33" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Text</x:t>
+          <x:t xml:space="preserve">Brand ID</x:t>
         </x:is>
       </x:c>
       <x:c r="H33" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">非空白，最多 200 字</x:t>
+          <x:t xml:space="preserve">MD.ITEM_BRAND.VIEW 可見的啟用品牌</x:t>
         </x:is>
       </x:c>
       <x:c r="I33" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.30.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.11.2</x:t>
         </x:is>
       </x:c>
       <x:c r="J33" s="2" t="inlineStr">
@@ -8964,47 +8964,47 @@
     <x:row r="34">
       <x:c r="A34" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.32.3</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.12.6</x:t>
         </x:is>
       </x:c>
       <x:c r="B34" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.32</x:t>
+          <x:t xml:space="preserve">4.4.1.8.12</x:t>
         </x:is>
       </x:c>
       <x:c r="C34" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Client Category Edit Interface</x:t>
+          <x:t xml:space="preserve">Item Create Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D34" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Active (Checkbox)</x:t>
+          <x:t xml:space="preserve">Category (Dropdown)</x:t>
         </x:is>
       </x:c>
       <x:c r="E34" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">控制是否可用於新客戶。</x:t>
+          <x:t xml:space="preserve">可空的階層分類，按樹縮排。</x:t>
         </x:is>
       </x:c>
       <x:c r="F34" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">保留歷史並停用。</x:t>
+          <x:t xml:space="preserve">分類物料。</x:t>
         </x:is>
       </x:c>
       <x:c r="G34" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Boolean</x:t>
+          <x:t xml:space="preserve">Category ID</x:t>
         </x:is>
       </x:c>
       <x:c r="H34" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">true／false</x:t>
+          <x:t xml:space="preserve">MD.ITEM_CATEGORY.VIEW 可見的啟用分類</x:t>
         </x:is>
       </x:c>
       <x:c r="I34" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.30.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.11.2</x:t>
         </x:is>
       </x:c>
       <x:c r="J34" s="2" t="inlineStr">
@@ -9021,32 +9021,32 @@
     <x:row r="35">
       <x:c r="A35" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.33.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.13.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B35" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.33</x:t>
+          <x:t xml:space="preserve">4.4.1.8.13</x:t>
         </x:is>
       </x:c>
       <x:c r="C35" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Supplier Category View Interface</x:t>
+          <x:t xml:space="preserve">Item Edit Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D35" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Search (Input)</x:t>
+          <x:t xml:space="preserve">Code (Label)</x:t>
         </x:is>
       </x:c>
       <x:c r="E35" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">依代碼或名稱搜尋目前公司分類。</x:t>
+          <x:t xml:space="preserve">編輯時不可修改。</x:t>
         </x:is>
       </x:c>
       <x:c r="F35" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">縮小列表。</x:t>
+          <x:t xml:space="preserve">保留既有識別。</x:t>
         </x:is>
       </x:c>
       <x:c r="G35" s="2" t="inlineStr">
@@ -9056,12 +9056,12 @@
       </x:c>
       <x:c r="H35" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">任意文字</x:t>
+          <x:t xml:space="preserve">最多 30 字</x:t>
         </x:is>
       </x:c>
       <x:c r="I35" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.33.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.11.2</x:t>
         </x:is>
       </x:c>
       <x:c r="J35" s="2" t="inlineStr">
@@ -9078,47 +9078,47 @@
     <x:row r="36">
       <x:c r="A36" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.33.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.13.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B36" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.33</x:t>
+          <x:t xml:space="preserve">4.4.1.8.13</x:t>
         </x:is>
       </x:c>
       <x:c r="C36" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Supplier Category View Interface</x:t>
+          <x:t xml:space="preserve">Item Edit Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D36" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Category List (Table)</x:t>
+          <x:t xml:space="preserve">Name / Specification / References (Form)</x:t>
         </x:is>
       </x:c>
       <x:c r="E36" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">代碼、名稱、啟用狀態，代碼及名稱可排序，伺服器分頁。</x:t>
+          <x:t xml:space="preserve">編輯名稱、規格、單位、品牌、分類；原參照已停用仍可保留。</x:t>
         </x:is>
       </x:c>
       <x:c r="F36" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">檢視分類。</x:t>
+          <x:t xml:space="preserve">維護物料。</x:t>
         </x:is>
       </x:c>
       <x:c r="G36" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Table</x:t>
+          <x:t xml:space="preserve">Text／IDs</x:t>
         </x:is>
       </x:c>
       <x:c r="H36" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">每頁 10／20／50／100／200</x:t>
+          <x:t xml:space="preserve">同建立；帶 version</x:t>
         </x:is>
       </x:c>
       <x:c r="I36" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.34.1, REQ_IO_A8.35.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.11.2</x:t>
         </x:is>
       </x:c>
       <x:c r="J36" s="2" t="inlineStr">
@@ -9135,47 +9135,47 @@
     <x:row r="37">
       <x:c r="A37" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.33.3</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.13.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B37" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.33</x:t>
+          <x:t xml:space="preserve">4.4.1.8.13</x:t>
         </x:is>
       </x:c>
       <x:c r="C37" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Supplier Category View Interface</x:t>
+          <x:t xml:space="preserve">Item Edit Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D37" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Delete (Button)</x:t>
+          <x:t xml:space="preserve">Active (Checkbox)</x:t>
         </x:is>
       </x:c>
       <x:c r="E37" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">二次確認後按版本軟刪除；被引用時顯示錯誤。</x:t>
+          <x:t xml:space="preserve">啟用或停用物料。</x:t>
         </x:is>
       </x:c>
       <x:c r="F37" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">移除未使用的分類。</x:t>
+          <x:t xml:space="preserve">控制可用狀態。</x:t>
         </x:is>
       </x:c>
       <x:c r="G37" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Button</x:t>
+          <x:t xml:space="preserve">Boolean</x:t>
         </x:is>
       </x:c>
       <x:c r="H37" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">DELETE 權限</x:t>
+          <x:t xml:space="preserve">true／false</x:t>
         </x:is>
       </x:c>
       <x:c r="I37" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.33.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.11.2</x:t>
         </x:is>
       </x:c>
       <x:c r="J37" s="2" t="inlineStr">
@@ -9192,32 +9192,32 @@
     <x:row r="38">
       <x:c r="A38" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.34.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.30.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B38" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.34</x:t>
+          <x:t xml:space="preserve">4.4.1.8.30</x:t>
         </x:is>
       </x:c>
       <x:c r="C38" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Supplier Category Create Interface</x:t>
+          <x:t xml:space="preserve">Client Category View Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D38" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Code (Input)</x:t>
+          <x:t xml:space="preserve">Search (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E38" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">建立時填寫並轉大寫。</x:t>
+          <x:t xml:space="preserve">依代碼或名稱搜尋目前公司分類。</x:t>
         </x:is>
       </x:c>
       <x:c r="F38" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">公司內唯一識別。</x:t>
+          <x:t xml:space="preserve">縮小列表。</x:t>
         </x:is>
       </x:c>
       <x:c r="G38" s="2" t="inlineStr">
@@ -9227,12 +9227,12 @@
       </x:c>
       <x:c r="H38" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1–30 位英數、-、_</x:t>
+          <x:t xml:space="preserve">任意文字</x:t>
         </x:is>
       </x:c>
       <x:c r="I38" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.33.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.30.2</x:t>
         </x:is>
       </x:c>
       <x:c r="J38" s="2" t="inlineStr">
@@ -9249,47 +9249,47 @@
     <x:row r="39">
       <x:c r="A39" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.34.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.30.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B39" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.34</x:t>
+          <x:t xml:space="preserve">4.4.1.8.30</x:t>
         </x:is>
       </x:c>
       <x:c r="C39" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Supplier Category Create Interface</x:t>
+          <x:t xml:space="preserve">Client Category View Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D39" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Name (Input)</x:t>
+          <x:t xml:space="preserve">Category List (Table)</x:t>
         </x:is>
       </x:c>
       <x:c r="E39" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">分類名稱。</x:t>
+          <x:t xml:space="preserve">代碼、名稱、啟用狀態，代碼及名稱可排序，伺服器分頁。</x:t>
         </x:is>
       </x:c>
       <x:c r="F39" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">向用戶顯示。</x:t>
+          <x:t xml:space="preserve">檢視分類。</x:t>
         </x:is>
       </x:c>
       <x:c r="G39" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Text</x:t>
+          <x:t xml:space="preserve">Table</x:t>
         </x:is>
       </x:c>
       <x:c r="H39" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">非空白，最多 200 字</x:t>
+          <x:t xml:space="preserve">每頁 10／20／50／100／200</x:t>
         </x:is>
       </x:c>
       <x:c r="I39" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.33.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.31.1, REQ_IO_A8.32.1</x:t>
         </x:is>
       </x:c>
       <x:c r="J39" s="2" t="inlineStr">
@@ -9306,47 +9306,47 @@
     <x:row r="40">
       <x:c r="A40" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.35.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.30.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B40" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.35</x:t>
+          <x:t xml:space="preserve">4.4.1.8.30</x:t>
         </x:is>
       </x:c>
       <x:c r="C40" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Supplier Category Edit Interface</x:t>
+          <x:t xml:space="preserve">Client Category View Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D40" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Code (Label)</x:t>
+          <x:t xml:space="preserve">Delete (Button)</x:t>
         </x:is>
       </x:c>
       <x:c r="E40" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">編輯時只讀。</x:t>
+          <x:t xml:space="preserve">二次確認後按版本軟刪除。</x:t>
         </x:is>
       </x:c>
       <x:c r="F40" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">防止歷史引用變更識別。</x:t>
+          <x:t xml:space="preserve">移除未使用的分類。</x:t>
         </x:is>
       </x:c>
       <x:c r="G40" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Text</x:t>
+          <x:t xml:space="preserve">Button</x:t>
         </x:is>
       </x:c>
       <x:c r="H40" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">最多 30 字</x:t>
+          <x:t xml:space="preserve">DELETE 權限</x:t>
         </x:is>
       </x:c>
       <x:c r="I40" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.33.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.30.2</x:t>
         </x:is>
       </x:c>
       <x:c r="J40" s="2" t="inlineStr">
@@ -9363,32 +9363,32 @@
     <x:row r="41">
       <x:c r="A41" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.35.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.31.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B41" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.35</x:t>
+          <x:t xml:space="preserve">4.4.1.8.31</x:t>
         </x:is>
       </x:c>
       <x:c r="C41" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Supplier Category Edit Interface</x:t>
+          <x:t xml:space="preserve">Client Category Create Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D41" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Name (Input)</x:t>
+          <x:t xml:space="preserve">Code (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E41" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">編輯分類名稱。</x:t>
+          <x:t xml:space="preserve">建立時填寫並轉大寫。</x:t>
         </x:is>
       </x:c>
       <x:c r="F41" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">更新顯示名稱。</x:t>
+          <x:t xml:space="preserve">公司內唯一識別。</x:t>
         </x:is>
       </x:c>
       <x:c r="G41" s="2" t="inlineStr">
@@ -9398,12 +9398,12 @@
       </x:c>
       <x:c r="H41" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">非空白，最多 200 字</x:t>
+          <x:t xml:space="preserve">1–30 位英數、-、_</x:t>
         </x:is>
       </x:c>
       <x:c r="I41" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.33.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.30.2</x:t>
         </x:is>
       </x:c>
       <x:c r="J41" s="2" t="inlineStr">
@@ -9420,47 +9420,47 @@
     <x:row r="42">
       <x:c r="A42" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.35.3</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.31.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B42" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.35</x:t>
+          <x:t xml:space="preserve">4.4.1.8.31</x:t>
         </x:is>
       </x:c>
       <x:c r="C42" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Supplier Category Edit Interface</x:t>
+          <x:t xml:space="preserve">Client Category Create Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D42" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Active (Checkbox)</x:t>
+          <x:t xml:space="preserve">Name (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E42" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">控制是否可用於新供應商。</x:t>
+          <x:t xml:space="preserve">分類名稱。</x:t>
         </x:is>
       </x:c>
       <x:c r="F42" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">保留歷史並停用。</x:t>
+          <x:t xml:space="preserve">向用戶顯示。</x:t>
         </x:is>
       </x:c>
       <x:c r="G42" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Boolean</x:t>
+          <x:t xml:space="preserve">Text</x:t>
         </x:is>
       </x:c>
       <x:c r="H42" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">true／false</x:t>
+          <x:t xml:space="preserve">非空白，最多 200 字</x:t>
         </x:is>
       </x:c>
       <x:c r="I42" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.33.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.30.2</x:t>
         </x:is>
       </x:c>
       <x:c r="J42" s="2" t="inlineStr">
@@ -9477,32 +9477,32 @@
     <x:row r="43">
       <x:c r="A43" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.36.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.32.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B43" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.36</x:t>
+          <x:t xml:space="preserve">4.4.1.8.32</x:t>
         </x:is>
       </x:c>
       <x:c r="C43" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Item Category View Interface</x:t>
+          <x:t xml:space="preserve">Client Category Edit Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D43" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Search (Input)</x:t>
+          <x:t xml:space="preserve">Code (Label)</x:t>
         </x:is>
       </x:c>
       <x:c r="E43" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">依代碼或名稱過濾分類樹，保留命中節點的上層。</x:t>
+          <x:t xml:space="preserve">編輯時只讀。</x:t>
         </x:is>
       </x:c>
       <x:c r="F43" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">找到分類。</x:t>
+          <x:t xml:space="preserve">防止歷史引用變更識別。</x:t>
         </x:is>
       </x:c>
       <x:c r="G43" s="2" t="inlineStr">
@@ -9512,12 +9512,12 @@
       </x:c>
       <x:c r="H43" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">任意文字</x:t>
+          <x:t xml:space="preserve">最多 30 字</x:t>
         </x:is>
       </x:c>
       <x:c r="I43" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.36.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.30.2</x:t>
         </x:is>
       </x:c>
       <x:c r="J43" s="2" t="inlineStr">
@@ -9534,47 +9534,47 @@
     <x:row r="44">
       <x:c r="A44" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.36.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.32.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B44" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.36</x:t>
+          <x:t xml:space="preserve">4.4.1.8.32</x:t>
         </x:is>
       </x:c>
       <x:c r="C44" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Item Category View Interface</x:t>
+          <x:t xml:space="preserve">Client Category Edit Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D44" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Category Tree (Table)</x:t>
+          <x:t xml:space="preserve">Name (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E44" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">代碼（按層級縮排）、名稱、狀態及新增子分類／編輯／刪除操作。</x:t>
+          <x:t xml:space="preserve">編輯分類名稱。</x:t>
         </x:is>
       </x:c>
       <x:c r="F44" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">檢視分類階層。</x:t>
+          <x:t xml:space="preserve">更新顯示名稱。</x:t>
         </x:is>
       </x:c>
       <x:c r="G44" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Table</x:t>
+          <x:t xml:space="preserve">Text</x:t>
         </x:is>
       </x:c>
       <x:c r="H44" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">全部未刪除分類，最多 5 層</x:t>
+          <x:t xml:space="preserve">非空白，最多 200 字</x:t>
         </x:is>
       </x:c>
       <x:c r="I44" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.37.1, REQ_IO_A8.38.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.30.2</x:t>
         </x:is>
       </x:c>
       <x:c r="J44" s="2" t="inlineStr">
@@ -9591,47 +9591,47 @@
     <x:row r="45">
       <x:c r="A45" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.36.3</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.32.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B45" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.36</x:t>
+          <x:t xml:space="preserve">4.4.1.8.32</x:t>
         </x:is>
       </x:c>
       <x:c r="C45" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Item Category View Interface</x:t>
+          <x:t xml:space="preserve">Client Category Edit Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D45" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Delete (Button)</x:t>
+          <x:t xml:space="preserve">Active (Checkbox)</x:t>
         </x:is>
       </x:c>
       <x:c r="E45" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">二次確認後按版本軟刪除；有子分類時顯示錯誤。</x:t>
+          <x:t xml:space="preserve">控制是否可用於新客戶。</x:t>
         </x:is>
       </x:c>
       <x:c r="F45" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">移除未使用的分類。</x:t>
+          <x:t xml:space="preserve">保留歷史並停用。</x:t>
         </x:is>
       </x:c>
       <x:c r="G45" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Button</x:t>
+          <x:t xml:space="preserve">Boolean</x:t>
         </x:is>
       </x:c>
       <x:c r="H45" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">DELETE 權限</x:t>
+          <x:t xml:space="preserve">true／false</x:t>
         </x:is>
       </x:c>
       <x:c r="I45" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.36.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.30.2</x:t>
         </x:is>
       </x:c>
       <x:c r="J45" s="2" t="inlineStr">
@@ -9648,32 +9648,32 @@
     <x:row r="46">
       <x:c r="A46" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.37.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.33.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B46" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.37</x:t>
+          <x:t xml:space="preserve">4.4.1.8.33</x:t>
         </x:is>
       </x:c>
       <x:c r="C46" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Item Category Create Interface</x:t>
+          <x:t xml:space="preserve">Supplier Category View Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D46" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Code (Input)</x:t>
+          <x:t xml:space="preserve">Search (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E46" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">建立時填寫並轉大寫。</x:t>
+          <x:t xml:space="preserve">依代碼或名稱搜尋目前公司分類。</x:t>
         </x:is>
       </x:c>
       <x:c r="F46" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">公司內唯一識別。</x:t>
+          <x:t xml:space="preserve">縮小列表。</x:t>
         </x:is>
       </x:c>
       <x:c r="G46" s="2" t="inlineStr">
@@ -9683,12 +9683,12 @@
       </x:c>
       <x:c r="H46" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1–30 位英數、-、_</x:t>
+          <x:t xml:space="preserve">任意文字</x:t>
         </x:is>
       </x:c>
       <x:c r="I46" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.36.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.33.2</x:t>
         </x:is>
       </x:c>
       <x:c r="J46" s="2" t="inlineStr">
@@ -9705,47 +9705,47 @@
     <x:row r="47">
       <x:c r="A47" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.37.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.33.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B47" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.37</x:t>
+          <x:t xml:space="preserve">4.4.1.8.33</x:t>
         </x:is>
       </x:c>
       <x:c r="C47" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Item Category Create Interface</x:t>
+          <x:t xml:space="preserve">Supplier Category View Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D47" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Name (Input)</x:t>
+          <x:t xml:space="preserve">Category List (Table)</x:t>
         </x:is>
       </x:c>
       <x:c r="E47" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">分類名稱。</x:t>
+          <x:t xml:space="preserve">代碼、名稱、啟用狀態，代碼及名稱可排序，伺服器分頁。</x:t>
         </x:is>
       </x:c>
       <x:c r="F47" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">向用戶顯示。</x:t>
+          <x:t xml:space="preserve">檢視分類。</x:t>
         </x:is>
       </x:c>
       <x:c r="G47" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Text</x:t>
+          <x:t xml:space="preserve">Table</x:t>
         </x:is>
       </x:c>
       <x:c r="H47" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">非空白，最多 200 字</x:t>
+          <x:t xml:space="preserve">每頁 10／20／50／100／200</x:t>
         </x:is>
       </x:c>
       <x:c r="I47" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.36.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.34.1, REQ_IO_A8.35.1</x:t>
         </x:is>
       </x:c>
       <x:c r="J47" s="2" t="inlineStr">
@@ -9762,47 +9762,47 @@
     <x:row r="48">
       <x:c r="A48" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.37.3</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.33.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B48" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.37</x:t>
+          <x:t xml:space="preserve">4.4.1.8.33</x:t>
         </x:is>
       </x:c>
       <x:c r="C48" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Item Category Create Interface</x:t>
+          <x:t xml:space="preserve">Supplier Category View Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D48" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Parent (Dropdown)</x:t>
+          <x:t xml:space="preserve">Delete (Button)</x:t>
         </x:is>
       </x:c>
       <x:c r="E48" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">上層分類，可不選（最上層）；選項按層級縮排。</x:t>
+          <x:t xml:space="preserve">二次確認後按版本軟刪除；被引用時顯示錯誤。</x:t>
         </x:is>
       </x:c>
       <x:c r="F48" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">決定分類位置。</x:t>
+          <x:t xml:space="preserve">移除未使用的分類。</x:t>
         </x:is>
       </x:c>
       <x:c r="G48" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Category ID</x:t>
+          <x:t xml:space="preserve">Button</x:t>
         </x:is>
       </x:c>
       <x:c r="H48" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">本公司啟用分類，新節點不超過第 5 層</x:t>
+          <x:t xml:space="preserve">DELETE 權限</x:t>
         </x:is>
       </x:c>
       <x:c r="I48" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.36.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.33.2</x:t>
         </x:is>
       </x:c>
       <x:c r="J48" s="2" t="inlineStr">
@@ -9819,32 +9819,32 @@
     <x:row r="49">
       <x:c r="A49" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.38.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.34.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B49" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.38</x:t>
+          <x:t xml:space="preserve">4.4.1.8.34</x:t>
         </x:is>
       </x:c>
       <x:c r="C49" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Item Category Edit Interface</x:t>
+          <x:t xml:space="preserve">Supplier Category Create Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D49" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Code (Label)</x:t>
+          <x:t xml:space="preserve">Code (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E49" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">編輯時只讀。</x:t>
+          <x:t xml:space="preserve">建立時填寫並轉大寫。</x:t>
         </x:is>
       </x:c>
       <x:c r="F49" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">防止歷史引用變更識別。</x:t>
+          <x:t xml:space="preserve">公司內唯一識別。</x:t>
         </x:is>
       </x:c>
       <x:c r="G49" s="2" t="inlineStr">
@@ -9854,12 +9854,12 @@
       </x:c>
       <x:c r="H49" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">最多 30 字</x:t>
+          <x:t xml:space="preserve">1–30 位英數、-、_</x:t>
         </x:is>
       </x:c>
       <x:c r="I49" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.36.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.33.2</x:t>
         </x:is>
       </x:c>
       <x:c r="J49" s="2" t="inlineStr">
@@ -9876,47 +9876,47 @@
     <x:row r="50">
       <x:c r="A50" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.38.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.34.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B50" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.38</x:t>
+          <x:t xml:space="preserve">4.4.1.8.34</x:t>
         </x:is>
       </x:c>
       <x:c r="C50" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Item Category Edit Interface</x:t>
+          <x:t xml:space="preserve">Supplier Category Create Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D50" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Name / Active</x:t>
+          <x:t xml:space="preserve">Name (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E50" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">修改名稱與啟用狀態。</x:t>
+          <x:t xml:space="preserve">分類名稱。</x:t>
         </x:is>
       </x:c>
       <x:c r="F50" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">維護分類。</x:t>
+          <x:t xml:space="preserve">向用戶顯示。</x:t>
         </x:is>
       </x:c>
       <x:c r="G50" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Text／Boolean</x:t>
+          <x:t xml:space="preserve">Text</x:t>
         </x:is>
       </x:c>
       <x:c r="H50" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">同建立</x:t>
+          <x:t xml:space="preserve">非空白，最多 200 字</x:t>
         </x:is>
       </x:c>
       <x:c r="I50" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.36.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.33.2</x:t>
         </x:is>
       </x:c>
       <x:c r="J50" s="2" t="inlineStr">
@@ -9933,47 +9933,47 @@
     <x:row r="51">
       <x:c r="A51" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.38.3</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.35.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B51" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.38</x:t>
+          <x:t xml:space="preserve">4.4.1.8.35</x:t>
         </x:is>
       </x:c>
       <x:c r="C51" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Item Category Edit Interface</x:t>
+          <x:t xml:space="preserve">Supplier Category Edit Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D51" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Parent (Dropdown)</x:t>
+          <x:t xml:space="preserve">Code (Label)</x:t>
         </x:is>
       </x:c>
       <x:c r="E51" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">搬移整棵子樹；排除自己與子孫。</x:t>
+          <x:t xml:space="preserve">編輯時只讀。</x:t>
         </x:is>
       </x:c>
       <x:c r="F51" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">調整階層。</x:t>
+          <x:t xml:space="preserve">防止歷史引用變更識別。</x:t>
         </x:is>
       </x:c>
       <x:c r="G51" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Category ID</x:t>
+          <x:t xml:space="preserve">Text</x:t>
         </x:is>
       </x:c>
       <x:c r="H51" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">啟用分類或目前上層，搬移後不超過 5 層</x:t>
+          <x:t xml:space="preserve">最多 30 字</x:t>
         </x:is>
       </x:c>
       <x:c r="I51" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.36.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.33.2</x:t>
         </x:is>
       </x:c>
       <x:c r="J51" s="2" t="inlineStr">
@@ -9990,32 +9990,32 @@
     <x:row r="52">
       <x:c r="A52" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.39.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.35.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B52" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.39</x:t>
+          <x:t xml:space="preserve">4.4.1.8.35</x:t>
         </x:is>
       </x:c>
       <x:c r="C52" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Item Brand View Interface</x:t>
+          <x:t xml:space="preserve">Supplier Category Edit Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D52" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Search (Input)</x:t>
+          <x:t xml:space="preserve">Name (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E52" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">依代碼或名稱搜尋目前公司品牌。</x:t>
+          <x:t xml:space="preserve">編輯分類名稱。</x:t>
         </x:is>
       </x:c>
       <x:c r="F52" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">縮小列表。</x:t>
+          <x:t xml:space="preserve">更新顯示名稱。</x:t>
         </x:is>
       </x:c>
       <x:c r="G52" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </x:c>
       <x:c r="H52" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">任意文字</x:t>
+          <x:t xml:space="preserve">非空白，最多 200 字</x:t>
         </x:is>
       </x:c>
       <x:c r="I52" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.39.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.33.2</x:t>
         </x:is>
       </x:c>
       <x:c r="J52" s="2" t="inlineStr">
@@ -10047,47 +10047,47 @@
     <x:row r="53">
       <x:c r="A53" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.39.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.35.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B53" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.39</x:t>
+          <x:t xml:space="preserve">4.4.1.8.35</x:t>
         </x:is>
       </x:c>
       <x:c r="C53" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Item Brand View Interface</x:t>
+          <x:t xml:space="preserve">Supplier Category Edit Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D53" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Brand List (Table)</x:t>
+          <x:t xml:space="preserve">Active (Checkbox)</x:t>
         </x:is>
       </x:c>
       <x:c r="E53" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">代碼、名稱、啟用狀態，代碼及名稱可排序，伺服器分頁。</x:t>
+          <x:t xml:space="preserve">控制是否可用於新供應商。</x:t>
         </x:is>
       </x:c>
       <x:c r="F53" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">檢視品牌。</x:t>
+          <x:t xml:space="preserve">保留歷史並停用。</x:t>
         </x:is>
       </x:c>
       <x:c r="G53" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Table</x:t>
+          <x:t xml:space="preserve">Boolean</x:t>
         </x:is>
       </x:c>
       <x:c r="H53" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">每頁 10／20／50／100／200</x:t>
+          <x:t xml:space="preserve">true／false</x:t>
         </x:is>
       </x:c>
       <x:c r="I53" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.40.1, REQ_IO_A8.41.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.33.2</x:t>
         </x:is>
       </x:c>
       <x:c r="J53" s="2" t="inlineStr">
@@ -10104,47 +10104,47 @@
     <x:row r="54">
       <x:c r="A54" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.39.3</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.36.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B54" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.39</x:t>
+          <x:t xml:space="preserve">4.4.1.8.36</x:t>
         </x:is>
       </x:c>
       <x:c r="C54" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Item Brand View Interface</x:t>
+          <x:t xml:space="preserve">Item Category View Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D54" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Delete (Button)</x:t>
+          <x:t xml:space="preserve">Search (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E54" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">二次確認後按版本軟刪除。</x:t>
+          <x:t xml:space="preserve">依代碼或名稱過濾分類樹，保留命中節點的上層。</x:t>
         </x:is>
       </x:c>
       <x:c r="F54" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">移除未使用的品牌。</x:t>
+          <x:t xml:space="preserve">找到分類。</x:t>
         </x:is>
       </x:c>
       <x:c r="G54" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Button</x:t>
+          <x:t xml:space="preserve">Text</x:t>
         </x:is>
       </x:c>
       <x:c r="H54" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">DELETE 權限</x:t>
+          <x:t xml:space="preserve">任意文字</x:t>
         </x:is>
       </x:c>
       <x:c r="I54" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.39.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.36.2</x:t>
         </x:is>
       </x:c>
       <x:c r="J54" s="2" t="inlineStr">
@@ -10161,47 +10161,47 @@
     <x:row r="55">
       <x:c r="A55" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.40.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.36.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B55" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.40</x:t>
+          <x:t xml:space="preserve">4.4.1.8.36</x:t>
         </x:is>
       </x:c>
       <x:c r="C55" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Item Brand Create Interface</x:t>
+          <x:t xml:space="preserve">Item Category View Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D55" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Code (Input)</x:t>
+          <x:t xml:space="preserve">Category Tree (Table)</x:t>
         </x:is>
       </x:c>
       <x:c r="E55" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">建立時填寫並轉大寫。</x:t>
+          <x:t xml:space="preserve">代碼（按層級縮排）、名稱、狀態及新增子分類／編輯／刪除操作。</x:t>
         </x:is>
       </x:c>
       <x:c r="F55" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">公司內唯一識別。</x:t>
+          <x:t xml:space="preserve">檢視分類階層。</x:t>
         </x:is>
       </x:c>
       <x:c r="G55" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Text</x:t>
+          <x:t xml:space="preserve">Table</x:t>
         </x:is>
       </x:c>
       <x:c r="H55" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1–30 位英數、-、_</x:t>
+          <x:t xml:space="preserve">全部未刪除分類，最多 5 層</x:t>
         </x:is>
       </x:c>
       <x:c r="I55" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.39.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.37.1, REQ_IO_A8.38.1</x:t>
         </x:is>
       </x:c>
       <x:c r="J55" s="2" t="inlineStr">
@@ -10218,47 +10218,47 @@
     <x:row r="56">
       <x:c r="A56" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.40.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.36.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B56" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.40</x:t>
+          <x:t xml:space="preserve">4.4.1.8.36</x:t>
         </x:is>
       </x:c>
       <x:c r="C56" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Item Brand Create Interface</x:t>
+          <x:t xml:space="preserve">Item Category View Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D56" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Name (Input)</x:t>
+          <x:t xml:space="preserve">Delete (Button)</x:t>
         </x:is>
       </x:c>
       <x:c r="E56" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">品牌名稱。</x:t>
+          <x:t xml:space="preserve">二次確認後按版本軟刪除；有子分類時顯示錯誤。</x:t>
         </x:is>
       </x:c>
       <x:c r="F56" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">向用戶顯示。</x:t>
+          <x:t xml:space="preserve">移除未使用的分類。</x:t>
         </x:is>
       </x:c>
       <x:c r="G56" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Text</x:t>
+          <x:t xml:space="preserve">Button</x:t>
         </x:is>
       </x:c>
       <x:c r="H56" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">非空白，最多 200 字</x:t>
+          <x:t xml:space="preserve">DELETE 權限</x:t>
         </x:is>
       </x:c>
       <x:c r="I56" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.39.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.36.2</x:t>
         </x:is>
       </x:c>
       <x:c r="J56" s="2" t="inlineStr">
@@ -10275,32 +10275,32 @@
     <x:row r="57">
       <x:c r="A57" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.41.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.37.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B57" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.41</x:t>
+          <x:t xml:space="preserve">4.4.1.8.37</x:t>
         </x:is>
       </x:c>
       <x:c r="C57" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Item Brand Edit Interface</x:t>
+          <x:t xml:space="preserve">Item Category Create Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D57" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Code (Label)</x:t>
+          <x:t xml:space="preserve">Code (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E57" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">編輯時只讀。</x:t>
+          <x:t xml:space="preserve">建立時填寫並轉大寫。</x:t>
         </x:is>
       </x:c>
       <x:c r="F57" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">防止歷史引用變更識別。</x:t>
+          <x:t xml:space="preserve">公司內唯一識別。</x:t>
         </x:is>
       </x:c>
       <x:c r="G57" s="2" t="inlineStr">
@@ -10310,12 +10310,12 @@
       </x:c>
       <x:c r="H57" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">最多 30 字</x:t>
+          <x:t xml:space="preserve">1–30 位英數、-、_</x:t>
         </x:is>
       </x:c>
       <x:c r="I57" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.39.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.36.2</x:t>
         </x:is>
       </x:c>
       <x:c r="J57" s="2" t="inlineStr">
@@ -10332,47 +10332,47 @@
     <x:row r="58">
       <x:c r="A58" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.41.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.37.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B58" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.41</x:t>
+          <x:t xml:space="preserve">4.4.1.8.37</x:t>
         </x:is>
       </x:c>
       <x:c r="C58" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Item Brand Edit Interface</x:t>
+          <x:t xml:space="preserve">Item Category Create Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D58" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Name / Active</x:t>
+          <x:t xml:space="preserve">Name (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E58" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">修改名稱與啟用狀態。</x:t>
+          <x:t xml:space="preserve">分類名稱。</x:t>
         </x:is>
       </x:c>
       <x:c r="F58" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">維護品牌。</x:t>
+          <x:t xml:space="preserve">向用戶顯示。</x:t>
         </x:is>
       </x:c>
       <x:c r="G58" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Text／Boolean</x:t>
+          <x:t xml:space="preserve">Text</x:t>
         </x:is>
       </x:c>
       <x:c r="H58" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">同建立</x:t>
+          <x:t xml:space="preserve">非空白，最多 200 字</x:t>
         </x:is>
       </x:c>
       <x:c r="I58" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.39.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.36.2</x:t>
         </x:is>
       </x:c>
       <x:c r="J58" s="2" t="inlineStr">
@@ -10389,47 +10389,47 @@
     <x:row r="59">
       <x:c r="A59" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.45.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.37.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B59" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.45</x:t>
+          <x:t xml:space="preserve">4.4.1.8.37</x:t>
         </x:is>
       </x:c>
       <x:c r="C59" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Unit of Measurement View Interface</x:t>
+          <x:t xml:space="preserve">Item Category Create Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D59" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Search (Input)</x:t>
+          <x:t xml:space="preserve">Parent (Dropdown)</x:t>
         </x:is>
       </x:c>
       <x:c r="E59" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">代碼或名稱關鍵字。</x:t>
+          <x:t xml:space="preserve">上層分類，可不選（最上層）；選項按層級縮排。</x:t>
         </x:is>
       </x:c>
       <x:c r="F59" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">縮小目前公司單位列表。</x:t>
+          <x:t xml:space="preserve">決定分類位置。</x:t>
         </x:is>
       </x:c>
       <x:c r="G59" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Text</x:t>
+          <x:t xml:space="preserve">Category ID</x:t>
         </x:is>
       </x:c>
       <x:c r="H59" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">任意文字</x:t>
+          <x:t xml:space="preserve">本公司啟用分類，新節點不超過第 5 層</x:t>
         </x:is>
       </x:c>
       <x:c r="I59" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.45.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.36.2</x:t>
         </x:is>
       </x:c>
       <x:c r="J59" s="2" t="inlineStr">
@@ -10446,47 +10446,47 @@
     <x:row r="60">
       <x:c r="A60" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.45.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.38.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B60" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.45</x:t>
+          <x:t xml:space="preserve">4.4.1.8.38</x:t>
         </x:is>
       </x:c>
       <x:c r="C60" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Unit of Measurement View Interface</x:t>
+          <x:t xml:space="preserve">Item Category Edit Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D60" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Unit List (Table)</x:t>
+          <x:t xml:space="preserve">Code (Label)</x:t>
         </x:is>
       </x:c>
       <x:c r="E60" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">代碼、名稱、小數位數、狀態及編輯／刪除操作；代碼與名稱可排序，伺服器分頁。</x:t>
+          <x:t xml:space="preserve">編輯時只讀。</x:t>
         </x:is>
       </x:c>
       <x:c r="F60" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">查看單位。</x:t>
+          <x:t xml:space="preserve">防止歷史引用變更識別。</x:t>
         </x:is>
       </x:c>
       <x:c r="G60" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Table</x:t>
+          <x:t xml:space="preserve">Text</x:t>
         </x:is>
       </x:c>
       <x:c r="H60" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">每頁 10／20／50／100／200</x:t>
+          <x:t xml:space="preserve">最多 30 字</x:t>
         </x:is>
       </x:c>
       <x:c r="I60" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.46.1, REQ_IO_A8.47.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.36.2</x:t>
         </x:is>
       </x:c>
       <x:c r="J60" s="2" t="inlineStr">
@@ -10503,47 +10503,47 @@
     <x:row r="61">
       <x:c r="A61" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.45.3</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.38.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B61" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.45</x:t>
+          <x:t xml:space="preserve">4.4.1.8.38</x:t>
         </x:is>
       </x:c>
       <x:c r="C61" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Unit of Measurement View Interface</x:t>
+          <x:t xml:space="preserve">Item Category Edit Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D61" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Conversion List (Table)</x:t>
+          <x:t xml:space="preserve">Name / Active</x:t>
         </x:is>
       </x:c>
       <x:c r="E61" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">來源、目標、換算規則及編輯／刪除操作。</x:t>
+          <x:t xml:space="preserve">修改名稱與啟用狀態。</x:t>
         </x:is>
       </x:c>
       <x:c r="F61" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">查看換算。</x:t>
+          <x:t xml:space="preserve">維護分類。</x:t>
         </x:is>
       </x:c>
       <x:c r="G61" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Table</x:t>
+          <x:t xml:space="preserve">Text／Boolean</x:t>
         </x:is>
       </x:c>
       <x:c r="H61" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">全部換算</x:t>
+          <x:t xml:space="preserve">同建立</x:t>
         </x:is>
       </x:c>
       <x:c r="I61" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.46.4</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.36.2</x:t>
         </x:is>
       </x:c>
       <x:c r="J61" s="2" t="inlineStr">
@@ -10560,47 +10560,47 @@
     <x:row r="62">
       <x:c r="A62" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.45.4</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.38.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B62" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.45</x:t>
+          <x:t xml:space="preserve">4.4.1.8.38</x:t>
         </x:is>
       </x:c>
       <x:c r="C62" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Unit of Measurement View Interface</x:t>
+          <x:t xml:space="preserve">Item Category Edit Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D62" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Calculator (Form)</x:t>
+          <x:t xml:space="preserve">Parent (Dropdown)</x:t>
         </x:is>
       </x:c>
       <x:c r="E62" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">數量、來源單位、目標單位、換算按鈕與結果。</x:t>
+          <x:t xml:space="preserve">搬移整棵子樹；排除自己與子孫。</x:t>
         </x:is>
       </x:c>
       <x:c r="F62" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">試算換算結果。</x:t>
+          <x:t xml:space="preserve">調整階層。</x:t>
         </x:is>
       </x:c>
       <x:c r="G62" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Decimal</x:t>
+          <x:t xml:space="preserve">Category ID</x:t>
         </x:is>
       </x:c>
       <x:c r="H62" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">數量最多 12 位整數及 6 位小數</x:t>
+          <x:t xml:space="preserve">啟用分類或目前上層，搬移後不超過 5 層</x:t>
         </x:is>
       </x:c>
       <x:c r="I62" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.45.3</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.36.2</x:t>
         </x:is>
       </x:c>
       <x:c r="J62" s="2" t="inlineStr">
@@ -10617,32 +10617,32 @@
     <x:row r="63">
       <x:c r="A63" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.46.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.39.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B63" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.46</x:t>
+          <x:t xml:space="preserve">4.4.1.8.39</x:t>
         </x:is>
       </x:c>
       <x:c r="C63" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Unit of Measurement Create Interface</x:t>
+          <x:t xml:space="preserve">Item Brand View Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D63" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Code (Input)</x:t>
+          <x:t xml:space="preserve">Search (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E63" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">建立時輸入並轉大寫。</x:t>
+          <x:t xml:space="preserve">依代碼或名稱搜尋目前公司品牌。</x:t>
         </x:is>
       </x:c>
       <x:c r="F63" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">公司內唯一識別。</x:t>
+          <x:t xml:space="preserve">縮小列表。</x:t>
         </x:is>
       </x:c>
       <x:c r="G63" s="2" t="inlineStr">
@@ -10652,12 +10652,12 @@
       </x:c>
       <x:c r="H63" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1–30 位英數、-、_</x:t>
+          <x:t xml:space="preserve">任意文字</x:t>
         </x:is>
       </x:c>
       <x:c r="I63" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.45.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.39.2</x:t>
         </x:is>
       </x:c>
       <x:c r="J63" s="2" t="inlineStr">
@@ -10674,47 +10674,47 @@
     <x:row r="64">
       <x:c r="A64" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.46.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.39.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B64" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.46</x:t>
+          <x:t xml:space="preserve">4.4.1.8.39</x:t>
         </x:is>
       </x:c>
       <x:c r="C64" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Unit of Measurement Create Interface</x:t>
+          <x:t xml:space="preserve">Item Brand View Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D64" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Name (Input)</x:t>
+          <x:t xml:space="preserve">Brand List (Table)</x:t>
         </x:is>
       </x:c>
       <x:c r="E64" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">單位名稱。</x:t>
+          <x:t xml:space="preserve">代碼、名稱、啟用狀態，代碼及名稱可排序，伺服器分頁。</x:t>
         </x:is>
       </x:c>
       <x:c r="F64" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">顯示單位。</x:t>
+          <x:t xml:space="preserve">檢視品牌。</x:t>
         </x:is>
       </x:c>
       <x:c r="G64" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Text</x:t>
+          <x:t xml:space="preserve">Table</x:t>
         </x:is>
       </x:c>
       <x:c r="H64" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">非空白、最多 200 字</x:t>
+          <x:t xml:space="preserve">每頁 10／20／50／100／200</x:t>
         </x:is>
       </x:c>
       <x:c r="I64" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.45.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.40.1, REQ_IO_A8.41.1</x:t>
         </x:is>
       </x:c>
       <x:c r="J64" s="2" t="inlineStr">
@@ -10731,47 +10731,47 @@
     <x:row r="65">
       <x:c r="A65" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.46.3</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.39.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B65" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.46</x:t>
+          <x:t xml:space="preserve">4.4.1.8.39</x:t>
         </x:is>
       </x:c>
       <x:c r="C65" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Unit of Measurement Create Interface</x:t>
+          <x:t xml:space="preserve">Item Brand View Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D65" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Decimal Places (Dropdown)</x:t>
+          <x:t xml:space="preserve">Delete (Button)</x:t>
         </x:is>
       </x:c>
       <x:c r="E65" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">數量小數位數。</x:t>
+          <x:t xml:space="preserve">二次確認後按版本軟刪除。</x:t>
         </x:is>
       </x:c>
       <x:c r="F65" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">換算結果捨入。</x:t>
+          <x:t xml:space="preserve">移除未使用的品牌。</x:t>
         </x:is>
       </x:c>
       <x:c r="G65" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Integer</x:t>
+          <x:t xml:space="preserve">Button</x:t>
         </x:is>
       </x:c>
       <x:c r="H65" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">0–6</x:t>
+          <x:t xml:space="preserve">DELETE 權限</x:t>
         </x:is>
       </x:c>
       <x:c r="I65" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.45.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.39.2</x:t>
         </x:is>
       </x:c>
       <x:c r="J65" s="2" t="inlineStr">
@@ -10788,47 +10788,47 @@
     <x:row r="66">
       <x:c r="A66" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.46.4</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.40.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B66" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.46</x:t>
+          <x:t xml:space="preserve">4.4.1.8.40</x:t>
         </x:is>
       </x:c>
       <x:c r="C66" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Unit of Measurement Create Interface</x:t>
+          <x:t xml:space="preserve">Item Brand Create Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D66" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">From / To Unit (Dropdown)</x:t>
+          <x:t xml:space="preserve">Code (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E66" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">換算兩端單位；停用單位不可選，兩端不可相同。</x:t>
+          <x:t xml:space="preserve">建立時填寫並轉大寫。</x:t>
         </x:is>
       </x:c>
       <x:c r="F66" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">定義換算。</x:t>
+          <x:t xml:space="preserve">公司內唯一識別。</x:t>
         </x:is>
       </x:c>
       <x:c r="G66" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Unit ID</x:t>
+          <x:t xml:space="preserve">Text</x:t>
         </x:is>
       </x:c>
       <x:c r="H66" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">本公司啟用單位</x:t>
+          <x:t xml:space="preserve">1–30 位英數、-、_</x:t>
         </x:is>
       </x:c>
       <x:c r="I66" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.45.3</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.39.2</x:t>
         </x:is>
       </x:c>
       <x:c r="J66" s="2" t="inlineStr">
@@ -10845,47 +10845,47 @@
     <x:row r="67">
       <x:c r="A67" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.46.5</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.40.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B67" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.46</x:t>
+          <x:t xml:space="preserve">4.4.1.8.40</x:t>
         </x:is>
       </x:c>
       <x:c r="C67" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Unit of Measurement Create Interface</x:t>
+          <x:t xml:space="preserve">Item Brand Create Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D67" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Factor (Input)</x:t>
+          <x:t xml:space="preserve">Name (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E67" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1 來源 = 係數 目標。</x:t>
+          <x:t xml:space="preserve">品牌名稱。</x:t>
         </x:is>
       </x:c>
       <x:c r="F67" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">換算係數。</x:t>
+          <x:t xml:space="preserve">向用戶顯示。</x:t>
         </x:is>
       </x:c>
       <x:c r="G67" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Decimal</x:t>
+          <x:t xml:space="preserve">Text</x:t>
         </x:is>
       </x:c>
       <x:c r="H67" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">大於 0，最多 9 位整數及 6 位小數</x:t>
+          <x:t xml:space="preserve">非空白，最多 200 字</x:t>
         </x:is>
       </x:c>
       <x:c r="I67" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.45.3</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.39.2</x:t>
         </x:is>
       </x:c>
       <x:c r="J67" s="2" t="inlineStr">
@@ -10902,17 +10902,17 @@
     <x:row r="68">
       <x:c r="A68" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.47.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.41.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B68" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.47</x:t>
+          <x:t xml:space="preserve">4.4.1.8.41</x:t>
         </x:is>
       </x:c>
       <x:c r="C68" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Unit of Measurement Edit Interface</x:t>
+          <x:t xml:space="preserve">Item Brand Edit Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D68" s="2" t="inlineStr">
@@ -10922,12 +10922,12 @@
       </x:c>
       <x:c r="E68" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">編輯時唯讀。</x:t>
+          <x:t xml:space="preserve">編輯時只讀。</x:t>
         </x:is>
       </x:c>
       <x:c r="F68" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">保持歷史識別。</x:t>
+          <x:t xml:space="preserve">防止歷史引用變更識別。</x:t>
         </x:is>
       </x:c>
       <x:c r="G68" s="2" t="inlineStr">
@@ -10942,7 +10942,7 @@
       </x:c>
       <x:c r="I68" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.45.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.39.2</x:t>
         </x:is>
       </x:c>
       <x:c r="J68" s="2" t="inlineStr">
@@ -10959,37 +10959,37 @@
     <x:row r="69">
       <x:c r="A69" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.47.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.41.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B69" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.47</x:t>
+          <x:t xml:space="preserve">4.4.1.8.41</x:t>
         </x:is>
       </x:c>
       <x:c r="C69" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Unit of Measurement Edit Interface</x:t>
+          <x:t xml:space="preserve">Item Brand Edit Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D69" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Name / Decimal Places / Active</x:t>
+          <x:t xml:space="preserve">Name / Active</x:t>
         </x:is>
       </x:c>
       <x:c r="E69" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">修改名稱、小數位數、啟用狀態。</x:t>
+          <x:t xml:space="preserve">修改名稱與啟用狀態。</x:t>
         </x:is>
       </x:c>
       <x:c r="F69" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">維護單位。</x:t>
+          <x:t xml:space="preserve">維護品牌。</x:t>
         </x:is>
       </x:c>
       <x:c r="G69" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Text／Integer／Boolean</x:t>
+          <x:t xml:space="preserve">Text／Boolean</x:t>
         </x:is>
       </x:c>
       <x:c r="H69" s="2" t="inlineStr">
@@ -10999,7 +10999,7 @@
       </x:c>
       <x:c r="I69" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.45.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.39.2</x:t>
         </x:is>
       </x:c>
       <x:c r="J69" s="2" t="inlineStr">
@@ -11016,47 +11016,47 @@
     <x:row r="70">
       <x:c r="A70" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.47.3</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.45.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B70" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.47</x:t>
+          <x:t xml:space="preserve">4.4.1.8.45</x:t>
         </x:is>
       </x:c>
       <x:c r="C70" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Unit of Measurement Edit Interface</x:t>
+          <x:t xml:space="preserve">Unit of Measurement View Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D70" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Factor (Input)</x:t>
+          <x:t xml:space="preserve">Search (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E70" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">編輯換算時只可改係數。</x:t>
+          <x:t xml:space="preserve">代碼或名稱關鍵字。</x:t>
         </x:is>
       </x:c>
       <x:c r="F70" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">修正換算。</x:t>
+          <x:t xml:space="preserve">縮小目前公司單位列表。</x:t>
         </x:is>
       </x:c>
       <x:c r="G70" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Decimal</x:t>
+          <x:t xml:space="preserve">Text</x:t>
         </x:is>
       </x:c>
       <x:c r="H70" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">同建立</x:t>
+          <x:t xml:space="preserve">任意文字</x:t>
         </x:is>
       </x:c>
       <x:c r="I70" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.45.3</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.45.2</x:t>
         </x:is>
       </x:c>
       <x:c r="J70" s="2" t="inlineStr">
@@ -11073,47 +11073,47 @@
     <x:row r="71">
       <x:c r="A71" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.47.4</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.45.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B71" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.47</x:t>
+          <x:t xml:space="preserve">4.4.1.8.45</x:t>
         </x:is>
       </x:c>
       <x:c r="C71" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Unit of Measurement Edit Interface</x:t>
+          <x:t xml:space="preserve">Unit of Measurement View Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D71" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Delete (Button)</x:t>
+          <x:t xml:space="preserve">Unit List (Table)</x:t>
         </x:is>
       </x:c>
       <x:c r="E71" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">確認後帶版本刪除單位或換算；被引用單位顯示 IN_USE。</x:t>
+          <x:t xml:space="preserve">代碼、名稱、小數位數、狀態及編輯／刪除操作；代碼與名稱可排序，伺服器分頁。</x:t>
         </x:is>
       </x:c>
       <x:c r="F71" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">移除錯誤資料。</x:t>
+          <x:t xml:space="preserve">查看單位。</x:t>
         </x:is>
       </x:c>
       <x:c r="G71" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Action</x:t>
+          <x:t xml:space="preserve">Table</x:t>
         </x:is>
       </x:c>
       <x:c r="H71" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">-</x:t>
+          <x:t xml:space="preserve">每頁 10／20／50／100／200</x:t>
         </x:is>
       </x:c>
       <x:c r="I71" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.45.2, REQ_IO_A8.45.3</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.46.1, REQ_IO_A8.47.1</x:t>
         </x:is>
       </x:c>
       <x:c r="J71" s="2" t="inlineStr">
@@ -11130,47 +11130,47 @@
     <x:row r="72">
       <x:c r="A72" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.55.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.45.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B72" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.55</x:t>
+          <x:t xml:space="preserve">4.4.1.8.45</x:t>
         </x:is>
       </x:c>
       <x:c r="C72" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Parameter Edit Interface</x:t>
+          <x:t xml:space="preserve">Unit of Measurement View Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D72" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Boolean Parameter (Switch)</x:t>
+          <x:t xml:space="preserve">Conversion List (Table)</x:t>
         </x:is>
       </x:c>
       <x:c r="E72" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">開關型參數</x:t>
+          <x:t xml:space="preserve">來源、目標、換算規則及編輯／刪除操作。</x:t>
         </x:is>
       </x:c>
       <x:c r="F72" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">啟用／停用功能</x:t>
+          <x:t xml:space="preserve">查看換算。</x:t>
         </x:is>
       </x:c>
       <x:c r="G72" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">true／false</x:t>
+          <x:t xml:space="preserve">Table</x:t>
         </x:is>
       </x:c>
       <x:c r="H72" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">—</x:t>
+          <x:t xml:space="preserve">全部換算</x:t>
         </x:is>
       </x:c>
       <x:c r="I72" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">None</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.46.4</x:t>
         </x:is>
       </x:c>
       <x:c r="J72" s="2" t="inlineStr">
@@ -11187,47 +11187,47 @@
     <x:row r="73">
       <x:c r="A73" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.55.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.45.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B73" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.55</x:t>
+          <x:t xml:space="preserve">4.4.1.8.45</x:t>
         </x:is>
       </x:c>
       <x:c r="C73" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Parameter Edit Interface</x:t>
+          <x:t xml:space="preserve">Unit of Measurement View Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D73" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Whole Number Parameter (Input)</x:t>
+          <x:t xml:space="preserve">Calculator (Form)</x:t>
         </x:is>
       </x:c>
       <x:c r="E73" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">整數參數</x:t>
+          <x:t xml:space="preserve">數量、來源單位、目標單位、換算按鈕與結果。</x:t>
         </x:is>
       </x:c>
       <x:c r="F73" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">例如小數位數</x:t>
+          <x:t xml:space="preserve">試算換算結果。</x:t>
         </x:is>
       </x:c>
       <x:c r="G73" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">整數字串</x:t>
+          <x:t xml:space="preserve">Decimal</x:t>
         </x:is>
       </x:c>
       <x:c r="H73" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">宣告的最小值至最大值</x:t>
+          <x:t xml:space="preserve">數量最多 12 位整數及 6 位小數</x:t>
         </x:is>
       </x:c>
       <x:c r="I73" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">None</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.45.3</x:t>
         </x:is>
       </x:c>
       <x:c r="J73" s="2" t="inlineStr">
@@ -11244,47 +11244,47 @@
     <x:row r="74">
       <x:c r="A74" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.55.3</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.46.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B74" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.55</x:t>
+          <x:t xml:space="preserve">4.4.1.8.46</x:t>
         </x:is>
       </x:c>
       <x:c r="C74" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Parameter Edit Interface</x:t>
+          <x:t xml:space="preserve">Unit of Measurement Create Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D74" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Number Parameter (Input)</x:t>
+          <x:t xml:space="preserve">Code (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E74" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">十進位參數</x:t>
+          <x:t xml:space="preserve">建立時輸入並轉大寫。</x:t>
         </x:is>
       </x:c>
       <x:c r="F74" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">數值設定</x:t>
+          <x:t xml:space="preserve">公司內唯一識別。</x:t>
         </x:is>
       </x:c>
       <x:c r="G74" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">十進位字串（不使用指數）</x:t>
+          <x:t xml:space="preserve">Text</x:t>
         </x:is>
       </x:c>
       <x:c r="H74" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">宣告的範圍；精度由伺服器判斷</x:t>
+          <x:t xml:space="preserve">1–30 位英數、-、_</x:t>
         </x:is>
       </x:c>
       <x:c r="I74" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">None</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.45.2</x:t>
         </x:is>
       </x:c>
       <x:c r="J74" s="2" t="inlineStr">
@@ -11301,32 +11301,32 @@
     <x:row r="75">
       <x:c r="A75" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.55.4</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.46.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B75" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.55</x:t>
+          <x:t xml:space="preserve">4.4.1.8.46</x:t>
         </x:is>
       </x:c>
       <x:c r="C75" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Parameter Edit Interface</x:t>
+          <x:t xml:space="preserve">Unit of Measurement Create Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D75" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Text Parameter (Input)</x:t>
+          <x:t xml:space="preserve">Name (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E75" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">文字參數</x:t>
+          <x:t xml:space="preserve">單位名稱。</x:t>
         </x:is>
       </x:c>
       <x:c r="F75" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">名稱、備註等</x:t>
+          <x:t xml:space="preserve">顯示單位。</x:t>
         </x:is>
       </x:c>
       <x:c r="G75" s="2" t="inlineStr">
@@ -11336,12 +11336,12 @@
       </x:c>
       <x:c r="H75" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">宣告的長度上限</x:t>
+          <x:t xml:space="preserve">非空白、最多 200 字</x:t>
         </x:is>
       </x:c>
       <x:c r="I75" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">None</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.45.2</x:t>
         </x:is>
       </x:c>
       <x:c r="J75" s="2" t="inlineStr">
@@ -11358,47 +11358,47 @@
     <x:row r="76">
       <x:c r="A76" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.55.5</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.46.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B76" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.55</x:t>
+          <x:t xml:space="preserve">4.4.1.8.46</x:t>
         </x:is>
       </x:c>
       <x:c r="C76" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Parameter Edit Interface</x:t>
+          <x:t xml:space="preserve">Unit of Measurement Create Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D76" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Option Parameter (Dropdown)</x:t>
+          <x:t xml:space="preserve">Decimal Places (Dropdown)</x:t>
         </x:is>
       </x:c>
       <x:c r="E76" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">選項參數</x:t>
+          <x:t xml:space="preserve">數量小數位數。</x:t>
         </x:is>
       </x:c>
       <x:c r="F76" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">從固定選項選擇</x:t>
+          <x:t xml:space="preserve">換算結果捨入。</x:t>
         </x:is>
       </x:c>
       <x:c r="G76" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Enum</x:t>
+          <x:t xml:space="preserve">Integer</x:t>
         </x:is>
       </x:c>
       <x:c r="H76" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">宣告的選項</x:t>
+          <x:t xml:space="preserve">0–6</x:t>
         </x:is>
       </x:c>
       <x:c r="I76" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">None</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.45.2</x:t>
         </x:is>
       </x:c>
       <x:c r="J76" s="2" t="inlineStr">
@@ -11415,47 +11415,47 @@
     <x:row r="77">
       <x:c r="A77" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.55.6</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.46.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B77" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.55</x:t>
+          <x:t xml:space="preserve">4.4.1.8.46</x:t>
         </x:is>
       </x:c>
       <x:c r="C77" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Parameter Edit Interface</x:t>
+          <x:t xml:space="preserve">Unit of Measurement Create Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D77" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Restore Default (Button)</x:t>
+          <x:t xml:space="preserve">From / To Unit (Dropdown)</x:t>
         </x:is>
       </x:c>
       <x:c r="E77" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">恢復預設</x:t>
+          <x:t xml:space="preserve">換算兩端單位；停用單位不可選，兩端不可相同。</x:t>
         </x:is>
       </x:c>
       <x:c r="F77" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">把欄位設回預設值</x:t>
+          <x:t xml:space="preserve">定義換算。</x:t>
         </x:is>
       </x:c>
       <x:c r="G77" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Button</x:t>
+          <x:t xml:space="preserve">Unit ID</x:t>
         </x:is>
       </x:c>
       <x:c r="H77" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">需 EDIT；保存後才生效</x:t>
+          <x:t xml:space="preserve">本公司啟用單位</x:t>
         </x:is>
       </x:c>
       <x:c r="I77" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.55.1, REQ_IO_A8.55.2, REQ_IO_A8.55.3, REQ_IO_A8.55.4, REQ_IO_A8.55.5</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.45.3</x:t>
         </x:is>
       </x:c>
       <x:c r="J77" s="2" t="inlineStr">
@@ -11472,47 +11472,47 @@
     <x:row r="78">
       <x:c r="A78" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.55.7</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.46.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B78" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.55</x:t>
+          <x:t xml:space="preserve">4.4.1.8.46</x:t>
         </x:is>
       </x:c>
       <x:c r="C78" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Parameter Edit Interface</x:t>
+          <x:t xml:space="preserve">Unit of Measurement Create Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D78" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Save (Button)</x:t>
+          <x:t xml:space="preserve">Factor (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E78" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">保存</x:t>
+          <x:t xml:space="preserve">1 來源 = 係數 目標。</x:t>
         </x:is>
       </x:c>
       <x:c r="F78" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">批次保存有修改的參數</x:t>
+          <x:t xml:space="preserve">換算係數。</x:t>
         </x:is>
       </x:c>
       <x:c r="G78" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Button</x:t>
+          <x:t xml:space="preserve">Decimal</x:t>
         </x:is>
       </x:c>
       <x:c r="H78" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">需 EDIT；只送有修改的項目並帶 version</x:t>
+          <x:t xml:space="preserve">大於 0，最多 9 位整數及 6 位小數</x:t>
         </x:is>
       </x:c>
       <x:c r="I78" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.55.1, REQ_IO_A8.55.2, REQ_IO_A8.55.3, REQ_IO_A8.55.4, REQ_IO_A8.55.5</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.45.3</x:t>
         </x:is>
       </x:c>
       <x:c r="J78" s="2" t="inlineStr">
@@ -11529,32 +11529,32 @@
     <x:row r="79">
       <x:c r="A79" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.56.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.47.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B79" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.56</x:t>
+          <x:t xml:space="preserve">4.4.1.8.47</x:t>
         </x:is>
       </x:c>
       <x:c r="C79" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Print Settings Edit Interface</x:t>
+          <x:t xml:space="preserve">Unit of Measurement Edit Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D79" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Company Name (Input)</x:t>
+          <x:t xml:space="preserve">Code (Label)</x:t>
         </x:is>
       </x:c>
       <x:c r="E79" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">列印公司名稱</x:t>
+          <x:t xml:space="preserve">編輯時唯讀。</x:t>
         </x:is>
       </x:c>
       <x:c r="F79" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">單據抬頭</x:t>
+          <x:t xml:space="preserve">保持歷史識別。</x:t>
         </x:is>
       </x:c>
       <x:c r="G79" s="2" t="inlineStr">
@@ -11564,12 +11564,12 @@
       </x:c>
       <x:c r="H79" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">最多 100 字；空白時用公司主檔名稱</x:t>
+          <x:t xml:space="preserve">最多 30 字</x:t>
         </x:is>
       </x:c>
       <x:c r="I79" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">None</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.45.2</x:t>
         </x:is>
       </x:c>
       <x:c r="J79" s="2" t="inlineStr">
@@ -11586,47 +11586,47 @@
     <x:row r="80">
       <x:c r="A80" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.56.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.47.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B80" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.56</x:t>
+          <x:t xml:space="preserve">4.4.1.8.47</x:t>
         </x:is>
       </x:c>
       <x:c r="C80" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Print Settings Edit Interface</x:t>
+          <x:t xml:space="preserve">Unit of Measurement Edit Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D80" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Address (Input)</x:t>
+          <x:t xml:space="preserve">Name / Decimal Places / Active</x:t>
         </x:is>
       </x:c>
       <x:c r="E80" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">地址</x:t>
+          <x:t xml:space="preserve">修改名稱、小數位數、啟用狀態。</x:t>
         </x:is>
       </x:c>
       <x:c r="F80" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">單據抬頭</x:t>
+          <x:t xml:space="preserve">維護單位。</x:t>
         </x:is>
       </x:c>
       <x:c r="G80" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Text</x:t>
+          <x:t xml:space="preserve">Text／Integer／Boolean</x:t>
         </x:is>
       </x:c>
       <x:c r="H80" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">最多 200 字</x:t>
+          <x:t xml:space="preserve">同建立</x:t>
         </x:is>
       </x:c>
       <x:c r="I80" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">None</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.45.2</x:t>
         </x:is>
       </x:c>
       <x:c r="J80" s="2" t="inlineStr">
@@ -11643,47 +11643,47 @@
     <x:row r="81">
       <x:c r="A81" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.56.3</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.47.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B81" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.56</x:t>
+          <x:t xml:space="preserve">4.4.1.8.47</x:t>
         </x:is>
       </x:c>
       <x:c r="C81" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Print Settings Edit Interface</x:t>
+          <x:t xml:space="preserve">Unit of Measurement Edit Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D81" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Postal Code (Input)</x:t>
+          <x:t xml:space="preserve">Factor (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E81" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">郵遞區號</x:t>
+          <x:t xml:space="preserve">編輯換算時只可改係數。</x:t>
         </x:is>
       </x:c>
       <x:c r="F81" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">單據抬頭</x:t>
+          <x:t xml:space="preserve">修正換算。</x:t>
         </x:is>
       </x:c>
       <x:c r="G81" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Text</x:t>
+          <x:t xml:space="preserve">Decimal</x:t>
         </x:is>
       </x:c>
       <x:c r="H81" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">最多 10 字</x:t>
+          <x:t xml:space="preserve">同建立</x:t>
         </x:is>
       </x:c>
       <x:c r="I81" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">None</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.45.3</x:t>
         </x:is>
       </x:c>
       <x:c r="J81" s="2" t="inlineStr">
@@ -11700,47 +11700,47 @@
     <x:row r="82">
       <x:c r="A82" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.56.4</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.47.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B82" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.56</x:t>
+          <x:t xml:space="preserve">4.4.1.8.47</x:t>
         </x:is>
       </x:c>
       <x:c r="C82" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Print Settings Edit Interface</x:t>
+          <x:t xml:space="preserve">Unit of Measurement Edit Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D82" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Phone (Input)</x:t>
+          <x:t xml:space="preserve">Delete (Button)</x:t>
         </x:is>
       </x:c>
       <x:c r="E82" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">電話</x:t>
+          <x:t xml:space="preserve">確認後帶版本刪除單位或換算；被引用單位顯示 IN_USE。</x:t>
         </x:is>
       </x:c>
       <x:c r="F82" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">單據抬頭</x:t>
+          <x:t xml:space="preserve">移除錯誤資料。</x:t>
         </x:is>
       </x:c>
       <x:c r="G82" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Text</x:t>
+          <x:t xml:space="preserve">Action</x:t>
         </x:is>
       </x:c>
       <x:c r="H82" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">最多 30 字</x:t>
+          <x:t xml:space="preserve">-</x:t>
         </x:is>
       </x:c>
       <x:c r="I82" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">None</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.45.2, REQ_IO_A8.45.3</x:t>
         </x:is>
       </x:c>
       <x:c r="J82" s="2" t="inlineStr">
@@ -11757,42 +11757,42 @@
     <x:row r="83">
       <x:c r="A83" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.56.5</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.55.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B83" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.56</x:t>
+          <x:t xml:space="preserve">4.4.1.8.55</x:t>
         </x:is>
       </x:c>
       <x:c r="C83" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Print Settings Edit Interface</x:t>
+          <x:t xml:space="preserve">Parameter Edit Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D83" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Fax (Input)</x:t>
+          <x:t xml:space="preserve">Boolean Parameter (Switch)</x:t>
         </x:is>
       </x:c>
       <x:c r="E83" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">傳真</x:t>
+          <x:t xml:space="preserve">開關型參數</x:t>
         </x:is>
       </x:c>
       <x:c r="F83" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">單據抬頭</x:t>
+          <x:t xml:space="preserve">啟用／停用功能</x:t>
         </x:is>
       </x:c>
       <x:c r="G83" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Text</x:t>
+          <x:t xml:space="preserve">true／false</x:t>
         </x:is>
       </x:c>
       <x:c r="H83" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">最多 30 字</x:t>
+          <x:t xml:space="preserve">—</x:t>
         </x:is>
       </x:c>
       <x:c r="I83" s="2" t="inlineStr">
@@ -11814,42 +11814,42 @@
     <x:row r="84">
       <x:c r="A84" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.56.6</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.55.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B84" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.56</x:t>
+          <x:t xml:space="preserve">4.4.1.8.55</x:t>
         </x:is>
       </x:c>
       <x:c r="C84" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Print Settings Edit Interface</x:t>
+          <x:t xml:space="preserve">Parameter Edit Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D84" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Purchase Order Footer (Textarea)</x:t>
+          <x:t xml:space="preserve">Whole Number Parameter (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E84" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">採購單頁尾備註</x:t>
+          <x:t xml:space="preserve">整數參數</x:t>
         </x:is>
       </x:c>
       <x:c r="F84" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">列印在採購單底部</x:t>
+          <x:t xml:space="preserve">例如小數位數</x:t>
         </x:is>
       </x:c>
       <x:c r="G84" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Text（可多行）</x:t>
+          <x:t xml:space="preserve">整數字串</x:t>
         </x:is>
       </x:c>
       <x:c r="H84" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">最多 500 字</x:t>
+          <x:t xml:space="preserve">宣告的最小值至最大值</x:t>
         </x:is>
       </x:c>
       <x:c r="I84" s="2" t="inlineStr">
@@ -11871,42 +11871,42 @@
     <x:row r="85">
       <x:c r="A85" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.56.7</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.55.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B85" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.56</x:t>
+          <x:t xml:space="preserve">4.4.1.8.55</x:t>
         </x:is>
       </x:c>
       <x:c r="C85" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Print Settings Edit Interface</x:t>
+          <x:t xml:space="preserve">Parameter Edit Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D85" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Sales Delivery Footer (Textarea)</x:t>
+          <x:t xml:space="preserve">Number Parameter (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E85" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">銷售出貨單頁尾備註</x:t>
+          <x:t xml:space="preserve">十進位參數</x:t>
         </x:is>
       </x:c>
       <x:c r="F85" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">列印在出貨單底部</x:t>
+          <x:t xml:space="preserve">數值設定</x:t>
         </x:is>
       </x:c>
       <x:c r="G85" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Text（可多行）</x:t>
+          <x:t xml:space="preserve">十進位字串（不使用指數）</x:t>
         </x:is>
       </x:c>
       <x:c r="H85" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">最多 500 字</x:t>
+          <x:t xml:space="preserve">宣告的範圍；精度由伺服器判斷</x:t>
         </x:is>
       </x:c>
       <x:c r="I85" s="2" t="inlineStr">
@@ -11928,42 +11928,42 @@
     <x:row r="86">
       <x:c r="A86" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.56.8</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.55.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B86" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.56</x:t>
+          <x:t xml:space="preserve">4.4.1.8.55</x:t>
         </x:is>
       </x:c>
       <x:c r="C86" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Print Settings Edit Interface</x:t>
+          <x:t xml:space="preserve">Parameter Edit Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D86" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Print Logo (Switch)</x:t>
+          <x:t xml:space="preserve">Text Parameter (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E86" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">是否列印 Logo</x:t>
+          <x:t xml:space="preserve">文字參數</x:t>
         </x:is>
       </x:c>
       <x:c r="F86" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">控制單據顯示 Logo</x:t>
+          <x:t xml:space="preserve">名稱、備註等</x:t>
         </x:is>
       </x:c>
       <x:c r="G86" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">true／false</x:t>
+          <x:t xml:space="preserve">Text</x:t>
         </x:is>
       </x:c>
       <x:c r="H86" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">預設否</x:t>
+          <x:t xml:space="preserve">宣告的長度上限</x:t>
         </x:is>
       </x:c>
       <x:c r="I86" s="2" t="inlineStr">
@@ -11985,42 +11985,42 @@
     <x:row r="87">
       <x:c r="A87" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.56.9</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.55.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B87" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.56</x:t>
+          <x:t xml:space="preserve">4.4.1.8.55</x:t>
         </x:is>
       </x:c>
       <x:c r="C87" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Print Settings Edit Interface</x:t>
+          <x:t xml:space="preserve">Parameter Edit Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D87" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Print Stamp (Switch)</x:t>
+          <x:t xml:space="preserve">Option Parameter (Dropdown)</x:t>
         </x:is>
       </x:c>
       <x:c r="E87" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">是否列印印章</x:t>
+          <x:t xml:space="preserve">選項參數</x:t>
         </x:is>
       </x:c>
       <x:c r="F87" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">控制單據顯示公司印章</x:t>
+          <x:t xml:space="preserve">從固定選項選擇</x:t>
         </x:is>
       </x:c>
       <x:c r="G87" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">true／false</x:t>
+          <x:t xml:space="preserve">Enum</x:t>
         </x:is>
       </x:c>
       <x:c r="H87" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">預設否</x:t>
+          <x:t xml:space="preserve">宣告的選項</x:t>
         </x:is>
       </x:c>
       <x:c r="I87" s="2" t="inlineStr">
@@ -12042,47 +12042,47 @@
     <x:row r="88">
       <x:c r="A88" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.56.10</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.55.6</x:t>
         </x:is>
       </x:c>
       <x:c r="B88" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.56</x:t>
+          <x:t xml:space="preserve">4.4.1.8.55</x:t>
         </x:is>
       </x:c>
       <x:c r="C88" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Print Settings Edit Interface</x:t>
+          <x:t xml:space="preserve">Parameter Edit Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D88" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Header Preview (Panel)</x:t>
+          <x:t xml:space="preserve">Restore Default (Button)</x:t>
         </x:is>
       </x:c>
       <x:c r="E88" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">抬頭預覽</x:t>
+          <x:t xml:space="preserve">恢復預設</x:t>
         </x:is>
       </x:c>
       <x:c r="F88" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">保存前確認版面</x:t>
+          <x:t xml:space="preserve">把欄位設回預設值</x:t>
         </x:is>
       </x:c>
       <x:c r="G88" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">唯讀</x:t>
+          <x:t xml:space="preserve">Button</x:t>
         </x:is>
       </x:c>
       <x:c r="H88" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">依草稿即時更新</x:t>
+          <x:t xml:space="preserve">需 EDIT；保存後才生效</x:t>
         </x:is>
       </x:c>
       <x:c r="I88" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.56.1, REQ_IO_A8.56.2, REQ_IO_A8.56.3, REQ_IO_A8.56.4, REQ_IO_A8.56.5, REQ_IO_A8.56.8, REQ_IO_A8.56.9</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.55.1, REQ_IO_A8.55.2, REQ_IO_A8.55.3, REQ_IO_A8.55.4, REQ_IO_A8.55.5</x:t>
         </x:is>
       </x:c>
       <x:c r="J88" s="2" t="inlineStr">
@@ -12099,17 +12099,17 @@
     <x:row r="89">
       <x:c r="A89" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.56.11</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.55.7</x:t>
         </x:is>
       </x:c>
       <x:c r="B89" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.56</x:t>
+          <x:t xml:space="preserve">4.4.1.8.55</x:t>
         </x:is>
       </x:c>
       <x:c r="C89" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Print Settings Edit Interface</x:t>
+          <x:t xml:space="preserve">Parameter Edit Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D89" s="2" t="inlineStr">
@@ -12124,7 +12124,7 @@
       </x:c>
       <x:c r="F89" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">批次保存有修改的列印設定</x:t>
+          <x:t xml:space="preserve">批次保存有修改的參數</x:t>
         </x:is>
       </x:c>
       <x:c r="G89" s="2" t="inlineStr">
@@ -12139,7 +12139,7 @@
       </x:c>
       <x:c r="I89" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.56.1, REQ_IO_A8.56.2, REQ_IO_A8.56.3, REQ_IO_A8.56.4, REQ_IO_A8.56.5, REQ_IO_A8.56.6, REQ_IO_A8.56.7, REQ_IO_A8.56.8, REQ_IO_A8.56.9</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.55.1, REQ_IO_A8.55.2, REQ_IO_A8.55.3, REQ_IO_A8.55.4, REQ_IO_A8.55.5</x:t>
         </x:is>
       </x:c>
       <x:c r="J89" s="2" t="inlineStr">
@@ -12156,42 +12156,42 @@
     <x:row r="90">
       <x:c r="A90" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.57.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.56.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B90" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.57</x:t>
+          <x:t xml:space="preserve">4.4.1.8.56</x:t>
         </x:is>
       </x:c>
       <x:c r="C90" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Logo &amp; Stamp Edit Interface</x:t>
+          <x:t xml:space="preserve">Print Settings Edit Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D90" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Logo Preview (Image)</x:t>
+          <x:t xml:space="preserve">Company Name (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E90" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Logo 預覽</x:t>
+          <x:t xml:space="preserve">列印公司名稱</x:t>
         </x:is>
       </x:c>
       <x:c r="F90" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">確認目前的 Logo</x:t>
+          <x:t xml:space="preserve">單據抬頭</x:t>
         </x:is>
       </x:c>
       <x:c r="G90" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">唯讀圖片</x:t>
+          <x:t xml:space="preserve">Text</x:t>
         </x:is>
       </x:c>
       <x:c r="H90" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">PNG／JPEG</x:t>
+          <x:t xml:space="preserve">最多 100 字；空白時用公司主檔名稱</x:t>
         </x:is>
       </x:c>
       <x:c r="I90" s="2" t="inlineStr">
@@ -12213,42 +12213,42 @@
     <x:row r="91">
       <x:c r="A91" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.57.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.56.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B91" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.57</x:t>
+          <x:t xml:space="preserve">4.4.1.8.56</x:t>
         </x:is>
       </x:c>
       <x:c r="C91" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Logo &amp; Stamp Edit Interface</x:t>
+          <x:t xml:space="preserve">Print Settings Edit Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D91" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Stamp Preview (Image)</x:t>
+          <x:t xml:space="preserve">Address (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E91" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">印章預覽</x:t>
+          <x:t xml:space="preserve">地址</x:t>
         </x:is>
       </x:c>
       <x:c r="F91" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">確認目前的印章</x:t>
+          <x:t xml:space="preserve">單據抬頭</x:t>
         </x:is>
       </x:c>
       <x:c r="G91" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">唯讀圖片</x:t>
+          <x:t xml:space="preserve">Text</x:t>
         </x:is>
       </x:c>
       <x:c r="H91" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">PNG／JPEG</x:t>
+          <x:t xml:space="preserve">最多 200 字</x:t>
         </x:is>
       </x:c>
       <x:c r="I91" s="2" t="inlineStr">
@@ -12270,47 +12270,47 @@
     <x:row r="92">
       <x:c r="A92" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.57.3</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.56.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B92" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.57</x:t>
+          <x:t xml:space="preserve">4.4.1.8.56</x:t>
         </x:is>
       </x:c>
       <x:c r="C92" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Logo &amp; Stamp Edit Interface</x:t>
+          <x:t xml:space="preserve">Print Settings Edit Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D92" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Image Details (Text)</x:t>
+          <x:t xml:space="preserve">Postal Code (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E92" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">檔案資料</x:t>
+          <x:t xml:space="preserve">郵遞區號</x:t>
         </x:is>
       </x:c>
       <x:c r="F92" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">顯示檔名、大小、寬高、上傳時間</x:t>
+          <x:t xml:space="preserve">單據抬頭</x:t>
         </x:is>
       </x:c>
       <x:c r="G92" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">唯讀</x:t>
+          <x:t xml:space="preserve">Text</x:t>
         </x:is>
       </x:c>
       <x:c r="H92" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">-</x:t>
+          <x:t xml:space="preserve">最多 10 字</x:t>
         </x:is>
       </x:c>
       <x:c r="I92" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.57.1, REQ_IO_A8.57.2</x:t>
+          <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
       <x:c r="J92" s="2" t="inlineStr">
@@ -12327,47 +12327,47 @@
     <x:row r="93">
       <x:c r="A93" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.57.4</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.56.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B93" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.57</x:t>
+          <x:t xml:space="preserve">4.4.1.8.56</x:t>
         </x:is>
       </x:c>
       <x:c r="C93" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Logo &amp; Stamp Edit Interface</x:t>
+          <x:t xml:space="preserve">Print Settings Edit Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D93" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Upload / Replace (Button)</x:t>
+          <x:t xml:space="preserve">Phone (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E93" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">上傳／替換</x:t>
+          <x:t xml:space="preserve">電話</x:t>
         </x:is>
       </x:c>
       <x:c r="F93" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">選擇圖片檔並上傳</x:t>
+          <x:t xml:space="preserve">單據抬頭</x:t>
         </x:is>
       </x:c>
       <x:c r="G93" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">File（accept="image/png,image/jpeg"）</x:t>
+          <x:t xml:space="preserve">Text</x:t>
         </x:is>
       </x:c>
       <x:c r="H93" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">需 EDIT；PNG／JPEG、1 MB、寬高 16–2048 像素</x:t>
+          <x:t xml:space="preserve">最多 30 字</x:t>
         </x:is>
       </x:c>
       <x:c r="I93" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.57.1, REQ_IO_A8.57.2</x:t>
+          <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
       <x:c r="J93" s="2" t="inlineStr">
@@ -12384,47 +12384,47 @@
     <x:row r="94">
       <x:c r="A94" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.57.5</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.56.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B94" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.57</x:t>
+          <x:t xml:space="preserve">4.4.1.8.56</x:t>
         </x:is>
       </x:c>
       <x:c r="C94" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Logo &amp; Stamp Edit Interface</x:t>
+          <x:t xml:space="preserve">Print Settings Edit Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D94" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Delete (Button)</x:t>
+          <x:t xml:space="preserve">Fax (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E94" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">刪除</x:t>
+          <x:t xml:space="preserve">傳真</x:t>
         </x:is>
       </x:c>
       <x:c r="F94" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">刪除圖片</x:t>
+          <x:t xml:space="preserve">單據抬頭</x:t>
         </x:is>
       </x:c>
       <x:c r="G94" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Button</x:t>
+          <x:t xml:space="preserve">Text</x:t>
         </x:is>
       </x:c>
       <x:c r="H94" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">需 EDIT；確認後帶 version 刪除</x:t>
+          <x:t xml:space="preserve">最多 30 字</x:t>
         </x:is>
       </x:c>
       <x:c r="I94" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.57.1, REQ_IO_A8.57.2</x:t>
+          <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
       <x:c r="J94" s="2" t="inlineStr">
@@ -12441,42 +12441,42 @@
     <x:row r="95">
       <x:c r="A95" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.58.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.56.6</x:t>
         </x:is>
       </x:c>
       <x:c r="B95" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.58</x:t>
+          <x:t xml:space="preserve">4.4.1.8.56</x:t>
         </x:is>
       </x:c>
       <x:c r="C95" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Company View Interface</x:t>
+          <x:t xml:space="preserve">Print Settings Edit Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D95" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Company Code (Input)</x:t>
+          <x:t xml:space="preserve">Purchase Order Footer (Textarea)</x:t>
         </x:is>
       </x:c>
       <x:c r="E95" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">公司代碼</x:t>
+          <x:t xml:space="preserve">採購單頁尾備註</x:t>
         </x:is>
       </x:c>
       <x:c r="F95" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">唯一識別公司</x:t>
+          <x:t xml:space="preserve">列印在採購單底部</x:t>
         </x:is>
       </x:c>
       <x:c r="G95" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">VARCHAR(30)</x:t>
+          <x:t xml:space="preserve">Text（可多行）</x:t>
         </x:is>
       </x:c>
       <x:c r="H95" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1–30 字元；ASCII 英文、數字、-、_</x:t>
+          <x:t xml:space="preserve">最多 500 字</x:t>
         </x:is>
       </x:c>
       <x:c r="I95" s="2" t="inlineStr">
@@ -12498,42 +12498,42 @@
     <x:row r="96">
       <x:c r="A96" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.58.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.56.7</x:t>
         </x:is>
       </x:c>
       <x:c r="B96" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.58</x:t>
+          <x:t xml:space="preserve">4.4.1.8.56</x:t>
         </x:is>
       </x:c>
       <x:c r="C96" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Company View Interface</x:t>
+          <x:t xml:space="preserve">Print Settings Edit Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D96" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Company Name (Input)</x:t>
+          <x:t xml:space="preserve">Sales Delivery Footer (Textarea)</x:t>
         </x:is>
       </x:c>
       <x:c r="E96" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">公司名稱</x:t>
+          <x:t xml:space="preserve">銷售出貨單頁尾備註</x:t>
         </x:is>
       </x:c>
       <x:c r="F96" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">顯示公司</x:t>
+          <x:t xml:space="preserve">列印在出貨單底部</x:t>
         </x:is>
       </x:c>
       <x:c r="G96" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">NVARCHAR(200)</x:t>
+          <x:t xml:space="preserve">Text（可多行）</x:t>
         </x:is>
       </x:c>
       <x:c r="H96" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1–200 字元</x:t>
+          <x:t xml:space="preserve">最多 500 字</x:t>
         </x:is>
       </x:c>
       <x:c r="I96" s="2" t="inlineStr">
@@ -12555,42 +12555,42 @@
     <x:row r="97">
       <x:c r="A97" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.59.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.56.8</x:t>
         </x:is>
       </x:c>
       <x:c r="B97" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.59</x:t>
+          <x:t xml:space="preserve">4.4.1.8.56</x:t>
         </x:is>
       </x:c>
       <x:c r="C97" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Branch View Interface</x:t>
+          <x:t xml:space="preserve">Print Settings Edit Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D97" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Branch Code (Input)</x:t>
+          <x:t xml:space="preserve">Print Logo (Switch)</x:t>
         </x:is>
       </x:c>
       <x:c r="E97" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">分店代碼</x:t>
+          <x:t xml:space="preserve">是否列印 Logo</x:t>
         </x:is>
       </x:c>
       <x:c r="F97" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">公司內唯一</x:t>
+          <x:t xml:space="preserve">控制單據顯示 Logo</x:t>
         </x:is>
       </x:c>
       <x:c r="G97" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">VARCHAR(30)</x:t>
+          <x:t xml:space="preserve">true／false</x:t>
         </x:is>
       </x:c>
       <x:c r="H97" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1–30 字元；ASCII 英文、數字、-、_</x:t>
+          <x:t xml:space="preserve">預設否</x:t>
         </x:is>
       </x:c>
       <x:c r="I97" s="2" t="inlineStr">
@@ -12612,42 +12612,42 @@
     <x:row r="98">
       <x:c r="A98" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.60.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.56.9</x:t>
         </x:is>
       </x:c>
       <x:c r="B98" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.60</x:t>
+          <x:t xml:space="preserve">4.4.1.8.56</x:t>
         </x:is>
       </x:c>
       <x:c r="C98" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Department View Interface</x:t>
+          <x:t xml:space="preserve">Print Settings Edit Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D98" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Department Code (Input)</x:t>
+          <x:t xml:space="preserve">Print Stamp (Switch)</x:t>
         </x:is>
       </x:c>
       <x:c r="E98" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">部門代碼</x:t>
+          <x:t xml:space="preserve">是否列印印章</x:t>
         </x:is>
       </x:c>
       <x:c r="F98" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">公司內唯一</x:t>
+          <x:t xml:space="preserve">控制單據顯示公司印章</x:t>
         </x:is>
       </x:c>
       <x:c r="G98" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">VARCHAR(30)</x:t>
+          <x:t xml:space="preserve">true／false</x:t>
         </x:is>
       </x:c>
       <x:c r="H98" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1–30 字元；ASCII 英文、數字、-、_</x:t>
+          <x:t xml:space="preserve">預設否</x:t>
         </x:is>
       </x:c>
       <x:c r="I98" s="2" t="inlineStr">
@@ -12669,47 +12669,47 @@
     <x:row r="99">
       <x:c r="A99" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.60.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.56.10</x:t>
         </x:is>
       </x:c>
       <x:c r="B99" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.60</x:t>
+          <x:t xml:space="preserve">4.4.1.8.56</x:t>
         </x:is>
       </x:c>
       <x:c r="C99" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Department View Interface</x:t>
+          <x:t xml:space="preserve">Print Settings Edit Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D99" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Parent Department (Dropdown)</x:t>
+          <x:t xml:space="preserve">Header Preview (Panel)</x:t>
         </x:is>
       </x:c>
       <x:c r="E99" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">上級部門</x:t>
+          <x:t xml:space="preserve">抬頭預覽</x:t>
         </x:is>
       </x:c>
       <x:c r="F99" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">建立層級</x:t>
+          <x:t xml:space="preserve">保存前確認版面</x:t>
         </x:is>
       </x:c>
       <x:c r="G99" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">bigint ID</x:t>
+          <x:t xml:space="preserve">唯讀</x:t>
         </x:is>
       </x:c>
       <x:c r="H99" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">同公司啟用部門</x:t>
+          <x:t xml:space="preserve">依草稿即時更新</x:t>
         </x:is>
       </x:c>
       <x:c r="I99" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">None</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.56.1, REQ_IO_A8.56.2, REQ_IO_A8.56.3, REQ_IO_A8.56.4, REQ_IO_A8.56.5, REQ_IO_A8.56.8, REQ_IO_A8.56.9</x:t>
         </x:is>
       </x:c>
       <x:c r="J99" s="2" t="inlineStr">
@@ -12726,47 +12726,47 @@
     <x:row r="100">
       <x:c r="A100" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.61.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.56.11</x:t>
         </x:is>
       </x:c>
       <x:c r="B100" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.61</x:t>
+          <x:t xml:space="preserve">4.4.1.8.56</x:t>
         </x:is>
       </x:c>
       <x:c r="C100" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">User Identity Create Interface</x:t>
+          <x:t xml:space="preserve">Print Settings Edit Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D100" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Username (Input)</x:t>
+          <x:t xml:space="preserve">Save (Button)</x:t>
         </x:is>
       </x:c>
       <x:c r="E100" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">帳號</x:t>
+          <x:t xml:space="preserve">保存</x:t>
         </x:is>
       </x:c>
       <x:c r="F100" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">建立登入身分</x:t>
+          <x:t xml:space="preserve">批次保存有修改的列印設定</x:t>
         </x:is>
       </x:c>
       <x:c r="G100" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ASCII text</x:t>
+          <x:t xml:space="preserve">Button</x:t>
         </x:is>
       </x:c>
       <x:c r="H100" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">去除前後空白後 3–100 字元，字母／數字／點／底線／連字號；不分大小寫唯一</x:t>
+          <x:t xml:space="preserve">需 EDIT；只送有修改的項目並帶 version</x:t>
         </x:is>
       </x:c>
       <x:c r="I100" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">None</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.56.1, REQ_IO_A8.56.2, REQ_IO_A8.56.3, REQ_IO_A8.56.4, REQ_IO_A8.56.5, REQ_IO_A8.56.6, REQ_IO_A8.56.7, REQ_IO_A8.56.8, REQ_IO_A8.56.9</x:t>
         </x:is>
       </x:c>
       <x:c r="J100" s="2" t="inlineStr">
@@ -12783,47 +12783,47 @@
     <x:row r="101">
       <x:c r="A101" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.61.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.57.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B101" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.61</x:t>
+          <x:t xml:space="preserve">4.4.1.8.57</x:t>
         </x:is>
       </x:c>
       <x:c r="C101" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">User Identity Create Interface</x:t>
+          <x:t xml:space="preserve">Logo &amp; Stamp Edit Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D101" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Password (Input)</x:t>
+          <x:t xml:space="preserve">Logo Preview (Image)</x:t>
         </x:is>
       </x:c>
       <x:c r="E101" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">初始密碼</x:t>
+          <x:t xml:space="preserve">Logo 預覽</x:t>
         </x:is>
       </x:c>
       <x:c r="F101" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">依目前政策驗證，提交後清空</x:t>
+          <x:t xml:space="preserve">確認目前的 Logo</x:t>
         </x:is>
       </x:c>
       <x:c r="G101" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Password，autocomplete=new-password</x:t>
+          <x:t xml:space="preserve">唯讀圖片</x:t>
         </x:is>
       </x:c>
       <x:c r="H101" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">必填，最多 128 字元；其餘依政策（預設 12 字元以上，含大小寫、數字、符號），不符時顯示政策說明</x:t>
+          <x:t xml:space="preserve">PNG／JPEG</x:t>
         </x:is>
       </x:c>
       <x:c r="I101" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.61.3</x:t>
+          <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
       <x:c r="J101" s="2" t="inlineStr">
@@ -12840,47 +12840,47 @@
     <x:row r="102">
       <x:c r="A102" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.61.3</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.57.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B102" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.61</x:t>
+          <x:t xml:space="preserve">4.4.1.8.57</x:t>
         </x:is>
       </x:c>
       <x:c r="C102" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">User Identity Create Interface</x:t>
+          <x:t xml:space="preserve">Logo &amp; Stamp Edit Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D102" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Confirm Password (Input)</x:t>
+          <x:t xml:space="preserve">Stamp Preview (Image)</x:t>
         </x:is>
       </x:c>
       <x:c r="E102" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">確認密碼</x:t>
+          <x:t xml:space="preserve">印章預覽</x:t>
         </x:is>
       </x:c>
       <x:c r="F102" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">防止輸入錯誤</x:t>
+          <x:t xml:space="preserve">確認目前的印章</x:t>
         </x:is>
       </x:c>
       <x:c r="G102" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Password</x:t>
+          <x:t xml:space="preserve">唯讀圖片</x:t>
         </x:is>
       </x:c>
       <x:c r="H102" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">須與密碼相同</x:t>
+          <x:t xml:space="preserve">PNG／JPEG</x:t>
         </x:is>
       </x:c>
       <x:c r="I102" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.61.2</x:t>
+          <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
       <x:c r="J102" s="2" t="inlineStr">
@@ -12897,47 +12897,47 @@
     <x:row r="103">
       <x:c r="A103" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.62.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.57.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B103" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.62</x:t>
+          <x:t xml:space="preserve">4.4.1.8.57</x:t>
         </x:is>
       </x:c>
       <x:c r="C103" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Login Interface</x:t>
+          <x:t xml:space="preserve">Logo &amp; Stamp Edit Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D103" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Username (Input)</x:t>
+          <x:t xml:space="preserve">Image Details (Text)</x:t>
         </x:is>
       </x:c>
       <x:c r="E103" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">帳號</x:t>
+          <x:t xml:space="preserve">檔案資料</x:t>
         </x:is>
       </x:c>
       <x:c r="F103" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">登入身分</x:t>
+          <x:t xml:space="preserve">顯示檔名、大小、寬高、上傳時間</x:t>
         </x:is>
       </x:c>
       <x:c r="G103" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Text，autocomplete=username</x:t>
+          <x:t xml:space="preserve">唯讀</x:t>
         </x:is>
       </x:c>
       <x:c r="H103" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">必填、非空白，最多 100 字元；送出前去除前後空白</x:t>
+          <x:t xml:space="preserve">-</x:t>
         </x:is>
       </x:c>
       <x:c r="I103" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">None</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.57.1, REQ_IO_A8.57.2</x:t>
         </x:is>
       </x:c>
       <x:c r="J103" s="2" t="inlineStr">
@@ -12954,47 +12954,47 @@
     <x:row r="104">
       <x:c r="A104" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.62.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.57.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B104" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.62</x:t>
+          <x:t xml:space="preserve">4.4.1.8.57</x:t>
         </x:is>
       </x:c>
       <x:c r="C104" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Login Interface</x:t>
+          <x:t xml:space="preserve">Logo &amp; Stamp Edit Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D104" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Password (Input)</x:t>
+          <x:t xml:space="preserve">Upload / Replace (Button)</x:t>
         </x:is>
       </x:c>
       <x:c r="E104" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">密碼</x:t>
+          <x:t xml:space="preserve">上傳／替換</x:t>
         </x:is>
       </x:c>
       <x:c r="F104" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">驗證身分</x:t>
+          <x:t xml:space="preserve">選擇圖片檔並上傳</x:t>
         </x:is>
       </x:c>
       <x:c r="G104" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Password，autocomplete=current-password</x:t>
+          <x:t xml:space="preserve">File（accept="image/png,image/jpeg"）</x:t>
         </x:is>
       </x:c>
       <x:c r="H104" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">必填，最多 128 字元；失敗後清空</x:t>
+          <x:t xml:space="preserve">需 EDIT；PNG／JPEG、1 MB、寬高 16–2048 像素</x:t>
         </x:is>
       </x:c>
       <x:c r="I104" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">None</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.57.1, REQ_IO_A8.57.2</x:t>
         </x:is>
       </x:c>
       <x:c r="J104" s="2" t="inlineStr">
@@ -13011,47 +13011,47 @@
     <x:row r="105">
       <x:c r="A105" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.62.3</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.57.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B105" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.62</x:t>
+          <x:t xml:space="preserve">4.4.1.8.57</x:t>
         </x:is>
       </x:c>
       <x:c r="C105" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Login Interface</x:t>
+          <x:t xml:space="preserve">Logo &amp; Stamp Edit Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D105" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Captcha Code (Input)</x:t>
+          <x:t xml:space="preserve">Delete (Button)</x:t>
         </x:is>
       </x:c>
       <x:c r="E105" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">驗證碼</x:t>
+          <x:t xml:space="preserve">刪除</x:t>
         </x:is>
       </x:c>
       <x:c r="F105" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">防自動化登入</x:t>
+          <x:t xml:space="preserve">刪除圖片</x:t>
         </x:is>
       </x:c>
       <x:c r="G105" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">數字，inputmode=numeric</x:t>
+          <x:t xml:space="preserve">Button</x:t>
         </x:is>
       </x:c>
       <x:c r="H105" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4–6 位數字（非數字自動移除）</x:t>
+          <x:t xml:space="preserve">需 EDIT；確認後帶 version 刪除</x:t>
         </x:is>
       </x:c>
       <x:c r="I105" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.62.4</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.57.1, REQ_IO_A8.57.2</x:t>
         </x:is>
       </x:c>
       <x:c r="J105" s="2" t="inlineStr">
@@ -13068,42 +13068,42 @@
     <x:row r="106">
       <x:c r="A106" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.62.4</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.58.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B106" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.62</x:t>
+          <x:t xml:space="preserve">4.4.1.8.58</x:t>
         </x:is>
       </x:c>
       <x:c r="C106" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Login Interface</x:t>
+          <x:t xml:space="preserve">Company View Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D106" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Captcha Image (Button)</x:t>
+          <x:t xml:space="preserve">Company Code (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E106" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">驗證碼圖片</x:t>
+          <x:t xml:space="preserve">公司代碼</x:t>
         </x:is>
       </x:c>
       <x:c r="F106" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">顯示題目，點擊換圖</x:t>
+          <x:t xml:space="preserve">唯一識別公司</x:t>
         </x:is>
       </x:c>
       <x:c r="G106" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SVG data URI</x:t>
+          <x:t xml:space="preserve">VARCHAR(30)</x:t>
         </x:is>
       </x:c>
       <x:c r="H106" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">每次送出失敗後自動換新</x:t>
+          <x:t xml:space="preserve">1–30 字元；ASCII 英文、數字、-、_</x:t>
         </x:is>
       </x:c>
       <x:c r="I106" s="2" t="inlineStr">
@@ -13125,42 +13125,42 @@
     <x:row r="107">
       <x:c r="A107" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.62.5</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.58.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B107" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.62</x:t>
+          <x:t xml:space="preserve">4.4.1.8.58</x:t>
         </x:is>
       </x:c>
       <x:c r="C107" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Login Interface</x:t>
+          <x:t xml:space="preserve">Company View Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D107" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Sign In (Button)</x:t>
+          <x:t xml:space="preserve">Company Name (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E107" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">登入</x:t>
+          <x:t xml:space="preserve">公司名稱</x:t>
         </x:is>
       </x:c>
       <x:c r="F107" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">送出</x:t>
+          <x:t xml:space="preserve">顯示公司</x:t>
         </x:is>
       </x:c>
       <x:c r="G107" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Button</x:t>
+          <x:t xml:space="preserve">NVARCHAR(200)</x:t>
         </x:is>
       </x:c>
       <x:c r="H107" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">送出中顯示載入狀態，不可重複送出</x:t>
+          <x:t xml:space="preserve">1–200 字元</x:t>
         </x:is>
       </x:c>
       <x:c r="I107" s="2" t="inlineStr">
@@ -13182,42 +13182,42 @@
     <x:row r="108">
       <x:c r="A108" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.62.6</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.59.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B108" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.62</x:t>
+          <x:t xml:space="preserve">4.4.1.8.59</x:t>
         </x:is>
       </x:c>
       <x:c r="C108" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Login Interface</x:t>
+          <x:t xml:space="preserve">Branch View Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D108" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Error Message (Alert)</x:t>
+          <x:t xml:space="preserve">Branch Code (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E108" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">錯誤訊息</x:t>
+          <x:t xml:space="preserve">分店代碼</x:t>
         </x:is>
       </x:c>
       <x:c r="F108" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">顯示 errors.&lt;errorCode&gt;</x:t>
+          <x:t xml:space="preserve">公司內唯一</x:t>
         </x:is>
       </x:c>
       <x:c r="G108" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Text</x:t>
+          <x:t xml:space="preserve">VARCHAR(30)</x:t>
         </x:is>
       </x:c>
       <x:c r="H108" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">INVALID_CREDENTIALS／CAPTCHA_INVALID／PASSWORD_EXPIRED／VALIDATION_FAILED／網路／未知</x:t>
+          <x:t xml:space="preserve">1–30 字元；ASCII 英文、數字、-、_</x:t>
         </x:is>
       </x:c>
       <x:c r="I108" s="2" t="inlineStr">
@@ -13239,42 +13239,42 @@
     <x:row r="109">
       <x:c r="A109" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.63.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.60.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B109" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.63</x:t>
+          <x:t xml:space="preserve">4.4.1.8.60</x:t>
         </x:is>
       </x:c>
       <x:c r="C109" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">User Maintenance Interface</x:t>
+          <x:t xml:space="preserve">Department View Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D109" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Keyword (Input)</x:t>
+          <x:t xml:space="preserve">Department Code (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E109" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">搜尋帳號</x:t>
+          <x:t xml:space="preserve">部門代碼</x:t>
         </x:is>
       </x:c>
       <x:c r="F109" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">篩選列表</x:t>
+          <x:t xml:space="preserve">公司內唯一</x:t>
         </x:is>
       </x:c>
       <x:c r="G109" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Text</x:t>
+          <x:t xml:space="preserve">VARCHAR(30)</x:t>
         </x:is>
       </x:c>
       <x:c r="H109" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">去除前後空白，不分大小寫</x:t>
+          <x:t xml:space="preserve">1–30 字元；ASCII 英文、數字、-、_</x:t>
         </x:is>
       </x:c>
       <x:c r="I109" s="2" t="inlineStr">
@@ -13296,42 +13296,42 @@
     <x:row r="110">
       <x:c r="A110" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.63.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.60.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B110" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.63</x:t>
+          <x:t xml:space="preserve">4.4.1.8.60</x:t>
         </x:is>
       </x:c>
       <x:c r="C110" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">User Maintenance Interface</x:t>
+          <x:t xml:space="preserve">Department View Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D110" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Status (Tag)</x:t>
+          <x:t xml:space="preserve">Parent Department (Dropdown)</x:t>
         </x:is>
       </x:c>
       <x:c r="E110" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">狀態</x:t>
+          <x:t xml:space="preserve">上級部門</x:t>
         </x:is>
       </x:c>
       <x:c r="F110" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">顯示啟用、鎖定、密碼過期</x:t>
+          <x:t xml:space="preserve">建立層級</x:t>
         </x:is>
       </x:c>
       <x:c r="G110" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Tag</x:t>
+          <x:t xml:space="preserve">bigint ID</x:t>
         </x:is>
       </x:c>
       <x:c r="H110" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">啟用／停用；已鎖定；密碼已過期</x:t>
+          <x:t xml:space="preserve">同公司啟用部門</x:t>
         </x:is>
       </x:c>
       <x:c r="I110" s="2" t="inlineStr">
@@ -13353,42 +13353,42 @@
     <x:row r="111">
       <x:c r="A111" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.63.3</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.61.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B111" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.63</x:t>
+          <x:t xml:space="preserve">4.4.1.8.61</x:t>
         </x:is>
       </x:c>
       <x:c r="C111" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">User Maintenance Interface</x:t>
+          <x:t xml:space="preserve">User Identity Create Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D111" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Activate / Deactivate (Button)</x:t>
+          <x:t xml:space="preserve">Username (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E111" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">啟用／停用</x:t>
+          <x:t xml:space="preserve">帳號</x:t>
         </x:is>
       </x:c>
       <x:c r="F111" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">切換帳號狀態</x:t>
+          <x:t xml:space="preserve">建立登入身分</x:t>
         </x:is>
       </x:c>
       <x:c r="G111" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Button</x:t>
+          <x:t xml:space="preserve">ASCII text</x:t>
         </x:is>
       </x:c>
       <x:c r="H111" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">帶讀取時的 version；不可停用自己</x:t>
+          <x:t xml:space="preserve">去除前後空白後 3–100 字元，字母／數字／點／底線／連字號；不分大小寫唯一</x:t>
         </x:is>
       </x:c>
       <x:c r="I111" s="2" t="inlineStr">
@@ -13410,47 +13410,47 @@
     <x:row r="112">
       <x:c r="A112" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.63.4</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.61.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B112" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.63</x:t>
+          <x:t xml:space="preserve">4.4.1.8.61</x:t>
         </x:is>
       </x:c>
       <x:c r="C112" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">User Maintenance Interface</x:t>
+          <x:t xml:space="preserve">User Identity Create Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D112" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Unlock (Button)</x:t>
+          <x:t xml:space="preserve">Password (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E112" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">解鎖</x:t>
+          <x:t xml:space="preserve">初始密碼</x:t>
         </x:is>
       </x:c>
       <x:c r="F112" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">清除鎖定</x:t>
+          <x:t xml:space="preserve">依目前政策驗證，提交後清空</x:t>
         </x:is>
       </x:c>
       <x:c r="G112" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Button</x:t>
+          <x:t xml:space="preserve">Password，autocomplete=new-password</x:t>
         </x:is>
       </x:c>
       <x:c r="H112" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">只在已鎖定時顯示</x:t>
+          <x:t xml:space="preserve">必填，最多 128 字元；其餘依政策（預設 12 字元以上，含大小寫、數字、符號），不符時顯示政策說明</x:t>
         </x:is>
       </x:c>
       <x:c r="I112" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">None</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.61.3</x:t>
         </x:is>
       </x:c>
       <x:c r="J112" s="2" t="inlineStr">
@@ -13467,42 +13467,42 @@
     <x:row r="113">
       <x:c r="A113" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.63.5</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.61.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B113" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.63</x:t>
+          <x:t xml:space="preserve">4.4.1.8.61</x:t>
         </x:is>
       </x:c>
       <x:c r="C113" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">User Maintenance Interface</x:t>
+          <x:t xml:space="preserve">User Identity Create Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D113" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Reset Password (Button)</x:t>
+          <x:t xml:space="preserve">Confirm Password (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E113" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">重設密碼</x:t>
+          <x:t xml:space="preserve">確認密碼</x:t>
         </x:is>
       </x:c>
       <x:c r="F113" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">開啟重設對話框</x:t>
+          <x:t xml:space="preserve">防止輸入錯誤</x:t>
         </x:is>
       </x:c>
       <x:c r="G113" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Button</x:t>
+          <x:t xml:space="preserve">Password</x:t>
         </x:is>
       </x:c>
       <x:c r="H113" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">新密碼依政策驗證，成功後清除鎖定並重新起算到期</x:t>
+          <x:t xml:space="preserve">須與密碼相同</x:t>
         </x:is>
       </x:c>
       <x:c r="I113" s="2" t="inlineStr">
@@ -13524,42 +13524,42 @@
     <x:row r="114">
       <x:c r="A114" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.64.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.62.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B114" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.64</x:t>
+          <x:t xml:space="preserve">4.4.1.8.62</x:t>
         </x:is>
       </x:c>
       <x:c r="C114" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Role Maintenance Interface</x:t>
+          <x:t xml:space="preserve">Login Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D114" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Role Code (Input)</x:t>
+          <x:t xml:space="preserve">Username (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E114" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">角色代碼</x:t>
+          <x:t xml:space="preserve">帳號</x:t>
         </x:is>
       </x:c>
       <x:c r="F114" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">全系統唯一識別角色</x:t>
+          <x:t xml:space="preserve">登入身分</x:t>
         </x:is>
       </x:c>
       <x:c r="G114" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">VARCHAR(50)</x:t>
+          <x:t xml:space="preserve">Text，autocomplete=username</x:t>
         </x:is>
       </x:c>
       <x:c r="H114" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1–50 字元；ASCII 英文、數字、-、_；保存為大寫；建立後不可修改</x:t>
+          <x:t xml:space="preserve">必填、非空白，最多 100 字元；送出前去除前後空白</x:t>
         </x:is>
       </x:c>
       <x:c r="I114" s="2" t="inlineStr">
@@ -13581,42 +13581,42 @@
     <x:row r="115">
       <x:c r="A115" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.64.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.62.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B115" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.64</x:t>
+          <x:t xml:space="preserve">4.4.1.8.62</x:t>
         </x:is>
       </x:c>
       <x:c r="C115" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Role Maintenance Interface</x:t>
+          <x:t xml:space="preserve">Login Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D115" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Role Name (Input)</x:t>
+          <x:t xml:space="preserve">Password (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E115" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">角色名稱</x:t>
+          <x:t xml:space="preserve">密碼</x:t>
         </x:is>
       </x:c>
       <x:c r="F115" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">顯示角色</x:t>
+          <x:t xml:space="preserve">驗證身分</x:t>
         </x:is>
       </x:c>
       <x:c r="G115" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">NVARCHAR(200)</x:t>
+          <x:t xml:space="preserve">Password，autocomplete=current-password</x:t>
         </x:is>
       </x:c>
       <x:c r="H115" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">去除空白後 1–200 字元</x:t>
+          <x:t xml:space="preserve">必填，最多 128 字元；失敗後清空</x:t>
         </x:is>
       </x:c>
       <x:c r="I115" s="2" t="inlineStr">
@@ -13638,47 +13638,47 @@
     <x:row r="116">
       <x:c r="A116" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.64.3</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.62.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B116" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.64</x:t>
+          <x:t xml:space="preserve">4.4.1.8.62</x:t>
         </x:is>
       </x:c>
       <x:c r="C116" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Role Maintenance Interface</x:t>
+          <x:t xml:space="preserve">Login Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D116" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Data Scope (Dropdown)</x:t>
+          <x:t xml:space="preserve">Captcha Code (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E116" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">資料範圍</x:t>
+          <x:t xml:space="preserve">驗證碼</x:t>
         </x:is>
       </x:c>
       <x:c r="F116" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">決定可見單據範圍</x:t>
+          <x:t xml:space="preserve">防自動化登入</x:t>
         </x:is>
       </x:c>
       <x:c r="G116" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Self／Department／Branch／Company</x:t>
+          <x:t xml:space="preserve">數字，inputmode=numeric</x:t>
         </x:is>
       </x:c>
       <x:c r="H116" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">必選，預設本人</x:t>
+          <x:t xml:space="preserve">4–6 位數字（非數字自動移除）</x:t>
         </x:is>
       </x:c>
       <x:c r="I116" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">None</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.62.4</x:t>
         </x:is>
       </x:c>
       <x:c r="J116" s="2" t="inlineStr">
@@ -13695,47 +13695,47 @@
     <x:row r="117">
       <x:c r="A117" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.64.4</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.62.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B117" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.64</x:t>
+          <x:t xml:space="preserve">4.4.1.8.62</x:t>
         </x:is>
       </x:c>
       <x:c r="C117" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Role Maintenance Interface</x:t>
+          <x:t xml:space="preserve">Login Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D117" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Full Access (Checkbox)</x:t>
+          <x:t xml:space="preserve">Captcha Image (Button)</x:t>
         </x:is>
       </x:c>
       <x:c r="E117" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">全權</x:t>
+          <x:t xml:space="preserve">驗證碼圖片</x:t>
         </x:is>
       </x:c>
       <x:c r="F117" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">擁有全部權限</x:t>
+          <x:t xml:space="preserve">顯示題目，點擊換圖</x:t>
         </x:is>
       </x:c>
       <x:c r="G117" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Boolean</x:t>
+          <x:t xml:space="preserve">SVG data URI</x:t>
         </x:is>
       </x:c>
       <x:c r="H117" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">勾選時權限清單停用</x:t>
+          <x:t xml:space="preserve">每次送出失敗後自動換新</x:t>
         </x:is>
       </x:c>
       <x:c r="I117" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.64.5</x:t>
+          <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
       <x:c r="J117" s="2" t="inlineStr">
@@ -13752,47 +13752,47 @@
     <x:row r="118">
       <x:c r="A118" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.64.5</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.62.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B118" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.64</x:t>
+          <x:t xml:space="preserve">4.4.1.8.62</x:t>
         </x:is>
       </x:c>
       <x:c r="C118" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Role Maintenance Interface</x:t>
+          <x:t xml:space="preserve">Login Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D118" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Permissions (Checkbox group)</x:t>
+          <x:t xml:space="preserve">Sign In (Button)</x:t>
         </x:is>
       </x:c>
       <x:c r="E118" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">權限</x:t>
+          <x:t xml:space="preserve">登入</x:t>
         </x:is>
       </x:c>
       <x:c r="F118" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">依模組勾選權限代碼</x:t>
+          <x:t xml:space="preserve">送出</x:t>
         </x:is>
       </x:c>
       <x:c r="G118" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">模組.資源.動作</x:t>
+          <x:t xml:space="preserve">Button</x:t>
         </x:is>
       </x:c>
       <x:c r="H118" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">只可選權限目錄內的代碼；模組可全選</x:t>
+          <x:t xml:space="preserve">送出中顯示載入狀態，不可重複送出</x:t>
         </x:is>
       </x:c>
       <x:c r="I118" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.64.4</x:t>
+          <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
       <x:c r="J118" s="2" t="inlineStr">
@@ -13809,42 +13809,42 @@
     <x:row r="119">
       <x:c r="A119" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.64.6</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.62.6</x:t>
         </x:is>
       </x:c>
       <x:c r="B119" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.64</x:t>
+          <x:t xml:space="preserve">4.4.1.8.62</x:t>
         </x:is>
       </x:c>
       <x:c r="C119" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Role Maintenance Interface</x:t>
+          <x:t xml:space="preserve">Login Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D119" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Delete (Button)</x:t>
+          <x:t xml:space="preserve">Error Message (Alert)</x:t>
         </x:is>
       </x:c>
       <x:c r="E119" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">刪除</x:t>
+          <x:t xml:space="preserve">錯誤訊息</x:t>
         </x:is>
       </x:c>
       <x:c r="F119" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">軟刪除未使用的角色</x:t>
+          <x:t xml:space="preserve">顯示 errors.&lt;errorCode&gt;</x:t>
         </x:is>
       </x:c>
       <x:c r="G119" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Button + popconfirm</x:t>
+          <x:t xml:space="preserve">Text</x:t>
         </x:is>
       </x:c>
       <x:c r="H119" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">帶 version；使用中回 SYS.ROLE.IN_USE</x:t>
+          <x:t xml:space="preserve">INVALID_CREDENTIALS／CAPTCHA_INVALID／PASSWORD_EXPIRED／VALIDATION_FAILED／網路／未知</x:t>
         </x:is>
       </x:c>
       <x:c r="I119" s="2" t="inlineStr">
@@ -13866,47 +13866,47 @@
     <x:row r="120">
       <x:c r="A120" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.65.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.63.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B120" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.65</x:t>
+          <x:t xml:space="preserve">4.4.1.8.63</x:t>
         </x:is>
       </x:c>
       <x:c r="C120" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">User Permission Edit Interface（BlueWhale 4.4.1.8.26）</x:t>
+          <x:t xml:space="preserve">User Maintenance Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D120" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Company (Dropdown)</x:t>
+          <x:t xml:space="preserve">Keyword (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E120" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">公司</x:t>
+          <x:t xml:space="preserve">搜尋帳號</x:t>
         </x:is>
       </x:c>
       <x:c r="F120" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">選擇要設定的公司</x:t>
+          <x:t xml:space="preserve">篩選列表</x:t>
         </x:is>
       </x:c>
       <x:c r="G120" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">bigint ID</x:t>
+          <x:t xml:space="preserve">Text</x:t>
         </x:is>
       </x:c>
       <x:c r="H120" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">操作者可切換的公司</x:t>
+          <x:t xml:space="preserve">去除前後空白，不分大小寫</x:t>
         </x:is>
       </x:c>
       <x:c r="I120" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.65.2</x:t>
+          <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
       <x:c r="J120" s="2" t="inlineStr">
@@ -13923,47 +13923,47 @@
     <x:row r="121">
       <x:c r="A121" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.65.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.63.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B121" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.65</x:t>
+          <x:t xml:space="preserve">4.4.1.8.63</x:t>
         </x:is>
       </x:c>
       <x:c r="C121" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">User Permission Edit Interface（BlueWhale 4.4.1.8.26）</x:t>
+          <x:t xml:space="preserve">User Maintenance Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D121" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Branch / Department (Dropdown)</x:t>
+          <x:t xml:space="preserve">Status (Tag)</x:t>
         </x:is>
       </x:c>
       <x:c r="E121" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">分店／部門</x:t>
+          <x:t xml:space="preserve">狀態</x:t>
         </x:is>
       </x:c>
       <x:c r="F121" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">組織歸屬（資料範圍用）</x:t>
+          <x:t xml:space="preserve">顯示啟用、鎖定、密碼過期</x:t>
         </x:is>
       </x:c>
       <x:c r="G121" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">bigint ID，可清空</x:t>
+          <x:t xml:space="preserve">Tag</x:t>
         </x:is>
       </x:c>
       <x:c r="H121" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">所選公司的啟用分店／部門</x:t>
+          <x:t xml:space="preserve">啟用／停用；已鎖定；密碼已過期</x:t>
         </x:is>
       </x:c>
       <x:c r="I121" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.65.1</x:t>
+          <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
       <x:c r="J121" s="2" t="inlineStr">
@@ -13980,42 +13980,42 @@
     <x:row r="122">
       <x:c r="A122" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.65.3</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.63.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B122" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.65</x:t>
+          <x:t xml:space="preserve">4.4.1.8.63</x:t>
         </x:is>
       </x:c>
       <x:c r="C122" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">User Permission Edit Interface（BlueWhale 4.4.1.8.26）</x:t>
+          <x:t xml:space="preserve">User Maintenance Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D122" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Roles (Multi-select)</x:t>
+          <x:t xml:space="preserve">Activate / Deactivate (Button)</x:t>
         </x:is>
       </x:c>
       <x:c r="E122" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">角色</x:t>
+          <x:t xml:space="preserve">啟用／停用</x:t>
         </x:is>
       </x:c>
       <x:c r="F122" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">整組取代該公司的角色</x:t>
+          <x:t xml:space="preserve">切換帳號狀態</x:t>
         </x:is>
       </x:c>
       <x:c r="G122" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">bigint ID 陣列</x:t>
+          <x:t xml:space="preserve">Button</x:t>
         </x:is>
       </x:c>
       <x:c r="H122" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">啟用角色；可為空（無權限）</x:t>
+          <x:t xml:space="preserve">帶讀取時的 version；不可停用自己</x:t>
         </x:is>
       </x:c>
       <x:c r="I122" s="2" t="inlineStr">
@@ -14037,42 +14037,42 @@
     <x:row r="123">
       <x:c r="A123" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.65.4</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.63.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B123" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.65</x:t>
+          <x:t xml:space="preserve">4.4.1.8.63</x:t>
         </x:is>
       </x:c>
       <x:c r="C123" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">User Permission Edit Interface（BlueWhale 4.4.1.8.26）</x:t>
+          <x:t xml:space="preserve">User Maintenance Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D123" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Default Company (Checkbox)</x:t>
+          <x:t xml:space="preserve">Unlock (Button)</x:t>
         </x:is>
       </x:c>
       <x:c r="E123" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">預設公司</x:t>
+          <x:t xml:space="preserve">解鎖</x:t>
         </x:is>
       </x:c>
       <x:c r="F123" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">登入後預設的操作公司</x:t>
+          <x:t xml:space="preserve">清除鎖定</x:t>
         </x:is>
       </x:c>
       <x:c r="G123" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Boolean</x:t>
+          <x:t xml:space="preserve">Button</x:t>
         </x:is>
       </x:c>
       <x:c r="H123" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">設定後取消其他預設</x:t>
+          <x:t xml:space="preserve">只在已鎖定時顯示</x:t>
         </x:is>
       </x:c>
       <x:c r="I123" s="2" t="inlineStr">
@@ -14094,47 +14094,47 @@
     <x:row r="124">
       <x:c r="A124" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.65.5</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.63.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B124" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.65</x:t>
+          <x:t xml:space="preserve">4.4.1.8.63</x:t>
         </x:is>
       </x:c>
       <x:c r="C124" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">User Permission Edit Interface（BlueWhale 4.4.1.8.26）</x:t>
+          <x:t xml:space="preserve">User Maintenance Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D124" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Access Active (Checkbox)</x:t>
+          <x:t xml:space="preserve">Reset Password (Button)</x:t>
         </x:is>
       </x:c>
       <x:c r="E124" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">啟用存取</x:t>
+          <x:t xml:space="preserve">重設密碼</x:t>
         </x:is>
       </x:c>
       <x:c r="F124" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">停用後該公司不授權</x:t>
+          <x:t xml:space="preserve">開啟重設對話框</x:t>
         </x:is>
       </x:c>
       <x:c r="G124" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Boolean</x:t>
+          <x:t xml:space="preserve">Button</x:t>
         </x:is>
       </x:c>
       <x:c r="H124" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">不可停用自己</x:t>
+          <x:t xml:space="preserve">新密碼依政策驗證，成功後清除鎖定並重新起算到期</x:t>
         </x:is>
       </x:c>
       <x:c r="I124" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">None</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.61.2</x:t>
         </x:is>
       </x:c>
       <x:c r="J124" s="2" t="inlineStr">
@@ -14151,42 +14151,42 @@
     <x:row r="125">
       <x:c r="A125" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.66.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.64.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B125" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.66</x:t>
+          <x:t xml:space="preserve">4.4.1.8.64</x:t>
         </x:is>
       </x:c>
       <x:c r="C125" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Audit Log Query Interface</x:t>
+          <x:t xml:space="preserve">Role Maintenance Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D125" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Date Range (Date inputs + quick buttons)</x:t>
+          <x:t xml:space="preserve">Role Code (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E125" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">開始／結束日期</x:t>
+          <x:t xml:space="preserve">角色代碼</x:t>
         </x:is>
       </x:c>
       <x:c r="F125" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">限制查詢期間</x:t>
+          <x:t xml:space="preserve">全系統唯一識別角色</x:t>
         </x:is>
       </x:c>
       <x:c r="G125" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">yyyy-MM-dd</x:t>
+          <x:t xml:space="preserve">VARCHAR(50)</x:t>
         </x:is>
       </x:c>
       <x:c r="H125" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">含頭尾；結束日不可早於開始日；快選今天、近 7、30 天</x:t>
+          <x:t xml:space="preserve">1–50 字元；ASCII 英文、數字、-、_；保存為大寫；建立後不可修改</x:t>
         </x:is>
       </x:c>
       <x:c r="I125" s="2" t="inlineStr">
@@ -14208,42 +14208,42 @@
     <x:row r="126">
       <x:c r="A126" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.66.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.64.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B126" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.66</x:t>
+          <x:t xml:space="preserve">4.4.1.8.64</x:t>
         </x:is>
       </x:c>
       <x:c r="C126" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Audit Log Query Interface</x:t>
+          <x:t xml:space="preserve">Role Maintenance Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D126" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Category (Dropdown)</x:t>
+          <x:t xml:space="preserve">Role Name (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E126" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">類別</x:t>
+          <x:t xml:space="preserve">角色名稱</x:t>
         </x:is>
       </x:c>
       <x:c r="F126" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">區分資料變更與安全事件</x:t>
+          <x:t xml:space="preserve">顯示角色</x:t>
         </x:is>
       </x:c>
       <x:c r="G126" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">DATA／SECURITY</x:t>
+          <x:t xml:space="preserve">NVARCHAR(200)</x:t>
         </x:is>
       </x:c>
       <x:c r="H126" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">可清空</x:t>
+          <x:t xml:space="preserve">去除空白後 1–200 字元</x:t>
         </x:is>
       </x:c>
       <x:c r="I126" s="2" t="inlineStr">
@@ -14265,42 +14265,42 @@
     <x:row r="127">
       <x:c r="A127" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.66.3</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.64.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B127" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.66</x:t>
+          <x:t xml:space="preserve">4.4.1.8.64</x:t>
         </x:is>
       </x:c>
       <x:c r="C127" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Audit Log Query Interface</x:t>
+          <x:t xml:space="preserve">Role Maintenance Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D127" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Action (Dropdown)</x:t>
+          <x:t xml:space="preserve">Data Scope (Dropdown)</x:t>
         </x:is>
       </x:c>
       <x:c r="E127" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">操作</x:t>
+          <x:t xml:space="preserve">資料範圍</x:t>
         </x:is>
       </x:c>
       <x:c r="F127" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">依操作類型篩選</x:t>
+          <x:t xml:space="preserve">決定可見單據範圍</x:t>
         </x:is>
       </x:c>
       <x:c r="G127" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">CREATE、UPDATE、DELETE、VOID、APPROVE、POST、LOGIN、LOGIN_FAILED、MASTER_CODE_LOGIN、LOGOUT、PERMISSION_CHANGE、EXPORT</x:t>
+          <x:t xml:space="preserve">Self／Department／Branch／Company</x:t>
         </x:is>
       </x:c>
       <x:c r="H127" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">可清空</x:t>
+          <x:t xml:space="preserve">必選，預設本人</x:t>
         </x:is>
       </x:c>
       <x:c r="I127" s="2" t="inlineStr">
@@ -14322,47 +14322,47 @@
     <x:row r="128">
       <x:c r="A128" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.66.4</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.64.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B128" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.66</x:t>
+          <x:t xml:space="preserve">4.4.1.8.64</x:t>
         </x:is>
       </x:c>
       <x:c r="C128" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Audit Log Query Interface</x:t>
+          <x:t xml:space="preserve">Role Maintenance Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D128" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Table / Record ID (Input)</x:t>
+          <x:t xml:space="preserve">Full Access (Checkbox)</x:t>
         </x:is>
       </x:c>
       <x:c r="E128" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">資料表、記錄 ID</x:t>
+          <x:t xml:space="preserve">全權</x:t>
         </x:is>
       </x:c>
       <x:c r="F128" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">查看單據修改歷史</x:t>
+          <x:t xml:space="preserve">擁有全部權限</x:t>
         </x:is>
       </x:c>
       <x:c r="G128" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Text</x:t>
+          <x:t xml:space="preserve">Boolean</x:t>
         </x:is>
       </x:c>
       <x:c r="H128" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">資料表最多 128 字元、記錄 ID 最多 100 字元；去除前後空白</x:t>
+          <x:t xml:space="preserve">勾選時權限清單停用</x:t>
         </x:is>
       </x:c>
       <x:c r="I128" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.66.6</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.64.5</x:t>
         </x:is>
       </x:c>
       <x:c r="J128" s="2" t="inlineStr">
@@ -14379,47 +14379,47 @@
     <x:row r="129">
       <x:c r="A129" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.66.5</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.64.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B129" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.66</x:t>
+          <x:t xml:space="preserve">4.4.1.8.64</x:t>
         </x:is>
       </x:c>
       <x:c r="C129" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Audit Log Query Interface</x:t>
+          <x:t xml:space="preserve">Role Maintenance Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D129" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Changes (Expandable row)</x:t>
+          <x:t xml:space="preserve">Permissions (Checkbox group)</x:t>
         </x:is>
       </x:c>
       <x:c r="E129" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">欄位差異</x:t>
+          <x:t xml:space="preserve">權限</x:t>
         </x:is>
       </x:c>
       <x:c r="F129" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">顯示修改前後的值</x:t>
+          <x:t xml:space="preserve">依模組勾選權限代碼</x:t>
         </x:is>
       </x:c>
       <x:c r="G129" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">欄位／修改前／修改後</x:t>
+          <x:t xml:space="preserve">模組.資源.動作</x:t>
         </x:is>
       </x:c>
       <x:c r="H129" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">敏感欄位顯示 *；空值顯示「（空）」</x:t>
+          <x:t xml:space="preserve">只可選權限目錄內的代碼；模組可全選</x:t>
         </x:is>
       </x:c>
       <x:c r="I129" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">None</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.64.4</x:t>
         </x:is>
       </x:c>
       <x:c r="J129" s="2" t="inlineStr">
@@ -14436,47 +14436,47 @@
     <x:row r="130">
       <x:c r="A130" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.66.6</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.64.6</x:t>
         </x:is>
       </x:c>
       <x:c r="B130" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.66</x:t>
+          <x:t xml:space="preserve">4.4.1.8.64</x:t>
         </x:is>
       </x:c>
       <x:c r="C130" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Audit Log Query Interface</x:t>
+          <x:t xml:space="preserve">Role Maintenance Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D130" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Record History (Link / query string)</x:t>
+          <x:t xml:space="preserve">Delete (Button)</x:t>
         </x:is>
       </x:c>
       <x:c r="E130" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">修改歷史</x:t>
+          <x:t xml:space="preserve">刪除</x:t>
         </x:is>
       </x:c>
       <x:c r="F130" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">由單據或列開啟單筆記錄歷史</x:t>
+          <x:t xml:space="preserve">軟刪除未使用的角色</x:t>
         </x:is>
       </x:c>
       <x:c r="G130" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">?tableName=&amp;recordId=</x:t>
+          <x:t xml:space="preserve">Button + popconfirm</x:t>
         </x:is>
       </x:c>
       <x:c r="H130" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">安全事件沒有記錄 ID，不可開啟</x:t>
+          <x:t xml:space="preserve">帶 version；使用中回 SYS.ROLE.IN_USE</x:t>
         </x:is>
       </x:c>
       <x:c r="I130" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.66.4</x:t>
+          <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
       <x:c r="J130" s="2" t="inlineStr">
@@ -14493,47 +14493,47 @@
     <x:row r="131">
       <x:c r="A131" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.67.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.65.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B131" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.67</x:t>
+          <x:t xml:space="preserve">4.4.1.8.65</x:t>
         </x:is>
       </x:c>
       <x:c r="C131" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Document Number Rule Interface</x:t>
+          <x:t xml:space="preserve">User Permission Edit Interface（BlueWhale 4.4.1.8.26）</x:t>
         </x:is>
       </x:c>
       <x:c r="D131" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Document Type (Input)</x:t>
+          <x:t xml:space="preserve">Company (Dropdown)</x:t>
         </x:is>
       </x:c>
       <x:c r="E131" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">單據類型</x:t>
+          <x:t xml:space="preserve">公司</x:t>
         </x:is>
       </x:c>
       <x:c r="F131" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">識別規則所屬單據</x:t>
+          <x:t xml:space="preserve">選擇要設定的公司</x:t>
         </x:is>
       </x:c>
       <x:c r="G131" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">{PREFIX}.{DOCUMENT}，例如 SD.ORDER</x:t>
+          <x:t xml:space="preserve">bigint ID</x:t>
         </x:is>
       </x:c>
       <x:c r="H131" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">英文字母、數字、底線，最多 50 字；保存為大寫；公司內唯一；建立後不可修改</x:t>
+          <x:t xml:space="preserve">操作者可切換的公司</x:t>
         </x:is>
       </x:c>
       <x:c r="I131" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">None</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.65.2</x:t>
         </x:is>
       </x:c>
       <x:c r="J131" s="2" t="inlineStr">
@@ -14550,47 +14550,47 @@
     <x:row r="132">
       <x:c r="A132" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.67.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.65.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B132" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.67</x:t>
+          <x:t xml:space="preserve">4.4.1.8.65</x:t>
         </x:is>
       </x:c>
       <x:c r="C132" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Document Number Rule Interface</x:t>
+          <x:t xml:space="preserve">User Permission Edit Interface（BlueWhale 4.4.1.8.26）</x:t>
         </x:is>
       </x:c>
       <x:c r="D132" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Name (Input)</x:t>
+          <x:t xml:space="preserve">Branch / Department (Dropdown)</x:t>
         </x:is>
       </x:c>
       <x:c r="E132" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">名稱</x:t>
+          <x:t xml:space="preserve">分店／部門</x:t>
         </x:is>
       </x:c>
       <x:c r="F132" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">規則說明</x:t>
+          <x:t xml:space="preserve">組織歸屬（資料範圍用）</x:t>
         </x:is>
       </x:c>
       <x:c r="G132" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Text</x:t>
+          <x:t xml:space="preserve">bigint ID，可清空</x:t>
         </x:is>
       </x:c>
       <x:c r="H132" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1–100 字元，去除前後空白</x:t>
+          <x:t xml:space="preserve">所選公司的啟用分店／部門</x:t>
         </x:is>
       </x:c>
       <x:c r="I132" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">None</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.65.1</x:t>
         </x:is>
       </x:c>
       <x:c r="J132" s="2" t="inlineStr">
@@ -14607,47 +14607,47 @@
     <x:row r="133">
       <x:c r="A133" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.67.3</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.65.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B133" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.67</x:t>
+          <x:t xml:space="preserve">4.4.1.8.65</x:t>
         </x:is>
       </x:c>
       <x:c r="C133" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Document Number Rule Interface</x:t>
+          <x:t xml:space="preserve">User Permission Edit Interface（BlueWhale 4.4.1.8.26）</x:t>
         </x:is>
       </x:c>
       <x:c r="D133" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Prefix (Input)</x:t>
+          <x:t xml:space="preserve">Roles (Multi-select)</x:t>
         </x:is>
       </x:c>
       <x:c r="E133" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">前綴</x:t>
+          <x:t xml:space="preserve">角色</x:t>
         </x:is>
       </x:c>
       <x:c r="F133" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">單號開頭</x:t>
+          <x:t xml:space="preserve">整組取代該公司的角色</x:t>
         </x:is>
       </x:c>
       <x:c r="G133" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Text</x:t>
+          <x:t xml:space="preserve">bigint ID 陣列</x:t>
         </x:is>
       </x:c>
       <x:c r="H133" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">0–10 個英數字、-、_；保存為大寫</x:t>
+          <x:t xml:space="preserve">啟用角色；可為空（無權限）</x:t>
         </x:is>
       </x:c>
       <x:c r="I133" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.67.7</x:t>
+          <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
       <x:c r="J133" s="2" t="inlineStr">
@@ -14664,47 +14664,47 @@
     <x:row r="134">
       <x:c r="A134" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.67.4</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.65.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B134" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.67</x:t>
+          <x:t xml:space="preserve">4.4.1.8.65</x:t>
         </x:is>
       </x:c>
       <x:c r="C134" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Document Number Rule Interface</x:t>
+          <x:t xml:space="preserve">User Permission Edit Interface（BlueWhale 4.4.1.8.26）</x:t>
         </x:is>
       </x:c>
       <x:c r="D134" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Date Format (Dropdown)</x:t>
+          <x:t xml:space="preserve">Default Company (Checkbox)</x:t>
         </x:is>
       </x:c>
       <x:c r="E134" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">日期格式</x:t>
+          <x:t xml:space="preserve">預設公司</x:t>
         </x:is>
       </x:c>
       <x:c r="F134" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">單號的日期部分</x:t>
+          <x:t xml:space="preserve">登入後預設的操作公司</x:t>
         </x:is>
       </x:c>
       <x:c r="G134" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">None／yyyy／yyyyMM／yyyyMMdd／yyMM／yyMMdd</x:t>
+          <x:t xml:space="preserve">Boolean</x:t>
         </x:is>
       </x:c>
       <x:c r="H134" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">已發號時不可修改</x:t>
+          <x:t xml:space="preserve">設定後取消其他預設</x:t>
         </x:is>
       </x:c>
       <x:c r="I134" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.67.6</x:t>
+          <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
       <x:c r="J134" s="2" t="inlineStr">
@@ -14721,47 +14721,47 @@
     <x:row r="135">
       <x:c r="A135" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.67.5</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.65.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B135" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.67</x:t>
+          <x:t xml:space="preserve">4.4.1.8.65</x:t>
         </x:is>
       </x:c>
       <x:c r="C135" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Document Number Rule Interface</x:t>
+          <x:t xml:space="preserve">User Permission Edit Interface（BlueWhale 4.4.1.8.26）</x:t>
         </x:is>
       </x:c>
       <x:c r="D135" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Sequence Length (Number)</x:t>
+          <x:t xml:space="preserve">Access Active (Checkbox)</x:t>
         </x:is>
       </x:c>
       <x:c r="E135" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">流水號長度</x:t>
+          <x:t xml:space="preserve">啟用存取</x:t>
         </x:is>
       </x:c>
       <x:c r="F135" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">補零位數</x:t>
+          <x:t xml:space="preserve">停用後該公司不授權</x:t>
         </x:is>
       </x:c>
       <x:c r="G135" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">整數</x:t>
+          <x:t xml:space="preserve">Boolean</x:t>
         </x:is>
       </x:c>
       <x:c r="H135" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">3–10；已發號時不可小於原長度</x:t>
+          <x:t xml:space="preserve">不可停用自己</x:t>
         </x:is>
       </x:c>
       <x:c r="I135" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.67.7</x:t>
+          <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
       <x:c r="J135" s="2" t="inlineStr">
@@ -14778,47 +14778,47 @@
     <x:row r="136">
       <x:c r="A136" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.67.6</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.66.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B136" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.67</x:t>
+          <x:t xml:space="preserve">4.4.1.8.66</x:t>
         </x:is>
       </x:c>
       <x:c r="C136" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Document Number Rule Interface</x:t>
+          <x:t xml:space="preserve">Audit Log Query Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D136" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Reset Period (Dropdown)</x:t>
+          <x:t xml:space="preserve">Date Range (Date inputs + quick buttons)</x:t>
         </x:is>
       </x:c>
       <x:c r="E136" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">重設週期</x:t>
+          <x:t xml:space="preserve">開始／結束日期</x:t>
         </x:is>
       </x:c>
       <x:c r="F136" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">流水號歸 1 的時機</x:t>
+          <x:t xml:space="preserve">限制查詢期間</x:t>
         </x:is>
       </x:c>
       <x:c r="G136" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">不重設／每年／每月／每日</x:t>
+          <x:t xml:space="preserve">yyyy-MM-dd</x:t>
         </x:is>
       </x:c>
       <x:c r="H136" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">必須包含在日期格式內；已發號時不可修改</x:t>
+          <x:t xml:space="preserve">含頭尾；結束日不可早於開始日；快選今天、近 7、30 天</x:t>
         </x:is>
       </x:c>
       <x:c r="I136" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.67.4</x:t>
+          <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
       <x:c r="J136" s="2" t="inlineStr">
@@ -14835,47 +14835,47 @@
     <x:row r="137">
       <x:c r="A137" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.67.7</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.66.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B137" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.67</x:t>
+          <x:t xml:space="preserve">4.4.1.8.66</x:t>
         </x:is>
       </x:c>
       <x:c r="C137" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Document Number Rule Interface</x:t>
+          <x:t xml:space="preserve">Audit Log Query Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D137" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Sample (Text)</x:t>
+          <x:t xml:space="preserve">Category (Dropdown)</x:t>
         </x:is>
       </x:c>
       <x:c r="E137" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">樣式</x:t>
+          <x:t xml:space="preserve">類別</x:t>
         </x:is>
       </x:c>
       <x:c r="F137" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">即時顯示今天第 1 號</x:t>
+          <x:t xml:space="preserve">區分資料變更與安全事件</x:t>
         </x:is>
       </x:c>
       <x:c r="G137" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">前綴＋日期＋補零流水號</x:t>
+          <x:t xml:space="preserve">DATA／SECURITY</x:t>
         </x:is>
       </x:c>
       <x:c r="H137" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">唯讀</x:t>
+          <x:t xml:space="preserve">可清空</x:t>
         </x:is>
       </x:c>
       <x:c r="I137" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.67.3</x:t>
+          <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
       <x:c r="J137" s="2" t="inlineStr">
@@ -14892,42 +14892,42 @@
     <x:row r="138">
       <x:c r="A138" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.67.8</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.66.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B138" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.67</x:t>
+          <x:t xml:space="preserve">4.4.1.8.66</x:t>
         </x:is>
       </x:c>
       <x:c r="C138" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Document Number Rule Interface</x:t>
+          <x:t xml:space="preserve">Audit Log Query Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D138" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Active (Checkbox)</x:t>
+          <x:t xml:space="preserve">Action (Dropdown)</x:t>
         </x:is>
       </x:c>
       <x:c r="E138" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">啟用</x:t>
+          <x:t xml:space="preserve">操作</x:t>
         </x:is>
       </x:c>
       <x:c r="F138" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">停用後各模組不可再取號</x:t>
+          <x:t xml:space="preserve">依操作類型篩選</x:t>
         </x:is>
       </x:c>
       <x:c r="G138" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Boolean</x:t>
+          <x:t xml:space="preserve">CREATE、UPDATE、DELETE、VOID、APPROVE、POST、LOGIN、LOGIN_FAILED、MASTER_CODE_LOGIN、LOGOUT、PERMISSION_CHANGE、EXPORT</x:t>
         </x:is>
       </x:c>
       <x:c r="H138" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">只在編輯時顯示</x:t>
+          <x:t xml:space="preserve">可清空</x:t>
         </x:is>
       </x:c>
       <x:c r="I138" s="2" t="inlineStr">
@@ -14949,47 +14949,47 @@
     <x:row r="139">
       <x:c r="A139" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.67.9</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.66.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B139" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.67</x:t>
+          <x:t xml:space="preserve">4.4.1.8.66</x:t>
         </x:is>
       </x:c>
       <x:c r="C139" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Document Number Rule Interface</x:t>
+          <x:t xml:space="preserve">Audit Log Query Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D139" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Preview Date (Date input)</x:t>
+          <x:t xml:space="preserve">Table / Record ID (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E139" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">單據日期</x:t>
+          <x:t xml:space="preserve">資料表、記錄 ID</x:t>
         </x:is>
       </x:c>
       <x:c r="F139" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">預覽該日期的下一個單號</x:t>
+          <x:t xml:space="preserve">查看單據修改歷史</x:t>
         </x:is>
       </x:c>
       <x:c r="G139" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">yyyy-MM-dd</x:t>
+          <x:t xml:space="preserve">Text</x:t>
         </x:is>
       </x:c>
       <x:c r="H139" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">預設今天；可清空（後端用今天）；不佔號</x:t>
+          <x:t xml:space="preserve">資料表最多 128 字元、記錄 ID 最多 100 字元；去除前後空白</x:t>
         </x:is>
       </x:c>
       <x:c r="I139" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">None</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.66.6</x:t>
         </x:is>
       </x:c>
       <x:c r="J139" s="2" t="inlineStr">
@@ -15006,42 +15006,42 @@
     <x:row r="140">
       <x:c r="A140" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.68.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.66.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B140" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.68</x:t>
+          <x:t xml:space="preserve">4.4.1.8.66</x:t>
         </x:is>
       </x:c>
       <x:c r="C140" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Approval Flow Maintenance Interface</x:t>
+          <x:t xml:space="preserve">Audit Log Query Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D140" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Document Type (Input)</x:t>
+          <x:t xml:space="preserve">Changes (Expandable row)</x:t>
         </x:is>
       </x:c>
       <x:c r="E140" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">單據類型</x:t>
+          <x:t xml:space="preserve">欄位差異</x:t>
         </x:is>
       </x:c>
       <x:c r="F140" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">流程所屬單據</x:t>
+          <x:t xml:space="preserve">顯示修改前後的值</x:t>
         </x:is>
       </x:c>
       <x:c r="G140" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">{PREFIX}.{DOCUMENT}，例如 PUR.ORDER</x:t>
+          <x:t xml:space="preserve">欄位／修改前／修改後</x:t>
         </x:is>
       </x:c>
       <x:c r="H140" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">英文字母、數字、底線，最多 50 字；保存為大寫；公司內唯一；建立後不可修改</x:t>
+          <x:t xml:space="preserve">敏感欄位顯示 *；空值顯示「（空）」</x:t>
         </x:is>
       </x:c>
       <x:c r="I140" s="2" t="inlineStr">
@@ -15063,47 +15063,47 @@
     <x:row r="141">
       <x:c r="A141" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.68.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.66.6</x:t>
         </x:is>
       </x:c>
       <x:c r="B141" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.68</x:t>
+          <x:t xml:space="preserve">4.4.1.8.66</x:t>
         </x:is>
       </x:c>
       <x:c r="C141" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Approval Flow Maintenance Interface</x:t>
+          <x:t xml:space="preserve">Audit Log Query Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D141" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Flow Name (Input)</x:t>
+          <x:t xml:space="preserve">Record History (Link / query string)</x:t>
         </x:is>
       </x:c>
       <x:c r="E141" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">流程名稱</x:t>
+          <x:t xml:space="preserve">修改歷史</x:t>
         </x:is>
       </x:c>
       <x:c r="F141" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">流程說明</x:t>
+          <x:t xml:space="preserve">由單據或列開啟單筆記錄歷史</x:t>
         </x:is>
       </x:c>
       <x:c r="G141" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Text</x:t>
+          <x:t xml:space="preserve">?tableName=&amp;recordId=</x:t>
         </x:is>
       </x:c>
       <x:c r="H141" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1–100 字元，去除前後空白</x:t>
+          <x:t xml:space="preserve">安全事件沒有記錄 ID，不可開啟</x:t>
         </x:is>
       </x:c>
       <x:c r="I141" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">None</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.66.4</x:t>
         </x:is>
       </x:c>
       <x:c r="J141" s="2" t="inlineStr">
@@ -15120,42 +15120,42 @@
     <x:row r="142">
       <x:c r="A142" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.68.3</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.67.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B142" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.68</x:t>
+          <x:t xml:space="preserve">4.4.1.8.67</x:t>
         </x:is>
       </x:c>
       <x:c r="C142" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Approval Flow Maintenance Interface</x:t>
+          <x:t xml:space="preserve">Document Number Rule Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D142" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Allow Self-approval (Checkbox)</x:t>
+          <x:t xml:space="preserve">Document Type (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E142" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">允許自審</x:t>
+          <x:t xml:space="preserve">單據類型</x:t>
         </x:is>
       </x:c>
       <x:c r="F142" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">送審人可否審批自己的單據</x:t>
+          <x:t xml:space="preserve">識別規則所屬單據</x:t>
         </x:is>
       </x:c>
       <x:c r="G142" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Boolean</x:t>
+          <x:t xml:space="preserve">{PREFIX}.{DOCUMENT}，例如 SD.ORDER</x:t>
         </x:is>
       </x:c>
       <x:c r="H142" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">預設否</x:t>
+          <x:t xml:space="preserve">英文字母、數字、底線，最多 50 字；保存為大寫；公司內唯一；建立後不可修改</x:t>
         </x:is>
       </x:c>
       <x:c r="I142" s="2" t="inlineStr">
@@ -15177,32 +15177,32 @@
     <x:row r="143">
       <x:c r="A143" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.68.4</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.67.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B143" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.68</x:t>
+          <x:t xml:space="preserve">4.4.1.8.67</x:t>
         </x:is>
       </x:c>
       <x:c r="C143" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Approval Flow Maintenance Interface</x:t>
+          <x:t xml:space="preserve">Document Number Rule Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D143" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Step Name (Input)</x:t>
+          <x:t xml:space="preserve">Name (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E143" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">步驟名稱</x:t>
+          <x:t xml:space="preserve">名稱</x:t>
         </x:is>
       </x:c>
       <x:c r="F143" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">顯示於待辦與記錄</x:t>
+          <x:t xml:space="preserve">規則說明</x:t>
         </x:is>
       </x:c>
       <x:c r="G143" s="2" t="inlineStr">
@@ -15212,7 +15212,7 @@
       </x:c>
       <x:c r="H143" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1–100 字元</x:t>
+          <x:t xml:space="preserve">1–100 字元，去除前後空白</x:t>
         </x:is>
       </x:c>
       <x:c r="I143" s="2" t="inlineStr">
@@ -15234,47 +15234,47 @@
     <x:row r="144">
       <x:c r="A144" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.68.5</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.67.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B144" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.68</x:t>
+          <x:t xml:space="preserve">4.4.1.8.67</x:t>
         </x:is>
       </x:c>
       <x:c r="C144" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Approval Flow Maintenance Interface</x:t>
+          <x:t xml:space="preserve">Document Number Rule Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D144" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Approver Type (Dropdown)</x:t>
+          <x:t xml:space="preserve">Prefix (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E144" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">審批人類型</x:t>
+          <x:t xml:space="preserve">前綴</x:t>
         </x:is>
       </x:c>
       <x:c r="F144" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">角色或指定用戶</x:t>
+          <x:t xml:space="preserve">單號開頭</x:t>
         </x:is>
       </x:c>
       <x:c r="G144" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Role／User</x:t>
+          <x:t xml:space="preserve">Text</x:t>
         </x:is>
       </x:c>
       <x:c r="H144" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">必填</x:t>
+          <x:t xml:space="preserve">0–10 個英數字、-、_；保存為大寫</x:t>
         </x:is>
       </x:c>
       <x:c r="I144" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.68.6</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.67.7</x:t>
         </x:is>
       </x:c>
       <x:c r="J144" s="2" t="inlineStr">
@@ -15291,47 +15291,47 @@
     <x:row r="145">
       <x:c r="A145" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.68.6</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.67.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B145" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.68</x:t>
+          <x:t xml:space="preserve">4.4.1.8.67</x:t>
         </x:is>
       </x:c>
       <x:c r="C145" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Approval Flow Maintenance Interface</x:t>
+          <x:t xml:space="preserve">Document Number Rule Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D145" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Approver (Dropdown)</x:t>
+          <x:t xml:space="preserve">Date Format (Dropdown)</x:t>
         </x:is>
       </x:c>
       <x:c r="E145" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">審批人</x:t>
+          <x:t xml:space="preserve">日期格式</x:t>
         </x:is>
       </x:c>
       <x:c r="F145" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">處理該步驟的角色或用戶</x:t>
+          <x:t xml:space="preserve">單號的日期部分</x:t>
         </x:is>
       </x:c>
       <x:c r="G145" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">bigint ID</x:t>
+          <x:t xml:space="preserve">None／yyyy／yyyyMM／yyyyMMdd／yyMM／yyMMdd</x:t>
         </x:is>
       </x:c>
       <x:c r="H145" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">啟用角色或本公司啟用用戶</x:t>
+          <x:t xml:space="preserve">已發號時不可修改</x:t>
         </x:is>
       </x:c>
       <x:c r="I145" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.68.5</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.67.6</x:t>
         </x:is>
       </x:c>
       <x:c r="J145" s="2" t="inlineStr">
@@ -15348,47 +15348,47 @@
     <x:row r="146">
       <x:c r="A146" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.68.7</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.67.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B146" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.68</x:t>
+          <x:t xml:space="preserve">4.4.1.8.67</x:t>
         </x:is>
       </x:c>
       <x:c r="C146" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Approval Flow Maintenance Interface</x:t>
+          <x:t xml:space="preserve">Document Number Rule Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D146" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Minimum Amount (Input)</x:t>
+          <x:t xml:space="preserve">Sequence Length (Number)</x:t>
         </x:is>
       </x:c>
       <x:c r="E146" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">最低金額</x:t>
+          <x:t xml:space="preserve">流水號長度</x:t>
         </x:is>
       </x:c>
       <x:c r="F146" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">金額門檻（本位幣）</x:t>
+          <x:t xml:space="preserve">補零位數</x:t>
         </x:is>
       </x:c>
       <x:c r="G146" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">數字</x:t>
+          <x:t xml:space="preserve">整數</x:t>
         </x:is>
       </x:c>
       <x:c r="H146" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">選填；≥ 0，最多 11 位整數、4 位小數</x:t>
+          <x:t xml:space="preserve">3–10；已發號時不可小於原長度</x:t>
         </x:is>
       </x:c>
       <x:c r="I146" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">None</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.67.7</x:t>
         </x:is>
       </x:c>
       <x:c r="J146" s="2" t="inlineStr">
@@ -15405,47 +15405,47 @@
     <x:row r="147">
       <x:c r="A147" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.68.8</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.67.6</x:t>
         </x:is>
       </x:c>
       <x:c r="B147" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.68</x:t>
+          <x:t xml:space="preserve">4.4.1.8.67</x:t>
         </x:is>
       </x:c>
       <x:c r="C147" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Approval Flow Maintenance Interface</x:t>
+          <x:t xml:space="preserve">Document Number Rule Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D147" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Active (Checkbox)</x:t>
+          <x:t xml:space="preserve">Reset Period (Dropdown)</x:t>
         </x:is>
       </x:c>
       <x:c r="E147" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">啟用</x:t>
+          <x:t xml:space="preserve">重設週期</x:t>
         </x:is>
       </x:c>
       <x:c r="F147" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">停用後送審自動核准</x:t>
+          <x:t xml:space="preserve">流水號歸 1 的時機</x:t>
         </x:is>
       </x:c>
       <x:c r="G147" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Boolean</x:t>
+          <x:t xml:space="preserve">不重設／每年／每月／每日</x:t>
         </x:is>
       </x:c>
       <x:c r="H147" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">只在編輯時顯示</x:t>
+          <x:t xml:space="preserve">必須包含在日期格式內；已發號時不可修改</x:t>
         </x:is>
       </x:c>
       <x:c r="I147" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">None</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.67.4</x:t>
         </x:is>
       </x:c>
       <x:c r="J147" s="2" t="inlineStr">
@@ -15462,47 +15462,47 @@
     <x:row r="148">
       <x:c r="A148" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.69.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.67.7</x:t>
         </x:is>
       </x:c>
       <x:c r="B148" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.69</x:t>
+          <x:t xml:space="preserve">4.4.1.8.67</x:t>
         </x:is>
       </x:c>
       <x:c r="C148" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Approval Delegation Interface</x:t>
+          <x:t xml:space="preserve">Document Number Rule Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D148" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Delegator (Dropdown)</x:t>
+          <x:t xml:space="preserve">Sample (Text)</x:t>
         </x:is>
       </x:c>
       <x:c r="E148" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">被代理人</x:t>
+          <x:t xml:space="preserve">樣式</x:t>
         </x:is>
       </x:c>
       <x:c r="F148" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">交出審批工作的用戶</x:t>
+          <x:t xml:space="preserve">即時顯示今天第 1 號</x:t>
         </x:is>
       </x:c>
       <x:c r="G148" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">bigint ID</x:t>
+          <x:t xml:space="preserve">前綴＋日期＋補零流水號</x:t>
         </x:is>
       </x:c>
       <x:c r="H148" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">本公司啟用用戶；建立後不可修改</x:t>
+          <x:t xml:space="preserve">唯讀</x:t>
         </x:is>
       </x:c>
       <x:c r="I148" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.69.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.67.3</x:t>
         </x:is>
       </x:c>
       <x:c r="J148" s="2" t="inlineStr">
@@ -15519,47 +15519,47 @@
     <x:row r="149">
       <x:c r="A149" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.69.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.67.8</x:t>
         </x:is>
       </x:c>
       <x:c r="B149" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.69</x:t>
+          <x:t xml:space="preserve">4.4.1.8.67</x:t>
         </x:is>
       </x:c>
       <x:c r="C149" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Approval Delegation Interface</x:t>
+          <x:t xml:space="preserve">Document Number Rule Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D149" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Delegate (Dropdown)</x:t>
+          <x:t xml:space="preserve">Active (Checkbox)</x:t>
         </x:is>
       </x:c>
       <x:c r="E149" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">代理人</x:t>
+          <x:t xml:space="preserve">啟用</x:t>
         </x:is>
       </x:c>
       <x:c r="F149" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">代為審批的用戶</x:t>
+          <x:t xml:space="preserve">停用後各模組不可再取號</x:t>
         </x:is>
       </x:c>
       <x:c r="G149" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">bigint ID</x:t>
+          <x:t xml:space="preserve">Boolean</x:t>
         </x:is>
       </x:c>
       <x:c r="H149" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">本公司啟用用戶，不可與被代理人相同；建立後不可修改</x:t>
+          <x:t xml:space="preserve">只在編輯時顯示</x:t>
         </x:is>
       </x:c>
       <x:c r="I149" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.69.1</x:t>
+          <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
       <x:c r="J149" s="2" t="inlineStr">
@@ -15576,32 +15576,32 @@
     <x:row r="150">
       <x:c r="A150" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.69.3</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.67.9</x:t>
         </x:is>
       </x:c>
       <x:c r="B150" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.69</x:t>
+          <x:t xml:space="preserve">4.4.1.8.67</x:t>
         </x:is>
       </x:c>
       <x:c r="C150" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Approval Delegation Interface</x:t>
+          <x:t xml:space="preserve">Document Number Rule Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D150" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Start / End Date (Date input)</x:t>
+          <x:t xml:space="preserve">Preview Date (Date input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E150" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">開始／結束日期</x:t>
+          <x:t xml:space="preserve">單據日期</x:t>
         </x:is>
       </x:c>
       <x:c r="F150" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">代理期間（含頭尾）</x:t>
+          <x:t xml:space="preserve">預覽該日期的下一個單號</x:t>
         </x:is>
       </x:c>
       <x:c r="G150" s="2" t="inlineStr">
@@ -15611,7 +15611,7 @@
       </x:c>
       <x:c r="H150" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">結束不早於開始；同一被代理人的啟用期間不可重疊</x:t>
+          <x:t xml:space="preserve">預設今天；可清空（後端用今天）；不佔號</x:t>
         </x:is>
       </x:c>
       <x:c r="I150" s="2" t="inlineStr">
@@ -15633,42 +15633,42 @@
     <x:row r="151">
       <x:c r="A151" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.69.4</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.68.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B151" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.69</x:t>
+          <x:t xml:space="preserve">4.4.1.8.68</x:t>
         </x:is>
       </x:c>
       <x:c r="C151" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Approval Delegation Interface</x:t>
+          <x:t xml:space="preserve">Approval Flow Maintenance Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D151" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Remark (Textarea)</x:t>
+          <x:t xml:space="preserve">Document Type (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E151" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">備註</x:t>
+          <x:t xml:space="preserve">單據類型</x:t>
         </x:is>
       </x:c>
       <x:c r="F151" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">代理原因</x:t>
+          <x:t xml:space="preserve">流程所屬單據</x:t>
         </x:is>
       </x:c>
       <x:c r="G151" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Text</x:t>
+          <x:t xml:space="preserve">{PREFIX}.{DOCUMENT}，例如 PUR.ORDER</x:t>
         </x:is>
       </x:c>
       <x:c r="H151" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">0–200 字元</x:t>
+          <x:t xml:space="preserve">英文字母、數字、底線，最多 50 字；保存為大寫；公司內唯一；建立後不可修改</x:t>
         </x:is>
       </x:c>
       <x:c r="I151" s="2" t="inlineStr">
@@ -15690,32 +15690,32 @@
     <x:row r="152">
       <x:c r="A152" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.70.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.68.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B152" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.70</x:t>
+          <x:t xml:space="preserve">4.4.1.8.68</x:t>
         </x:is>
       </x:c>
       <x:c r="C152" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Approval Inbox Interface</x:t>
+          <x:t xml:space="preserve">Approval Flow Maintenance Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D152" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Comment (Textarea)</x:t>
+          <x:t xml:space="preserve">Flow Name (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E152" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">意見</x:t>
+          <x:t xml:space="preserve">流程名稱</x:t>
         </x:is>
       </x:c>
       <x:c r="F152" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">核准或駁回的說明</x:t>
+          <x:t xml:space="preserve">流程說明</x:t>
         </x:is>
       </x:c>
       <x:c r="G152" s="2" t="inlineStr">
@@ -15725,7 +15725,7 @@
       </x:c>
       <x:c r="H152" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">0–500 字元；駁回必填</x:t>
+          <x:t xml:space="preserve">1–100 字元，去除前後空白</x:t>
         </x:is>
       </x:c>
       <x:c r="I152" s="2" t="inlineStr">
@@ -15747,42 +15747,42 @@
     <x:row r="153">
       <x:c r="A153" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.70.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.68.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B153" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.70</x:t>
+          <x:t xml:space="preserve">4.4.1.8.68</x:t>
         </x:is>
       </x:c>
       <x:c r="C153" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Approval Inbox Interface</x:t>
+          <x:t xml:space="preserve">Approval Flow Maintenance Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D153" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Status Filter (Dropdown)</x:t>
+          <x:t xml:space="preserve">Allow Self-approval (Checkbox)</x:t>
         </x:is>
       </x:c>
       <x:c r="E153" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">狀態</x:t>
+          <x:t xml:space="preserve">允許自審</x:t>
         </x:is>
       </x:c>
       <x:c r="F153" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">篩選審批歷史</x:t>
+          <x:t xml:space="preserve">送審人可否審批自己的單據</x:t>
         </x:is>
       </x:c>
       <x:c r="G153" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">審批中／已核准／已駁回／已撤回</x:t>
+          <x:t xml:space="preserve">Boolean</x:t>
         </x:is>
       </x:c>
       <x:c r="H153" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">可清除</x:t>
+          <x:t xml:space="preserve">預設否</x:t>
         </x:is>
       </x:c>
       <x:c r="I153" s="2" t="inlineStr">
@@ -15804,42 +15804,42 @@
     <x:row r="154">
       <x:c r="A154" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.71.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.68.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B154" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.71</x:t>
+          <x:t xml:space="preserve">4.4.1.8.68</x:t>
         </x:is>
       </x:c>
       <x:c r="C154" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Confirmation / Prompt Box Interface（BlueWhale 4.4.1.9）</x:t>
+          <x:t xml:space="preserve">Approval Flow Maintenance Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D154" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">OK / Cancel (Button)</x:t>
+          <x:t xml:space="preserve">Step Name (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E154" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">確定／取消</x:t>
+          <x:t xml:space="preserve">步驟名稱</x:t>
         </x:is>
       </x:c>
       <x:c r="F154" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">確認或放棄動作</x:t>
+          <x:t xml:space="preserve">顯示於待辦與記錄</x:t>
         </x:is>
       </x:c>
       <x:c r="G154" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Button</x:t>
+          <x:t xml:space="preserve">Text</x:t>
         </x:is>
       </x:c>
       <x:c r="H154" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">確認框兩個按鈕，提示框只有確定；Esc 等同取消</x:t>
+          <x:t xml:space="preserve">1–100 字元</x:t>
         </x:is>
       </x:c>
       <x:c r="I154" s="2" t="inlineStr">
@@ -15861,47 +15861,47 @@
     <x:row r="155">
       <x:c r="A155" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.72.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.68.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B155" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.72</x:t>
+          <x:t xml:space="preserve">4.4.1.8.68</x:t>
         </x:is>
       </x:c>
       <x:c r="C155" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Select Dialog Interface（BlueWhale 4.4.1.9 Select Client / Supplier / Item）</x:t>
+          <x:t xml:space="preserve">Approval Flow Maintenance Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D155" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Keyword (Input)</x:t>
+          <x:t xml:space="preserve">Approver Type (Dropdown)</x:t>
         </x:is>
       </x:c>
       <x:c r="E155" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">關鍵字</x:t>
+          <x:t xml:space="preserve">審批人類型</x:t>
         </x:is>
       </x:c>
       <x:c r="F155" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">搜尋主檔</x:t>
+          <x:t xml:space="preserve">角色或指定用戶</x:t>
         </x:is>
       </x:c>
       <x:c r="G155" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Text</x:t>
+          <x:t xml:space="preserve">Role／User</x:t>
         </x:is>
       </x:c>
       <x:c r="H155" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">去除前後空白；查詢回到第 1 頁</x:t>
+          <x:t xml:space="preserve">必填</x:t>
         </x:is>
       </x:c>
       <x:c r="I155" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">None</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.68.6</x:t>
         </x:is>
       </x:c>
       <x:c r="J155" s="2" t="inlineStr">
@@ -15918,47 +15918,47 @@
     <x:row r="156">
       <x:c r="A156" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.72.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.68.6</x:t>
         </x:is>
       </x:c>
       <x:c r="B156" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.72</x:t>
+          <x:t xml:space="preserve">4.4.1.8.68</x:t>
         </x:is>
       </x:c>
       <x:c r="C156" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Select Dialog Interface（BlueWhale 4.4.1.9 Select Client / Supplier / Item）</x:t>
+          <x:t xml:space="preserve">Approval Flow Maintenance Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D156" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Selection (Checkbox / Row)</x:t>
+          <x:t xml:space="preserve">Approver (Dropdown)</x:t>
         </x:is>
       </x:c>
       <x:c r="E156" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">選取</x:t>
+          <x:t xml:space="preserve">審批人</x:t>
         </x:is>
       </x:c>
       <x:c r="F156" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">選擇主檔資料</x:t>
+          <x:t xml:space="preserve">處理該步驟的角色或用戶</x:t>
         </x:is>
       </x:c>
       <x:c r="G156" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Row key</x:t>
+          <x:t xml:space="preserve">bigint ID</x:t>
         </x:is>
       </x:c>
       <x:c r="H156" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">單選 1 筆、多選跨頁累積；至少 1 筆才可確定</x:t>
+          <x:t xml:space="preserve">啟用角色或本公司啟用用戶</x:t>
         </x:is>
       </x:c>
       <x:c r="I156" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.72.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.68.5</x:t>
         </x:is>
       </x:c>
       <x:c r="J156" s="2" t="inlineStr">
@@ -15975,42 +15975,42 @@
     <x:row r="157">
       <x:c r="A157" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.73.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.68.7</x:t>
         </x:is>
       </x:c>
       <x:c r="B157" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.73</x:t>
+          <x:t xml:space="preserve">4.4.1.8.68</x:t>
         </x:is>
       </x:c>
       <x:c r="C157" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Standard List Page Template</x:t>
+          <x:t xml:space="preserve">Approval Flow Maintenance Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D157" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Date Range (Date inputs + quick buttons)</x:t>
+          <x:t xml:space="preserve">Minimum Amount (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E157" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">開始／結束日期</x:t>
+          <x:t xml:space="preserve">最低金額</x:t>
         </x:is>
       </x:c>
       <x:c r="F157" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">限制查詢期間</x:t>
+          <x:t xml:space="preserve">金額門檻（本位幣）</x:t>
         </x:is>
       </x:c>
       <x:c r="G157" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">yyyy-MM-dd</x:t>
+          <x:t xml:space="preserve">數字</x:t>
         </x:is>
       </x:c>
       <x:c r="H157" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">含頭尾；快選今天、本週、本月、上月、本季、本年；開始晚於結束時提示</x:t>
+          <x:t xml:space="preserve">選填；≥ 0，最多 11 位整數、4 位小數</x:t>
         </x:is>
       </x:c>
       <x:c r="I157" s="2" t="inlineStr">
@@ -16032,42 +16032,42 @@
     <x:row r="158">
       <x:c r="A158" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.73.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.68.8</x:t>
         </x:is>
       </x:c>
       <x:c r="B158" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.73</x:t>
+          <x:t xml:space="preserve">4.4.1.8.68</x:t>
         </x:is>
       </x:c>
       <x:c r="C158" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Standard List Page Template</x:t>
+          <x:t xml:space="preserve">Approval Flow Maintenance Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D158" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Page Size (Dropdown)</x:t>
+          <x:t xml:space="preserve">Active (Checkbox)</x:t>
         </x:is>
       </x:c>
       <x:c r="E158" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">每頁筆數</x:t>
+          <x:t xml:space="preserve">啟用</x:t>
         </x:is>
       </x:c>
       <x:c r="F158" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">分頁</x:t>
+          <x:t xml:space="preserve">停用後送審自動核准</x:t>
         </x:is>
       </x:c>
       <x:c r="G158" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">整數</x:t>
+          <x:t xml:space="preserve">Boolean</x:t>
         </x:is>
       </x:c>
       <x:c r="H158" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">10／20／50／100／200</x:t>
+          <x:t xml:space="preserve">只在編輯時顯示</x:t>
         </x:is>
       </x:c>
       <x:c r="I158" s="2" t="inlineStr">
@@ -16089,47 +16089,47 @@
     <x:row r="159">
       <x:c r="A159" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.74.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.69.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B159" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.74</x:t>
+          <x:t xml:space="preserve">4.4.1.8.69</x:t>
         </x:is>
       </x:c>
       <x:c r="C159" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Standard Document Page Template</x:t>
+          <x:t xml:space="preserve">Approval Delegation Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D159" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Previous / Next (Button)</x:t>
+          <x:t xml:space="preserve">Delegator (Dropdown)</x:t>
         </x:is>
       </x:c>
       <x:c r="E159" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">上一筆／下一筆</x:t>
+          <x:t xml:space="preserve">被代理人</x:t>
         </x:is>
       </x:c>
       <x:c r="F159" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">依列表順序切換單據</x:t>
+          <x:t xml:space="preserve">交出審批工作的用戶</x:t>
         </x:is>
       </x:c>
       <x:c r="G159" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Button</x:t>
+          <x:t xml:space="preserve">bigint ID</x:t>
         </x:is>
       </x:c>
       <x:c r="H159" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">第一筆停用上一筆、最後一筆停用下一筆</x:t>
+          <x:t xml:space="preserve">本公司啟用用戶；建立後不可修改</x:t>
         </x:is>
       </x:c>
       <x:c r="I159" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">None</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.69.2</x:t>
         </x:is>
       </x:c>
       <x:c r="J159" s="2" t="inlineStr">
@@ -16146,47 +16146,47 @@
     <x:row r="160">
       <x:c r="A160" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.75.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.69.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B160" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.75</x:t>
+          <x:t xml:space="preserve">4.4.1.8.69</x:t>
         </x:is>
       </x:c>
       <x:c r="C160" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">IP Whitelist Interface</x:t>
+          <x:t xml:space="preserve">Approval Delegation Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D160" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Keyword (Input)</x:t>
+          <x:t xml:space="preserve">Delegate (Dropdown)</x:t>
         </x:is>
       </x:c>
       <x:c r="E160" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">網段或備註關鍵字</x:t>
+          <x:t xml:space="preserve">代理人</x:t>
         </x:is>
       </x:c>
       <x:c r="F160" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">篩選列表</x:t>
+          <x:t xml:space="preserve">代為審批的用戶</x:t>
         </x:is>
       </x:c>
       <x:c r="G160" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Text</x:t>
+          <x:t xml:space="preserve">bigint ID</x:t>
         </x:is>
       </x:c>
       <x:c r="H160" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">去除前後空白，查詢回第 1 頁</x:t>
+          <x:t xml:space="preserve">本公司啟用用戶，不可與被代理人相同；建立後不可修改</x:t>
         </x:is>
       </x:c>
       <x:c r="I160" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">None</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.69.1</x:t>
         </x:is>
       </x:c>
       <x:c r="J160" s="2" t="inlineStr">
@@ -16203,47 +16203,47 @@
     <x:row r="161">
       <x:c r="A161" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.75.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.69.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B161" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.75</x:t>
+          <x:t xml:space="preserve">4.4.1.8.69</x:t>
         </x:is>
       </x:c>
       <x:c r="C161" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">IP Whitelist Interface</x:t>
+          <x:t xml:space="preserve">Approval Delegation Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D161" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Scope (Dropdown)</x:t>
+          <x:t xml:space="preserve">Start / End Date (Date input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E161" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">全系統／角色／用戶</x:t>
+          <x:t xml:space="preserve">開始／結束日期</x:t>
         </x:is>
       </x:c>
       <x:c r="F161" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">設定比對層級</x:t>
+          <x:t xml:space="preserve">代理期間（含頭尾）</x:t>
         </x:is>
       </x:c>
       <x:c r="G161" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Enum</x:t>
+          <x:t xml:space="preserve">yyyy-MM-dd</x:t>
         </x:is>
       </x:c>
       <x:c r="H161" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">建立時可選；編輯唯讀</x:t>
+          <x:t xml:space="preserve">結束不早於開始；同一被代理人的啟用期間不可重疊</x:t>
         </x:is>
       </x:c>
       <x:c r="I161" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.75.3</x:t>
+          <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
       <x:c r="J161" s="2" t="inlineStr">
@@ -16260,47 +16260,47 @@
     <x:row r="162">
       <x:c r="A162" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.75.3</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.69.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B162" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.75</x:t>
+          <x:t xml:space="preserve">4.4.1.8.69</x:t>
         </x:is>
       </x:c>
       <x:c r="C162" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">IP Whitelist Interface</x:t>
+          <x:t xml:space="preserve">Approval Delegation Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D162" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Target ID (Input)</x:t>
+          <x:t xml:space="preserve">Remark (Textarea)</x:t>
         </x:is>
       </x:c>
       <x:c r="E162" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">角色或用戶 ID</x:t>
+          <x:t xml:space="preserve">備註</x:t>
         </x:is>
       </x:c>
       <x:c r="F162" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">指定對象</x:t>
+          <x:t xml:space="preserve">代理原因</x:t>
         </x:is>
       </x:c>
       <x:c r="G162" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Positive integer</x:t>
+          <x:t xml:space="preserve">Text</x:t>
         </x:is>
       </x:c>
       <x:c r="H162" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">全系統留空；角色／用戶必填</x:t>
+          <x:t xml:space="preserve">0–200 字元</x:t>
         </x:is>
       </x:c>
       <x:c r="I162" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.75.2</x:t>
+          <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
       <x:c r="J162" s="2" t="inlineStr">
@@ -16317,42 +16317,42 @@
     <x:row r="163">
       <x:c r="A163" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.75.4</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.70.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B163" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.75</x:t>
+          <x:t xml:space="preserve">4.4.1.8.70</x:t>
         </x:is>
       </x:c>
       <x:c r="C163" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">IP Whitelist Interface</x:t>
+          <x:t xml:space="preserve">Approval Inbox Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D163" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">IP Address / Range (Input)</x:t>
+          <x:t xml:space="preserve">Comment (Textarea)</x:t>
         </x:is>
       </x:c>
       <x:c r="E163" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">IP 或 CIDR</x:t>
+          <x:t xml:space="preserve">意見</x:t>
         </x:is>
       </x:c>
       <x:c r="F163" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">設定允許來源</x:t>
+          <x:t xml:space="preserve">核准或駁回的說明</x:t>
         </x:is>
       </x:c>
       <x:c r="G163" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">IPv4 / IPv6 / CIDR</x:t>
+          <x:t xml:space="preserve">Text</x:t>
         </x:is>
       </x:c>
       <x:c r="H163" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">完整位址；CIDR 網段從網路位址開始；伺服器作最終驗證</x:t>
+          <x:t xml:space="preserve">0–500 字元；駁回必填</x:t>
         </x:is>
       </x:c>
       <x:c r="I163" s="2" t="inlineStr">
@@ -16374,42 +16374,42 @@
     <x:row r="164">
       <x:c r="A164" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.75.5</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.70.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B164" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.75</x:t>
+          <x:t xml:space="preserve">4.4.1.8.70</x:t>
         </x:is>
       </x:c>
       <x:c r="C164" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">IP Whitelist Interface</x:t>
+          <x:t xml:space="preserve">Approval Inbox Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D164" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Valid From / To (Date Picker)</x:t>
+          <x:t xml:space="preserve">Status Filter (Dropdown)</x:t>
         </x:is>
       </x:c>
       <x:c r="E164" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">有效期間</x:t>
+          <x:t xml:space="preserve">狀態</x:t>
         </x:is>
       </x:c>
       <x:c r="F164" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">控制規則生效日期</x:t>
+          <x:t xml:space="preserve">篩選審批歷史</x:t>
         </x:is>
       </x:c>
       <x:c r="G164" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">yyyy-MM-dd</x:t>
+          <x:t xml:space="preserve">審批中／已核准／已駁回／已撤回</x:t>
         </x:is>
       </x:c>
       <x:c r="H164" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">可留空；結束不得早於開始</x:t>
+          <x:t xml:space="preserve">可清除</x:t>
         </x:is>
       </x:c>
       <x:c r="I164" s="2" t="inlineStr">
@@ -16431,42 +16431,42 @@
     <x:row r="165">
       <x:c r="A165" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.75.6</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.71.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B165" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.75</x:t>
+          <x:t xml:space="preserve">4.4.1.8.71</x:t>
         </x:is>
       </x:c>
       <x:c r="C165" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">IP Whitelist Interface</x:t>
+          <x:t xml:space="preserve">Confirmation / Prompt Box Interface（BlueWhale 4.4.1.9）</x:t>
         </x:is>
       </x:c>
       <x:c r="D165" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Description (Input)</x:t>
+          <x:t xml:space="preserve">OK / Cancel (Button)</x:t>
         </x:is>
       </x:c>
       <x:c r="E165" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">備註</x:t>
+          <x:t xml:space="preserve">確定／取消</x:t>
         </x:is>
       </x:c>
       <x:c r="F165" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">辨識規則用途</x:t>
+          <x:t xml:space="preserve">確認或放棄動作</x:t>
         </x:is>
       </x:c>
       <x:c r="G165" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Text</x:t>
+          <x:t xml:space="preserve">Button</x:t>
         </x:is>
       </x:c>
       <x:c r="H165" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">最長 200 字元</x:t>
+          <x:t xml:space="preserve">確認框兩個按鈕，提示框只有確定；Esc 等同取消</x:t>
         </x:is>
       </x:c>
       <x:c r="I165" s="2" t="inlineStr">
@@ -16488,47 +16488,47 @@
     <x:row r="166">
       <x:c r="A166" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.75.7</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.72.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B166" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.75</x:t>
+          <x:t xml:space="preserve">4.4.1.8.72</x:t>
         </x:is>
       </x:c>
       <x:c r="C166" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">IP Whitelist Interface</x:t>
+          <x:t xml:space="preserve">Select Dialog Interface（BlueWhale 4.4.1.9 Select Client / Supplier / Item）</x:t>
         </x:is>
       </x:c>
       <x:c r="D166" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Disable (Button)</x:t>
+          <x:t xml:space="preserve">Keyword (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E166" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">停用規則</x:t>
+          <x:t xml:space="preserve">關鍵字</x:t>
         </x:is>
       </x:c>
       <x:c r="F166" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">保留稽核歷史</x:t>
+          <x:t xml:space="preserve">搜尋主檔</x:t>
         </x:is>
       </x:c>
       <x:c r="G166" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Button</x:t>
+          <x:t xml:space="preserve">Text</x:t>
         </x:is>
       </x:c>
       <x:c r="H166" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">需 EDIT 權限；確認後帶版本送出</x:t>
+          <x:t xml:space="preserve">去除前後空白；查詢回到第 1 頁</x:t>
         </x:is>
       </x:c>
       <x:c r="I166" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.75.4</x:t>
+          <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
       <x:c r="J166" s="2" t="inlineStr">
@@ -16545,47 +16545,47 @@
     <x:row r="167">
       <x:c r="A167" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.76.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.72.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B167" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.76</x:t>
+          <x:t xml:space="preserve">4.4.1.8.72</x:t>
         </x:is>
       </x:c>
       <x:c r="C167" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Notification View Interface</x:t>
+          <x:t xml:space="preserve">Select Dialog Interface（BlueWhale 4.4.1.9 Select Client / Supplier / Item）</x:t>
         </x:is>
       </x:c>
       <x:c r="D167" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Unread Badge (Label)</x:t>
+          <x:t xml:space="preserve">Selection (Checkbox / Row)</x:t>
         </x:is>
       </x:c>
       <x:c r="E167" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">頂列未讀數</x:t>
+          <x:t xml:space="preserve">選取</x:t>
         </x:is>
       </x:c>
       <x:c r="F167" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">快速辨識新通知</x:t>
+          <x:t xml:space="preserve">選擇主檔資料</x:t>
         </x:is>
       </x:c>
       <x:c r="G167" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Integer</x:t>
+          <x:t xml:space="preserve">Row key</x:t>
         </x:is>
       </x:c>
       <x:c r="H167" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">0 隱藏；超過 99 顯示 99+</x:t>
+          <x:t xml:space="preserve">單選 1 筆、多選跨頁累積；至少 1 筆才可確定</x:t>
         </x:is>
       </x:c>
       <x:c r="I167" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">收件箱</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.72.1</x:t>
         </x:is>
       </x:c>
       <x:c r="J167" s="2" t="inlineStr">
@@ -16602,47 +16602,47 @@
     <x:row r="168">
       <x:c r="A168" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.76.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.73.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B168" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.76</x:t>
+          <x:t xml:space="preserve">4.4.1.8.73</x:t>
         </x:is>
       </x:c>
       <x:c r="C168" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Notification View Interface</x:t>
+          <x:t xml:space="preserve">Standard List Page Template</x:t>
         </x:is>
       </x:c>
       <x:c r="D168" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Unread Only (Button)</x:t>
+          <x:t xml:space="preserve">Date Range (Date inputs + quick buttons)</x:t>
         </x:is>
       </x:c>
       <x:c r="E168" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">未讀篩選</x:t>
+          <x:t xml:space="preserve">開始／結束日期</x:t>
         </x:is>
       </x:c>
       <x:c r="F168" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">切換全部／未讀</x:t>
+          <x:t xml:space="preserve">限制查詢期間</x:t>
         </x:is>
       </x:c>
       <x:c r="G168" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Button</x:t>
+          <x:t xml:space="preserve">yyyy-MM-dd</x:t>
         </x:is>
       </x:c>
       <x:c r="H168" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">切換後回第 1 頁</x:t>
+          <x:t xml:space="preserve">含頭尾；快選今天、本週、本月、上月、本季、本年；開始晚於結束時提示</x:t>
         </x:is>
       </x:c>
       <x:c r="I168" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">通知列表</x:t>
+          <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
       <x:c r="J168" s="2" t="inlineStr">
@@ -16659,47 +16659,47 @@
     <x:row r="169">
       <x:c r="A169" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.76.3</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.73.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B169" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.76</x:t>
+          <x:t xml:space="preserve">4.4.1.8.73</x:t>
         </x:is>
       </x:c>
       <x:c r="C169" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Notification View Interface</x:t>
+          <x:t xml:space="preserve">Standard List Page Template</x:t>
         </x:is>
       </x:c>
       <x:c r="D169" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Notification List (Table)</x:t>
+          <x:t xml:space="preserve">Page Size (Dropdown)</x:t>
         </x:is>
       </x:c>
       <x:c r="E169" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">類別、標題、內文、時間、狀態</x:t>
+          <x:t xml:space="preserve">每頁筆數</x:t>
         </x:is>
       </x:c>
       <x:c r="F169" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">瀏覽本人通知</x:t>
+          <x:t xml:space="preserve">分頁</x:t>
         </x:is>
       </x:c>
       <x:c r="G169" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Paged table</x:t>
+          <x:t xml:space="preserve">整數</x:t>
         </x:is>
       </x:c>
       <x:c r="H169" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">每頁 20，伺服器分頁</x:t>
+          <x:t xml:space="preserve">10／20／50／100／200</x:t>
         </x:is>
       </x:c>
       <x:c r="I169" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">未讀篩選</x:t>
+          <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
       <x:c r="J169" s="2" t="inlineStr">
@@ -16716,32 +16716,32 @@
     <x:row r="170">
       <x:c r="A170" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.76.4</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.74.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B170" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.76</x:t>
+          <x:t xml:space="preserve">4.4.1.8.74</x:t>
         </x:is>
       </x:c>
       <x:c r="C170" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Notification View Interface</x:t>
+          <x:t xml:space="preserve">Standard Document Page Template</x:t>
         </x:is>
       </x:c>
       <x:c r="D170" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Mark Read (Button)</x:t>
+          <x:t xml:space="preserve">Previous / Next (Button)</x:t>
         </x:is>
       </x:c>
       <x:c r="E170" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">單則已讀</x:t>
+          <x:t xml:space="preserve">上一筆／下一筆</x:t>
         </x:is>
       </x:c>
       <x:c r="F170" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">清除該筆未讀狀態</x:t>
+          <x:t xml:space="preserve">依列表順序切換單據</x:t>
         </x:is>
       </x:c>
       <x:c r="G170" s="2" t="inlineStr">
@@ -16751,12 +16751,12 @@
       </x:c>
       <x:c r="H170" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">只在未讀且有 READ 權限時顯示</x:t>
+          <x:t xml:space="preserve">第一筆停用上一筆、最後一筆停用下一筆</x:t>
         </x:is>
       </x:c>
       <x:c r="I170" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">通知列表</x:t>
+          <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
       <x:c r="J170" s="2" t="inlineStr">
@@ -16773,47 +16773,47 @@
     <x:row r="171">
       <x:c r="A171" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.76.5</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.75.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B171" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.76</x:t>
+          <x:t xml:space="preserve">4.4.1.8.75</x:t>
         </x:is>
       </x:c>
       <x:c r="C171" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Notification View Interface</x:t>
+          <x:t xml:space="preserve">IP Whitelist Interface</x:t>
         </x:is>
       </x:c>
       <x:c r="D171" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Mark All Read (Button)</x:t>
+          <x:t xml:space="preserve">Keyword (Input)</x:t>
         </x:is>
       </x:c>
       <x:c r="E171" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">全部已讀</x:t>
+          <x:t xml:space="preserve">網段或備註關鍵字</x:t>
         </x:is>
       </x:c>
       <x:c r="F171" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">清除目前公司本人未讀狀態</x:t>
+          <x:t xml:space="preserve">篩選列表</x:t>
         </x:is>
       </x:c>
       <x:c r="G171" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Button</x:t>
+          <x:t xml:space="preserve">Text</x:t>
         </x:is>
       </x:c>
       <x:c r="H171" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">未讀數為 0 時停用</x:t>
+          <x:t xml:space="preserve">去除前後空白，查詢回第 1 頁</x:t>
         </x:is>
       </x:c>
       <x:c r="I171" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">通知列表</x:t>
+          <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
       <x:c r="J171" s="2" t="inlineStr">
@@ -16830,55 +16830,682 @@
     <x:row r="172">
       <x:c r="A172" s="2" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.75.2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B172" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.75</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C172" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">IP Whitelist Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D172" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Scope (Dropdown)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E172" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">全系統／角色／用戶</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F172" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">設定比對層級</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G172" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Enum</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H172" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">建立時可選；編輯唯讀</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I172" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.75.3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J172" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K172" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="173">
+      <x:c r="A173" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.75.3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B173" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.75</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C173" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">IP Whitelist Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D173" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Target ID (Input)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E173" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">角色或用戶 ID</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F173" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">指定對象</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G173" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Positive integer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H173" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">全系統留空；角色／用戶必填</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I173" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.75.2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J173" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K173" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="174">
+      <x:c r="A174" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.75.4</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B174" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.75</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C174" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">IP Whitelist Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D174" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">IP Address / Range (Input)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E174" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">IP 或 CIDR</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F174" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">設定允許來源</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G174" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">IPv4 / IPv6 / CIDR</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H174" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">完整位址；CIDR 網段從網路位址開始；伺服器作最終驗證</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I174" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J174" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K174" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="175">
+      <x:c r="A175" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.75.5</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B175" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.75</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C175" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">IP Whitelist Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D175" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Valid From / To (Date Picker)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E175" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">有效期間</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F175" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">控制規則生效日期</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G175" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">yyyy-MM-dd</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H175" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">可留空；結束不得早於開始</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I175" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J175" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K175" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="176">
+      <x:c r="A176" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.75.6</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B176" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.75</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C176" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">IP Whitelist Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D176" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Description (Input)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E176" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">備註</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F176" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">辨識規則用途</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G176" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Text</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H176" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">最長 200 字元</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I176" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J176" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K176" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="177">
+      <x:c r="A177" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.75.7</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B177" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.75</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C177" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">IP Whitelist Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D177" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Disable (Button)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E177" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">停用規則</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F177" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">保留稽核歷史</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G177" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Button</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H177" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">需 EDIT 權限；確認後帶版本送出</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I177" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.75.4</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J177" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K177" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="178">
+      <x:c r="A178" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.76.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B178" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.76</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C178" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Notification View Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D178" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Unread Badge (Label)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E178" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">頂列未讀數</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F178" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">快速辨識新通知</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G178" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Integer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H178" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">0 隱藏；超過 99 顯示 99+</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I178" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">收件箱</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J178" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K178" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="179">
+      <x:c r="A179" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.76.2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B179" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.76</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C179" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Notification View Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D179" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Unread Only (Button)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E179" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">未讀篩選</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F179" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">切換全部／未讀</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G179" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Button</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H179" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">切換後回第 1 頁</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I179" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">通知列表</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J179" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K179" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="180">
+      <x:c r="A180" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.76.3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B180" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.76</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C180" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Notification View Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D180" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Notification List (Table)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E180" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">類別、標題、內文、時間、狀態</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F180" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">瀏覽本人通知</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G180" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Paged table</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H180" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">每頁 20，伺服器分頁</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I180" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">未讀篩選</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J180" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K180" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="181">
+      <x:c r="A181" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.76.4</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B181" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.76</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C181" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Notification View Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D181" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Mark Read (Button)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E181" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">單則已讀</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F181" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">清除該筆未讀狀態</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G181" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Button</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H181" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">只在未讀且有 READ 權限時顯示</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I181" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">通知列表</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J181" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K181" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="182">
+      <x:c r="A182" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.76.5</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B182" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.76</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C182" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Notification View Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D182" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Mark All Read (Button)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E182" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">全部已讀</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F182" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">清除目前公司本人未讀狀態</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G182" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Button</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H182" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">未讀數為 0 時停用</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I182" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">通知列表</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J182" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K182" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="183">
+      <x:c r="A183" s="2" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">REQ_IO_A8.76.6</x:t>
         </x:is>
       </x:c>
-      <x:c r="B172" s="2" t="inlineStr">
+      <x:c r="B183" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">4.4.1.8.76</x:t>
         </x:is>
       </x:c>
-      <x:c r="C172" s="2" t="inlineStr">
+      <x:c r="C183" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Notification View Interface</x:t>
         </x:is>
       </x:c>
-      <x:c r="D172" s="2" t="inlineStr">
+      <x:c r="D183" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Open (Link)</x:t>
         </x:is>
       </x:c>
-      <x:c r="E172" s="2" t="inlineStr">
+      <x:c r="E183" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">站內目標</x:t>
         </x:is>
       </x:c>
-      <x:c r="F172" s="2" t="inlineStr">
+      <x:c r="F183" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">跳至通知相關頁</x:t>
         </x:is>
       </x:c>
-      <x:c r="G172" s="2" t="inlineStr">
+      <x:c r="G183" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Internal route</x:t>
         </x:is>
       </x:c>
-      <x:c r="H172" s="2" t="inlineStr">
+      <x:c r="H183" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">無路徑則隱藏</x:t>
         </x:is>
       </x:c>
-      <x:c r="I172" s="2" t="inlineStr">
+      <x:c r="I183" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">通知列表</x:t>
         </x:is>
       </x:c>
-      <x:c r="J172" s="2" t="inlineStr">
+      <x:c r="J183" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="K172" s="2" t="inlineStr">
+      <x:c r="K183" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Developer</x:t>
         </x:is>
@@ -17880,22 +18507,22 @@
       </x:c>
       <x:c r="D27" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">4.4.1.8.11</x:t>
         </x:is>
       </x:c>
       <x:c r="E27" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.11.1, REQ_IO_A8.11.2</x:t>
         </x:is>
       </x:c>
       <x:c r="F27" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MD-ITEM-001</x:t>
+          <x:t xml:space="preserve">MD-ITEM-001, MD-ITEM-UI-001</x:t>
         </x:is>
       </x:c>
       <x:c r="G27" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -17917,22 +18544,22 @@
       </x:c>
       <x:c r="D28" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">4.4.1.8.12</x:t>
         </x:is>
       </x:c>
       <x:c r="E28" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.12.1, REQ_IO_A8.12.2, REQ_IO_A8.12.3, REQ_IO_A8.12.4, REQ_IO_A8.12.5, REQ_IO_A8.12.6</x:t>
         </x:is>
       </x:c>
       <x:c r="F28" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MD-ITEM-001, MD-ITEM-002</x:t>
+          <x:t xml:space="preserve">MD-ITEM-001, MD-ITEM-002, MD-ITEM-UI-001</x:t>
         </x:is>
       </x:c>
       <x:c r="G28" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -17954,22 +18581,22 @@
       </x:c>
       <x:c r="D29" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">4.4.1.8.13</x:t>
         </x:is>
       </x:c>
       <x:c r="E29" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.13.1, REQ_IO_A8.13.2, REQ_IO_A8.13.3</x:t>
         </x:is>
       </x:c>
       <x:c r="F29" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MD-ITEM-001, MD-ITEM-002</x:t>
+          <x:t xml:space="preserve">MD-ITEM-001, MD-ITEM-002, MD-ITEM-UI-001</x:t>
         </x:is>
       </x:c>
       <x:c r="G29" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>

--- a/docs/99-output/MyERP_Requirements.xlsx
+++ b/docs/99-output/MyERP_Requirements.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="1" r:id="R603da4a0fae5476d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Non-Functional" sheetId="2" r:id="Rdf2b37433cf04c47"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Structure" sheetId="3" r:id="R2dfe845f850c46b0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interface" sheetId="4" r:id="R36b00d86e5a541d4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traceability Matrix" sheetId="5" r:id="R01138b28362d45e5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BlueWhale Parity" sheetId="6" r:id="R45c45d59174d453b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timeline" sheetId="7" r:id="R5e59aba686a849d4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Human Resources" sheetId="8" r:id="R5fa68518848e4db5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="9" r:id="R175b889a503c47c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="1" r:id="R3631db8cdfae40cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Non-Functional" sheetId="2" r:id="Rbe7f0b75f6d54d0a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Structure" sheetId="3" r:id="Rc1757e9c17c143a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interface" sheetId="4" r:id="R7e76eaf84faf47c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traceability Matrix" sheetId="5" r:id="Rb698d63988f04f7e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BlueWhale Parity" sheetId="6" r:id="R610133687aab4eff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timeline" sheetId="7" r:id="R476fa2c723714ab1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Human Resources" sheetId="8" r:id="Ra3b24e16293942f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="9" r:id="R33618b8097774ffb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -494,7 +494,7 @@
     <x:row r="11">
       <x:c r="A11" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.8.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.3.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B11" s="2" t="inlineStr">
@@ -504,7 +504,7 @@
       </x:c>
       <x:c r="C11" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Client Category</x:t>
+          <x:t xml:space="preserve">Product Management</x:t>
         </x:is>
       </x:c>
       <x:c r="D11" s="2" t="inlineStr">
@@ -514,7 +514,7 @@
       </x:c>
       <x:c r="E11" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to view records of client categories.</x:t>
+          <x:t xml:space="preserve">System should enable user to view product.</x:t>
         </x:is>
       </x:c>
       <x:c r="F11" s="2" t="inlineStr">
@@ -524,19 +524,19 @@
       </x:c>
       <x:c r="G11" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">具 MD.CUSTOMER_CATEGORY.VIEW 可依目前公司分頁、搜尋代碼／名稱、排序；已軟刪除及別公司資料不出現；可看停用分類。</x:t>
+          <x:t xml:space="preserve">MD.ITEM.VIEW 可在目前公司按代碼、名稱或規格搜尋，按代碼／名稱排序及分頁；含停用物料，不含其他公司。未選公司回 403。</x:t>
         </x:is>
       </x:c>
       <x:c r="H11" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:23</x:t>
+          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:110</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.8.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.3.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B12" s="2" t="inlineStr">
@@ -546,7 +546,7 @@
       </x:c>
       <x:c r="C12" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Client Category</x:t>
+          <x:t xml:space="preserve">Product Management</x:t>
         </x:is>
       </x:c>
       <x:c r="D12" s="2" t="inlineStr">
@@ -556,7 +556,7 @@
       </x:c>
       <x:c r="E12" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to create records of client categories.</x:t>
+          <x:t xml:space="preserve">System should enable user to create product.</x:t>
         </x:is>
       </x:c>
       <x:c r="F12" s="2" t="inlineStr">
@@ -566,19 +566,19 @@
       </x:c>
       <x:c r="G12" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">具 CREATE 權限可建立公司內唯一的代碼（1–30 英數、-、_，轉大寫）及非空白名稱（最多 200 字）；重複代碼回 409，軟刪除資料的代碼也不可重用。</x:t>
+          <x:t xml:space="preserve">MD.ITEM.CREATE 可建立公司內永久唯一、轉大寫的 1–30 位代碼、非空白名稱（最多 200 字）、可空規格（最多 500 字）、本公司啟用的基本單位、可空的啟用品牌與分類。重複代碼 409，別公司／停用參照 400。</x:t>
         </x:is>
       </x:c>
       <x:c r="H12" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:24</x:t>
+          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:111</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.8.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.3.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B13" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
       </x:c>
       <x:c r="C13" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Client Category</x:t>
+          <x:t xml:space="preserve">Product Management</x:t>
         </x:is>
       </x:c>
       <x:c r="D13" s="2" t="inlineStr">
@@ -598,7 +598,7 @@
       </x:c>
       <x:c r="E13" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to edit records of client categories.</x:t>
+          <x:t xml:space="preserve">System should enable user to edit product.</x:t>
         </x:is>
       </x:c>
       <x:c r="F13" s="2" t="inlineStr">
@@ -608,19 +608,19 @@
       </x:c>
       <x:c r="G13" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">具 EDIT 權限可以版本號修改名稱及啟用狀態；代碼不可修改，版本衝突回 409，別公司或已刪除資料回 404。</x:t>
+          <x:t xml:space="preserve">MD.ITEM.EDIT 可帶版本修改名稱、規格、基本單位、品牌、分類、啟用狀態，代碼不可改；原參照停用後可保留，重新選擇須啟用。舊版本 409、別公司物料 404。已被物料引用的單位、品牌、分類不可刪除，只可停用。物料有專屬換算時修改基本單位回 409 MD.ITEM.BASE_UOM_LOCKED（WU-MD-012c）。</x:t>
         </x:is>
       </x:c>
       <x:c r="H13" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:25</x:t>
+          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:112</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.8.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.3.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B14" s="2" t="inlineStr">
@@ -630,7 +630,7 @@
       </x:c>
       <x:c r="C14" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Client Category</x:t>
+          <x:t xml:space="preserve">Product Management</x:t>
         </x:is>
       </x:c>
       <x:c r="D14" s="2" t="inlineStr">
@@ -640,7 +640,7 @@
       </x:c>
       <x:c r="E14" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to delete records of client categories.</x:t>
+          <x:t xml:space="preserve">System should enable user to maintain item-specific unit conversions.</x:t>
         </x:is>
       </x:c>
       <x:c r="F14" s="2" t="inlineStr">
@@ -650,19 +650,19 @@
       </x:c>
       <x:c r="G14" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">具 DELETE 權限可用版本號軟刪除未被引用的分類；再次刪除或別公司資料回 404；已有客戶引用後僅能停用。</x:t>
+          <x:t xml:space="preserve">MD.ITEM.VIEW 可查看物料專屬換算（1 換算單位 = 係數 基本單位，依單位代碼排序）並按物料試算；MD.ITEM.EDIT 可新增、帶版本修改係數及軟刪除。單位須為本公司啟用單位且不是基本單位（400 uomId）；同一物料同一單位只能一條（409 MD.ITEM_UOM_CONVERSION.DUPLICATE）；係數 &gt; 0、最多 9 位整數及 6 位小數（400 factor）。按物料換算時，專屬換算覆寫該單位的公司級換算，其他單位以公司級路徑換到基本單位；任一端換不到基本單位時用公司級直接路徑；都沒有回 422 MD.UOM_CONVERSION.NO_PATH。結果按目標單位小數位數遠離零捨入。別公司物料 404 MD.ITEM.NOT_FOUND；換算不屬該物料 404 MD.ITEM_UOM_CONVERSION.NOT_FOUND；舊版本 409。被專屬換算引用的單位不可刪除（409 MD.UOM.IN_USE）。其他模組經 IUomConverter.ConvertForItemAsync 使用。</x:t>
         </x:is>
       </x:c>
       <x:c r="H14" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:26</x:t>
+          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:120</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.9.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.8.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B15" s="2" t="inlineStr">
@@ -672,7 +672,7 @@
       </x:c>
       <x:c r="C15" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Supplier Category</x:t>
+          <x:t xml:space="preserve">Client Category</x:t>
         </x:is>
       </x:c>
       <x:c r="D15" s="2" t="inlineStr">
@@ -682,7 +682,7 @@
       </x:c>
       <x:c r="E15" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to view records of supplier categories.</x:t>
+          <x:t xml:space="preserve">System should enable user to view records of client categories.</x:t>
         </x:is>
       </x:c>
       <x:c r="F15" s="2" t="inlineStr">
@@ -692,19 +692,19 @@
       </x:c>
       <x:c r="G15" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">具 MD.SUPPLIER_CATEGORY.VIEW 可依目前公司分頁、搜尋代碼／名稱、以代碼或名稱排序；已軟刪除及別公司資料不出現；可看停用分類。未選公司回 403。</x:t>
+          <x:t xml:space="preserve">具 MD.CUSTOMER_CATEGORY.VIEW 可依目前公司分頁、搜尋代碼／名稱、排序；已軟刪除及別公司資料不出現；可看停用分類。</x:t>
         </x:is>
       </x:c>
       <x:c r="H15" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:50</x:t>
+          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:23</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.9.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.8.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B16" s="2" t="inlineStr">
@@ -714,7 +714,7 @@
       </x:c>
       <x:c r="C16" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Supplier Category</x:t>
+          <x:t xml:space="preserve">Client Category</x:t>
         </x:is>
       </x:c>
       <x:c r="D16" s="2" t="inlineStr">
@@ -724,7 +724,7 @@
       </x:c>
       <x:c r="E16" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to create records of supplier categories.</x:t>
+          <x:t xml:space="preserve">System should enable user to create records of client categories.</x:t>
         </x:is>
       </x:c>
       <x:c r="F16" s="2" t="inlineStr">
@@ -734,19 +734,19 @@
       </x:c>
       <x:c r="G16" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">具 CREATE 權限可建立公司內唯一的代碼（1–30 英數、-、_，轉大寫）及非空白名稱（最多 200 字）；重複代碼回 409 MD.SUPPLIER_CATEGORY.DUPLICATE_CODE，軟刪除資料的代碼也不可重用；不同公司可用相同代碼。</x:t>
+          <x:t xml:space="preserve">具 CREATE 權限可建立公司內唯一的代碼（1–30 英數、-、_，轉大寫）及非空白名稱（最多 200 字）；重複代碼回 409，軟刪除資料的代碼也不可重用。</x:t>
         </x:is>
       </x:c>
       <x:c r="H16" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:51</x:t>
+          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:24</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.9.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.8.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B17" s="2" t="inlineStr">
@@ -756,7 +756,7 @@
       </x:c>
       <x:c r="C17" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Supplier Category</x:t>
+          <x:t xml:space="preserve">Client Category</x:t>
         </x:is>
       </x:c>
       <x:c r="D17" s="2" t="inlineStr">
@@ -766,7 +766,7 @@
       </x:c>
       <x:c r="E17" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to edit records of supplier categories.</x:t>
+          <x:t xml:space="preserve">System should enable user to edit records of client categories.</x:t>
         </x:is>
       </x:c>
       <x:c r="F17" s="2" t="inlineStr">
@@ -776,19 +776,19 @@
       </x:c>
       <x:c r="G17" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">具 EDIT 權限可以版本號修改名稱及啟用狀態；代碼不可修改；版本衝突回 409，別公司或已刪除資料回 404 MD.SUPPLIER_CATEGORY.NOT_FOUND。</x:t>
+          <x:t xml:space="preserve">具 EDIT 權限可以版本號修改名稱及啟用狀態；代碼不可修改，版本衝突回 409，別公司或已刪除資料回 404。</x:t>
         </x:is>
       </x:c>
       <x:c r="H17" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:52</x:t>
+          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:25</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.9.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.8.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B18" s="2" t="inlineStr">
@@ -798,7 +798,7 @@
       </x:c>
       <x:c r="C18" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Supplier Category</x:t>
+          <x:t xml:space="preserve">Client Category</x:t>
         </x:is>
       </x:c>
       <x:c r="D18" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </x:c>
       <x:c r="E18" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to delete records of supplier categories.</x:t>
+          <x:t xml:space="preserve">System should enable user to delete records of client categories.</x:t>
         </x:is>
       </x:c>
       <x:c r="F18" s="2" t="inlineStr">
@@ -818,19 +818,19 @@
       </x:c>
       <x:c r="G18" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">具 DELETE 權限可用版本號軟刪除；再次刪除或別公司資料回 404。WU-MD-007 建立供應商後，已被供應商引用的分類回 409 MD.SUPPLIER_CATEGORY.IN_USE，只能停用。</x:t>
+          <x:t xml:space="preserve">具 DELETE 權限可用版本號軟刪除未被引用的分類；再次刪除或別公司資料回 404；已有客戶引用後僅能停用。</x:t>
         </x:is>
       </x:c>
       <x:c r="H18" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:53</x:t>
+          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:26</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.10.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.9.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B19" s="2" t="inlineStr">
@@ -840,7 +840,7 @@
       </x:c>
       <x:c r="C19" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Item Category</x:t>
+          <x:t xml:space="preserve">Supplier Category</x:t>
         </x:is>
       </x:c>
       <x:c r="D19" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </x:c>
       <x:c r="E19" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to view item category.</x:t>
+          <x:t xml:space="preserve">System should enable user to view records of supplier categories.</x:t>
         </x:is>
       </x:c>
       <x:c r="F19" s="2" t="inlineStr">
@@ -860,19 +860,19 @@
       </x:c>
       <x:c r="G19" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">具 MD.ITEM_CATEGORY.VIEW 可取得目前公司全部未刪除分類（含停用，按代碼排序），以 parentId 組成最多 5 層的樹；排除別公司資料；未選公司回 403。</x:t>
+          <x:t xml:space="preserve">具 MD.SUPPLIER_CATEGORY.VIEW 可依目前公司分頁、搜尋代碼／名稱、以代碼或名稱排序；已軟刪除及別公司資料不出現；可看停用分類。未選公司回 403。</x:t>
         </x:is>
       </x:c>
       <x:c r="H19" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:93</x:t>
+          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:50</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.10.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.9.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B20" s="2" t="inlineStr">
@@ -882,7 +882,7 @@
       </x:c>
       <x:c r="C20" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Item Category</x:t>
+          <x:t xml:space="preserve">Supplier Category</x:t>
         </x:is>
       </x:c>
       <x:c r="D20" s="2" t="inlineStr">
@@ -892,7 +892,7 @@
       </x:c>
       <x:c r="E20" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to create item category.</x:t>
+          <x:t xml:space="preserve">System should enable user to create records of supplier categories.</x:t>
         </x:is>
       </x:c>
       <x:c r="F20" s="2" t="inlineStr">
@@ -902,19 +902,19 @@
       </x:c>
       <x:c r="G20" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">具 CREATE 權限可建立公司內唯一代碼（1–30 英數、-、_，轉大寫，軟刪除後仍保留）、非空白名稱（最多 200 字）的分類，可選上層；上層必須是本公司未刪除且啟用的分類（否則 422 MD.ITEM_CATEGORY.INVALID_PARENT），超過 5 層回 422 MD.ITEM_CATEGORY.TOO_DEEP；重複代碼 409 MD.ITEM_CATEGORY.DUPLICATE_CODE。</x:t>
+          <x:t xml:space="preserve">具 CREATE 權限可建立公司內唯一的代碼（1–30 英數、-、_，轉大寫）及非空白名稱（最多 200 字）；重複代碼回 409 MD.SUPPLIER_CATEGORY.DUPLICATE_CODE，軟刪除資料的代碼也不可重用；不同公司可用相同代碼。</x:t>
         </x:is>
       </x:c>
       <x:c r="H20" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:94</x:t>
+          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:51</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.10.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.9.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B21" s="2" t="inlineStr">
@@ -924,7 +924,7 @@
       </x:c>
       <x:c r="C21" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Item Category</x:t>
+          <x:t xml:space="preserve">Supplier Category</x:t>
         </x:is>
       </x:c>
       <x:c r="D21" s="2" t="inlineStr">
@@ -934,7 +934,7 @@
       </x:c>
       <x:c r="E21" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to edit item category.</x:t>
+          <x:t xml:space="preserve">System should enable user to edit records of supplier categories.</x:t>
         </x:is>
       </x:c>
       <x:c r="F21" s="2" t="inlineStr">
@@ -944,19 +944,19 @@
       </x:c>
       <x:c r="G21" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">具 EDIT 權限可帶版本修改名稱、啟用狀態與上層（整棵子樹一起移動）；代碼不可變。不可掛到自己或子孫下（422 MD.ITEM_CATEGORY.CYCLE），移動後子樹不可超過 5 層；上層不變時即使已停用亦可保留。版本衝突 409，別公司或不存在 404 MD.ITEM_CATEGORY.NOT_FOUND。</x:t>
+          <x:t xml:space="preserve">具 EDIT 權限可以版本號修改名稱及啟用狀態；代碼不可修改；版本衝突回 409，別公司或已刪除資料回 404 MD.SUPPLIER_CATEGORY.NOT_FOUND。</x:t>
         </x:is>
       </x:c>
       <x:c r="H21" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:95</x:t>
+          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:52</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.10.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.9.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B22" s="2" t="inlineStr">
@@ -966,7 +966,7 @@
       </x:c>
       <x:c r="C22" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Item Category</x:t>
+          <x:t xml:space="preserve">Supplier Category</x:t>
         </x:is>
       </x:c>
       <x:c r="D22" s="2" t="inlineStr">
@@ -976,7 +976,7 @@
       </x:c>
       <x:c r="E22" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to delete item category.</x:t>
+          <x:t xml:space="preserve">System should enable user to delete records of supplier categories.</x:t>
         </x:is>
       </x:c>
       <x:c r="F22" s="2" t="inlineStr">
@@ -986,19 +986,19 @@
       </x:c>
       <x:c r="G22" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">具 DELETE 權限可帶版本軟刪除分類；有未刪除子分類時回 409 MD.ITEM_CATEGORY.HAS_CHILDREN。物料主檔（WU-MD-012）加入後，被物料引用的分類亦不可刪除。</x:t>
+          <x:t xml:space="preserve">具 DELETE 權限可用版本號軟刪除；再次刪除或別公司資料回 404。WU-MD-007 建立供應商後，已被供應商引用的分類回 409 MD.SUPPLIER_CATEGORY.IN_USE，只能停用。</x:t>
         </x:is>
       </x:c>
       <x:c r="H22" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:96</x:t>
+          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:53</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.11.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.10.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B23" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </x:c>
       <x:c r="C23" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Item Brand</x:t>
+          <x:t xml:space="preserve">Item Category</x:t>
         </x:is>
       </x:c>
       <x:c r="D23" s="2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </x:c>
       <x:c r="E23" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to view item brand.</x:t>
+          <x:t xml:space="preserve">System should enable user to view item category.</x:t>
         </x:is>
       </x:c>
       <x:c r="F23" s="2" t="inlineStr">
@@ -1028,19 +1028,19 @@
       </x:c>
       <x:c r="G23" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">具 MD.ITEM_BRAND.VIEW 可按目前公司以代碼或名稱搜尋、分頁及排序（代碼／名稱）品牌，含停用品牌；排除軟刪除及別公司資料；未選公司回 403。</x:t>
+          <x:t xml:space="preserve">具 MD.ITEM_CATEGORY.VIEW 可取得目前公司全部未刪除分類（含停用，按代碼排序），以 parentId 組成最多 5 層的樹；排除別公司資料；未選公司回 403。</x:t>
         </x:is>
       </x:c>
       <x:c r="H23" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:97</x:t>
+          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:93</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.11.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.10.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B24" s="2" t="inlineStr">
@@ -1050,7 +1050,7 @@
       </x:c>
       <x:c r="C24" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Item Brand</x:t>
+          <x:t xml:space="preserve">Item Category</x:t>
         </x:is>
       </x:c>
       <x:c r="D24" s="2" t="inlineStr">
@@ -1060,7 +1060,7 @@
       </x:c>
       <x:c r="E24" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to create item brand.</x:t>
+          <x:t xml:space="preserve">System should enable user to create item category.</x:t>
         </x:is>
       </x:c>
       <x:c r="F24" s="2" t="inlineStr">
@@ -1070,19 +1070,19 @@
       </x:c>
       <x:c r="G24" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">具 CREATE 權限可建立公司內唯一代碼（規則同分類）、非空白名稱的品牌；重複代碼 409 MD.ITEM_BRAND.DUPLICATE_CODE。</x:t>
+          <x:t xml:space="preserve">具 CREATE 權限可建立公司內唯一代碼（1–30 英數、-、_，轉大寫，軟刪除後仍保留）、非空白名稱（最多 200 字）的分類，可選上層；上層必須是本公司未刪除且啟用的分類（否則 422 MD.ITEM_CATEGORY.INVALID_PARENT），超過 5 層回 422 MD.ITEM_CATEGORY.TOO_DEEP；重複代碼 409 MD.ITEM_CATEGORY.DUPLICATE_CODE。</x:t>
         </x:is>
       </x:c>
       <x:c r="H24" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:98</x:t>
+          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:94</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.11.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.10.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B25" s="2" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </x:c>
       <x:c r="C25" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Item Brand</x:t>
+          <x:t xml:space="preserve">Item Category</x:t>
         </x:is>
       </x:c>
       <x:c r="D25" s="2" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </x:c>
       <x:c r="E25" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to edit item brand.</x:t>
+          <x:t xml:space="preserve">System should enable user to edit item category.</x:t>
         </x:is>
       </x:c>
       <x:c r="F25" s="2" t="inlineStr">
@@ -1112,19 +1112,19 @@
       </x:c>
       <x:c r="G25" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">具 EDIT 權限可帶版本修改名稱及啟用狀態（代碼不可變）；版本衝突 409，別公司或不存在 404 MD.ITEM_BRAND.NOT_FOUND。</x:t>
+          <x:t xml:space="preserve">具 EDIT 權限可帶版本修改名稱、啟用狀態與上層（整棵子樹一起移動）；代碼不可變。不可掛到自己或子孫下（422 MD.ITEM_CATEGORY.CYCLE），移動後子樹不可超過 5 層；上層不變時即使已停用亦可保留。版本衝突 409，別公司或不存在 404 MD.ITEM_CATEGORY.NOT_FOUND。</x:t>
         </x:is>
       </x:c>
       <x:c r="H25" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:99</x:t>
+          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:95</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.11.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.10.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B26" s="2" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </x:c>
       <x:c r="C26" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Item Brand</x:t>
+          <x:t xml:space="preserve">Item Category</x:t>
         </x:is>
       </x:c>
       <x:c r="D26" s="2" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </x:c>
       <x:c r="E26" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to delete item brand.</x:t>
+          <x:t xml:space="preserve">System should enable user to delete item category.</x:t>
         </x:is>
       </x:c>
       <x:c r="F26" s="2" t="inlineStr">
@@ -1154,19 +1154,19 @@
       </x:c>
       <x:c r="G26" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">具 DELETE 權限可帶版本軟刪除品牌，代碼仍保留。物料主檔（WU-MD-012）加入後，被物料引用的品牌回 409 MD.ITEM_BRAND.IN_USE，只可停用。</x:t>
+          <x:t xml:space="preserve">具 DELETE 權限可帶版本軟刪除分類；有未刪除子分類時回 409 MD.ITEM_CATEGORY.HAS_CHILDREN。物料主檔（WU-MD-012）加入後，被物料引用的分類亦不可刪除。</x:t>
         </x:is>
       </x:c>
       <x:c r="H26" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:100</x:t>
+          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:96</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.12.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.11.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B27" s="2" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </x:c>
       <x:c r="C27" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Item Master</x:t>
+          <x:t xml:space="preserve">Item Brand</x:t>
         </x:is>
       </x:c>
       <x:c r="D27" s="2" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </x:c>
       <x:c r="E27" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to view items.</x:t>
+          <x:t xml:space="preserve">System should enable user to view item brand.</x:t>
         </x:is>
       </x:c>
       <x:c r="F27" s="2" t="inlineStr">
@@ -1196,19 +1196,19 @@
       </x:c>
       <x:c r="G27" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MD.ITEM.VIEW 可在目前公司按代碼、名稱或規格搜尋，按代碼／名稱排序及分頁；含停用物料，不含其他公司。未選公司回 403。</x:t>
+          <x:t xml:space="preserve">具 MD.ITEM_BRAND.VIEW 可按目前公司以代碼或名稱搜尋、分頁及排序（代碼／名稱）品牌，含停用品牌；排除軟刪除及別公司資料；未選公司回 403。</x:t>
         </x:is>
       </x:c>
       <x:c r="H27" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:110</x:t>
+          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:97</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.12.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.11.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B28" s="2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </x:c>
       <x:c r="C28" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Item Master</x:t>
+          <x:t xml:space="preserve">Item Brand</x:t>
         </x:is>
       </x:c>
       <x:c r="D28" s="2" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </x:c>
       <x:c r="E28" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to create items.</x:t>
+          <x:t xml:space="preserve">System should enable user to create item brand.</x:t>
         </x:is>
       </x:c>
       <x:c r="F28" s="2" t="inlineStr">
@@ -1238,19 +1238,19 @@
       </x:c>
       <x:c r="G28" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MD.ITEM.CREATE 可建立公司內永久唯一、轉大寫的 1–30 位代碼、非空白名稱（最多 200 字）、可空規格（最多 500 字）、本公司啟用的基本單位、可空的啟用品牌與分類。重複代碼 409，別公司／停用參照 400。</x:t>
+          <x:t xml:space="preserve">具 CREATE 權限可建立公司內唯一代碼（規則同分類）、非空白名稱的品牌；重複代碼 409 MD.ITEM_BRAND.DUPLICATE_CODE。</x:t>
         </x:is>
       </x:c>
       <x:c r="H28" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:111</x:t>
+          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:98</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.12.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.11.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B29" s="2" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </x:c>
       <x:c r="C29" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Item Master</x:t>
+          <x:t xml:space="preserve">Item Brand</x:t>
         </x:is>
       </x:c>
       <x:c r="D29" s="2" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </x:c>
       <x:c r="E29" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to edit items.</x:t>
+          <x:t xml:space="preserve">System should enable user to edit item brand.</x:t>
         </x:is>
       </x:c>
       <x:c r="F29" s="2" t="inlineStr">
@@ -1280,19 +1280,19 @@
       </x:c>
       <x:c r="G29" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MD.ITEM.EDIT 可帶版本修改名稱、規格、基本單位、品牌、分類、啟用狀態，代碼不可改；原參照停用後可保留，重新選擇須啟用。舊版本 409、別公司物料 404。已被物料引用的單位、品牌、分類不可刪除，只可停用。</x:t>
+          <x:t xml:space="preserve">具 EDIT 權限可帶版本修改名稱及啟用狀態（代碼不可變）；版本衝突 409，別公司或不存在 404 MD.ITEM_BRAND.NOT_FOUND。</x:t>
         </x:is>
       </x:c>
       <x:c r="H29" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:112</x:t>
+          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:99</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.13.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.11.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B30" s="2" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </x:c>
       <x:c r="C30" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Unit of Measurement</x:t>
+          <x:t xml:space="preserve">Item Brand</x:t>
         </x:is>
       </x:c>
       <x:c r="D30" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </x:c>
       <x:c r="E30" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to view unit of measurement.</x:t>
+          <x:t xml:space="preserve">System should enable user to delete item brand.</x:t>
         </x:is>
       </x:c>
       <x:c r="F30" s="2" t="inlineStr">
@@ -1322,19 +1322,19 @@
       </x:c>
       <x:c r="G30" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">具 MD.UOM.VIEW 可按目前公司以代碼或名稱搜尋、分頁及排序（代碼／名稱）單位，含停用單位；可查看全部換算及以換算試算數量（結果按目標單位小數位數四捨五入）。排除軟刪除及別公司資料；未選公司回 403。</x:t>
+          <x:t xml:space="preserve">具 DELETE 權限可帶版本軟刪除品牌，代碼仍保留。物料主檔（WU-MD-012）加入後，被物料引用的品牌回 409 MD.ITEM_BRAND.IN_USE，只可停用。</x:t>
         </x:is>
       </x:c>
       <x:c r="H30" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:77</x:t>
+          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:100</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.13.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.13.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B31" s="2" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </x:c>
       <x:c r="E31" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to create unit of measurement.</x:t>
+          <x:t xml:space="preserve">System should enable user to view unit of measurement.</x:t>
         </x:is>
       </x:c>
       <x:c r="F31" s="2" t="inlineStr">
@@ -1364,19 +1364,19 @@
       </x:c>
       <x:c r="G31" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">具 CREATE 權限可建立公司內唯一代碼（1–30 英數、-、_，轉大寫）、非空白名稱（最多 200 字）及小數位數（0–6）的單位；重複代碼回 409 MD.UOM.DUPLICATE_CODE。可新增換算（1 來源 = 係數 目標；係數 &gt; 0、最多 9 位整數及 6 位小數）：兩端須為本公司啟用單位且不同；兩單位已可直接、反向或經其他單位換算時回 409 MD.UOM_CONVERSION.PATH_EXISTS。</x:t>
+          <x:t xml:space="preserve">具 MD.UOM.VIEW 可按目前公司以代碼或名稱搜尋、分頁及排序（代碼／名稱）單位，含停用單位；可查看全部換算及以換算試算數量（結果按目標單位小數位數四捨五入）。排除軟刪除及別公司資料；未選公司回 403。</x:t>
         </x:is>
       </x:c>
       <x:c r="H31" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:78</x:t>
+          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:77</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.13.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.13.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B32" s="2" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </x:c>
       <x:c r="E32" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to edit unit of measurement.</x:t>
+          <x:t xml:space="preserve">System should enable user to create unit of measurement.</x:t>
         </x:is>
       </x:c>
       <x:c r="F32" s="2" t="inlineStr">
@@ -1406,19 +1406,19 @@
       </x:c>
       <x:c r="G32" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">具 EDIT 權限可帶版本修改單位名稱、小數位數及啟用狀態（代碼不可變），以及換算係數；版本衝突 409，別公司或不存在 404（MD.UOM.NOT_FOUND／MD.UOM_CONVERSION.NOT_FOUND）。</x:t>
+          <x:t xml:space="preserve">具 CREATE 權限可建立公司內唯一代碼（1–30 英數、-、_，轉大寫）、非空白名稱（最多 200 字）及小數位數（0–6）的單位；重複代碼回 409 MD.UOM.DUPLICATE_CODE。可新增換算（1 來源 = 係數 目標；係數 &gt; 0、最多 9 位整數及 6 位小數）：兩端須為本公司啟用單位且不同；兩單位已可直接、反向或經其他單位換算時回 409 MD.UOM_CONVERSION.PATH_EXISTS。</x:t>
         </x:is>
       </x:c>
       <x:c r="H32" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:79</x:t>
+          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:78</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.13.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.13.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B33" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </x:c>
       <x:c r="E33" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to delete unit of measurement.</x:t>
+          <x:t xml:space="preserve">System should enable user to edit unit of measurement.</x:t>
         </x:is>
       </x:c>
       <x:c r="F33" s="2" t="inlineStr">
@@ -1448,19 +1448,19 @@
       </x:c>
       <x:c r="G33" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">具 DELETE 權限可帶版本軟刪除單位或換算；單位代碼刪除後仍保留；被換算引用的單位回 409 MD.UOM.IN_USE，只可停用。</x:t>
+          <x:t xml:space="preserve">具 EDIT 權限可帶版本修改單位名稱、小數位數及啟用狀態（代碼不可變），以及換算係數；版本衝突 409，別公司或不存在 404（MD.UOM.NOT_FOUND／MD.UOM_CONVERSION.NOT_FOUND）。</x:t>
         </x:is>
       </x:c>
       <x:c r="H33" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:80</x:t>
+          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:79</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.17.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.13.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B34" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </x:c>
       <x:c r="C34" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Parameter Settings</x:t>
+          <x:t xml:space="preserve">Unit of Measurement</x:t>
         </x:is>
       </x:c>
       <x:c r="D34" s="2" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </x:c>
       <x:c r="E34" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to view parameter settings.</x:t>
+          <x:t xml:space="preserve">System should enable user to delete unit of measurement.</x:t>
         </x:is>
       </x:c>
       <x:c r="F34" s="2" t="inlineStr">
@@ -1490,19 +1490,19 @@
       </x:c>
       <x:c r="G34" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">具 DELETE 權限可帶版本軟刪除單位或換算；單位代碼刪除後仍保留；被換算引用的單位回 409 MD.UOM.IN_USE，只可停用。</x:t>
         </x:is>
       </x:c>
       <x:c r="H34" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:234</x:t>
+          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:80</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.17.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.17.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B35" s="2" t="inlineStr">
@@ -1522,7 +1522,7 @@
       </x:c>
       <x:c r="E35" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to edit parameter settings.</x:t>
+          <x:t xml:space="preserve">System should enable user to view parameter settings.</x:t>
         </x:is>
       </x:c>
       <x:c r="F35" s="2" t="inlineStr">
@@ -1537,14 +1537,14 @@
       </x:c>
       <x:c r="H35" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:235</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:234</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.17.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.17.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B36" s="2" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </x:c>
       <x:c r="E36" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should let every module declare typed company parameters with defaults and read them in process.</x:t>
+          <x:t xml:space="preserve">System should enable user to edit parameter settings.</x:t>
         </x:is>
       </x:c>
       <x:c r="F36" s="2" t="inlineStr">
@@ -1579,14 +1579,14 @@
       </x:c>
       <x:c r="H36" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:236</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:235</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.17.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.17.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B37" s="2" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </x:c>
       <x:c r="E37" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should provide a parameter edit interface grouped by module.</x:t>
+          <x:t xml:space="preserve">System should let every module declare typed company parameters with defaults and read them in process.</x:t>
         </x:is>
       </x:c>
       <x:c r="F37" s="2" t="inlineStr">
@@ -1621,14 +1621,14 @@
       </x:c>
       <x:c r="H37" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:237</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:236</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.18.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.17.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B38" s="2" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </x:c>
       <x:c r="C38" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Print Settings</x:t>
+          <x:t xml:space="preserve">Parameter Settings</x:t>
         </x:is>
       </x:c>
       <x:c r="D38" s="2" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </x:c>
       <x:c r="E38" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to view print settings.</x:t>
+          <x:t xml:space="preserve">System should provide a parameter edit interface grouped by module.</x:t>
         </x:is>
       </x:c>
       <x:c r="F38" s="2" t="inlineStr">
@@ -1663,14 +1663,14 @@
       </x:c>
       <x:c r="H38" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:250</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:237</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.18.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.18.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B39" s="2" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </x:c>
       <x:c r="E39" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to edit print settings.</x:t>
+          <x:t xml:space="preserve">System should enable user to view print settings.</x:t>
         </x:is>
       </x:c>
       <x:c r="F39" s="2" t="inlineStr">
@@ -1705,14 +1705,14 @@
       </x:c>
       <x:c r="H39" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:251</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:250</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.18.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.18.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B40" s="2" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </x:c>
       <x:c r="E40" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should let printing modules read the company's print settings.</x:t>
+          <x:t xml:space="preserve">System should enable user to edit print settings.</x:t>
         </x:is>
       </x:c>
       <x:c r="F40" s="2" t="inlineStr">
@@ -1747,14 +1747,14 @@
       </x:c>
       <x:c r="H40" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:252</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:251</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.19.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.18.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B41" s="2" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </x:c>
       <x:c r="C41" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Logo &amp; Stamp</x:t>
+          <x:t xml:space="preserve">Print Settings</x:t>
         </x:is>
       </x:c>
       <x:c r="D41" s="2" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </x:c>
       <x:c r="E41" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to view the logo and stamp.</x:t>
+          <x:t xml:space="preserve">System should let printing modules read the company's print settings.</x:t>
         </x:is>
       </x:c>
       <x:c r="F41" s="2" t="inlineStr">
@@ -1789,14 +1789,14 @@
       </x:c>
       <x:c r="H41" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:264</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:252</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.19.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.19.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B42" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </x:c>
       <x:c r="E42" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to edit the logo and stamp.</x:t>
+          <x:t xml:space="preserve">System should enable user to view the logo and stamp.</x:t>
         </x:is>
       </x:c>
       <x:c r="F42" s="2" t="inlineStr">
@@ -1831,14 +1831,14 @@
       </x:c>
       <x:c r="H42" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:265</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:264</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.19.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.19.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B43" s="2" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </x:c>
       <x:c r="E43" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should let printing modules read the company's logo and stamp.</x:t>
+          <x:t xml:space="preserve">System should enable user to edit the logo and stamp.</x:t>
         </x:is>
       </x:c>
       <x:c r="F43" s="2" t="inlineStr">
@@ -1873,14 +1873,14 @@
       </x:c>
       <x:c r="H43" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:266</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:265</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.20.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.19.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B44" s="2" t="inlineStr">
@@ -1890,17 +1890,17 @@
       </x:c>
       <x:c r="C44" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Company Management</x:t>
+          <x:t xml:space="preserve">Logo &amp; Stamp</x:t>
         </x:is>
       </x:c>
       <x:c r="D44" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1.2</x:t>
+          <x:t xml:space="preserve">1.0</x:t>
         </x:is>
       </x:c>
       <x:c r="E44" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to view company details.</x:t>
+          <x:t xml:space="preserve">System should let printing modules read the company's logo and stamp.</x:t>
         </x:is>
       </x:c>
       <x:c r="F44" s="2" t="inlineStr">
@@ -1910,19 +1910,19 @@
       </x:c>
       <x:c r="G44" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">僅有組織檢視權的用戶可見其獲授權且未刪除的公司；預設只列啟用公司，勾選「顯示已停用」時一併列出停用公司；列表支援分頁、關鍵字及代碼／名稱排序；無權限回 403。</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="H44" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:13</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:266</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.20.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.20.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B45" s="2" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </x:c>
       <x:c r="E45" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to create a company.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to view company details.</x:t>
         </x:is>
       </x:c>
       <x:c r="F45" s="2" t="inlineStr">
@@ -1952,19 +1952,19 @@
       </x:c>
       <x:c r="G45" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">代碼全系統唯一；代碼與名稱必填；代碼限 1–30 字元的 ASCII 英文、數字、-、_，保存為大寫；重複代碼回 409；建立者在同一交易內獲授權新公司，角色沿用其在目前公司的角色（ADR-015）。</x:t>
+          <x:t xml:space="preserve">僅有組織檢視權的用戶可見其獲授權且未刪除的公司；預設只列啟用公司，勾選「顯示已停用」時一併列出停用公司；列表支援分頁、關鍵字及代碼／名稱排序；無權限回 403。</x:t>
         </x:is>
       </x:c>
       <x:c r="H45" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:14</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:13</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.20.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.20.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B46" s="2" t="inlineStr">
@@ -1984,7 +1984,7 @@
       </x:c>
       <x:c r="E46" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to edit a company.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to create a company.</x:t>
         </x:is>
       </x:c>
       <x:c r="F46" s="2" t="inlineStr">
@@ -1994,19 +1994,19 @@
       </x:c>
       <x:c r="G46" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">版本不符回 409；審計欄位記錄修改者；目標公司不是用戶獲授權的公司時回 404；操作者在被修改的公司（含已停用）亦須有 SYS.COMPANY.EDIT，否則 403（ADR-032）。</x:t>
+          <x:t xml:space="preserve">代碼全系統唯一；代碼與名稱必填；代碼限 1–30 字元的 ASCII 英文、數字、-、_，保存為大寫；重複代碼回 409；建立者在同一交易內獲授權新公司，角色沿用其在目前公司的角色（ADR-015）。</x:t>
         </x:is>
       </x:c>
       <x:c r="H46" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:15</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:14</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.20.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.20.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B47" s="2" t="inlineStr">
@@ -2021,12 +2021,12 @@
       </x:c>
       <x:c r="D47" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1.0</x:t>
+          <x:t xml:space="preserve">1.2</x:t>
         </x:is>
       </x:c>
       <x:c r="E47" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to deactivate a company.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to edit a company.</x:t>
         </x:is>
       </x:c>
       <x:c r="F47" s="2" t="inlineStr">
@@ -2036,19 +2036,19 @@
       </x:c>
       <x:c r="G47" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">停用後不能成為新操作的公司上下文；歷史資料保留。</x:t>
+          <x:t xml:space="preserve">版本不符回 409；審計欄位記錄修改者；目標公司不是用戶獲授權的公司時回 404；操作者在被修改的公司（含已停用）亦須有 SYS.COMPANY.EDIT，否則 403（ADR-032）。</x:t>
         </x:is>
       </x:c>
       <x:c r="H47" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:16</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:15</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.21.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.20.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B48" s="2" t="inlineStr">
@@ -2058,7 +2058,7 @@
       </x:c>
       <x:c r="C48" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Branch Management</x:t>
+          <x:t xml:space="preserve">Company Management</x:t>
         </x:is>
       </x:c>
       <x:c r="D48" s="2" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </x:c>
       <x:c r="E48" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to view branches in the selected company.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to deactivate a company.</x:t>
         </x:is>
       </x:c>
       <x:c r="F48" s="2" t="inlineStr">
@@ -2078,19 +2078,19 @@
       </x:c>
       <x:c r="G48" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">公司 A 的查詢不返回公司 B 分店；未選公司結果為空。</x:t>
+          <x:t xml:space="preserve">停用後不能成為新操作的公司上下文；歷史資料保留。</x:t>
         </x:is>
       </x:c>
       <x:c r="H48" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:17</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:16</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.21.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.21.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B49" s="2" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </x:c>
       <x:c r="E49" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to create a branch.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to view branches in the selected company.</x:t>
         </x:is>
       </x:c>
       <x:c r="F49" s="2" t="inlineStr">
@@ -2120,19 +2120,19 @@
       </x:c>
       <x:c r="G49" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">公司內代碼唯一；所屬公司必須為授權公司。</x:t>
+          <x:t xml:space="preserve">公司 A 的查詢不返回公司 B 分店；未選公司結果為空。</x:t>
         </x:is>
       </x:c>
       <x:c r="H49" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:18</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:17</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.21.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.21.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B50" s="2" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </x:c>
       <x:c r="E50" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to edit or deactivate a branch.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to create a branch.</x:t>
         </x:is>
       </x:c>
       <x:c r="F50" s="2" t="inlineStr">
@@ -2162,19 +2162,19 @@
       </x:c>
       <x:c r="G50" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">版本不符回 409；被引用時只可停用，不得刪除。</x:t>
+          <x:t xml:space="preserve">公司內代碼唯一；所屬公司必須為授權公司。</x:t>
         </x:is>
       </x:c>
       <x:c r="H50" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:19</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:18</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.22.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.21.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B51" s="2" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </x:c>
       <x:c r="C51" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Department Management</x:t>
+          <x:t xml:space="preserve">Branch Management</x:t>
         </x:is>
       </x:c>
       <x:c r="D51" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </x:c>
       <x:c r="E51" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to view departments in the selected company.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to edit or deactivate a branch.</x:t>
         </x:is>
       </x:c>
       <x:c r="F51" s="2" t="inlineStr">
@@ -2204,19 +2204,19 @@
       </x:c>
       <x:c r="G51" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">公司隔離、軟刪除篩選生效。</x:t>
+          <x:t xml:space="preserve">版本不符回 409；被引用時只可停用，不得刪除。</x:t>
         </x:is>
       </x:c>
       <x:c r="H51" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:20</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:19</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.22.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.22.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B52" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </x:c>
       <x:c r="E52" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to create a department under a branch or parent department.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to view departments in the selected company.</x:t>
         </x:is>
       </x:c>
       <x:c r="F52" s="2" t="inlineStr">
@@ -2246,19 +2246,19 @@
       </x:c>
       <x:c r="G52" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">分店與上級部門必須屬於同一公司；不得循環參照。</x:t>
+          <x:t xml:space="preserve">公司隔離、軟刪除篩選生效。</x:t>
         </x:is>
       </x:c>
       <x:c r="H52" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:21</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:20</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.22.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.22.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B53" s="2" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </x:c>
       <x:c r="E53" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to edit or deactivate a department.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to create a department under a branch or parent department.</x:t>
         </x:is>
       </x:c>
       <x:c r="F53" s="2" t="inlineStr">
@@ -2288,19 +2288,19 @@
       </x:c>
       <x:c r="G53" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">版本不符回 409；被引用時只可停用。</x:t>
+          <x:t xml:space="preserve">分店與上級部門必須屬於同一公司；不得循環參照。</x:t>
         </x:is>
       </x:c>
       <x:c r="H53" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:22</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:21</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.23.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.22.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B54" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </x:c>
       <x:c r="C54" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">User Identity and Password Security</x:t>
+          <x:t xml:space="preserve">Department Management</x:t>
         </x:is>
       </x:c>
       <x:c r="D54" s="2" t="inlineStr">
@@ -2320,7 +2320,7 @@
       </x:c>
       <x:c r="E54" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to create a unique user identity.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to edit or deactivate a department.</x:t>
         </x:is>
       </x:c>
       <x:c r="F54" s="2" t="inlineStr">
@@ -2330,19 +2330,19 @@
       </x:c>
       <x:c r="G54" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">帳號不分大小寫唯一，停用及軟刪除後仍不可重用；僅保存雜湊，不保存明文密碼。</x:t>
+          <x:t xml:space="preserve">版本不符回 409；被引用時只可停用。</x:t>
         </x:is>
       </x:c>
       <x:c r="H54" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:54</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:22</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="55">
       <x:c r="A55" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.23.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.23.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B55" s="2" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </x:c>
       <x:c r="E55" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enforce a configurable password policy.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to create a unique user identity.</x:t>
         </x:is>
       </x:c>
       <x:c r="F55" s="2" t="inlineStr">
@@ -2372,19 +2372,19 @@
       </x:c>
       <x:c r="G55" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">預設 12–128 字元且含大小寫、數字及符號；長度、複雜度與到期天數可由設定調整，不合法設定拒絕啟動。</x:t>
+          <x:t xml:space="preserve">帳號不分大小寫唯一，停用及軟刪除後仍不可重用；僅保存雜湊，不保存明文密碼。</x:t>
         </x:is>
       </x:c>
       <x:c r="H55" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:55</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:54</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="56">
       <x:c r="A56" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.23.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.23.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B56" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </x:c>
       <x:c r="E56" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should lock an account after five consecutive failed password attempts.</x:t>
+          <x:t xml:space="preserve">System should enforce a configurable password policy.</x:t>
         </x:is>
       </x:c>
       <x:c r="F56" s="2" t="inlineStr">
@@ -2414,19 +2414,19 @@
       </x:c>
       <x:c r="G56" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">第 5 次連續失敗鎖定 15 分鐘；鎖定期間正確密碼亦不得通過；鎖定到期後開啟新失敗計數窗口，成功後清除計數。</x:t>
+          <x:t xml:space="preserve">預設 12–128 字元且含大小寫、數字及符號；長度、複雜度與到期天數可由設定調整，不合法設定拒絕啟動。</x:t>
         </x:is>
       </x:c>
       <x:c r="H56" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:56</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:55</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="57">
       <x:c r="A57" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.23.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.23.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B57" s="2" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </x:c>
       <x:c r="E57" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should determine whether a user's password has expired.</x:t>
+          <x:t xml:space="preserve">System should lock an account after five consecutive failed password attempts.</x:t>
         </x:is>
       </x:c>
       <x:c r="F57" s="2" t="inlineStr">
@@ -2456,19 +2456,19 @@
       </x:c>
       <x:c r="G57" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">依設定天數及 password_changed_at 判斷；0 代表不設到期。登入簽發 Token 前必須檢查。</x:t>
+          <x:t xml:space="preserve">第 5 次連續失敗鎖定 15 分鐘；鎖定期間正確密碼亦不得通過；鎖定到期後開啟新失敗計數窗口，成功後清除計數。</x:t>
         </x:is>
       </x:c>
       <x:c r="H57" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:57</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:56</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="58">
       <x:c r="A58" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.23.5</x:t>
+          <x:t xml:space="preserve">REQ_F4118.23.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B58" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </x:c>
       <x:c r="E58" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should list the users of the current company with paging, keyword and sorting.</x:t>
+          <x:t xml:space="preserve">System should determine whether a user's password has expired.</x:t>
         </x:is>
       </x:c>
       <x:c r="F58" s="2" t="inlineStr">
@@ -2498,19 +2498,19 @@
       </x:c>
       <x:c r="G58" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">只列在目前公司有用戶公司關聯的用戶（含停用）；關鍵字不分大小寫比對帳號；排序 username／-username，其他欄位 400；回應不含雜湊、失敗次數及鎖定期限，只回 isLocked、isPasswordExpired（ADR-016）。</x:t>
+          <x:t xml:space="preserve">依設定天數及 password_changed_at 判斷；0 代表不設到期。登入簽發 Token 前必須檢查。</x:t>
         </x:is>
       </x:c>
       <x:c r="H58" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:58</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:57</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="59">
       <x:c r="A59" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.23.6</x:t>
+          <x:t xml:space="preserve">REQ_F4118.23.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B59" s="2" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </x:c>
       <x:c r="E59" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to create a user in the current company.</x:t>
+          <x:t xml:space="preserve">System should list the users of the current company with paging, keyword and sorting.</x:t>
         </x:is>
       </x:c>
       <x:c r="F59" s="2" t="inlineStr">
@@ -2540,19 +2540,19 @@
       </x:c>
       <x:c r="G59" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">需 SYS.USER.CREATE；同一交易建立身分及目前公司的預設關聯（無角色）；重複帳號（不分大小寫、含他公司）409 SYS.USER.DUPLICATE；弱密碼或帳號格式錯誤 400；建立後可登入。</x:t>
+          <x:t xml:space="preserve">只列在目前公司有用戶公司關聯的用戶（含停用）；關鍵字不分大小寫比對帳號；排序 username／-username，其他欄位 400；回應不含雜湊、失敗次數及鎖定期限，只回 isLocked、isPasswordExpired（ADR-016）。</x:t>
         </x:is>
       </x:c>
       <x:c r="H59" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:59</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:58</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="60">
       <x:c r="A60" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.23.7</x:t>
+          <x:t xml:space="preserve">REQ_F4118.23.6</x:t>
         </x:is>
       </x:c>
       <x:c r="B60" s="2" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </x:c>
       <x:c r="D60" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1.1</x:t>
+          <x:t xml:space="preserve">1.0</x:t>
         </x:is>
       </x:c>
       <x:c r="E60" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to activate or deactivate a user.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to create a user in the current company.</x:t>
         </x:is>
       </x:c>
       <x:c r="F60" s="2" t="inlineStr">
@@ -2582,19 +2582,19 @@
       </x:c>
       <x:c r="G60" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">需 SYS.USER.EDIT 並帶 version（過期 409）；停用後不可登入與刷新，重新啟用後可登入；不可停用自己 422 SYS.USER.SELF_DEACTIVATION；他公司用戶 404；用戶亦屬於其他公司時，操作者在每間已啟用關聯的公司都要有 SYS.USER.EDIT（否則 403 COMMON.PERMISSION.DENIED），且用戶角色不超出操作者權限（否則 403 SYS.ROLE.BEYOND_AUTHORITY），ADR-032。</x:t>
+          <x:t xml:space="preserve">需 SYS.USER.CREATE；同一交易建立身分及目前公司的預設關聯（無角色）；重複帳號（不分大小寫、含他公司）409 SYS.USER.DUPLICATE；弱密碼或帳號格式錯誤 400；建立後可登入。</x:t>
         </x:is>
       </x:c>
       <x:c r="H60" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:60</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:59</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="61">
       <x:c r="A61" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.23.8</x:t>
+          <x:t xml:space="preserve">REQ_F4118.23.7</x:t>
         </x:is>
       </x:c>
       <x:c r="B61" s="2" t="inlineStr">
@@ -2614,7 +2614,7 @@
       </x:c>
       <x:c r="E61" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to reset a password and unlock a locked user.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to activate or deactivate a user.</x:t>
         </x:is>
       </x:c>
       <x:c r="F61" s="2" t="inlineStr">
@@ -2624,19 +2624,19 @@
       </x:c>
       <x:c r="G61" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">重設密碼需 SYS.USER.RESET_PASSWORD，依密碼政策驗證，重新起算到期並清除鎖定，舊密碼即失效；解鎖需 SYS.USER.EDIT，清除失敗計數與鎖定，未鎖定時亦回 204；他公司用戶 404；跨公司與角色上限檢查同 REQ_F4118.23.7（ADR-032）。</x:t>
+          <x:t xml:space="preserve">需 SYS.USER.EDIT 並帶 version（過期 409）；停用後不可登入與刷新，重新啟用後可登入；不可停用自己 422 SYS.USER.SELF_DEACTIVATION；他公司用戶 404；用戶亦屬於其他公司時，操作者在每間已啟用關聯的公司都要有 SYS.USER.EDIT（否則 403 COMMON.PERMISSION.DENIED），且用戶角色不超出操作者權限（否則 403 SYS.ROLE.BEYOND_AUTHORITY），ADR-032。</x:t>
         </x:is>
       </x:c>
       <x:c r="H61" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:61</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:60</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="62">
       <x:c r="A62" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.24.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.23.8</x:t>
         </x:is>
       </x:c>
       <x:c r="B62" s="2" t="inlineStr">
@@ -2646,17 +2646,17 @@
       </x:c>
       <x:c r="C62" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Login, Token and Captcha</x:t>
+          <x:t xml:space="preserve">User Identity and Password Security</x:t>
         </x:is>
       </x:c>
       <x:c r="D62" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1.0</x:t>
+          <x:t xml:space="preserve">1.1</x:t>
         </x:is>
       </x:c>
       <x:c r="E62" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow a user to log in with username, password and a numeric captcha.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to reset a password and unlock a locked user.</x:t>
         </x:is>
       </x:c>
       <x:c r="F62" s="2" t="inlineStr">
@@ -2666,19 +2666,19 @@
       </x:c>
       <x:c r="G62" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">帳號不分大小寫；Captcha 4–6 位數字，答案只存伺服器端，驗證一次即作廢（不論對錯）；帳密錯誤、帳號不存在、停用或鎖定一律回 401 SYS.AUTH.INVALID_CREDENTIALS；密碼到期回 403 SYS.AUTH.PASSWORD_EXPIRED 且不發 Token。</x:t>
+          <x:t xml:space="preserve">重設密碼需 SYS.USER.RESET_PASSWORD，依密碼政策驗證，重新起算到期並清除鎖定，舊密碼即失效；解鎖需 SYS.USER.EDIT，清除失敗計數與鎖定，未鎖定時亦回 204；他公司用戶 404；跨公司與角色上限檢查同 REQ_F4118.23.7（ADR-032）。</x:t>
         </x:is>
       </x:c>
       <x:c r="H62" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:73</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:61</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="63">
       <x:c r="A63" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.24.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.24.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B63" s="2" t="inlineStr">
@@ -2698,7 +2698,7 @@
       </x:c>
       <x:c r="E63" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should issue a 15-minute access token and a 7-day rotating refresh token.</x:t>
+          <x:t xml:space="preserve">System should allow a user to log in with username, password and a numeric captcha.</x:t>
         </x:is>
       </x:c>
       <x:c r="F63" s="2" t="inlineStr">
@@ -2708,19 +2708,19 @@
       </x:c>
       <x:c r="G63" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Access Token 為 HS256 JWT，sub 為用戶 Id；Refresh Token 只以 SHA-256 雜湊存 Redis，使用一次即輪替，並發重放只有一個成功。</x:t>
+          <x:t xml:space="preserve">帳號不分大小寫；Captcha 4–6 位數字，答案只存伺服器端，驗證一次即作廢（不論對錯）；帳密錯誤、帳號不存在、停用或鎖定一律回 401 SYS.AUTH.INVALID_CREDENTIALS；密碼到期回 403 SYS.AUTH.PASSWORD_EXPIRED 且不發 Token。</x:t>
         </x:is>
       </x:c>
       <x:c r="H63" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:74</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:73</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="64">
       <x:c r="A64" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.24.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.24.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B64" s="2" t="inlineStr">
@@ -2740,7 +2740,7 @@
       </x:c>
       <x:c r="E64" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow a logged-in user to log out and invalidate the refresh token.</x:t>
+          <x:t xml:space="preserve">System should issue a 15-minute access token and a 7-day rotating refresh token.</x:t>
         </x:is>
       </x:c>
       <x:c r="F64" s="2" t="inlineStr">
@@ -2750,19 +2750,19 @@
       </x:c>
       <x:c r="G64" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">登出須帶有效 Access Token；只撤銷屬於本人的 Refresh Token，撤銷後刷新回 401。</x:t>
+          <x:t xml:space="preserve">Access Token 為 HS256 JWT，sub 為用戶 Id；Refresh Token 只以 SHA-256 雜湊存 Redis，使用一次即輪替，並發重放只有一個成功。</x:t>
         </x:is>
       </x:c>
       <x:c r="H64" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:75</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:74</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="65">
       <x:c r="A65" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.24.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.24.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B65" s="2" t="inlineStr">
@@ -2782,7 +2782,7 @@
       </x:c>
       <x:c r="E65" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should provide a development-only captcha master code with startup protection.</x:t>
+          <x:t xml:space="preserve">System should allow a logged-in user to log out and invalidate the refresh token.</x:t>
         </x:is>
       </x:c>
       <x:c r="F65" s="2" t="inlineStr">
@@ -2792,19 +2792,19 @@
       </x:c>
       <x:c r="G65" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Captcha:MasterCode 只在 Development 生效且須為 4–6 位數字；其他環境有設定即寫 Error 並拒絕啟動；每次使用寫 Warning（帳號、IP），並寫 sys_audit_log 安全事件 MASTER_CODE_LOGIN（REQ_F4118.27.3）。</x:t>
+          <x:t xml:space="preserve">登出須帶有效 Access Token；只撤銷屬於本人的 Refresh Token，撤銷後刷新回 401。</x:t>
         </x:is>
       </x:c>
       <x:c r="H65" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:76</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:75</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="66">
       <x:c r="A66" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.24.5</x:t>
+          <x:t xml:space="preserve">REQ_F4118.24.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B66" s="2" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </x:c>
       <x:c r="E66" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should provide a trilingual login page that keeps the session and refreshes tokens automatically.</x:t>
+          <x:t xml:space="preserve">System should provide a development-only captcha master code with startup protection.</x:t>
         </x:is>
       </x:c>
       <x:c r="F66" s="2" t="inlineStr">
@@ -2834,19 +2834,19 @@
       </x:c>
       <x:c r="G66" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">未登入進入主框架導向 /login?returnUrl=…，登入後只回到站內路徑；Captcha 元件只收 4–6 位數字，失敗後換新圖並清空密碼；錯誤依 errorCode 三語顯示；API 請求帶 Bearer，401 時只刷新一次並重送，並發 401 共用同一 refresh；刷新失敗清除 Session 回登入頁；登出撤銷 Refresh Token，伺服器失敗也清除本機 Session。</x:t>
+          <x:t xml:space="preserve">Captcha:MasterCode 只在 Development 生效且須為 4–6 位數字；其他環境有設定即寫 Error 並拒絕啟動；每次使用寫 Warning（帳號、IP），並寫 sys_audit_log 安全事件 MASTER_CODE_LOGIN（REQ_F4118.27.3）。</x:t>
         </x:is>
       </x:c>
       <x:c r="H66" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:77</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:76</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.25.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.24.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B67" s="2" t="inlineStr">
@@ -2856,7 +2856,7 @@
       </x:c>
       <x:c r="C67" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Role, Permission and Data Scope</x:t>
+          <x:t xml:space="preserve">Login, Token and Captcha</x:t>
         </x:is>
       </x:c>
       <x:c r="D67" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </x:c>
       <x:c r="E67" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to view roles and the permission catalog.</x:t>
+          <x:t xml:space="preserve">System should provide a trilingual login page that keeps the session and refreshes tokens automatically.</x:t>
         </x:is>
       </x:c>
       <x:c r="F67" s="2" t="inlineStr">
@@ -2876,19 +2876,19 @@
       </x:c>
       <x:c r="G67" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">需 SYS.ROLE.VIEW；角色列表支援分頁、關鍵字（代碼／名稱）、code／name 排序；權限目錄列出各模組宣告的全部代碼；已軟刪除角色不顯示，查詢回 404。</x:t>
+          <x:t xml:space="preserve">未登入進入主框架導向 /login?returnUrl=…，登入後只回到站內路徑；Captcha 元件只收 4–6 位數字，失敗後換新圖並清空密碼；錯誤依 errorCode 三語顯示；API 請求帶 Bearer，401 時只刷新一次並重送，並發 401 共用同一 refresh；刷新失敗清除 Session 回登入頁；登出撤銷 Refresh Token，伺服器失敗也清除本機 Session。</x:t>
         </x:is>
       </x:c>
       <x:c r="H67" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:89</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:77</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.25.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.25.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B68" s="2" t="inlineStr">
@@ -2908,7 +2908,7 @@
       </x:c>
       <x:c r="E68" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to create a role with permissions and a data scope.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to view roles and the permission catalog.</x:t>
         </x:is>
       </x:c>
       <x:c r="F68" s="2" t="inlineStr">
@@ -2918,19 +2918,19 @@
       </x:c>
       <x:c r="G68" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">需 SYS.ROLE.CREATE；代碼 1–50 字元 ASCII 英文、數字、-、_，保存為大寫，全系統唯一（含已刪除），重複回 409 SYS.ROLE.DUPLICATE_CODE；權限代碼不分大小寫輸入，必須在權限目錄內，否則 400；資料範圍為 Self／Department／Branch／Company。</x:t>
+          <x:t xml:space="preserve">需 SYS.ROLE.VIEW；角色列表支援分頁、關鍵字（代碼／名稱）、code／name 排序；權限目錄列出各模組宣告的全部代碼；已軟刪除角色不顯示，查詢回 404。</x:t>
         </x:is>
       </x:c>
       <x:c r="H68" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:90</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:89</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="69">
       <x:c r="A69" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.25.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.25.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B69" s="2" t="inlineStr">
@@ -2950,7 +2950,7 @@
       </x:c>
       <x:c r="E69" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to edit or deactivate a role.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to create a role with permissions and a data scope.</x:t>
         </x:is>
       </x:c>
       <x:c r="F69" s="2" t="inlineStr">
@@ -2960,19 +2960,19 @@
       </x:c>
       <x:c r="G69" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">需 SYS.ROLE.EDIT；帶 version，不符回 409，且權限集合不變（同一交易）；停用角色立即不再授予權限。角色是全系統定義：操作者在角色已指派的每間公司都必須全權，否則 403 SYS.AUTHORITY.FULL_ACCESS_REQUIRED（ADR-033）。</x:t>
+          <x:t xml:space="preserve">需 SYS.ROLE.CREATE；代碼 1–50 字元 ASCII 英文、數字、-、_，保存為大寫，全系統唯一（含已刪除），重複回 409 SYS.ROLE.DUPLICATE_CODE；權限代碼不分大小寫輸入，必須在權限目錄內，否則 400；資料範圍為 Self／Department／Branch／Company。</x:t>
         </x:is>
       </x:c>
       <x:c r="H69" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:91</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:90</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="70">
       <x:c r="A70" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.25.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.25.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B70" s="2" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </x:c>
       <x:c r="E70" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to delete an unused role.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to edit or deactivate a role.</x:t>
         </x:is>
       </x:c>
       <x:c r="F70" s="2" t="inlineStr">
@@ -3002,19 +3002,19 @@
       </x:c>
       <x:c r="G70" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">需 SYS.ROLE.DELETE；仍有用戶使用回 422 SYS.ROLE.IN_USE；軟刪除，代碼不可重用。</x:t>
+          <x:t xml:space="preserve">需 SYS.ROLE.EDIT；帶 version，不符回 409，且權限集合不變（同一交易）；停用角色立即不再授予權限。角色是全系統定義：操作者在角色已指派的每間公司都必須全權，否則 403 SYS.AUTHORITY.FULL_ACCESS_REQUIRED（ADR-033）。</x:t>
         </x:is>
       </x:c>
       <x:c r="H70" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:92</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:91</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="71">
       <x:c r="A71" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.25.5</x:t>
+          <x:t xml:space="preserve">REQ_F4118.25.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B71" s="2" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </x:c>
       <x:c r="E71" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enforce permission codes on every API with the backend as the authority.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to delete an unused role.</x:t>
         </x:is>
       </x:c>
       <x:c r="F71" s="2" t="inlineStr">
@@ -3044,19 +3044,19 @@
       </x:c>
       <x:c r="G71" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">每個 API 動作標註 模組.資源.動作 權限（ArchitectureTests 檢查）；未登入 401；缺權限或沒有公司上下文 403 COMMON.PERMISSION.DENIED；已登入請求的 X-Company-Id 不可存取（未授權、用戶公司關聯停用、公司停用）一律 403 COMMON.COMPANY.ACCESS_DENIED。</x:t>
+          <x:t xml:space="preserve">需 SYS.ROLE.DELETE；仍有用戶使用回 422 SYS.ROLE.IN_USE；軟刪除，代碼不可重用。</x:t>
         </x:is>
       </x:c>
       <x:c r="H71" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:93</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:92</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="72">
       <x:c r="A72" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.25.6</x:t>
+          <x:t xml:space="preserve">REQ_F4118.25.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B72" s="2" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </x:c>
       <x:c r="D72" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1.1</x:t>
+          <x:t xml:space="preserve">1.0</x:t>
         </x:is>
       </x:c>
       <x:c r="E72" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to grant a user access to a company with roles, organization and default company.</x:t>
+          <x:t xml:space="preserve">System should enforce permission codes on every API with the backend as the authority.</x:t>
         </x:is>
       </x:c>
       <x:c r="F72" s="2" t="inlineStr">
@@ -3086,19 +3086,19 @@
       </x:c>
       <x:c r="G72" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">需 SYS.USER.EDIT；公司必須啟用；分店／部門必須屬於該公司且啟用；角色必須存在且啟用；角色整組取代；每位用戶最多一間預設公司（設定新預設會取消舊預設）。用戶不存在或不屬於目前公司回 404 SYS.USER.NOT_FOUND；目標公司不是操作者獲授權的公司回 404 SYS.COMPANY.NOT_FOUND；不可停用自己的公司授權（422 SYS.USER.SELF_DEACTIVATION）（ADR-017）。操作者在目標公司亦須有 SYS.USER.EDIT（否則 403 COMMON.PERMISSION.DENIED）；新增或移除的角色須在操作者權限之內（全權角色只限全權操作者；一般角色的每個權限操作者都有且範圍不窄於角色），否則 403 SYS.ROLE.BEYOND_AUTHORITY；不可變更自己的角色（422 SYS.USER.SELF_ROLE_CHANGE），角色不變時可改組織與預設公司（ADR-032）。</x:t>
+          <x:t xml:space="preserve">每個 API 動作標註 模組.資源.動作 權限（ArchitectureTests 檢查）；未登入 401；缺權限或沒有公司上下文 403 COMMON.PERMISSION.DENIED；已登入請求的 X-Company-Id 不可存取（未授權、用戶公司關聯停用、公司停用）一律 403 COMMON.COMPANY.ACCESS_DENIED。</x:t>
         </x:is>
       </x:c>
       <x:c r="H72" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:94</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:93</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="73">
       <x:c r="A73" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.25.7</x:t>
+          <x:t xml:space="preserve">REQ_F4118.25.6</x:t>
         </x:is>
       </x:c>
       <x:c r="B73" s="2" t="inlineStr">
@@ -3113,12 +3113,12 @@
       </x:c>
       <x:c r="D73" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1.0</x:t>
+          <x:t xml:space="preserve">1.1</x:t>
         </x:is>
       </x:c>
       <x:c r="E73" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should resolve the user's effective permissions and data scope per company and hide unauthorized UI.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to grant a user access to a company with roles, organization and default company.</x:t>
         </x:is>
       </x:c>
       <x:c r="F73" s="2" t="inlineStr">
@@ -3128,19 +3128,19 @@
       </x:c>
       <x:c r="G73" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">同一權限取各啟用角色最寬的資料範圍；全權角色視為全部權限、全公司範圍；分店／部門範圍但用戶無對應歸屬時退回本人。GET /api/v1/sys/auth/authorization 回傳可存取公司（預設在前）與目前公司權限；前端 *erpHasPermission、permissionGuard 與選單依此隱藏，切換公司重新載入；本機記住的公司不可存取時改用預設公司。</x:t>
+          <x:t xml:space="preserve">需 SYS.USER.EDIT；公司必須啟用；分店／部門必須屬於該公司且啟用；角色必須存在且啟用；角色整組取代；每位用戶最多一間預設公司（設定新預設會取消舊預設）。用戶不存在或不屬於目前公司回 404 SYS.USER.NOT_FOUND；目標公司不是操作者獲授權的公司回 404 SYS.COMPANY.NOT_FOUND；不可停用自己的公司授權（422 SYS.USER.SELF_DEACTIVATION）（ADR-017）。操作者在目標公司亦須有 SYS.USER.EDIT（否則 403 COMMON.PERMISSION.DENIED）；新增或移除的角色須在操作者權限之內（全權角色只限全權操作者；一般角色的每個權限操作者都有且範圍不窄於角色），否則 403 SYS.ROLE.BEYOND_AUTHORITY；不可變更自己的角色（422 SYS.USER.SELF_ROLE_CHANGE），角色不變時可改組織與預設公司（ADR-032）。</x:t>
         </x:is>
       </x:c>
       <x:c r="H73" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:95</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:94</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="74">
       <x:c r="A74" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.25.8</x:t>
+          <x:t xml:space="preserve">REQ_F4118.25.7</x:t>
         </x:is>
       </x:c>
       <x:c r="B74" s="2" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </x:c>
       <x:c r="E74" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to view a user's company access, organization and roles.</x:t>
+          <x:t xml:space="preserve">System should resolve the user's effective permissions and data scope per company and hide unauthorized UI.</x:t>
         </x:is>
       </x:c>
       <x:c r="F74" s="2" t="inlineStr">
@@ -3170,19 +3170,19 @@
       </x:c>
       <x:c r="G74" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">需 SYS.USER.VIEW；用戶須屬於目前公司，否則 404；只列出操作者獲授權公司的指派（公司代碼／名稱、分店、部門、預設、啟用、角色 ID），依公司代碼排序（ADR-017）。</x:t>
+          <x:t xml:space="preserve">同一權限取各啟用角色最寬的資料範圍；全權角色視為全部權限、全公司範圍；分店／部門範圍但用戶無對應歸屬時退回本人。GET /api/v1/sys/auth/authorization 回傳可存取公司（預設在前）與目前公司權限；前端 *erpHasPermission、permissionGuard 與選單依此隱藏，切換公司重新載入；本機記住的公司不可存取時改用預設公司。</x:t>
         </x:is>
       </x:c>
       <x:c r="H74" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:96</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:95</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="75">
       <x:c r="A75" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.26.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.25.8</x:t>
         </x:is>
       </x:c>
       <x:c r="B75" s="2" t="inlineStr">
@@ -3192,7 +3192,7 @@
       </x:c>
       <x:c r="C75" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Web Security Middleware</x:t>
+          <x:t xml:space="preserve">Role, Permission and Data Scope</x:t>
         </x:is>
       </x:c>
       <x:c r="D75" s="2" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </x:c>
       <x:c r="E75" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enforce HTTPS with HSTS outside the development environment.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to view a user's company access, organization and roles.</x:t>
         </x:is>
       </x:c>
       <x:c r="F75" s="2" t="inlineStr">
@@ -3212,19 +3212,19 @@
       </x:c>
       <x:c r="G75" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">非 Development：HTTP 請求 307 轉 HTTPS；HTTPS 回應帶 Strict-Transport-Security: max-age=31536000; includeSubDomains（天數可設定）。Development 不轉址、不送 HSTS。</x:t>
+          <x:t xml:space="preserve">需 SYS.USER.VIEW；用戶須屬於目前公司，否則 404；只列出操作者獲授權公司的指派（公司代碼／名稱、分店、部門、預設、啟用、角色 ID），依公司代碼排序（ADR-017）。</x:t>
         </x:is>
       </x:c>
       <x:c r="H75" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:110</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:96</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="76">
       <x:c r="A76" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.26.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.26.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B76" s="2" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </x:c>
       <x:c r="E76" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow cross-origin requests only from configured frontend origins.</x:t>
+          <x:t xml:space="preserve">System should enforce HTTPS with HSTS outside the development environment.</x:t>
         </x:is>
       </x:c>
       <x:c r="F76" s="2" t="inlineStr">
@@ -3254,19 +3254,19 @@
       </x:c>
       <x:c r="G76" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">來源清單在 Security:Cors:AllowedOrigins，預設空（不允許跨來源）；只接受 scheme://host[:port]，萬用字元、含路徑或非 http(s) 拒絕啟動；不允許 Credentials；允許標頭 Authorization、Content-Type、Accept、Accept-Language、X-Company-Id；公開 Retry-After、Content-Disposition；未列明的來源預檢回應不含 Access-Control-Allow-Origin。</x:t>
+          <x:t xml:space="preserve">非 Development：HTTP 請求 307 轉 HTTPS；HTTPS 回應帶 Strict-Transport-Security: max-age=31536000; includeSubDomains（天數可設定）。Development 不轉址、不送 HSTS。</x:t>
         </x:is>
       </x:c>
       <x:c r="H76" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:111</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:110</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="77">
       <x:c r="A77" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.26.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.26.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B77" s="2" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </x:c>
       <x:c r="E77" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should rate-limit login, token refresh and captcha requests per client IP.</x:t>
+          <x:t xml:space="preserve">System should allow cross-origin requests only from configured frontend origins.</x:t>
         </x:is>
       </x:c>
       <x:c r="F77" s="2" t="inlineStr">
@@ -3296,19 +3296,19 @@
       </x:c>
       <x:c r="G77" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">登入、Token 刷新每 IP 每端點每分鐘 5 次；Captcha 每 IP 每分鐘 10 次（ADR-018）；超過回 429 ProblemDetails，errorCode 為 COMMON.REQUEST.RATE_LIMITED，標題依 Accept-Language 三語，帶 Retry-After；寫 Warning 日誌（方法、路徑、IP）。CORS 預檢不計入。每個匿名端點必須套用按 IP 的限流政策（ArchitectureTests 檢查）。</x:t>
+          <x:t xml:space="preserve">來源清單在 Security:Cors:AllowedOrigins，預設空（不允許跨來源）；只接受 scheme://host[:port]，萬用字元、含路徑或非 http(s) 拒絕啟動；不允許 Credentials；允許標頭 Authorization、Content-Type、Accept、Accept-Language、X-Company-Id；公開 Retry-After、Content-Disposition；未列明的來源預檢回應不含 Access-Control-Allow-Origin。</x:t>
         </x:is>
       </x:c>
       <x:c r="H77" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:112</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:111</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="78">
       <x:c r="A78" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.26.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.26.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B78" s="2" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </x:c>
       <x:c r="E78" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should rate-limit authenticated API requests per user.</x:t>
+          <x:t xml:space="preserve">System should rate-limit login, token refresh and captcha requests per client IP.</x:t>
         </x:is>
       </x:c>
       <x:c r="F78" s="2" t="inlineStr">
@@ -3338,19 +3338,19 @@
       </x:c>
       <x:c r="G78" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">已登入請求每用戶每分鐘 300 次（可設定），不同用戶分開計數；匯出報表政策每用戶每分鐘 10 次，供日後匯出端點套用。白名單內的 IP 仍受限流。</x:t>
+          <x:t xml:space="preserve">登入、Token 刷新每 IP 每端點每分鐘 5 次；Captcha 每 IP 每分鐘 10 次（ADR-018）；超過回 429 ProblemDetails，errorCode 為 COMMON.REQUEST.RATE_LIMITED，標題依 Accept-Language 三語，帶 Retry-After；寫 Warning 日誌（方法、路徑、IP）。CORS 預檢不計入。每個匿名端點必須套用按 IP 的限流政策（ArchitectureTests 檢查）。</x:t>
         </x:is>
       </x:c>
       <x:c r="H78" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:113</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:112</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="79">
       <x:c r="A79" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.26.5</x:t>
+          <x:t xml:space="preserve">REQ_F4118.26.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B79" s="2" t="inlineStr">
@@ -3370,7 +3370,7 @@
       </x:c>
       <x:c r="E79" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should add security headers to every API response.</x:t>
+          <x:t xml:space="preserve">System should rate-limit authenticated API requests per user.</x:t>
         </x:is>
       </x:c>
       <x:c r="F79" s="2" t="inlineStr">
@@ -3380,19 +3380,19 @@
       </x:c>
       <x:c r="G79" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">所有回應（含 404、429、500）帶 X-Content-Type-Options: nosniff、X-Frame-Options: DENY、Referrer-Policy: no-referrer、Content-Security-Policy: default-src 'none'; frame-ancestors 'none'; base-uri 'none'; form-action 'none'。前端站台的 CSP 見 architecture/security.md，E2E 在該 CSP 下執行。</x:t>
+          <x:t xml:space="preserve">已登入請求每用戶每分鐘 300 次（可設定），不同用戶分開計數；匯出報表政策每用戶每分鐘 10 次，供日後匯出端點套用。白名單內的 IP 仍受限流。</x:t>
         </x:is>
       </x:c>
       <x:c r="H79" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:114</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:113</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="80">
       <x:c r="A80" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.26.6</x:t>
+          <x:t xml:space="preserve">REQ_F4118.26.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B80" s="2" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </x:c>
       <x:c r="E80" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should honour X-Forwarded-For only from configured proxies.</x:t>
+          <x:t xml:space="preserve">System should add security headers to every API response.</x:t>
         </x:is>
       </x:c>
       <x:c r="F80" s="2" t="inlineStr">
@@ -3422,19 +3422,19 @@
       </x:c>
       <x:c r="G80" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Security:ForwardedHeaders:KnownProxies（IP）與 KnownNetworks（CIDR）皆空時不處理 X-Forwarded-*；有設定時只信任列明來源，其他來源偽造的 X-Forwarded-For 被忽略，限流與日誌使用連線 IP；格式錯誤拒絕啟動。</x:t>
+          <x:t xml:space="preserve">所有回應（含 404、429、500）帶 X-Content-Type-Options: nosniff、X-Frame-Options: DENY、Referrer-Policy: no-referrer、Content-Security-Policy: default-src 'none'; frame-ancestors 'none'; base-uri 'none'; form-action 'none'。前端站台的 CSP 見 architecture/security.md，E2E 在該 CSP 下執行。</x:t>
         </x:is>
       </x:c>
       <x:c r="H80" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:115</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:114</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="81">
       <x:c r="A81" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.26.7</x:t>
+          <x:t xml:space="preserve">REQ_F4118.26.6</x:t>
         </x:is>
       </x:c>
       <x:c r="B81" s="2" t="inlineStr">
@@ -3454,7 +3454,7 @@
       </x:c>
       <x:c r="E81" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should show a trilingual "too many requests" message when an API call is rate-limited.</x:t>
+          <x:t xml:space="preserve">System should honour X-Forwarded-For only from configured proxies.</x:t>
         </x:is>
       </x:c>
       <x:c r="F81" s="2" t="inlineStr">
@@ -3464,19 +3464,19 @@
       </x:c>
       <x:c r="G81" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">前端收到 429 一律顯示 errors.COMMON.REQUEST.RATE_LIMITED（三語），登入頁、組織、用戶、角色頁共用 apiErrorKey。</x:t>
+          <x:t xml:space="preserve">Security:ForwardedHeaders:KnownProxies（IP）與 KnownNetworks（CIDR）皆空時不處理 X-Forwarded-*；有設定時只信任列明來源，其他來源偽造的 X-Forwarded-For 被忽略，限流與日誌使用連線 IP；格式錯誤拒絕啟動。</x:t>
         </x:is>
       </x:c>
       <x:c r="H81" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:116</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:115</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="82">
       <x:c r="A82" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.27.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.26.7</x:t>
         </x:is>
       </x:c>
       <x:c r="B82" s="2" t="inlineStr">
@@ -3486,7 +3486,7 @@
       </x:c>
       <x:c r="C82" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Audit Log</x:t>
+          <x:t xml:space="preserve">Web Security Middleware</x:t>
         </x:is>
       </x:c>
       <x:c r="D82" s="2" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </x:c>
       <x:c r="E82" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should record every data change in sys_audit_log within the same transaction.</x:t>
+          <x:t xml:space="preserve">System should show a trilingual "too many requests" message when an API call is rate-limited.</x:t>
         </x:is>
       </x:c>
       <x:c r="F82" s="2" t="inlineStr">
@@ -3506,19 +3506,19 @@
       </x:c>
       <x:c r="G82" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">透過 EF 新增、修改、刪除（含軟刪除）都寫一筆記錄，內容包括公司、用戶（背景程序為系統用戶）、時間（IClock）、表名、記錄 Id、操作類型（CREATE／UPDATE／DELETE，可由 Application 指定 VOID／APPROVE／POST）、欄位差異 JSON（修改只列有變更的欄位）、來源 IP、TraceId。沒有欄位變更不寫記錄。交易回滾或 SaveChanges 失敗（含樂觀鎖衝突）不留記錄，重試時也不會重複（ADR-019）。</x:t>
+          <x:t xml:space="preserve">前端收到 429 一律顯示 errors.COMMON.REQUEST.RATE_LIMITED（三語），登入頁、組織、用戶、角色頁共用 apiErrorKey。</x:t>
         </x:is>
       </x:c>
       <x:c r="H82" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:128</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:116</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="83">
       <x:c r="A83" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.27.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.27.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B83" s="2" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </x:c>
       <x:c r="E83" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should protect audit records and sensitive values.</x:t>
+          <x:t xml:space="preserve">System should record every data change in sys_audit_log within the same transaction.</x:t>
         </x:is>
       </x:c>
       <x:c r="F83" s="2" t="inlineStr">
@@ -3548,19 +3548,19 @@
       </x:c>
       <x:c r="G83" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">[SensitiveData] 欄位（例如 password_hash）的值以 * 遮蔽；主鍵、審計欄位、version、company_id 不記錄差異。sys_audit_log 只能新增，UPDATE 或 DELETE 由 trigger 拒絕（append-only）；changes 必須是 JSON。</x:t>
+          <x:t xml:space="preserve">透過 EF 新增、修改、刪除（含軟刪除）都寫一筆記錄，內容包括公司、用戶（背景程序為系統用戶）、時間（IClock）、表名、記錄 Id、操作類型（CREATE／UPDATE／DELETE，可由 Application 指定 VOID／APPROVE／POST）、欄位差異 JSON（修改只列有變更的欄位）、來源 IP、TraceId。沒有欄位變更不寫記錄。交易回滾或 SaveChanges 失敗（含樂觀鎖衝突）不留記錄，重試時也不會重複（ADR-019）。</x:t>
         </x:is>
       </x:c>
       <x:c r="H83" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:129</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:128</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="84">
       <x:c r="A84" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.27.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.27.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B84" s="2" t="inlineStr">
@@ -3580,7 +3580,7 @@
       </x:c>
       <x:c r="E84" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should record login, failed login, logout and captcha master-code login as security events.</x:t>
+          <x:t xml:space="preserve">System should protect audit records and sensitive values.</x:t>
         </x:is>
       </x:c>
       <x:c r="F84" s="2" t="inlineStr">
@@ -3590,19 +3590,19 @@
       </x:c>
       <x:c r="G84" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">安全事件記錄帳號、IP、時間與 TraceId。LOGIN_FAILED 的原因只寫 INVALID_CREDENTIALS 或 PASSWORD_EXPIRED，不寫密碼。萬用碼登入不論結果都寫 MASTER_CODE_LOGIN（REQ_F4118.24.4）。</x:t>
+          <x:t xml:space="preserve">[SensitiveData] 欄位（例如 password_hash）的值以 * 遮蔽；主鍵、審計欄位、version、company_id 不記錄差異。sys_audit_log 只能新增，UPDATE 或 DELETE 由 trigger 拒絕（append-only）；changes 必須是 JSON。</x:t>
         </x:is>
       </x:c>
       <x:c r="H84" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:130</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:129</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="85">
       <x:c r="A85" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.27.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.27.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B85" s="2" t="inlineStr">
@@ -3622,7 +3622,7 @@
       </x:c>
       <x:c r="E85" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to query audit logs of the current company.</x:t>
+          <x:t xml:space="preserve">System should record login, failed login, logout and captcha master-code login as security events.</x:t>
         </x:is>
       </x:c>
       <x:c r="F85" s="2" t="inlineStr">
@@ -3632,19 +3632,19 @@
       </x:c>
       <x:c r="G85" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GET /api/v1/sys/audit-logs 需 SYS.AUDIT.VIEW，支援分頁、日期範圍（含頭尾）、類別、操作類型、表名＋記錄 Id（單據修改歷史）、用戶篩選，以時間排序。只列出目前公司的記錄，以及屬於目前公司用戶、沒有公司的安全事件；其他公司的記錄看不到。資料變更記錄會補上帳號。to 早於 from、類別未知或長度超限時回 400。</x:t>
+          <x:t xml:space="preserve">安全事件記錄帳號、IP、時間與 TraceId。LOGIN_FAILED 的原因只寫 INVALID_CREDENTIALS 或 PASSWORD_EXPIRED，不寫密碼。萬用碼登入不論結果都寫 MASTER_CODE_LOGIN（REQ_F4118.24.4）。</x:t>
         </x:is>
       </x:c>
       <x:c r="H85" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:131</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:130</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="86">
       <x:c r="A86" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.27.5</x:t>
+          <x:t xml:space="preserve">REQ_F4118.27.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B86" s="2" t="inlineStr">
@@ -3664,7 +3664,7 @@
       </x:c>
       <x:c r="E86" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should record role permission and user company access changes as security events.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to query audit logs of the current company.</x:t>
         </x:is>
       </x:c>
       <x:c r="F86" s="2" t="inlineStr">
@@ -3674,19 +3674,19 @@
       </x:c>
       <x:c r="G86" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">修改角色的權限、資料範圍、全權或啟用狀態，以及指派用戶公司授權，都寫 PERMISSION_CHANGE，與變更同一交易。記錄內容包括操作者、公司、新增與移除的權限，或指派後的角色、組織、預設公司與啟用狀態。</x:t>
+          <x:t xml:space="preserve">GET /api/v1/sys/audit-logs 需 SYS.AUDIT.VIEW，支援分頁、日期範圍（含頭尾）、類別、操作類型、表名＋記錄 Id（單據修改歷史）、用戶篩選，以時間排序。只列出目前公司的記錄，以及屬於目前公司用戶、沒有公司的安全事件；其他公司的記錄看不到。資料變更記錄會補上帳號。to 早於 from、類別未知或長度超限時回 400。</x:t>
         </x:is>
       </x:c>
       <x:c r="H86" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:132</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:131</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="87">
       <x:c r="A87" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.27.6</x:t>
+          <x:t xml:space="preserve">REQ_F4118.27.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B87" s="2" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </x:c>
       <x:c r="E87" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should provide a trilingual audit log page with per-record change history.</x:t>
+          <x:t xml:space="preserve">System should record role permission and user company access changes as security events.</x:t>
         </x:is>
       </x:c>
       <x:c r="F87" s="2" t="inlineStr">
@@ -3716,19 +3716,19 @@
       </x:c>
       <x:c r="G87" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">三語稽核查詢頁 /sys/audit-logs（介面 8.66），需 SYS.AUDIT.VIEW，無權限時選單不顯示、直接進入顯示 403。可依日期範圍（含快選今天、近 7、30 天；結束日早於開始日時不送出）、類別、操作、資料表＋記錄 ID 篩選，伺服器端分頁並依時間排序。可展開欄位差異（修改前→修改後，* 照原樣顯示）或安全事件明細。?tableName=&amp;recordId= 開啟單筆記錄的修改歷史，供單據頁的稽核頁籤連結。操作與類別有三語標籤，未知操作顯示原代碼。切換公司後重新查詢。</x:t>
+          <x:t xml:space="preserve">修改角色的權限、資料範圍、全權或啟用狀態，以及指派用戶公司授權，都寫 PERMISSION_CHANGE，與變更同一交易。記錄內容包括操作者、公司、新增與移除的權限，或指派後的角色、組織、預設公司與啟用狀態。</x:t>
         </x:is>
       </x:c>
       <x:c r="H87" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:133</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:132</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="88">
       <x:c r="A88" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.28.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.27.6</x:t>
         </x:is>
       </x:c>
       <x:c r="B88" s="2" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </x:c>
       <x:c r="C88" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Document Number Rule</x:t>
+          <x:t xml:space="preserve">Audit Log</x:t>
         </x:is>
       </x:c>
       <x:c r="D88" s="2" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </x:c>
       <x:c r="E88" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow user to view document number rules of the current company.</x:t>
+          <x:t xml:space="preserve">System should provide a trilingual audit log page with per-record change history.</x:t>
         </x:is>
       </x:c>
       <x:c r="F88" s="2" t="inlineStr">
@@ -3758,19 +3758,19 @@
       </x:c>
       <x:c r="G88" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">三語稽核查詢頁 /sys/audit-logs（介面 8.66），需 SYS.AUDIT.VIEW，無權限時選單不顯示、直接進入顯示 403。可依日期範圍（含快選今天、近 7、30 天；結束日早於開始日時不送出）、類別、操作、資料表＋記錄 ID 篩選，伺服器端分頁並依時間排序。可展開欄位差異（修改前→修改後，* 照原樣顯示）或安全事件明細。?tableName=&amp;recordId= 開啟單筆記錄的修改歷史，供單據頁的稽核頁籤連結。操作與類別有三語標籤，未知操作顯示原代碼。切換公司後重新查詢。</x:t>
         </x:is>
       </x:c>
       <x:c r="H88" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:167</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:133</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="89">
       <x:c r="A89" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.28.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.28.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B89" s="2" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </x:c>
       <x:c r="E89" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow user to create a document number rule with prefix, date format, sequence length and reset period.</x:t>
+          <x:t xml:space="preserve">System should allow user to view document number rules of the current company.</x:t>
         </x:is>
       </x:c>
       <x:c r="F89" s="2" t="inlineStr">
@@ -3805,14 +3805,14 @@
       </x:c>
       <x:c r="H89" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:168</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:167</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="90">
       <x:c r="A90" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.28.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.28.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B90" s="2" t="inlineStr">
@@ -3832,7 +3832,7 @@
       </x:c>
       <x:c r="E90" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow user to edit or deactivate a document number rule without breaking issued numbers.</x:t>
+          <x:t xml:space="preserve">System should allow user to create a document number rule with prefix, date format, sequence length and reset period.</x:t>
         </x:is>
       </x:c>
       <x:c r="F90" s="2" t="inlineStr">
@@ -3847,14 +3847,14 @@
       </x:c>
       <x:c r="H90" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:169</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:168</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="91">
       <x:c r="A91" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.28.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.28.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B91" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </x:c>
       <x:c r="E91" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow user to preview the next document number for a business date.</x:t>
+          <x:t xml:space="preserve">System should allow user to edit or deactivate a document number rule without breaking issued numbers.</x:t>
         </x:is>
       </x:c>
       <x:c r="F91" s="2" t="inlineStr">
@@ -3889,14 +3889,14 @@
       </x:c>
       <x:c r="H91" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:170</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:169</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="92">
       <x:c r="A92" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.28.5</x:t>
+          <x:t xml:space="preserve">REQ_F4118.28.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B92" s="2" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </x:c>
       <x:c r="E92" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should generate unique, gap-free document numbers for every module under concurrency.</x:t>
+          <x:t xml:space="preserve">System should allow user to preview the next document number for a business date.</x:t>
         </x:is>
       </x:c>
       <x:c r="F92" s="2" t="inlineStr">
@@ -3931,14 +3931,14 @@
       </x:c>
       <x:c r="H92" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:171</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:170</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="93">
       <x:c r="A93" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.28.6</x:t>
+          <x:t xml:space="preserve">REQ_F4118.28.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B93" s="2" t="inlineStr">
@@ -3958,7 +3958,7 @@
       </x:c>
       <x:c r="E93" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should provide a trilingual number rule maintenance page.</x:t>
+          <x:t xml:space="preserve">System should generate unique, gap-free document numbers for every module under concurrency.</x:t>
         </x:is>
       </x:c>
       <x:c r="F93" s="2" t="inlineStr">
@@ -3973,14 +3973,14 @@
       </x:c>
       <x:c r="H93" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:172</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:171</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="94">
       <x:c r="A94" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.29.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.28.6</x:t>
         </x:is>
       </x:c>
       <x:c r="B94" s="2" t="inlineStr">
@@ -3990,7 +3990,7 @@
       </x:c>
       <x:c r="C94" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Approval Workflow</x:t>
+          <x:t xml:space="preserve">Document Number Rule</x:t>
         </x:is>
       </x:c>
       <x:c r="D94" s="2" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </x:c>
       <x:c r="E94" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow user to view and create multi-level approval flows with amount thresholds.</x:t>
+          <x:t xml:space="preserve">System should provide a trilingual number rule maintenance page.</x:t>
         </x:is>
       </x:c>
       <x:c r="F94" s="2" t="inlineStr">
@@ -4015,14 +4015,14 @@
       </x:c>
       <x:c r="H94" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:146</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:172</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="95">
       <x:c r="A95" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.29.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.29.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B95" s="2" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </x:c>
       <x:c r="E95" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow user to edit or deactivate an approval flow without affecting pending approvals.</x:t>
+          <x:t xml:space="preserve">System should allow user to view and create multi-level approval flows with amount thresholds.</x:t>
         </x:is>
       </x:c>
       <x:c r="F95" s="2" t="inlineStr">
@@ -4057,14 +4057,14 @@
       </x:c>
       <x:c r="H95" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:147</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:146</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="96">
       <x:c r="A96" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.29.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.29.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B96" s="2" t="inlineStr">
@@ -4084,7 +4084,7 @@
       </x:c>
       <x:c r="E96" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow user to assign an approval delegate for a date range.</x:t>
+          <x:t xml:space="preserve">System should allow user to edit or deactivate an approval flow without affecting pending approvals.</x:t>
         </x:is>
       </x:c>
       <x:c r="F96" s="2" t="inlineStr">
@@ -4099,14 +4099,14 @@
       </x:c>
       <x:c r="H96" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:148</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:147</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="97">
       <x:c r="A97" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.29.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.29.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B97" s="2" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </x:c>
       <x:c r="E97" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable every module to submit documents for approval through the shared workflow engine.</x:t>
+          <x:t xml:space="preserve">System should allow user to assign an approval delegate for a date range.</x:t>
         </x:is>
       </x:c>
       <x:c r="F97" s="2" t="inlineStr">
@@ -4141,14 +4141,14 @@
       </x:c>
       <x:c r="H97" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:149</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:148</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="98">
       <x:c r="A98" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.29.5</x:t>
+          <x:t xml:space="preserve">REQ_F4118.29.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B98" s="2" t="inlineStr">
@@ -4168,7 +4168,7 @@
       </x:c>
       <x:c r="E98" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow approvers or their delegates to approve or reject the current approval step.</x:t>
+          <x:t xml:space="preserve">System should enable every module to submit documents for approval through the shared workflow engine.</x:t>
         </x:is>
       </x:c>
       <x:c r="F98" s="2" t="inlineStr">
@@ -4183,14 +4183,14 @@
       </x:c>
       <x:c r="H98" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:150</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:149</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="99">
       <x:c r="A99" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.29.6</x:t>
+          <x:t xml:space="preserve">REQ_F4118.29.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B99" s="2" t="inlineStr">
@@ -4210,7 +4210,7 @@
       </x:c>
       <x:c r="E99" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should list the pending approval tasks of the current user.</x:t>
+          <x:t xml:space="preserve">System should allow approvers or their delegates to approve or reject the current approval step.</x:t>
         </x:is>
       </x:c>
       <x:c r="F99" s="2" t="inlineStr">
@@ -4225,14 +4225,14 @@
       </x:c>
       <x:c r="H99" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:151</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:150</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="100">
       <x:c r="A100" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.29.7</x:t>
+          <x:t xml:space="preserve">REQ_F4118.29.6</x:t>
         </x:is>
       </x:c>
       <x:c r="B100" s="2" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </x:c>
       <x:c r="E100" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow user to view the approval history of a document.</x:t>
+          <x:t xml:space="preserve">System should list the pending approval tasks of the current user.</x:t>
         </x:is>
       </x:c>
       <x:c r="F100" s="2" t="inlineStr">
@@ -4267,14 +4267,14 @@
       </x:c>
       <x:c r="H100" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:152</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:151</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="101">
       <x:c r="A101" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.29.8</x:t>
+          <x:t xml:space="preserve">REQ_F4118.29.7</x:t>
         </x:is>
       </x:c>
       <x:c r="B101" s="2" t="inlineStr">
@@ -4294,7 +4294,7 @@
       </x:c>
       <x:c r="E101" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should provide trilingual approval flow and delegation maintenance pages.</x:t>
+          <x:t xml:space="preserve">System should allow user to view the approval history of a document.</x:t>
         </x:is>
       </x:c>
       <x:c r="F101" s="2" t="inlineStr">
@@ -4309,14 +4309,14 @@
       </x:c>
       <x:c r="H101" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:153</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:152</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="102">
       <x:c r="A102" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.29.9</x:t>
+          <x:t xml:space="preserve">REQ_F4118.29.8</x:t>
         </x:is>
       </x:c>
       <x:c r="B102" s="2" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </x:c>
       <x:c r="E102" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should provide a trilingual approval inbox with approval history.</x:t>
+          <x:t xml:space="preserve">System should provide trilingual approval flow and delegation maintenance pages.</x:t>
         </x:is>
       </x:c>
       <x:c r="F102" s="2" t="inlineStr">
@@ -4351,14 +4351,14 @@
       </x:c>
       <x:c r="H102" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:154</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:153</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="103">
       <x:c r="A103" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.30.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.29.9</x:t>
         </x:is>
       </x:c>
       <x:c r="B103" s="2" t="inlineStr">
@@ -4368,7 +4368,7 @@
       </x:c>
       <x:c r="C103" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Development Seed Data</x:t>
+          <x:t xml:space="preserve">Approval Workflow</x:t>
         </x:is>
       </x:c>
       <x:c r="D103" s="2" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </x:c>
       <x:c r="E103" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should load demo companies, branches, departments and roles for the Development environment.</x:t>
+          <x:t xml:space="preserve">System should provide a trilingual approval inbox with approval history.</x:t>
         </x:is>
       </x:c>
       <x:c r="F103" s="2" t="inlineStr">
@@ -4393,14 +4393,14 @@
       </x:c>
       <x:c r="H103" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:186</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:154</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="104">
       <x:c r="A104" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.30.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.30.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B104" s="2" t="inlineStr">
@@ -4420,7 +4420,7 @@
       </x:c>
       <x:c r="E104" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should create the test accounts of the SeedUsers setting with hashed passwords and company assignments.</x:t>
+          <x:t xml:space="preserve">System should load demo companies, branches, departments and roles for the Development environment.</x:t>
         </x:is>
       </x:c>
       <x:c r="F104" s="2" t="inlineStr">
@@ -4435,14 +4435,14 @@
       </x:c>
       <x:c r="H104" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:187</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:186</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="105">
       <x:c r="A105" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.30.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.30.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B105" s="2" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </x:c>
       <x:c r="E105" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow the seed to run repeatedly without duplicating or overwriting data.</x:t>
+          <x:t xml:space="preserve">System should create the test accounts of the SeedUsers setting with hashed passwords and company assignments.</x:t>
         </x:is>
       </x:c>
       <x:c r="F105" s="2" t="inlineStr">
@@ -4477,14 +4477,14 @@
       </x:c>
       <x:c r="H105" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:188</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:187</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="106">
       <x:c r="A106" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.31.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.30.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B106" s="2" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </x:c>
       <x:c r="C106" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Shared Dialogs and Page Templates</x:t>
+          <x:t xml:space="preserve">Development Seed Data</x:t>
         </x:is>
       </x:c>
       <x:c r="D106" s="2" t="inlineStr">
@@ -4504,7 +4504,7 @@
       </x:c>
       <x:c r="E106" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should ask for confirmation in a shared trilingual confirmation box before dangerous actions.</x:t>
+          <x:t xml:space="preserve">System should allow the seed to run repeatedly without duplicating or overwriting data.</x:t>
         </x:is>
       </x:c>
       <x:c r="F106" s="2" t="inlineStr">
@@ -4519,14 +4519,14 @@
       </x:c>
       <x:c r="H106" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:200</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:188</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="107">
       <x:c r="A107" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.31.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.31.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B107" s="2" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </x:c>
       <x:c r="E107" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should show results that need the user's attention in a shared prompt box, and short success messages as toasts.</x:t>
+          <x:t xml:space="preserve">System should ask for confirmation in a shared trilingual confirmation box before dangerous actions.</x:t>
         </x:is>
       </x:c>
       <x:c r="F107" s="2" t="inlineStr">
@@ -4561,14 +4561,14 @@
       </x:c>
       <x:c r="H107" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:201</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:200</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="108">
       <x:c r="A108" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.31.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.31.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B108" s="2" t="inlineStr">
@@ -4588,7 +4588,7 @@
       </x:c>
       <x:c r="E108" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should provide a shared selection window for choosing master data with search and server-side paging.</x:t>
+          <x:t xml:space="preserve">System should show results that need the user's attention in a shared prompt box, and short success messages as toasts.</x:t>
         </x:is>
       </x:c>
       <x:c r="F108" s="2" t="inlineStr">
@@ -4603,14 +4603,14 @@
       </x:c>
       <x:c r="H108" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:202</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:201</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="109">
       <x:c r="A109" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.31.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.31.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B109" s="2" t="inlineStr">
@@ -4630,7 +4630,7 @@
       </x:c>
       <x:c r="E109" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should provide a standard list page template reused by every module.</x:t>
+          <x:t xml:space="preserve">System should provide a shared selection window for choosing master data with search and server-side paging.</x:t>
         </x:is>
       </x:c>
       <x:c r="F109" s="2" t="inlineStr">
@@ -4645,14 +4645,14 @@
       </x:c>
       <x:c r="H109" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:203</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:202</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="110">
       <x:c r="A110" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.31.5</x:t>
+          <x:t xml:space="preserve">REQ_F4118.31.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B110" s="2" t="inlineStr">
@@ -4672,7 +4672,7 @@
       </x:c>
       <x:c r="E110" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should provide a standard document page template with status, previous / next navigation and unsaved-change protection.</x:t>
+          <x:t xml:space="preserve">System should provide a standard list page template reused by every module.</x:t>
         </x:is>
       </x:c>
       <x:c r="F110" s="2" t="inlineStr">
@@ -4687,14 +4687,14 @@
       </x:c>
       <x:c r="H110" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:204</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:203</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="111">
       <x:c r="A111" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.31.6</x:t>
+          <x:t xml:space="preserve">REQ_F4118.31.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B111" s="2" t="inlineStr">
@@ -4714,7 +4714,7 @@
       </x:c>
       <x:c r="E111" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should provide a date range filter with quick ranges and a document status tag following the macaron status colours.</x:t>
+          <x:t xml:space="preserve">System should provide a standard document page template with status, previous / next navigation and unsaved-change protection.</x:t>
         </x:is>
       </x:c>
       <x:c r="F111" s="2" t="inlineStr">
@@ -4729,14 +4729,14 @@
       </x:c>
       <x:c r="H111" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:205</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:204</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="112">
       <x:c r="A112" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.32.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.31.6</x:t>
         </x:is>
       </x:c>
       <x:c r="B112" s="2" t="inlineStr">
@@ -4746,7 +4746,7 @@
       </x:c>
       <x:c r="C112" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">IP Whitelist</x:t>
+          <x:t xml:space="preserve">Shared Dialogs and Page Templates</x:t>
         </x:is>
       </x:c>
       <x:c r="D112" s="2" t="inlineStr">
@@ -4756,7 +4756,7 @@
       </x:c>
       <x:c r="E112" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to view IP whitelist rules.</x:t>
+          <x:t xml:space="preserve">System should provide a date range filter with quick ranges and a document status tag following the macaron status colours.</x:t>
         </x:is>
       </x:c>
       <x:c r="F112" s="2" t="inlineStr">
@@ -4771,14 +4771,14 @@
       </x:c>
       <x:c r="H112" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:217</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:205</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="113">
       <x:c r="A113" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.32.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.32.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B113" s="2" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </x:c>
       <x:c r="E113" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to create and deactivate IP whitelist rules.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to view IP whitelist rules.</x:t>
         </x:is>
       </x:c>
       <x:c r="F113" s="2" t="inlineStr">
@@ -4813,14 +4813,14 @@
       </x:c>
       <x:c r="H113" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:218</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:217</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="114">
       <x:c r="A114" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.32.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.32.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B114" s="2" t="inlineStr">
@@ -4840,7 +4840,7 @@
       </x:c>
       <x:c r="E114" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow single IPv4 or IPv6 addresses and CIDR networks in system, role or user scope.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to create and deactivate IP whitelist rules.</x:t>
         </x:is>
       </x:c>
       <x:c r="F114" s="2" t="inlineStr">
@@ -4855,14 +4855,14 @@
       </x:c>
       <x:c r="H114" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:219</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:218</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="115">
       <x:c r="A115" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.32.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.32.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B115" s="2" t="inlineStr">
@@ -4882,7 +4882,7 @@
       </x:c>
       <x:c r="E115" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should reject disallowed requests and audit each rejection.</x:t>
+          <x:t xml:space="preserve">System should allow single IPv4 or IPv6 addresses and CIDR networks in system, role or user scope.</x:t>
         </x:is>
       </x:c>
       <x:c r="F115" s="2" t="inlineStr">
@@ -4897,14 +4897,14 @@
       </x:c>
       <x:c r="H115" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:220</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:219</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="116">
       <x:c r="A116" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.32.5</x:t>
+          <x:t xml:space="preserve">REQ_F4118.32.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B116" s="2" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </x:c>
       <x:c r="E116" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow operators to disable IP filtering through server configuration.</x:t>
+          <x:t xml:space="preserve">System should reject disallowed requests and audit each rejection.</x:t>
         </x:is>
       </x:c>
       <x:c r="F116" s="2" t="inlineStr">
@@ -4939,14 +4939,14 @@
       </x:c>
       <x:c r="H116" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:221</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:220</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="117">
       <x:c r="A117" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.32.6</x:t>
+          <x:t xml:space="preserve">REQ_F4118.32.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B117" s="2" t="inlineStr">
@@ -4966,7 +4966,7 @@
       </x:c>
       <x:c r="E117" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should provide a trilingual IP whitelist maintenance page.</x:t>
+          <x:t xml:space="preserve">System should allow operators to disable IP filtering through server configuration.</x:t>
         </x:is>
       </x:c>
       <x:c r="F117" s="2" t="inlineStr">
@@ -4981,14 +4981,14 @@
       </x:c>
       <x:c r="H117" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:222</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:221</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="118">
       <x:c r="A118" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.33.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.32.6</x:t>
         </x:is>
       </x:c>
       <x:c r="B118" s="2" t="inlineStr">
@@ -4998,17 +4998,17 @@
       </x:c>
       <x:c r="C118" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">In-app Notification</x:t>
+          <x:t xml:space="preserve">IP Whitelist</x:t>
         </x:is>
       </x:c>
       <x:c r="D118" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">1.1</x:t>
+          <x:t xml:space="preserve">1.0</x:t>
         </x:is>
       </x:c>
       <x:c r="E118" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable modules to publish notifications to a user.</x:t>
+          <x:t xml:space="preserve">System should provide a trilingual IP whitelist maintenance page.</x:t>
         </x:is>
       </x:c>
       <x:c r="F118" s="2" t="inlineStr">
@@ -5023,14 +5023,14 @@
       </x:c>
       <x:c r="H118" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:278</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:222</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="119">
       <x:c r="A119" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.33.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.33.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B119" s="2" t="inlineStr">
@@ -5050,7 +5050,7 @@
       </x:c>
       <x:c r="E119" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to view notifications.</x:t>
+          <x:t xml:space="preserve">System should enable modules to publish notifications to a user.</x:t>
         </x:is>
       </x:c>
       <x:c r="F119" s="2" t="inlineStr">
@@ -5065,14 +5065,14 @@
       </x:c>
       <x:c r="H119" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:279</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:278</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="120">
       <x:c r="A120" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.33.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.33.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B120" s="2" t="inlineStr">
@@ -5092,7 +5092,7 @@
       </x:c>
       <x:c r="E120" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to mark notifications as read.</x:t>
+          <x:t xml:space="preserve">System should enable user to view notifications.</x:t>
         </x:is>
       </x:c>
       <x:c r="F120" s="2" t="inlineStr">
@@ -5107,47 +5107,89 @@
       </x:c>
       <x:c r="H120" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:280</x:t>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:279</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="121">
       <x:c r="A121" s="2" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">REQ_F4118.33.3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B121" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C121" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">In-app Notification</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D121" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E121" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should enable user to mark notifications as read.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F121" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G121" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve"/>
+        </x:is>
+      </x:c>
+      <x:c r="H121" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/SYS/requirements.md:280</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="122">
+      <x:c r="A122" s="2" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">REQ_F4118.34.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="B121" s="2" t="inlineStr">
+      <x:c r="B122" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Settings</x:t>
         </x:is>
       </x:c>
-      <x:c r="C121" s="2" t="inlineStr">
+      <x:c r="C122" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Master Data Portal</x:t>
         </x:is>
       </x:c>
-      <x:c r="D121" s="2" t="inlineStr">
+      <x:c r="D122" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1.0</x:t>
         </x:is>
       </x:c>
-      <x:c r="E121" s="2" t="inlineStr">
+      <x:c r="E122" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">System should allow authorized users to view the master data portal.</x:t>
         </x:is>
       </x:c>
-      <x:c r="F121" s="2" t="inlineStr">
+      <x:c r="F122" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Developer</x:t>
         </x:is>
       </x:c>
-      <x:c r="G121" s="2" t="inlineStr">
+      <x:c r="G122" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">/md 僅向已登入且在目前公司有 MD.MASTER.VIEW 的用戶開放；無權限導向 403；三語標題與說明一致。</x:t>
         </x:is>
       </x:c>
-      <x:c r="H121" s="2" t="inlineStr">
+      <x:c r="H122" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:11</x:t>
         </x:is>
@@ -7056,7 +7098,39 @@
       </x:c>
       <x:c r="F30" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.12.1, REQ_F4118.12.2, REQ_F4118.12.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.3.1, REQ_F4118.3.2, REQ_F4118.3.3, REQ_F4118.3.5</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.114</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B31" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C31" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">md_item_uom_conversion</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D31" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">This table stores item-specific conversion factors from alternate units to the item base unit within a company.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E31" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F31" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.3.5</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -7071,7 +7145,7 @@
     <x:col min="2" max="2" width="15" customWidth="1"/>
     <x:col min="3" max="3" width="60" customWidth="1"/>
     <x:col min="4" max="4" width="42" customWidth="1"/>
-    <x:col min="5" max="5" width="39" customWidth="1"/>
+    <x:col min="5" max="5" width="60" customWidth="1"/>
     <x:col min="6" max="6" width="23" customWidth="1"/>
     <x:col min="7" max="7" width="60" customWidth="1"/>
     <x:col min="8" max="8" width="60" customWidth="1"/>
@@ -8642,7 +8716,7 @@
       </x:c>
       <x:c r="E28" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">代碼、名稱、規格、單位、品牌、分類、狀態；代碼與名稱可排序，伺服器分頁。</x:t>
+          <x:t xml:space="preserve">代碼、名稱、規格、單位、品牌、分類、狀態；代碼與名稱可排序，伺服器分頁；每列有「換算」開啟介面 8.77。</x:t>
         </x:is>
       </x:c>
       <x:c r="F28" s="2" t="inlineStr">
@@ -8662,7 +8736,7 @@
       </x:c>
       <x:c r="I28" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.12.1, REQ_IO_A8.13.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.12.1, REQ_IO_A8.13.1, REQ_IO_A8.77.1</x:t>
         </x:is>
       </x:c>
       <x:c r="J28" s="2" t="inlineStr">
@@ -9098,7 +9172,7 @@
       </x:c>
       <x:c r="E36" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">編輯名稱、規格、單位、品牌、分類；原參照已停用仍可保留。</x:t>
+          <x:t xml:space="preserve">編輯名稱、規格、單位、品牌、分類；原參照已停用仍可保留；有專屬換算時改基本單位顯示 BASE_UOM_LOCKED。</x:t>
         </x:is>
       </x:c>
       <x:c r="F36" s="2" t="inlineStr">
@@ -17506,6 +17580,291 @@
         </x:is>
       </x:c>
       <x:c r="K183" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="184">
+      <x:c r="A184" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.77.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B184" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.77</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C184" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Item Unit Conversion Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D184" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Conversion List (Table)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E184" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">單位、換算規則（1 單位 = 係數 基本單位）、編輯／刪除操作。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F184" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">查看物料專屬換算。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G184" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Table</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H184" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">該物料全部換算</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I184" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.11.2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J184" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K184" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="185">
+      <x:c r="A185" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.77.2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B185" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.77</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C185" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Item Unit Conversion Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D185" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Unit (Dropdown)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E185" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">換算單位；排除基本單位，停用單位不可新選，編輯時唯讀。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F185" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">選擇包裝等單位。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G185" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Unit ID</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H185" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">本公司啟用單位</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I185" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.77.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J185" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K185" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="186">
+      <x:c r="A186" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.77.3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B186" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.77</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C186" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Item Unit Conversion Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D186" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Factor (Input)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E186" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1 單位 = 係數 基本單位。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F186" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">設定物料換算係數。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G186" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Decimal</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H186" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">大於 0，最多 9 位整數及 6 位小數</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I186" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.77.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J186" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K186" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="187">
+      <x:c r="A187" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.77.4</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B187" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.77</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C187" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Item Unit Conversion Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D187" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Delete (Button)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E187" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">確認後帶版本刪除換算。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F187" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">移除換算，以便修改基本單位。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G187" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Action</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H187" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">MD.ITEM.EDIT</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I187" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.77.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J187" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K187" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="188">
+      <x:c r="A188" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.77.5</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B188" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.77</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C188" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Item Unit Conversion Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D188" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Calculator (Form)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E188" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">數量、來源與目標單位、換算按鈕及結果。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F188" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">按物料試算數量。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G188" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Decimal</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H188" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">數量最多 12 位整數及 6 位小數</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I188" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.77.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J188" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K188" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Developer</x:t>
         </x:is>
@@ -17900,32 +18259,32 @@
     <x:row r="11">
       <x:c r="A11" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.8.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.3.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B11" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to view records of client categories.</x:t>
+          <x:t xml:space="preserve">System should enable user to view product.</x:t>
         </x:is>
       </x:c>
       <x:c r="C11" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.105</x:t>
+          <x:t xml:space="preserve">REQ_DS43.113</x:t>
         </x:is>
       </x:c>
       <x:c r="D11" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.30</x:t>
+          <x:t xml:space="preserve">4.4.1.8.11</x:t>
         </x:is>
       </x:c>
       <x:c r="E11" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.30.1, REQ_IO_A8.30.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.11.1, REQ_IO_A8.11.2</x:t>
         </x:is>
       </x:c>
       <x:c r="F11" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MD-CAT-001, MD-CAT-002, MD-CAT-003, MD-CAT-004, MD-CAT-005</x:t>
+          <x:t xml:space="preserve">MD-ITEM-001, MD-ITEM-UI-001</x:t>
         </x:is>
       </x:c>
       <x:c r="G11" s="2" t="inlineStr">
@@ -17937,32 +18296,32 @@
     <x:row r="12">
       <x:c r="A12" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.8.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.3.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B12" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to create records of client categories.</x:t>
+          <x:t xml:space="preserve">System should enable user to create product.</x:t>
         </x:is>
       </x:c>
       <x:c r="C12" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.105</x:t>
+          <x:t xml:space="preserve">REQ_DS43.113</x:t>
         </x:is>
       </x:c>
       <x:c r="D12" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.31</x:t>
+          <x:t xml:space="preserve">4.4.1.8.12</x:t>
         </x:is>
       </x:c>
       <x:c r="E12" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.31.1, REQ_IO_A8.31.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.12.1, REQ_IO_A8.12.2, REQ_IO_A8.12.3, REQ_IO_A8.12.4, REQ_IO_A8.12.5, REQ_IO_A8.12.6</x:t>
         </x:is>
       </x:c>
       <x:c r="F12" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MD-CAT-001, MD-CAT-002, MD-CAT-003, MD-CAT-004</x:t>
+          <x:t xml:space="preserve">MD-ITEM-001, MD-ITEM-002, MD-ITEM-UI-001</x:t>
         </x:is>
       </x:c>
       <x:c r="G12" s="2" t="inlineStr">
@@ -17974,32 +18333,32 @@
     <x:row r="13">
       <x:c r="A13" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.8.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.3.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B13" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to edit records of client categories.</x:t>
+          <x:t xml:space="preserve">System should enable user to edit product.</x:t>
         </x:is>
       </x:c>
       <x:c r="C13" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.105</x:t>
+          <x:t xml:space="preserve">REQ_DS43.113</x:t>
         </x:is>
       </x:c>
       <x:c r="D13" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.32</x:t>
+          <x:t xml:space="preserve">4.4.1.8.13</x:t>
         </x:is>
       </x:c>
       <x:c r="E13" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.32.1, REQ_IO_A8.32.2, REQ_IO_A8.32.3</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.13.1, REQ_IO_A8.13.2, REQ_IO_A8.13.3</x:t>
         </x:is>
       </x:c>
       <x:c r="F13" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MD-CAT-001, MD-CAT-003, MD-CAT-004, MD-CAT-005</x:t>
+          <x:t xml:space="preserve">MD-ITEM-001, MD-ITEM-002, MD-ITEM-UI-001, MD-ITEM-CONV-002, MD-ITEM-CONV-UI-001</x:t>
         </x:is>
       </x:c>
       <x:c r="G13" s="2" t="inlineStr">
@@ -18011,32 +18370,32 @@
     <x:row r="14">
       <x:c r="A14" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.8.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.3.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B14" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to delete records of client categories.</x:t>
+          <x:t xml:space="preserve">System should enable user to maintain item-specific unit conversions.</x:t>
         </x:is>
       </x:c>
       <x:c r="C14" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.105</x:t>
+          <x:t xml:space="preserve">REQ_DS43.113, REQ_DS43.114</x:t>
         </x:is>
       </x:c>
       <x:c r="D14" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.30</x:t>
+          <x:t xml:space="preserve">4.4.1.8.77</x:t>
         </x:is>
       </x:c>
       <x:c r="E14" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.30.3</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.77.1, REQ_IO_A8.77.2, REQ_IO_A8.77.3, REQ_IO_A8.77.4, REQ_IO_A8.77.5</x:t>
         </x:is>
       </x:c>
       <x:c r="F14" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MD-CAT-001, MD-CAT-003, MD-CAT-004</x:t>
+          <x:t xml:space="preserve">MD-ITEM-CONV-001, MD-ITEM-CONV-002, MD-ITEM-CONV-003, MD-ITEM-CONV-UI-001, MD-ITEM-CONV-UI-002</x:t>
         </x:is>
       </x:c>
       <x:c r="G14" s="2" t="inlineStr">
@@ -18048,32 +18407,32 @@
     <x:row r="15">
       <x:c r="A15" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.9.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.8.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B15" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to view records of supplier categories.</x:t>
+          <x:t xml:space="preserve">System should enable user to view records of client categories.</x:t>
         </x:is>
       </x:c>
       <x:c r="C15" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.107</x:t>
+          <x:t xml:space="preserve">REQ_DS43.105</x:t>
         </x:is>
       </x:c>
       <x:c r="D15" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.33</x:t>
+          <x:t xml:space="preserve">4.4.1.8.30</x:t>
         </x:is>
       </x:c>
       <x:c r="E15" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.33.1, REQ_IO_A8.33.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.30.1, REQ_IO_A8.30.2</x:t>
         </x:is>
       </x:c>
       <x:c r="F15" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MD-SCAT-001, MD-SCAT-002, MD-SCAT-003, MD-SCAT-004</x:t>
+          <x:t xml:space="preserve">MD-CAT-001, MD-CAT-002, MD-CAT-003, MD-CAT-004, MD-CAT-005</x:t>
         </x:is>
       </x:c>
       <x:c r="G15" s="2" t="inlineStr">
@@ -18085,32 +18444,32 @@
     <x:row r="16">
       <x:c r="A16" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.9.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.8.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B16" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to create records of supplier categories.</x:t>
+          <x:t xml:space="preserve">System should enable user to create records of client categories.</x:t>
         </x:is>
       </x:c>
       <x:c r="C16" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.107</x:t>
+          <x:t xml:space="preserve">REQ_DS43.105</x:t>
         </x:is>
       </x:c>
       <x:c r="D16" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.34</x:t>
+          <x:t xml:space="preserve">4.4.1.8.31</x:t>
         </x:is>
       </x:c>
       <x:c r="E16" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.34.1, REQ_IO_A8.34.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.31.1, REQ_IO_A8.31.2</x:t>
         </x:is>
       </x:c>
       <x:c r="F16" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MD-SCAT-001, MD-SCAT-002, MD-SCAT-003, MD-SCAT-004</x:t>
+          <x:t xml:space="preserve">MD-CAT-001, MD-CAT-002, MD-CAT-003, MD-CAT-004</x:t>
         </x:is>
       </x:c>
       <x:c r="G16" s="2" t="inlineStr">
@@ -18122,32 +18481,32 @@
     <x:row r="17">
       <x:c r="A17" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.9.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.8.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B17" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to edit records of supplier categories.</x:t>
+          <x:t xml:space="preserve">System should enable user to edit records of client categories.</x:t>
         </x:is>
       </x:c>
       <x:c r="C17" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.107</x:t>
+          <x:t xml:space="preserve">REQ_DS43.105</x:t>
         </x:is>
       </x:c>
       <x:c r="D17" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.35</x:t>
+          <x:t xml:space="preserve">4.4.1.8.32</x:t>
         </x:is>
       </x:c>
       <x:c r="E17" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.35.1, REQ_IO_A8.35.2, REQ_IO_A8.35.3</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.32.1, REQ_IO_A8.32.2, REQ_IO_A8.32.3</x:t>
         </x:is>
       </x:c>
       <x:c r="F17" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MD-SCAT-001, MD-SCAT-002, MD-SCAT-003, MD-SCAT-004</x:t>
+          <x:t xml:space="preserve">MD-CAT-001, MD-CAT-003, MD-CAT-004, MD-CAT-005</x:t>
         </x:is>
       </x:c>
       <x:c r="G17" s="2" t="inlineStr">
@@ -18159,32 +18518,32 @@
     <x:row r="18">
       <x:c r="A18" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.9.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.8.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B18" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to delete records of supplier categories.</x:t>
+          <x:t xml:space="preserve">System should enable user to delete records of client categories.</x:t>
         </x:is>
       </x:c>
       <x:c r="C18" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.107</x:t>
+          <x:t xml:space="preserve">REQ_DS43.105</x:t>
         </x:is>
       </x:c>
       <x:c r="D18" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.33</x:t>
+          <x:t xml:space="preserve">4.4.1.8.30</x:t>
         </x:is>
       </x:c>
       <x:c r="E18" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.33.3</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.30.3</x:t>
         </x:is>
       </x:c>
       <x:c r="F18" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MD-SCAT-001, MD-SCAT-003, MD-SCAT-004</x:t>
+          <x:t xml:space="preserve">MD-CAT-001, MD-CAT-003, MD-CAT-004</x:t>
         </x:is>
       </x:c>
       <x:c r="G18" s="2" t="inlineStr">
@@ -18196,32 +18555,32 @@
     <x:row r="19">
       <x:c r="A19" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.10.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.9.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B19" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to view item category.</x:t>
+          <x:t xml:space="preserve">System should enable user to view records of supplier categories.</x:t>
         </x:is>
       </x:c>
       <x:c r="C19" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.112</x:t>
+          <x:t xml:space="preserve">REQ_DS43.107</x:t>
         </x:is>
       </x:c>
       <x:c r="D19" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.36</x:t>
+          <x:t xml:space="preserve">4.4.1.8.33</x:t>
         </x:is>
       </x:c>
       <x:c r="E19" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.36.1, REQ_IO_A8.36.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.33.1, REQ_IO_A8.33.2</x:t>
         </x:is>
       </x:c>
       <x:c r="F19" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MD-ICAT-001, MD-ICAT-004, MD-ICAT-005, MD-ICAT-006</x:t>
+          <x:t xml:space="preserve">MD-SCAT-001, MD-SCAT-002, MD-SCAT-003, MD-SCAT-004</x:t>
         </x:is>
       </x:c>
       <x:c r="G19" s="2" t="inlineStr">
@@ -18233,32 +18592,32 @@
     <x:row r="20">
       <x:c r="A20" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.10.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.9.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B20" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to create item category.</x:t>
+          <x:t xml:space="preserve">System should enable user to create records of supplier categories.</x:t>
         </x:is>
       </x:c>
       <x:c r="C20" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.112</x:t>
+          <x:t xml:space="preserve">REQ_DS43.107</x:t>
         </x:is>
       </x:c>
       <x:c r="D20" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.37</x:t>
+          <x:t xml:space="preserve">4.4.1.8.34</x:t>
         </x:is>
       </x:c>
       <x:c r="E20" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.37.1, REQ_IO_A8.37.2, REQ_IO_A8.37.3</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.34.1, REQ_IO_A8.34.2</x:t>
         </x:is>
       </x:c>
       <x:c r="F20" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MD-ICAT-001, MD-ICAT-002, MD-ICAT-004, MD-ICAT-005, MD-ICAT-006</x:t>
+          <x:t xml:space="preserve">MD-SCAT-001, MD-SCAT-002, MD-SCAT-003, MD-SCAT-004</x:t>
         </x:is>
       </x:c>
       <x:c r="G20" s="2" t="inlineStr">
@@ -18270,32 +18629,32 @@
     <x:row r="21">
       <x:c r="A21" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.10.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.9.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B21" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to edit item category.</x:t>
+          <x:t xml:space="preserve">System should enable user to edit records of supplier categories.</x:t>
         </x:is>
       </x:c>
       <x:c r="C21" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.112</x:t>
+          <x:t xml:space="preserve">REQ_DS43.107</x:t>
         </x:is>
       </x:c>
       <x:c r="D21" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.38</x:t>
+          <x:t xml:space="preserve">4.4.1.8.35</x:t>
         </x:is>
       </x:c>
       <x:c r="E21" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.38.1, REQ_IO_A8.38.2, REQ_IO_A8.38.3</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.35.1, REQ_IO_A8.35.2, REQ_IO_A8.35.3</x:t>
         </x:is>
       </x:c>
       <x:c r="F21" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MD-ICAT-001, MD-ICAT-002, MD-ICAT-004, MD-ICAT-005, MD-ICAT-006</x:t>
+          <x:t xml:space="preserve">MD-SCAT-001, MD-SCAT-002, MD-SCAT-003, MD-SCAT-004</x:t>
         </x:is>
       </x:c>
       <x:c r="G21" s="2" t="inlineStr">
@@ -18307,32 +18666,32 @@
     <x:row r="22">
       <x:c r="A22" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.10.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.9.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B22" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to delete item category.</x:t>
+          <x:t xml:space="preserve">System should enable user to delete records of supplier categories.</x:t>
         </x:is>
       </x:c>
       <x:c r="C22" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.112</x:t>
+          <x:t xml:space="preserve">REQ_DS43.107</x:t>
         </x:is>
       </x:c>
       <x:c r="D22" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.36</x:t>
+          <x:t xml:space="preserve">4.4.1.8.33</x:t>
         </x:is>
       </x:c>
       <x:c r="E22" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.36.3</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.33.3</x:t>
         </x:is>
       </x:c>
       <x:c r="F22" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MD-ICAT-003, MD-ICAT-004, MD-ICAT-005, MD-ICAT-006</x:t>
+          <x:t xml:space="preserve">MD-SCAT-001, MD-SCAT-003, MD-SCAT-004</x:t>
         </x:is>
       </x:c>
       <x:c r="G22" s="2" t="inlineStr">
@@ -18344,32 +18703,32 @@
     <x:row r="23">
       <x:c r="A23" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.11.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.10.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B23" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to view item brand.</x:t>
+          <x:t xml:space="preserve">System should enable user to view item category.</x:t>
         </x:is>
       </x:c>
       <x:c r="C23" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.111</x:t>
+          <x:t xml:space="preserve">REQ_DS43.112</x:t>
         </x:is>
       </x:c>
       <x:c r="D23" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.39</x:t>
+          <x:t xml:space="preserve">4.4.1.8.36</x:t>
         </x:is>
       </x:c>
       <x:c r="E23" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.39.1, REQ_IO_A8.39.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.36.1, REQ_IO_A8.36.2</x:t>
         </x:is>
       </x:c>
       <x:c r="F23" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MD-BRD-001, MD-BRD-002, MD-BRD-003</x:t>
+          <x:t xml:space="preserve">MD-ICAT-001, MD-ICAT-004, MD-ICAT-005, MD-ICAT-006</x:t>
         </x:is>
       </x:c>
       <x:c r="G23" s="2" t="inlineStr">
@@ -18381,32 +18740,32 @@
     <x:row r="24">
       <x:c r="A24" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.11.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.10.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B24" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to create item brand.</x:t>
+          <x:t xml:space="preserve">System should enable user to create item category.</x:t>
         </x:is>
       </x:c>
       <x:c r="C24" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.111</x:t>
+          <x:t xml:space="preserve">REQ_DS43.112</x:t>
         </x:is>
       </x:c>
       <x:c r="D24" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.40</x:t>
+          <x:t xml:space="preserve">4.4.1.8.37</x:t>
         </x:is>
       </x:c>
       <x:c r="E24" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.40.1, REQ_IO_A8.40.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.37.1, REQ_IO_A8.37.2, REQ_IO_A8.37.3</x:t>
         </x:is>
       </x:c>
       <x:c r="F24" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MD-BRD-001, MD-BRD-002, MD-BRD-003</x:t>
+          <x:t xml:space="preserve">MD-ICAT-001, MD-ICAT-002, MD-ICAT-004, MD-ICAT-005, MD-ICAT-006</x:t>
         </x:is>
       </x:c>
       <x:c r="G24" s="2" t="inlineStr">
@@ -18418,32 +18777,32 @@
     <x:row r="25">
       <x:c r="A25" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.11.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.10.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B25" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to edit item brand.</x:t>
+          <x:t xml:space="preserve">System should enable user to edit item category.</x:t>
         </x:is>
       </x:c>
       <x:c r="C25" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.111</x:t>
+          <x:t xml:space="preserve">REQ_DS43.112</x:t>
         </x:is>
       </x:c>
       <x:c r="D25" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.41</x:t>
+          <x:t xml:space="preserve">4.4.1.8.38</x:t>
         </x:is>
       </x:c>
       <x:c r="E25" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.41.1, REQ_IO_A8.41.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.38.1, REQ_IO_A8.38.2, REQ_IO_A8.38.3</x:t>
         </x:is>
       </x:c>
       <x:c r="F25" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MD-BRD-001, MD-BRD-002, MD-BRD-003</x:t>
+          <x:t xml:space="preserve">MD-ICAT-001, MD-ICAT-002, MD-ICAT-004, MD-ICAT-005, MD-ICAT-006</x:t>
         </x:is>
       </x:c>
       <x:c r="G25" s="2" t="inlineStr">
@@ -18455,32 +18814,32 @@
     <x:row r="26">
       <x:c r="A26" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.11.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.10.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B26" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to delete item brand.</x:t>
+          <x:t xml:space="preserve">System should enable user to delete item category.</x:t>
         </x:is>
       </x:c>
       <x:c r="C26" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.111</x:t>
+          <x:t xml:space="preserve">REQ_DS43.112</x:t>
         </x:is>
       </x:c>
       <x:c r="D26" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.39</x:t>
+          <x:t xml:space="preserve">4.4.1.8.36</x:t>
         </x:is>
       </x:c>
       <x:c r="E26" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.39.3</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.36.3</x:t>
         </x:is>
       </x:c>
       <x:c r="F26" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MD-BRD-001, MD-BRD-002, MD-BRD-003</x:t>
+          <x:t xml:space="preserve">MD-ICAT-003, MD-ICAT-004, MD-ICAT-005, MD-ICAT-006</x:t>
         </x:is>
       </x:c>
       <x:c r="G26" s="2" t="inlineStr">
@@ -18492,32 +18851,32 @@
     <x:row r="27">
       <x:c r="A27" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.12.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.11.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B27" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to view items.</x:t>
+          <x:t xml:space="preserve">System should enable user to view item brand.</x:t>
         </x:is>
       </x:c>
       <x:c r="C27" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.113</x:t>
+          <x:t xml:space="preserve">REQ_DS43.111</x:t>
         </x:is>
       </x:c>
       <x:c r="D27" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.11</x:t>
+          <x:t xml:space="preserve">4.4.1.8.39</x:t>
         </x:is>
       </x:c>
       <x:c r="E27" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.11.1, REQ_IO_A8.11.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.39.1, REQ_IO_A8.39.2</x:t>
         </x:is>
       </x:c>
       <x:c r="F27" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MD-ITEM-001, MD-ITEM-UI-001</x:t>
+          <x:t xml:space="preserve">MD-BRD-001, MD-BRD-002, MD-BRD-003</x:t>
         </x:is>
       </x:c>
       <x:c r="G27" s="2" t="inlineStr">
@@ -18529,32 +18888,32 @@
     <x:row r="28">
       <x:c r="A28" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.12.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.11.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B28" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to create items.</x:t>
+          <x:t xml:space="preserve">System should enable user to create item brand.</x:t>
         </x:is>
       </x:c>
       <x:c r="C28" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.113</x:t>
+          <x:t xml:space="preserve">REQ_DS43.111</x:t>
         </x:is>
       </x:c>
       <x:c r="D28" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.12</x:t>
+          <x:t xml:space="preserve">4.4.1.8.40</x:t>
         </x:is>
       </x:c>
       <x:c r="E28" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.12.1, REQ_IO_A8.12.2, REQ_IO_A8.12.3, REQ_IO_A8.12.4, REQ_IO_A8.12.5, REQ_IO_A8.12.6</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.40.1, REQ_IO_A8.40.2</x:t>
         </x:is>
       </x:c>
       <x:c r="F28" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MD-ITEM-001, MD-ITEM-002, MD-ITEM-UI-001</x:t>
+          <x:t xml:space="preserve">MD-BRD-001, MD-BRD-002, MD-BRD-003</x:t>
         </x:is>
       </x:c>
       <x:c r="G28" s="2" t="inlineStr">
@@ -18566,32 +18925,32 @@
     <x:row r="29">
       <x:c r="A29" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.12.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.11.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B29" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to edit items.</x:t>
+          <x:t xml:space="preserve">System should enable user to edit item brand.</x:t>
         </x:is>
       </x:c>
       <x:c r="C29" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.113</x:t>
+          <x:t xml:space="preserve">REQ_DS43.111</x:t>
         </x:is>
       </x:c>
       <x:c r="D29" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.13</x:t>
+          <x:t xml:space="preserve">4.4.1.8.41</x:t>
         </x:is>
       </x:c>
       <x:c r="E29" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.13.1, REQ_IO_A8.13.2, REQ_IO_A8.13.3</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.41.1, REQ_IO_A8.41.2</x:t>
         </x:is>
       </x:c>
       <x:c r="F29" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MD-ITEM-001, MD-ITEM-002, MD-ITEM-UI-001</x:t>
+          <x:t xml:space="preserve">MD-BRD-001, MD-BRD-002, MD-BRD-003</x:t>
         </x:is>
       </x:c>
       <x:c r="G29" s="2" t="inlineStr">
@@ -18603,32 +18962,32 @@
     <x:row r="30">
       <x:c r="A30" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.13.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.11.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B30" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to view unit of measurement.</x:t>
+          <x:t xml:space="preserve">System should enable user to delete item brand.</x:t>
         </x:is>
       </x:c>
       <x:c r="C30" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.109, REQ_DS43.110</x:t>
+          <x:t xml:space="preserve">REQ_DS43.111</x:t>
         </x:is>
       </x:c>
       <x:c r="D30" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.45</x:t>
+          <x:t xml:space="preserve">4.4.1.8.39</x:t>
         </x:is>
       </x:c>
       <x:c r="E30" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.45.1, REQ_IO_A8.45.2, REQ_IO_A8.45.3, REQ_IO_A8.45.4</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.39.3</x:t>
         </x:is>
       </x:c>
       <x:c r="F30" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MD-UOM-001, MD-UOM-002, MD-UOM-003, MD-UOM-004, MD-UOM-005</x:t>
+          <x:t xml:space="preserve">MD-BRD-001, MD-BRD-002, MD-BRD-003</x:t>
         </x:is>
       </x:c>
       <x:c r="G30" s="2" t="inlineStr">
@@ -18640,12 +18999,12 @@
     <x:row r="31">
       <x:c r="A31" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.13.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.13.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B31" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to create unit of measurement.</x:t>
+          <x:t xml:space="preserve">System should enable user to view unit of measurement.</x:t>
         </x:is>
       </x:c>
       <x:c r="C31" s="2" t="inlineStr">
@@ -18655,12 +19014,12 @@
       </x:c>
       <x:c r="D31" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.46</x:t>
+          <x:t xml:space="preserve">4.4.1.8.45</x:t>
         </x:is>
       </x:c>
       <x:c r="E31" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.46.1, REQ_IO_A8.46.2, REQ_IO_A8.46.3, REQ_IO_A8.46.4, REQ_IO_A8.46.5</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.45.1, REQ_IO_A8.45.2, REQ_IO_A8.45.3, REQ_IO_A8.45.4</x:t>
         </x:is>
       </x:c>
       <x:c r="F31" s="2" t="inlineStr">
@@ -18677,12 +19036,12 @@
     <x:row r="32">
       <x:c r="A32" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.13.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.13.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B32" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to edit unit of measurement.</x:t>
+          <x:t xml:space="preserve">System should enable user to create unit of measurement.</x:t>
         </x:is>
       </x:c>
       <x:c r="C32" s="2" t="inlineStr">
@@ -18692,17 +19051,17 @@
       </x:c>
       <x:c r="D32" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.47</x:t>
+          <x:t xml:space="preserve">4.4.1.8.46</x:t>
         </x:is>
       </x:c>
       <x:c r="E32" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.47.1, REQ_IO_A8.47.2, REQ_IO_A8.47.3</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.46.1, REQ_IO_A8.46.2, REQ_IO_A8.46.3, REQ_IO_A8.46.4, REQ_IO_A8.46.5</x:t>
         </x:is>
       </x:c>
       <x:c r="F32" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">MD-UOM-001, MD-UOM-003, MD-UOM-004, MD-UOM-005</x:t>
+          <x:t xml:space="preserve">MD-UOM-001, MD-UOM-002, MD-UOM-003, MD-UOM-004, MD-UOM-005</x:t>
         </x:is>
       </x:c>
       <x:c r="G32" s="2" t="inlineStr">
@@ -18714,12 +19073,12 @@
     <x:row r="33">
       <x:c r="A33" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.13.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.13.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B33" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to delete unit of measurement.</x:t>
+          <x:t xml:space="preserve">System should enable user to edit unit of measurement.</x:t>
         </x:is>
       </x:c>
       <x:c r="C33" s="2" t="inlineStr">
@@ -18734,7 +19093,7 @@
       </x:c>
       <x:c r="E33" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.47.4</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.47.1, REQ_IO_A8.47.2, REQ_IO_A8.47.3</x:t>
         </x:is>
       </x:c>
       <x:c r="F33" s="2" t="inlineStr">
@@ -18751,32 +19110,32 @@
     <x:row r="34">
       <x:c r="A34" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.17.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.13.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B34" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to view parameter settings.</x:t>
+          <x:t xml:space="preserve">System should enable user to delete unit of measurement.</x:t>
         </x:is>
       </x:c>
       <x:c r="C34" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.73</x:t>
+          <x:t xml:space="preserve">REQ_DS43.109, REQ_DS43.110</x:t>
         </x:is>
       </x:c>
       <x:c r="D34" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.55</x:t>
+          <x:t xml:space="preserve">4.4.1.8.47</x:t>
         </x:is>
       </x:c>
       <x:c r="E34" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.47.4</x:t>
         </x:is>
       </x:c>
       <x:c r="F34" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-PARAM-002</x:t>
+          <x:t xml:space="preserve">MD-UOM-001, MD-UOM-003, MD-UOM-004, MD-UOM-005</x:t>
         </x:is>
       </x:c>
       <x:c r="G34" s="2" t="inlineStr">
@@ -18788,12 +19147,12 @@
     <x:row r="35">
       <x:c r="A35" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.17.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.17.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B35" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to edit parameter settings.</x:t>
+          <x:t xml:space="preserve">System should enable user to view parameter settings.</x:t>
         </x:is>
       </x:c>
       <x:c r="C35" s="2" t="inlineStr">
@@ -18808,12 +19167,12 @@
       </x:c>
       <x:c r="E35" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.55.1, REQ_IO_A8.55.2, REQ_IO_A8.55.3, REQ_IO_A8.55.4, REQ_IO_A8.55.5, REQ_IO_A8.55.7</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="F35" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-PARAM-002, SYS-PARAM-003</x:t>
+          <x:t xml:space="preserve">SYS-PARAM-002</x:t>
         </x:is>
       </x:c>
       <x:c r="G35" s="2" t="inlineStr">
@@ -18825,12 +19184,12 @@
     <x:row r="36">
       <x:c r="A36" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.17.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.17.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B36" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should let every module declare typed company parameters with defaults and read them in process.</x:t>
+          <x:t xml:space="preserve">System should enable user to edit parameter settings.</x:t>
         </x:is>
       </x:c>
       <x:c r="C36" s="2" t="inlineStr">
@@ -18840,34 +19199,34 @@
       </x:c>
       <x:c r="D36" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">4.4.1.8.55</x:t>
         </x:is>
       </x:c>
       <x:c r="E36" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.55.1, REQ_IO_A8.55.2, REQ_IO_A8.55.3, REQ_IO_A8.55.4, REQ_IO_A8.55.5, REQ_IO_A8.55.7</x:t>
         </x:is>
       </x:c>
       <x:c r="F36" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-PARAM-001, SYS-PARAM-004</x:t>
+          <x:t xml:space="preserve">SYS-PARAM-002, SYS-PARAM-003</x:t>
         </x:is>
       </x:c>
       <x:c r="G36" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.17.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.17.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B37" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should provide a parameter edit interface grouped by module.</x:t>
+          <x:t xml:space="preserve">System should let every module declare typed company parameters with defaults and read them in process.</x:t>
         </x:is>
       </x:c>
       <x:c r="C37" s="2" t="inlineStr">
@@ -18877,34 +19236,34 @@
       </x:c>
       <x:c r="D37" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.55</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="E37" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.55.1, REQ_IO_A8.55.2, REQ_IO_A8.55.3, REQ_IO_A8.55.4, REQ_IO_A8.55.5, REQ_IO_A8.55.6, REQ_IO_A8.55.7</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="F37" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-PARAM-005, SYS-PARAM-006, SYS-PARAM-007</x:t>
+          <x:t xml:space="preserve">SYS-PARAM-001, SYS-PARAM-004</x:t>
         </x:is>
       </x:c>
       <x:c r="G37" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Covered</x:t>
+          <x:t xml:space="preserve">Partial</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.18.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.17.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B38" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to view print settings.</x:t>
+          <x:t xml:space="preserve">System should provide a parameter edit interface grouped by module.</x:t>
         </x:is>
       </x:c>
       <x:c r="C38" s="2" t="inlineStr">
@@ -18914,17 +19273,17 @@
       </x:c>
       <x:c r="D38" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.56</x:t>
+          <x:t xml:space="preserve">4.4.1.8.55</x:t>
         </x:is>
       </x:c>
       <x:c r="E38" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.56.1, REQ_IO_A8.56.2, REQ_IO_A8.56.3, REQ_IO_A8.56.4, REQ_IO_A8.56.5, REQ_IO_A8.56.6, REQ_IO_A8.56.7, REQ_IO_A8.56.8, REQ_IO_A8.56.9, REQ_IO_A8.56.10</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.55.1, REQ_IO_A8.55.2, REQ_IO_A8.55.3, REQ_IO_A8.55.4, REQ_IO_A8.55.5, REQ_IO_A8.55.6, REQ_IO_A8.55.7</x:t>
         </x:is>
       </x:c>
       <x:c r="F38" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-PRINT-004, SYS-PRINT-005</x:t>
+          <x:t xml:space="preserve">SYS-PARAM-005, SYS-PARAM-006, SYS-PARAM-007</x:t>
         </x:is>
       </x:c>
       <x:c r="G38" s="2" t="inlineStr">
@@ -18936,12 +19295,12 @@
     <x:row r="39">
       <x:c r="A39" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.18.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.18.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B39" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to edit print settings.</x:t>
+          <x:t xml:space="preserve">System should enable user to view print settings.</x:t>
         </x:is>
       </x:c>
       <x:c r="C39" s="2" t="inlineStr">
@@ -18956,12 +19315,12 @@
       </x:c>
       <x:c r="E39" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.56.1, REQ_IO_A8.56.2, REQ_IO_A8.56.3, REQ_IO_A8.56.4, REQ_IO_A8.56.5, REQ_IO_A8.56.6, REQ_IO_A8.56.7, REQ_IO_A8.56.8, REQ_IO_A8.56.9, REQ_IO_A8.56.11</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.56.1, REQ_IO_A8.56.2, REQ_IO_A8.56.3, REQ_IO_A8.56.4, REQ_IO_A8.56.5, REQ_IO_A8.56.6, REQ_IO_A8.56.7, REQ_IO_A8.56.8, REQ_IO_A8.56.9, REQ_IO_A8.56.10</x:t>
         </x:is>
       </x:c>
       <x:c r="F39" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-PRINT-001, SYS-PRINT-002, SYS-PRINT-004, SYS-PRINT-005</x:t>
+          <x:t xml:space="preserve">SYS-PRINT-004, SYS-PRINT-005</x:t>
         </x:is>
       </x:c>
       <x:c r="G39" s="2" t="inlineStr">
@@ -18973,12 +19332,12 @@
     <x:row r="40">
       <x:c r="A40" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.18.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.18.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B40" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should let printing modules read the company's print settings.</x:t>
+          <x:t xml:space="preserve">System should enable user to edit print settings.</x:t>
         </x:is>
       </x:c>
       <x:c r="C40" s="2" t="inlineStr">
@@ -18988,71 +19347,71 @@
       </x:c>
       <x:c r="D40" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">4.4.1.8.56</x:t>
         </x:is>
       </x:c>
       <x:c r="E40" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.56.1, REQ_IO_A8.56.2, REQ_IO_A8.56.3, REQ_IO_A8.56.4, REQ_IO_A8.56.5, REQ_IO_A8.56.6, REQ_IO_A8.56.7, REQ_IO_A8.56.8, REQ_IO_A8.56.9, REQ_IO_A8.56.11</x:t>
         </x:is>
       </x:c>
       <x:c r="F40" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-PRINT-003</x:t>
+          <x:t xml:space="preserve">SYS-PRINT-001, SYS-PRINT-002, SYS-PRINT-004, SYS-PRINT-005</x:t>
         </x:is>
       </x:c>
       <x:c r="G40" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.19.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.18.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B41" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to view the logo and stamp.</x:t>
+          <x:t xml:space="preserve">System should let printing modules read the company's print settings.</x:t>
         </x:is>
       </x:c>
       <x:c r="C41" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.103</x:t>
+          <x:t xml:space="preserve">REQ_DS43.73</x:t>
         </x:is>
       </x:c>
       <x:c r="D41" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.57</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="E41" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.57.1, REQ_IO_A8.57.2, REQ_IO_A8.57.3</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="F41" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-IMG-003, SYS-IMG-005, SYS-IMG-007, SYS-IMG-008</x:t>
+          <x:t xml:space="preserve">SYS-PRINT-003</x:t>
         </x:is>
       </x:c>
       <x:c r="G41" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Covered</x:t>
+          <x:t xml:space="preserve">Partial</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.19.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.19.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B42" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to edit the logo and stamp.</x:t>
+          <x:t xml:space="preserve">System should enable user to view the logo and stamp.</x:t>
         </x:is>
       </x:c>
       <x:c r="C42" s="2" t="inlineStr">
@@ -19067,12 +19426,12 @@
       </x:c>
       <x:c r="E42" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.57.4, REQ_IO_A8.57.5</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.57.1, REQ_IO_A8.57.2, REQ_IO_A8.57.3</x:t>
         </x:is>
       </x:c>
       <x:c r="F42" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-IMG-001, SYS-IMG-002, SYS-IMG-003, SYS-IMG-004, SYS-IMG-005, SYS-IMG-007, SYS-IMG-008</x:t>
+          <x:t xml:space="preserve">SYS-IMG-003, SYS-IMG-005, SYS-IMG-007, SYS-IMG-008</x:t>
         </x:is>
       </x:c>
       <x:c r="G42" s="2" t="inlineStr">
@@ -19084,12 +19443,12 @@
     <x:row r="43">
       <x:c r="A43" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.19.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.19.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B43" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should let printing modules read the company's logo and stamp.</x:t>
+          <x:t xml:space="preserve">System should enable user to edit the logo and stamp.</x:t>
         </x:is>
       </x:c>
       <x:c r="C43" s="2" t="inlineStr">
@@ -19099,44 +19458,44 @@
       </x:c>
       <x:c r="D43" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">4.4.1.8.57</x:t>
         </x:is>
       </x:c>
       <x:c r="E43" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.57.4, REQ_IO_A8.57.5</x:t>
         </x:is>
       </x:c>
       <x:c r="F43" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-IMG-006</x:t>
+          <x:t xml:space="preserve">SYS-IMG-001, SYS-IMG-002, SYS-IMG-003, SYS-IMG-004, SYS-IMG-005, SYS-IMG-007, SYS-IMG-008</x:t>
         </x:is>
       </x:c>
       <x:c r="G43" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.20.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.19.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B44" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to view company details.</x:t>
+          <x:t xml:space="preserve">System should let printing modules read the company's logo and stamp.</x:t>
         </x:is>
       </x:c>
       <x:c r="C44" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.20</x:t>
+          <x:t xml:space="preserve">REQ_DS43.103</x:t>
         </x:is>
       </x:c>
       <x:c r="D44" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.58</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="E44" s="2" t="inlineStr">
@@ -19146,24 +19505,24 @@
       </x:c>
       <x:c r="F44" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-ORG-004, SYS-ORG-011, SYS-ORG-012, SYS-ORG-020, SYS-ORG-026</x:t>
+          <x:t xml:space="preserve">SYS-IMG-006</x:t>
         </x:is>
       </x:c>
       <x:c r="G44" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Covered</x:t>
+          <x:t xml:space="preserve">Partial</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.20.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.20.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B45" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to create a company.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to view company details.</x:t>
         </x:is>
       </x:c>
       <x:c r="C45" s="2" t="inlineStr">
@@ -19178,12 +19537,12 @@
       </x:c>
       <x:c r="E45" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.58.1, REQ_IO_A8.58.2</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="F45" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-ORG-001, SYS-ORG-008, SYS-ORG-013, SYS-ORG-021</x:t>
+          <x:t xml:space="preserve">SYS-ORG-004, SYS-ORG-011, SYS-ORG-012, SYS-ORG-020, SYS-ORG-026</x:t>
         </x:is>
       </x:c>
       <x:c r="G45" s="2" t="inlineStr">
@@ -19195,12 +19554,12 @@
     <x:row r="46">
       <x:c r="A46" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.20.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.20.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B46" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to edit a company.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to create a company.</x:t>
         </x:is>
       </x:c>
       <x:c r="C46" s="2" t="inlineStr">
@@ -19215,12 +19574,12 @@
       </x:c>
       <x:c r="E46" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.58.1, REQ_IO_A8.58.2</x:t>
         </x:is>
       </x:c>
       <x:c r="F46" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-ORG-005, SYS-ORG-009, SYS-ORG-013, SYS-ORG-021, SYS-PERM-030</x:t>
+          <x:t xml:space="preserve">SYS-ORG-001, SYS-ORG-008, SYS-ORG-013, SYS-ORG-021</x:t>
         </x:is>
       </x:c>
       <x:c r="G46" s="2" t="inlineStr">
@@ -19232,12 +19591,12 @@
     <x:row r="47">
       <x:c r="A47" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.20.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.20.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B47" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to deactivate a company.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to edit a company.</x:t>
         </x:is>
       </x:c>
       <x:c r="C47" s="2" t="inlineStr">
@@ -19257,7 +19616,7 @@
       </x:c>
       <x:c r="F47" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-ORG-006, SYS-ORG-021</x:t>
+          <x:t xml:space="preserve">SYS-ORG-005, SYS-ORG-009, SYS-ORG-013, SYS-ORG-021, SYS-PERM-030</x:t>
         </x:is>
       </x:c>
       <x:c r="G47" s="2" t="inlineStr">
@@ -19269,22 +19628,22 @@
     <x:row r="48">
       <x:c r="A48" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.21.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.20.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B48" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to view branches in the selected company.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to deactivate a company.</x:t>
         </x:is>
       </x:c>
       <x:c r="C48" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.89</x:t>
+          <x:t xml:space="preserve">REQ_DS43.20</x:t>
         </x:is>
       </x:c>
       <x:c r="D48" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.59</x:t>
+          <x:t xml:space="preserve">4.4.1.8.58</x:t>
         </x:is>
       </x:c>
       <x:c r="E48" s="2" t="inlineStr">
@@ -19294,7 +19653,7 @@
       </x:c>
       <x:c r="F48" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-ORG-002, SYS-ORG-004, SYS-ORG-010, SYS-ORG-012, SYS-ORG-020, SYS-ORG-022, SYS-ORG-024, SYS-ORG-025, SYS-ORG-027</x:t>
+          <x:t xml:space="preserve">SYS-ORG-006, SYS-ORG-021</x:t>
         </x:is>
       </x:c>
       <x:c r="G48" s="2" t="inlineStr">
@@ -19306,12 +19665,12 @@
     <x:row r="49">
       <x:c r="A49" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.21.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.21.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B49" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to create a branch.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to view branches in the selected company.</x:t>
         </x:is>
       </x:c>
       <x:c r="C49" s="2" t="inlineStr">
@@ -19326,12 +19685,12 @@
       </x:c>
       <x:c r="E49" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.59.1</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="F49" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-ORG-001, SYS-ORG-013, SYS-ORG-020, SYS-ORG-022, SYS-ORG-024</x:t>
+          <x:t xml:space="preserve">SYS-ORG-002, SYS-ORG-004, SYS-ORG-010, SYS-ORG-012, SYS-ORG-020, SYS-ORG-022, SYS-ORG-024, SYS-ORG-025, SYS-ORG-027</x:t>
         </x:is>
       </x:c>
       <x:c r="G49" s="2" t="inlineStr">
@@ -19343,12 +19702,12 @@
     <x:row r="50">
       <x:c r="A50" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.21.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.21.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B50" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to edit or deactivate a branch.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to create a branch.</x:t>
         </x:is>
       </x:c>
       <x:c r="C50" s="2" t="inlineStr">
@@ -19363,12 +19722,12 @@
       </x:c>
       <x:c r="E50" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.59.1</x:t>
         </x:is>
       </x:c>
       <x:c r="F50" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-ORG-005, SYS-ORG-022</x:t>
+          <x:t xml:space="preserve">SYS-ORG-001, SYS-ORG-013, SYS-ORG-020, SYS-ORG-022, SYS-ORG-024</x:t>
         </x:is>
       </x:c>
       <x:c r="G50" s="2" t="inlineStr">
@@ -19380,22 +19739,22 @@
     <x:row r="51">
       <x:c r="A51" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.22.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.21.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B51" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to view departments in the selected company.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to edit or deactivate a branch.</x:t>
         </x:is>
       </x:c>
       <x:c r="C51" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.22</x:t>
+          <x:t xml:space="preserve">REQ_DS43.89</x:t>
         </x:is>
       </x:c>
       <x:c r="D51" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.60</x:t>
+          <x:t xml:space="preserve">4.4.1.8.59</x:t>
         </x:is>
       </x:c>
       <x:c r="E51" s="2" t="inlineStr">
@@ -19405,7 +19764,7 @@
       </x:c>
       <x:c r="F51" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-ORG-002, SYS-ORG-004, SYS-ORG-010, SYS-ORG-012, SYS-ORG-020, SYS-ORG-023, SYS-ORG-026, SYS-ORG-027</x:t>
+          <x:t xml:space="preserve">SYS-ORG-005, SYS-ORG-022</x:t>
         </x:is>
       </x:c>
       <x:c r="G51" s="2" t="inlineStr">
@@ -19417,12 +19776,12 @@
     <x:row r="52">
       <x:c r="A52" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.22.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.22.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B52" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to create a department under a branch or parent department.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to view departments in the selected company.</x:t>
         </x:is>
       </x:c>
       <x:c r="C52" s="2" t="inlineStr">
@@ -19437,12 +19796,12 @@
       </x:c>
       <x:c r="E52" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.60.1, REQ_IO_A8.60.2</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="F52" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-ORG-001, SYS-ORG-003, SYS-ORG-013, SYS-ORG-023</x:t>
+          <x:t xml:space="preserve">SYS-ORG-002, SYS-ORG-004, SYS-ORG-010, SYS-ORG-012, SYS-ORG-020, SYS-ORG-023, SYS-ORG-026, SYS-ORG-027</x:t>
         </x:is>
       </x:c>
       <x:c r="G52" s="2" t="inlineStr">
@@ -19454,12 +19813,12 @@
     <x:row r="53">
       <x:c r="A53" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.22.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.22.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B53" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to edit or deactivate a department.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to create a department under a branch or parent department.</x:t>
         </x:is>
       </x:c>
       <x:c r="C53" s="2" t="inlineStr">
@@ -19474,12 +19833,12 @@
       </x:c>
       <x:c r="E53" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.60.1, REQ_IO_A8.60.2</x:t>
         </x:is>
       </x:c>
       <x:c r="F53" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-ORG-005, SYS-ORG-007, SYS-ORG-009, SYS-ORG-023, SYS-ORG-026</x:t>
+          <x:t xml:space="preserve">SYS-ORG-001, SYS-ORG-003, SYS-ORG-013, SYS-ORG-023</x:t>
         </x:is>
       </x:c>
       <x:c r="G53" s="2" t="inlineStr">
@@ -19491,32 +19850,32 @@
     <x:row r="54">
       <x:c r="A54" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.23.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.22.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B54" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to create a unique user identity.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to edit or deactivate a department.</x:t>
         </x:is>
       </x:c>
       <x:c r="C54" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.82</x:t>
+          <x:t xml:space="preserve">REQ_DS43.22</x:t>
         </x:is>
       </x:c>
       <x:c r="D54" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.61</x:t>
+          <x:t xml:space="preserve">4.4.1.8.60</x:t>
         </x:is>
       </x:c>
       <x:c r="E54" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.61.1</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="F54" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-ORG-027, SYS-USER-001, SYS-USER-004, SYS-USER-012</x:t>
+          <x:t xml:space="preserve">SYS-ORG-005, SYS-ORG-007, SYS-ORG-009, SYS-ORG-023, SYS-ORG-026</x:t>
         </x:is>
       </x:c>
       <x:c r="G54" s="2" t="inlineStr">
@@ -19528,12 +19887,12 @@
     <x:row r="55">
       <x:c r="A55" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.23.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.23.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B55" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enforce a configurable password policy.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to create a unique user identity.</x:t>
         </x:is>
       </x:c>
       <x:c r="C55" s="2" t="inlineStr">
@@ -19548,12 +19907,12 @@
       </x:c>
       <x:c r="E55" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.61.2, REQ_IO_A8.61.3</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.61.1</x:t>
         </x:is>
       </x:c>
       <x:c r="F55" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-USER-001, SYS-USER-007, SYS-USER-012</x:t>
+          <x:t xml:space="preserve">SYS-ORG-027, SYS-USER-001, SYS-USER-004, SYS-USER-012</x:t>
         </x:is>
       </x:c>
       <x:c r="G55" s="2" t="inlineStr">
@@ -19565,12 +19924,12 @@
     <x:row r="56">
       <x:c r="A56" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.23.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.23.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B56" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should lock an account after five consecutive failed password attempts.</x:t>
+          <x:t xml:space="preserve">System should enforce a configurable password policy.</x:t>
         </x:is>
       </x:c>
       <x:c r="C56" s="2" t="inlineStr">
@@ -19580,34 +19939,34 @@
       </x:c>
       <x:c r="D56" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">4.4.1.8.61</x:t>
         </x:is>
       </x:c>
       <x:c r="E56" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.61.2, REQ_IO_A8.61.3</x:t>
         </x:is>
       </x:c>
       <x:c r="F56" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-USER-002, SYS-USER-003, SYS-USER-005, SYS-USER-014</x:t>
+          <x:t xml:space="preserve">SYS-USER-001, SYS-USER-007, SYS-USER-012</x:t>
         </x:is>
       </x:c>
       <x:c r="G56" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="57">
       <x:c r="A57" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.23.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.23.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B57" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should determine whether a user's password has expired.</x:t>
+          <x:t xml:space="preserve">System should lock an account after five consecutive failed password attempts.</x:t>
         </x:is>
       </x:c>
       <x:c r="C57" s="2" t="inlineStr">
@@ -19627,7 +19986,7 @@
       </x:c>
       <x:c r="F57" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-USER-003</x:t>
+          <x:t xml:space="preserve">SYS-USER-002, SYS-USER-003, SYS-USER-005, SYS-USER-014</x:t>
         </x:is>
       </x:c>
       <x:c r="G57" s="2" t="inlineStr">
@@ -19639,49 +19998,49 @@
     <x:row r="58">
       <x:c r="A58" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.23.5</x:t>
+          <x:t xml:space="preserve">REQ_F4118.23.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B58" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should list the users of the current company with paging, keyword and sorting.</x:t>
+          <x:t xml:space="preserve">System should determine whether a user's password has expired.</x:t>
         </x:is>
       </x:c>
       <x:c r="C58" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.82, REQ_DS43.92</x:t>
+          <x:t xml:space="preserve">REQ_DS43.82</x:t>
         </x:is>
       </x:c>
       <x:c r="D58" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.63</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="E58" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.63.1, REQ_IO_A8.63.2</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="F58" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-USER-006, SYS-USER-010, SYS-USER-011, SYS-USER-015</x:t>
+          <x:t xml:space="preserve">SYS-USER-003</x:t>
         </x:is>
       </x:c>
       <x:c r="G58" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Covered</x:t>
+          <x:t xml:space="preserve">Partial</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="59">
       <x:c r="A59" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.23.6</x:t>
+          <x:t xml:space="preserve">REQ_F4118.23.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B59" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to create a user in the current company.</x:t>
+          <x:t xml:space="preserve">System should list the users of the current company with paging, keyword and sorting.</x:t>
         </x:is>
       </x:c>
       <x:c r="C59" s="2" t="inlineStr">
@@ -19691,17 +20050,17 @@
       </x:c>
       <x:c r="D59" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.61</x:t>
+          <x:t xml:space="preserve">4.4.1.8.63</x:t>
         </x:is>
       </x:c>
       <x:c r="E59" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.63.1, REQ_IO_A8.63.2</x:t>
         </x:is>
       </x:c>
       <x:c r="F59" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-USER-006, SYS-USER-010, SYS-USER-011, SYS-USER-012</x:t>
+          <x:t xml:space="preserve">SYS-USER-006, SYS-USER-010, SYS-USER-011, SYS-USER-015</x:t>
         </x:is>
       </x:c>
       <x:c r="G59" s="2" t="inlineStr">
@@ -19713,32 +20072,32 @@
     <x:row r="60">
       <x:c r="A60" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.23.7</x:t>
+          <x:t xml:space="preserve">REQ_F4118.23.6</x:t>
         </x:is>
       </x:c>
       <x:c r="B60" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to activate or deactivate a user.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to create a user in the current company.</x:t>
         </x:is>
       </x:c>
       <x:c r="C60" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.82</x:t>
+          <x:t xml:space="preserve">REQ_DS43.82, REQ_DS43.92</x:t>
         </x:is>
       </x:c>
       <x:c r="D60" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.63</x:t>
+          <x:t xml:space="preserve">4.4.1.8.61</x:t>
         </x:is>
       </x:c>
       <x:c r="E60" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.63.3</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="F60" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-USER-006, SYS-USER-010, SYS-USER-013, SYS-USER-015, SYS-PERM-029</x:t>
+          <x:t xml:space="preserve">SYS-USER-006, SYS-USER-010, SYS-USER-011, SYS-USER-012</x:t>
         </x:is>
       </x:c>
       <x:c r="G60" s="2" t="inlineStr">
@@ -19750,12 +20109,12 @@
     <x:row r="61">
       <x:c r="A61" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.23.8</x:t>
+          <x:t xml:space="preserve">REQ_F4118.23.7</x:t>
         </x:is>
       </x:c>
       <x:c r="B61" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to reset a password and unlock a locked user.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to activate or deactivate a user.</x:t>
         </x:is>
       </x:c>
       <x:c r="C61" s="2" t="inlineStr">
@@ -19770,12 +20129,12 @@
       </x:c>
       <x:c r="E61" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.63.4, REQ_IO_A8.63.5</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.63.3</x:t>
         </x:is>
       </x:c>
       <x:c r="F61" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-USER-006, SYS-USER-010, SYS-USER-014, SYS-PERM-029</x:t>
+          <x:t xml:space="preserve">SYS-USER-006, SYS-USER-010, SYS-USER-013, SYS-USER-015, SYS-PERM-029</x:t>
         </x:is>
       </x:c>
       <x:c r="G61" s="2" t="inlineStr">
@@ -19787,49 +20146,49 @@
     <x:row r="62">
       <x:c r="A62" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.24.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.23.8</x:t>
         </x:is>
       </x:c>
       <x:c r="B62" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow a user to log in with username, password and a numeric captcha.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to reset a password and unlock a locked user.</x:t>
         </x:is>
       </x:c>
       <x:c r="C62" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_DS43.82</x:t>
         </x:is>
       </x:c>
       <x:c r="D62" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.62</x:t>
+          <x:t xml:space="preserve">4.4.1.8.63</x:t>
         </x:is>
       </x:c>
       <x:c r="E62" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.62.1, REQ_IO_A8.62.2, REQ_IO_A8.62.3, REQ_IO_A8.62.4</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.63.4, REQ_IO_A8.63.5</x:t>
         </x:is>
       </x:c>
       <x:c r="F62" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-AUTH-001, SYS-AUTH-002, SYS-AUTH-005, SYS-AUTH-006, SYS-AUTH-009, SYS-AUTH-014, SYS-AUTH-015, SYS-AUTH-016, SYS-AUTH-017</x:t>
+          <x:t xml:space="preserve">SYS-USER-006, SYS-USER-010, SYS-USER-014, SYS-PERM-029</x:t>
         </x:is>
       </x:c>
       <x:c r="G62" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="63">
       <x:c r="A63" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.24.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.24.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B63" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should issue a 15-minute access token and a 7-day rotating refresh token.</x:t>
+          <x:t xml:space="preserve">System should allow a user to log in with username, password and a numeric captcha.</x:t>
         </x:is>
       </x:c>
       <x:c r="C63" s="2" t="inlineStr">
@@ -19839,17 +20198,17 @@
       </x:c>
       <x:c r="D63" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">4.4.1.8.62</x:t>
         </x:is>
       </x:c>
       <x:c r="E63" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.62.1, REQ_IO_A8.62.2, REQ_IO_A8.62.3, REQ_IO_A8.62.4</x:t>
         </x:is>
       </x:c>
       <x:c r="F63" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-AUTH-001, SYS-AUTH-004, SYS-AUTH-007, SYS-AUTH-009, SYS-AUTH-010, SYS-AUTH-016, SYS-AUTH-017</x:t>
+          <x:t xml:space="preserve">SYS-AUTH-001, SYS-AUTH-002, SYS-AUTH-005, SYS-AUTH-006, SYS-AUTH-009, SYS-AUTH-014, SYS-AUTH-015, SYS-AUTH-016, SYS-AUTH-017</x:t>
         </x:is>
       </x:c>
       <x:c r="G63" s="2" t="inlineStr">
@@ -19861,12 +20220,12 @@
     <x:row r="64">
       <x:c r="A64" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.24.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.24.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B64" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow a logged-in user to log out and invalidate the refresh token.</x:t>
+          <x:t xml:space="preserve">System should issue a 15-minute access token and a 7-day rotating refresh token.</x:t>
         </x:is>
       </x:c>
       <x:c r="C64" s="2" t="inlineStr">
@@ -19886,7 +20245,7 @@
       </x:c>
       <x:c r="F64" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-AUTH-008, SYS-AUTH-016, SYS-AUTH-017</x:t>
+          <x:t xml:space="preserve">SYS-AUTH-001, SYS-AUTH-004, SYS-AUTH-007, SYS-AUTH-009, SYS-AUTH-010, SYS-AUTH-016, SYS-AUTH-017</x:t>
         </x:is>
       </x:c>
       <x:c r="G64" s="2" t="inlineStr">
@@ -19898,12 +20257,12 @@
     <x:row r="65">
       <x:c r="A65" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.24.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.24.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B65" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should provide a development-only captcha master code with startup protection.</x:t>
+          <x:t xml:space="preserve">System should allow a logged-in user to log out and invalidate the refresh token.</x:t>
         </x:is>
       </x:c>
       <x:c r="C65" s="2" t="inlineStr">
@@ -19923,7 +20282,7 @@
       </x:c>
       <x:c r="F65" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-AUTH-003, SYS-AUTH-004, SYS-AUTH-016, SYS-AUTH-017</x:t>
+          <x:t xml:space="preserve">SYS-AUTH-008, SYS-AUTH-016, SYS-AUTH-017</x:t>
         </x:is>
       </x:c>
       <x:c r="G65" s="2" t="inlineStr">
@@ -19935,12 +20294,12 @@
     <x:row r="66">
       <x:c r="A66" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.24.5</x:t>
+          <x:t xml:space="preserve">REQ_F4118.24.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B66" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should provide a trilingual login page that keeps the session and refreshes tokens automatically.</x:t>
+          <x:t xml:space="preserve">System should provide a development-only captcha master code with startup protection.</x:t>
         </x:is>
       </x:c>
       <x:c r="C66" s="2" t="inlineStr">
@@ -19950,17 +20309,17 @@
       </x:c>
       <x:c r="D66" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.62</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="E66" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.62.5, REQ_IO_A8.62.6</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="F66" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-AUTH-011, SYS-AUTH-012, SYS-AUTH-013, SYS-AUTH-015, SYS-AUTH-016, SYS-AUTH-017</x:t>
+          <x:t xml:space="preserve">SYS-AUTH-003, SYS-AUTH-004, SYS-AUTH-016, SYS-AUTH-017</x:t>
         </x:is>
       </x:c>
       <x:c r="G66" s="2" t="inlineStr">
@@ -19972,54 +20331,54 @@
     <x:row r="67">
       <x:c r="A67" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.25.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.24.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B67" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to view roles and the permission catalog.</x:t>
+          <x:t xml:space="preserve">System should provide a trilingual login page that keeps the session and refreshes tokens automatically.</x:t>
         </x:is>
       </x:c>
       <x:c r="C67" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.90</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="D67" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.64</x:t>
+          <x:t xml:space="preserve">4.4.1.8.62</x:t>
         </x:is>
       </x:c>
       <x:c r="E67" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.62.5, REQ_IO_A8.62.6</x:t>
         </x:is>
       </x:c>
       <x:c r="F67" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-ORG-027, SYS-PERM-004, SYS-PERM-011, SYS-PERM-024, SYS-PERM-025</x:t>
+          <x:t xml:space="preserve">SYS-AUTH-011, SYS-AUTH-012, SYS-AUTH-013, SYS-AUTH-015, SYS-AUTH-016, SYS-AUTH-017</x:t>
         </x:is>
       </x:c>
       <x:c r="G67" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Covered</x:t>
+          <x:t xml:space="preserve">Partial</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.25.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.25.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B68" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to create a role with permissions and a data scope.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to view roles and the permission catalog.</x:t>
         </x:is>
       </x:c>
       <x:c r="C68" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.90, REQ_DS43.91</x:t>
+          <x:t xml:space="preserve">REQ_DS43.90</x:t>
         </x:is>
       </x:c>
       <x:c r="D68" s="2" t="inlineStr">
@@ -20029,12 +20388,12 @@
       </x:c>
       <x:c r="E68" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.64.1, REQ_IO_A8.64.2, REQ_IO_A8.64.3, REQ_IO_A8.64.4, REQ_IO_A8.64.5</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="F68" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-PERM-011, SYS-PERM-024, SYS-PERM-025</x:t>
+          <x:t xml:space="preserve">SYS-ORG-027, SYS-PERM-004, SYS-PERM-011, SYS-PERM-024, SYS-PERM-025</x:t>
         </x:is>
       </x:c>
       <x:c r="G68" s="2" t="inlineStr">
@@ -20046,12 +20405,12 @@
     <x:row r="69">
       <x:c r="A69" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.25.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.25.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B69" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to edit or deactivate a role.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to create a role with permissions and a data scope.</x:t>
         </x:is>
       </x:c>
       <x:c r="C69" s="2" t="inlineStr">
@@ -20066,12 +20425,12 @@
       </x:c>
       <x:c r="E69" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.64.2, REQ_IO_A8.64.5</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.64.1, REQ_IO_A8.64.2, REQ_IO_A8.64.3, REQ_IO_A8.64.4, REQ_IO_A8.64.5</x:t>
         </x:is>
       </x:c>
       <x:c r="F69" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-PERM-011, SYS-PERM-024, SYS-PERM-025, SYS-PERM-031, SYS-PERM-032</x:t>
+          <x:t xml:space="preserve">SYS-PERM-011, SYS-PERM-024, SYS-PERM-025</x:t>
         </x:is>
       </x:c>
       <x:c r="G69" s="2" t="inlineStr">
@@ -20083,17 +20442,17 @@
     <x:row r="70">
       <x:c r="A70" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.25.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.25.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B70" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to delete an unused role.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to edit or deactivate a role.</x:t>
         </x:is>
       </x:c>
       <x:c r="C70" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.90</x:t>
+          <x:t xml:space="preserve">REQ_DS43.90, REQ_DS43.91</x:t>
         </x:is>
       </x:c>
       <x:c r="D70" s="2" t="inlineStr">
@@ -20103,12 +20462,12 @@
       </x:c>
       <x:c r="E70" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.64.6</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.64.2, REQ_IO_A8.64.5</x:t>
         </x:is>
       </x:c>
       <x:c r="F70" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-PERM-012, SYS-PERM-024, SYS-PERM-025</x:t>
+          <x:t xml:space="preserve">SYS-PERM-011, SYS-PERM-024, SYS-PERM-025, SYS-PERM-031, SYS-PERM-032</x:t>
         </x:is>
       </x:c>
       <x:c r="G70" s="2" t="inlineStr">
@@ -20120,197 +20479,197 @@
     <x:row r="71">
       <x:c r="A71" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.25.5</x:t>
+          <x:t xml:space="preserve">REQ_F4118.25.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B71" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enforce permission codes on every API with the backend as the authority.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to delete an unused role.</x:t>
         </x:is>
       </x:c>
       <x:c r="C71" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.92</x:t>
+          <x:t xml:space="preserve">REQ_DS43.90</x:t>
         </x:is>
       </x:c>
       <x:c r="D71" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">4.4.1.8.64</x:t>
         </x:is>
       </x:c>
       <x:c r="E71" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.64.6</x:t>
         </x:is>
       </x:c>
       <x:c r="F71" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-PERM-001, SYS-PERM-005, SYS-PERM-006, SYS-PERM-010</x:t>
+          <x:t xml:space="preserve">SYS-PERM-012, SYS-PERM-024, SYS-PERM-025</x:t>
         </x:is>
       </x:c>
       <x:c r="G71" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="72">
       <x:c r="A72" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.25.6</x:t>
+          <x:t xml:space="preserve">REQ_F4118.25.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B72" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to grant a user access to a company with roles, organization and default company.</x:t>
+          <x:t xml:space="preserve">System should enforce permission codes on every API with the backend as the authority.</x:t>
         </x:is>
       </x:c>
       <x:c r="C72" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.92, REQ_DS43.93</x:t>
+          <x:t xml:space="preserve">REQ_DS43.92</x:t>
         </x:is>
       </x:c>
       <x:c r="D72" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.65</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="E72" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.65.1, REQ_IO_A8.65.2, REQ_IO_A8.65.3, REQ_IO_A8.65.4, REQ_IO_A8.65.5</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="F72" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-PERM-015, SYS-PERM-016, SYS-PERM-017, SYS-PERM-018, SYS-PERM-026, SYS-PERM-027, SYS-PERM-028</x:t>
+          <x:t xml:space="preserve">SYS-PERM-001, SYS-PERM-005, SYS-PERM-006, SYS-PERM-010</x:t>
         </x:is>
       </x:c>
       <x:c r="G72" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Covered</x:t>
+          <x:t xml:space="preserve">Partial</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="73">
       <x:c r="A73" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.25.7</x:t>
+          <x:t xml:space="preserve">REQ_F4118.25.6</x:t>
         </x:is>
       </x:c>
       <x:c r="B73" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should resolve the user's effective permissions and data scope per company and hide unauthorized UI.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to grant a user access to a company with roles, organization and default company.</x:t>
         </x:is>
       </x:c>
       <x:c r="C73" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.91, REQ_DS43.92, REQ_DS43.93</x:t>
+          <x:t xml:space="preserve">REQ_DS43.92, REQ_DS43.93</x:t>
         </x:is>
       </x:c>
       <x:c r="D73" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">4.4.1.8.65</x:t>
         </x:is>
       </x:c>
       <x:c r="E73" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.65.1, REQ_IO_A8.65.2, REQ_IO_A8.65.3, REQ_IO_A8.65.4, REQ_IO_A8.65.5</x:t>
         </x:is>
       </x:c>
       <x:c r="F73" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-PERM-002, SYS-PERM-003, SYS-PERM-013, SYS-PERM-014, SYS-PERM-020, SYS-PERM-021, SYS-PERM-022, SYS-PERM-023</x:t>
+          <x:t xml:space="preserve">SYS-PERM-015, SYS-PERM-016, SYS-PERM-017, SYS-PERM-018, SYS-PERM-026, SYS-PERM-027, SYS-PERM-028</x:t>
         </x:is>
       </x:c>
       <x:c r="G73" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="74">
       <x:c r="A74" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.25.8</x:t>
+          <x:t xml:space="preserve">REQ_F4118.25.7</x:t>
         </x:is>
       </x:c>
       <x:c r="B74" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to view a user's company access, organization and roles.</x:t>
+          <x:t xml:space="preserve">System should resolve the user's effective permissions and data scope per company and hide unauthorized UI.</x:t>
         </x:is>
       </x:c>
       <x:c r="C74" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.92, REQ_DS43.93</x:t>
+          <x:t xml:space="preserve">REQ_DS43.91, REQ_DS43.92, REQ_DS43.93</x:t>
         </x:is>
       </x:c>
       <x:c r="D74" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.65</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="E74" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.65.1</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="F74" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-PERM-017, SYS-PERM-018, SYS-PERM-026, SYS-PERM-027</x:t>
+          <x:t xml:space="preserve">SYS-PERM-002, SYS-PERM-003, SYS-PERM-013, SYS-PERM-014, SYS-PERM-020, SYS-PERM-021, SYS-PERM-022, SYS-PERM-023</x:t>
         </x:is>
       </x:c>
       <x:c r="G74" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Covered</x:t>
+          <x:t xml:space="preserve">Partial</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="75">
       <x:c r="A75" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.26.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.25.8</x:t>
         </x:is>
       </x:c>
       <x:c r="B75" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enforce HTTPS with HSTS outside the development environment.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to view a user's company access, organization and roles.</x:t>
         </x:is>
       </x:c>
       <x:c r="C75" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_DS43.92, REQ_DS43.93</x:t>
         </x:is>
       </x:c>
       <x:c r="D75" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">4.4.1.8.65</x:t>
         </x:is>
       </x:c>
       <x:c r="E75" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.65.1</x:t>
         </x:is>
       </x:c>
       <x:c r="F75" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-SEC-004</x:t>
+          <x:t xml:space="preserve">SYS-PERM-017, SYS-PERM-018, SYS-PERM-026, SYS-PERM-027</x:t>
         </x:is>
       </x:c>
       <x:c r="G75" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="76">
       <x:c r="A76" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.26.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.26.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B76" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow cross-origin requests only from configured frontend origins.</x:t>
+          <x:t xml:space="preserve">System should enforce HTTPS with HSTS outside the development environment.</x:t>
         </x:is>
       </x:c>
       <x:c r="C76" s="2" t="inlineStr">
@@ -20330,7 +20689,7 @@
       </x:c>
       <x:c r="F76" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-SEC-002, SYS-SEC-003, SYS-SEC-006</x:t>
+          <x:t xml:space="preserve">SYS-SEC-004</x:t>
         </x:is>
       </x:c>
       <x:c r="G76" s="2" t="inlineStr">
@@ -20342,12 +20701,12 @@
     <x:row r="77">
       <x:c r="A77" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.26.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.26.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B77" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should rate-limit login, token refresh and captcha requests per client IP.</x:t>
+          <x:t xml:space="preserve">System should allow cross-origin requests only from configured frontend origins.</x:t>
         </x:is>
       </x:c>
       <x:c r="C77" s="2" t="inlineStr">
@@ -20367,7 +20726,7 @@
       </x:c>
       <x:c r="F77" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-SEC-003, SYS-SEC-005, SYS-SEC-006, SYS-SEC-007, SYS-SEC-011, SYS-SEC-012</x:t>
+          <x:t xml:space="preserve">SYS-SEC-002, SYS-SEC-003, SYS-SEC-006</x:t>
         </x:is>
       </x:c>
       <x:c r="G77" s="2" t="inlineStr">
@@ -20379,12 +20738,12 @@
     <x:row r="78">
       <x:c r="A78" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.26.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.26.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B78" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should rate-limit authenticated API requests per user.</x:t>
+          <x:t xml:space="preserve">System should rate-limit login, token refresh and captcha requests per client IP.</x:t>
         </x:is>
       </x:c>
       <x:c r="C78" s="2" t="inlineStr">
@@ -20404,7 +20763,7 @@
       </x:c>
       <x:c r="F78" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-SEC-010</x:t>
+          <x:t xml:space="preserve">SYS-SEC-003, SYS-SEC-005, SYS-SEC-006, SYS-SEC-007, SYS-SEC-011, SYS-SEC-012</x:t>
         </x:is>
       </x:c>
       <x:c r="G78" s="2" t="inlineStr">
@@ -20416,12 +20775,12 @@
     <x:row r="79">
       <x:c r="A79" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.26.5</x:t>
+          <x:t xml:space="preserve">REQ_F4118.26.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B79" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should add security headers to every API response.</x:t>
+          <x:t xml:space="preserve">System should rate-limit authenticated API requests per user.</x:t>
         </x:is>
       </x:c>
       <x:c r="C79" s="2" t="inlineStr">
@@ -20441,7 +20800,7 @@
       </x:c>
       <x:c r="F79" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-SEC-001, SYS-SEC-014</x:t>
+          <x:t xml:space="preserve">SYS-SEC-010</x:t>
         </x:is>
       </x:c>
       <x:c r="G79" s="2" t="inlineStr">
@@ -20453,12 +20812,12 @@
     <x:row r="80">
       <x:c r="A80" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.26.6</x:t>
+          <x:t xml:space="preserve">REQ_F4118.26.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B80" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should honour X-Forwarded-For only from configured proxies.</x:t>
+          <x:t xml:space="preserve">System should add security headers to every API response.</x:t>
         </x:is>
       </x:c>
       <x:c r="C80" s="2" t="inlineStr">
@@ -20478,7 +20837,7 @@
       </x:c>
       <x:c r="F80" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-SEC-003, SYS-SEC-008, SYS-SEC-009</x:t>
+          <x:t xml:space="preserve">SYS-SEC-001, SYS-SEC-014</x:t>
         </x:is>
       </x:c>
       <x:c r="G80" s="2" t="inlineStr">
@@ -20490,12 +20849,12 @@
     <x:row r="81">
       <x:c r="A81" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.26.7</x:t>
+          <x:t xml:space="preserve">REQ_F4118.26.6</x:t>
         </x:is>
       </x:c>
       <x:c r="B81" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should show a trilingual "too many requests" message when an API call is rate-limited.</x:t>
+          <x:t xml:space="preserve">System should honour X-Forwarded-For only from configured proxies.</x:t>
         </x:is>
       </x:c>
       <x:c r="C81" s="2" t="inlineStr">
@@ -20515,7 +20874,7 @@
       </x:c>
       <x:c r="F81" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-SEC-013, SYS-SEC-014</x:t>
+          <x:t xml:space="preserve">SYS-SEC-003, SYS-SEC-008, SYS-SEC-009</x:t>
         </x:is>
       </x:c>
       <x:c r="G81" s="2" t="inlineStr">
@@ -20527,17 +20886,17 @@
     <x:row r="82">
       <x:c r="A82" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.27.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.26.7</x:t>
         </x:is>
       </x:c>
       <x:c r="B82" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should record every data change in sys_audit_log within the same transaction.</x:t>
+          <x:t xml:space="preserve">System should show a trilingual "too many requests" message when an API call is rate-limited.</x:t>
         </x:is>
       </x:c>
       <x:c r="C82" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.94</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="D82" s="2" t="inlineStr">
@@ -20552,7 +20911,7 @@
       </x:c>
       <x:c r="F82" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-AUDIT-001, SYS-AUDIT-002, SYS-AUDIT-003, SYS-AUDIT-004, SYS-AUDIT-005, SYS-AUDIT-006, SYS-AUDIT-010</x:t>
+          <x:t xml:space="preserve">SYS-SEC-013, SYS-SEC-014</x:t>
         </x:is>
       </x:c>
       <x:c r="G82" s="2" t="inlineStr">
@@ -20564,12 +20923,12 @@
     <x:row r="83">
       <x:c r="A83" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.27.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.27.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B83" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should protect audit records and sensitive values.</x:t>
+          <x:t xml:space="preserve">System should record every data change in sys_audit_log within the same transaction.</x:t>
         </x:is>
       </x:c>
       <x:c r="C83" s="2" t="inlineStr">
@@ -20584,29 +20943,29 @@
       </x:c>
       <x:c r="E83" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.66.5</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="F83" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-AUDIT-003, SYS-AUDIT-008, SYS-AUDIT-011</x:t>
+          <x:t xml:space="preserve">SYS-AUDIT-001, SYS-AUDIT-002, SYS-AUDIT-003, SYS-AUDIT-004, SYS-AUDIT-005, SYS-AUDIT-006, SYS-AUDIT-010</x:t>
         </x:is>
       </x:c>
       <x:c r="G83" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Covered</x:t>
+          <x:t xml:space="preserve">Partial</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="84">
       <x:c r="A84" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.27.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.27.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B84" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should record login, failed login, logout and captcha master-code login as security events.</x:t>
+          <x:t xml:space="preserve">System should protect audit records and sensitive values.</x:t>
         </x:is>
       </x:c>
       <x:c r="C84" s="2" t="inlineStr">
@@ -20621,29 +20980,29 @@
       </x:c>
       <x:c r="E84" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.66.5</x:t>
         </x:is>
       </x:c>
       <x:c r="F84" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-AUDIT-007, SYS-AUDIT-012</x:t>
+          <x:t xml:space="preserve">SYS-AUDIT-003, SYS-AUDIT-008, SYS-AUDIT-011</x:t>
         </x:is>
       </x:c>
       <x:c r="G84" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="85">
       <x:c r="A85" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.27.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.27.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B85" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to query audit logs of the current company.</x:t>
+          <x:t xml:space="preserve">System should record login, failed login, logout and captcha master-code login as security events.</x:t>
         </x:is>
       </x:c>
       <x:c r="C85" s="2" t="inlineStr">
@@ -20653,34 +21012,34 @@
       </x:c>
       <x:c r="D85" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.66</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="E85" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.66.1</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="F85" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-AUDIT-009, SYS-AUDIT-010</x:t>
+          <x:t xml:space="preserve">SYS-AUDIT-007, SYS-AUDIT-012</x:t>
         </x:is>
       </x:c>
       <x:c r="G85" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Covered</x:t>
+          <x:t xml:space="preserve">Partial</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="86">
       <x:c r="A86" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.27.5</x:t>
+          <x:t xml:space="preserve">REQ_F4118.27.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B86" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should record role permission and user company access changes as security events.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to query audit logs of the current company.</x:t>
         </x:is>
       </x:c>
       <x:c r="C86" s="2" t="inlineStr">
@@ -20690,34 +21049,34 @@
       </x:c>
       <x:c r="D86" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">4.4.1.8.66</x:t>
         </x:is>
       </x:c>
       <x:c r="E86" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.66.1</x:t>
         </x:is>
       </x:c>
       <x:c r="F86" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-AUDIT-013</x:t>
+          <x:t xml:space="preserve">SYS-AUDIT-009, SYS-AUDIT-010</x:t>
         </x:is>
       </x:c>
       <x:c r="G86" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="87">
       <x:c r="A87" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.27.6</x:t>
+          <x:t xml:space="preserve">REQ_F4118.27.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B87" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should provide a trilingual audit log page with per-record change history.</x:t>
+          <x:t xml:space="preserve">System should record role permission and user company access changes as security events.</x:t>
         </x:is>
       </x:c>
       <x:c r="C87" s="2" t="inlineStr">
@@ -20727,54 +21086,54 @@
       </x:c>
       <x:c r="D87" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.66</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="E87" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.66.1, REQ_IO_A8.66.2, REQ_IO_A8.66.3, REQ_IO_A8.66.4, REQ_IO_A8.66.5, REQ_IO_A8.66.6</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="F87" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-AUDIT-014</x:t>
+          <x:t xml:space="preserve">SYS-AUDIT-013</x:t>
         </x:is>
       </x:c>
       <x:c r="G87" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Covered</x:t>
+          <x:t xml:space="preserve">Partial</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="88">
       <x:c r="A88" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.28.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.27.6</x:t>
         </x:is>
       </x:c>
       <x:c r="B88" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow user to view document number rules of the current company.</x:t>
+          <x:t xml:space="preserve">System should provide a trilingual audit log page with per-record change history.</x:t>
         </x:is>
       </x:c>
       <x:c r="C88" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.95</x:t>
+          <x:t xml:space="preserve">REQ_DS43.94</x:t>
         </x:is>
       </x:c>
       <x:c r="D88" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.67</x:t>
+          <x:t xml:space="preserve">4.4.1.8.66</x:t>
         </x:is>
       </x:c>
       <x:c r="E88" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.66.1, REQ_IO_A8.66.2, REQ_IO_A8.66.3, REQ_IO_A8.66.4, REQ_IO_A8.66.5, REQ_IO_A8.66.6</x:t>
         </x:is>
       </x:c>
       <x:c r="F88" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-NUM-006, SYS-NUM-008, SYS-NUM-010</x:t>
+          <x:t xml:space="preserve">SYS-AUDIT-014</x:t>
         </x:is>
       </x:c>
       <x:c r="G88" s="2" t="inlineStr">
@@ -20786,12 +21145,12 @@
     <x:row r="89">
       <x:c r="A89" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.28.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.28.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B89" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow user to create a document number rule with prefix, date format, sequence length and reset period.</x:t>
+          <x:t xml:space="preserve">System should allow user to view document number rules of the current company.</x:t>
         </x:is>
       </x:c>
       <x:c r="C89" s="2" t="inlineStr">
@@ -20806,12 +21165,12 @@
       </x:c>
       <x:c r="E89" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.67.1, REQ_IO_A8.67.2, REQ_IO_A8.67.3, REQ_IO_A8.67.4, REQ_IO_A8.67.5, REQ_IO_A8.67.6</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="F89" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-NUM-006, SYS-NUM-007, SYS-NUM-008, SYS-NUM-010, SYS-NUM-011</x:t>
+          <x:t xml:space="preserve">SYS-NUM-006, SYS-NUM-008, SYS-NUM-010</x:t>
         </x:is>
       </x:c>
       <x:c r="G89" s="2" t="inlineStr">
@@ -20823,17 +21182,17 @@
     <x:row r="90">
       <x:c r="A90" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.28.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.28.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B90" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow user to edit or deactivate a document number rule without breaking issued numbers.</x:t>
+          <x:t xml:space="preserve">System should allow user to create a document number rule with prefix, date format, sequence length and reset period.</x:t>
         </x:is>
       </x:c>
       <x:c r="C90" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.95, REQ_DS43.96</x:t>
+          <x:t xml:space="preserve">REQ_DS43.95</x:t>
         </x:is>
       </x:c>
       <x:c r="D90" s="2" t="inlineStr">
@@ -20843,12 +21202,12 @@
       </x:c>
       <x:c r="E90" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.67.2, REQ_IO_A8.67.3, REQ_IO_A8.67.4, REQ_IO_A8.67.5, REQ_IO_A8.67.6, REQ_IO_A8.67.8</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.67.1, REQ_IO_A8.67.2, REQ_IO_A8.67.3, REQ_IO_A8.67.4, REQ_IO_A8.67.5, REQ_IO_A8.67.6</x:t>
         </x:is>
       </x:c>
       <x:c r="F90" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-NUM-006, SYS-NUM-008, SYS-NUM-009, SYS-NUM-010, SYS-NUM-011</x:t>
+          <x:t xml:space="preserve">SYS-NUM-006, SYS-NUM-007, SYS-NUM-008, SYS-NUM-010, SYS-NUM-011</x:t>
         </x:is>
       </x:c>
       <x:c r="G90" s="2" t="inlineStr">
@@ -20860,12 +21219,12 @@
     <x:row r="91">
       <x:c r="A91" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.28.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.28.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B91" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow user to preview the next document number for a business date.</x:t>
+          <x:t xml:space="preserve">System should allow user to edit or deactivate a document number rule without breaking issued numbers.</x:t>
         </x:is>
       </x:c>
       <x:c r="C91" s="2" t="inlineStr">
@@ -20880,12 +21239,12 @@
       </x:c>
       <x:c r="E91" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.67.9</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.67.2, REQ_IO_A8.67.3, REQ_IO_A8.67.4, REQ_IO_A8.67.5, REQ_IO_A8.67.6, REQ_IO_A8.67.8</x:t>
         </x:is>
       </x:c>
       <x:c r="F91" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-NUM-006, SYS-NUM-008, SYS-NUM-010, SYS-NUM-011</x:t>
+          <x:t xml:space="preserve">SYS-NUM-006, SYS-NUM-008, SYS-NUM-009, SYS-NUM-010, SYS-NUM-011</x:t>
         </x:is>
       </x:c>
       <x:c r="G91" s="2" t="inlineStr">
@@ -20897,12 +21256,12 @@
     <x:row r="92">
       <x:c r="A92" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.28.5</x:t>
+          <x:t xml:space="preserve">REQ_F4118.28.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B92" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should generate unique, gap-free document numbers for every module under concurrency.</x:t>
+          <x:t xml:space="preserve">System should allow user to preview the next document number for a business date.</x:t>
         </x:is>
       </x:c>
       <x:c r="C92" s="2" t="inlineStr">
@@ -20912,91 +21271,91 @@
       </x:c>
       <x:c r="D92" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">4.4.1.8.67</x:t>
         </x:is>
       </x:c>
       <x:c r="E92" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.67.9</x:t>
         </x:is>
       </x:c>
       <x:c r="F92" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-NUM-001, SYS-NUM-002, SYS-NUM-003, SYS-NUM-004, SYS-NUM-005, SYS-NUM-009</x:t>
+          <x:t xml:space="preserve">SYS-NUM-006, SYS-NUM-008, SYS-NUM-010, SYS-NUM-011</x:t>
         </x:is>
       </x:c>
       <x:c r="G92" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="93">
       <x:c r="A93" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.28.6</x:t>
+          <x:t xml:space="preserve">REQ_F4118.28.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B93" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should provide a trilingual number rule maintenance page.</x:t>
+          <x:t xml:space="preserve">System should generate unique, gap-free document numbers for every module under concurrency.</x:t>
         </x:is>
       </x:c>
       <x:c r="C93" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.95</x:t>
+          <x:t xml:space="preserve">REQ_DS43.95, REQ_DS43.96</x:t>
         </x:is>
       </x:c>
       <x:c r="D93" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.67</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="E93" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.67.1, REQ_IO_A8.67.7</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="F93" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-NUM-010, SYS-NUM-011</x:t>
+          <x:t xml:space="preserve">SYS-NUM-001, SYS-NUM-002, SYS-NUM-003, SYS-NUM-004, SYS-NUM-005, SYS-NUM-009</x:t>
         </x:is>
       </x:c>
       <x:c r="G93" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Covered</x:t>
+          <x:t xml:space="preserve">Partial</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="94">
       <x:c r="A94" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.29.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.28.6</x:t>
         </x:is>
       </x:c>
       <x:c r="B94" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow user to view and create multi-level approval flows with amount thresholds.</x:t>
+          <x:t xml:space="preserve">System should provide a trilingual number rule maintenance page.</x:t>
         </x:is>
       </x:c>
       <x:c r="C94" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.97, REQ_DS43.98</x:t>
+          <x:t xml:space="preserve">REQ_DS43.95</x:t>
         </x:is>
       </x:c>
       <x:c r="D94" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.68</x:t>
+          <x:t xml:space="preserve">4.4.1.8.67</x:t>
         </x:is>
       </x:c>
       <x:c r="E94" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.68.1, REQ_IO_A8.68.2, REQ_IO_A8.68.3, REQ_IO_A8.68.4, REQ_IO_A8.68.5, REQ_IO_A8.68.6, REQ_IO_A8.68.7</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.67.1, REQ_IO_A8.67.7</x:t>
         </x:is>
       </x:c>
       <x:c r="F94" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-APR-008, SYS-APR-010, SYS-APR-012, SYS-APR-013</x:t>
+          <x:t xml:space="preserve">SYS-NUM-010, SYS-NUM-011</x:t>
         </x:is>
       </x:c>
       <x:c r="G94" s="2" t="inlineStr">
@@ -21008,12 +21367,12 @@
     <x:row r="95">
       <x:c r="A95" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.29.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.29.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B95" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow user to edit or deactivate an approval flow without affecting pending approvals.</x:t>
+          <x:t xml:space="preserve">System should allow user to view and create multi-level approval flows with amount thresholds.</x:t>
         </x:is>
       </x:c>
       <x:c r="C95" s="2" t="inlineStr">
@@ -21028,12 +21387,12 @@
       </x:c>
       <x:c r="E95" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.68.2, REQ_IO_A8.68.3, REQ_IO_A8.68.8</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.68.1, REQ_IO_A8.68.2, REQ_IO_A8.68.3, REQ_IO_A8.68.4, REQ_IO_A8.68.5, REQ_IO_A8.68.6, REQ_IO_A8.68.7</x:t>
         </x:is>
       </x:c>
       <x:c r="F95" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-APR-003, SYS-APR-008, SYS-APR-010, SYS-APR-012, SYS-APR-013</x:t>
+          <x:t xml:space="preserve">SYS-APR-008, SYS-APR-010, SYS-APR-012, SYS-APR-013</x:t>
         </x:is>
       </x:c>
       <x:c r="G95" s="2" t="inlineStr">
@@ -21045,32 +21404,32 @@
     <x:row r="96">
       <x:c r="A96" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.29.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.29.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B96" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow user to assign an approval delegate for a date range.</x:t>
+          <x:t xml:space="preserve">System should allow user to edit or deactivate an approval flow without affecting pending approvals.</x:t>
         </x:is>
       </x:c>
       <x:c r="C96" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.99</x:t>
+          <x:t xml:space="preserve">REQ_DS43.97, REQ_DS43.98</x:t>
         </x:is>
       </x:c>
       <x:c r="D96" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.69</x:t>
+          <x:t xml:space="preserve">4.4.1.8.68</x:t>
         </x:is>
       </x:c>
       <x:c r="E96" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.69.1, REQ_IO_A8.69.2, REQ_IO_A8.69.3, REQ_IO_A8.69.4</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.68.2, REQ_IO_A8.68.3, REQ_IO_A8.68.8</x:t>
         </x:is>
       </x:c>
       <x:c r="F96" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-APR-005, SYS-APR-010, SYS-APR-012, SYS-APR-013</x:t>
+          <x:t xml:space="preserve">SYS-APR-003, SYS-APR-008, SYS-APR-010, SYS-APR-012, SYS-APR-013</x:t>
         </x:is>
       </x:c>
       <x:c r="G96" s="2" t="inlineStr">
@@ -21082,86 +21441,86 @@
     <x:row r="97">
       <x:c r="A97" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.29.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.29.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B97" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable every module to submit documents for approval through the shared workflow engine.</x:t>
+          <x:t xml:space="preserve">System should allow user to assign an approval delegate for a date range.</x:t>
         </x:is>
       </x:c>
       <x:c r="C97" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.97, REQ_DS43.98, REQ_DS43.100, REQ_DS43.101</x:t>
+          <x:t xml:space="preserve">REQ_DS43.99</x:t>
         </x:is>
       </x:c>
       <x:c r="D97" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">4.4.1.8.69</x:t>
         </x:is>
       </x:c>
       <x:c r="E97" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.69.1, REQ_IO_A8.69.2, REQ_IO_A8.69.3, REQ_IO_A8.69.4</x:t>
         </x:is>
       </x:c>
       <x:c r="F97" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-APR-001, SYS-APR-002, SYS-APR-003, SYS-APR-007, SYS-APR-011</x:t>
+          <x:t xml:space="preserve">SYS-APR-005, SYS-APR-010, SYS-APR-012, SYS-APR-013</x:t>
         </x:is>
       </x:c>
       <x:c r="G97" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="98">
       <x:c r="A98" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.29.5</x:t>
+          <x:t xml:space="preserve">REQ_F4118.29.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B98" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow approvers or their delegates to approve or reject the current approval step.</x:t>
+          <x:t xml:space="preserve">System should enable every module to submit documents for approval through the shared workflow engine.</x:t>
         </x:is>
       </x:c>
       <x:c r="C98" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.99, REQ_DS43.100, REQ_DS43.101</x:t>
+          <x:t xml:space="preserve">REQ_DS43.97, REQ_DS43.98, REQ_DS43.100, REQ_DS43.101</x:t>
         </x:is>
       </x:c>
       <x:c r="D98" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.70</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="E98" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.70.1</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="F98" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-APR-001, SYS-APR-002, SYS-APR-004, SYS-APR-005, SYS-APR-006, SYS-APR-007, SYS-APR-011, SYS-APR-012, SYS-APR-013</x:t>
+          <x:t xml:space="preserve">SYS-APR-001, SYS-APR-002, SYS-APR-003, SYS-APR-007, SYS-APR-011</x:t>
         </x:is>
       </x:c>
       <x:c r="G98" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Covered</x:t>
+          <x:t xml:space="preserve">Partial</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="99">
       <x:c r="A99" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.29.6</x:t>
+          <x:t xml:space="preserve">REQ_F4118.29.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B99" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should list the pending approval tasks of the current user.</x:t>
+          <x:t xml:space="preserve">System should allow approvers or their delegates to approve or reject the current approval step.</x:t>
         </x:is>
       </x:c>
       <x:c r="C99" s="2" t="inlineStr">
@@ -21176,12 +21535,12 @@
       </x:c>
       <x:c r="E99" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.70.1</x:t>
         </x:is>
       </x:c>
       <x:c r="F99" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-APR-004, SYS-APR-005, SYS-APR-011, SYS-APR-012, SYS-APR-013</x:t>
+          <x:t xml:space="preserve">SYS-APR-001, SYS-APR-002, SYS-APR-004, SYS-APR-005, SYS-APR-006, SYS-APR-007, SYS-APR-011, SYS-APR-012, SYS-APR-013</x:t>
         </x:is>
       </x:c>
       <x:c r="G99" s="2" t="inlineStr">
@@ -21193,17 +21552,17 @@
     <x:row r="100">
       <x:c r="A100" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.29.7</x:t>
+          <x:t xml:space="preserve">REQ_F4118.29.6</x:t>
         </x:is>
       </x:c>
       <x:c r="B100" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow user to view the approval history of a document.</x:t>
+          <x:t xml:space="preserve">System should list the pending approval tasks of the current user.</x:t>
         </x:is>
       </x:c>
       <x:c r="C100" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.100, REQ_DS43.101</x:t>
+          <x:t xml:space="preserve">REQ_DS43.99, REQ_DS43.100, REQ_DS43.101</x:t>
         </x:is>
       </x:c>
       <x:c r="D100" s="2" t="inlineStr">
@@ -21213,12 +21572,12 @@
       </x:c>
       <x:c r="E100" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.70.2</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="F100" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-APR-001, SYS-APR-002, SYS-APR-008, SYS-APR-011, SYS-APR-012, SYS-APR-013</x:t>
+          <x:t xml:space="preserve">SYS-APR-004, SYS-APR-005, SYS-APR-011, SYS-APR-012, SYS-APR-013</x:t>
         </x:is>
       </x:c>
       <x:c r="G100" s="2" t="inlineStr">
@@ -21230,32 +21589,32 @@
     <x:row r="101">
       <x:c r="A101" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.29.8</x:t>
+          <x:t xml:space="preserve">REQ_F4118.29.7</x:t>
         </x:is>
       </x:c>
       <x:c r="B101" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should provide trilingual approval flow and delegation maintenance pages.</x:t>
+          <x:t xml:space="preserve">System should allow user to view the approval history of a document.</x:t>
         </x:is>
       </x:c>
       <x:c r="C101" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.97, REQ_DS43.98, REQ_DS43.99</x:t>
+          <x:t xml:space="preserve">REQ_DS43.100, REQ_DS43.101</x:t>
         </x:is>
       </x:c>
       <x:c r="D101" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.68, 4.4.1.8.69</x:t>
+          <x:t xml:space="preserve">4.4.1.8.70</x:t>
         </x:is>
       </x:c>
       <x:c r="E101" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.68.1, REQ_IO_A8.68.4, REQ_IO_A8.68.5, REQ_IO_A8.68.6, REQ_IO_A8.68.7</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.70.2</x:t>
         </x:is>
       </x:c>
       <x:c r="F101" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-APR-012, SYS-APR-013</x:t>
+          <x:t xml:space="preserve">SYS-APR-001, SYS-APR-002, SYS-APR-008, SYS-APR-011, SYS-APR-012, SYS-APR-013</x:t>
         </x:is>
       </x:c>
       <x:c r="G101" s="2" t="inlineStr">
@@ -21267,27 +21626,27 @@
     <x:row r="102">
       <x:c r="A102" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.29.9</x:t>
+          <x:t xml:space="preserve">REQ_F4118.29.8</x:t>
         </x:is>
       </x:c>
       <x:c r="B102" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should provide a trilingual approval inbox with approval history.</x:t>
+          <x:t xml:space="preserve">System should provide trilingual approval flow and delegation maintenance pages.</x:t>
         </x:is>
       </x:c>
       <x:c r="C102" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.100, REQ_DS43.101</x:t>
+          <x:t xml:space="preserve">REQ_DS43.97, REQ_DS43.98, REQ_DS43.99</x:t>
         </x:is>
       </x:c>
       <x:c r="D102" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.70</x:t>
+          <x:t xml:space="preserve">4.4.1.8.68, 4.4.1.8.69</x:t>
         </x:is>
       </x:c>
       <x:c r="E102" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.70.1, REQ_IO_A8.70.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.68.1, REQ_IO_A8.68.4, REQ_IO_A8.68.5, REQ_IO_A8.68.6, REQ_IO_A8.68.7</x:t>
         </x:is>
       </x:c>
       <x:c r="F102" s="2" t="inlineStr">
@@ -21304,54 +21663,54 @@
     <x:row r="103">
       <x:c r="A103" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.30.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.29.9</x:t>
         </x:is>
       </x:c>
       <x:c r="B103" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should load demo companies, branches, departments and roles for the Development environment.</x:t>
+          <x:t xml:space="preserve">System should provide a trilingual approval inbox with approval history.</x:t>
         </x:is>
       </x:c>
       <x:c r="C103" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.20, REQ_DS43.22, REQ_DS43.89, REQ_DS43.90, REQ_DS43.91</x:t>
+          <x:t xml:space="preserve">REQ_DS43.100, REQ_DS43.101</x:t>
         </x:is>
       </x:c>
       <x:c r="D103" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">4.4.1.8.70</x:t>
         </x:is>
       </x:c>
       <x:c r="E103" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.70.1, REQ_IO_A8.70.2</x:t>
         </x:is>
       </x:c>
       <x:c r="F103" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-SEED-001, SYS-SEED-002, SYS-SEED-003, SYS-SEED-006</x:t>
+          <x:t xml:space="preserve">SYS-APR-012, SYS-APR-013</x:t>
         </x:is>
       </x:c>
       <x:c r="G103" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="104">
       <x:c r="A104" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.30.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.30.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B104" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should create the test accounts of the SeedUsers setting with hashed passwords and company assignments.</x:t>
+          <x:t xml:space="preserve">System should load demo companies, branches, departments and roles for the Development environment.</x:t>
         </x:is>
       </x:c>
       <x:c r="C104" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.82, REQ_DS43.92, REQ_DS43.93</x:t>
+          <x:t xml:space="preserve">REQ_DS43.20, REQ_DS43.22, REQ_DS43.89, REQ_DS43.90, REQ_DS43.91</x:t>
         </x:is>
       </x:c>
       <x:c r="D104" s="2" t="inlineStr">
@@ -21366,7 +21725,7 @@
       </x:c>
       <x:c r="F104" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-SEED-001, SYS-SEED-005</x:t>
+          <x:t xml:space="preserve">SYS-SEED-001, SYS-SEED-002, SYS-SEED-003, SYS-SEED-006</x:t>
         </x:is>
       </x:c>
       <x:c r="G104" s="2" t="inlineStr">
@@ -21378,17 +21737,17 @@
     <x:row r="105">
       <x:c r="A105" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.30.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.30.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B105" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow the seed to run repeatedly without duplicating or overwriting data.</x:t>
+          <x:t xml:space="preserve">System should create the test accounts of the SeedUsers setting with hashed passwords and company assignments.</x:t>
         </x:is>
       </x:c>
       <x:c r="C105" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.20, REQ_DS43.82, REQ_DS43.91</x:t>
+          <x:t xml:space="preserve">REQ_DS43.82, REQ_DS43.92, REQ_DS43.93</x:t>
         </x:is>
       </x:c>
       <x:c r="D105" s="2" t="inlineStr">
@@ -21403,7 +21762,7 @@
       </x:c>
       <x:c r="F105" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-SEED-001, SYS-SEED-003, SYS-SEED-004</x:t>
+          <x:t xml:space="preserve">SYS-SEED-001, SYS-SEED-005</x:t>
         </x:is>
       </x:c>
       <x:c r="G105" s="2" t="inlineStr">
@@ -21415,32 +21774,32 @@
     <x:row r="106">
       <x:c r="A106" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.31.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.30.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B106" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should ask for confirmation in a shared trilingual confirmation box before dangerous actions.</x:t>
+          <x:t xml:space="preserve">System should allow the seed to run repeatedly without duplicating or overwriting data.</x:t>
         </x:is>
       </x:c>
       <x:c r="C106" s="2" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">REQ_DS43.20, REQ_DS43.82, REQ_DS43.91</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D106" s="2" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
-      <x:c r="D106" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">4.4.1.8.71</x:t>
-        </x:is>
-      </x:c>
       <x:c r="E106" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.71.1</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="F106" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-UI-001, SYS-UI-002, SYS-UI-003</x:t>
+          <x:t xml:space="preserve">SYS-SEED-001, SYS-SEED-003, SYS-SEED-004</x:t>
         </x:is>
       </x:c>
       <x:c r="G106" s="2" t="inlineStr">
@@ -21452,12 +21811,12 @@
     <x:row r="107">
       <x:c r="A107" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.31.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.31.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B107" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should show results that need the user's attention in a shared prompt box, and short success messages as toasts.</x:t>
+          <x:t xml:space="preserve">System should ask for confirmation in a shared trilingual confirmation box before dangerous actions.</x:t>
         </x:is>
       </x:c>
       <x:c r="C107" s="2" t="inlineStr">
@@ -21477,7 +21836,7 @@
       </x:c>
       <x:c r="F107" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-UI-001</x:t>
+          <x:t xml:space="preserve">SYS-UI-001, SYS-UI-002, SYS-UI-003</x:t>
         </x:is>
       </x:c>
       <x:c r="G107" s="2" t="inlineStr">
@@ -21489,12 +21848,12 @@
     <x:row r="108">
       <x:c r="A108" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.31.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.31.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B108" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should provide a shared selection window for choosing master data with search and server-side paging.</x:t>
+          <x:t xml:space="preserve">System should show results that need the user's attention in a shared prompt box, and short success messages as toasts.</x:t>
         </x:is>
       </x:c>
       <x:c r="C108" s="2" t="inlineStr">
@@ -21504,12 +21863,12 @@
       </x:c>
       <x:c r="D108" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.72</x:t>
+          <x:t xml:space="preserve">4.4.1.8.71</x:t>
         </x:is>
       </x:c>
       <x:c r="E108" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.72.1, REQ_IO_A8.72.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.71.1</x:t>
         </x:is>
       </x:c>
       <x:c r="F108" s="2" t="inlineStr">
@@ -21526,12 +21885,12 @@
     <x:row r="109">
       <x:c r="A109" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.31.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.31.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B109" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should provide a standard list page template reused by every module.</x:t>
+          <x:t xml:space="preserve">System should provide a shared selection window for choosing master data with search and server-side paging.</x:t>
         </x:is>
       </x:c>
       <x:c r="C109" s="2" t="inlineStr">
@@ -21541,17 +21900,17 @@
       </x:c>
       <x:c r="D109" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.73</x:t>
+          <x:t xml:space="preserve">4.4.1.8.72</x:t>
         </x:is>
       </x:c>
       <x:c r="E109" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.73.2</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.72.1, REQ_IO_A8.72.2</x:t>
         </x:is>
       </x:c>
       <x:c r="F109" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-UI-001, SYS-UI-002</x:t>
+          <x:t xml:space="preserve">SYS-UI-001</x:t>
         </x:is>
       </x:c>
       <x:c r="G109" s="2" t="inlineStr">
@@ -21563,12 +21922,12 @@
     <x:row r="110">
       <x:c r="A110" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.31.5</x:t>
+          <x:t xml:space="preserve">REQ_F4118.31.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B110" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should provide a standard document page template with status, previous / next navigation and unsaved-change protection.</x:t>
+          <x:t xml:space="preserve">System should provide a standard list page template reused by every module.</x:t>
         </x:is>
       </x:c>
       <x:c r="C110" s="2" t="inlineStr">
@@ -21578,17 +21937,17 @@
       </x:c>
       <x:c r="D110" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.74</x:t>
+          <x:t xml:space="preserve">4.4.1.8.73</x:t>
         </x:is>
       </x:c>
       <x:c r="E110" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.74.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.73.2</x:t>
         </x:is>
       </x:c>
       <x:c r="F110" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-UI-001</x:t>
+          <x:t xml:space="preserve">SYS-UI-001, SYS-UI-002</x:t>
         </x:is>
       </x:c>
       <x:c r="G110" s="2" t="inlineStr">
@@ -21600,12 +21959,12 @@
     <x:row r="111">
       <x:c r="A111" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.31.6</x:t>
+          <x:t xml:space="preserve">REQ_F4118.31.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B111" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should provide a date range filter with quick ranges and a document status tag following the macaron status colours.</x:t>
+          <x:t xml:space="preserve">System should provide a standard document page template with status, previous / next navigation and unsaved-change protection.</x:t>
         </x:is>
       </x:c>
       <x:c r="C111" s="2" t="inlineStr">
@@ -21615,12 +21974,12 @@
       </x:c>
       <x:c r="D111" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.73, 4.4.1.8.74</x:t>
+          <x:t xml:space="preserve">4.4.1.8.74</x:t>
         </x:is>
       </x:c>
       <x:c r="E111" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.73.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.74.1</x:t>
         </x:is>
       </x:c>
       <x:c r="F111" s="2" t="inlineStr">
@@ -21637,49 +21996,49 @@
     <x:row r="112">
       <x:c r="A112" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.32.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.31.6</x:t>
         </x:is>
       </x:c>
       <x:c r="B112" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to view IP whitelist rules.</x:t>
+          <x:t xml:space="preserve">System should provide a date range filter with quick ranges and a document status tag following the macaron status colours.</x:t>
         </x:is>
       </x:c>
       <x:c r="C112" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.102</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="D112" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.75</x:t>
+          <x:t xml:space="preserve">4.4.1.8.73, 4.4.1.8.74</x:t>
         </x:is>
       </x:c>
       <x:c r="E112" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.75.1</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.73.1</x:t>
         </x:is>
       </x:c>
       <x:c r="F112" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-IPW-004, SYS-IPW-009</x:t>
+          <x:t xml:space="preserve">SYS-UI-001</x:t>
         </x:is>
       </x:c>
       <x:c r="G112" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Covered</x:t>
+          <x:t xml:space="preserve">Partial</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="113">
       <x:c r="A113" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.32.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.32.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B113" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow authorized users to create and deactivate IP whitelist rules.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to view IP whitelist rules.</x:t>
         </x:is>
       </x:c>
       <x:c r="C113" s="2" t="inlineStr">
@@ -21694,12 +22053,12 @@
       </x:c>
       <x:c r="E113" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.75.2, REQ_IO_A8.75.3, REQ_IO_A8.75.5, REQ_IO_A8.75.6, REQ_IO_A8.75.7</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.75.1</x:t>
         </x:is>
       </x:c>
       <x:c r="F113" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-PERM-032, SYS-IPW-004, SYS-IPW-005, SYS-IPW-008, SYS-IPW-009</x:t>
+          <x:t xml:space="preserve">SYS-IPW-004, SYS-IPW-009</x:t>
         </x:is>
       </x:c>
       <x:c r="G113" s="2" t="inlineStr">
@@ -21711,12 +22070,12 @@
     <x:row r="114">
       <x:c r="A114" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.32.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.32.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B114" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow single IPv4 or IPv6 addresses and CIDR networks in system, role or user scope.</x:t>
+          <x:t xml:space="preserve">System should allow authorized users to create and deactivate IP whitelist rules.</x:t>
         </x:is>
       </x:c>
       <x:c r="C114" s="2" t="inlineStr">
@@ -21731,12 +22090,12 @@
       </x:c>
       <x:c r="E114" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.75.4</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.75.2, REQ_IO_A8.75.3, REQ_IO_A8.75.5, REQ_IO_A8.75.6, REQ_IO_A8.75.7</x:t>
         </x:is>
       </x:c>
       <x:c r="F114" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-IPW-001, SYS-IPW-002, SYS-IPW-005, SYS-IPW-006</x:t>
+          <x:t xml:space="preserve">SYS-PERM-032, SYS-IPW-004, SYS-IPW-005, SYS-IPW-008, SYS-IPW-009</x:t>
         </x:is>
       </x:c>
       <x:c r="G114" s="2" t="inlineStr">
@@ -21748,12 +22107,12 @@
     <x:row r="115">
       <x:c r="A115" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.32.4</x:t>
+          <x:t xml:space="preserve">REQ_F4118.32.3</x:t>
         </x:is>
       </x:c>
       <x:c r="B115" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should reject disallowed requests and audit each rejection.</x:t>
+          <x:t xml:space="preserve">System should allow single IPv4 or IPv6 addresses and CIDR networks in system, role or user scope.</x:t>
         </x:is>
       </x:c>
       <x:c r="C115" s="2" t="inlineStr">
@@ -21763,54 +22122,54 @@
       </x:c>
       <x:c r="D115" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">4.4.1.8.75</x:t>
         </x:is>
       </x:c>
       <x:c r="E115" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.75.4</x:t>
         </x:is>
       </x:c>
       <x:c r="F115" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-IPW-003, SYS-IPW-006</x:t>
+          <x:t xml:space="preserve">SYS-IPW-001, SYS-IPW-002, SYS-IPW-005, SYS-IPW-006</x:t>
         </x:is>
       </x:c>
       <x:c r="G115" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Partial</x:t>
+          <x:t xml:space="preserve">Covered</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="116">
       <x:c r="A116" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.32.5</x:t>
+          <x:t xml:space="preserve">REQ_F4118.32.4</x:t>
         </x:is>
       </x:c>
       <x:c r="B116" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should allow operators to disable IP filtering through server configuration.</x:t>
+          <x:t xml:space="preserve">System should reject disallowed requests and audit each rejection.</x:t>
         </x:is>
       </x:c>
       <x:c r="C116" s="2" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">REQ_DS43.102</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D116" s="2" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
-      <x:c r="D116" s="2" t="inlineStr">
+      <x:c r="E116" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
-      <x:c r="E116" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
       <x:c r="F116" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-IPW-006</x:t>
+          <x:t xml:space="preserve">SYS-IPW-003, SYS-IPW-006</x:t>
         </x:is>
       </x:c>
       <x:c r="G116" s="2" t="inlineStr">
@@ -21822,12 +22181,12 @@
     <x:row r="117">
       <x:c r="A117" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.32.6</x:t>
+          <x:t xml:space="preserve">REQ_F4118.32.5</x:t>
         </x:is>
       </x:c>
       <x:c r="B117" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should provide a trilingual IP whitelist maintenance page.</x:t>
+          <x:t xml:space="preserve">System should allow operators to disable IP filtering through server configuration.</x:t>
         </x:is>
       </x:c>
       <x:c r="C117" s="2" t="inlineStr">
@@ -21837,17 +22196,17 @@
       </x:c>
       <x:c r="D117" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.75</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="E117" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.75.1, REQ_IO_A8.75.2, REQ_IO_A8.75.3, REQ_IO_A8.75.4, REQ_IO_A8.75.5, REQ_IO_A8.75.6, REQ_IO_A8.75.7</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="F117" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-IPW-007</x:t>
+          <x:t xml:space="preserve">SYS-IPW-006</x:t>
         </x:is>
       </x:c>
       <x:c r="G117" s="2" t="inlineStr">
@@ -21859,32 +22218,32 @@
     <x:row r="118">
       <x:c r="A118" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.33.1</x:t>
+          <x:t xml:space="preserve">REQ_F4118.32.6</x:t>
         </x:is>
       </x:c>
       <x:c r="B118" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable modules to publish notifications to a user.</x:t>
+          <x:t xml:space="preserve">System should provide a trilingual IP whitelist maintenance page.</x:t>
         </x:is>
       </x:c>
       <x:c r="C118" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_DS43.104</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="D118" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">4.4.1.8.75</x:t>
         </x:is>
       </x:c>
       <x:c r="E118" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve"/>
+          <x:t xml:space="preserve">REQ_IO_A8.75.1, REQ_IO_A8.75.2, REQ_IO_A8.75.3, REQ_IO_A8.75.4, REQ_IO_A8.75.5, REQ_IO_A8.75.6, REQ_IO_A8.75.7</x:t>
         </x:is>
       </x:c>
       <x:c r="F118" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-NOTIFY-001, SYS-NOTIFY-002, SYS-NOTIFY-003</x:t>
+          <x:t xml:space="preserve">SYS-IPW-007</x:t>
         </x:is>
       </x:c>
       <x:c r="G118" s="2" t="inlineStr">
@@ -21896,12 +22255,12 @@
     <x:row r="119">
       <x:c r="A119" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.33.2</x:t>
+          <x:t xml:space="preserve">REQ_F4118.33.1</x:t>
         </x:is>
       </x:c>
       <x:c r="B119" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to view notifications.</x:t>
+          <x:t xml:space="preserve">System should enable modules to publish notifications to a user.</x:t>
         </x:is>
       </x:c>
       <x:c r="C119" s="2" t="inlineStr">
@@ -21911,34 +22270,34 @@
       </x:c>
       <x:c r="D119" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">4.4.1.8.76</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="E119" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.76.1, REQ_IO_A8.76.2, REQ_IO_A8.76.3, REQ_IO_A8.76.6</x:t>
+          <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
       <x:c r="F119" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">SYS-NOTIFY-004, SYS-NOTIFY-005, SYS-NOTIFY-006, SYS-NOTIFY-007</x:t>
+          <x:t xml:space="preserve">SYS-NOTIFY-001, SYS-NOTIFY-002, SYS-NOTIFY-003</x:t>
         </x:is>
       </x:c>
       <x:c r="G119" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Covered</x:t>
+          <x:t xml:space="preserve">Partial</x:t>
         </x:is>
       </x:c>
     </x:row>
     <x:row r="120">
       <x:c r="A120" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_F4118.33.3</x:t>
+          <x:t xml:space="preserve">REQ_F4118.33.2</x:t>
         </x:is>
       </x:c>
       <x:c r="B120" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">System should enable user to mark notifications as read.</x:t>
+          <x:t xml:space="preserve">System should enable user to view notifications.</x:t>
         </x:is>
       </x:c>
       <x:c r="C120" s="2" t="inlineStr">
@@ -21953,7 +22312,7 @@
       </x:c>
       <x:c r="E120" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">REQ_IO_A8.76.4, REQ_IO_A8.76.5</x:t>
+          <x:t xml:space="preserve">REQ_IO_A8.76.1, REQ_IO_A8.76.2, REQ_IO_A8.76.3, REQ_IO_A8.76.6</x:t>
         </x:is>
       </x:c>
       <x:c r="F120" s="2" t="inlineStr">
@@ -21970,35 +22329,72 @@
     <x:row r="121">
       <x:c r="A121" s="2" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">REQ_F4118.33.3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B121" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should enable user to mark notifications as read.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C121" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.104</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D121" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.76</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E121" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.76.4, REQ_IO_A8.76.5</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F121" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">SYS-NOTIFY-004, SYS-NOTIFY-005, SYS-NOTIFY-006, SYS-NOTIFY-007</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G121" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Covered</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="122">
+      <x:c r="A122" s="2" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">REQ_F4118.34.1</x:t>
         </x:is>
       </x:c>
-      <x:c r="B121" s="2" t="inlineStr">
+      <x:c r="B122" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">System should allow authorized users to view the master data portal.</x:t>
         </x:is>
       </x:c>
-      <x:c r="C121" s="2" t="inlineStr">
+      <x:c r="C122" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
-      <x:c r="D121" s="2" t="inlineStr">
+      <x:c r="D122" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
-      <x:c r="E121" s="2" t="inlineStr">
+      <x:c r="E122" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
-      <x:c r="F121" s="2" t="inlineStr">
+      <x:c r="F122" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve"/>
         </x:is>
       </x:c>
-      <x:c r="G121" s="2" t="inlineStr">
+      <x:c r="G122" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">Not covered</x:t>
         </x:is>
@@ -27263,7 +27659,7 @@
       </x:c>
       <x:c r="F164" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">未開始</x:t>
+          <x:t xml:space="preserve">完成</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -27295,7 +27691,7 @@
       </x:c>
       <x:c r="F165" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">未開始</x:t>
+          <x:t xml:space="preserve">完成</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -27327,7 +27723,7 @@
       </x:c>
       <x:c r="F166" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">未開始</x:t>
+          <x:t xml:space="preserve">完成</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -32383,7 +32779,7 @@
       </x:c>
       <x:c r="F324" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">未開始</x:t>
+          <x:t xml:space="preserve">完成</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -32415,7 +32811,7 @@
       </x:c>
       <x:c r="F325" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">未開始</x:t>
+          <x:t xml:space="preserve">完成</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -32447,7 +32843,7 @@
       </x:c>
       <x:c r="F326" s="2" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">未開始</x:t>
+          <x:t xml:space="preserve">完成</x:t>
         </x:is>
       </x:c>
     </x:row>

--- a/docs/99-output/MyERP_Requirements.xlsx
+++ b/docs/99-output/MyERP_Requirements.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="1" r:id="Re203fd047cdb4f52"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Non-Functional" sheetId="2" r:id="R77eb2bd63ee143a1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Structure" sheetId="3" r:id="Ra616986e7388439c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interface" sheetId="4" r:id="Rf0060c6df84a47ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traceability Matrix" sheetId="5" r:id="Rab28e20f391544b1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BlueWhale Parity" sheetId="6" r:id="R42588197280c4018"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timeline" sheetId="7" r:id="R98fcf46b1b744484"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Human Resources" sheetId="8" r:id="Rfd385159b10740d1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="9" r:id="Rce3f74d82bb54c50"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="1" r:id="R6eb35489d94843ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Non-Functional" sheetId="2" r:id="R063bec3fe220488f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Structure" sheetId="3" r:id="R14cd5036934849d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interface" sheetId="4" r:id="Re085d3a521de45ea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traceability Matrix" sheetId="5" r:id="R9af716dafb32427a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BlueWhale Parity" sheetId="6" r:id="R999523d0be2a4c9b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Timeline" sheetId="7" r:id="Re42952122eaa4e60"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Human Resources" sheetId="8" r:id="R9d5c2224e67b43f1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="9" r:id="R72d35c93ae484d54"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -5405,6 +5405,384 @@
         </x:is>
       </x:c>
     </x:row>
+    <x:row r="128">
+      <x:c r="A128" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.35.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B128" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C128" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Currency</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D128" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E128" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should enable user to view currencies.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F128" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G128" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">具 MD.CURRENCY.VIEW 可按目前公司以代碼或名稱搜尋、按代碼／名稱排序及分頁幣別（含停用），顯示符號、金額小數位與本位幣標記；排除軟刪除及別公司資料；未選公司回 403。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H128" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:147</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="129">
+      <x:c r="A129" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.35.2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B129" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C129" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Currency</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D129" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E129" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should enable user to create currencies.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F129" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G129" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">具 MD.CURRENCY.CREATE 可建立 ISO 4217 三個英文字母代碼（轉大寫，公司內永久唯一含已刪除，409 MD.CURRENCY.DUPLICATE_CODE；格式不符 400 code）、非空白名稱（200）、可空符號（10，400 symbol）、金額小數位 0–4（400 decimalPlaces），可同時設為本位幣。不同公司可用相同代碼。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H129" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:148</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="130">
+      <x:c r="A130" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.35.3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B130" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C130" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Currency</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D130" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E130" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should enable user to edit currencies and set the base currency.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F130" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G130" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">具 MD.CURRENCY.EDIT 可帶版本修改名稱、符號、小數位、啟用狀態與本位幣；代碼不可變。每間公司最多一個本位幣，設定新本位幣時自動取消舊的；公司已有匯率後不可更換本位幣（409 MD.CURRENCY.BASE_LOCKED）；不可直接取消本位幣（422 MD.CURRENCY.BASE_REQUIRED），本位幣必須啟用（422 MD.CURRENCY.BASE_INACTIVE）。舊版本 409，別公司或已刪除 404 MD.CURRENCY.NOT_FOUND。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H130" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:149</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="131">
+      <x:c r="A131" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.35.4</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B131" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C131" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Currency</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D131" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E131" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should enable user to delete currencies.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F131" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G131" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">具 MD.CURRENCY.DELETE 可帶版本軟刪除幣別，代碼仍保留；本位幣 409 MD.CURRENCY.IS_BASE；有未刪除匯率 409 MD.CURRENCY.IN_USE。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H131" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:150</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="132">
+      <x:c r="A132" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.36.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B132" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C132" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Exchange Rate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D132" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E132" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should enable user to view exchange rates of a currency.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F132" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G132" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">MD.CURRENCY.VIEW 可查看某幣別的匯率（1 外幣 = 匯率 本位幣），預設按生效日新到舊、可改舊到新，可篩選某日適用的匯率，分頁；幣別不屬目前公司 404 MD.CURRENCY.NOT_FOUND。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H132" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:151</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="133">
+      <x:c r="A133" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.36.2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B133" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C133" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Exchange Rate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D133" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E133" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should enable user to create exchange rates.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F133" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G133" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">MD.CURRENCY.EDIT 可為啟用的外幣新增匯率：生效日、可空到期日（含當日；早於生效日 400 effectiveTo）、匯率大於 0、最多 11 位整數及 8 位小數（400 rate）。同幣別未刪除的期間不可重疊（409 MD.EXCHANGE_RATE.OVERLAP）；本位幣 422 MD.EXCHANGE_RATE.BASE_CURRENCY；公司未設本位幣 422 MD.EXCHANGE_RATE.NO_BASE_CURRENCY；停用幣別 422 MD.EXCHANGE_RATE.CURRENCY_INACTIVE。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H133" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:152</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="134">
+      <x:c r="A134" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.36.3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B134" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C134" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Exchange Rate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D134" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E134" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should enable user to edit exchange rates.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F134" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G134" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">MD.CURRENCY.EDIT 可帶版本修改生效日、到期日與匯率，驗證與重疊規則同新增（排除自己）；幣別不可修改；匯率不屬該幣別 404 MD.EXCHANGE_RATE.NOT_FOUND；舊版本 409。已存單據保存自己的成交匯率，不受影響。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H134" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:153</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="135">
+      <x:c r="A135" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.36.4</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B135" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C135" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Exchange Rate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D135" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E135" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should enable user to delete exchange rates.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F135" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G135" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">MD.CURRENCY.EDIT 可帶版本軟刪除匯率，刪除後該期間可重新設定；不屬該幣別 404。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H135" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:154</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="136">
+      <x:c r="A136" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.36.5</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B136" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Settings</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C136" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Exchange Rate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D136" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E136" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">System should enable other modules and users to look up the exchange rate of a business date.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F136" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G136" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ICurrencyLookup.GetRateAsync 與 GET /api/v1/md/exchange-rates/lookup?currencyCode=&amp;date=（MD.CURRENCY.VIEW）回傳涵蓋該業務日期的匯率，代碼不分大小寫，本位幣回 1；停用幣別仍可查詢；幣別不存在 404 MD.CURRENCY.NOT_FOUND；沒有本位幣或沒有匯率 422 MD.EXCHANGE_RATE.NO_BASE_CURRENCY／MD.EXCHANGE_RATE.NOT_FOUND。GetPrecisionAsync 以主檔小數位提供 Money.Round 的捨入設定。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H136" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">docs/02-modules/MD/requirements.md:155</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
   </x:sheetData>
 </x:worksheet>
 </file>
@@ -7408,6 +7786,70 @@
         </x:is>
       </x:c>
     </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.117</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B34" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C34" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">md_currency</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D34" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">This table stores currencies and the base currency of a company.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E34" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F34" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.35.1, REQ_F4118.35.2, REQ_F4118.35.3, REQ_F4118.35.4</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_DS43.118</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B35" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C35" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">md_exchange_rate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D35" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">This table stores exchange rates of foreign currencies against the base currency.</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E35" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F35" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_F4118.36.1, REQ_F4118.36.2, REQ_F4118.36.3, REQ_F4118.36.4, REQ_F4118.36.5</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
   </x:sheetData>
 </x:worksheet>
 </file>
@@ -7418,7 +7860,7 @@
     <x:col min="1" max="1" width="17" customWidth="1"/>
     <x:col min="2" max="2" width="15" customWidth="1"/>
     <x:col min="3" max="3" width="60" customWidth="1"/>
-    <x:col min="4" max="4" width="42" customWidth="1"/>
+    <x:col min="4" max="4" width="49" customWidth="1"/>
     <x:col min="5" max="5" width="60" customWidth="1"/>
     <x:col min="6" max="6" width="23" customWidth="1"/>
     <x:col min="7" max="7" width="60" customWidth="1"/>
@@ -18823,6 +19265,804 @@
         </x:is>
       </x:c>
       <x:c r="K200" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="201">
+      <x:c r="A201" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.79.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B201" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.79</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C201" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Currency View Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D201" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Search (Input)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E201" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">搜尋代碼或名稱。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F201" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">找到目前公司幣別。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G201" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Text</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H201" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">任意文字</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I201" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.79.2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J201" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K201" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="202">
+      <x:c r="A202" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.79.2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B202" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.79</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C202" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Currency View Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D202" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Currency List (Table)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E202" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">代碼（本位幣加標籤）、名稱、符號、金額小數位、狀態；代碼與名稱可排序，伺服器分頁；外幣列有匯率／編輯／刪除，本位幣列只有編輯。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F202" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">查看幣別與本位幣。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G202" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Table</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H202" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">每頁 10／20／50／100／200</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I202" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.80.1, REQ_IO_A8.81.1, REQ_IO_A8.82.1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J202" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K202" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="203">
+      <x:c r="A203" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.79.3</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B203" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.4.1.8.79</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C203" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Currency View Interface</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D203" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Delete (Button)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E203" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">二次確認後帶版本軟刪除；有匯率時顯示錯誤。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F203" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">移除未使用的外幣。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G203" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Button</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H203" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">DELETE 權限，本位幣不顯示</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I203" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">REQ_IO_A8.79.2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J203" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="K203" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Developer</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="204">
+      <x:c r="A204" s="2" t="inlineStr"